--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -131,7 +131,30 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0">
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+填写 dropGroup.xlsx配置表中 trunkID 字中的值
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F125" authorId="0">
       <text>
         <r>
           <rPr>
@@ -153,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="0">
+    <comment ref="F167" authorId="0">
       <text>
         <r>
           <rPr>
@@ -175,56 +198,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="F37" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-不可见的常规道具</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F38" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-不可见的常规道具</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="242">
   <si>
     <t>道具ID</t>
   </si>
@@ -262,6 +241,9 @@
     <t>使用道具后获得道具</t>
   </si>
   <si>
+    <t>掉落ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -304,6 +286,9 @@
     <t>getItem</t>
   </si>
   <si>
+    <t>dropId</t>
+  </si>
+  <si>
     <t>金币礼包</t>
   </si>
   <si>
@@ -325,6 +310,39 @@
     <t>1980000_10000</t>
   </si>
   <si>
+    <t>赌场材料随机包(普通)</t>
+  </si>
+  <si>
+    <t>itemicon_1010101.png</t>
+  </si>
+  <si>
+    <t>使用后随机获得N个赌赌场材料道具</t>
+  </si>
+  <si>
+    <t>赌场材料随机包(豪华)</t>
+  </si>
+  <si>
+    <t>赌场材料随机包(尊贵)</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(一星)</t>
+  </si>
+  <si>
+    <t>使用后随机获得N个拼图碎片道具</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(二星)</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(三星)</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(四星)</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(五星)</t>
+  </si>
+  <si>
     <t>白金卡</t>
   </si>
   <si>
@@ -352,28 +370,325 @@
     <t>测试道具6</t>
   </si>
   <si>
-    <t>图鉴1</t>
-  </si>
-  <si>
-    <t>图鉴2</t>
-  </si>
-  <si>
-    <t>图鉴3</t>
-  </si>
-  <si>
-    <t>图鉴4</t>
-  </si>
-  <si>
-    <t>图鉴5</t>
-  </si>
-  <si>
-    <t>图鉴6</t>
-  </si>
-  <si>
-    <t>图鉴7</t>
-  </si>
-  <si>
-    <t>图鉴8</t>
+    <t>图鉴1-图片</t>
+  </si>
+  <si>
+    <t>一張精美的圖片，由12張碎片組成</t>
+  </si>
+  <si>
+    <t>图鉴2-图片</t>
+  </si>
+  <si>
+    <t>图鉴3-图片</t>
+  </si>
+  <si>
+    <t>图鉴4-图片</t>
+  </si>
+  <si>
+    <t>图鉴5-图片</t>
+  </si>
+  <si>
+    <t>图鉴6-图片</t>
+  </si>
+  <si>
+    <t>图鉴7-图片</t>
+  </si>
+  <si>
+    <t>图鉴8-图片</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片1</t>
+  </si>
+  <si>
+    <t>itemicon_1020001.png</t>
+  </si>
+  <si>
+    <t>用於組成一張精美圖片[圖片名稱]的碎片，在各遊戲中下注有概率獲得</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片2</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片3</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片4</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片5</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片6</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片7</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片8</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片9</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片10</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片11</t>
+  </si>
+  <si>
+    <t>图鉴1-碎片12</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片1</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片2</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片3</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片4</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片5</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片6</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片7</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片8</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片9</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片10</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片11</t>
+  </si>
+  <si>
+    <t>图鉴2-碎片12</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片1</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片2</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片3</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片4</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片5</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片6</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片7</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片8</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片9</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片10</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片11</t>
+  </si>
+  <si>
+    <t>图鉴3-碎片12</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片1</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片2</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片3</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片4</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片5</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片6</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片7</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片8</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片9</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片10</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片11</t>
+  </si>
+  <si>
+    <t>图鉴4-碎片12</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片1</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片2</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片3</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片4</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片5</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片6</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片7</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片8</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片9</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片10</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片11</t>
+  </si>
+  <si>
+    <t>图鉴5-碎片12</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片1</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片2</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片3</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片4</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片5</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片6</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片7</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片8</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片9</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片10</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片11</t>
+  </si>
+  <si>
+    <t>图鉴6-碎片12</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片1</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片2</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片3</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片4</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片5</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片6</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片7</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片8</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片9</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片10</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片11</t>
+  </si>
+  <si>
+    <t>图鉴7-碎片12</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片1</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片2</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片3</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片4</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片5</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片6</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片7</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片8</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片9</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片10</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片11</t>
+  </si>
+  <si>
+    <t>图鉴8-碎片12</t>
   </si>
   <si>
     <t>头像2</t>
@@ -388,6 +703,18 @@
     <t>头像框3</t>
   </si>
   <si>
+    <t>头像框-特权卡专属</t>
+  </si>
+  <si>
+    <t>frame_801.png</t>
+  </si>
+  <si>
+    <t>头像框-首充专属</t>
+  </si>
+  <si>
+    <t>frame_018.png</t>
+  </si>
+  <si>
     <t>国旗2</t>
   </si>
   <si>
@@ -418,6 +745,177 @@
     <t>大厅背景3</t>
   </si>
   <si>
+    <t>祈福卡</t>
+  </si>
+  <si>
+    <t>在搖錢樹活動中祈福使用，可在指定禮包中購買獲得</t>
+  </si>
+  <si>
+    <t>1星扳手</t>
+  </si>
+  <si>
+    <t>wddc_bs_1.png</t>
+  </si>
+  <si>
+    <t>升级机台的必要道具</t>
+  </si>
+  <si>
+    <t>2星扳手</t>
+  </si>
+  <si>
+    <t>wddc_bs_2.png</t>
+  </si>
+  <si>
+    <t>3星扳手</t>
+  </si>
+  <si>
+    <t>wddc_bs_3.png</t>
+  </si>
+  <si>
+    <t>4星扳手</t>
+  </si>
+  <si>
+    <t>wddc_bs_4.png</t>
+  </si>
+  <si>
+    <t>5星扳手</t>
+  </si>
+  <si>
+    <t>wddc_bs_5.png</t>
+  </si>
+  <si>
+    <t>1星筹码</t>
+  </si>
+  <si>
+    <t>wddc_cm_1.png</t>
+  </si>
+  <si>
+    <t>升级牌桌和转盘的必要道具</t>
+  </si>
+  <si>
+    <t>2星筹码</t>
+  </si>
+  <si>
+    <t>wddc_cm_2.png</t>
+  </si>
+  <si>
+    <t>3星筹码</t>
+  </si>
+  <si>
+    <t>wddc_cm_3.png</t>
+  </si>
+  <si>
+    <t>4星筹码</t>
+  </si>
+  <si>
+    <t>wddc_cm_4.png</t>
+  </si>
+  <si>
+    <t>5星筹码</t>
+  </si>
+  <si>
+    <t>wddc_cm_5.png</t>
+  </si>
+  <si>
+    <t>1星螺母</t>
+  </si>
+  <si>
+    <t>wddc_lsd_1.png</t>
+  </si>
+  <si>
+    <t>升级提款机的必要道具</t>
+  </si>
+  <si>
+    <t>2星螺母</t>
+  </si>
+  <si>
+    <t>wddc_lsd_2.png</t>
+  </si>
+  <si>
+    <t>3星螺母</t>
+  </si>
+  <si>
+    <t>wddc_lsd_3.png</t>
+  </si>
+  <si>
+    <t>4星螺母</t>
+  </si>
+  <si>
+    <t>wddc_lsd_4.png</t>
+  </si>
+  <si>
+    <t>5星螺母</t>
+  </si>
+  <si>
+    <t>wddc_lsd_5.png</t>
+  </si>
+  <si>
+    <t>1星木材</t>
+  </si>
+  <si>
+    <t>wddc_mt_1.png</t>
+  </si>
+  <si>
+    <t>升级休息区的必要道具</t>
+  </si>
+  <si>
+    <t>2星木材</t>
+  </si>
+  <si>
+    <t>wddc_mt_2.png</t>
+  </si>
+  <si>
+    <t>3星木材</t>
+  </si>
+  <si>
+    <t>wddc_mt_3.png</t>
+  </si>
+  <si>
+    <t>4星木材</t>
+  </si>
+  <si>
+    <t>wddc_mt_4.png</t>
+  </si>
+  <si>
+    <t>5星木材</t>
+  </si>
+  <si>
+    <t>wddc_mt_5.png</t>
+  </si>
+  <si>
+    <t>1星酒瓶</t>
+  </si>
+  <si>
+    <t>wddc_pz_1.png</t>
+  </si>
+  <si>
+    <t>升级酒水区的必要道具</t>
+  </si>
+  <si>
+    <t>2星酒瓶</t>
+  </si>
+  <si>
+    <t>wddc_pz_2.png</t>
+  </si>
+  <si>
+    <t>3星酒瓶</t>
+  </si>
+  <si>
+    <t>wddc_pz_3.png</t>
+  </si>
+  <si>
+    <t>4星酒瓶</t>
+  </si>
+  <si>
+    <t>wddc_pz_4.png</t>
+  </si>
+  <si>
+    <t>5星酒瓶</t>
+  </si>
+  <si>
+    <t>wddc_pz_5.png</t>
+  </si>
+  <si>
     <t>金币</t>
   </si>
   <si>
@@ -431,15 +929,6 @@
   </si>
   <si>
     <t>在私密房间内下注时需要用的货币，同时是使用部分功能需要消耗的特殊货币</t>
-  </si>
-  <si>
-    <t>图鉴礼包</t>
-  </si>
-  <si>
-    <t>不可见道具</t>
-  </si>
-  <si>
-    <t>图鉴碎片</t>
   </si>
 </sst>
 </file>
@@ -452,10 +941,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -612,12 +1107,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -632,6 +1127,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.15"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -639,12 +1140,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,16 +1495,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1018,123 +1510,129 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1143,16 +1641,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
@@ -1165,9 +1669,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1695,11 +2196,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
-    <col min="3" max="4" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="17.05" customWidth="1"/>
     <col min="5" max="5" width="5.5" customWidth="1"/>
     <col min="6" max="6" width="10.875" customWidth="1"/>
     <col min="7" max="7" width="8.875" customWidth="1"/>
@@ -1715,25 +2217,25 @@
     <col min="20" max="20" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="I1" t="s">
@@ -1748,127 +2250,136 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="O1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="3" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>12</v>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="O2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="P2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="H3" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="N3" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="P3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
     </row>
     <row r="5" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A5">
-        <f>1000000+E5*10000+B5</f>
+        <f t="shared" ref="A5:A14" si="0">1000000+E5*10000+B5</f>
         <v>1010101</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>101</v>
       </c>
       <c r="C5">
         <v>1010101</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" ref="H5:H16" si="0">"itemicon_"&amp;A5&amp;".png"</f>
+        <f>"itemicon_"&amp;A5&amp;".png"</f>
         <v>itemicon_1010101.png</v>
       </c>
       <c r="I5">
-        <f>2000000+E5*10000+B5</f>
+        <f t="shared" ref="I5:I14" si="1">2000000+E5*10000+B5</f>
         <v>2010101</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1876,43 +2387,43 @@
       <c r="N5">
         <v>999</v>
       </c>
-      <c r="O5" s="12" t="s">
-        <v>29</v>
+      <c r="O5" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A6">
-        <f t="shared" ref="A6:A17" si="1">1000000+E6*10000+B6</f>
+        <f t="shared" si="0"/>
         <v>1010201</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>201</v>
       </c>
       <c r="C6">
         <v>1010201</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" si="0"/>
+        <f>"itemicon_"&amp;A6&amp;".png"</f>
         <v>itemicon_1010201.png</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I16" si="2">2000000+E6*10000+B6</f>
+        <f t="shared" si="1"/>
         <v>2010201</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -1920,83 +2431,85 @@
       <c r="N6">
         <v>999</v>
       </c>
-      <c r="O6" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" ht="21" customHeight="1" spans="1:14">
-      <c r="A7">
+      <c r="O6" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>1010301</v>
+      </c>
+      <c r="B7" s="1">
+        <v>301</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" ref="C7:C14" si="2">1000000+E7*100000+B7</f>
+        <v>1100301</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="1">
         <f t="shared" si="1"/>
-        <v>1020001</v>
-      </c>
-      <c r="B7" s="6">
-        <f>COUNTIF($F$1:F7,F7)</f>
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1020001</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="str">
+        <v>2010301</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>999</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="1">
+        <v>100003</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>itemicon_1020001.png</v>
-      </c>
-      <c r="I7">
+        <v>1010302</v>
+      </c>
+      <c r="B8" s="1">
+        <v>302</v>
+      </c>
+      <c r="C8" s="1">
         <f t="shared" si="2"/>
-        <v>2020001</v>
-      </c>
-      <c r="J7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="21" customHeight="1" spans="1:14">
-      <c r="A8" s="1">
+        <v>1100302</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="1">
+        <v>4</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="1">
         <f t="shared" si="1"/>
-        <v>1020002</v>
-      </c>
-      <c r="B8" s="1">
-        <f>COUNTIF($F$1:F8,F8)</f>
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1020002</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2</v>
-      </c>
-      <c r="H8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>itemicon_1020002.png</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="2"/>
-        <v>2020002</v>
+        <v>2010302</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>37</v>
@@ -2007,38 +2520,41 @@
       <c r="N8" s="1">
         <v>999</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="O8" s="9"/>
+      <c r="P8" s="1">
+        <v>100004</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>1010303</v>
+      </c>
+      <c r="B9" s="1">
+        <v>303</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="2"/>
+        <v>1100303</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="1">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="1">
         <f t="shared" si="1"/>
-        <v>1020003</v>
-      </c>
-      <c r="B9" s="1">
-        <f>COUNTIF($F$1:F9,F9)</f>
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1020003</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="1">
-        <v>3</v>
-      </c>
-      <c r="H9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>itemicon_1020003.png</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="2"/>
-        <v>2020003</v>
+        <v>2010303</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>37</v>
@@ -2049,41 +2565,44 @@
       <c r="N9" s="1">
         <v>999</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="O9" s="9"/>
+      <c r="P9" s="1">
+        <v>100005</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>1010311</v>
+      </c>
+      <c r="B10" s="1">
+        <v>311</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="2"/>
+        <v>1100311</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="1">
         <f t="shared" si="1"/>
-        <v>1020004</v>
-      </c>
-      <c r="B10" s="1">
-        <f>COUNTIF($F$1:F10,F10)</f>
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1020004</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4</v>
-      </c>
-      <c r="H10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>itemicon_1020004.png</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="2"/>
-        <v>2020004</v>
+        <v>2010311</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -2091,41 +2610,44 @@
       <c r="N10" s="1">
         <v>999</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="O10" s="9"/>
+      <c r="P10" s="1">
+        <v>100006</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>1010312</v>
+      </c>
+      <c r="B11" s="1">
+        <v>312</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="2"/>
+        <v>1100312</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="1">
         <f t="shared" si="1"/>
-        <v>1020005</v>
-      </c>
-      <c r="B11" s="1">
-        <f>COUNTIF($F$1:F11,F11)</f>
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1020005</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="1">
-        <v>2</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="1">
-        <v>5</v>
-      </c>
-      <c r="H11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>itemicon_1020005.png</v>
-      </c>
-      <c r="I11" s="1">
-        <f t="shared" si="2"/>
-        <v>2020005</v>
+        <v>2010312</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -2133,41 +2655,44 @@
       <c r="N11" s="1">
         <v>999</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="O11" s="9"/>
+      <c r="P11" s="1">
+        <v>100007</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>1010313</v>
+      </c>
+      <c r="B12" s="1">
+        <v>313</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="2"/>
+        <v>1100313</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="1">
         <f t="shared" si="1"/>
-        <v>1020006</v>
-      </c>
-      <c r="B12" s="1">
-        <f>COUNTIF($F$1:F12,F12)</f>
-        <v>6</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1020006</v>
-      </c>
-      <c r="D12" s="1" t="s">
+        <v>2010313</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E12" s="1">
-        <v>2</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="1">
-        <v>6</v>
-      </c>
-      <c r="H12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>itemicon_1020006.png</v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="2"/>
-        <v>2020006</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -2175,983 +2700,989 @@
       <c r="N12" s="1">
         <v>999</v>
       </c>
-    </row>
-    <row r="13" ht="23" customHeight="1" spans="1:14">
-      <c r="A13">
-        <f>1000000+E13*10000+B13</f>
-        <v>1020007</v>
-      </c>
-      <c r="B13" s="6">
-        <f>COUNTIF($F$1:F13,F13)</f>
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <f>1000000+E13*100000+B13</f>
-        <v>1200007</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" t="str">
-        <f t="shared" ref="H13:H34" si="3">"itemicon_"&amp;A13&amp;".png"</f>
-        <v>itemicon_1020007.png</v>
-      </c>
-      <c r="I13">
-        <f t="shared" ref="I13:I34" si="4">2000000+E13*10000+B13</f>
-        <v>2020007</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="M13">
+      <c r="O12" s="9"/>
+      <c r="P12" s="1">
+        <v>100008</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>1010314</v>
+      </c>
+      <c r="B13" s="1">
+        <v>314</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="2"/>
+        <v>1100314</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1">
+        <v>5</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" si="1"/>
+        <v>2010314</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>999</v>
+      </c>
+      <c r="O13" s="9"/>
+      <c r="P13" s="1">
+        <v>100009</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>1010315</v>
+      </c>
+      <c r="B14" s="1">
+        <v>315</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="2"/>
+        <v>1100315</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="1">
+        <v>6</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="1"/>
+        <v>2010315</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>999</v>
+      </c>
+      <c r="O14" s="9"/>
+      <c r="P14" s="1">
+        <v>100010</v>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1" spans="1:14">
+      <c r="A15">
+        <f t="shared" ref="A15:A29" si="3">1000000+E15*10000+B15</f>
+        <v>1020001</v>
+      </c>
+      <c r="B15" s="7">
+        <f>COUNTIF($F$1:F15,F15)</f>
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1020001</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" ref="H15:H28" si="4">"itemicon_"&amp;A15&amp;".png"</f>
+        <v>itemicon_1020001.png</v>
+      </c>
+      <c r="I15">
+        <f t="shared" ref="I15:I29" si="5">2000000+E15*10000+B15</f>
+        <v>2020001</v>
+      </c>
+      <c r="J15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A16" s="2">
+        <f t="shared" si="3"/>
+        <v>1020002</v>
+      </c>
+      <c r="B16" s="2">
+        <f>COUNTIF($F$1:F16,F16)</f>
+        <v>2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1020002</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="2">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020002.png</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="5"/>
+        <v>2020002</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A17" s="2">
+        <f t="shared" si="3"/>
+        <v>1020003</v>
+      </c>
+      <c r="B17" s="2">
+        <f>COUNTIF($F$1:F17,F17)</f>
+        <v>3</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1020003</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="2">
+        <v>3</v>
+      </c>
+      <c r="H17" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020003.png</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="5"/>
+        <v>2020003</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A18" s="2">
+        <f t="shared" si="3"/>
+        <v>1020004</v>
+      </c>
+      <c r="B18" s="2">
+        <f>COUNTIF($F$1:F18,F18)</f>
+        <v>4</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1020004</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="2">
+        <v>4</v>
+      </c>
+      <c r="H18" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020004.png</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="5"/>
+        <v>2020004</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A19" s="2">
+        <f t="shared" si="3"/>
+        <v>1020005</v>
+      </c>
+      <c r="B19" s="2">
+        <f>COUNTIF($F$1:F19,F19)</f>
+        <v>5</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1020005</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="2">
+        <v>5</v>
+      </c>
+      <c r="H19" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020005.png</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="5"/>
+        <v>2020005</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A20" s="2">
+        <f t="shared" si="3"/>
+        <v>1020006</v>
+      </c>
+      <c r="B20" s="2">
+        <f>COUNTIF($F$1:F20,F20)</f>
+        <v>6</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1020006</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="2">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020006.png</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="5"/>
+        <v>2020006</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="21" ht="23" customHeight="1" spans="1:14">
+      <c r="A21">
+        <f t="shared" si="3"/>
+        <v>1020011</v>
+      </c>
+      <c r="B21" s="7">
+        <v>11</v>
+      </c>
+      <c r="C21">
+        <f t="shared" ref="C21:C29" si="6">1000000+E21*100000+B21</f>
+        <v>1200011</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020011.png</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="5"/>
+        <v>2020011</v>
+      </c>
+      <c r="J21" t="s">
+        <v>56</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>10001</v>
       </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="23" customHeight="1" spans="1:14">
-      <c r="A14">
-        <f t="shared" ref="A14:A34" si="5">1000000+E14*10000+B14</f>
-        <v>1020008</v>
-      </c>
-      <c r="B14" s="6">
-        <f>COUNTIF($F$1:F14,F14)</f>
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <f t="shared" ref="C14:C34" si="6">1000000+E14*100000+B14</f>
-        <v>1200008</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="str">
+      <c r="N21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="23" customHeight="1" spans="1:14">
+      <c r="A22">
         <f t="shared" si="3"/>
-        <v>itemicon_1020008.png</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="4"/>
-        <v>2020008</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>10002</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="23" customHeight="1" spans="1:14">
-      <c r="A15">
-        <f t="shared" si="5"/>
-        <v>1020009</v>
-      </c>
-      <c r="B15" s="6">
-        <f>COUNTIF($F$1:F15,F15)</f>
-        <v>9</v>
-      </c>
-      <c r="C15">
-        <f t="shared" si="6"/>
-        <v>1200009</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1020009.png</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="4"/>
-        <v>2020009</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>10003</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="23" customHeight="1" spans="1:14">
-      <c r="A16">
-        <f t="shared" si="5"/>
-        <v>1020010</v>
-      </c>
-      <c r="B16" s="6">
-        <f>COUNTIF($F$1:F16,F16)</f>
-        <v>10</v>
-      </c>
-      <c r="C16">
-        <f t="shared" si="6"/>
-        <v>1200010</v>
-      </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1020010.png</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="4"/>
-        <v>2020010</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>10004</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="23" customHeight="1" spans="1:14">
-      <c r="A17">
-        <f t="shared" si="5"/>
-        <v>1020011</v>
-      </c>
-      <c r="B17" s="6">
-        <f>COUNTIF($F$1:F17,F17)</f>
-        <v>11</v>
-      </c>
-      <c r="C17">
-        <f t="shared" si="6"/>
-        <v>1200011</v>
-      </c>
-      <c r="D17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1020011.png</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="4"/>
-        <v>2020011</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>10005</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="23" customHeight="1" spans="1:14">
-      <c r="A18">
-        <f t="shared" si="5"/>
         <v>1020012</v>
       </c>
-      <c r="B18" s="6">
-        <f>COUNTIF($F$1:F18,F18)</f>
+      <c r="B22" s="7">
         <v>12</v>
       </c>
-      <c r="C18">
+      <c r="C22">
         <f t="shared" si="6"/>
         <v>1200012</v>
       </c>
-      <c r="D18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" t="str">
+      <c r="D22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020012.png</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="5"/>
+        <v>2020012</v>
+      </c>
+      <c r="J22" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>10002</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="23" customHeight="1" spans="1:14">
+      <c r="A23">
         <f t="shared" si="3"/>
-        <v>itemicon_1020012.png</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="4"/>
-        <v>2020012</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>10006</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="23" customHeight="1" spans="1:14">
-      <c r="A19">
-        <f t="shared" si="5"/>
         <v>1020013</v>
       </c>
-      <c r="B19" s="6">
-        <f>COUNTIF($F$1:F19,F19)</f>
+      <c r="B23" s="7">
         <v>13</v>
       </c>
-      <c r="C19">
+      <c r="C23">
         <f t="shared" si="6"/>
         <v>1200013</v>
       </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-      <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" t="str">
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020013.png</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="5"/>
+        <v>2020013</v>
+      </c>
+      <c r="J23" t="s">
+        <v>56</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>10003</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="23" customHeight="1" spans="1:14">
+      <c r="A24">
         <f t="shared" si="3"/>
-        <v>itemicon_1020013.png</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="4"/>
-        <v>2020013</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>10007</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="23" customHeight="1" spans="1:14">
-      <c r="A20">
-        <f t="shared" si="5"/>
         <v>1020014</v>
       </c>
-      <c r="B20" s="6">
-        <f>COUNTIF($F$1:F20,F20)</f>
+      <c r="B24" s="7">
         <v>14</v>
       </c>
-      <c r="C20">
+      <c r="C24">
         <f t="shared" si="6"/>
         <v>1200014</v>
       </c>
-      <c r="D20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20" t="str">
+      <c r="D24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020014.png</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="5"/>
+        <v>2020014</v>
+      </c>
+      <c r="J24" t="s">
+        <v>56</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>10004</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="23" customHeight="1" spans="1:14">
+      <c r="A25">
         <f t="shared" si="3"/>
-        <v>itemicon_1020014.png</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="4"/>
-        <v>2020014</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>10008</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A21">
-        <f t="shared" si="5"/>
-        <v>1021001</v>
-      </c>
-      <c r="B21" s="6">
-        <v>1001</v>
-      </c>
-      <c r="C21">
-        <f t="shared" si="6"/>
-        <v>1201001</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1021001.png</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="4"/>
-        <v>2021001</v>
-      </c>
-      <c r="K21" s="6">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>2</v>
-      </c>
-      <c r="M21"/>
-      <c r="N21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A22">
-        <f t="shared" si="5"/>
-        <v>1021002</v>
-      </c>
-      <c r="B22" s="6">
-        <v>1002</v>
-      </c>
-      <c r="C22">
-        <f t="shared" si="6"/>
-        <v>1201002</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1021002.png</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="4"/>
-        <v>2021002</v>
-      </c>
-      <c r="K22" s="6">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>3</v>
-      </c>
-      <c r="M22"/>
-      <c r="N22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A23">
-        <f t="shared" si="5"/>
-        <v>1021201</v>
-      </c>
-      <c r="B23" s="6">
-        <v>1201</v>
-      </c>
-      <c r="C23">
-        <f t="shared" si="6"/>
-        <v>1201201</v>
-      </c>
-      <c r="D23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1021201.png</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="4"/>
-        <v>2021201</v>
-      </c>
-      <c r="K23" s="6">
-        <v>1</v>
-      </c>
-      <c r="L23">
-        <v>1002</v>
-      </c>
-      <c r="M23"/>
-      <c r="N23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A24">
-        <f t="shared" si="5"/>
-        <v>1021202</v>
-      </c>
-      <c r="B24" s="6">
-        <v>1202</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="6"/>
-        <v>1201202</v>
-      </c>
-      <c r="D24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
-      <c r="F24" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1021202.png</v>
-      </c>
-      <c r="I24">
-        <f t="shared" si="4"/>
-        <v>2021202</v>
-      </c>
-      <c r="K24" s="6">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>1003</v>
-      </c>
-      <c r="M24"/>
-      <c r="N24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A25">
-        <f t="shared" si="5"/>
-        <v>1021401</v>
-      </c>
-      <c r="B25" s="6">
-        <v>1401</v>
+        <v>1020015</v>
+      </c>
+      <c r="B25" s="7">
+        <v>15</v>
       </c>
       <c r="C25">
         <f t="shared" si="6"/>
-        <v>1201401</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>54</v>
+        <v>1200015</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020015.png</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="5"/>
+        <v>2020015</v>
+      </c>
+      <c r="J25" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>10005</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="23" customHeight="1" spans="1:14">
+      <c r="A26">
         <f t="shared" si="3"/>
-        <v>itemicon_1021401.png</v>
-      </c>
-      <c r="I25">
-        <f t="shared" si="4"/>
-        <v>2021401</v>
-      </c>
-      <c r="K25" s="6">
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <v>2002</v>
-      </c>
-      <c r="M25"/>
-      <c r="N25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A26">
-        <f t="shared" si="5"/>
-        <v>1021402</v>
-      </c>
-      <c r="B26" s="6">
-        <v>1402</v>
+        <v>1020016</v>
+      </c>
+      <c r="B26" s="7">
+        <v>16</v>
       </c>
       <c r="C26">
         <f t="shared" si="6"/>
-        <v>1201402</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>55</v>
+        <v>1200016</v>
+      </c>
+      <c r="D26" t="s">
+        <v>61</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020016.png</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="5"/>
+        <v>2020016</v>
+      </c>
+      <c r="J26" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>10006</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="23" customHeight="1" spans="1:14">
+      <c r="A27">
         <f t="shared" si="3"/>
-        <v>itemicon_1021402.png</v>
-      </c>
-      <c r="I26">
-        <f t="shared" si="4"/>
-        <v>2021402</v>
-      </c>
-      <c r="K26" s="6">
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <v>2003</v>
-      </c>
-      <c r="M26"/>
-      <c r="N26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A27">
-        <f t="shared" si="5"/>
-        <v>1021601</v>
-      </c>
-      <c r="B27" s="6">
-        <v>1601</v>
+        <v>1020017</v>
+      </c>
+      <c r="B27" s="7">
+        <v>17</v>
       </c>
       <c r="C27">
         <f t="shared" si="6"/>
-        <v>1201601</v>
-      </c>
-      <c r="D27" s="8" t="s">
+        <v>1200017</v>
+      </c>
+      <c r="D27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1020017.png</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="5"/>
+        <v>2020017</v>
+      </c>
+      <c r="J27" t="s">
         <v>56</v>
       </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="F27" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27" t="str">
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>10007</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="23" customHeight="1" spans="1:14">
+      <c r="A28">
         <f t="shared" si="3"/>
-        <v>itemicon_1021601.png</v>
-      </c>
-      <c r="I27">
-        <f t="shared" si="4"/>
-        <v>2021601</v>
-      </c>
-      <c r="K27" s="6">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>3002</v>
-      </c>
-      <c r="M27"/>
-      <c r="N27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A28">
-        <f t="shared" si="5"/>
-        <v>1021602</v>
-      </c>
-      <c r="B28" s="6">
-        <v>1602</v>
+        <v>1020018</v>
+      </c>
+      <c r="B28" s="7">
+        <v>18</v>
       </c>
       <c r="C28">
         <f t="shared" si="6"/>
-        <v>1201602</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>57</v>
+        <v>1200018</v>
+      </c>
+      <c r="D28" t="s">
+        <v>63</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1021602.png</v>
+        <f t="shared" si="4"/>
+        <v>itemicon_1020018.png</v>
       </c>
       <c r="I28">
-        <f t="shared" si="4"/>
-        <v>2021602</v>
-      </c>
-      <c r="K28" s="6">
-        <v>1</v>
-      </c>
-      <c r="L28">
-        <v>3003</v>
-      </c>
-      <c r="M28"/>
+        <f t="shared" si="5"/>
+        <v>2020018</v>
+      </c>
+      <c r="J28" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>10008</v>
+      </c>
       <c r="N28">
         <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A29">
-        <f t="shared" si="5"/>
-        <v>1021801</v>
-      </c>
-      <c r="B29" s="6">
-        <v>1801</v>
+        <f t="shared" si="3"/>
+        <v>1020101</v>
+      </c>
+      <c r="B29" s="7">
+        <v>101</v>
       </c>
       <c r="C29">
         <f t="shared" si="6"/>
-        <v>1201801</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>58</v>
+        <v>1200101</v>
+      </c>
+      <c r="D29" t="s">
+        <v>64</v>
       </c>
       <c r="E29">
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
-      <c r="H29" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1021801.png</v>
+      <c r="H29" t="s">
+        <v>65</v>
       </c>
       <c r="I29">
-        <f t="shared" si="4"/>
-        <v>2021801</v>
-      </c>
-      <c r="K29" s="6">
-        <v>1</v>
-      </c>
-      <c r="L29">
-        <v>4002</v>
-      </c>
-      <c r="M29"/>
+        <f t="shared" si="5"/>
+        <v>2020101</v>
+      </c>
+      <c r="J29" t="s">
+        <v>66</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
       <c r="N29">
         <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A30">
-        <f t="shared" si="5"/>
-        <v>1021802</v>
-      </c>
-      <c r="B30" s="6">
-        <v>1802</v>
+        <f t="shared" ref="A30:A40" si="7">1000000+E30*10000+B30</f>
+        <v>1020102</v>
+      </c>
+      <c r="B30" s="7">
+        <v>102</v>
       </c>
       <c r="C30">
-        <f t="shared" si="6"/>
-        <v>1201802</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>59</v>
+        <f t="shared" ref="C30:C40" si="8">1000000+E30*100000+B30</f>
+        <v>1200102</v>
+      </c>
+      <c r="D30" t="s">
+        <v>67</v>
       </c>
       <c r="E30">
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
-      <c r="H30" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1021802.png</v>
+      <c r="H30" t="s">
+        <v>65</v>
       </c>
       <c r="I30">
-        <f t="shared" si="4"/>
-        <v>2021802</v>
-      </c>
-      <c r="K30" s="6">
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <v>4003</v>
-      </c>
-      <c r="M30"/>
+        <f t="shared" ref="I30:I61" si="9">2000000+E30*10000+B30</f>
+        <v>2020102</v>
+      </c>
+      <c r="J30" t="s">
+        <v>66</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
       <c r="N30">
         <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A31">
-        <f t="shared" si="5"/>
-        <v>1022001</v>
-      </c>
-      <c r="B31" s="6">
-        <v>2001</v>
+        <f t="shared" si="7"/>
+        <v>1020103</v>
+      </c>
+      <c r="B31" s="7">
+        <v>103</v>
       </c>
       <c r="C31">
-        <f t="shared" si="6"/>
-        <v>1202001</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>60</v>
+        <f t="shared" si="8"/>
+        <v>1200103</v>
+      </c>
+      <c r="D31" t="s">
+        <v>68</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1022001.png</v>
+        <v>2</v>
+      </c>
+      <c r="H31" t="s">
+        <v>65</v>
       </c>
       <c r="I31">
-        <f t="shared" si="4"/>
-        <v>2022001</v>
-      </c>
-      <c r="K31" s="6">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>5002</v>
-      </c>
-      <c r="M31"/>
+        <f t="shared" si="9"/>
+        <v>2020103</v>
+      </c>
+      <c r="J31" t="s">
+        <v>66</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
       <c r="N31">
         <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A32">
-        <f t="shared" si="5"/>
-        <v>1022002</v>
-      </c>
-      <c r="B32" s="6">
-        <v>2002</v>
+        <f t="shared" si="7"/>
+        <v>1020104</v>
+      </c>
+      <c r="B32" s="7">
+        <v>104</v>
       </c>
       <c r="C32">
-        <f t="shared" si="6"/>
-        <v>1202002</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>61</v>
+        <f t="shared" si="8"/>
+        <v>1200104</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1022002.png</v>
+        <v>2</v>
+      </c>
+      <c r="H32" t="s">
+        <v>65</v>
       </c>
       <c r="I32">
-        <f t="shared" si="4"/>
-        <v>2022002</v>
-      </c>
-      <c r="K32" s="6">
-        <v>1</v>
-      </c>
-      <c r="L32">
-        <v>5003</v>
-      </c>
-      <c r="M32"/>
+        <f t="shared" si="9"/>
+        <v>2020104</v>
+      </c>
+      <c r="J32" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
       <c r="N32">
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A33">
-        <f t="shared" si="5"/>
-        <v>1022201</v>
-      </c>
-      <c r="B33" s="6">
-        <v>2201</v>
+        <f t="shared" si="7"/>
+        <v>1020105</v>
+      </c>
+      <c r="B33" s="7">
+        <v>105</v>
       </c>
       <c r="C33">
-        <f t="shared" si="6"/>
-        <v>1202201</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>62</v>
+        <f t="shared" si="8"/>
+        <v>1200105</v>
+      </c>
+      <c r="D33" t="s">
+        <v>70</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1022201.png</v>
+        <v>3</v>
+      </c>
+      <c r="H33" t="s">
+        <v>65</v>
       </c>
       <c r="I33">
-        <f t="shared" si="4"/>
-        <v>2022201</v>
-      </c>
-      <c r="K33" s="6">
-        <v>1</v>
-      </c>
-      <c r="L33">
-        <v>6002</v>
-      </c>
-      <c r="M33"/>
+        <f t="shared" si="9"/>
+        <v>2020105</v>
+      </c>
+      <c r="J33" t="s">
+        <v>66</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
       <c r="N33">
         <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A34">
-        <f t="shared" si="5"/>
-        <v>1022202</v>
-      </c>
-      <c r="B34" s="6">
-        <v>2202</v>
+        <f t="shared" si="7"/>
+        <v>1020106</v>
+      </c>
+      <c r="B34" s="7">
+        <v>106</v>
       </c>
       <c r="C34">
-        <f t="shared" si="6"/>
-        <v>1202202</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>63</v>
+        <f t="shared" si="8"/>
+        <v>1200106</v>
+      </c>
+      <c r="D34" t="s">
+        <v>71</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34" t="str">
-        <f t="shared" si="3"/>
-        <v>itemicon_1022202.png</v>
+        <v>3</v>
+      </c>
+      <c r="H34" t="s">
+        <v>65</v>
       </c>
       <c r="I34">
-        <f t="shared" si="4"/>
-        <v>2022202</v>
-      </c>
-      <c r="K34" s="6">
-        <v>1</v>
-      </c>
-      <c r="L34">
-        <v>6003</v>
-      </c>
-      <c r="M34"/>
+        <f t="shared" si="9"/>
+        <v>2020106</v>
+      </c>
+      <c r="J34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
       <c r="N34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="21" customHeight="1" spans="1:14">
+    <row r="35" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A35">
-        <f>1000000+E35*10000+B35</f>
-        <v>1990000</v>
-      </c>
-      <c r="B35" s="6">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1020107</v>
+      </c>
+      <c r="B35" s="7">
+        <v>107</v>
       </c>
       <c r="C35">
-        <v>1990000</v>
+        <f t="shared" si="8"/>
+        <v>1200107</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E35">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35" t="str">
-        <f>"itemicon_"&amp;A35&amp;".png"</f>
-        <v>itemicon_1990000.png</v>
+        <v>4</v>
+      </c>
+      <c r="H35" t="s">
+        <v>65</v>
       </c>
       <c r="I35">
-        <f>2000000+E35*10000+B35</f>
-        <v>2990000</v>
+        <f t="shared" si="9"/>
+        <v>2020107</v>
       </c>
       <c r="J35" t="s">
         <v>66</v>
@@ -3160,127 +3691,5359 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1" spans="1:14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A36">
-        <f>1000000+E36*10000+B36</f>
-        <v>1980000</v>
-      </c>
-      <c r="B36" s="6">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1020108</v>
+      </c>
+      <c r="B36" s="7">
+        <v>108</v>
       </c>
       <c r="C36">
-        <v>1980000</v>
+        <f t="shared" si="8"/>
+        <v>1200108</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E36">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36" t="str">
-        <f>"itemicon_"&amp;A36&amp;".png"</f>
-        <v>itemicon_1980000.png</v>
+        <v>4</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
       </c>
       <c r="I36">
-        <f>2000000+E36*10000+B36</f>
-        <v>2980000</v>
+        <f t="shared" si="9"/>
+        <v>2020108</v>
       </c>
       <c r="J36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="N36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" ht="23" customHeight="1" spans="1:14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A37">
-        <f>1000000+E37*10000+B37</f>
-        <v>1040001</v>
-      </c>
-      <c r="B37" s="6">
-        <f>COUNTIF($F$1:F37,F37)</f>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>1020109</v>
+      </c>
+      <c r="B37" s="7">
+        <v>109</v>
       </c>
       <c r="C37">
-        <f>1000000+E37*100000+B37</f>
-        <v>1400001</v>
+        <f t="shared" si="8"/>
+        <v>1200109</v>
       </c>
       <c r="D37" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37" t="str">
-        <f>"itemicon_"&amp;A37&amp;".png"</f>
-        <v>itemicon_1040001.png</v>
+        <v>5</v>
+      </c>
+      <c r="H37" t="s">
+        <v>65</v>
       </c>
       <c r="I37">
-        <f>2000000+E37*10000+B37</f>
-        <v>2040001</v>
+        <f t="shared" si="9"/>
+        <v>2020109</v>
+      </c>
+      <c r="J37" t="s">
+        <v>66</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A38">
-        <f>1000000+E38*10000+B38</f>
-        <v>1040002</v>
-      </c>
-      <c r="B38" s="6">
-        <f>COUNTIF($F$1:F38,F38)</f>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>1020110</v>
+      </c>
+      <c r="B38" s="7">
+        <v>110</v>
       </c>
       <c r="C38">
-        <f>1000000+E38*100000+B38</f>
-        <v>1400002</v>
+        <f t="shared" si="8"/>
+        <v>1200110</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="H38" t="s">
+        <v>65</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="9"/>
+        <v>2020110</v>
+      </c>
+      <c r="J38" t="s">
+        <v>66</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A39">
+        <f t="shared" si="7"/>
+        <v>1020111</v>
+      </c>
+      <c r="B39" s="7">
+        <v>111</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="8"/>
+        <v>1200111</v>
+      </c>
+      <c r="D39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>47</v>
+      </c>
+      <c r="G39">
+        <v>6</v>
+      </c>
+      <c r="H39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="9"/>
+        <v>2020111</v>
+      </c>
+      <c r="J39" t="s">
+        <v>66</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A40">
+        <f t="shared" si="7"/>
+        <v>1020112</v>
+      </c>
+      <c r="B40" s="7">
+        <v>112</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="8"/>
+        <v>1200112</v>
+      </c>
+      <c r="D40" t="s">
+        <v>77</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40">
+        <v>6</v>
+      </c>
+      <c r="H40" t="s">
+        <v>65</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="9"/>
+        <v>2020112</v>
+      </c>
+      <c r="J40" t="s">
+        <v>66</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A41">
+        <f t="shared" ref="A41:A66" si="10">1000000+E41*10000+B41</f>
+        <v>1020121</v>
+      </c>
+      <c r="B41" s="7">
+        <v>121</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:C66" si="11">1000000+E41*100000+B41</f>
+        <v>1200121</v>
+      </c>
+      <c r="D41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41" t="s">
+        <v>47</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>65</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="9"/>
+        <v>2020121</v>
+      </c>
+      <c r="J41" t="s">
+        <v>66</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A42">
+        <f t="shared" si="10"/>
+        <v>1020122</v>
+      </c>
+      <c r="B42" s="7">
+        <v>122</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="11"/>
+        <v>1200122</v>
+      </c>
+      <c r="D42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>65</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="9"/>
+        <v>2020122</v>
+      </c>
+      <c r="J42" t="s">
+        <v>66</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A43">
+        <f t="shared" si="10"/>
+        <v>1020123</v>
+      </c>
+      <c r="B43" s="7">
+        <v>123</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="11"/>
+        <v>1200123</v>
+      </c>
+      <c r="D43" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>47</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="9"/>
+        <v>2020123</v>
+      </c>
+      <c r="J43" t="s">
+        <v>66</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A44">
+        <f t="shared" si="10"/>
+        <v>1020124</v>
+      </c>
+      <c r="B44" s="7">
+        <v>124</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="11"/>
+        <v>1200124</v>
+      </c>
+      <c r="D44" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44" t="s">
+        <v>65</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="9"/>
+        <v>2020124</v>
+      </c>
+      <c r="J44" t="s">
+        <v>66</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A45">
+        <f t="shared" si="10"/>
+        <v>1020125</v>
+      </c>
+      <c r="B45" s="7">
+        <v>125</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="11"/>
+        <v>1200125</v>
+      </c>
+      <c r="D45" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="F45" t="s">
+        <v>47</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+      <c r="H45" t="s">
+        <v>65</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="9"/>
+        <v>2020125</v>
+      </c>
+      <c r="J45" t="s">
+        <v>66</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A46">
+        <f t="shared" si="10"/>
+        <v>1020126</v>
+      </c>
+      <c r="B46" s="7">
+        <v>126</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="11"/>
+        <v>1200126</v>
+      </c>
+      <c r="D46" t="s">
+        <v>83</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+      <c r="H46" t="s">
+        <v>65</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="9"/>
+        <v>2020126</v>
+      </c>
+      <c r="J46" t="s">
+        <v>66</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A47">
+        <f t="shared" si="10"/>
+        <v>1020127</v>
+      </c>
+      <c r="B47" s="7">
+        <v>127</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="11"/>
+        <v>1200127</v>
+      </c>
+      <c r="D47" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>47</v>
+      </c>
+      <c r="G47">
         <v>4</v>
       </c>
-      <c r="F38" t="s">
-        <v>70</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-      <c r="H38" t="str">
-        <f>"itemicon_"&amp;A38&amp;".png"</f>
-        <v>itemicon_1040002.png</v>
-      </c>
-      <c r="I38">
-        <f>2000000+E38*10000+B38</f>
-        <v>2040002</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="N38">
+      <c r="H47" t="s">
+        <v>65</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="9"/>
+        <v>2020127</v>
+      </c>
+      <c r="J47" t="s">
+        <v>66</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A48">
+        <f t="shared" si="10"/>
+        <v>1020128</v>
+      </c>
+      <c r="B48" s="7">
+        <v>128</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="11"/>
+        <v>1200128</v>
+      </c>
+      <c r="D48" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48" t="s">
+        <v>47</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
+      </c>
+      <c r="H48" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="9"/>
+        <v>2020128</v>
+      </c>
+      <c r="J48" t="s">
+        <v>66</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A49">
+        <f t="shared" si="10"/>
+        <v>1020129</v>
+      </c>
+      <c r="B49" s="7">
+        <v>129</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="11"/>
+        <v>1200129</v>
+      </c>
+      <c r="D49" t="s">
+        <v>86</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G49">
+        <v>5</v>
+      </c>
+      <c r="H49" t="s">
+        <v>65</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="9"/>
+        <v>2020129</v>
+      </c>
+      <c r="J49" t="s">
+        <v>66</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A50">
+        <f t="shared" si="10"/>
+        <v>1020130</v>
+      </c>
+      <c r="B50" s="7">
+        <v>130</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="11"/>
+        <v>1200130</v>
+      </c>
+      <c r="D50" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50" t="s">
+        <v>47</v>
+      </c>
+      <c r="G50">
+        <v>5</v>
+      </c>
+      <c r="H50" t="s">
+        <v>65</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="9"/>
+        <v>2020130</v>
+      </c>
+      <c r="J50" t="s">
+        <v>66</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A51">
+        <f t="shared" si="10"/>
+        <v>1020131</v>
+      </c>
+      <c r="B51" s="7">
+        <v>131</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="11"/>
+        <v>1200131</v>
+      </c>
+      <c r="D51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>47</v>
+      </c>
+      <c r="G51">
+        <v>6</v>
+      </c>
+      <c r="H51" t="s">
+        <v>65</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="9"/>
+        <v>2020131</v>
+      </c>
+      <c r="J51" t="s">
+        <v>66</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A52">
+        <f t="shared" si="10"/>
+        <v>1020132</v>
+      </c>
+      <c r="B52" s="7">
+        <v>132</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="11"/>
+        <v>1200132</v>
+      </c>
+      <c r="D52" t="s">
+        <v>89</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52" t="s">
+        <v>47</v>
+      </c>
+      <c r="G52">
+        <v>6</v>
+      </c>
+      <c r="H52" t="s">
+        <v>65</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="9"/>
+        <v>2020132</v>
+      </c>
+      <c r="J52" t="s">
+        <v>66</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A53">
+        <f t="shared" si="10"/>
+        <v>1020141</v>
+      </c>
+      <c r="B53" s="7">
+        <v>141</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="11"/>
+        <v>1200141</v>
+      </c>
+      <c r="D53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53" t="s">
+        <v>47</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>65</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="9"/>
+        <v>2020141</v>
+      </c>
+      <c r="J53" t="s">
+        <v>66</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A54">
+        <f t="shared" si="10"/>
+        <v>1020142</v>
+      </c>
+      <c r="B54" s="7">
+        <v>142</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="11"/>
+        <v>1200142</v>
+      </c>
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54" t="s">
+        <v>47</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>65</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="9"/>
+        <v>2020142</v>
+      </c>
+      <c r="J54" t="s">
+        <v>66</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A55">
+        <f t="shared" si="10"/>
+        <v>1020143</v>
+      </c>
+      <c r="B55" s="7">
+        <v>143</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="11"/>
+        <v>1200143</v>
+      </c>
+      <c r="D55" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55" t="s">
+        <v>65</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="9"/>
+        <v>2020143</v>
+      </c>
+      <c r="J55" t="s">
+        <v>66</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A56">
+        <f t="shared" si="10"/>
+        <v>1020144</v>
+      </c>
+      <c r="B56" s="7">
+        <v>144</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="11"/>
+        <v>1200144</v>
+      </c>
+      <c r="D56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56" t="s">
+        <v>47</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56" t="s">
+        <v>65</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="9"/>
+        <v>2020144</v>
+      </c>
+      <c r="J56" t="s">
+        <v>66</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A57">
+        <f t="shared" si="10"/>
+        <v>1020145</v>
+      </c>
+      <c r="B57" s="7">
+        <v>145</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="11"/>
+        <v>1200145</v>
+      </c>
+      <c r="D57" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57" t="s">
+        <v>47</v>
+      </c>
+      <c r="G57">
+        <v>3</v>
+      </c>
+      <c r="H57" t="s">
+        <v>65</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="9"/>
+        <v>2020145</v>
+      </c>
+      <c r="J57" t="s">
+        <v>66</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A58">
+        <f t="shared" si="10"/>
+        <v>1020146</v>
+      </c>
+      <c r="B58" s="7">
+        <v>146</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="11"/>
+        <v>1200146</v>
+      </c>
+      <c r="D58" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="F58" t="s">
+        <v>47</v>
+      </c>
+      <c r="G58">
+        <v>3</v>
+      </c>
+      <c r="H58" t="s">
+        <v>65</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="9"/>
+        <v>2020146</v>
+      </c>
+      <c r="J58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A59">
+        <f t="shared" si="10"/>
+        <v>1020147</v>
+      </c>
+      <c r="B59" s="7">
+        <v>147</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="11"/>
+        <v>1200147</v>
+      </c>
+      <c r="D59" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59" t="s">
+        <v>47</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
+      </c>
+      <c r="H59" t="s">
+        <v>65</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="9"/>
+        <v>2020147</v>
+      </c>
+      <c r="J59" t="s">
+        <v>66</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A60">
+        <f t="shared" si="10"/>
+        <v>1020148</v>
+      </c>
+      <c r="B60" s="7">
+        <v>148</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="11"/>
+        <v>1200148</v>
+      </c>
+      <c r="D60" t="s">
+        <v>97</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="F60" t="s">
+        <v>47</v>
+      </c>
+      <c r="G60">
+        <v>4</v>
+      </c>
+      <c r="H60" t="s">
+        <v>65</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="9"/>
+        <v>2020148</v>
+      </c>
+      <c r="J60" t="s">
+        <v>66</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A61">
+        <f t="shared" si="10"/>
+        <v>1020149</v>
+      </c>
+      <c r="B61" s="7">
+        <v>149</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="11"/>
+        <v>1200149</v>
+      </c>
+      <c r="D61" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61" t="s">
+        <v>47</v>
+      </c>
+      <c r="G61">
+        <v>5</v>
+      </c>
+      <c r="H61" t="s">
+        <v>65</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="9"/>
+        <v>2020149</v>
+      </c>
+      <c r="J61" t="s">
+        <v>66</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A62">
+        <f t="shared" si="10"/>
+        <v>1020150</v>
+      </c>
+      <c r="B62" s="7">
+        <v>150</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="11"/>
+        <v>1200150</v>
+      </c>
+      <c r="D62" t="s">
+        <v>99</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62" t="s">
+        <v>47</v>
+      </c>
+      <c r="G62">
+        <v>5</v>
+      </c>
+      <c r="H62" t="s">
+        <v>65</v>
+      </c>
+      <c r="I62">
+        <f t="shared" ref="I62:I93" si="12">2000000+E62*10000+B62</f>
+        <v>2020150</v>
+      </c>
+      <c r="J62" t="s">
+        <v>66</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A63">
+        <f t="shared" si="10"/>
+        <v>1020151</v>
+      </c>
+      <c r="B63" s="7">
+        <v>151</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="11"/>
+        <v>1200151</v>
+      </c>
+      <c r="D63" t="s">
+        <v>100</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63" t="s">
+        <v>47</v>
+      </c>
+      <c r="G63">
+        <v>6</v>
+      </c>
+      <c r="H63" t="s">
+        <v>65</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="12"/>
+        <v>2020151</v>
+      </c>
+      <c r="J63" t="s">
+        <v>66</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A64">
+        <f t="shared" si="10"/>
+        <v>1020152</v>
+      </c>
+      <c r="B64" s="7">
+        <v>152</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="11"/>
+        <v>1200152</v>
+      </c>
+      <c r="D64" t="s">
+        <v>101</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64" t="s">
+        <v>47</v>
+      </c>
+      <c r="G64">
+        <v>6</v>
+      </c>
+      <c r="H64" t="s">
+        <v>65</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="12"/>
+        <v>2020152</v>
+      </c>
+      <c r="J64" t="s">
+        <v>66</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A65">
+        <f t="shared" si="10"/>
+        <v>1020161</v>
+      </c>
+      <c r="B65" s="7">
+        <v>161</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="11"/>
+        <v>1200161</v>
+      </c>
+      <c r="D65" t="s">
+        <v>102</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65" t="s">
+        <v>47</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>65</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="12"/>
+        <v>2020161</v>
+      </c>
+      <c r="J65" t="s">
+        <v>66</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A66">
+        <f t="shared" si="10"/>
+        <v>1020162</v>
+      </c>
+      <c r="B66" s="7">
+        <v>162</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="11"/>
+        <v>1200162</v>
+      </c>
+      <c r="D66" t="s">
+        <v>103</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66" t="s">
+        <v>47</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>65</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="12"/>
+        <v>2020162</v>
+      </c>
+      <c r="J66" t="s">
+        <v>66</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A67">
+        <f t="shared" ref="A67:A98" si="13">1000000+E67*10000+B67</f>
+        <v>1020163</v>
+      </c>
+      <c r="B67" s="7">
+        <v>163</v>
+      </c>
+      <c r="C67">
+        <f t="shared" ref="C67:C98" si="14">1000000+E67*100000+B67</f>
+        <v>1200163</v>
+      </c>
+      <c r="D67" t="s">
+        <v>104</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67" t="s">
+        <v>47</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67" t="s">
+        <v>65</v>
+      </c>
+      <c r="I67">
+        <f t="shared" si="12"/>
+        <v>2020163</v>
+      </c>
+      <c r="J67" t="s">
+        <v>66</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A68">
+        <f t="shared" si="13"/>
+        <v>1020164</v>
+      </c>
+      <c r="B68" s="7">
+        <v>164</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="14"/>
+        <v>1200164</v>
+      </c>
+      <c r="D68" t="s">
+        <v>105</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68" t="s">
+        <v>65</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="12"/>
+        <v>2020164</v>
+      </c>
+      <c r="J68" t="s">
+        <v>66</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A69">
+        <f t="shared" si="13"/>
+        <v>1020165</v>
+      </c>
+      <c r="B69" s="7">
+        <v>165</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="14"/>
+        <v>1200165</v>
+      </c>
+      <c r="D69" t="s">
+        <v>106</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="F69" t="s">
+        <v>47</v>
+      </c>
+      <c r="G69">
+        <v>3</v>
+      </c>
+      <c r="H69" t="s">
+        <v>65</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="12"/>
+        <v>2020165</v>
+      </c>
+      <c r="J69" t="s">
+        <v>66</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A70">
+        <f t="shared" si="13"/>
+        <v>1020166</v>
+      </c>
+      <c r="B70" s="7">
+        <v>166</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="14"/>
+        <v>1200166</v>
+      </c>
+      <c r="D70" t="s">
+        <v>107</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="F70" t="s">
+        <v>47</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
+      </c>
+      <c r="H70" t="s">
+        <v>65</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="12"/>
+        <v>2020166</v>
+      </c>
+      <c r="J70" t="s">
+        <v>66</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A71">
+        <f t="shared" si="13"/>
+        <v>1020167</v>
+      </c>
+      <c r="B71" s="7">
+        <v>167</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="14"/>
+        <v>1200167</v>
+      </c>
+      <c r="D71" t="s">
+        <v>108</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="F71" t="s">
+        <v>47</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
+      </c>
+      <c r="H71" t="s">
+        <v>65</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="12"/>
+        <v>2020167</v>
+      </c>
+      <c r="J71" t="s">
+        <v>66</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A72">
+        <f t="shared" si="13"/>
+        <v>1020168</v>
+      </c>
+      <c r="B72" s="7">
+        <v>168</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="14"/>
+        <v>1200168</v>
+      </c>
+      <c r="D72" t="s">
+        <v>109</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72" t="s">
+        <v>47</v>
+      </c>
+      <c r="G72">
+        <v>4</v>
+      </c>
+      <c r="H72" t="s">
+        <v>65</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="12"/>
+        <v>2020168</v>
+      </c>
+      <c r="J72" t="s">
+        <v>66</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A73">
+        <f t="shared" si="13"/>
+        <v>1020169</v>
+      </c>
+      <c r="B73" s="7">
+        <v>169</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="14"/>
+        <v>1200169</v>
+      </c>
+      <c r="D73" t="s">
+        <v>110</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73" t="s">
+        <v>47</v>
+      </c>
+      <c r="G73">
+        <v>5</v>
+      </c>
+      <c r="H73" t="s">
+        <v>65</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="12"/>
+        <v>2020169</v>
+      </c>
+      <c r="J73" t="s">
+        <v>66</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A74">
+        <f t="shared" si="13"/>
+        <v>1020170</v>
+      </c>
+      <c r="B74" s="7">
+        <v>170</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="14"/>
+        <v>1200170</v>
+      </c>
+      <c r="D74" t="s">
+        <v>111</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74" t="s">
+        <v>47</v>
+      </c>
+      <c r="G74">
+        <v>5</v>
+      </c>
+      <c r="H74" t="s">
+        <v>65</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="12"/>
+        <v>2020170</v>
+      </c>
+      <c r="J74" t="s">
+        <v>66</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A75">
+        <f t="shared" si="13"/>
+        <v>1020171</v>
+      </c>
+      <c r="B75" s="7">
+        <v>171</v>
+      </c>
+      <c r="C75">
+        <f t="shared" si="14"/>
+        <v>1200171</v>
+      </c>
+      <c r="D75" t="s">
+        <v>112</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G75">
+        <v>6</v>
+      </c>
+      <c r="H75" t="s">
+        <v>65</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="12"/>
+        <v>2020171</v>
+      </c>
+      <c r="J75" t="s">
+        <v>66</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A76">
+        <f t="shared" si="13"/>
+        <v>1020172</v>
+      </c>
+      <c r="B76" s="7">
+        <v>172</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="14"/>
+        <v>1200172</v>
+      </c>
+      <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76" t="s">
+        <v>47</v>
+      </c>
+      <c r="G76">
+        <v>6</v>
+      </c>
+      <c r="H76" t="s">
+        <v>65</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="12"/>
+        <v>2020172</v>
+      </c>
+      <c r="J76" t="s">
+        <v>66</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A77">
+        <f t="shared" si="13"/>
+        <v>1020181</v>
+      </c>
+      <c r="B77" s="7">
+        <v>181</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="14"/>
+        <v>1200181</v>
+      </c>
+      <c r="D77" t="s">
+        <v>114</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="F77" t="s">
+        <v>47</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
+        <v>65</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="12"/>
+        <v>2020181</v>
+      </c>
+      <c r="J77" t="s">
+        <v>66</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A78">
+        <f t="shared" si="13"/>
+        <v>1020182</v>
+      </c>
+      <c r="B78" s="7">
+        <v>182</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="14"/>
+        <v>1200182</v>
+      </c>
+      <c r="D78" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78" t="s">
+        <v>47</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78" t="s">
+        <v>65</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="12"/>
+        <v>2020182</v>
+      </c>
+      <c r="J78" t="s">
+        <v>66</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A79">
+        <f t="shared" si="13"/>
+        <v>1020183</v>
+      </c>
+      <c r="B79" s="7">
+        <v>183</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="14"/>
+        <v>1200183</v>
+      </c>
+      <c r="D79" t="s">
+        <v>116</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+      <c r="F79" t="s">
+        <v>47</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79" t="s">
+        <v>65</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="12"/>
+        <v>2020183</v>
+      </c>
+      <c r="J79" t="s">
+        <v>66</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A80">
+        <f t="shared" si="13"/>
+        <v>1020184</v>
+      </c>
+      <c r="B80" s="7">
+        <v>184</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="14"/>
+        <v>1200184</v>
+      </c>
+      <c r="D80" t="s">
+        <v>117</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="F80" t="s">
+        <v>47</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80" t="s">
+        <v>65</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="12"/>
+        <v>2020184</v>
+      </c>
+      <c r="J80" t="s">
+        <v>66</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A81">
+        <f t="shared" si="13"/>
+        <v>1020185</v>
+      </c>
+      <c r="B81" s="7">
+        <v>185</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="14"/>
+        <v>1200185</v>
+      </c>
+      <c r="D81" t="s">
+        <v>118</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="F81" t="s">
+        <v>47</v>
+      </c>
+      <c r="G81">
+        <v>3</v>
+      </c>
+      <c r="H81" t="s">
+        <v>65</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="12"/>
+        <v>2020185</v>
+      </c>
+      <c r="J81" t="s">
+        <v>66</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A82">
+        <f t="shared" si="13"/>
+        <v>1020186</v>
+      </c>
+      <c r="B82" s="7">
+        <v>186</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="14"/>
+        <v>1200186</v>
+      </c>
+      <c r="D82" t="s">
+        <v>119</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="F82" t="s">
+        <v>47</v>
+      </c>
+      <c r="G82">
+        <v>3</v>
+      </c>
+      <c r="H82" t="s">
+        <v>65</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="12"/>
+        <v>2020186</v>
+      </c>
+      <c r="J82" t="s">
+        <v>66</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A83">
+        <f t="shared" si="13"/>
+        <v>1020187</v>
+      </c>
+      <c r="B83" s="7">
+        <v>187</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="14"/>
+        <v>1200187</v>
+      </c>
+      <c r="D83" t="s">
+        <v>120</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83" t="s">
+        <v>47</v>
+      </c>
+      <c r="G83">
+        <v>4</v>
+      </c>
+      <c r="H83" t="s">
+        <v>65</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="12"/>
+        <v>2020187</v>
+      </c>
+      <c r="J83" t="s">
+        <v>66</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A84">
+        <f t="shared" si="13"/>
+        <v>1020188</v>
+      </c>
+      <c r="B84" s="7">
+        <v>188</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="14"/>
+        <v>1200188</v>
+      </c>
+      <c r="D84" t="s">
+        <v>121</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="F84" t="s">
+        <v>47</v>
+      </c>
+      <c r="G84">
+        <v>4</v>
+      </c>
+      <c r="H84" t="s">
+        <v>65</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="12"/>
+        <v>2020188</v>
+      </c>
+      <c r="J84" t="s">
+        <v>66</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A85">
+        <f t="shared" si="13"/>
+        <v>1020189</v>
+      </c>
+      <c r="B85" s="7">
+        <v>189</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="14"/>
+        <v>1200189</v>
+      </c>
+      <c r="D85" t="s">
+        <v>122</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="F85" t="s">
+        <v>47</v>
+      </c>
+      <c r="G85">
+        <v>5</v>
+      </c>
+      <c r="H85" t="s">
+        <v>65</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="12"/>
+        <v>2020189</v>
+      </c>
+      <c r="J85" t="s">
+        <v>66</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A86">
+        <f t="shared" si="13"/>
+        <v>1020190</v>
+      </c>
+      <c r="B86" s="7">
+        <v>190</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="14"/>
+        <v>1200190</v>
+      </c>
+      <c r="D86" t="s">
+        <v>123</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="F86" t="s">
+        <v>47</v>
+      </c>
+      <c r="G86">
+        <v>5</v>
+      </c>
+      <c r="H86" t="s">
+        <v>65</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="12"/>
+        <v>2020190</v>
+      </c>
+      <c r="J86" t="s">
+        <v>66</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A87">
+        <f t="shared" si="13"/>
+        <v>1020191</v>
+      </c>
+      <c r="B87" s="7">
+        <v>191</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="14"/>
+        <v>1200191</v>
+      </c>
+      <c r="D87" t="s">
+        <v>124</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87" t="s">
+        <v>47</v>
+      </c>
+      <c r="G87">
+        <v>6</v>
+      </c>
+      <c r="H87" t="s">
+        <v>65</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="12"/>
+        <v>2020191</v>
+      </c>
+      <c r="J87" t="s">
+        <v>66</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A88">
+        <f t="shared" si="13"/>
+        <v>1020192</v>
+      </c>
+      <c r="B88" s="7">
+        <v>192</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="14"/>
+        <v>1200192</v>
+      </c>
+      <c r="D88" t="s">
+        <v>125</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88" t="s">
+        <v>47</v>
+      </c>
+      <c r="G88">
+        <v>6</v>
+      </c>
+      <c r="H88" t="s">
+        <v>65</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="12"/>
+        <v>2020192</v>
+      </c>
+      <c r="J88" t="s">
+        <v>66</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A89">
+        <f t="shared" si="13"/>
+        <v>1020201</v>
+      </c>
+      <c r="B89" s="7">
+        <v>201</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="14"/>
+        <v>1200201</v>
+      </c>
+      <c r="D89" t="s">
+        <v>126</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89" t="s">
+        <v>47</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>65</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="12"/>
+        <v>2020201</v>
+      </c>
+      <c r="J89" t="s">
+        <v>66</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A90">
+        <f t="shared" si="13"/>
+        <v>1020202</v>
+      </c>
+      <c r="B90" s="7">
+        <v>202</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="14"/>
+        <v>1200202</v>
+      </c>
+      <c r="D90" t="s">
+        <v>127</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="F90" t="s">
+        <v>47</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
+        <v>65</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="12"/>
+        <v>2020202</v>
+      </c>
+      <c r="J90" t="s">
+        <v>66</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A91">
+        <f t="shared" si="13"/>
+        <v>1020203</v>
+      </c>
+      <c r="B91" s="7">
+        <v>203</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="14"/>
+        <v>1200203</v>
+      </c>
+      <c r="D91" t="s">
+        <v>128</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="F91" t="s">
+        <v>47</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+      <c r="H91" t="s">
+        <v>65</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="12"/>
+        <v>2020203</v>
+      </c>
+      <c r="J91" t="s">
+        <v>66</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A92">
+        <f t="shared" si="13"/>
+        <v>1020204</v>
+      </c>
+      <c r="B92" s="7">
+        <v>204</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="14"/>
+        <v>1200204</v>
+      </c>
+      <c r="D92" t="s">
+        <v>129</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="F92" t="s">
+        <v>47</v>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+      <c r="H92" t="s">
+        <v>65</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="12"/>
+        <v>2020204</v>
+      </c>
+      <c r="J92" t="s">
+        <v>66</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A93">
+        <f t="shared" si="13"/>
+        <v>1020205</v>
+      </c>
+      <c r="B93" s="7">
+        <v>205</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="14"/>
+        <v>1200205</v>
+      </c>
+      <c r="D93" t="s">
+        <v>130</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>47</v>
+      </c>
+      <c r="G93">
+        <v>3</v>
+      </c>
+      <c r="H93" t="s">
+        <v>65</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="12"/>
+        <v>2020205</v>
+      </c>
+      <c r="J93" t="s">
+        <v>66</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A94">
+        <f t="shared" si="13"/>
+        <v>1020206</v>
+      </c>
+      <c r="B94" s="7">
+        <v>206</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="14"/>
+        <v>1200206</v>
+      </c>
+      <c r="D94" t="s">
+        <v>131</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+      <c r="F94" t="s">
+        <v>47</v>
+      </c>
+      <c r="G94">
+        <v>3</v>
+      </c>
+      <c r="H94" t="s">
+        <v>65</v>
+      </c>
+      <c r="I94">
+        <f t="shared" ref="I94:I124" si="15">2000000+E94*10000+B94</f>
+        <v>2020206</v>
+      </c>
+      <c r="J94" t="s">
+        <v>66</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A95">
+        <f t="shared" si="13"/>
+        <v>1020207</v>
+      </c>
+      <c r="B95" s="7">
+        <v>207</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="14"/>
+        <v>1200207</v>
+      </c>
+      <c r="D95" t="s">
+        <v>132</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="F95" t="s">
+        <v>47</v>
+      </c>
+      <c r="G95">
+        <v>4</v>
+      </c>
+      <c r="H95" t="s">
+        <v>65</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="15"/>
+        <v>2020207</v>
+      </c>
+      <c r="J95" t="s">
+        <v>66</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A96">
+        <f t="shared" si="13"/>
+        <v>1020208</v>
+      </c>
+      <c r="B96" s="7">
+        <v>208</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="14"/>
+        <v>1200208</v>
+      </c>
+      <c r="D96" t="s">
+        <v>133</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="F96" t="s">
+        <v>47</v>
+      </c>
+      <c r="G96">
+        <v>4</v>
+      </c>
+      <c r="H96" t="s">
+        <v>65</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="15"/>
+        <v>2020208</v>
+      </c>
+      <c r="J96" t="s">
+        <v>66</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A97">
+        <f t="shared" si="13"/>
+        <v>1020209</v>
+      </c>
+      <c r="B97" s="7">
+        <v>209</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="14"/>
+        <v>1200209</v>
+      </c>
+      <c r="D97" t="s">
+        <v>134</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="F97" t="s">
+        <v>47</v>
+      </c>
+      <c r="G97">
+        <v>5</v>
+      </c>
+      <c r="H97" t="s">
+        <v>65</v>
+      </c>
+      <c r="I97">
+        <f t="shared" si="15"/>
+        <v>2020209</v>
+      </c>
+      <c r="J97" t="s">
+        <v>66</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A98">
+        <f t="shared" si="13"/>
+        <v>1020210</v>
+      </c>
+      <c r="B98" s="7">
+        <v>210</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="14"/>
+        <v>1200210</v>
+      </c>
+      <c r="D98" t="s">
+        <v>135</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="F98" t="s">
+        <v>47</v>
+      </c>
+      <c r="G98">
+        <v>5</v>
+      </c>
+      <c r="H98" t="s">
+        <v>65</v>
+      </c>
+      <c r="I98">
+        <f t="shared" si="15"/>
+        <v>2020210</v>
+      </c>
+      <c r="J98" t="s">
+        <v>66</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A99">
+        <f t="shared" ref="A99:A124" si="16">1000000+E99*10000+B99</f>
+        <v>1020211</v>
+      </c>
+      <c r="B99" s="7">
+        <v>211</v>
+      </c>
+      <c r="C99">
+        <f t="shared" ref="C99:C124" si="17">1000000+E99*100000+B99</f>
+        <v>1200211</v>
+      </c>
+      <c r="D99" t="s">
+        <v>136</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99" t="s">
+        <v>47</v>
+      </c>
+      <c r="G99">
+        <v>6</v>
+      </c>
+      <c r="H99" t="s">
+        <v>65</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="15"/>
+        <v>2020211</v>
+      </c>
+      <c r="J99" t="s">
+        <v>66</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A100">
+        <f t="shared" si="16"/>
+        <v>1020212</v>
+      </c>
+      <c r="B100" s="7">
+        <v>212</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="17"/>
+        <v>1200212</v>
+      </c>
+      <c r="D100" t="s">
+        <v>137</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="F100" t="s">
+        <v>47</v>
+      </c>
+      <c r="G100">
+        <v>6</v>
+      </c>
+      <c r="H100" t="s">
+        <v>65</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="15"/>
+        <v>2020212</v>
+      </c>
+      <c r="J100" t="s">
+        <v>66</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A101">
+        <f t="shared" si="16"/>
+        <v>1020221</v>
+      </c>
+      <c r="B101" s="7">
+        <v>221</v>
+      </c>
+      <c r="C101">
+        <f t="shared" si="17"/>
+        <v>1200221</v>
+      </c>
+      <c r="D101" t="s">
+        <v>138</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+      <c r="F101" t="s">
+        <v>47</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101" t="s">
+        <v>65</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="15"/>
+        <v>2020221</v>
+      </c>
+      <c r="J101" t="s">
+        <v>66</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A102">
+        <f t="shared" si="16"/>
+        <v>1020222</v>
+      </c>
+      <c r="B102" s="7">
+        <v>222</v>
+      </c>
+      <c r="C102">
+        <f t="shared" si="17"/>
+        <v>1200222</v>
+      </c>
+      <c r="D102" t="s">
+        <v>139</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="F102" t="s">
+        <v>47</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102" t="s">
+        <v>65</v>
+      </c>
+      <c r="I102">
+        <f t="shared" si="15"/>
+        <v>2020222</v>
+      </c>
+      <c r="J102" t="s">
+        <v>66</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A103">
+        <f t="shared" si="16"/>
+        <v>1020223</v>
+      </c>
+      <c r="B103" s="7">
+        <v>223</v>
+      </c>
+      <c r="C103">
+        <f t="shared" si="17"/>
+        <v>1200223</v>
+      </c>
+      <c r="D103" t="s">
+        <v>140</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103" t="s">
+        <v>47</v>
+      </c>
+      <c r="G103">
+        <v>2</v>
+      </c>
+      <c r="H103" t="s">
+        <v>65</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="15"/>
+        <v>2020223</v>
+      </c>
+      <c r="J103" t="s">
+        <v>66</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A104">
+        <f t="shared" si="16"/>
+        <v>1020224</v>
+      </c>
+      <c r="B104" s="7">
+        <v>224</v>
+      </c>
+      <c r="C104">
+        <f t="shared" si="17"/>
+        <v>1200224</v>
+      </c>
+      <c r="D104" t="s">
+        <v>141</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="F104" t="s">
+        <v>47</v>
+      </c>
+      <c r="G104">
+        <v>2</v>
+      </c>
+      <c r="H104" t="s">
+        <v>65</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="15"/>
+        <v>2020224</v>
+      </c>
+      <c r="J104" t="s">
+        <v>66</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A105">
+        <f t="shared" si="16"/>
+        <v>1020225</v>
+      </c>
+      <c r="B105" s="7">
+        <v>225</v>
+      </c>
+      <c r="C105">
+        <f t="shared" si="17"/>
+        <v>1200225</v>
+      </c>
+      <c r="D105" t="s">
+        <v>142</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="F105" t="s">
+        <v>47</v>
+      </c>
+      <c r="G105">
+        <v>3</v>
+      </c>
+      <c r="H105" t="s">
+        <v>65</v>
+      </c>
+      <c r="I105">
+        <f t="shared" si="15"/>
+        <v>2020225</v>
+      </c>
+      <c r="J105" t="s">
+        <v>66</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A106">
+        <f t="shared" si="16"/>
+        <v>1020226</v>
+      </c>
+      <c r="B106" s="7">
+        <v>226</v>
+      </c>
+      <c r="C106">
+        <f t="shared" si="17"/>
+        <v>1200226</v>
+      </c>
+      <c r="D106" t="s">
+        <v>143</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106" t="s">
+        <v>47</v>
+      </c>
+      <c r="G106">
+        <v>3</v>
+      </c>
+      <c r="H106" t="s">
+        <v>65</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="15"/>
+        <v>2020226</v>
+      </c>
+      <c r="J106" t="s">
+        <v>66</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A107">
+        <f t="shared" si="16"/>
+        <v>1020227</v>
+      </c>
+      <c r="B107" s="7">
+        <v>227</v>
+      </c>
+      <c r="C107">
+        <f t="shared" si="17"/>
+        <v>1200227</v>
+      </c>
+      <c r="D107" t="s">
+        <v>144</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="F107" t="s">
+        <v>47</v>
+      </c>
+      <c r="G107">
+        <v>4</v>
+      </c>
+      <c r="H107" t="s">
+        <v>65</v>
+      </c>
+      <c r="I107">
+        <f t="shared" si="15"/>
+        <v>2020227</v>
+      </c>
+      <c r="J107" t="s">
+        <v>66</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A108">
+        <f t="shared" si="16"/>
+        <v>1020228</v>
+      </c>
+      <c r="B108" s="7">
+        <v>228</v>
+      </c>
+      <c r="C108">
+        <f t="shared" si="17"/>
+        <v>1200228</v>
+      </c>
+      <c r="D108" t="s">
+        <v>145</v>
+      </c>
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="F108" t="s">
+        <v>47</v>
+      </c>
+      <c r="G108">
+        <v>4</v>
+      </c>
+      <c r="H108" t="s">
+        <v>65</v>
+      </c>
+      <c r="I108">
+        <f t="shared" si="15"/>
+        <v>2020228</v>
+      </c>
+      <c r="J108" t="s">
+        <v>66</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A109">
+        <f t="shared" si="16"/>
+        <v>1020229</v>
+      </c>
+      <c r="B109" s="7">
+        <v>229</v>
+      </c>
+      <c r="C109">
+        <f t="shared" si="17"/>
+        <v>1200229</v>
+      </c>
+      <c r="D109" t="s">
+        <v>146</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="F109" t="s">
+        <v>47</v>
+      </c>
+      <c r="G109">
+        <v>5</v>
+      </c>
+      <c r="H109" t="s">
+        <v>65</v>
+      </c>
+      <c r="I109">
+        <f t="shared" si="15"/>
+        <v>2020229</v>
+      </c>
+      <c r="J109" t="s">
+        <v>66</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A110">
+        <f t="shared" si="16"/>
+        <v>1020230</v>
+      </c>
+      <c r="B110" s="7">
+        <v>230</v>
+      </c>
+      <c r="C110">
+        <f t="shared" si="17"/>
+        <v>1200230</v>
+      </c>
+      <c r="D110" t="s">
+        <v>147</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="F110" t="s">
+        <v>47</v>
+      </c>
+      <c r="G110">
+        <v>5</v>
+      </c>
+      <c r="H110" t="s">
+        <v>65</v>
+      </c>
+      <c r="I110">
+        <f t="shared" si="15"/>
+        <v>2020230</v>
+      </c>
+      <c r="J110" t="s">
+        <v>66</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A111">
+        <f t="shared" si="16"/>
+        <v>1020231</v>
+      </c>
+      <c r="B111" s="7">
+        <v>231</v>
+      </c>
+      <c r="C111">
+        <f t="shared" si="17"/>
+        <v>1200231</v>
+      </c>
+      <c r="D111" t="s">
+        <v>148</v>
+      </c>
+      <c r="E111">
+        <v>2</v>
+      </c>
+      <c r="F111" t="s">
+        <v>47</v>
+      </c>
+      <c r="G111">
+        <v>6</v>
+      </c>
+      <c r="H111" t="s">
+        <v>65</v>
+      </c>
+      <c r="I111">
+        <f t="shared" si="15"/>
+        <v>2020231</v>
+      </c>
+      <c r="J111" t="s">
+        <v>66</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A112">
+        <f t="shared" si="16"/>
+        <v>1020232</v>
+      </c>
+      <c r="B112" s="7">
+        <v>232</v>
+      </c>
+      <c r="C112">
+        <f t="shared" si="17"/>
+        <v>1200232</v>
+      </c>
+      <c r="D112" t="s">
+        <v>149</v>
+      </c>
+      <c r="E112">
+        <v>2</v>
+      </c>
+      <c r="F112" t="s">
+        <v>47</v>
+      </c>
+      <c r="G112">
+        <v>6</v>
+      </c>
+      <c r="H112" t="s">
+        <v>65</v>
+      </c>
+      <c r="I112">
+        <f t="shared" si="15"/>
+        <v>2020232</v>
+      </c>
+      <c r="J112" t="s">
+        <v>66</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A113">
+        <f t="shared" si="16"/>
+        <v>1020241</v>
+      </c>
+      <c r="B113" s="7">
+        <v>241</v>
+      </c>
+      <c r="C113">
+        <f t="shared" si="17"/>
+        <v>1200241</v>
+      </c>
+      <c r="D113" t="s">
+        <v>150</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113" t="s">
+        <v>47</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113" t="s">
+        <v>65</v>
+      </c>
+      <c r="I113">
+        <f t="shared" si="15"/>
+        <v>2020241</v>
+      </c>
+      <c r="J113" t="s">
+        <v>66</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A114">
+        <f t="shared" si="16"/>
+        <v>1020242</v>
+      </c>
+      <c r="B114" s="7">
+        <v>242</v>
+      </c>
+      <c r="C114">
+        <f t="shared" si="17"/>
+        <v>1200242</v>
+      </c>
+      <c r="D114" t="s">
+        <v>151</v>
+      </c>
+      <c r="E114">
+        <v>2</v>
+      </c>
+      <c r="F114" t="s">
+        <v>47</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114" t="s">
+        <v>65</v>
+      </c>
+      <c r="I114">
+        <f t="shared" si="15"/>
+        <v>2020242</v>
+      </c>
+      <c r="J114" t="s">
+        <v>66</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A115">
+        <f t="shared" si="16"/>
+        <v>1020243</v>
+      </c>
+      <c r="B115" s="7">
+        <v>243</v>
+      </c>
+      <c r="C115">
+        <f t="shared" si="17"/>
+        <v>1200243</v>
+      </c>
+      <c r="D115" t="s">
+        <v>152</v>
+      </c>
+      <c r="E115">
+        <v>2</v>
+      </c>
+      <c r="F115" t="s">
+        <v>47</v>
+      </c>
+      <c r="G115">
+        <v>2</v>
+      </c>
+      <c r="H115" t="s">
+        <v>65</v>
+      </c>
+      <c r="I115">
+        <f t="shared" si="15"/>
+        <v>2020243</v>
+      </c>
+      <c r="J115" t="s">
+        <v>66</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A116">
+        <f t="shared" si="16"/>
+        <v>1020244</v>
+      </c>
+      <c r="B116" s="7">
+        <v>244</v>
+      </c>
+      <c r="C116">
+        <f t="shared" si="17"/>
+        <v>1200244</v>
+      </c>
+      <c r="D116" t="s">
+        <v>153</v>
+      </c>
+      <c r="E116">
+        <v>2</v>
+      </c>
+      <c r="F116" t="s">
+        <v>47</v>
+      </c>
+      <c r="G116">
+        <v>2</v>
+      </c>
+      <c r="H116" t="s">
+        <v>65</v>
+      </c>
+      <c r="I116">
+        <f t="shared" si="15"/>
+        <v>2020244</v>
+      </c>
+      <c r="J116" t="s">
+        <v>66</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A117">
+        <f t="shared" si="16"/>
+        <v>1020245</v>
+      </c>
+      <c r="B117" s="7">
+        <v>245</v>
+      </c>
+      <c r="C117">
+        <f t="shared" si="17"/>
+        <v>1200245</v>
+      </c>
+      <c r="D117" t="s">
+        <v>154</v>
+      </c>
+      <c r="E117">
+        <v>2</v>
+      </c>
+      <c r="F117" t="s">
+        <v>47</v>
+      </c>
+      <c r="G117">
+        <v>3</v>
+      </c>
+      <c r="H117" t="s">
+        <v>65</v>
+      </c>
+      <c r="I117">
+        <f t="shared" si="15"/>
+        <v>2020245</v>
+      </c>
+      <c r="J117" t="s">
+        <v>66</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A118">
+        <f t="shared" si="16"/>
+        <v>1020246</v>
+      </c>
+      <c r="B118" s="7">
+        <v>246</v>
+      </c>
+      <c r="C118">
+        <f t="shared" si="17"/>
+        <v>1200246</v>
+      </c>
+      <c r="D118" t="s">
+        <v>155</v>
+      </c>
+      <c r="E118">
+        <v>2</v>
+      </c>
+      <c r="F118" t="s">
+        <v>47</v>
+      </c>
+      <c r="G118">
+        <v>3</v>
+      </c>
+      <c r="H118" t="s">
+        <v>65</v>
+      </c>
+      <c r="I118">
+        <f t="shared" si="15"/>
+        <v>2020246</v>
+      </c>
+      <c r="J118" t="s">
+        <v>66</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A119">
+        <f t="shared" si="16"/>
+        <v>1020247</v>
+      </c>
+      <c r="B119" s="7">
+        <v>247</v>
+      </c>
+      <c r="C119">
+        <f t="shared" si="17"/>
+        <v>1200247</v>
+      </c>
+      <c r="D119" t="s">
+        <v>156</v>
+      </c>
+      <c r="E119">
+        <v>2</v>
+      </c>
+      <c r="F119" t="s">
+        <v>47</v>
+      </c>
+      <c r="G119">
+        <v>4</v>
+      </c>
+      <c r="H119" t="s">
+        <v>65</v>
+      </c>
+      <c r="I119">
+        <f t="shared" si="15"/>
+        <v>2020247</v>
+      </c>
+      <c r="J119" t="s">
+        <v>66</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A120">
+        <f t="shared" si="16"/>
+        <v>1020248</v>
+      </c>
+      <c r="B120" s="7">
+        <v>248</v>
+      </c>
+      <c r="C120">
+        <f t="shared" si="17"/>
+        <v>1200248</v>
+      </c>
+      <c r="D120" t="s">
+        <v>157</v>
+      </c>
+      <c r="E120">
+        <v>2</v>
+      </c>
+      <c r="F120" t="s">
+        <v>47</v>
+      </c>
+      <c r="G120">
+        <v>4</v>
+      </c>
+      <c r="H120" t="s">
+        <v>65</v>
+      </c>
+      <c r="I120">
+        <f t="shared" si="15"/>
+        <v>2020248</v>
+      </c>
+      <c r="J120" t="s">
+        <v>66</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A121">
+        <f t="shared" si="16"/>
+        <v>1020249</v>
+      </c>
+      <c r="B121" s="7">
+        <v>249</v>
+      </c>
+      <c r="C121">
+        <f t="shared" si="17"/>
+        <v>1200249</v>
+      </c>
+      <c r="D121" t="s">
+        <v>158</v>
+      </c>
+      <c r="E121">
+        <v>2</v>
+      </c>
+      <c r="F121" t="s">
+        <v>47</v>
+      </c>
+      <c r="G121">
+        <v>5</v>
+      </c>
+      <c r="H121" t="s">
+        <v>65</v>
+      </c>
+      <c r="I121">
+        <f t="shared" si="15"/>
+        <v>2020249</v>
+      </c>
+      <c r="J121" t="s">
+        <v>66</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A122">
+        <f t="shared" si="16"/>
+        <v>1020250</v>
+      </c>
+      <c r="B122" s="7">
+        <v>250</v>
+      </c>
+      <c r="C122">
+        <f t="shared" si="17"/>
+        <v>1200250</v>
+      </c>
+      <c r="D122" t="s">
+        <v>159</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122" t="s">
+        <v>47</v>
+      </c>
+      <c r="G122">
+        <v>5</v>
+      </c>
+      <c r="H122" t="s">
+        <v>65</v>
+      </c>
+      <c r="I122">
+        <f t="shared" si="15"/>
+        <v>2020250</v>
+      </c>
+      <c r="J122" t="s">
+        <v>66</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A123">
+        <f t="shared" si="16"/>
+        <v>1020251</v>
+      </c>
+      <c r="B123" s="7">
+        <v>251</v>
+      </c>
+      <c r="C123">
+        <f t="shared" si="17"/>
+        <v>1200251</v>
+      </c>
+      <c r="D123" t="s">
+        <v>160</v>
+      </c>
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123" t="s">
+        <v>47</v>
+      </c>
+      <c r="G123">
+        <v>6</v>
+      </c>
+      <c r="H123" t="s">
+        <v>65</v>
+      </c>
+      <c r="I123">
+        <f t="shared" si="15"/>
+        <v>2020251</v>
+      </c>
+      <c r="J123" t="s">
+        <v>66</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A124">
+        <f t="shared" si="16"/>
+        <v>1020252</v>
+      </c>
+      <c r="B124" s="7">
+        <v>252</v>
+      </c>
+      <c r="C124">
+        <f t="shared" si="17"/>
+        <v>1200252</v>
+      </c>
+      <c r="D124" t="s">
+        <v>161</v>
+      </c>
+      <c r="E124">
+        <v>2</v>
+      </c>
+      <c r="F124" t="s">
+        <v>47</v>
+      </c>
+      <c r="G124">
+        <v>6</v>
+      </c>
+      <c r="H124" t="s">
+        <v>65</v>
+      </c>
+      <c r="I124">
+        <f t="shared" si="15"/>
+        <v>2020252</v>
+      </c>
+      <c r="J124" t="s">
+        <v>66</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A125">
+        <f>1000000+E125*10000+B125</f>
+        <v>1021001</v>
+      </c>
+      <c r="B125" s="7">
+        <v>1001</v>
+      </c>
+      <c r="C125">
+        <f>1000000+E125*100000+B125</f>
+        <v>1201001</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E125">
+        <v>2</v>
+      </c>
+      <c r="F125" t="s">
+        <v>47</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+      <c r="H125" t="str">
+        <f>"itemicon_"&amp;A125&amp;".png"</f>
+        <v>itemicon_1021001.png</v>
+      </c>
+      <c r="I125">
+        <f>2000000+E125*10000+B125</f>
+        <v>2021001</v>
+      </c>
+      <c r="K125" s="7">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>2</v>
+      </c>
+      <c r="M125"/>
+      <c r="N125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A126">
+        <f>1000000+E126*10000+B126</f>
+        <v>1021002</v>
+      </c>
+      <c r="B126" s="7">
+        <v>1002</v>
+      </c>
+      <c r="C126">
+        <f>1000000+E126*100000+B126</f>
+        <v>1201002</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E126">
+        <v>2</v>
+      </c>
+      <c r="F126" t="s">
+        <v>47</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126" t="str">
+        <f>"itemicon_"&amp;A126&amp;".png"</f>
+        <v>itemicon_1021002.png</v>
+      </c>
+      <c r="I126">
+        <f>2000000+E126*10000+B126</f>
+        <v>2021002</v>
+      </c>
+      <c r="K126" s="7">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>3</v>
+      </c>
+      <c r="M126"/>
+      <c r="N126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A127">
+        <f>1000000+E127*10000+B127</f>
+        <v>1021201</v>
+      </c>
+      <c r="B127" s="7">
+        <v>1201</v>
+      </c>
+      <c r="C127">
+        <f>1000000+E127*100000+B127</f>
+        <v>1201201</v>
+      </c>
+      <c r="D127" t="s">
+        <v>164</v>
+      </c>
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127" t="s">
+        <v>47</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127" t="str">
+        <f>"itemicon_"&amp;A127&amp;".png"</f>
+        <v>itemicon_1021201.png</v>
+      </c>
+      <c r="I127">
+        <f>2000000+E127*10000+B127</f>
+        <v>2021201</v>
+      </c>
+      <c r="K127" s="7">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>1002</v>
+      </c>
+      <c r="M127"/>
+      <c r="N127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A128">
+        <f>1000000+E128*10000+B128</f>
+        <v>1021202</v>
+      </c>
+      <c r="B128" s="7">
+        <v>1202</v>
+      </c>
+      <c r="C128">
+        <f>1000000+E128*100000+B128</f>
+        <v>1201202</v>
+      </c>
+      <c r="D128" t="s">
+        <v>165</v>
+      </c>
+      <c r="E128">
+        <v>2</v>
+      </c>
+      <c r="F128" t="s">
+        <v>47</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128" t="str">
+        <f>"itemicon_"&amp;A128&amp;".png"</f>
+        <v>itemicon_1021202.png</v>
+      </c>
+      <c r="I128">
+        <f>2000000+E128*10000+B128</f>
+        <v>2021202</v>
+      </c>
+      <c r="K128" s="7">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>1003</v>
+      </c>
+      <c r="M128"/>
+      <c r="N128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A129">
+        <f>1000000+E129*10000+B129</f>
+        <v>1021350</v>
+      </c>
+      <c r="B129" s="7">
+        <v>1350</v>
+      </c>
+      <c r="C129">
+        <v>101801</v>
+      </c>
+      <c r="D129" t="s">
+        <v>166</v>
+      </c>
+      <c r="E129">
+        <v>2</v>
+      </c>
+      <c r="F129" t="s">
+        <v>47</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="H129" t="s">
+        <v>167</v>
+      </c>
+      <c r="I129">
+        <v>201801</v>
+      </c>
+      <c r="K129" s="7">
+        <v>1</v>
+      </c>
+      <c r="L129">
+        <v>1801</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A130">
+        <f>1000000+E130*10000+B130</f>
+        <v>1021351</v>
+      </c>
+      <c r="B130" s="7">
+        <v>1351</v>
+      </c>
+      <c r="C130">
+        <v>101802</v>
+      </c>
+      <c r="D130" t="s">
+        <v>168</v>
+      </c>
+      <c r="E130">
+        <v>2</v>
+      </c>
+      <c r="F130" t="s">
+        <v>47</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+      <c r="H130" t="s">
+        <v>169</v>
+      </c>
+      <c r="I130">
+        <v>201802</v>
+      </c>
+      <c r="K130" s="7">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>1802</v>
+      </c>
+      <c r="N130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A131">
+        <f t="shared" ref="A131:A144" si="18">1000000+E131*10000+B131</f>
+        <v>1021401</v>
+      </c>
+      <c r="B131" s="7">
+        <v>1401</v>
+      </c>
+      <c r="C131">
+        <f t="shared" ref="C131:C141" si="19">1000000+E131*100000+B131</f>
+        <v>1201401</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E131">
+        <v>2</v>
+      </c>
+      <c r="F131" t="s">
+        <v>47</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131" t="str">
+        <f t="shared" ref="H131:H144" si="20">"itemicon_"&amp;A131&amp;".png"</f>
+        <v>itemicon_1021401.png</v>
+      </c>
+      <c r="I131">
+        <f t="shared" ref="I131:I144" si="21">2000000+E131*10000+B131</f>
+        <v>2021401</v>
+      </c>
+      <c r="K131" s="7">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>2002</v>
+      </c>
+      <c r="M131"/>
+      <c r="N131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A132">
+        <f t="shared" si="18"/>
+        <v>1021402</v>
+      </c>
+      <c r="B132" s="7">
+        <v>1402</v>
+      </c>
+      <c r="C132">
+        <f t="shared" si="19"/>
+        <v>1201402</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E132">
+        <v>2</v>
+      </c>
+      <c r="F132" t="s">
+        <v>47</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1021402.png</v>
+      </c>
+      <c r="I132">
+        <f t="shared" si="21"/>
+        <v>2021402</v>
+      </c>
+      <c r="K132" s="7">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>2003</v>
+      </c>
+      <c r="M132"/>
+      <c r="N132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A133">
+        <f t="shared" si="18"/>
+        <v>1021601</v>
+      </c>
+      <c r="B133" s="7">
+        <v>1601</v>
+      </c>
+      <c r="C133">
+        <f t="shared" si="19"/>
+        <v>1201601</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E133">
+        <v>2</v>
+      </c>
+      <c r="F133" t="s">
+        <v>47</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1021601.png</v>
+      </c>
+      <c r="I133">
+        <f t="shared" si="21"/>
+        <v>2021601</v>
+      </c>
+      <c r="K133" s="7">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>3002</v>
+      </c>
+      <c r="M133"/>
+      <c r="N133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A134">
+        <f t="shared" si="18"/>
+        <v>1021602</v>
+      </c>
+      <c r="B134" s="7">
+        <v>1602</v>
+      </c>
+      <c r="C134">
+        <f t="shared" si="19"/>
+        <v>1201602</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
+      <c r="F134" t="s">
+        <v>47</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1021602.png</v>
+      </c>
+      <c r="I134">
+        <f t="shared" si="21"/>
+        <v>2021602</v>
+      </c>
+      <c r="K134" s="7">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>3003</v>
+      </c>
+      <c r="M134"/>
+      <c r="N134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A135">
+        <f t="shared" si="18"/>
+        <v>1021801</v>
+      </c>
+      <c r="B135" s="7">
+        <v>1801</v>
+      </c>
+      <c r="C135">
+        <f t="shared" si="19"/>
+        <v>1201801</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
+      <c r="F135" t="s">
+        <v>47</v>
+      </c>
+      <c r="G135">
+        <v>1</v>
+      </c>
+      <c r="H135" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1021801.png</v>
+      </c>
+      <c r="I135">
+        <f t="shared" si="21"/>
+        <v>2021801</v>
+      </c>
+      <c r="K135" s="7">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>4002</v>
+      </c>
+      <c r="M135"/>
+      <c r="N135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A136">
+        <f t="shared" si="18"/>
+        <v>1021802</v>
+      </c>
+      <c r="B136" s="7">
+        <v>1802</v>
+      </c>
+      <c r="C136">
+        <f t="shared" si="19"/>
+        <v>1201802</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E136">
+        <v>2</v>
+      </c>
+      <c r="F136" t="s">
+        <v>47</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="H136" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1021802.png</v>
+      </c>
+      <c r="I136">
+        <f t="shared" si="21"/>
+        <v>2021802</v>
+      </c>
+      <c r="K136" s="7">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>4003</v>
+      </c>
+      <c r="M136"/>
+      <c r="N136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A137">
+        <f t="shared" si="18"/>
+        <v>1022001</v>
+      </c>
+      <c r="B137" s="7">
+        <v>2001</v>
+      </c>
+      <c r="C137">
+        <f t="shared" si="19"/>
+        <v>1202001</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E137">
+        <v>2</v>
+      </c>
+      <c r="F137" t="s">
+        <v>47</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1022001.png</v>
+      </c>
+      <c r="I137">
+        <f t="shared" si="21"/>
+        <v>2022001</v>
+      </c>
+      <c r="K137" s="7">
+        <v>1</v>
+      </c>
+      <c r="L137">
+        <v>5002</v>
+      </c>
+      <c r="M137"/>
+      <c r="N137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A138">
+        <f t="shared" si="18"/>
+        <v>1022002</v>
+      </c>
+      <c r="B138" s="7">
+        <v>2002</v>
+      </c>
+      <c r="C138">
+        <f t="shared" si="19"/>
+        <v>1202002</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E138">
+        <v>2</v>
+      </c>
+      <c r="F138" t="s">
+        <v>47</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1022002.png</v>
+      </c>
+      <c r="I138">
+        <f t="shared" si="21"/>
+        <v>2022002</v>
+      </c>
+      <c r="K138" s="7">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>5003</v>
+      </c>
+      <c r="M138"/>
+      <c r="N138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A139">
+        <f t="shared" si="18"/>
+        <v>1022201</v>
+      </c>
+      <c r="B139" s="7">
+        <v>2201</v>
+      </c>
+      <c r="C139">
+        <f t="shared" si="19"/>
+        <v>1202201</v>
+      </c>
+      <c r="D139" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E139">
+        <v>2</v>
+      </c>
+      <c r="F139" t="s">
+        <v>47</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+      <c r="H139" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1022201.png</v>
+      </c>
+      <c r="I139">
+        <f t="shared" si="21"/>
+        <v>2022201</v>
+      </c>
+      <c r="K139" s="7">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>6002</v>
+      </c>
+      <c r="M139"/>
+      <c r="N139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A140">
+        <f t="shared" si="18"/>
+        <v>1022202</v>
+      </c>
+      <c r="B140" s="7">
+        <v>2202</v>
+      </c>
+      <c r="C140">
+        <f t="shared" si="19"/>
+        <v>1202202</v>
+      </c>
+      <c r="D140" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="E140">
+        <v>2</v>
+      </c>
+      <c r="F140" t="s">
+        <v>47</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="H140" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1022202.png</v>
+      </c>
+      <c r="I140">
+        <f t="shared" si="21"/>
+        <v>2022202</v>
+      </c>
+      <c r="K140" s="7">
+        <v>1</v>
+      </c>
+      <c r="L140">
+        <v>6003</v>
+      </c>
+      <c r="M140"/>
+      <c r="N140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1" spans="1:14">
+      <c r="A141">
+        <f t="shared" si="18"/>
+        <v>1022501</v>
+      </c>
+      <c r="B141">
+        <v>2501</v>
+      </c>
+      <c r="C141">
+        <f t="shared" si="19"/>
+        <v>1202501</v>
+      </c>
+      <c r="D141" t="s">
+        <v>180</v>
+      </c>
+      <c r="E141">
+        <v>2</v>
+      </c>
+      <c r="F141" t="s">
+        <v>47</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+      <c r="H141" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1022501.png</v>
+      </c>
+      <c r="I141">
+        <f t="shared" si="21"/>
+        <v>2022501</v>
+      </c>
+      <c r="J141" t="s">
+        <v>181</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="142" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A142">
+        <v>1023001</v>
+      </c>
+      <c r="B142" s="7"/>
+      <c r="C142">
+        <v>1023001</v>
+      </c>
+      <c r="D142" t="s">
+        <v>182</v>
+      </c>
+      <c r="E142">
+        <v>2</v>
+      </c>
+      <c r="F142" t="s">
+        <v>47</v>
+      </c>
+      <c r="G142">
+        <v>2</v>
+      </c>
+      <c r="H142" t="s">
+        <v>183</v>
+      </c>
+      <c r="I142">
+        <v>2023001</v>
+      </c>
+      <c r="J142" t="s">
+        <v>184</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="143" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A143">
+        <v>1023002</v>
+      </c>
+      <c r="B143" s="7"/>
+      <c r="C143">
+        <v>1023002</v>
+      </c>
+      <c r="D143" t="s">
+        <v>185</v>
+      </c>
+      <c r="E143">
+        <v>2</v>
+      </c>
+      <c r="F143" t="s">
+        <v>47</v>
+      </c>
+      <c r="G143">
+        <v>3</v>
+      </c>
+      <c r="H143" t="s">
+        <v>186</v>
+      </c>
+      <c r="I143">
+        <v>2023002</v>
+      </c>
+      <c r="J143" t="s">
+        <v>184</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="144" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A144">
+        <v>1023003</v>
+      </c>
+      <c r="B144" s="7"/>
+      <c r="C144">
+        <v>1023003</v>
+      </c>
+      <c r="D144" t="s">
+        <v>187</v>
+      </c>
+      <c r="E144">
+        <v>2</v>
+      </c>
+      <c r="F144" t="s">
+        <v>47</v>
+      </c>
+      <c r="G144">
+        <v>4</v>
+      </c>
+      <c r="H144" t="s">
+        <v>188</v>
+      </c>
+      <c r="I144">
+        <v>2023003</v>
+      </c>
+      <c r="J144" t="s">
+        <v>184</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="145" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A145">
+        <v>1023004</v>
+      </c>
+      <c r="B145" s="7"/>
+      <c r="C145">
+        <v>1023004</v>
+      </c>
+      <c r="D145" t="s">
+        <v>189</v>
+      </c>
+      <c r="E145">
+        <v>2</v>
+      </c>
+      <c r="F145" t="s">
+        <v>47</v>
+      </c>
+      <c r="G145">
+        <v>5</v>
+      </c>
+      <c r="H145" t="s">
+        <v>190</v>
+      </c>
+      <c r="I145">
+        <v>2023004</v>
+      </c>
+      <c r="J145" t="s">
+        <v>184</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="146" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A146">
+        <v>1023005</v>
+      </c>
+      <c r="B146" s="7"/>
+      <c r="C146">
+        <v>1023005</v>
+      </c>
+      <c r="D146" t="s">
+        <v>191</v>
+      </c>
+      <c r="E146">
+        <v>2</v>
+      </c>
+      <c r="F146" t="s">
+        <v>47</v>
+      </c>
+      <c r="G146">
+        <v>6</v>
+      </c>
+      <c r="H146" t="s">
+        <v>192</v>
+      </c>
+      <c r="I146">
+        <v>2023005</v>
+      </c>
+      <c r="J146" t="s">
+        <v>184</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A147">
+        <v>1023101</v>
+      </c>
+      <c r="B147" s="7"/>
+      <c r="C147">
+        <v>1023101</v>
+      </c>
+      <c r="D147" t="s">
+        <v>193</v>
+      </c>
+      <c r="E147">
+        <v>2</v>
+      </c>
+      <c r="F147" t="s">
+        <v>47</v>
+      </c>
+      <c r="G147">
+        <v>2</v>
+      </c>
+      <c r="H147" t="s">
+        <v>194</v>
+      </c>
+      <c r="I147">
+        <v>2023101</v>
+      </c>
+      <c r="J147" t="s">
+        <v>195</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A148">
+        <v>1023102</v>
+      </c>
+      <c r="B148" s="7"/>
+      <c r="C148">
+        <v>1023102</v>
+      </c>
+      <c r="D148" t="s">
+        <v>196</v>
+      </c>
+      <c r="E148">
+        <v>2</v>
+      </c>
+      <c r="F148" t="s">
+        <v>47</v>
+      </c>
+      <c r="G148">
+        <v>3</v>
+      </c>
+      <c r="H148" t="s">
+        <v>197</v>
+      </c>
+      <c r="I148">
+        <v>2023102</v>
+      </c>
+      <c r="J148" t="s">
+        <v>195</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A149">
+        <v>1023103</v>
+      </c>
+      <c r="B149" s="7"/>
+      <c r="C149">
+        <v>1023103</v>
+      </c>
+      <c r="D149" t="s">
+        <v>198</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+      <c r="F149" t="s">
+        <v>47</v>
+      </c>
+      <c r="G149">
+        <v>4</v>
+      </c>
+      <c r="H149" t="s">
+        <v>199</v>
+      </c>
+      <c r="I149">
+        <v>2023103</v>
+      </c>
+      <c r="J149" t="s">
+        <v>195</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A150">
+        <v>1023104</v>
+      </c>
+      <c r="B150" s="7"/>
+      <c r="C150">
+        <v>1023104</v>
+      </c>
+      <c r="D150" t="s">
+        <v>200</v>
+      </c>
+      <c r="E150">
+        <v>2</v>
+      </c>
+      <c r="F150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G150">
+        <v>5</v>
+      </c>
+      <c r="H150" t="s">
+        <v>201</v>
+      </c>
+      <c r="I150">
+        <v>2023104</v>
+      </c>
+      <c r="J150" t="s">
+        <v>195</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A151">
+        <v>1023105</v>
+      </c>
+      <c r="B151" s="7"/>
+      <c r="C151">
+        <v>1023105</v>
+      </c>
+      <c r="D151" t="s">
+        <v>202</v>
+      </c>
+      <c r="E151">
+        <v>2</v>
+      </c>
+      <c r="F151" t="s">
+        <v>47</v>
+      </c>
+      <c r="G151">
+        <v>6</v>
+      </c>
+      <c r="H151" t="s">
+        <v>203</v>
+      </c>
+      <c r="I151">
+        <v>2023105</v>
+      </c>
+      <c r="J151" t="s">
+        <v>195</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A152">
+        <v>1023201</v>
+      </c>
+      <c r="B152" s="7"/>
+      <c r="C152">
+        <v>1023201</v>
+      </c>
+      <c r="D152" t="s">
+        <v>204</v>
+      </c>
+      <c r="E152">
+        <v>2</v>
+      </c>
+      <c r="F152" t="s">
+        <v>47</v>
+      </c>
+      <c r="G152">
+        <v>2</v>
+      </c>
+      <c r="H152" t="s">
+        <v>205</v>
+      </c>
+      <c r="I152">
+        <v>2023201</v>
+      </c>
+      <c r="J152" t="s">
+        <v>206</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A153">
+        <v>1023202</v>
+      </c>
+      <c r="B153" s="7"/>
+      <c r="C153">
+        <v>1023202</v>
+      </c>
+      <c r="D153" t="s">
+        <v>207</v>
+      </c>
+      <c r="E153">
+        <v>2</v>
+      </c>
+      <c r="F153" t="s">
+        <v>47</v>
+      </c>
+      <c r="G153">
+        <v>3</v>
+      </c>
+      <c r="H153" t="s">
+        <v>208</v>
+      </c>
+      <c r="I153">
+        <v>2023202</v>
+      </c>
+      <c r="J153" t="s">
+        <v>206</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A154">
+        <v>1023203</v>
+      </c>
+      <c r="B154" s="7"/>
+      <c r="C154">
+        <v>1023203</v>
+      </c>
+      <c r="D154" t="s">
+        <v>209</v>
+      </c>
+      <c r="E154">
+        <v>2</v>
+      </c>
+      <c r="F154" t="s">
+        <v>47</v>
+      </c>
+      <c r="G154">
+        <v>4</v>
+      </c>
+      <c r="H154" t="s">
+        <v>210</v>
+      </c>
+      <c r="I154">
+        <v>2023203</v>
+      </c>
+      <c r="J154" t="s">
+        <v>206</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A155">
+        <v>1023204</v>
+      </c>
+      <c r="B155" s="7"/>
+      <c r="C155">
+        <v>1023204</v>
+      </c>
+      <c r="D155" t="s">
+        <v>211</v>
+      </c>
+      <c r="E155">
+        <v>2</v>
+      </c>
+      <c r="F155" t="s">
+        <v>47</v>
+      </c>
+      <c r="G155">
+        <v>5</v>
+      </c>
+      <c r="H155" t="s">
+        <v>212</v>
+      </c>
+      <c r="I155">
+        <v>2023204</v>
+      </c>
+      <c r="J155" t="s">
+        <v>206</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A156">
+        <v>1023205</v>
+      </c>
+      <c r="B156" s="7"/>
+      <c r="C156">
+        <v>1023205</v>
+      </c>
+      <c r="D156" t="s">
+        <v>213</v>
+      </c>
+      <c r="E156">
+        <v>2</v>
+      </c>
+      <c r="F156" t="s">
+        <v>47</v>
+      </c>
+      <c r="G156">
+        <v>6</v>
+      </c>
+      <c r="H156" t="s">
+        <v>214</v>
+      </c>
+      <c r="I156">
+        <v>2023205</v>
+      </c>
+      <c r="J156" t="s">
+        <v>206</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A157">
+        <v>1023301</v>
+      </c>
+      <c r="B157" s="7"/>
+      <c r="C157">
+        <v>1023301</v>
+      </c>
+      <c r="D157" t="s">
+        <v>215</v>
+      </c>
+      <c r="E157">
+        <v>2</v>
+      </c>
+      <c r="F157" t="s">
+        <v>47</v>
+      </c>
+      <c r="G157">
+        <v>2</v>
+      </c>
+      <c r="H157" t="s">
+        <v>216</v>
+      </c>
+      <c r="I157">
+        <v>2023301</v>
+      </c>
+      <c r="J157" t="s">
+        <v>217</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A158">
+        <v>1023302</v>
+      </c>
+      <c r="B158" s="7"/>
+      <c r="C158">
+        <v>1023302</v>
+      </c>
+      <c r="D158" t="s">
+        <v>218</v>
+      </c>
+      <c r="E158">
+        <v>2</v>
+      </c>
+      <c r="F158" t="s">
+        <v>47</v>
+      </c>
+      <c r="G158">
+        <v>3</v>
+      </c>
+      <c r="H158" t="s">
+        <v>219</v>
+      </c>
+      <c r="I158">
+        <v>2023302</v>
+      </c>
+      <c r="J158" t="s">
+        <v>217</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="N158">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A159">
+        <v>1023303</v>
+      </c>
+      <c r="B159" s="7"/>
+      <c r="C159">
+        <v>1023303</v>
+      </c>
+      <c r="D159" t="s">
+        <v>220</v>
+      </c>
+      <c r="E159">
+        <v>2</v>
+      </c>
+      <c r="F159" t="s">
+        <v>47</v>
+      </c>
+      <c r="G159">
+        <v>4</v>
+      </c>
+      <c r="H159" t="s">
+        <v>221</v>
+      </c>
+      <c r="I159">
+        <v>2023303</v>
+      </c>
+      <c r="J159" t="s">
+        <v>217</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A160">
+        <v>1023304</v>
+      </c>
+      <c r="B160" s="7"/>
+      <c r="C160">
+        <v>1023304</v>
+      </c>
+      <c r="D160" t="s">
+        <v>222</v>
+      </c>
+      <c r="E160">
+        <v>2</v>
+      </c>
+      <c r="F160" t="s">
+        <v>47</v>
+      </c>
+      <c r="G160">
+        <v>5</v>
+      </c>
+      <c r="H160" t="s">
+        <v>223</v>
+      </c>
+      <c r="I160">
+        <v>2023304</v>
+      </c>
+      <c r="J160" t="s">
+        <v>217</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A161">
+        <v>1023305</v>
+      </c>
+      <c r="B161" s="7"/>
+      <c r="C161">
+        <v>1023305</v>
+      </c>
+      <c r="D161" t="s">
+        <v>224</v>
+      </c>
+      <c r="E161">
+        <v>2</v>
+      </c>
+      <c r="F161" t="s">
+        <v>47</v>
+      </c>
+      <c r="G161">
+        <v>6</v>
+      </c>
+      <c r="H161" t="s">
+        <v>225</v>
+      </c>
+      <c r="I161">
+        <v>2023305</v>
+      </c>
+      <c r="J161" t="s">
+        <v>217</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="N161">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A162">
+        <v>1023401</v>
+      </c>
+      <c r="B162" s="7"/>
+      <c r="C162">
+        <v>1023401</v>
+      </c>
+      <c r="D162" t="s">
+        <v>226</v>
+      </c>
+      <c r="E162">
+        <v>2</v>
+      </c>
+      <c r="F162" t="s">
+        <v>47</v>
+      </c>
+      <c r="G162">
+        <v>2</v>
+      </c>
+      <c r="H162" t="s">
+        <v>227</v>
+      </c>
+      <c r="I162">
+        <v>2023401</v>
+      </c>
+      <c r="J162" t="s">
+        <v>228</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="N162">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A163">
+        <v>1023402</v>
+      </c>
+      <c r="B163" s="7"/>
+      <c r="C163">
+        <v>1023402</v>
+      </c>
+      <c r="D163" t="s">
+        <v>229</v>
+      </c>
+      <c r="E163">
+        <v>2</v>
+      </c>
+      <c r="F163" t="s">
+        <v>47</v>
+      </c>
+      <c r="G163">
+        <v>3</v>
+      </c>
+      <c r="H163" t="s">
+        <v>230</v>
+      </c>
+      <c r="I163">
+        <v>2023402</v>
+      </c>
+      <c r="J163" t="s">
+        <v>228</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A164">
+        <v>1023403</v>
+      </c>
+      <c r="B164" s="7"/>
+      <c r="C164">
+        <v>1023403</v>
+      </c>
+      <c r="D164" t="s">
+        <v>231</v>
+      </c>
+      <c r="E164">
+        <v>2</v>
+      </c>
+      <c r="F164" t="s">
+        <v>47</v>
+      </c>
+      <c r="G164">
+        <v>4</v>
+      </c>
+      <c r="H164" t="s">
+        <v>232</v>
+      </c>
+      <c r="I164">
+        <v>2023403</v>
+      </c>
+      <c r="J164" t="s">
+        <v>228</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A165">
+        <v>1023404</v>
+      </c>
+      <c r="B165" s="7"/>
+      <c r="C165">
+        <v>1023404</v>
+      </c>
+      <c r="D165" t="s">
+        <v>233</v>
+      </c>
+      <c r="E165">
+        <v>2</v>
+      </c>
+      <c r="F165" t="s">
+        <v>47</v>
+      </c>
+      <c r="G165">
+        <v>5</v>
+      </c>
+      <c r="H165" t="s">
+        <v>234</v>
+      </c>
+      <c r="I165">
+        <v>2023404</v>
+      </c>
+      <c r="J165" t="s">
+        <v>228</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A166">
+        <v>1023405</v>
+      </c>
+      <c r="B166" s="7"/>
+      <c r="C166">
+        <v>1023405</v>
+      </c>
+      <c r="D166" t="s">
+        <v>235</v>
+      </c>
+      <c r="E166">
+        <v>2</v>
+      </c>
+      <c r="F166" t="s">
+        <v>47</v>
+      </c>
+      <c r="G166">
+        <v>6</v>
+      </c>
+      <c r="H166" t="s">
+        <v>236</v>
+      </c>
+      <c r="I166">
+        <v>2023405</v>
+      </c>
+      <c r="J166" t="s">
+        <v>228</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="167" ht="21" customHeight="1" spans="1:14">
+      <c r="A167">
+        <f>1000000+E167*10000+B167</f>
+        <v>1990000</v>
+      </c>
+      <c r="B167" s="7">
+        <v>0</v>
+      </c>
+      <c r="C167">
+        <v>1990000</v>
+      </c>
+      <c r="D167" t="s">
+        <v>237</v>
+      </c>
+      <c r="E167">
+        <v>99</v>
+      </c>
+      <c r="F167" t="s">
+        <v>238</v>
+      </c>
+      <c r="G167">
+        <v>1</v>
+      </c>
+      <c r="H167" t="str">
+        <f>"itemicon_"&amp;A167&amp;".png"</f>
+        <v>itemicon_1990000.png</v>
+      </c>
+      <c r="I167">
+        <f>2000000+E167*10000+B167</f>
+        <v>2990000</v>
+      </c>
+      <c r="J167" t="s">
+        <v>239</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="168" ht="21" customHeight="1" spans="1:14">
+      <c r="A168">
+        <f>1000000+E168*10000+B168</f>
+        <v>1980000</v>
+      </c>
+      <c r="B168" s="7">
+        <v>0</v>
+      </c>
+      <c r="C168">
+        <v>1980000</v>
+      </c>
+      <c r="D168" t="s">
+        <v>240</v>
+      </c>
+      <c r="E168">
+        <v>98</v>
+      </c>
+      <c r="F168" t="s">
+        <v>238</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168" t="str">
+        <f>"itemicon_"&amp;A168&amp;".png"</f>
+        <v>itemicon_1980000.png</v>
+      </c>
+      <c r="I168">
+        <f>2000000+E168*10000+B168</f>
+        <v>2980000</v>
+      </c>
+      <c r="J168" t="s">
+        <v>241</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="N168">
         <v>-1</v>
       </c>
     </row>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -176,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F167" authorId="0">
+    <comment ref="F168" authorId="0">
       <text>
         <r>
           <rPr>
@@ -203,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="245">
   <si>
     <t>道具ID</t>
   </si>
@@ -749,6 +749,15 @@
   </si>
   <si>
     <t>在搖錢樹活動中祈福使用，可在指定禮包中購買獲得</t>
+  </si>
+  <si>
+    <t>刮刮卡</t>
+  </si>
+  <si>
+    <t>itemicon_1022501.png</t>
+  </si>
+  <si>
+    <t>在指定的游戏中产出</t>
   </si>
   <si>
     <t>1星扳手</t>
@@ -2196,7 +2205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P168"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
@@ -6100,7 +6109,7 @@
         <v>65</v>
       </c>
       <c r="I94">
-        <f t="shared" ref="I94:I124" si="15">2000000+E94*10000+B94</f>
+        <f t="shared" ref="I94:I128" si="15">2000000+E94*10000+B94</f>
         <v>2020206</v>
       </c>
       <c r="J94" t="s">
@@ -6279,14 +6288,14 @@
     </row>
     <row r="99" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A99">
-        <f t="shared" ref="A99:A124" si="16">1000000+E99*10000+B99</f>
+        <f t="shared" ref="A99:A130" si="16">1000000+E99*10000+B99</f>
         <v>1020211</v>
       </c>
       <c r="B99" s="7">
         <v>211</v>
       </c>
       <c r="C99">
-        <f t="shared" ref="C99:C124" si="17">1000000+E99*100000+B99</f>
+        <f t="shared" ref="C99:C128" si="17">1000000+E99*100000+B99</f>
         <v>1200211</v>
       </c>
       <c r="D99" t="s">
@@ -7345,14 +7354,14 @@
     </row>
     <row r="125" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A125">
-        <f>1000000+E125*10000+B125</f>
+        <f t="shared" si="16"/>
         <v>1021001</v>
       </c>
       <c r="B125" s="7">
         <v>1001</v>
       </c>
       <c r="C125">
-        <f>1000000+E125*100000+B125</f>
+        <f t="shared" si="17"/>
         <v>1201001</v>
       </c>
       <c r="D125" s="7" t="s">
@@ -7372,7 +7381,7 @@
         <v>itemicon_1021001.png</v>
       </c>
       <c r="I125">
-        <f>2000000+E125*10000+B125</f>
+        <f t="shared" si="15"/>
         <v>2021001</v>
       </c>
       <c r="K125" s="7">
@@ -7388,14 +7397,14 @@
     </row>
     <row r="126" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A126">
-        <f>1000000+E126*10000+B126</f>
+        <f t="shared" si="16"/>
         <v>1021002</v>
       </c>
       <c r="B126" s="7">
         <v>1002</v>
       </c>
       <c r="C126">
-        <f>1000000+E126*100000+B126</f>
+        <f t="shared" si="17"/>
         <v>1201002</v>
       </c>
       <c r="D126" s="7" t="s">
@@ -7415,7 +7424,7 @@
         <v>itemicon_1021002.png</v>
       </c>
       <c r="I126">
-        <f>2000000+E126*10000+B126</f>
+        <f t="shared" si="15"/>
         <v>2021002</v>
       </c>
       <c r="K126" s="7">
@@ -7431,14 +7440,14 @@
     </row>
     <row r="127" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A127">
-        <f>1000000+E127*10000+B127</f>
+        <f t="shared" si="16"/>
         <v>1021201</v>
       </c>
       <c r="B127" s="7">
         <v>1201</v>
       </c>
       <c r="C127">
-        <f>1000000+E127*100000+B127</f>
+        <f t="shared" si="17"/>
         <v>1201201</v>
       </c>
       <c r="D127" t="s">
@@ -7458,7 +7467,7 @@
         <v>itemicon_1021201.png</v>
       </c>
       <c r="I127">
-        <f>2000000+E127*10000+B127</f>
+        <f t="shared" si="15"/>
         <v>2021201</v>
       </c>
       <c r="K127" s="7">
@@ -7474,14 +7483,14 @@
     </row>
     <row r="128" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A128">
-        <f>1000000+E128*10000+B128</f>
+        <f t="shared" si="16"/>
         <v>1021202</v>
       </c>
       <c r="B128" s="7">
         <v>1202</v>
       </c>
       <c r="C128">
-        <f>1000000+E128*100000+B128</f>
+        <f t="shared" si="17"/>
         <v>1201202</v>
       </c>
       <c r="D128" t="s">
@@ -7501,7 +7510,7 @@
         <v>itemicon_1021202.png</v>
       </c>
       <c r="I128">
-        <f>2000000+E128*10000+B128</f>
+        <f t="shared" si="15"/>
         <v>2021202</v>
       </c>
       <c r="K128" s="7">
@@ -7517,7 +7526,7 @@
     </row>
     <row r="129" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A129">
-        <f>1000000+E129*10000+B129</f>
+        <f t="shared" si="16"/>
         <v>1021350</v>
       </c>
       <c r="B129" s="7">
@@ -7556,7 +7565,7 @@
     </row>
     <row r="130" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A130">
-        <f>1000000+E130*10000+B130</f>
+        <f t="shared" si="16"/>
         <v>1021351</v>
       </c>
       <c r="B130" s="7">
@@ -7602,7 +7611,7 @@
         <v>1401</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:C141" si="19">1000000+E131*100000+B131</f>
+        <f t="shared" ref="C131:C142" si="19">1000000+E131*100000+B131</f>
         <v>1201401</v>
       </c>
       <c r="D131" s="10" t="s">
@@ -8065,13 +8074,17 @@
         <v>999</v>
       </c>
     </row>
-    <row r="142" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="142" customFormat="1" ht="18" customHeight="1" spans="1:14">
       <c r="A142">
-        <v>1023001</v>
-      </c>
-      <c r="B142" s="7"/>
+        <f t="shared" si="18"/>
+        <v>1022502</v>
+      </c>
+      <c r="B142">
+        <v>2502</v>
+      </c>
       <c r="C142">
-        <v>1023001</v>
+        <f t="shared" si="19"/>
+        <v>1202502</v>
       </c>
       <c r="D142" t="s">
         <v>182</v>
@@ -8083,13 +8096,14 @@
         <v>47</v>
       </c>
       <c r="G142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142" t="s">
         <v>183</v>
       </c>
       <c r="I142">
-        <v>2023001</v>
+        <f t="shared" si="21"/>
+        <v>2022502</v>
       </c>
       <c r="J142" t="s">
         <v>184</v>
@@ -8103,11 +8117,11 @@
     </row>
     <row r="143" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A143">
-        <v>1023002</v>
+        <v>1023001</v>
       </c>
       <c r="B143" s="7"/>
       <c r="C143">
-        <v>1023002</v>
+        <v>1023001</v>
       </c>
       <c r="D143" t="s">
         <v>185</v>
@@ -8119,16 +8133,16 @@
         <v>47</v>
       </c>
       <c r="G143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H143" t="s">
         <v>186</v>
       </c>
       <c r="I143">
-        <v>2023002</v>
+        <v>2023001</v>
       </c>
       <c r="J143" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -8139,32 +8153,32 @@
     </row>
     <row r="144" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A144">
-        <v>1023003</v>
+        <v>1023002</v>
       </c>
       <c r="B144" s="7"/>
       <c r="C144">
-        <v>1023003</v>
+        <v>1023002</v>
       </c>
       <c r="D144" t="s">
+        <v>188</v>
+      </c>
+      <c r="E144">
+        <v>2</v>
+      </c>
+      <c r="F144" t="s">
+        <v>47</v>
+      </c>
+      <c r="G144">
+        <v>3</v>
+      </c>
+      <c r="H144" t="s">
+        <v>189</v>
+      </c>
+      <c r="I144">
+        <v>2023002</v>
+      </c>
+      <c r="J144" t="s">
         <v>187</v>
-      </c>
-      <c r="E144">
-        <v>2</v>
-      </c>
-      <c r="F144" t="s">
-        <v>47</v>
-      </c>
-      <c r="G144">
-        <v>4</v>
-      </c>
-      <c r="H144" t="s">
-        <v>188</v>
-      </c>
-      <c r="I144">
-        <v>2023003</v>
-      </c>
-      <c r="J144" t="s">
-        <v>184</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -8175,14 +8189,14 @@
     </row>
     <row r="145" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A145">
-        <v>1023004</v>
+        <v>1023003</v>
       </c>
       <c r="B145" s="7"/>
       <c r="C145">
-        <v>1023004</v>
+        <v>1023003</v>
       </c>
       <c r="D145" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E145">
         <v>2</v>
@@ -8191,16 +8205,16 @@
         <v>47</v>
       </c>
       <c r="G145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H145" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I145">
-        <v>2023004</v>
+        <v>2023003</v>
       </c>
       <c r="J145" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -8211,14 +8225,14 @@
     </row>
     <row r="146" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A146">
-        <v>1023005</v>
+        <v>1023004</v>
       </c>
       <c r="B146" s="7"/>
       <c r="C146">
-        <v>1023005</v>
+        <v>1023004</v>
       </c>
       <c r="D146" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E146">
         <v>2</v>
@@ -8227,16 +8241,16 @@
         <v>47</v>
       </c>
       <c r="G146">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H146" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I146">
-        <v>2023005</v>
+        <v>2023004</v>
       </c>
       <c r="J146" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K146">
         <v>0</v>
@@ -8247,14 +8261,14 @@
     </row>
     <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A147">
-        <v>1023101</v>
+        <v>1023005</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147">
-        <v>1023101</v>
+        <v>1023005</v>
       </c>
       <c r="D147" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E147">
         <v>2</v>
@@ -8263,16 +8277,16 @@
         <v>47</v>
       </c>
       <c r="G147">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H147" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I147">
-        <v>2023101</v>
+        <v>2023005</v>
       </c>
       <c r="J147" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -8283,11 +8297,11 @@
     </row>
     <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A148">
-        <v>1023102</v>
+        <v>1023101</v>
       </c>
       <c r="B148" s="7"/>
       <c r="C148">
-        <v>1023102</v>
+        <v>1023101</v>
       </c>
       <c r="D148" t="s">
         <v>196</v>
@@ -8299,16 +8313,16 @@
         <v>47</v>
       </c>
       <c r="G148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H148" t="s">
         <v>197</v>
       </c>
       <c r="I148">
-        <v>2023102</v>
+        <v>2023101</v>
       </c>
       <c r="J148" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -8319,32 +8333,32 @@
     </row>
     <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A149">
-        <v>1023103</v>
+        <v>1023102</v>
       </c>
       <c r="B149" s="7"/>
       <c r="C149">
-        <v>1023103</v>
+        <v>1023102</v>
       </c>
       <c r="D149" t="s">
+        <v>199</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+      <c r="F149" t="s">
+        <v>47</v>
+      </c>
+      <c r="G149">
+        <v>3</v>
+      </c>
+      <c r="H149" t="s">
+        <v>200</v>
+      </c>
+      <c r="I149">
+        <v>2023102</v>
+      </c>
+      <c r="J149" t="s">
         <v>198</v>
-      </c>
-      <c r="E149">
-        <v>2</v>
-      </c>
-      <c r="F149" t="s">
-        <v>47</v>
-      </c>
-      <c r="G149">
-        <v>4</v>
-      </c>
-      <c r="H149" t="s">
-        <v>199</v>
-      </c>
-      <c r="I149">
-        <v>2023103</v>
-      </c>
-      <c r="J149" t="s">
-        <v>195</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -8355,14 +8369,14 @@
     </row>
     <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A150">
-        <v>1023104</v>
+        <v>1023103</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150">
-        <v>1023104</v>
+        <v>1023103</v>
       </c>
       <c r="D150" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E150">
         <v>2</v>
@@ -8371,16 +8385,16 @@
         <v>47</v>
       </c>
       <c r="G150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H150" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I150">
-        <v>2023104</v>
+        <v>2023103</v>
       </c>
       <c r="J150" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -8391,14 +8405,14 @@
     </row>
     <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A151">
-        <v>1023105</v>
+        <v>1023104</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151">
-        <v>1023105</v>
+        <v>1023104</v>
       </c>
       <c r="D151" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E151">
         <v>2</v>
@@ -8407,16 +8421,16 @@
         <v>47</v>
       </c>
       <c r="G151">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H151" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I151">
-        <v>2023105</v>
+        <v>2023104</v>
       </c>
       <c r="J151" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K151">
         <v>0</v>
@@ -8427,14 +8441,14 @@
     </row>
     <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A152">
-        <v>1023201</v>
+        <v>1023105</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152">
-        <v>1023201</v>
+        <v>1023105</v>
       </c>
       <c r="D152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -8443,16 +8457,16 @@
         <v>47</v>
       </c>
       <c r="G152">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H152" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I152">
-        <v>2023201</v>
+        <v>2023105</v>
       </c>
       <c r="J152" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="K152">
         <v>0</v>
@@ -8463,11 +8477,11 @@
     </row>
     <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A153">
-        <v>1023202</v>
+        <v>1023201</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153">
-        <v>1023202</v>
+        <v>1023201</v>
       </c>
       <c r="D153" t="s">
         <v>207</v>
@@ -8479,16 +8493,16 @@
         <v>47</v>
       </c>
       <c r="G153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H153" t="s">
         <v>208</v>
       </c>
       <c r="I153">
-        <v>2023202</v>
+        <v>2023201</v>
       </c>
       <c r="J153" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K153">
         <v>0</v>
@@ -8499,32 +8513,32 @@
     </row>
     <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A154">
-        <v>1023203</v>
+        <v>1023202</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154">
-        <v>1023203</v>
+        <v>1023202</v>
       </c>
       <c r="D154" t="s">
+        <v>210</v>
+      </c>
+      <c r="E154">
+        <v>2</v>
+      </c>
+      <c r="F154" t="s">
+        <v>47</v>
+      </c>
+      <c r="G154">
+        <v>3</v>
+      </c>
+      <c r="H154" t="s">
+        <v>211</v>
+      </c>
+      <c r="I154">
+        <v>2023202</v>
+      </c>
+      <c r="J154" t="s">
         <v>209</v>
-      </c>
-      <c r="E154">
-        <v>2</v>
-      </c>
-      <c r="F154" t="s">
-        <v>47</v>
-      </c>
-      <c r="G154">
-        <v>4</v>
-      </c>
-      <c r="H154" t="s">
-        <v>210</v>
-      </c>
-      <c r="I154">
-        <v>2023203</v>
-      </c>
-      <c r="J154" t="s">
-        <v>206</v>
       </c>
       <c r="K154">
         <v>0</v>
@@ -8535,14 +8549,14 @@
     </row>
     <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A155">
-        <v>1023204</v>
+        <v>1023203</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155">
-        <v>1023204</v>
+        <v>1023203</v>
       </c>
       <c r="D155" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -8551,16 +8565,16 @@
         <v>47</v>
       </c>
       <c r="G155">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H155" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I155">
-        <v>2023204</v>
+        <v>2023203</v>
       </c>
       <c r="J155" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K155">
         <v>0</v>
@@ -8571,14 +8585,14 @@
     </row>
     <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A156">
-        <v>1023205</v>
+        <v>1023204</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156">
-        <v>1023205</v>
+        <v>1023204</v>
       </c>
       <c r="D156" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E156">
         <v>2</v>
@@ -8587,16 +8601,16 @@
         <v>47</v>
       </c>
       <c r="G156">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H156" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I156">
-        <v>2023205</v>
+        <v>2023204</v>
       </c>
       <c r="J156" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K156">
         <v>0</v>
@@ -8607,14 +8621,14 @@
     </row>
     <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A157">
-        <v>1023301</v>
+        <v>1023205</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157">
-        <v>1023301</v>
+        <v>1023205</v>
       </c>
       <c r="D157" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -8623,16 +8637,16 @@
         <v>47</v>
       </c>
       <c r="G157">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H157" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I157">
-        <v>2023301</v>
+        <v>2023205</v>
       </c>
       <c r="J157" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="K157">
         <v>0</v>
@@ -8643,11 +8657,11 @@
     </row>
     <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A158">
-        <v>1023302</v>
+        <v>1023301</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158">
-        <v>1023302</v>
+        <v>1023301</v>
       </c>
       <c r="D158" t="s">
         <v>218</v>
@@ -8659,16 +8673,16 @@
         <v>47</v>
       </c>
       <c r="G158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H158" t="s">
         <v>219</v>
       </c>
       <c r="I158">
-        <v>2023302</v>
+        <v>2023301</v>
       </c>
       <c r="J158" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K158">
         <v>0</v>
@@ -8679,32 +8693,32 @@
     </row>
     <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A159">
-        <v>1023303</v>
+        <v>1023302</v>
       </c>
       <c r="B159" s="7"/>
       <c r="C159">
-        <v>1023303</v>
+        <v>1023302</v>
       </c>
       <c r="D159" t="s">
+        <v>221</v>
+      </c>
+      <c r="E159">
+        <v>2</v>
+      </c>
+      <c r="F159" t="s">
+        <v>47</v>
+      </c>
+      <c r="G159">
+        <v>3</v>
+      </c>
+      <c r="H159" t="s">
+        <v>222</v>
+      </c>
+      <c r="I159">
+        <v>2023302</v>
+      </c>
+      <c r="J159" t="s">
         <v>220</v>
-      </c>
-      <c r="E159">
-        <v>2</v>
-      </c>
-      <c r="F159" t="s">
-        <v>47</v>
-      </c>
-      <c r="G159">
-        <v>4</v>
-      </c>
-      <c r="H159" t="s">
-        <v>221</v>
-      </c>
-      <c r="I159">
-        <v>2023303</v>
-      </c>
-      <c r="J159" t="s">
-        <v>217</v>
       </c>
       <c r="K159">
         <v>0</v>
@@ -8715,14 +8729,14 @@
     </row>
     <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A160">
-        <v>1023304</v>
+        <v>1023303</v>
       </c>
       <c r="B160" s="7"/>
       <c r="C160">
-        <v>1023304</v>
+        <v>1023303</v>
       </c>
       <c r="D160" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E160">
         <v>2</v>
@@ -8731,16 +8745,16 @@
         <v>47</v>
       </c>
       <c r="G160">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H160" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I160">
-        <v>2023304</v>
+        <v>2023303</v>
       </c>
       <c r="J160" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K160">
         <v>0</v>
@@ -8751,14 +8765,14 @@
     </row>
     <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A161">
-        <v>1023305</v>
+        <v>1023304</v>
       </c>
       <c r="B161" s="7"/>
       <c r="C161">
-        <v>1023305</v>
+        <v>1023304</v>
       </c>
       <c r="D161" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -8767,16 +8781,16 @@
         <v>47</v>
       </c>
       <c r="G161">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H161" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I161">
-        <v>2023305</v>
+        <v>2023304</v>
       </c>
       <c r="J161" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K161">
         <v>0</v>
@@ -8787,14 +8801,14 @@
     </row>
     <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A162">
-        <v>1023401</v>
+        <v>1023305</v>
       </c>
       <c r="B162" s="7"/>
       <c r="C162">
-        <v>1023401</v>
+        <v>1023305</v>
       </c>
       <c r="D162" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -8803,16 +8817,16 @@
         <v>47</v>
       </c>
       <c r="G162">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H162" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I162">
-        <v>2023401</v>
+        <v>2023305</v>
       </c>
       <c r="J162" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="K162">
         <v>0</v>
@@ -8823,11 +8837,11 @@
     </row>
     <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A163">
-        <v>1023402</v>
+        <v>1023401</v>
       </c>
       <c r="B163" s="7"/>
       <c r="C163">
-        <v>1023402</v>
+        <v>1023401</v>
       </c>
       <c r="D163" t="s">
         <v>229</v>
@@ -8839,16 +8853,16 @@
         <v>47</v>
       </c>
       <c r="G163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H163" t="s">
         <v>230</v>
       </c>
       <c r="I163">
-        <v>2023402</v>
+        <v>2023401</v>
       </c>
       <c r="J163" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K163">
         <v>0</v>
@@ -8859,32 +8873,32 @@
     </row>
     <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A164">
-        <v>1023403</v>
+        <v>1023402</v>
       </c>
       <c r="B164" s="7"/>
       <c r="C164">
-        <v>1023403</v>
+        <v>1023402</v>
       </c>
       <c r="D164" t="s">
+        <v>232</v>
+      </c>
+      <c r="E164">
+        <v>2</v>
+      </c>
+      <c r="F164" t="s">
+        <v>47</v>
+      </c>
+      <c r="G164">
+        <v>3</v>
+      </c>
+      <c r="H164" t="s">
+        <v>233</v>
+      </c>
+      <c r="I164">
+        <v>2023402</v>
+      </c>
+      <c r="J164" t="s">
         <v>231</v>
-      </c>
-      <c r="E164">
-        <v>2</v>
-      </c>
-      <c r="F164" t="s">
-        <v>47</v>
-      </c>
-      <c r="G164">
-        <v>4</v>
-      </c>
-      <c r="H164" t="s">
-        <v>232</v>
-      </c>
-      <c r="I164">
-        <v>2023403</v>
-      </c>
-      <c r="J164" t="s">
-        <v>228</v>
       </c>
       <c r="K164">
         <v>0</v>
@@ -8895,14 +8909,14 @@
     </row>
     <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A165">
-        <v>1023404</v>
+        <v>1023403</v>
       </c>
       <c r="B165" s="7"/>
       <c r="C165">
-        <v>1023404</v>
+        <v>1023403</v>
       </c>
       <c r="D165" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E165">
         <v>2</v>
@@ -8911,16 +8925,16 @@
         <v>47</v>
       </c>
       <c r="G165">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H165" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I165">
-        <v>2023404</v>
+        <v>2023403</v>
       </c>
       <c r="J165" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K165">
         <v>0</v>
@@ -8931,14 +8945,14 @@
     </row>
     <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A166">
-        <v>1023405</v>
+        <v>1023404</v>
       </c>
       <c r="B166" s="7"/>
       <c r="C166">
-        <v>1023405</v>
+        <v>1023404</v>
       </c>
       <c r="D166" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -8947,16 +8961,16 @@
         <v>47</v>
       </c>
       <c r="G166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H166" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I166">
-        <v>2023405</v>
+        <v>2023404</v>
       </c>
       <c r="J166" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K166">
         <v>0</v>
@@ -8965,85 +8979,121 @@
         <v>999</v>
       </c>
     </row>
-    <row r="167" ht="21" customHeight="1" spans="1:14">
+    <row r="167" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A167">
-        <f>1000000+E167*10000+B167</f>
-        <v>1990000</v>
-      </c>
-      <c r="B167" s="7">
-        <v>0</v>
-      </c>
+        <v>1023405</v>
+      </c>
+      <c r="B167" s="7"/>
       <c r="C167">
-        <v>1990000</v>
+        <v>1023405</v>
       </c>
       <c r="D167" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E167">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>238</v>
+        <v>47</v>
       </c>
       <c r="G167">
-        <v>1</v>
-      </c>
-      <c r="H167" t="str">
-        <f>"itemicon_"&amp;A167&amp;".png"</f>
-        <v>itemicon_1990000.png</v>
+        <v>6</v>
+      </c>
+      <c r="H167" t="s">
+        <v>239</v>
       </c>
       <c r="I167">
-        <f>2000000+E167*10000+B167</f>
-        <v>2990000</v>
+        <v>2023405</v>
       </c>
       <c r="J167" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="K167">
         <v>0</v>
       </c>
       <c r="N167">
-        <v>-1</v>
+        <v>999</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1" spans="1:14">
       <c r="A168">
         <f>1000000+E168*10000+B168</f>
-        <v>1980000</v>
+        <v>1990000</v>
       </c>
       <c r="B168" s="7">
         <v>0</v>
       </c>
       <c r="C168">
-        <v>1980000</v>
+        <v>1990000</v>
       </c>
       <c r="D168" t="s">
         <v>240</v>
       </c>
       <c r="E168">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F168" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G168">
         <v>1</v>
       </c>
       <c r="H168" t="str">
         <f>"itemicon_"&amp;A168&amp;".png"</f>
-        <v>itemicon_1980000.png</v>
+        <v>itemicon_1990000.png</v>
       </c>
       <c r="I168">
         <f>2000000+E168*10000+B168</f>
+        <v>2990000</v>
+      </c>
+      <c r="J168" t="s">
+        <v>242</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="169" ht="21" customHeight="1" spans="1:14">
+      <c r="A169">
+        <f>1000000+E169*10000+B169</f>
+        <v>1980000</v>
+      </c>
+      <c r="B169" s="7">
+        <v>0</v>
+      </c>
+      <c r="C169">
+        <v>1980000</v>
+      </c>
+      <c r="D169" t="s">
+        <v>243</v>
+      </c>
+      <c r="E169">
+        <v>98</v>
+      </c>
+      <c r="F169" t="s">
+        <v>241</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+      <c r="H169" t="str">
+        <f>"itemicon_"&amp;A169&amp;".png"</f>
+        <v>itemicon_1980000.png</v>
+      </c>
+      <c r="I169">
+        <f>2000000+E169*10000+B169</f>
         <v>2980000</v>
       </c>
-      <c r="J168" t="s">
-        <v>241</v>
-      </c>
-      <c r="K168">
-        <v>0</v>
-      </c>
-      <c r="N168">
+      <c r="J169" t="s">
+        <v>244</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="N169">
         <v>-1</v>
       </c>
     </row>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -52,6 +52,7 @@
           <t xml:space="preserve">
 1：可使用道具
 2：常规道具
+3：自动使用（激活）
 ---------------
 每种货币一个类型ID
 99:金币
@@ -87,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -105,7 +106,9 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-自动使用并删除此道具</t>
+当值为1时，不在背包内显示
+为0时，不处理
+</t>
         </r>
       </text>
     </comment>
@@ -220,15 +223,15 @@
     <t>道具品质</t>
   </si>
   <si>
+    <t>是否允许在背包内展示</t>
+  </si>
+  <si>
     <t>图标资源名</t>
   </si>
   <si>
     <t>描述多语言ID</t>
   </si>
   <si>
-    <t>获得后是否使用并激活装扮和图鉴</t>
-  </si>
-  <si>
     <t>激活的装扮</t>
   </si>
   <si>
@@ -265,13 +268,13 @@
     <t>quality</t>
   </si>
   <si>
+    <t>displayOrNot</t>
+  </si>
+  <si>
     <t>icon</t>
   </si>
   <si>
     <t>text</t>
-  </si>
-  <si>
-    <t>autoActivate</t>
   </si>
   <si>
     <t>avatarID</t>
@@ -2214,10 +2217,10 @@
     <col min="5" max="5" width="5.5" customWidth="1"/>
     <col min="6" max="6" width="10.875" customWidth="1"/>
     <col min="7" max="7" width="8.875" customWidth="1"/>
-    <col min="8" max="8" width="22.625" customWidth="1"/>
-    <col min="9" max="9" width="12.0583333333333" customWidth="1"/>
-    <col min="10" max="10" width="28.825" customWidth="1"/>
-    <col min="11" max="11" width="27.2083333333333" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="22.625" customWidth="1"/>
+    <col min="10" max="10" width="12.0583333333333" customWidth="1"/>
+    <col min="11" max="11" width="28.825" customWidth="1"/>
     <col min="12" max="12" width="10.875" customWidth="1"/>
     <col min="13" max="13" width="17.25" customWidth="1"/>
     <col min="14" max="14" width="12.2" customWidth="1"/>
@@ -2247,10 +2250,10 @@
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
       <c r="L1" t="s">
@@ -2286,15 +2289,15 @@
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
@@ -2330,10 +2333,10 @@
       <c r="H3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K3" t="s">
+      <c r="J3" t="s">
         <v>22</v>
       </c>
       <c r="L3" t="s">
@@ -2379,19 +2382,19 @@
       <c r="G5">
         <v>4</v>
       </c>
-      <c r="H5" t="str">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="str">
         <f>"itemicon_"&amp;A5&amp;".png"</f>
         <v>itemicon_1010101.png</v>
       </c>
-      <c r="I5">
-        <f t="shared" ref="I5:I14" si="1">2000000+E5*10000+B5</f>
+      <c r="J5">
+        <f t="shared" ref="J5:J14" si="1">2000000+E5*10000+B5</f>
         <v>2010101</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>30</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
       </c>
       <c r="N5">
         <v>999</v>
@@ -2423,19 +2426,19 @@
       <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6" t="str">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="str">
         <f>"itemicon_"&amp;A6&amp;".png"</f>
         <v>itemicon_1010201.png</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <f t="shared" si="1"/>
         <v>2010201</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>33</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
       </c>
       <c r="N6">
         <v>999</v>
@@ -2468,18 +2471,18 @@
       <c r="G7" s="1">
         <v>3</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <f t="shared" si="1"/>
         <v>2010301</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
       </c>
       <c r="N7" s="1">
         <v>999</v>
@@ -2513,18 +2516,18 @@
       <c r="G8" s="1">
         <v>4</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <f t="shared" si="1"/>
         <v>2010302</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
       </c>
       <c r="N8" s="1">
         <v>999</v>
@@ -2558,18 +2561,18 @@
       <c r="G9" s="1">
         <v>5</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <f t="shared" si="1"/>
         <v>2010303</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
       </c>
       <c r="N9" s="1">
         <v>999</v>
@@ -2603,18 +2606,18 @@
       <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <f t="shared" si="1"/>
         <v>2010311</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
       </c>
       <c r="N10" s="1">
         <v>999</v>
@@ -2648,18 +2651,18 @@
       <c r="G11" s="1">
         <v>3</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <f t="shared" si="1"/>
         <v>2010312</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
       </c>
       <c r="N11" s="1">
         <v>999</v>
@@ -2693,18 +2696,18 @@
       <c r="G12" s="1">
         <v>4</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <f t="shared" si="1"/>
         <v>2010313</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
       </c>
       <c r="N12" s="1">
         <v>999</v>
@@ -2738,18 +2741,18 @@
       <c r="G13" s="1">
         <v>5</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <f t="shared" si="1"/>
         <v>2010314</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
       </c>
       <c r="N13" s="1">
         <v>999</v>
@@ -2783,18 +2786,18 @@
       <c r="G14" s="1">
         <v>6</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <f t="shared" si="1"/>
         <v>2010315</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
       </c>
       <c r="N14" s="1">
         <v>999</v>
@@ -2828,19 +2831,19 @@
       <c r="G15">
         <v>1</v>
       </c>
-      <c r="H15" t="str">
-        <f t="shared" ref="H15:H28" si="4">"itemicon_"&amp;A15&amp;".png"</f>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" ref="I15:I28" si="4">"itemicon_"&amp;A15&amp;".png"</f>
         <v>itemicon_1020001.png</v>
       </c>
-      <c r="I15">
-        <f t="shared" ref="I15:I29" si="5">2000000+E15*10000+B15</f>
+      <c r="J15">
+        <f t="shared" ref="J15:J29" si="5">2000000+E15*10000+B15</f>
         <v>2020001</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>48</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
       </c>
       <c r="N15">
         <v>999</v>
@@ -2870,19 +2873,19 @@
       <c r="G16" s="2">
         <v>2</v>
       </c>
-      <c r="H16" s="2" t="str">
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="str">
         <f t="shared" si="4"/>
         <v>itemicon_1020002.png</v>
       </c>
-      <c r="I16" s="2">
+      <c r="J16" s="2">
         <f t="shared" si="5"/>
         <v>2020002</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="K16" s="2">
-        <v>0</v>
       </c>
       <c r="N16" s="2">
         <v>999</v>
@@ -2912,19 +2915,19 @@
       <c r="G17" s="2">
         <v>3</v>
       </c>
-      <c r="H17" s="2" t="str">
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="str">
         <f t="shared" si="4"/>
         <v>itemicon_1020003.png</v>
       </c>
-      <c r="I17" s="2">
+      <c r="J17" s="2">
         <f t="shared" si="5"/>
         <v>2020003</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="K17" s="2">
-        <v>0</v>
       </c>
       <c r="N17" s="2">
         <v>999</v>
@@ -2954,19 +2957,19 @@
       <c r="G18" s="2">
         <v>4</v>
       </c>
-      <c r="H18" s="2" t="str">
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="str">
         <f t="shared" si="4"/>
         <v>itemicon_1020004.png</v>
       </c>
-      <c r="I18" s="2">
+      <c r="J18" s="2">
         <f t="shared" si="5"/>
         <v>2020004</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="K18" s="2">
-        <v>0</v>
       </c>
       <c r="N18" s="2">
         <v>999</v>
@@ -2996,19 +2999,19 @@
       <c r="G19" s="2">
         <v>5</v>
       </c>
-      <c r="H19" s="2" t="str">
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2" t="str">
         <f t="shared" si="4"/>
         <v>itemicon_1020005.png</v>
       </c>
-      <c r="I19" s="2">
+      <c r="J19" s="2">
         <f t="shared" si="5"/>
         <v>2020005</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="K19" s="2">
-        <v>0</v>
       </c>
       <c r="N19" s="2">
         <v>999</v>
@@ -3038,19 +3041,19 @@
       <c r="G20" s="2">
         <v>6</v>
       </c>
-      <c r="H20" s="2" t="str">
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="str">
         <f t="shared" si="4"/>
         <v>itemicon_1020006.png</v>
       </c>
-      <c r="I20" s="2">
+      <c r="J20" s="2">
         <f t="shared" si="5"/>
         <v>2020006</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="K20" s="2">
-        <v>0</v>
       </c>
       <c r="N20" s="2">
         <v>999</v>
@@ -3059,20 +3062,20 @@
     <row r="21" ht="23" customHeight="1" spans="1:14">
       <c r="A21">
         <f t="shared" si="3"/>
-        <v>1020011</v>
+        <v>1030011</v>
       </c>
       <c r="B21" s="7">
         <v>11</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:C29" si="6">1000000+E21*100000+B21</f>
-        <v>1200011</v>
+        <v>1300011</v>
       </c>
       <c r="D21" t="s">
         <v>55</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
         <v>47</v>
@@ -3080,19 +3083,19 @@
       <c r="G21">
         <v>1</v>
       </c>
-      <c r="H21" t="str">
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020011.png</v>
-      </c>
-      <c r="I21">
+        <v>itemicon_1030011.png</v>
+      </c>
+      <c r="J21">
         <f t="shared" si="5"/>
-        <v>2020011</v>
-      </c>
-      <c r="J21" t="s">
+        <v>2030011</v>
+      </c>
+      <c r="K21" t="s">
         <v>56</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
       </c>
       <c r="M21">
         <v>10001</v>
@@ -3104,20 +3107,20 @@
     <row r="22" ht="23" customHeight="1" spans="1:14">
       <c r="A22">
         <f t="shared" si="3"/>
-        <v>1020012</v>
+        <v>1030012</v>
       </c>
       <c r="B22" s="7">
         <v>12</v>
       </c>
       <c r="C22">
         <f t="shared" si="6"/>
-        <v>1200012</v>
+        <v>1300012</v>
       </c>
       <c r="D22" t="s">
         <v>57</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
         <v>47</v>
@@ -3125,19 +3128,19 @@
       <c r="G22">
         <v>1</v>
       </c>
-      <c r="H22" t="str">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020012.png</v>
-      </c>
-      <c r="I22">
+        <v>itemicon_1030012.png</v>
+      </c>
+      <c r="J22">
         <f t="shared" si="5"/>
-        <v>2020012</v>
-      </c>
-      <c r="J22" t="s">
+        <v>2030012</v>
+      </c>
+      <c r="K22" t="s">
         <v>56</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
       </c>
       <c r="M22">
         <v>10002</v>
@@ -3149,20 +3152,20 @@
     <row r="23" ht="23" customHeight="1" spans="1:14">
       <c r="A23">
         <f t="shared" si="3"/>
-        <v>1020013</v>
+        <v>1030013</v>
       </c>
       <c r="B23" s="7">
         <v>13</v>
       </c>
       <c r="C23">
         <f t="shared" si="6"/>
-        <v>1200013</v>
+        <v>1300013</v>
       </c>
       <c r="D23" t="s">
         <v>58</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="s">
         <v>47</v>
@@ -3170,19 +3173,19 @@
       <c r="G23">
         <v>1</v>
       </c>
-      <c r="H23" t="str">
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020013.png</v>
-      </c>
-      <c r="I23">
+        <v>itemicon_1030013.png</v>
+      </c>
+      <c r="J23">
         <f t="shared" si="5"/>
-        <v>2020013</v>
-      </c>
-      <c r="J23" t="s">
+        <v>2030013</v>
+      </c>
+      <c r="K23" t="s">
         <v>56</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
       </c>
       <c r="M23">
         <v>10003</v>
@@ -3194,20 +3197,20 @@
     <row r="24" ht="23" customHeight="1" spans="1:14">
       <c r="A24">
         <f t="shared" si="3"/>
-        <v>1020014</v>
+        <v>1030014</v>
       </c>
       <c r="B24" s="7">
         <v>14</v>
       </c>
       <c r="C24">
         <f t="shared" si="6"/>
-        <v>1200014</v>
+        <v>1300014</v>
       </c>
       <c r="D24" t="s">
         <v>59</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="s">
         <v>47</v>
@@ -3215,19 +3218,19 @@
       <c r="G24">
         <v>1</v>
       </c>
-      <c r="H24" t="str">
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020014.png</v>
-      </c>
-      <c r="I24">
+        <v>itemicon_1030014.png</v>
+      </c>
+      <c r="J24">
         <f t="shared" si="5"/>
-        <v>2020014</v>
-      </c>
-      <c r="J24" t="s">
+        <v>2030014</v>
+      </c>
+      <c r="K24" t="s">
         <v>56</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
       </c>
       <c r="M24">
         <v>10004</v>
@@ -3239,20 +3242,20 @@
     <row r="25" ht="23" customHeight="1" spans="1:14">
       <c r="A25">
         <f t="shared" si="3"/>
-        <v>1020015</v>
+        <v>1030015</v>
       </c>
       <c r="B25" s="7">
         <v>15</v>
       </c>
       <c r="C25">
         <f t="shared" si="6"/>
-        <v>1200015</v>
+        <v>1300015</v>
       </c>
       <c r="D25" t="s">
         <v>60</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="s">
         <v>47</v>
@@ -3260,19 +3263,19 @@
       <c r="G25">
         <v>1</v>
       </c>
-      <c r="H25" t="str">
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020015.png</v>
-      </c>
-      <c r="I25">
+        <v>itemicon_1030015.png</v>
+      </c>
+      <c r="J25">
         <f t="shared" si="5"/>
-        <v>2020015</v>
-      </c>
-      <c r="J25" t="s">
+        <v>2030015</v>
+      </c>
+      <c r="K25" t="s">
         <v>56</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
       </c>
       <c r="M25">
         <v>10005</v>
@@ -3284,20 +3287,20 @@
     <row r="26" ht="23" customHeight="1" spans="1:14">
       <c r="A26">
         <f t="shared" si="3"/>
-        <v>1020016</v>
+        <v>1030016</v>
       </c>
       <c r="B26" s="7">
         <v>16</v>
       </c>
       <c r="C26">
         <f t="shared" si="6"/>
-        <v>1200016</v>
+        <v>1300016</v>
       </c>
       <c r="D26" t="s">
         <v>61</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="s">
         <v>47</v>
@@ -3305,19 +3308,19 @@
       <c r="G26">
         <v>1</v>
       </c>
-      <c r="H26" t="str">
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020016.png</v>
-      </c>
-      <c r="I26">
+        <v>itemicon_1030016.png</v>
+      </c>
+      <c r="J26">
         <f t="shared" si="5"/>
-        <v>2020016</v>
-      </c>
-      <c r="J26" t="s">
+        <v>2030016</v>
+      </c>
+      <c r="K26" t="s">
         <v>56</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
       </c>
       <c r="M26">
         <v>10006</v>
@@ -3329,20 +3332,20 @@
     <row r="27" ht="23" customHeight="1" spans="1:14">
       <c r="A27">
         <f t="shared" si="3"/>
-        <v>1020017</v>
+        <v>1030017</v>
       </c>
       <c r="B27" s="7">
         <v>17</v>
       </c>
       <c r="C27">
         <f t="shared" si="6"/>
-        <v>1200017</v>
+        <v>1300017</v>
       </c>
       <c r="D27" t="s">
         <v>62</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" t="s">
         <v>47</v>
@@ -3350,19 +3353,19 @@
       <c r="G27">
         <v>1</v>
       </c>
-      <c r="H27" t="str">
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020017.png</v>
-      </c>
-      <c r="I27">
+        <v>itemicon_1030017.png</v>
+      </c>
+      <c r="J27">
         <f t="shared" si="5"/>
-        <v>2020017</v>
-      </c>
-      <c r="J27" t="s">
+        <v>2030017</v>
+      </c>
+      <c r="K27" t="s">
         <v>56</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
       </c>
       <c r="M27">
         <v>10007</v>
@@ -3374,20 +3377,20 @@
     <row r="28" ht="23" customHeight="1" spans="1:14">
       <c r="A28">
         <f t="shared" si="3"/>
-        <v>1020018</v>
+        <v>1030018</v>
       </c>
       <c r="B28" s="7">
         <v>18</v>
       </c>
       <c r="C28">
         <f t="shared" si="6"/>
-        <v>1200018</v>
+        <v>1300018</v>
       </c>
       <c r="D28" t="s">
         <v>63</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="s">
         <v>47</v>
@@ -3395,19 +3398,19 @@
       <c r="G28">
         <v>1</v>
       </c>
-      <c r="H28" t="str">
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020018.png</v>
-      </c>
-      <c r="I28">
+        <v>itemicon_1030018.png</v>
+      </c>
+      <c r="J28">
         <f t="shared" si="5"/>
-        <v>2020018</v>
-      </c>
-      <c r="J28" t="s">
+        <v>2030018</v>
+      </c>
+      <c r="K28" t="s">
         <v>56</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
       </c>
       <c r="M28">
         <v>10008</v>
@@ -3419,20 +3422,20 @@
     <row r="29" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A29">
         <f t="shared" si="3"/>
-        <v>1020101</v>
+        <v>1030101</v>
       </c>
       <c r="B29" s="7">
         <v>101</v>
       </c>
       <c r="C29">
         <f t="shared" si="6"/>
-        <v>1200101</v>
+        <v>1300101</v>
       </c>
       <c r="D29" t="s">
         <v>64</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" t="s">
         <v>47</v>
@@ -3440,18 +3443,18 @@
       <c r="G29">
         <v>1</v>
       </c>
-      <c r="H29" t="s">
-        <v>65</v>
-      </c>
-      <c r="I29">
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29" t="s">
+        <v>65</v>
+      </c>
+      <c r="J29">
         <f t="shared" si="5"/>
-        <v>2020101</v>
-      </c>
-      <c r="J29" t="s">
-        <v>66</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
+        <v>2030101</v>
+      </c>
+      <c r="K29" t="s">
+        <v>66</v>
       </c>
       <c r="N29">
         <v>1</v>
@@ -3460,20 +3463,20 @@
     <row r="30" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A30">
         <f t="shared" ref="A30:A40" si="7">1000000+E30*10000+B30</f>
-        <v>1020102</v>
+        <v>1030102</v>
       </c>
       <c r="B30" s="7">
         <v>102</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="8">1000000+E30*100000+B30</f>
-        <v>1200102</v>
+        <v>1300102</v>
       </c>
       <c r="D30" t="s">
         <v>67</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="s">
         <v>47</v>
@@ -3481,18 +3484,18 @@
       <c r="G30">
         <v>1</v>
       </c>
-      <c r="H30" t="s">
-        <v>65</v>
-      </c>
-      <c r="I30">
-        <f t="shared" ref="I30:I61" si="9">2000000+E30*10000+B30</f>
-        <v>2020102</v>
-      </c>
-      <c r="J30" t="s">
-        <v>66</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>65</v>
+      </c>
+      <c r="J30">
+        <f t="shared" ref="J30:J61" si="9">2000000+E30*10000+B30</f>
+        <v>2030102</v>
+      </c>
+      <c r="K30" t="s">
+        <v>66</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -3501,20 +3504,20 @@
     <row r="31" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A31">
         <f t="shared" si="7"/>
-        <v>1020103</v>
+        <v>1030103</v>
       </c>
       <c r="B31" s="7">
         <v>103</v>
       </c>
       <c r="C31">
         <f t="shared" si="8"/>
-        <v>1200103</v>
+        <v>1300103</v>
       </c>
       <c r="D31" t="s">
         <v>68</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="s">
         <v>47</v>
@@ -3522,18 +3525,18 @@
       <c r="G31">
         <v>2</v>
       </c>
-      <c r="H31" t="s">
-        <v>65</v>
-      </c>
-      <c r="I31">
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>65</v>
+      </c>
+      <c r="J31">
         <f t="shared" si="9"/>
-        <v>2020103</v>
-      </c>
-      <c r="J31" t="s">
-        <v>66</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
+        <v>2030103</v>
+      </c>
+      <c r="K31" t="s">
+        <v>66</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -3542,20 +3545,20 @@
     <row r="32" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A32">
         <f t="shared" si="7"/>
-        <v>1020104</v>
+        <v>1030104</v>
       </c>
       <c r="B32" s="7">
         <v>104</v>
       </c>
       <c r="C32">
         <f t="shared" si="8"/>
-        <v>1200104</v>
+        <v>1300104</v>
       </c>
       <c r="D32" t="s">
         <v>69</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="s">
         <v>47</v>
@@ -3563,18 +3566,18 @@
       <c r="G32">
         <v>2</v>
       </c>
-      <c r="H32" t="s">
-        <v>65</v>
-      </c>
-      <c r="I32">
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>65</v>
+      </c>
+      <c r="J32">
         <f t="shared" si="9"/>
-        <v>2020104</v>
-      </c>
-      <c r="J32" t="s">
-        <v>66</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
+        <v>2030104</v>
+      </c>
+      <c r="K32" t="s">
+        <v>66</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -3583,20 +3586,20 @@
     <row r="33" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A33">
         <f t="shared" si="7"/>
-        <v>1020105</v>
+        <v>1030105</v>
       </c>
       <c r="B33" s="7">
         <v>105</v>
       </c>
       <c r="C33">
         <f t="shared" si="8"/>
-        <v>1200105</v>
+        <v>1300105</v>
       </c>
       <c r="D33" t="s">
         <v>70</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="s">
         <v>47</v>
@@ -3604,18 +3607,18 @@
       <c r="G33">
         <v>3</v>
       </c>
-      <c r="H33" t="s">
-        <v>65</v>
-      </c>
-      <c r="I33">
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>65</v>
+      </c>
+      <c r="J33">
         <f t="shared" si="9"/>
-        <v>2020105</v>
-      </c>
-      <c r="J33" t="s">
-        <v>66</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
+        <v>2030105</v>
+      </c>
+      <c r="K33" t="s">
+        <v>66</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -3624,20 +3627,20 @@
     <row r="34" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A34">
         <f t="shared" si="7"/>
-        <v>1020106</v>
+        <v>1030106</v>
       </c>
       <c r="B34" s="7">
         <v>106</v>
       </c>
       <c r="C34">
         <f t="shared" si="8"/>
-        <v>1200106</v>
+        <v>1300106</v>
       </c>
       <c r="D34" t="s">
         <v>71</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" t="s">
         <v>47</v>
@@ -3645,18 +3648,18 @@
       <c r="G34">
         <v>3</v>
       </c>
-      <c r="H34" t="s">
-        <v>65</v>
-      </c>
-      <c r="I34">
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J34">
         <f t="shared" si="9"/>
-        <v>2020106</v>
-      </c>
-      <c r="J34" t="s">
-        <v>66</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
+        <v>2030106</v>
+      </c>
+      <c r="K34" t="s">
+        <v>66</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -3665,20 +3668,20 @@
     <row r="35" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A35">
         <f t="shared" si="7"/>
-        <v>1020107</v>
+        <v>1030107</v>
       </c>
       <c r="B35" s="7">
         <v>107</v>
       </c>
       <c r="C35">
         <f t="shared" si="8"/>
-        <v>1200107</v>
+        <v>1300107</v>
       </c>
       <c r="D35" t="s">
         <v>72</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" t="s">
         <v>47</v>
@@ -3686,18 +3689,18 @@
       <c r="G35">
         <v>4</v>
       </c>
-      <c r="H35" t="s">
-        <v>65</v>
-      </c>
-      <c r="I35">
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>65</v>
+      </c>
+      <c r="J35">
         <f t="shared" si="9"/>
-        <v>2020107</v>
-      </c>
-      <c r="J35" t="s">
-        <v>66</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
+        <v>2030107</v>
+      </c>
+      <c r="K35" t="s">
+        <v>66</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -3706,20 +3709,20 @@
     <row r="36" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A36">
         <f t="shared" si="7"/>
-        <v>1020108</v>
+        <v>1030108</v>
       </c>
       <c r="B36" s="7">
         <v>108</v>
       </c>
       <c r="C36">
         <f t="shared" si="8"/>
-        <v>1200108</v>
+        <v>1300108</v>
       </c>
       <c r="D36" t="s">
         <v>73</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" t="s">
         <v>47</v>
@@ -3727,18 +3730,18 @@
       <c r="G36">
         <v>4</v>
       </c>
-      <c r="H36" t="s">
-        <v>65</v>
-      </c>
-      <c r="I36">
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36">
         <f t="shared" si="9"/>
-        <v>2020108</v>
-      </c>
-      <c r="J36" t="s">
-        <v>66</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
+        <v>2030108</v>
+      </c>
+      <c r="K36" t="s">
+        <v>66</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -3747,20 +3750,20 @@
     <row r="37" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A37">
         <f t="shared" si="7"/>
-        <v>1020109</v>
+        <v>1030109</v>
       </c>
       <c r="B37" s="7">
         <v>109</v>
       </c>
       <c r="C37">
         <f t="shared" si="8"/>
-        <v>1200109</v>
+        <v>1300109</v>
       </c>
       <c r="D37" t="s">
         <v>74</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" t="s">
         <v>47</v>
@@ -3768,18 +3771,18 @@
       <c r="G37">
         <v>5</v>
       </c>
-      <c r="H37" t="s">
-        <v>65</v>
-      </c>
-      <c r="I37">
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>65</v>
+      </c>
+      <c r="J37">
         <f t="shared" si="9"/>
-        <v>2020109</v>
-      </c>
-      <c r="J37" t="s">
-        <v>66</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
+        <v>2030109</v>
+      </c>
+      <c r="K37" t="s">
+        <v>66</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -3788,20 +3791,20 @@
     <row r="38" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A38">
         <f t="shared" si="7"/>
-        <v>1020110</v>
+        <v>1030110</v>
       </c>
       <c r="B38" s="7">
         <v>110</v>
       </c>
       <c r="C38">
         <f t="shared" si="8"/>
-        <v>1200110</v>
+        <v>1300110</v>
       </c>
       <c r="D38" t="s">
         <v>75</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" t="s">
         <v>47</v>
@@ -3809,18 +3812,18 @@
       <c r="G38">
         <v>5</v>
       </c>
-      <c r="H38" t="s">
-        <v>65</v>
-      </c>
-      <c r="I38">
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38">
         <f t="shared" si="9"/>
-        <v>2020110</v>
-      </c>
-      <c r="J38" t="s">
-        <v>66</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
+        <v>2030110</v>
+      </c>
+      <c r="K38" t="s">
+        <v>66</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -3829,20 +3832,20 @@
     <row r="39" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A39">
         <f t="shared" si="7"/>
-        <v>1020111</v>
+        <v>1030111</v>
       </c>
       <c r="B39" s="7">
         <v>111</v>
       </c>
       <c r="C39">
         <f t="shared" si="8"/>
-        <v>1200111</v>
+        <v>1300111</v>
       </c>
       <c r="D39" t="s">
         <v>76</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" t="s">
         <v>47</v>
@@ -3850,18 +3853,18 @@
       <c r="G39">
         <v>6</v>
       </c>
-      <c r="H39" t="s">
-        <v>65</v>
-      </c>
-      <c r="I39">
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>65</v>
+      </c>
+      <c r="J39">
         <f t="shared" si="9"/>
-        <v>2020111</v>
-      </c>
-      <c r="J39" t="s">
-        <v>66</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
+        <v>2030111</v>
+      </c>
+      <c r="K39" t="s">
+        <v>66</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -3870,20 +3873,20 @@
     <row r="40" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A40">
         <f t="shared" si="7"/>
-        <v>1020112</v>
+        <v>1030112</v>
       </c>
       <c r="B40" s="7">
         <v>112</v>
       </c>
       <c r="C40">
         <f t="shared" si="8"/>
-        <v>1200112</v>
+        <v>1300112</v>
       </c>
       <c r="D40" t="s">
         <v>77</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="s">
         <v>47</v>
@@ -3891,18 +3894,18 @@
       <c r="G40">
         <v>6</v>
       </c>
-      <c r="H40" t="s">
-        <v>65</v>
-      </c>
-      <c r="I40">
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>65</v>
+      </c>
+      <c r="J40">
         <f t="shared" si="9"/>
-        <v>2020112</v>
-      </c>
-      <c r="J40" t="s">
-        <v>66</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
+        <v>2030112</v>
+      </c>
+      <c r="K40" t="s">
+        <v>66</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -3911,20 +3914,20 @@
     <row r="41" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A41">
         <f t="shared" ref="A41:A66" si="10">1000000+E41*10000+B41</f>
-        <v>1020121</v>
+        <v>1030121</v>
       </c>
       <c r="B41" s="7">
         <v>121</v>
       </c>
       <c r="C41">
         <f t="shared" ref="C41:C66" si="11">1000000+E41*100000+B41</f>
-        <v>1200121</v>
+        <v>1300121</v>
       </c>
       <c r="D41" t="s">
         <v>78</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="s">
         <v>47</v>
@@ -3932,18 +3935,18 @@
       <c r="G41">
         <v>1</v>
       </c>
-      <c r="H41" t="s">
-        <v>65</v>
-      </c>
-      <c r="I41">
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>65</v>
+      </c>
+      <c r="J41">
         <f t="shared" si="9"/>
-        <v>2020121</v>
-      </c>
-      <c r="J41" t="s">
-        <v>66</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
+        <v>2030121</v>
+      </c>
+      <c r="K41" t="s">
+        <v>66</v>
       </c>
       <c r="N41">
         <v>1</v>
@@ -3952,20 +3955,20 @@
     <row r="42" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A42">
         <f t="shared" si="10"/>
-        <v>1020122</v>
+        <v>1030122</v>
       </c>
       <c r="B42" s="7">
         <v>122</v>
       </c>
       <c r="C42">
         <f t="shared" si="11"/>
-        <v>1200122</v>
+        <v>1300122</v>
       </c>
       <c r="D42" t="s">
         <v>79</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" t="s">
         <v>47</v>
@@ -3973,18 +3976,18 @@
       <c r="G42">
         <v>1</v>
       </c>
-      <c r="H42" t="s">
-        <v>65</v>
-      </c>
-      <c r="I42">
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>65</v>
+      </c>
+      <c r="J42">
         <f t="shared" si="9"/>
-        <v>2020122</v>
-      </c>
-      <c r="J42" t="s">
-        <v>66</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
+        <v>2030122</v>
+      </c>
+      <c r="K42" t="s">
+        <v>66</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -3993,20 +3996,20 @@
     <row r="43" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A43">
         <f t="shared" si="10"/>
-        <v>1020123</v>
+        <v>1030123</v>
       </c>
       <c r="B43" s="7">
         <v>123</v>
       </c>
       <c r="C43">
         <f t="shared" si="11"/>
-        <v>1200123</v>
+        <v>1300123</v>
       </c>
       <c r="D43" t="s">
         <v>80</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" t="s">
         <v>47</v>
@@ -4014,18 +4017,18 @@
       <c r="G43">
         <v>2</v>
       </c>
-      <c r="H43" t="s">
-        <v>65</v>
-      </c>
-      <c r="I43">
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>65</v>
+      </c>
+      <c r="J43">
         <f t="shared" si="9"/>
-        <v>2020123</v>
-      </c>
-      <c r="J43" t="s">
-        <v>66</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
+        <v>2030123</v>
+      </c>
+      <c r="K43" t="s">
+        <v>66</v>
       </c>
       <c r="N43">
         <v>1</v>
@@ -4034,20 +4037,20 @@
     <row r="44" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A44">
         <f t="shared" si="10"/>
-        <v>1020124</v>
+        <v>1030124</v>
       </c>
       <c r="B44" s="7">
         <v>124</v>
       </c>
       <c r="C44">
         <f t="shared" si="11"/>
-        <v>1200124</v>
+        <v>1300124</v>
       </c>
       <c r="D44" t="s">
         <v>81</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="s">
         <v>47</v>
@@ -4055,18 +4058,18 @@
       <c r="G44">
         <v>2</v>
       </c>
-      <c r="H44" t="s">
-        <v>65</v>
-      </c>
-      <c r="I44">
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>65</v>
+      </c>
+      <c r="J44">
         <f t="shared" si="9"/>
-        <v>2020124</v>
-      </c>
-      <c r="J44" t="s">
-        <v>66</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
+        <v>2030124</v>
+      </c>
+      <c r="K44" t="s">
+        <v>66</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -4075,20 +4078,20 @@
     <row r="45" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A45">
         <f t="shared" si="10"/>
-        <v>1020125</v>
+        <v>1030125</v>
       </c>
       <c r="B45" s="7">
         <v>125</v>
       </c>
       <c r="C45">
         <f t="shared" si="11"/>
-        <v>1200125</v>
+        <v>1300125</v>
       </c>
       <c r="D45" t="s">
         <v>82</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" t="s">
         <v>47</v>
@@ -4096,18 +4099,18 @@
       <c r="G45">
         <v>3</v>
       </c>
-      <c r="H45" t="s">
-        <v>65</v>
-      </c>
-      <c r="I45">
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>65</v>
+      </c>
+      <c r="J45">
         <f t="shared" si="9"/>
-        <v>2020125</v>
-      </c>
-      <c r="J45" t="s">
-        <v>66</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
+        <v>2030125</v>
+      </c>
+      <c r="K45" t="s">
+        <v>66</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -4116,20 +4119,20 @@
     <row r="46" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A46">
         <f t="shared" si="10"/>
-        <v>1020126</v>
+        <v>1030126</v>
       </c>
       <c r="B46" s="7">
         <v>126</v>
       </c>
       <c r="C46">
         <f t="shared" si="11"/>
-        <v>1200126</v>
+        <v>1300126</v>
       </c>
       <c r="D46" t="s">
         <v>83</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="s">
         <v>47</v>
@@ -4137,18 +4140,18 @@
       <c r="G46">
         <v>3</v>
       </c>
-      <c r="H46" t="s">
-        <v>65</v>
-      </c>
-      <c r="I46">
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
+        <v>65</v>
+      </c>
+      <c r="J46">
         <f t="shared" si="9"/>
-        <v>2020126</v>
-      </c>
-      <c r="J46" t="s">
-        <v>66</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
+        <v>2030126</v>
+      </c>
+      <c r="K46" t="s">
+        <v>66</v>
       </c>
       <c r="N46">
         <v>1</v>
@@ -4157,20 +4160,20 @@
     <row r="47" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A47">
         <f t="shared" si="10"/>
-        <v>1020127</v>
+        <v>1030127</v>
       </c>
       <c r="B47" s="7">
         <v>127</v>
       </c>
       <c r="C47">
         <f t="shared" si="11"/>
-        <v>1200127</v>
+        <v>1300127</v>
       </c>
       <c r="D47" t="s">
         <v>84</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" t="s">
         <v>47</v>
@@ -4178,18 +4181,18 @@
       <c r="G47">
         <v>4</v>
       </c>
-      <c r="H47" t="s">
-        <v>65</v>
-      </c>
-      <c r="I47">
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>65</v>
+      </c>
+      <c r="J47">
         <f t="shared" si="9"/>
-        <v>2020127</v>
-      </c>
-      <c r="J47" t="s">
-        <v>66</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
+        <v>2030127</v>
+      </c>
+      <c r="K47" t="s">
+        <v>66</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -4198,20 +4201,20 @@
     <row r="48" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A48">
         <f t="shared" si="10"/>
-        <v>1020128</v>
+        <v>1030128</v>
       </c>
       <c r="B48" s="7">
         <v>128</v>
       </c>
       <c r="C48">
         <f t="shared" si="11"/>
-        <v>1200128</v>
+        <v>1300128</v>
       </c>
       <c r="D48" t="s">
         <v>85</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" t="s">
         <v>47</v>
@@ -4219,18 +4222,18 @@
       <c r="G48">
         <v>4</v>
       </c>
-      <c r="H48" t="s">
-        <v>65</v>
-      </c>
-      <c r="I48">
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>65</v>
+      </c>
+      <c r="J48">
         <f t="shared" si="9"/>
-        <v>2020128</v>
-      </c>
-      <c r="J48" t="s">
-        <v>66</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
+        <v>2030128</v>
+      </c>
+      <c r="K48" t="s">
+        <v>66</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -4239,20 +4242,20 @@
     <row r="49" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A49">
         <f t="shared" si="10"/>
-        <v>1020129</v>
+        <v>1030129</v>
       </c>
       <c r="B49" s="7">
         <v>129</v>
       </c>
       <c r="C49">
         <f t="shared" si="11"/>
-        <v>1200129</v>
+        <v>1300129</v>
       </c>
       <c r="D49" t="s">
         <v>86</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" t="s">
         <v>47</v>
@@ -4260,18 +4263,18 @@
       <c r="G49">
         <v>5</v>
       </c>
-      <c r="H49" t="s">
-        <v>65</v>
-      </c>
-      <c r="I49">
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>65</v>
+      </c>
+      <c r="J49">
         <f t="shared" si="9"/>
-        <v>2020129</v>
-      </c>
-      <c r="J49" t="s">
-        <v>66</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
+        <v>2030129</v>
+      </c>
+      <c r="K49" t="s">
+        <v>66</v>
       </c>
       <c r="N49">
         <v>1</v>
@@ -4280,20 +4283,20 @@
     <row r="50" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A50">
         <f t="shared" si="10"/>
-        <v>1020130</v>
+        <v>1030130</v>
       </c>
       <c r="B50" s="7">
         <v>130</v>
       </c>
       <c r="C50">
         <f t="shared" si="11"/>
-        <v>1200130</v>
+        <v>1300130</v>
       </c>
       <c r="D50" t="s">
         <v>87</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" t="s">
         <v>47</v>
@@ -4301,18 +4304,18 @@
       <c r="G50">
         <v>5</v>
       </c>
-      <c r="H50" t="s">
-        <v>65</v>
-      </c>
-      <c r="I50">
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>65</v>
+      </c>
+      <c r="J50">
         <f t="shared" si="9"/>
-        <v>2020130</v>
-      </c>
-      <c r="J50" t="s">
-        <v>66</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
+        <v>2030130</v>
+      </c>
+      <c r="K50" t="s">
+        <v>66</v>
       </c>
       <c r="N50">
         <v>1</v>
@@ -4321,20 +4324,20 @@
     <row r="51" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A51">
         <f t="shared" si="10"/>
-        <v>1020131</v>
+        <v>1030131</v>
       </c>
       <c r="B51" s="7">
         <v>131</v>
       </c>
       <c r="C51">
         <f t="shared" si="11"/>
-        <v>1200131</v>
+        <v>1300131</v>
       </c>
       <c r="D51" t="s">
         <v>88</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" t="s">
         <v>47</v>
@@ -4342,18 +4345,18 @@
       <c r="G51">
         <v>6</v>
       </c>
-      <c r="H51" t="s">
-        <v>65</v>
-      </c>
-      <c r="I51">
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>65</v>
+      </c>
+      <c r="J51">
         <f t="shared" si="9"/>
-        <v>2020131</v>
-      </c>
-      <c r="J51" t="s">
-        <v>66</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
+        <v>2030131</v>
+      </c>
+      <c r="K51" t="s">
+        <v>66</v>
       </c>
       <c r="N51">
         <v>1</v>
@@ -4362,20 +4365,20 @@
     <row r="52" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A52">
         <f t="shared" si="10"/>
-        <v>1020132</v>
+        <v>1030132</v>
       </c>
       <c r="B52" s="7">
         <v>132</v>
       </c>
       <c r="C52">
         <f t="shared" si="11"/>
-        <v>1200132</v>
+        <v>1300132</v>
       </c>
       <c r="D52" t="s">
         <v>89</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" t="s">
         <v>47</v>
@@ -4383,18 +4386,18 @@
       <c r="G52">
         <v>6</v>
       </c>
-      <c r="H52" t="s">
-        <v>65</v>
-      </c>
-      <c r="I52">
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52" t="s">
+        <v>65</v>
+      </c>
+      <c r="J52">
         <f t="shared" si="9"/>
-        <v>2020132</v>
-      </c>
-      <c r="J52" t="s">
-        <v>66</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
+        <v>2030132</v>
+      </c>
+      <c r="K52" t="s">
+        <v>66</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -4403,20 +4406,20 @@
     <row r="53" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A53">
         <f t="shared" si="10"/>
-        <v>1020141</v>
+        <v>1030141</v>
       </c>
       <c r="B53" s="7">
         <v>141</v>
       </c>
       <c r="C53">
         <f t="shared" si="11"/>
-        <v>1200141</v>
+        <v>1300141</v>
       </c>
       <c r="D53" t="s">
         <v>90</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" t="s">
         <v>47</v>
@@ -4424,18 +4427,18 @@
       <c r="G53">
         <v>1</v>
       </c>
-      <c r="H53" t="s">
-        <v>65</v>
-      </c>
-      <c r="I53">
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53" t="s">
+        <v>65</v>
+      </c>
+      <c r="J53">
         <f t="shared" si="9"/>
-        <v>2020141</v>
-      </c>
-      <c r="J53" t="s">
-        <v>66</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
+        <v>2030141</v>
+      </c>
+      <c r="K53" t="s">
+        <v>66</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -4444,20 +4447,20 @@
     <row r="54" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A54">
         <f t="shared" si="10"/>
-        <v>1020142</v>
+        <v>1030142</v>
       </c>
       <c r="B54" s="7">
         <v>142</v>
       </c>
       <c r="C54">
         <f t="shared" si="11"/>
-        <v>1200142</v>
+        <v>1300142</v>
       </c>
       <c r="D54" t="s">
         <v>91</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" t="s">
         <v>47</v>
@@ -4465,18 +4468,18 @@
       <c r="G54">
         <v>1</v>
       </c>
-      <c r="H54" t="s">
-        <v>65</v>
-      </c>
-      <c r="I54">
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54" t="s">
+        <v>65</v>
+      </c>
+      <c r="J54">
         <f t="shared" si="9"/>
-        <v>2020142</v>
-      </c>
-      <c r="J54" t="s">
-        <v>66</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
+        <v>2030142</v>
+      </c>
+      <c r="K54" t="s">
+        <v>66</v>
       </c>
       <c r="N54">
         <v>1</v>
@@ -4485,20 +4488,20 @@
     <row r="55" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A55">
         <f t="shared" si="10"/>
-        <v>1020143</v>
+        <v>1030143</v>
       </c>
       <c r="B55" s="7">
         <v>143</v>
       </c>
       <c r="C55">
         <f t="shared" si="11"/>
-        <v>1200143</v>
+        <v>1300143</v>
       </c>
       <c r="D55" t="s">
         <v>92</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="s">
         <v>47</v>
@@ -4506,18 +4509,18 @@
       <c r="G55">
         <v>2</v>
       </c>
-      <c r="H55" t="s">
-        <v>65</v>
-      </c>
-      <c r="I55">
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55" t="s">
+        <v>65</v>
+      </c>
+      <c r="J55">
         <f t="shared" si="9"/>
-        <v>2020143</v>
-      </c>
-      <c r="J55" t="s">
-        <v>66</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
+        <v>2030143</v>
+      </c>
+      <c r="K55" t="s">
+        <v>66</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -4526,20 +4529,20 @@
     <row r="56" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A56">
         <f t="shared" si="10"/>
-        <v>1020144</v>
+        <v>1030144</v>
       </c>
       <c r="B56" s="7">
         <v>144</v>
       </c>
       <c r="C56">
         <f t="shared" si="11"/>
-        <v>1200144</v>
+        <v>1300144</v>
       </c>
       <c r="D56" t="s">
         <v>93</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="s">
         <v>47</v>
@@ -4547,18 +4550,18 @@
       <c r="G56">
         <v>2</v>
       </c>
-      <c r="H56" t="s">
-        <v>65</v>
-      </c>
-      <c r="I56">
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56" t="s">
+        <v>65</v>
+      </c>
+      <c r="J56">
         <f t="shared" si="9"/>
-        <v>2020144</v>
-      </c>
-      <c r="J56" t="s">
-        <v>66</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
+        <v>2030144</v>
+      </c>
+      <c r="K56" t="s">
+        <v>66</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -4567,20 +4570,20 @@
     <row r="57" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A57">
         <f t="shared" si="10"/>
-        <v>1020145</v>
+        <v>1030145</v>
       </c>
       <c r="B57" s="7">
         <v>145</v>
       </c>
       <c r="C57">
         <f t="shared" si="11"/>
-        <v>1200145</v>
+        <v>1300145</v>
       </c>
       <c r="D57" t="s">
         <v>94</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="s">
         <v>47</v>
@@ -4588,18 +4591,18 @@
       <c r="G57">
         <v>3</v>
       </c>
-      <c r="H57" t="s">
-        <v>65</v>
-      </c>
-      <c r="I57">
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>65</v>
+      </c>
+      <c r="J57">
         <f t="shared" si="9"/>
-        <v>2020145</v>
-      </c>
-      <c r="J57" t="s">
-        <v>66</v>
-      </c>
-      <c r="K57">
-        <v>0</v>
+        <v>2030145</v>
+      </c>
+      <c r="K57" t="s">
+        <v>66</v>
       </c>
       <c r="N57">
         <v>1</v>
@@ -4608,20 +4611,20 @@
     <row r="58" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A58">
         <f t="shared" si="10"/>
-        <v>1020146</v>
+        <v>1030146</v>
       </c>
       <c r="B58" s="7">
         <v>146</v>
       </c>
       <c r="C58">
         <f t="shared" si="11"/>
-        <v>1200146</v>
+        <v>1300146</v>
       </c>
       <c r="D58" t="s">
         <v>95</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" t="s">
         <v>47</v>
@@ -4629,18 +4632,18 @@
       <c r="G58">
         <v>3</v>
       </c>
-      <c r="H58" t="s">
-        <v>65</v>
-      </c>
-      <c r="I58">
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58" t="s">
+        <v>65</v>
+      </c>
+      <c r="J58">
         <f t="shared" si="9"/>
-        <v>2020146</v>
-      </c>
-      <c r="J58" t="s">
-        <v>66</v>
-      </c>
-      <c r="K58">
-        <v>0</v>
+        <v>2030146</v>
+      </c>
+      <c r="K58" t="s">
+        <v>66</v>
       </c>
       <c r="N58">
         <v>1</v>
@@ -4649,20 +4652,20 @@
     <row r="59" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A59">
         <f t="shared" si="10"/>
-        <v>1020147</v>
+        <v>1030147</v>
       </c>
       <c r="B59" s="7">
         <v>147</v>
       </c>
       <c r="C59">
         <f t="shared" si="11"/>
-        <v>1200147</v>
+        <v>1300147</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" t="s">
         <v>47</v>
@@ -4670,18 +4673,18 @@
       <c r="G59">
         <v>4</v>
       </c>
-      <c r="H59" t="s">
-        <v>65</v>
-      </c>
-      <c r="I59">
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59" t="s">
+        <v>65</v>
+      </c>
+      <c r="J59">
         <f t="shared" si="9"/>
-        <v>2020147</v>
-      </c>
-      <c r="J59" t="s">
-        <v>66</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
+        <v>2030147</v>
+      </c>
+      <c r="K59" t="s">
+        <v>66</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -4690,20 +4693,20 @@
     <row r="60" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A60">
         <f t="shared" si="10"/>
-        <v>1020148</v>
+        <v>1030148</v>
       </c>
       <c r="B60" s="7">
         <v>148</v>
       </c>
       <c r="C60">
         <f t="shared" si="11"/>
-        <v>1200148</v>
+        <v>1300148</v>
       </c>
       <c r="D60" t="s">
         <v>97</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" t="s">
         <v>47</v>
@@ -4711,18 +4714,18 @@
       <c r="G60">
         <v>4</v>
       </c>
-      <c r="H60" t="s">
-        <v>65</v>
-      </c>
-      <c r="I60">
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60" t="s">
+        <v>65</v>
+      </c>
+      <c r="J60">
         <f t="shared" si="9"/>
-        <v>2020148</v>
-      </c>
-      <c r="J60" t="s">
-        <v>66</v>
-      </c>
-      <c r="K60">
-        <v>0</v>
+        <v>2030148</v>
+      </c>
+      <c r="K60" t="s">
+        <v>66</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -4731,20 +4734,20 @@
     <row r="61" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A61">
         <f t="shared" si="10"/>
-        <v>1020149</v>
+        <v>1030149</v>
       </c>
       <c r="B61" s="7">
         <v>149</v>
       </c>
       <c r="C61">
         <f t="shared" si="11"/>
-        <v>1200149</v>
+        <v>1300149</v>
       </c>
       <c r="D61" t="s">
         <v>98</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" t="s">
         <v>47</v>
@@ -4752,18 +4755,18 @@
       <c r="G61">
         <v>5</v>
       </c>
-      <c r="H61" t="s">
-        <v>65</v>
-      </c>
-      <c r="I61">
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>65</v>
+      </c>
+      <c r="J61">
         <f t="shared" si="9"/>
-        <v>2020149</v>
-      </c>
-      <c r="J61" t="s">
-        <v>66</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
+        <v>2030149</v>
+      </c>
+      <c r="K61" t="s">
+        <v>66</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -4772,20 +4775,20 @@
     <row r="62" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A62">
         <f t="shared" si="10"/>
-        <v>1020150</v>
+        <v>1030150</v>
       </c>
       <c r="B62" s="7">
         <v>150</v>
       </c>
       <c r="C62">
         <f t="shared" si="11"/>
-        <v>1200150</v>
+        <v>1300150</v>
       </c>
       <c r="D62" t="s">
         <v>99</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" t="s">
         <v>47</v>
@@ -4793,18 +4796,18 @@
       <c r="G62">
         <v>5</v>
       </c>
-      <c r="H62" t="s">
-        <v>65</v>
-      </c>
-      <c r="I62">
-        <f t="shared" ref="I62:I93" si="12">2000000+E62*10000+B62</f>
-        <v>2020150</v>
-      </c>
-      <c r="J62" t="s">
-        <v>66</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>65</v>
+      </c>
+      <c r="J62">
+        <f t="shared" ref="J62:J93" si="12">2000000+E62*10000+B62</f>
+        <v>2030150</v>
+      </c>
+      <c r="K62" t="s">
+        <v>66</v>
       </c>
       <c r="N62">
         <v>1</v>
@@ -4813,20 +4816,20 @@
     <row r="63" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A63">
         <f t="shared" si="10"/>
-        <v>1020151</v>
+        <v>1030151</v>
       </c>
       <c r="B63" s="7">
         <v>151</v>
       </c>
       <c r="C63">
         <f t="shared" si="11"/>
-        <v>1200151</v>
+        <v>1300151</v>
       </c>
       <c r="D63" t="s">
         <v>100</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" t="s">
         <v>47</v>
@@ -4834,18 +4837,18 @@
       <c r="G63">
         <v>6</v>
       </c>
-      <c r="H63" t="s">
-        <v>65</v>
-      </c>
-      <c r="I63">
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63" t="s">
+        <v>65</v>
+      </c>
+      <c r="J63">
         <f t="shared" si="12"/>
-        <v>2020151</v>
-      </c>
-      <c r="J63" t="s">
-        <v>66</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
+        <v>2030151</v>
+      </c>
+      <c r="K63" t="s">
+        <v>66</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -4854,20 +4857,20 @@
     <row r="64" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A64">
         <f t="shared" si="10"/>
-        <v>1020152</v>
+        <v>1030152</v>
       </c>
       <c r="B64" s="7">
         <v>152</v>
       </c>
       <c r="C64">
         <f t="shared" si="11"/>
-        <v>1200152</v>
+        <v>1300152</v>
       </c>
       <c r="D64" t="s">
         <v>101</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" t="s">
         <v>47</v>
@@ -4875,18 +4878,18 @@
       <c r="G64">
         <v>6</v>
       </c>
-      <c r="H64" t="s">
-        <v>65</v>
-      </c>
-      <c r="I64">
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64" t="s">
+        <v>65</v>
+      </c>
+      <c r="J64">
         <f t="shared" si="12"/>
-        <v>2020152</v>
-      </c>
-      <c r="J64" t="s">
-        <v>66</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
+        <v>2030152</v>
+      </c>
+      <c r="K64" t="s">
+        <v>66</v>
       </c>
       <c r="N64">
         <v>1</v>
@@ -4895,20 +4898,20 @@
     <row r="65" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A65">
         <f t="shared" si="10"/>
-        <v>1020161</v>
+        <v>1030161</v>
       </c>
       <c r="B65" s="7">
         <v>161</v>
       </c>
       <c r="C65">
         <f t="shared" si="11"/>
-        <v>1200161</v>
+        <v>1300161</v>
       </c>
       <c r="D65" t="s">
         <v>102</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" t="s">
         <v>47</v>
@@ -4916,18 +4919,18 @@
       <c r="G65">
         <v>1</v>
       </c>
-      <c r="H65" t="s">
-        <v>65</v>
-      </c>
-      <c r="I65">
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65" t="s">
+        <v>65</v>
+      </c>
+      <c r="J65">
         <f t="shared" si="12"/>
-        <v>2020161</v>
-      </c>
-      <c r="J65" t="s">
-        <v>66</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
+        <v>2030161</v>
+      </c>
+      <c r="K65" t="s">
+        <v>66</v>
       </c>
       <c r="N65">
         <v>1</v>
@@ -4936,20 +4939,20 @@
     <row r="66" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A66">
         <f t="shared" si="10"/>
-        <v>1020162</v>
+        <v>1030162</v>
       </c>
       <c r="B66" s="7">
         <v>162</v>
       </c>
       <c r="C66">
         <f t="shared" si="11"/>
-        <v>1200162</v>
+        <v>1300162</v>
       </c>
       <c r="D66" t="s">
         <v>103</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" t="s">
         <v>47</v>
@@ -4957,18 +4960,18 @@
       <c r="G66">
         <v>1</v>
       </c>
-      <c r="H66" t="s">
-        <v>65</v>
-      </c>
-      <c r="I66">
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>65</v>
+      </c>
+      <c r="J66">
         <f t="shared" si="12"/>
-        <v>2020162</v>
-      </c>
-      <c r="J66" t="s">
-        <v>66</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
+        <v>2030162</v>
+      </c>
+      <c r="K66" t="s">
+        <v>66</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -4977,20 +4980,20 @@
     <row r="67" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A67">
         <f t="shared" ref="A67:A98" si="13">1000000+E67*10000+B67</f>
-        <v>1020163</v>
+        <v>1030163</v>
       </c>
       <c r="B67" s="7">
         <v>163</v>
       </c>
       <c r="C67">
         <f t="shared" ref="C67:C98" si="14">1000000+E67*100000+B67</f>
-        <v>1200163</v>
+        <v>1300163</v>
       </c>
       <c r="D67" t="s">
         <v>104</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" t="s">
         <v>47</v>
@@ -4998,18 +5001,18 @@
       <c r="G67">
         <v>2</v>
       </c>
-      <c r="H67" t="s">
-        <v>65</v>
-      </c>
-      <c r="I67">
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67" t="s">
+        <v>65</v>
+      </c>
+      <c r="J67">
         <f t="shared" si="12"/>
-        <v>2020163</v>
-      </c>
-      <c r="J67" t="s">
-        <v>66</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
+        <v>2030163</v>
+      </c>
+      <c r="K67" t="s">
+        <v>66</v>
       </c>
       <c r="N67">
         <v>1</v>
@@ -5018,20 +5021,20 @@
     <row r="68" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A68">
         <f t="shared" si="13"/>
-        <v>1020164</v>
+        <v>1030164</v>
       </c>
       <c r="B68" s="7">
         <v>164</v>
       </c>
       <c r="C68">
         <f t="shared" si="14"/>
-        <v>1200164</v>
+        <v>1300164</v>
       </c>
       <c r="D68" t="s">
         <v>105</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F68" t="s">
         <v>47</v>
@@ -5039,18 +5042,18 @@
       <c r="G68">
         <v>2</v>
       </c>
-      <c r="H68" t="s">
-        <v>65</v>
-      </c>
-      <c r="I68">
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>65</v>
+      </c>
+      <c r="J68">
         <f t="shared" si="12"/>
-        <v>2020164</v>
-      </c>
-      <c r="J68" t="s">
-        <v>66</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
+        <v>2030164</v>
+      </c>
+      <c r="K68" t="s">
+        <v>66</v>
       </c>
       <c r="N68">
         <v>1</v>
@@ -5059,20 +5062,20 @@
     <row r="69" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A69">
         <f t="shared" si="13"/>
-        <v>1020165</v>
+        <v>1030165</v>
       </c>
       <c r="B69" s="7">
         <v>165</v>
       </c>
       <c r="C69">
         <f t="shared" si="14"/>
-        <v>1200165</v>
+        <v>1300165</v>
       </c>
       <c r="D69" t="s">
         <v>106</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" t="s">
         <v>47</v>
@@ -5080,18 +5083,18 @@
       <c r="G69">
         <v>3</v>
       </c>
-      <c r="H69" t="s">
-        <v>65</v>
-      </c>
-      <c r="I69">
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69" t="s">
+        <v>65</v>
+      </c>
+      <c r="J69">
         <f t="shared" si="12"/>
-        <v>2020165</v>
-      </c>
-      <c r="J69" t="s">
-        <v>66</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
+        <v>2030165</v>
+      </c>
+      <c r="K69" t="s">
+        <v>66</v>
       </c>
       <c r="N69">
         <v>1</v>
@@ -5100,20 +5103,20 @@
     <row r="70" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A70">
         <f t="shared" si="13"/>
-        <v>1020166</v>
+        <v>1030166</v>
       </c>
       <c r="B70" s="7">
         <v>166</v>
       </c>
       <c r="C70">
         <f t="shared" si="14"/>
-        <v>1200166</v>
+        <v>1300166</v>
       </c>
       <c r="D70" t="s">
         <v>107</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" t="s">
         <v>47</v>
@@ -5121,18 +5124,18 @@
       <c r="G70">
         <v>3</v>
       </c>
-      <c r="H70" t="s">
-        <v>65</v>
-      </c>
-      <c r="I70">
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70" t="s">
+        <v>65</v>
+      </c>
+      <c r="J70">
         <f t="shared" si="12"/>
-        <v>2020166</v>
-      </c>
-      <c r="J70" t="s">
-        <v>66</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
+        <v>2030166</v>
+      </c>
+      <c r="K70" t="s">
+        <v>66</v>
       </c>
       <c r="N70">
         <v>1</v>
@@ -5141,20 +5144,20 @@
     <row r="71" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A71">
         <f t="shared" si="13"/>
-        <v>1020167</v>
+        <v>1030167</v>
       </c>
       <c r="B71" s="7">
         <v>167</v>
       </c>
       <c r="C71">
         <f t="shared" si="14"/>
-        <v>1200167</v>
+        <v>1300167</v>
       </c>
       <c r="D71" t="s">
         <v>108</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71" t="s">
         <v>47</v>
@@ -5162,18 +5165,18 @@
       <c r="G71">
         <v>4</v>
       </c>
-      <c r="H71" t="s">
-        <v>65</v>
-      </c>
-      <c r="I71">
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71" t="s">
+        <v>65</v>
+      </c>
+      <c r="J71">
         <f t="shared" si="12"/>
-        <v>2020167</v>
-      </c>
-      <c r="J71" t="s">
-        <v>66</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
+        <v>2030167</v>
+      </c>
+      <c r="K71" t="s">
+        <v>66</v>
       </c>
       <c r="N71">
         <v>1</v>
@@ -5182,20 +5185,20 @@
     <row r="72" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A72">
         <f t="shared" si="13"/>
-        <v>1020168</v>
+        <v>1030168</v>
       </c>
       <c r="B72" s="7">
         <v>168</v>
       </c>
       <c r="C72">
         <f t="shared" si="14"/>
-        <v>1200168</v>
+        <v>1300168</v>
       </c>
       <c r="D72" t="s">
         <v>109</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" t="s">
         <v>47</v>
@@ -5203,18 +5206,18 @@
       <c r="G72">
         <v>4</v>
       </c>
-      <c r="H72" t="s">
-        <v>65</v>
-      </c>
-      <c r="I72">
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>65</v>
+      </c>
+      <c r="J72">
         <f t="shared" si="12"/>
-        <v>2020168</v>
-      </c>
-      <c r="J72" t="s">
-        <v>66</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
+        <v>2030168</v>
+      </c>
+      <c r="K72" t="s">
+        <v>66</v>
       </c>
       <c r="N72">
         <v>1</v>
@@ -5223,20 +5226,20 @@
     <row r="73" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A73">
         <f t="shared" si="13"/>
-        <v>1020169</v>
+        <v>1030169</v>
       </c>
       <c r="B73" s="7">
         <v>169</v>
       </c>
       <c r="C73">
         <f t="shared" si="14"/>
-        <v>1200169</v>
+        <v>1300169</v>
       </c>
       <c r="D73" t="s">
         <v>110</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="s">
         <v>47</v>
@@ -5244,18 +5247,18 @@
       <c r="G73">
         <v>5</v>
       </c>
-      <c r="H73" t="s">
-        <v>65</v>
-      </c>
-      <c r="I73">
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>65</v>
+      </c>
+      <c r="J73">
         <f t="shared" si="12"/>
-        <v>2020169</v>
-      </c>
-      <c r="J73" t="s">
-        <v>66</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
+        <v>2030169</v>
+      </c>
+      <c r="K73" t="s">
+        <v>66</v>
       </c>
       <c r="N73">
         <v>1</v>
@@ -5264,20 +5267,20 @@
     <row r="74" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A74">
         <f t="shared" si="13"/>
-        <v>1020170</v>
+        <v>1030170</v>
       </c>
       <c r="B74" s="7">
         <v>170</v>
       </c>
       <c r="C74">
         <f t="shared" si="14"/>
-        <v>1200170</v>
+        <v>1300170</v>
       </c>
       <c r="D74" t="s">
         <v>111</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" t="s">
         <v>47</v>
@@ -5285,18 +5288,18 @@
       <c r="G74">
         <v>5</v>
       </c>
-      <c r="H74" t="s">
-        <v>65</v>
-      </c>
-      <c r="I74">
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>65</v>
+      </c>
+      <c r="J74">
         <f t="shared" si="12"/>
-        <v>2020170</v>
-      </c>
-      <c r="J74" t="s">
-        <v>66</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
+        <v>2030170</v>
+      </c>
+      <c r="K74" t="s">
+        <v>66</v>
       </c>
       <c r="N74">
         <v>1</v>
@@ -5305,20 +5308,20 @@
     <row r="75" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A75">
         <f t="shared" si="13"/>
-        <v>1020171</v>
+        <v>1030171</v>
       </c>
       <c r="B75" s="7">
         <v>171</v>
       </c>
       <c r="C75">
         <f t="shared" si="14"/>
-        <v>1200171</v>
+        <v>1300171</v>
       </c>
       <c r="D75" t="s">
         <v>112</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75" t="s">
         <v>47</v>
@@ -5326,18 +5329,18 @@
       <c r="G75">
         <v>6</v>
       </c>
-      <c r="H75" t="s">
-        <v>65</v>
-      </c>
-      <c r="I75">
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>65</v>
+      </c>
+      <c r="J75">
         <f t="shared" si="12"/>
-        <v>2020171</v>
-      </c>
-      <c r="J75" t="s">
-        <v>66</v>
-      </c>
-      <c r="K75">
-        <v>0</v>
+        <v>2030171</v>
+      </c>
+      <c r="K75" t="s">
+        <v>66</v>
       </c>
       <c r="N75">
         <v>1</v>
@@ -5346,20 +5349,20 @@
     <row r="76" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A76">
         <f t="shared" si="13"/>
-        <v>1020172</v>
+        <v>1030172</v>
       </c>
       <c r="B76" s="7">
         <v>172</v>
       </c>
       <c r="C76">
         <f t="shared" si="14"/>
-        <v>1200172</v>
+        <v>1300172</v>
       </c>
       <c r="D76" t="s">
         <v>113</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" t="s">
         <v>47</v>
@@ -5367,18 +5370,18 @@
       <c r="G76">
         <v>6</v>
       </c>
-      <c r="H76" t="s">
-        <v>65</v>
-      </c>
-      <c r="I76">
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76" t="s">
+        <v>65</v>
+      </c>
+      <c r="J76">
         <f t="shared" si="12"/>
-        <v>2020172</v>
-      </c>
-      <c r="J76" t="s">
-        <v>66</v>
-      </c>
-      <c r="K76">
-        <v>0</v>
+        <v>2030172</v>
+      </c>
+      <c r="K76" t="s">
+        <v>66</v>
       </c>
       <c r="N76">
         <v>1</v>
@@ -5387,20 +5390,20 @@
     <row r="77" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A77">
         <f t="shared" si="13"/>
-        <v>1020181</v>
+        <v>1030181</v>
       </c>
       <c r="B77" s="7">
         <v>181</v>
       </c>
       <c r="C77">
         <f t="shared" si="14"/>
-        <v>1200181</v>
+        <v>1300181</v>
       </c>
       <c r="D77" t="s">
         <v>114</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" t="s">
         <v>47</v>
@@ -5408,18 +5411,18 @@
       <c r="G77">
         <v>1</v>
       </c>
-      <c r="H77" t="s">
-        <v>65</v>
-      </c>
-      <c r="I77">
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77" t="s">
+        <v>65</v>
+      </c>
+      <c r="J77">
         <f t="shared" si="12"/>
-        <v>2020181</v>
-      </c>
-      <c r="J77" t="s">
-        <v>66</v>
-      </c>
-      <c r="K77">
-        <v>0</v>
+        <v>2030181</v>
+      </c>
+      <c r="K77" t="s">
+        <v>66</v>
       </c>
       <c r="N77">
         <v>1</v>
@@ -5428,20 +5431,20 @@
     <row r="78" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A78">
         <f t="shared" si="13"/>
-        <v>1020182</v>
+        <v>1030182</v>
       </c>
       <c r="B78" s="7">
         <v>182</v>
       </c>
       <c r="C78">
         <f t="shared" si="14"/>
-        <v>1200182</v>
+        <v>1300182</v>
       </c>
       <c r="D78" t="s">
         <v>115</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78" t="s">
         <v>47</v>
@@ -5449,18 +5452,18 @@
       <c r="G78">
         <v>1</v>
       </c>
-      <c r="H78" t="s">
-        <v>65</v>
-      </c>
-      <c r="I78">
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>65</v>
+      </c>
+      <c r="J78">
         <f t="shared" si="12"/>
-        <v>2020182</v>
-      </c>
-      <c r="J78" t="s">
-        <v>66</v>
-      </c>
-      <c r="K78">
-        <v>0</v>
+        <v>2030182</v>
+      </c>
+      <c r="K78" t="s">
+        <v>66</v>
       </c>
       <c r="N78">
         <v>1</v>
@@ -5469,20 +5472,20 @@
     <row r="79" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A79">
         <f t="shared" si="13"/>
-        <v>1020183</v>
+        <v>1030183</v>
       </c>
       <c r="B79" s="7">
         <v>183</v>
       </c>
       <c r="C79">
         <f t="shared" si="14"/>
-        <v>1200183</v>
+        <v>1300183</v>
       </c>
       <c r="D79" t="s">
         <v>116</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" t="s">
         <v>47</v>
@@ -5490,18 +5493,18 @@
       <c r="G79">
         <v>2</v>
       </c>
-      <c r="H79" t="s">
-        <v>65</v>
-      </c>
-      <c r="I79">
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>65</v>
+      </c>
+      <c r="J79">
         <f t="shared" si="12"/>
-        <v>2020183</v>
-      </c>
-      <c r="J79" t="s">
-        <v>66</v>
-      </c>
-      <c r="K79">
-        <v>0</v>
+        <v>2030183</v>
+      </c>
+      <c r="K79" t="s">
+        <v>66</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -5510,20 +5513,20 @@
     <row r="80" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A80">
         <f t="shared" si="13"/>
-        <v>1020184</v>
+        <v>1030184</v>
       </c>
       <c r="B80" s="7">
         <v>184</v>
       </c>
       <c r="C80">
         <f t="shared" si="14"/>
-        <v>1200184</v>
+        <v>1300184</v>
       </c>
       <c r="D80" t="s">
         <v>117</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="s">
         <v>47</v>
@@ -5531,18 +5534,18 @@
       <c r="G80">
         <v>2</v>
       </c>
-      <c r="H80" t="s">
-        <v>65</v>
-      </c>
-      <c r="I80">
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80" t="s">
+        <v>65</v>
+      </c>
+      <c r="J80">
         <f t="shared" si="12"/>
-        <v>2020184</v>
-      </c>
-      <c r="J80" t="s">
-        <v>66</v>
-      </c>
-      <c r="K80">
-        <v>0</v>
+        <v>2030184</v>
+      </c>
+      <c r="K80" t="s">
+        <v>66</v>
       </c>
       <c r="N80">
         <v>1</v>
@@ -5551,20 +5554,20 @@
     <row r="81" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A81">
         <f t="shared" si="13"/>
-        <v>1020185</v>
+        <v>1030185</v>
       </c>
       <c r="B81" s="7">
         <v>185</v>
       </c>
       <c r="C81">
         <f t="shared" si="14"/>
-        <v>1200185</v>
+        <v>1300185</v>
       </c>
       <c r="D81" t="s">
         <v>118</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="s">
         <v>47</v>
@@ -5572,18 +5575,18 @@
       <c r="G81">
         <v>3</v>
       </c>
-      <c r="H81" t="s">
-        <v>65</v>
-      </c>
-      <c r="I81">
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81" t="s">
+        <v>65</v>
+      </c>
+      <c r="J81">
         <f t="shared" si="12"/>
-        <v>2020185</v>
-      </c>
-      <c r="J81" t="s">
-        <v>66</v>
-      </c>
-      <c r="K81">
-        <v>0</v>
+        <v>2030185</v>
+      </c>
+      <c r="K81" t="s">
+        <v>66</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -5592,20 +5595,20 @@
     <row r="82" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A82">
         <f t="shared" si="13"/>
-        <v>1020186</v>
+        <v>1030186</v>
       </c>
       <c r="B82" s="7">
         <v>186</v>
       </c>
       <c r="C82">
         <f t="shared" si="14"/>
-        <v>1200186</v>
+        <v>1300186</v>
       </c>
       <c r="D82" t="s">
         <v>119</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="s">
         <v>47</v>
@@ -5613,18 +5616,18 @@
       <c r="G82">
         <v>3</v>
       </c>
-      <c r="H82" t="s">
-        <v>65</v>
-      </c>
-      <c r="I82">
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82" t="s">
+        <v>65</v>
+      </c>
+      <c r="J82">
         <f t="shared" si="12"/>
-        <v>2020186</v>
-      </c>
-      <c r="J82" t="s">
-        <v>66</v>
-      </c>
-      <c r="K82">
-        <v>0</v>
+        <v>2030186</v>
+      </c>
+      <c r="K82" t="s">
+        <v>66</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -5633,20 +5636,20 @@
     <row r="83" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A83">
         <f t="shared" si="13"/>
-        <v>1020187</v>
+        <v>1030187</v>
       </c>
       <c r="B83" s="7">
         <v>187</v>
       </c>
       <c r="C83">
         <f t="shared" si="14"/>
-        <v>1200187</v>
+        <v>1300187</v>
       </c>
       <c r="D83" t="s">
         <v>120</v>
       </c>
       <c r="E83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="s">
         <v>47</v>
@@ -5654,18 +5657,18 @@
       <c r="G83">
         <v>4</v>
       </c>
-      <c r="H83" t="s">
-        <v>65</v>
-      </c>
-      <c r="I83">
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83" t="s">
+        <v>65</v>
+      </c>
+      <c r="J83">
         <f t="shared" si="12"/>
-        <v>2020187</v>
-      </c>
-      <c r="J83" t="s">
-        <v>66</v>
-      </c>
-      <c r="K83">
-        <v>0</v>
+        <v>2030187</v>
+      </c>
+      <c r="K83" t="s">
+        <v>66</v>
       </c>
       <c r="N83">
         <v>1</v>
@@ -5674,20 +5677,20 @@
     <row r="84" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A84">
         <f t="shared" si="13"/>
-        <v>1020188</v>
+        <v>1030188</v>
       </c>
       <c r="B84" s="7">
         <v>188</v>
       </c>
       <c r="C84">
         <f t="shared" si="14"/>
-        <v>1200188</v>
+        <v>1300188</v>
       </c>
       <c r="D84" t="s">
         <v>121</v>
       </c>
       <c r="E84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" t="s">
         <v>47</v>
@@ -5695,18 +5698,18 @@
       <c r="G84">
         <v>4</v>
       </c>
-      <c r="H84" t="s">
-        <v>65</v>
-      </c>
-      <c r="I84">
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84" t="s">
+        <v>65</v>
+      </c>
+      <c r="J84">
         <f t="shared" si="12"/>
-        <v>2020188</v>
-      </c>
-      <c r="J84" t="s">
-        <v>66</v>
-      </c>
-      <c r="K84">
-        <v>0</v>
+        <v>2030188</v>
+      </c>
+      <c r="K84" t="s">
+        <v>66</v>
       </c>
       <c r="N84">
         <v>1</v>
@@ -5715,20 +5718,20 @@
     <row r="85" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A85">
         <f t="shared" si="13"/>
-        <v>1020189</v>
+        <v>1030189</v>
       </c>
       <c r="B85" s="7">
         <v>189</v>
       </c>
       <c r="C85">
         <f t="shared" si="14"/>
-        <v>1200189</v>
+        <v>1300189</v>
       </c>
       <c r="D85" t="s">
         <v>122</v>
       </c>
       <c r="E85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" t="s">
         <v>47</v>
@@ -5736,18 +5739,18 @@
       <c r="G85">
         <v>5</v>
       </c>
-      <c r="H85" t="s">
-        <v>65</v>
-      </c>
-      <c r="I85">
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85" t="s">
+        <v>65</v>
+      </c>
+      <c r="J85">
         <f t="shared" si="12"/>
-        <v>2020189</v>
-      </c>
-      <c r="J85" t="s">
-        <v>66</v>
-      </c>
-      <c r="K85">
-        <v>0</v>
+        <v>2030189</v>
+      </c>
+      <c r="K85" t="s">
+        <v>66</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -5756,20 +5759,20 @@
     <row r="86" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A86">
         <f t="shared" si="13"/>
-        <v>1020190</v>
+        <v>1030190</v>
       </c>
       <c r="B86" s="7">
         <v>190</v>
       </c>
       <c r="C86">
         <f t="shared" si="14"/>
-        <v>1200190</v>
+        <v>1300190</v>
       </c>
       <c r="D86" t="s">
         <v>123</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" t="s">
         <v>47</v>
@@ -5777,18 +5780,18 @@
       <c r="G86">
         <v>5</v>
       </c>
-      <c r="H86" t="s">
-        <v>65</v>
-      </c>
-      <c r="I86">
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86" t="s">
+        <v>65</v>
+      </c>
+      <c r="J86">
         <f t="shared" si="12"/>
-        <v>2020190</v>
-      </c>
-      <c r="J86" t="s">
-        <v>66</v>
-      </c>
-      <c r="K86">
-        <v>0</v>
+        <v>2030190</v>
+      </c>
+      <c r="K86" t="s">
+        <v>66</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -5797,20 +5800,20 @@
     <row r="87" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A87">
         <f t="shared" si="13"/>
-        <v>1020191</v>
+        <v>1030191</v>
       </c>
       <c r="B87" s="7">
         <v>191</v>
       </c>
       <c r="C87">
         <f t="shared" si="14"/>
-        <v>1200191</v>
+        <v>1300191</v>
       </c>
       <c r="D87" t="s">
         <v>124</v>
       </c>
       <c r="E87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" t="s">
         <v>47</v>
@@ -5818,18 +5821,18 @@
       <c r="G87">
         <v>6</v>
       </c>
-      <c r="H87" t="s">
-        <v>65</v>
-      </c>
-      <c r="I87">
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87" t="s">
+        <v>65</v>
+      </c>
+      <c r="J87">
         <f t="shared" si="12"/>
-        <v>2020191</v>
-      </c>
-      <c r="J87" t="s">
-        <v>66</v>
-      </c>
-      <c r="K87">
-        <v>0</v>
+        <v>2030191</v>
+      </c>
+      <c r="K87" t="s">
+        <v>66</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -5838,20 +5841,20 @@
     <row r="88" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A88">
         <f t="shared" si="13"/>
-        <v>1020192</v>
+        <v>1030192</v>
       </c>
       <c r="B88" s="7">
         <v>192</v>
       </c>
       <c r="C88">
         <f t="shared" si="14"/>
-        <v>1200192</v>
+        <v>1300192</v>
       </c>
       <c r="D88" t="s">
         <v>125</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" t="s">
         <v>47</v>
@@ -5859,18 +5862,18 @@
       <c r="G88">
         <v>6</v>
       </c>
-      <c r="H88" t="s">
-        <v>65</v>
-      </c>
-      <c r="I88">
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88" t="s">
+        <v>65</v>
+      </c>
+      <c r="J88">
         <f t="shared" si="12"/>
-        <v>2020192</v>
-      </c>
-      <c r="J88" t="s">
-        <v>66</v>
-      </c>
-      <c r="K88">
-        <v>0</v>
+        <v>2030192</v>
+      </c>
+      <c r="K88" t="s">
+        <v>66</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -5879,20 +5882,20 @@
     <row r="89" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A89">
         <f t="shared" si="13"/>
-        <v>1020201</v>
+        <v>1030201</v>
       </c>
       <c r="B89" s="7">
         <v>201</v>
       </c>
       <c r="C89">
         <f t="shared" si="14"/>
-        <v>1200201</v>
+        <v>1300201</v>
       </c>
       <c r="D89" t="s">
         <v>126</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" t="s">
         <v>47</v>
@@ -5900,18 +5903,18 @@
       <c r="G89">
         <v>1</v>
       </c>
-      <c r="H89" t="s">
-        <v>65</v>
-      </c>
-      <c r="I89">
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89" t="s">
+        <v>65</v>
+      </c>
+      <c r="J89">
         <f t="shared" si="12"/>
-        <v>2020201</v>
-      </c>
-      <c r="J89" t="s">
-        <v>66</v>
-      </c>
-      <c r="K89">
-        <v>0</v>
+        <v>2030201</v>
+      </c>
+      <c r="K89" t="s">
+        <v>66</v>
       </c>
       <c r="N89">
         <v>1</v>
@@ -5920,20 +5923,20 @@
     <row r="90" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A90">
         <f t="shared" si="13"/>
-        <v>1020202</v>
+        <v>1030202</v>
       </c>
       <c r="B90" s="7">
         <v>202</v>
       </c>
       <c r="C90">
         <f t="shared" si="14"/>
-        <v>1200202</v>
+        <v>1300202</v>
       </c>
       <c r="D90" t="s">
         <v>127</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" t="s">
         <v>47</v>
@@ -5941,18 +5944,18 @@
       <c r="G90">
         <v>1</v>
       </c>
-      <c r="H90" t="s">
-        <v>65</v>
-      </c>
-      <c r="I90">
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90" t="s">
+        <v>65</v>
+      </c>
+      <c r="J90">
         <f t="shared" si="12"/>
-        <v>2020202</v>
-      </c>
-      <c r="J90" t="s">
-        <v>66</v>
-      </c>
-      <c r="K90">
-        <v>0</v>
+        <v>2030202</v>
+      </c>
+      <c r="K90" t="s">
+        <v>66</v>
       </c>
       <c r="N90">
         <v>1</v>
@@ -5961,20 +5964,20 @@
     <row r="91" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A91">
         <f t="shared" si="13"/>
-        <v>1020203</v>
+        <v>1030203</v>
       </c>
       <c r="B91" s="7">
         <v>203</v>
       </c>
       <c r="C91">
         <f t="shared" si="14"/>
-        <v>1200203</v>
+        <v>1300203</v>
       </c>
       <c r="D91" t="s">
         <v>128</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" t="s">
         <v>47</v>
@@ -5982,18 +5985,18 @@
       <c r="G91">
         <v>2</v>
       </c>
-      <c r="H91" t="s">
-        <v>65</v>
-      </c>
-      <c r="I91">
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91" t="s">
+        <v>65</v>
+      </c>
+      <c r="J91">
         <f t="shared" si="12"/>
-        <v>2020203</v>
-      </c>
-      <c r="J91" t="s">
-        <v>66</v>
-      </c>
-      <c r="K91">
-        <v>0</v>
+        <v>2030203</v>
+      </c>
+      <c r="K91" t="s">
+        <v>66</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -6002,20 +6005,20 @@
     <row r="92" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A92">
         <f t="shared" si="13"/>
-        <v>1020204</v>
+        <v>1030204</v>
       </c>
       <c r="B92" s="7">
         <v>204</v>
       </c>
       <c r="C92">
         <f t="shared" si="14"/>
-        <v>1200204</v>
+        <v>1300204</v>
       </c>
       <c r="D92" t="s">
         <v>129</v>
       </c>
       <c r="E92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" t="s">
         <v>47</v>
@@ -6023,18 +6026,18 @@
       <c r="G92">
         <v>2</v>
       </c>
-      <c r="H92" t="s">
-        <v>65</v>
-      </c>
-      <c r="I92">
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92" t="s">
+        <v>65</v>
+      </c>
+      <c r="J92">
         <f t="shared" si="12"/>
-        <v>2020204</v>
-      </c>
-      <c r="J92" t="s">
-        <v>66</v>
-      </c>
-      <c r="K92">
-        <v>0</v>
+        <v>2030204</v>
+      </c>
+      <c r="K92" t="s">
+        <v>66</v>
       </c>
       <c r="N92">
         <v>1</v>
@@ -6043,20 +6046,20 @@
     <row r="93" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A93">
         <f t="shared" si="13"/>
-        <v>1020205</v>
+        <v>1030205</v>
       </c>
       <c r="B93" s="7">
         <v>205</v>
       </c>
       <c r="C93">
         <f t="shared" si="14"/>
-        <v>1200205</v>
+        <v>1300205</v>
       </c>
       <c r="D93" t="s">
         <v>130</v>
       </c>
       <c r="E93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="s">
         <v>47</v>
@@ -6064,18 +6067,18 @@
       <c r="G93">
         <v>3</v>
       </c>
-      <c r="H93" t="s">
-        <v>65</v>
-      </c>
-      <c r="I93">
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93" t="s">
+        <v>65</v>
+      </c>
+      <c r="J93">
         <f t="shared" si="12"/>
-        <v>2020205</v>
-      </c>
-      <c r="J93" t="s">
-        <v>66</v>
-      </c>
-      <c r="K93">
-        <v>0</v>
+        <v>2030205</v>
+      </c>
+      <c r="K93" t="s">
+        <v>66</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -6084,20 +6087,20 @@
     <row r="94" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A94">
         <f t="shared" si="13"/>
-        <v>1020206</v>
+        <v>1030206</v>
       </c>
       <c r="B94" s="7">
         <v>206</v>
       </c>
       <c r="C94">
         <f t="shared" si="14"/>
-        <v>1200206</v>
+        <v>1300206</v>
       </c>
       <c r="D94" t="s">
         <v>131</v>
       </c>
       <c r="E94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="s">
         <v>47</v>
@@ -6105,18 +6108,18 @@
       <c r="G94">
         <v>3</v>
       </c>
-      <c r="H94" t="s">
-        <v>65</v>
-      </c>
-      <c r="I94">
-        <f t="shared" ref="I94:I128" si="15">2000000+E94*10000+B94</f>
-        <v>2020206</v>
-      </c>
-      <c r="J94" t="s">
-        <v>66</v>
-      </c>
-      <c r="K94">
-        <v>0</v>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94" t="s">
+        <v>65</v>
+      </c>
+      <c r="J94">
+        <f t="shared" ref="J94:J128" si="15">2000000+E94*10000+B94</f>
+        <v>2030206</v>
+      </c>
+      <c r="K94" t="s">
+        <v>66</v>
       </c>
       <c r="N94">
         <v>1</v>
@@ -6125,20 +6128,20 @@
     <row r="95" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A95">
         <f t="shared" si="13"/>
-        <v>1020207</v>
+        <v>1030207</v>
       </c>
       <c r="B95" s="7">
         <v>207</v>
       </c>
       <c r="C95">
         <f t="shared" si="14"/>
-        <v>1200207</v>
+        <v>1300207</v>
       </c>
       <c r="D95" t="s">
         <v>132</v>
       </c>
       <c r="E95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" t="s">
         <v>47</v>
@@ -6146,18 +6149,18 @@
       <c r="G95">
         <v>4</v>
       </c>
-      <c r="H95" t="s">
-        <v>65</v>
-      </c>
-      <c r="I95">
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95" t="s">
+        <v>65</v>
+      </c>
+      <c r="J95">
         <f t="shared" si="15"/>
-        <v>2020207</v>
-      </c>
-      <c r="J95" t="s">
-        <v>66</v>
-      </c>
-      <c r="K95">
-        <v>0</v>
+        <v>2030207</v>
+      </c>
+      <c r="K95" t="s">
+        <v>66</v>
       </c>
       <c r="N95">
         <v>1</v>
@@ -6166,20 +6169,20 @@
     <row r="96" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A96">
         <f t="shared" si="13"/>
-        <v>1020208</v>
+        <v>1030208</v>
       </c>
       <c r="B96" s="7">
         <v>208</v>
       </c>
       <c r="C96">
         <f t="shared" si="14"/>
-        <v>1200208</v>
+        <v>1300208</v>
       </c>
       <c r="D96" t="s">
         <v>133</v>
       </c>
       <c r="E96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" t="s">
         <v>47</v>
@@ -6187,18 +6190,18 @@
       <c r="G96">
         <v>4</v>
       </c>
-      <c r="H96" t="s">
-        <v>65</v>
-      </c>
-      <c r="I96">
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96" t="s">
+        <v>65</v>
+      </c>
+      <c r="J96">
         <f t="shared" si="15"/>
-        <v>2020208</v>
-      </c>
-      <c r="J96" t="s">
-        <v>66</v>
-      </c>
-      <c r="K96">
-        <v>0</v>
+        <v>2030208</v>
+      </c>
+      <c r="K96" t="s">
+        <v>66</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -6207,20 +6210,20 @@
     <row r="97" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A97">
         <f t="shared" si="13"/>
-        <v>1020209</v>
+        <v>1030209</v>
       </c>
       <c r="B97" s="7">
         <v>209</v>
       </c>
       <c r="C97">
         <f t="shared" si="14"/>
-        <v>1200209</v>
+        <v>1300209</v>
       </c>
       <c r="D97" t="s">
         <v>134</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" t="s">
         <v>47</v>
@@ -6228,18 +6231,18 @@
       <c r="G97">
         <v>5</v>
       </c>
-      <c r="H97" t="s">
-        <v>65</v>
-      </c>
-      <c r="I97">
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97" t="s">
+        <v>65</v>
+      </c>
+      <c r="J97">
         <f t="shared" si="15"/>
-        <v>2020209</v>
-      </c>
-      <c r="J97" t="s">
-        <v>66</v>
-      </c>
-      <c r="K97">
-        <v>0</v>
+        <v>2030209</v>
+      </c>
+      <c r="K97" t="s">
+        <v>66</v>
       </c>
       <c r="N97">
         <v>1</v>
@@ -6248,20 +6251,20 @@
     <row r="98" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A98">
         <f t="shared" si="13"/>
-        <v>1020210</v>
+        <v>1030210</v>
       </c>
       <c r="B98" s="7">
         <v>210</v>
       </c>
       <c r="C98">
         <f t="shared" si="14"/>
-        <v>1200210</v>
+        <v>1300210</v>
       </c>
       <c r="D98" t="s">
         <v>135</v>
       </c>
       <c r="E98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" t="s">
         <v>47</v>
@@ -6269,18 +6272,18 @@
       <c r="G98">
         <v>5</v>
       </c>
-      <c r="H98" t="s">
-        <v>65</v>
-      </c>
-      <c r="I98">
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98" t="s">
+        <v>65</v>
+      </c>
+      <c r="J98">
         <f t="shared" si="15"/>
-        <v>2020210</v>
-      </c>
-      <c r="J98" t="s">
-        <v>66</v>
-      </c>
-      <c r="K98">
-        <v>0</v>
+        <v>2030210</v>
+      </c>
+      <c r="K98" t="s">
+        <v>66</v>
       </c>
       <c r="N98">
         <v>1</v>
@@ -6289,20 +6292,20 @@
     <row r="99" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A99">
         <f t="shared" ref="A99:A130" si="16">1000000+E99*10000+B99</f>
-        <v>1020211</v>
+        <v>1030211</v>
       </c>
       <c r="B99" s="7">
         <v>211</v>
       </c>
       <c r="C99">
         <f t="shared" ref="C99:C128" si="17">1000000+E99*100000+B99</f>
-        <v>1200211</v>
+        <v>1300211</v>
       </c>
       <c r="D99" t="s">
         <v>136</v>
       </c>
       <c r="E99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" t="s">
         <v>47</v>
@@ -6310,18 +6313,18 @@
       <c r="G99">
         <v>6</v>
       </c>
-      <c r="H99" t="s">
-        <v>65</v>
-      </c>
-      <c r="I99">
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99" t="s">
+        <v>65</v>
+      </c>
+      <c r="J99">
         <f t="shared" si="15"/>
-        <v>2020211</v>
-      </c>
-      <c r="J99" t="s">
-        <v>66</v>
-      </c>
-      <c r="K99">
-        <v>0</v>
+        <v>2030211</v>
+      </c>
+      <c r="K99" t="s">
+        <v>66</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -6330,20 +6333,20 @@
     <row r="100" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A100">
         <f t="shared" si="16"/>
-        <v>1020212</v>
+        <v>1030212</v>
       </c>
       <c r="B100" s="7">
         <v>212</v>
       </c>
       <c r="C100">
         <f t="shared" si="17"/>
-        <v>1200212</v>
+        <v>1300212</v>
       </c>
       <c r="D100" t="s">
         <v>137</v>
       </c>
       <c r="E100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" t="s">
         <v>47</v>
@@ -6351,18 +6354,18 @@
       <c r="G100">
         <v>6</v>
       </c>
-      <c r="H100" t="s">
-        <v>65</v>
-      </c>
-      <c r="I100">
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100" t="s">
+        <v>65</v>
+      </c>
+      <c r="J100">
         <f t="shared" si="15"/>
-        <v>2020212</v>
-      </c>
-      <c r="J100" t="s">
-        <v>66</v>
-      </c>
-      <c r="K100">
-        <v>0</v>
+        <v>2030212</v>
+      </c>
+      <c r="K100" t="s">
+        <v>66</v>
       </c>
       <c r="N100">
         <v>1</v>
@@ -6371,20 +6374,20 @@
     <row r="101" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A101">
         <f t="shared" si="16"/>
-        <v>1020221</v>
+        <v>1030221</v>
       </c>
       <c r="B101" s="7">
         <v>221</v>
       </c>
       <c r="C101">
         <f t="shared" si="17"/>
-        <v>1200221</v>
+        <v>1300221</v>
       </c>
       <c r="D101" t="s">
         <v>138</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" t="s">
         <v>47</v>
@@ -6392,18 +6395,18 @@
       <c r="G101">
         <v>1</v>
       </c>
-      <c r="H101" t="s">
-        <v>65</v>
-      </c>
-      <c r="I101">
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101" t="s">
+        <v>65</v>
+      </c>
+      <c r="J101">
         <f t="shared" si="15"/>
-        <v>2020221</v>
-      </c>
-      <c r="J101" t="s">
-        <v>66</v>
-      </c>
-      <c r="K101">
-        <v>0</v>
+        <v>2030221</v>
+      </c>
+      <c r="K101" t="s">
+        <v>66</v>
       </c>
       <c r="N101">
         <v>1</v>
@@ -6412,20 +6415,20 @@
     <row r="102" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A102">
         <f t="shared" si="16"/>
-        <v>1020222</v>
+        <v>1030222</v>
       </c>
       <c r="B102" s="7">
         <v>222</v>
       </c>
       <c r="C102">
         <f t="shared" si="17"/>
-        <v>1200222</v>
+        <v>1300222</v>
       </c>
       <c r="D102" t="s">
         <v>139</v>
       </c>
       <c r="E102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" t="s">
         <v>47</v>
@@ -6433,18 +6436,18 @@
       <c r="G102">
         <v>1</v>
       </c>
-      <c r="H102" t="s">
-        <v>65</v>
-      </c>
-      <c r="I102">
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102" t="s">
+        <v>65</v>
+      </c>
+      <c r="J102">
         <f t="shared" si="15"/>
-        <v>2020222</v>
-      </c>
-      <c r="J102" t="s">
-        <v>66</v>
-      </c>
-      <c r="K102">
-        <v>0</v>
+        <v>2030222</v>
+      </c>
+      <c r="K102" t="s">
+        <v>66</v>
       </c>
       <c r="N102">
         <v>1</v>
@@ -6453,20 +6456,20 @@
     <row r="103" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A103">
         <f t="shared" si="16"/>
-        <v>1020223</v>
+        <v>1030223</v>
       </c>
       <c r="B103" s="7">
         <v>223</v>
       </c>
       <c r="C103">
         <f t="shared" si="17"/>
-        <v>1200223</v>
+        <v>1300223</v>
       </c>
       <c r="D103" t="s">
         <v>140</v>
       </c>
       <c r="E103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" t="s">
         <v>47</v>
@@ -6474,18 +6477,18 @@
       <c r="G103">
         <v>2</v>
       </c>
-      <c r="H103" t="s">
-        <v>65</v>
-      </c>
-      <c r="I103">
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103" t="s">
+        <v>65</v>
+      </c>
+      <c r="J103">
         <f t="shared" si="15"/>
-        <v>2020223</v>
-      </c>
-      <c r="J103" t="s">
-        <v>66</v>
-      </c>
-      <c r="K103">
-        <v>0</v>
+        <v>2030223</v>
+      </c>
+      <c r="K103" t="s">
+        <v>66</v>
       </c>
       <c r="N103">
         <v>1</v>
@@ -6494,20 +6497,20 @@
     <row r="104" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A104">
         <f t="shared" si="16"/>
-        <v>1020224</v>
+        <v>1030224</v>
       </c>
       <c r="B104" s="7">
         <v>224</v>
       </c>
       <c r="C104">
         <f t="shared" si="17"/>
-        <v>1200224</v>
+        <v>1300224</v>
       </c>
       <c r="D104" t="s">
         <v>141</v>
       </c>
       <c r="E104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" t="s">
         <v>47</v>
@@ -6515,18 +6518,18 @@
       <c r="G104">
         <v>2</v>
       </c>
-      <c r="H104" t="s">
-        <v>65</v>
-      </c>
-      <c r="I104">
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104" t="s">
+        <v>65</v>
+      </c>
+      <c r="J104">
         <f t="shared" si="15"/>
-        <v>2020224</v>
-      </c>
-      <c r="J104" t="s">
-        <v>66</v>
-      </c>
-      <c r="K104">
-        <v>0</v>
+        <v>2030224</v>
+      </c>
+      <c r="K104" t="s">
+        <v>66</v>
       </c>
       <c r="N104">
         <v>1</v>
@@ -6535,20 +6538,20 @@
     <row r="105" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A105">
         <f t="shared" si="16"/>
-        <v>1020225</v>
+        <v>1030225</v>
       </c>
       <c r="B105" s="7">
         <v>225</v>
       </c>
       <c r="C105">
         <f t="shared" si="17"/>
-        <v>1200225</v>
+        <v>1300225</v>
       </c>
       <c r="D105" t="s">
         <v>142</v>
       </c>
       <c r="E105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" t="s">
         <v>47</v>
@@ -6556,18 +6559,18 @@
       <c r="G105">
         <v>3</v>
       </c>
-      <c r="H105" t="s">
-        <v>65</v>
-      </c>
-      <c r="I105">
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105" t="s">
+        <v>65</v>
+      </c>
+      <c r="J105">
         <f t="shared" si="15"/>
-        <v>2020225</v>
-      </c>
-      <c r="J105" t="s">
-        <v>66</v>
-      </c>
-      <c r="K105">
-        <v>0</v>
+        <v>2030225</v>
+      </c>
+      <c r="K105" t="s">
+        <v>66</v>
       </c>
       <c r="N105">
         <v>1</v>
@@ -6576,20 +6579,20 @@
     <row r="106" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A106">
         <f t="shared" si="16"/>
-        <v>1020226</v>
+        <v>1030226</v>
       </c>
       <c r="B106" s="7">
         <v>226</v>
       </c>
       <c r="C106">
         <f t="shared" si="17"/>
-        <v>1200226</v>
+        <v>1300226</v>
       </c>
       <c r="D106" t="s">
         <v>143</v>
       </c>
       <c r="E106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" t="s">
         <v>47</v>
@@ -6597,18 +6600,18 @@
       <c r="G106">
         <v>3</v>
       </c>
-      <c r="H106" t="s">
-        <v>65</v>
-      </c>
-      <c r="I106">
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106" t="s">
+        <v>65</v>
+      </c>
+      <c r="J106">
         <f t="shared" si="15"/>
-        <v>2020226</v>
-      </c>
-      <c r="J106" t="s">
-        <v>66</v>
-      </c>
-      <c r="K106">
-        <v>0</v>
+        <v>2030226</v>
+      </c>
+      <c r="K106" t="s">
+        <v>66</v>
       </c>
       <c r="N106">
         <v>1</v>
@@ -6617,20 +6620,20 @@
     <row r="107" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A107">
         <f t="shared" si="16"/>
-        <v>1020227</v>
+        <v>1030227</v>
       </c>
       <c r="B107" s="7">
         <v>227</v>
       </c>
       <c r="C107">
         <f t="shared" si="17"/>
-        <v>1200227</v>
+        <v>1300227</v>
       </c>
       <c r="D107" t="s">
         <v>144</v>
       </c>
       <c r="E107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107" t="s">
         <v>47</v>
@@ -6638,18 +6641,18 @@
       <c r="G107">
         <v>4</v>
       </c>
-      <c r="H107" t="s">
-        <v>65</v>
-      </c>
-      <c r="I107">
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107" t="s">
+        <v>65</v>
+      </c>
+      <c r="J107">
         <f t="shared" si="15"/>
-        <v>2020227</v>
-      </c>
-      <c r="J107" t="s">
-        <v>66</v>
-      </c>
-      <c r="K107">
-        <v>0</v>
+        <v>2030227</v>
+      </c>
+      <c r="K107" t="s">
+        <v>66</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -6658,20 +6661,20 @@
     <row r="108" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A108">
         <f t="shared" si="16"/>
-        <v>1020228</v>
+        <v>1030228</v>
       </c>
       <c r="B108" s="7">
         <v>228</v>
       </c>
       <c r="C108">
         <f t="shared" si="17"/>
-        <v>1200228</v>
+        <v>1300228</v>
       </c>
       <c r="D108" t="s">
         <v>145</v>
       </c>
       <c r="E108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" t="s">
         <v>47</v>
@@ -6679,18 +6682,18 @@
       <c r="G108">
         <v>4</v>
       </c>
-      <c r="H108" t="s">
-        <v>65</v>
-      </c>
-      <c r="I108">
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108" t="s">
+        <v>65</v>
+      </c>
+      <c r="J108">
         <f t="shared" si="15"/>
-        <v>2020228</v>
-      </c>
-      <c r="J108" t="s">
-        <v>66</v>
-      </c>
-      <c r="K108">
-        <v>0</v>
+        <v>2030228</v>
+      </c>
+      <c r="K108" t="s">
+        <v>66</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -6699,20 +6702,20 @@
     <row r="109" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A109">
         <f t="shared" si="16"/>
-        <v>1020229</v>
+        <v>1030229</v>
       </c>
       <c r="B109" s="7">
         <v>229</v>
       </c>
       <c r="C109">
         <f t="shared" si="17"/>
-        <v>1200229</v>
+        <v>1300229</v>
       </c>
       <c r="D109" t="s">
         <v>146</v>
       </c>
       <c r="E109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" t="s">
         <v>47</v>
@@ -6720,18 +6723,18 @@
       <c r="G109">
         <v>5</v>
       </c>
-      <c r="H109" t="s">
-        <v>65</v>
-      </c>
-      <c r="I109">
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109" t="s">
+        <v>65</v>
+      </c>
+      <c r="J109">
         <f t="shared" si="15"/>
-        <v>2020229</v>
-      </c>
-      <c r="J109" t="s">
-        <v>66</v>
-      </c>
-      <c r="K109">
-        <v>0</v>
+        <v>2030229</v>
+      </c>
+      <c r="K109" t="s">
+        <v>66</v>
       </c>
       <c r="N109">
         <v>1</v>
@@ -6740,20 +6743,20 @@
     <row r="110" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A110">
         <f t="shared" si="16"/>
-        <v>1020230</v>
+        <v>1030230</v>
       </c>
       <c r="B110" s="7">
         <v>230</v>
       </c>
       <c r="C110">
         <f t="shared" si="17"/>
-        <v>1200230</v>
+        <v>1300230</v>
       </c>
       <c r="D110" t="s">
         <v>147</v>
       </c>
       <c r="E110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" t="s">
         <v>47</v>
@@ -6761,18 +6764,18 @@
       <c r="G110">
         <v>5</v>
       </c>
-      <c r="H110" t="s">
-        <v>65</v>
-      </c>
-      <c r="I110">
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110" t="s">
+        <v>65</v>
+      </c>
+      <c r="J110">
         <f t="shared" si="15"/>
-        <v>2020230</v>
-      </c>
-      <c r="J110" t="s">
-        <v>66</v>
-      </c>
-      <c r="K110">
-        <v>0</v>
+        <v>2030230</v>
+      </c>
+      <c r="K110" t="s">
+        <v>66</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -6781,20 +6784,20 @@
     <row r="111" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A111">
         <f t="shared" si="16"/>
-        <v>1020231</v>
+        <v>1030231</v>
       </c>
       <c r="B111" s="7">
         <v>231</v>
       </c>
       <c r="C111">
         <f t="shared" si="17"/>
-        <v>1200231</v>
+        <v>1300231</v>
       </c>
       <c r="D111" t="s">
         <v>148</v>
       </c>
       <c r="E111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" t="s">
         <v>47</v>
@@ -6802,18 +6805,18 @@
       <c r="G111">
         <v>6</v>
       </c>
-      <c r="H111" t="s">
-        <v>65</v>
-      </c>
-      <c r="I111">
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111" t="s">
+        <v>65</v>
+      </c>
+      <c r="J111">
         <f t="shared" si="15"/>
-        <v>2020231</v>
-      </c>
-      <c r="J111" t="s">
-        <v>66</v>
-      </c>
-      <c r="K111">
-        <v>0</v>
+        <v>2030231</v>
+      </c>
+      <c r="K111" t="s">
+        <v>66</v>
       </c>
       <c r="N111">
         <v>1</v>
@@ -6822,20 +6825,20 @@
     <row r="112" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A112">
         <f t="shared" si="16"/>
-        <v>1020232</v>
+        <v>1030232</v>
       </c>
       <c r="B112" s="7">
         <v>232</v>
       </c>
       <c r="C112">
         <f t="shared" si="17"/>
-        <v>1200232</v>
+        <v>1300232</v>
       </c>
       <c r="D112" t="s">
         <v>149</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" t="s">
         <v>47</v>
@@ -6843,18 +6846,18 @@
       <c r="G112">
         <v>6</v>
       </c>
-      <c r="H112" t="s">
-        <v>65</v>
-      </c>
-      <c r="I112">
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112" t="s">
+        <v>65</v>
+      </c>
+      <c r="J112">
         <f t="shared" si="15"/>
-        <v>2020232</v>
-      </c>
-      <c r="J112" t="s">
-        <v>66</v>
-      </c>
-      <c r="K112">
-        <v>0</v>
+        <v>2030232</v>
+      </c>
+      <c r="K112" t="s">
+        <v>66</v>
       </c>
       <c r="N112">
         <v>1</v>
@@ -6863,20 +6866,20 @@
     <row r="113" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A113">
         <f t="shared" si="16"/>
-        <v>1020241</v>
+        <v>1030241</v>
       </c>
       <c r="B113" s="7">
         <v>241</v>
       </c>
       <c r="C113">
         <f t="shared" si="17"/>
-        <v>1200241</v>
+        <v>1300241</v>
       </c>
       <c r="D113" t="s">
         <v>150</v>
       </c>
       <c r="E113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" t="s">
         <v>47</v>
@@ -6884,18 +6887,18 @@
       <c r="G113">
         <v>1</v>
       </c>
-      <c r="H113" t="s">
-        <v>65</v>
-      </c>
-      <c r="I113">
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="I113" t="s">
+        <v>65</v>
+      </c>
+      <c r="J113">
         <f t="shared" si="15"/>
-        <v>2020241</v>
-      </c>
-      <c r="J113" t="s">
-        <v>66</v>
-      </c>
-      <c r="K113">
-        <v>0</v>
+        <v>2030241</v>
+      </c>
+      <c r="K113" t="s">
+        <v>66</v>
       </c>
       <c r="N113">
         <v>1</v>
@@ -6904,20 +6907,20 @@
     <row r="114" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A114">
         <f t="shared" si="16"/>
-        <v>1020242</v>
+        <v>1030242</v>
       </c>
       <c r="B114" s="7">
         <v>242</v>
       </c>
       <c r="C114">
         <f t="shared" si="17"/>
-        <v>1200242</v>
+        <v>1300242</v>
       </c>
       <c r="D114" t="s">
         <v>151</v>
       </c>
       <c r="E114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" t="s">
         <v>47</v>
@@ -6925,18 +6928,18 @@
       <c r="G114">
         <v>1</v>
       </c>
-      <c r="H114" t="s">
-        <v>65</v>
-      </c>
-      <c r="I114">
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114" t="s">
+        <v>65</v>
+      </c>
+      <c r="J114">
         <f t="shared" si="15"/>
-        <v>2020242</v>
-      </c>
-      <c r="J114" t="s">
-        <v>66</v>
-      </c>
-      <c r="K114">
-        <v>0</v>
+        <v>2030242</v>
+      </c>
+      <c r="K114" t="s">
+        <v>66</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -6945,20 +6948,20 @@
     <row r="115" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A115">
         <f t="shared" si="16"/>
-        <v>1020243</v>
+        <v>1030243</v>
       </c>
       <c r="B115" s="7">
         <v>243</v>
       </c>
       <c r="C115">
         <f t="shared" si="17"/>
-        <v>1200243</v>
+        <v>1300243</v>
       </c>
       <c r="D115" t="s">
         <v>152</v>
       </c>
       <c r="E115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" t="s">
         <v>47</v>
@@ -6966,18 +6969,18 @@
       <c r="G115">
         <v>2</v>
       </c>
-      <c r="H115" t="s">
-        <v>65</v>
-      </c>
-      <c r="I115">
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115" t="s">
+        <v>65</v>
+      </c>
+      <c r="J115">
         <f t="shared" si="15"/>
-        <v>2020243</v>
-      </c>
-      <c r="J115" t="s">
-        <v>66</v>
-      </c>
-      <c r="K115">
-        <v>0</v>
+        <v>2030243</v>
+      </c>
+      <c r="K115" t="s">
+        <v>66</v>
       </c>
       <c r="N115">
         <v>1</v>
@@ -6986,20 +6989,20 @@
     <row r="116" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A116">
         <f t="shared" si="16"/>
-        <v>1020244</v>
+        <v>1030244</v>
       </c>
       <c r="B116" s="7">
         <v>244</v>
       </c>
       <c r="C116">
         <f t="shared" si="17"/>
-        <v>1200244</v>
+        <v>1300244</v>
       </c>
       <c r="D116" t="s">
         <v>153</v>
       </c>
       <c r="E116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F116" t="s">
         <v>47</v>
@@ -7007,18 +7010,18 @@
       <c r="G116">
         <v>2</v>
       </c>
-      <c r="H116" t="s">
-        <v>65</v>
-      </c>
-      <c r="I116">
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116" t="s">
+        <v>65</v>
+      </c>
+      <c r="J116">
         <f t="shared" si="15"/>
-        <v>2020244</v>
-      </c>
-      <c r="J116" t="s">
-        <v>66</v>
-      </c>
-      <c r="K116">
-        <v>0</v>
+        <v>2030244</v>
+      </c>
+      <c r="K116" t="s">
+        <v>66</v>
       </c>
       <c r="N116">
         <v>1</v>
@@ -7027,20 +7030,20 @@
     <row r="117" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A117">
         <f t="shared" si="16"/>
-        <v>1020245</v>
+        <v>1030245</v>
       </c>
       <c r="B117" s="7">
         <v>245</v>
       </c>
       <c r="C117">
         <f t="shared" si="17"/>
-        <v>1200245</v>
+        <v>1300245</v>
       </c>
       <c r="D117" t="s">
         <v>154</v>
       </c>
       <c r="E117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" t="s">
         <v>47</v>
@@ -7048,18 +7051,18 @@
       <c r="G117">
         <v>3</v>
       </c>
-      <c r="H117" t="s">
-        <v>65</v>
-      </c>
-      <c r="I117">
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117" t="s">
+        <v>65</v>
+      </c>
+      <c r="J117">
         <f t="shared" si="15"/>
-        <v>2020245</v>
-      </c>
-      <c r="J117" t="s">
-        <v>66</v>
-      </c>
-      <c r="K117">
-        <v>0</v>
+        <v>2030245</v>
+      </c>
+      <c r="K117" t="s">
+        <v>66</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -7068,20 +7071,20 @@
     <row r="118" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A118">
         <f t="shared" si="16"/>
-        <v>1020246</v>
+        <v>1030246</v>
       </c>
       <c r="B118" s="7">
         <v>246</v>
       </c>
       <c r="C118">
         <f t="shared" si="17"/>
-        <v>1200246</v>
+        <v>1300246</v>
       </c>
       <c r="D118" t="s">
         <v>155</v>
       </c>
       <c r="E118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F118" t="s">
         <v>47</v>
@@ -7089,18 +7092,18 @@
       <c r="G118">
         <v>3</v>
       </c>
-      <c r="H118" t="s">
-        <v>65</v>
-      </c>
-      <c r="I118">
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118" t="s">
+        <v>65</v>
+      </c>
+      <c r="J118">
         <f t="shared" si="15"/>
-        <v>2020246</v>
-      </c>
-      <c r="J118" t="s">
-        <v>66</v>
-      </c>
-      <c r="K118">
-        <v>0</v>
+        <v>2030246</v>
+      </c>
+      <c r="K118" t="s">
+        <v>66</v>
       </c>
       <c r="N118">
         <v>1</v>
@@ -7109,20 +7112,20 @@
     <row r="119" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A119">
         <f t="shared" si="16"/>
-        <v>1020247</v>
+        <v>1030247</v>
       </c>
       <c r="B119" s="7">
         <v>247</v>
       </c>
       <c r="C119">
         <f t="shared" si="17"/>
-        <v>1200247</v>
+        <v>1300247</v>
       </c>
       <c r="D119" t="s">
         <v>156</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" t="s">
         <v>47</v>
@@ -7130,18 +7133,18 @@
       <c r="G119">
         <v>4</v>
       </c>
-      <c r="H119" t="s">
-        <v>65</v>
-      </c>
-      <c r="I119">
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="I119" t="s">
+        <v>65</v>
+      </c>
+      <c r="J119">
         <f t="shared" si="15"/>
-        <v>2020247</v>
-      </c>
-      <c r="J119" t="s">
-        <v>66</v>
-      </c>
-      <c r="K119">
-        <v>0</v>
+        <v>2030247</v>
+      </c>
+      <c r="K119" t="s">
+        <v>66</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -7150,20 +7153,20 @@
     <row r="120" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A120">
         <f t="shared" si="16"/>
-        <v>1020248</v>
+        <v>1030248</v>
       </c>
       <c r="B120" s="7">
         <v>248</v>
       </c>
       <c r="C120">
         <f t="shared" si="17"/>
-        <v>1200248</v>
+        <v>1300248</v>
       </c>
       <c r="D120" t="s">
         <v>157</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" t="s">
         <v>47</v>
@@ -7171,18 +7174,18 @@
       <c r="G120">
         <v>4</v>
       </c>
-      <c r="H120" t="s">
-        <v>65</v>
-      </c>
-      <c r="I120">
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120" t="s">
+        <v>65</v>
+      </c>
+      <c r="J120">
         <f t="shared" si="15"/>
-        <v>2020248</v>
-      </c>
-      <c r="J120" t="s">
-        <v>66</v>
-      </c>
-      <c r="K120">
-        <v>0</v>
+        <v>2030248</v>
+      </c>
+      <c r="K120" t="s">
+        <v>66</v>
       </c>
       <c r="N120">
         <v>1</v>
@@ -7191,20 +7194,20 @@
     <row r="121" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A121">
         <f t="shared" si="16"/>
-        <v>1020249</v>
+        <v>1030249</v>
       </c>
       <c r="B121" s="7">
         <v>249</v>
       </c>
       <c r="C121">
         <f t="shared" si="17"/>
-        <v>1200249</v>
+        <v>1300249</v>
       </c>
       <c r="D121" t="s">
         <v>158</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" t="s">
         <v>47</v>
@@ -7212,18 +7215,18 @@
       <c r="G121">
         <v>5</v>
       </c>
-      <c r="H121" t="s">
-        <v>65</v>
-      </c>
-      <c r="I121">
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121" t="s">
+        <v>65</v>
+      </c>
+      <c r="J121">
         <f t="shared" si="15"/>
-        <v>2020249</v>
-      </c>
-      <c r="J121" t="s">
-        <v>66</v>
-      </c>
-      <c r="K121">
-        <v>0</v>
+        <v>2030249</v>
+      </c>
+      <c r="K121" t="s">
+        <v>66</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -7232,20 +7235,20 @@
     <row r="122" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A122">
         <f t="shared" si="16"/>
-        <v>1020250</v>
+        <v>1030250</v>
       </c>
       <c r="B122" s="7">
         <v>250</v>
       </c>
       <c r="C122">
         <f t="shared" si="17"/>
-        <v>1200250</v>
+        <v>1300250</v>
       </c>
       <c r="D122" t="s">
         <v>159</v>
       </c>
       <c r="E122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" t="s">
         <v>47</v>
@@ -7253,18 +7256,18 @@
       <c r="G122">
         <v>5</v>
       </c>
-      <c r="H122" t="s">
-        <v>65</v>
-      </c>
-      <c r="I122">
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122" t="s">
+        <v>65</v>
+      </c>
+      <c r="J122">
         <f t="shared" si="15"/>
-        <v>2020250</v>
-      </c>
-      <c r="J122" t="s">
-        <v>66</v>
-      </c>
-      <c r="K122">
-        <v>0</v>
+        <v>2030250</v>
+      </c>
+      <c r="K122" t="s">
+        <v>66</v>
       </c>
       <c r="N122">
         <v>1</v>
@@ -7273,20 +7276,20 @@
     <row r="123" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A123">
         <f t="shared" si="16"/>
-        <v>1020251</v>
+        <v>1030251</v>
       </c>
       <c r="B123" s="7">
         <v>251</v>
       </c>
       <c r="C123">
         <f t="shared" si="17"/>
-        <v>1200251</v>
+        <v>1300251</v>
       </c>
       <c r="D123" t="s">
         <v>160</v>
       </c>
       <c r="E123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" t="s">
         <v>47</v>
@@ -7294,18 +7297,18 @@
       <c r="G123">
         <v>6</v>
       </c>
-      <c r="H123" t="s">
-        <v>65</v>
-      </c>
-      <c r="I123">
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123" t="s">
+        <v>65</v>
+      </c>
+      <c r="J123">
         <f t="shared" si="15"/>
-        <v>2020251</v>
-      </c>
-      <c r="J123" t="s">
-        <v>66</v>
-      </c>
-      <c r="K123">
-        <v>0</v>
+        <v>2030251</v>
+      </c>
+      <c r="K123" t="s">
+        <v>66</v>
       </c>
       <c r="N123">
         <v>1</v>
@@ -7314,20 +7317,20 @@
     <row r="124" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A124">
         <f t="shared" si="16"/>
-        <v>1020252</v>
+        <v>1030252</v>
       </c>
       <c r="B124" s="7">
         <v>252</v>
       </c>
       <c r="C124">
         <f t="shared" si="17"/>
-        <v>1200252</v>
+        <v>1300252</v>
       </c>
       <c r="D124" t="s">
         <v>161</v>
       </c>
       <c r="E124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" t="s">
         <v>47</v>
@@ -7335,18 +7338,18 @@
       <c r="G124">
         <v>6</v>
       </c>
-      <c r="H124" t="s">
-        <v>65</v>
-      </c>
-      <c r="I124">
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124" t="s">
+        <v>65</v>
+      </c>
+      <c r="J124">
         <f t="shared" si="15"/>
-        <v>2020252</v>
-      </c>
-      <c r="J124" t="s">
-        <v>66</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
+        <v>2030252</v>
+      </c>
+      <c r="K124" t="s">
+        <v>66</v>
       </c>
       <c r="N124">
         <v>1</v>
@@ -7355,20 +7358,20 @@
     <row r="125" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A125">
         <f t="shared" si="16"/>
-        <v>1021001</v>
+        <v>1031001</v>
       </c>
       <c r="B125" s="7">
         <v>1001</v>
       </c>
       <c r="C125">
         <f t="shared" si="17"/>
-        <v>1201001</v>
+        <v>1301001</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>162</v>
       </c>
       <c r="E125">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" t="s">
         <v>47</v>
@@ -7376,16 +7379,16 @@
       <c r="G125">
         <v>1</v>
       </c>
-      <c r="H125" t="str">
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="I125" t="str">
         <f>"itemicon_"&amp;A125&amp;".png"</f>
-        <v>itemicon_1021001.png</v>
-      </c>
-      <c r="I125">
+        <v>itemicon_1031001.png</v>
+      </c>
+      <c r="J125">
         <f t="shared" si="15"/>
-        <v>2021001</v>
-      </c>
-      <c r="K125" s="7">
-        <v>1</v>
+        <v>2031001</v>
       </c>
       <c r="L125">
         <v>2</v>
@@ -7398,20 +7401,20 @@
     <row r="126" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A126">
         <f t="shared" si="16"/>
-        <v>1021002</v>
+        <v>1031002</v>
       </c>
       <c r="B126" s="7">
         <v>1002</v>
       </c>
       <c r="C126">
         <f t="shared" si="17"/>
-        <v>1201002</v>
+        <v>1301002</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>163</v>
       </c>
       <c r="E126">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" t="s">
         <v>47</v>
@@ -7419,16 +7422,16 @@
       <c r="G126">
         <v>1</v>
       </c>
-      <c r="H126" t="str">
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126" t="str">
         <f>"itemicon_"&amp;A126&amp;".png"</f>
-        <v>itemicon_1021002.png</v>
-      </c>
-      <c r="I126">
+        <v>itemicon_1031002.png</v>
+      </c>
+      <c r="J126">
         <f t="shared" si="15"/>
-        <v>2021002</v>
-      </c>
-      <c r="K126" s="7">
-        <v>1</v>
+        <v>2031002</v>
       </c>
       <c r="L126">
         <v>3</v>
@@ -7441,20 +7444,20 @@
     <row r="127" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A127">
         <f t="shared" si="16"/>
-        <v>1021201</v>
+        <v>1031201</v>
       </c>
       <c r="B127" s="7">
         <v>1201</v>
       </c>
       <c r="C127">
         <f t="shared" si="17"/>
-        <v>1201201</v>
+        <v>1301201</v>
       </c>
       <c r="D127" t="s">
         <v>164</v>
       </c>
       <c r="E127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F127" t="s">
         <v>47</v>
@@ -7462,16 +7465,16 @@
       <c r="G127">
         <v>1</v>
       </c>
-      <c r="H127" t="str">
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127" t="str">
         <f>"itemicon_"&amp;A127&amp;".png"</f>
-        <v>itemicon_1021201.png</v>
-      </c>
-      <c r="I127">
+        <v>itemicon_1031201.png</v>
+      </c>
+      <c r="J127">
         <f t="shared" si="15"/>
-        <v>2021201</v>
-      </c>
-      <c r="K127" s="7">
-        <v>1</v>
+        <v>2031201</v>
       </c>
       <c r="L127">
         <v>1002</v>
@@ -7484,20 +7487,20 @@
     <row r="128" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A128">
         <f t="shared" si="16"/>
-        <v>1021202</v>
+        <v>1031202</v>
       </c>
       <c r="B128" s="7">
         <v>1202</v>
       </c>
       <c r="C128">
         <f t="shared" si="17"/>
-        <v>1201202</v>
+        <v>1301202</v>
       </c>
       <c r="D128" t="s">
         <v>165</v>
       </c>
       <c r="E128">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" t="s">
         <v>47</v>
@@ -7505,16 +7508,16 @@
       <c r="G128">
         <v>1</v>
       </c>
-      <c r="H128" t="str">
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128" t="str">
         <f>"itemicon_"&amp;A128&amp;".png"</f>
-        <v>itemicon_1021202.png</v>
-      </c>
-      <c r="I128">
+        <v>itemicon_1031202.png</v>
+      </c>
+      <c r="J128">
         <f t="shared" si="15"/>
-        <v>2021202</v>
-      </c>
-      <c r="K128" s="7">
-        <v>1</v>
+        <v>2031202</v>
       </c>
       <c r="L128">
         <v>1003</v>
@@ -7527,7 +7530,7 @@
     <row r="129" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A129">
         <f t="shared" si="16"/>
-        <v>1021350</v>
+        <v>1031350</v>
       </c>
       <c r="B129" s="7">
         <v>1350</v>
@@ -7539,7 +7542,7 @@
         <v>166</v>
       </c>
       <c r="E129">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F129" t="s">
         <v>47</v>
@@ -7547,14 +7550,14 @@
       <c r="G129">
         <v>1</v>
       </c>
-      <c r="H129" t="s">
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129" t="s">
         <v>167</v>
       </c>
-      <c r="I129">
+      <c r="J129">
         <v>201801</v>
-      </c>
-      <c r="K129" s="7">
-        <v>1</v>
       </c>
       <c r="L129">
         <v>1801</v>
@@ -7566,7 +7569,7 @@
     <row r="130" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A130">
         <f t="shared" si="16"/>
-        <v>1021351</v>
+        <v>1031351</v>
       </c>
       <c r="B130" s="7">
         <v>1351</v>
@@ -7578,7 +7581,7 @@
         <v>168</v>
       </c>
       <c r="E130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" t="s">
         <v>47</v>
@@ -7586,14 +7589,14 @@
       <c r="G130">
         <v>1</v>
       </c>
-      <c r="H130" t="s">
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130" t="s">
         <v>169</v>
       </c>
-      <c r="I130">
+      <c r="J130">
         <v>201802</v>
-      </c>
-      <c r="K130" s="7">
-        <v>1</v>
       </c>
       <c r="L130">
         <v>1802</v>
@@ -7626,16 +7629,16 @@
       <c r="G131">
         <v>1</v>
       </c>
-      <c r="H131" t="str">
-        <f t="shared" ref="H131:H144" si="20">"itemicon_"&amp;A131&amp;".png"</f>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131" t="str">
+        <f t="shared" ref="I131:I144" si="20">"itemicon_"&amp;A131&amp;".png"</f>
         <v>itemicon_1021401.png</v>
       </c>
-      <c r="I131">
-        <f t="shared" ref="I131:I144" si="21">2000000+E131*10000+B131</f>
+      <c r="J131">
+        <f t="shared" ref="J131:J144" si="21">2000000+E131*10000+B131</f>
         <v>2021401</v>
-      </c>
-      <c r="K131" s="7">
-        <v>1</v>
       </c>
       <c r="L131">
         <v>2002</v>
@@ -7669,16 +7672,16 @@
       <c r="G132">
         <v>1</v>
       </c>
-      <c r="H132" t="str">
+      <c r="H132">
+        <v>1</v>
+      </c>
+      <c r="I132" t="str">
         <f t="shared" si="20"/>
         <v>itemicon_1021402.png</v>
       </c>
-      <c r="I132">
+      <c r="J132">
         <f t="shared" si="21"/>
         <v>2021402</v>
-      </c>
-      <c r="K132" s="7">
-        <v>1</v>
       </c>
       <c r="L132">
         <v>2003</v>
@@ -7691,20 +7694,20 @@
     <row r="133" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A133">
         <f t="shared" si="18"/>
-        <v>1021601</v>
+        <v>1031601</v>
       </c>
       <c r="B133" s="7">
         <v>1601</v>
       </c>
       <c r="C133">
         <f t="shared" si="19"/>
-        <v>1201601</v>
+        <v>1301601</v>
       </c>
       <c r="D133" s="11" t="s">
         <v>172</v>
       </c>
       <c r="E133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" t="s">
         <v>47</v>
@@ -7712,16 +7715,16 @@
       <c r="G133">
         <v>1</v>
       </c>
-      <c r="H133" t="str">
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1021601.png</v>
-      </c>
-      <c r="I133">
+        <v>itemicon_1031601.png</v>
+      </c>
+      <c r="J133">
         <f t="shared" si="21"/>
-        <v>2021601</v>
-      </c>
-      <c r="K133" s="7">
-        <v>1</v>
+        <v>2031601</v>
       </c>
       <c r="L133">
         <v>3002</v>
@@ -7734,20 +7737,20 @@
     <row r="134" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A134">
         <f t="shared" si="18"/>
-        <v>1021602</v>
+        <v>1031602</v>
       </c>
       <c r="B134" s="7">
         <v>1602</v>
       </c>
       <c r="C134">
         <f t="shared" si="19"/>
-        <v>1201602</v>
+        <v>1301602</v>
       </c>
       <c r="D134" s="11" t="s">
         <v>173</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" t="s">
         <v>47</v>
@@ -7755,16 +7758,16 @@
       <c r="G134">
         <v>1</v>
       </c>
-      <c r="H134" t="str">
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1021602.png</v>
-      </c>
-      <c r="I134">
+        <v>itemicon_1031602.png</v>
+      </c>
+      <c r="J134">
         <f t="shared" si="21"/>
-        <v>2021602</v>
-      </c>
-      <c r="K134" s="7">
-        <v>1</v>
+        <v>2031602</v>
       </c>
       <c r="L134">
         <v>3003</v>
@@ -7777,20 +7780,20 @@
     <row r="135" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A135">
         <f t="shared" si="18"/>
-        <v>1021801</v>
+        <v>1031801</v>
       </c>
       <c r="B135" s="7">
         <v>1801</v>
       </c>
       <c r="C135">
         <f t="shared" si="19"/>
-        <v>1201801</v>
+        <v>1301801</v>
       </c>
       <c r="D135" s="12" t="s">
         <v>174</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" t="s">
         <v>47</v>
@@ -7798,16 +7801,16 @@
       <c r="G135">
         <v>1</v>
       </c>
-      <c r="H135" t="str">
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1021801.png</v>
-      </c>
-      <c r="I135">
+        <v>itemicon_1031801.png</v>
+      </c>
+      <c r="J135">
         <f t="shared" si="21"/>
-        <v>2021801</v>
-      </c>
-      <c r="K135" s="7">
-        <v>1</v>
+        <v>2031801</v>
       </c>
       <c r="L135">
         <v>4002</v>
@@ -7820,20 +7823,20 @@
     <row r="136" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A136">
         <f t="shared" si="18"/>
-        <v>1021802</v>
+        <v>1031802</v>
       </c>
       <c r="B136" s="7">
         <v>1802</v>
       </c>
       <c r="C136">
         <f t="shared" si="19"/>
-        <v>1201802</v>
+        <v>1301802</v>
       </c>
       <c r="D136" s="12" t="s">
         <v>175</v>
       </c>
       <c r="E136">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" t="s">
         <v>47</v>
@@ -7841,16 +7844,16 @@
       <c r="G136">
         <v>1</v>
       </c>
-      <c r="H136" t="str">
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1021802.png</v>
-      </c>
-      <c r="I136">
+        <v>itemicon_1031802.png</v>
+      </c>
+      <c r="J136">
         <f t="shared" si="21"/>
-        <v>2021802</v>
-      </c>
-      <c r="K136" s="7">
-        <v>1</v>
+        <v>2031802</v>
       </c>
       <c r="L136">
         <v>4003</v>
@@ -7863,20 +7866,20 @@
     <row r="137" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A137">
         <f t="shared" si="18"/>
-        <v>1022001</v>
+        <v>1032001</v>
       </c>
       <c r="B137" s="7">
         <v>2001</v>
       </c>
       <c r="C137">
         <f t="shared" si="19"/>
-        <v>1202001</v>
+        <v>1302001</v>
       </c>
       <c r="D137" s="13" t="s">
         <v>176</v>
       </c>
       <c r="E137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" t="s">
         <v>47</v>
@@ -7884,16 +7887,16 @@
       <c r="G137">
         <v>1</v>
       </c>
-      <c r="H137" t="str">
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1022001.png</v>
-      </c>
-      <c r="I137">
+        <v>itemicon_1032001.png</v>
+      </c>
+      <c r="J137">
         <f t="shared" si="21"/>
-        <v>2022001</v>
-      </c>
-      <c r="K137" s="7">
-        <v>1</v>
+        <v>2032001</v>
       </c>
       <c r="L137">
         <v>5002</v>
@@ -7906,20 +7909,20 @@
     <row r="138" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A138">
         <f t="shared" si="18"/>
-        <v>1022002</v>
+        <v>1032002</v>
       </c>
       <c r="B138" s="7">
         <v>2002</v>
       </c>
       <c r="C138">
         <f t="shared" si="19"/>
-        <v>1202002</v>
+        <v>1302002</v>
       </c>
       <c r="D138" s="13" t="s">
         <v>177</v>
       </c>
       <c r="E138">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" t="s">
         <v>47</v>
@@ -7927,16 +7930,16 @@
       <c r="G138">
         <v>1</v>
       </c>
-      <c r="H138" t="str">
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1022002.png</v>
-      </c>
-      <c r="I138">
+        <v>itemicon_1032002.png</v>
+      </c>
+      <c r="J138">
         <f t="shared" si="21"/>
-        <v>2022002</v>
-      </c>
-      <c r="K138" s="7">
-        <v>1</v>
+        <v>2032002</v>
       </c>
       <c r="L138">
         <v>5003</v>
@@ -7949,20 +7952,20 @@
     <row r="139" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A139">
         <f t="shared" si="18"/>
-        <v>1022201</v>
+        <v>1032201</v>
       </c>
       <c r="B139" s="7">
         <v>2201</v>
       </c>
       <c r="C139">
         <f t="shared" si="19"/>
-        <v>1202201</v>
+        <v>1302201</v>
       </c>
       <c r="D139" s="14" t="s">
         <v>178</v>
       </c>
       <c r="E139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139" t="s">
         <v>47</v>
@@ -7970,16 +7973,16 @@
       <c r="G139">
         <v>1</v>
       </c>
-      <c r="H139" t="str">
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1022201.png</v>
-      </c>
-      <c r="I139">
+        <v>itemicon_1032201.png</v>
+      </c>
+      <c r="J139">
         <f t="shared" si="21"/>
-        <v>2022201</v>
-      </c>
-      <c r="K139" s="7">
-        <v>1</v>
+        <v>2032201</v>
       </c>
       <c r="L139">
         <v>6002</v>
@@ -7992,20 +7995,20 @@
     <row r="140" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A140">
         <f t="shared" si="18"/>
-        <v>1022202</v>
+        <v>1032202</v>
       </c>
       <c r="B140" s="7">
         <v>2202</v>
       </c>
       <c r="C140">
         <f t="shared" si="19"/>
-        <v>1202202</v>
+        <v>1302202</v>
       </c>
       <c r="D140" s="14" t="s">
         <v>179</v>
       </c>
       <c r="E140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F140" t="s">
         <v>47</v>
@@ -8013,16 +8016,16 @@
       <c r="G140">
         <v>1</v>
       </c>
-      <c r="H140" t="str">
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1022202.png</v>
-      </c>
-      <c r="I140">
+        <v>itemicon_1032202.png</v>
+      </c>
+      <c r="J140">
         <f t="shared" si="21"/>
-        <v>2022202</v>
-      </c>
-      <c r="K140" s="7">
-        <v>1</v>
+        <v>2032202</v>
       </c>
       <c r="L140">
         <v>6003</v>
@@ -8056,19 +8059,19 @@
       <c r="G141">
         <v>1</v>
       </c>
-      <c r="H141" t="str">
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141" t="str">
         <f t="shared" si="20"/>
         <v>itemicon_1022501.png</v>
       </c>
-      <c r="I141">
+      <c r="J141">
         <f t="shared" si="21"/>
         <v>2022501</v>
       </c>
-      <c r="J141" t="s">
+      <c r="K141" t="s">
         <v>181</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
       </c>
       <c r="N141">
         <v>999</v>
@@ -8098,18 +8101,18 @@
       <c r="G142">
         <v>1</v>
       </c>
-      <c r="H142" t="s">
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142" t="s">
         <v>183</v>
       </c>
-      <c r="I142">
+      <c r="J142">
         <f t="shared" si="21"/>
         <v>2022502</v>
       </c>
-      <c r="J142" t="s">
+      <c r="K142" t="s">
         <v>184</v>
-      </c>
-      <c r="K142">
-        <v>0</v>
       </c>
       <c r="N142">
         <v>999</v>
@@ -8135,17 +8138,17 @@
       <c r="G143">
         <v>2</v>
       </c>
-      <c r="H143" t="s">
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143" t="s">
         <v>186</v>
       </c>
-      <c r="I143">
+      <c r="J143">
         <v>2023001</v>
       </c>
-      <c r="J143" t="s">
+      <c r="K143" t="s">
         <v>187</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
       </c>
       <c r="N143">
         <v>999</v>
@@ -8171,17 +8174,17 @@
       <c r="G144">
         <v>3</v>
       </c>
-      <c r="H144" t="s">
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144" t="s">
         <v>189</v>
       </c>
-      <c r="I144">
+      <c r="J144">
         <v>2023002</v>
       </c>
-      <c r="J144" t="s">
+      <c r="K144" t="s">
         <v>187</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
       </c>
       <c r="N144">
         <v>999</v>
@@ -8207,17 +8210,17 @@
       <c r="G145">
         <v>4</v>
       </c>
-      <c r="H145" t="s">
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145" t="s">
         <v>191</v>
       </c>
-      <c r="I145">
+      <c r="J145">
         <v>2023003</v>
       </c>
-      <c r="J145" t="s">
+      <c r="K145" t="s">
         <v>187</v>
-      </c>
-      <c r="K145">
-        <v>0</v>
       </c>
       <c r="N145">
         <v>999</v>
@@ -8243,17 +8246,17 @@
       <c r="G146">
         <v>5</v>
       </c>
-      <c r="H146" t="s">
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146" t="s">
         <v>193</v>
       </c>
-      <c r="I146">
+      <c r="J146">
         <v>2023004</v>
       </c>
-      <c r="J146" t="s">
+      <c r="K146" t="s">
         <v>187</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
       </c>
       <c r="N146">
         <v>999</v>
@@ -8279,17 +8282,17 @@
       <c r="G147">
         <v>6</v>
       </c>
-      <c r="H147" t="s">
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147" t="s">
         <v>195</v>
       </c>
-      <c r="I147">
+      <c r="J147">
         <v>2023005</v>
       </c>
-      <c r="J147" t="s">
+      <c r="K147" t="s">
         <v>187</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
       </c>
       <c r="N147">
         <v>999</v>
@@ -8315,17 +8318,17 @@
       <c r="G148">
         <v>2</v>
       </c>
-      <c r="H148" t="s">
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148" t="s">
         <v>197</v>
       </c>
-      <c r="I148">
+      <c r="J148">
         <v>2023101</v>
       </c>
-      <c r="J148" t="s">
+      <c r="K148" t="s">
         <v>198</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
       </c>
       <c r="N148">
         <v>999</v>
@@ -8351,17 +8354,17 @@
       <c r="G149">
         <v>3</v>
       </c>
-      <c r="H149" t="s">
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149" t="s">
         <v>200</v>
       </c>
-      <c r="I149">
+      <c r="J149">
         <v>2023102</v>
       </c>
-      <c r="J149" t="s">
+      <c r="K149" t="s">
         <v>198</v>
-      </c>
-      <c r="K149">
-        <v>0</v>
       </c>
       <c r="N149">
         <v>999</v>
@@ -8387,17 +8390,17 @@
       <c r="G150">
         <v>4</v>
       </c>
-      <c r="H150" t="s">
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150" t="s">
         <v>202</v>
       </c>
-      <c r="I150">
+      <c r="J150">
         <v>2023103</v>
       </c>
-      <c r="J150" t="s">
+      <c r="K150" t="s">
         <v>198</v>
-      </c>
-      <c r="K150">
-        <v>0</v>
       </c>
       <c r="N150">
         <v>999</v>
@@ -8423,17 +8426,17 @@
       <c r="G151">
         <v>5</v>
       </c>
-      <c r="H151" t="s">
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151" t="s">
         <v>204</v>
       </c>
-      <c r="I151">
+      <c r="J151">
         <v>2023104</v>
       </c>
-      <c r="J151" t="s">
+      <c r="K151" t="s">
         <v>198</v>
-      </c>
-      <c r="K151">
-        <v>0</v>
       </c>
       <c r="N151">
         <v>999</v>
@@ -8459,17 +8462,17 @@
       <c r="G152">
         <v>6</v>
       </c>
-      <c r="H152" t="s">
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152" t="s">
         <v>206</v>
       </c>
-      <c r="I152">
+      <c r="J152">
         <v>2023105</v>
       </c>
-      <c r="J152" t="s">
+      <c r="K152" t="s">
         <v>198</v>
-      </c>
-      <c r="K152">
-        <v>0</v>
       </c>
       <c r="N152">
         <v>999</v>
@@ -8495,17 +8498,17 @@
       <c r="G153">
         <v>2</v>
       </c>
-      <c r="H153" t="s">
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153" t="s">
         <v>208</v>
       </c>
-      <c r="I153">
+      <c r="J153">
         <v>2023201</v>
       </c>
-      <c r="J153" t="s">
+      <c r="K153" t="s">
         <v>209</v>
-      </c>
-      <c r="K153">
-        <v>0</v>
       </c>
       <c r="N153">
         <v>999</v>
@@ -8531,17 +8534,17 @@
       <c r="G154">
         <v>3</v>
       </c>
-      <c r="H154" t="s">
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154" t="s">
         <v>211</v>
       </c>
-      <c r="I154">
+      <c r="J154">
         <v>2023202</v>
       </c>
-      <c r="J154" t="s">
+      <c r="K154" t="s">
         <v>209</v>
-      </c>
-      <c r="K154">
-        <v>0</v>
       </c>
       <c r="N154">
         <v>999</v>
@@ -8567,17 +8570,17 @@
       <c r="G155">
         <v>4</v>
       </c>
-      <c r="H155" t="s">
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155" t="s">
         <v>213</v>
       </c>
-      <c r="I155">
+      <c r="J155">
         <v>2023203</v>
       </c>
-      <c r="J155" t="s">
+      <c r="K155" t="s">
         <v>209</v>
-      </c>
-      <c r="K155">
-        <v>0</v>
       </c>
       <c r="N155">
         <v>999</v>
@@ -8603,17 +8606,17 @@
       <c r="G156">
         <v>5</v>
       </c>
-      <c r="H156" t="s">
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156" t="s">
         <v>215</v>
       </c>
-      <c r="I156">
+      <c r="J156">
         <v>2023204</v>
       </c>
-      <c r="J156" t="s">
+      <c r="K156" t="s">
         <v>209</v>
-      </c>
-      <c r="K156">
-        <v>0</v>
       </c>
       <c r="N156">
         <v>999</v>
@@ -8639,17 +8642,17 @@
       <c r="G157">
         <v>6</v>
       </c>
-      <c r="H157" t="s">
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157" t="s">
         <v>217</v>
       </c>
-      <c r="I157">
+      <c r="J157">
         <v>2023205</v>
       </c>
-      <c r="J157" t="s">
+      <c r="K157" t="s">
         <v>209</v>
-      </c>
-      <c r="K157">
-        <v>0</v>
       </c>
       <c r="N157">
         <v>999</v>
@@ -8675,17 +8678,17 @@
       <c r="G158">
         <v>2</v>
       </c>
-      <c r="H158" t="s">
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158" t="s">
         <v>219</v>
       </c>
-      <c r="I158">
+      <c r="J158">
         <v>2023301</v>
       </c>
-      <c r="J158" t="s">
+      <c r="K158" t="s">
         <v>220</v>
-      </c>
-      <c r="K158">
-        <v>0</v>
       </c>
       <c r="N158">
         <v>999</v>
@@ -8711,17 +8714,17 @@
       <c r="G159">
         <v>3</v>
       </c>
-      <c r="H159" t="s">
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159" t="s">
         <v>222</v>
       </c>
-      <c r="I159">
+      <c r="J159">
         <v>2023302</v>
       </c>
-      <c r="J159" t="s">
+      <c r="K159" t="s">
         <v>220</v>
-      </c>
-      <c r="K159">
-        <v>0</v>
       </c>
       <c r="N159">
         <v>999</v>
@@ -8747,17 +8750,17 @@
       <c r="G160">
         <v>4</v>
       </c>
-      <c r="H160" t="s">
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160" t="s">
         <v>224</v>
       </c>
-      <c r="I160">
+      <c r="J160">
         <v>2023303</v>
       </c>
-      <c r="J160" t="s">
+      <c r="K160" t="s">
         <v>220</v>
-      </c>
-      <c r="K160">
-        <v>0</v>
       </c>
       <c r="N160">
         <v>999</v>
@@ -8783,17 +8786,17 @@
       <c r="G161">
         <v>5</v>
       </c>
-      <c r="H161" t="s">
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161" t="s">
         <v>226</v>
       </c>
-      <c r="I161">
+      <c r="J161">
         <v>2023304</v>
       </c>
-      <c r="J161" t="s">
+      <c r="K161" t="s">
         <v>220</v>
-      </c>
-      <c r="K161">
-        <v>0</v>
       </c>
       <c r="N161">
         <v>999</v>
@@ -8819,17 +8822,17 @@
       <c r="G162">
         <v>6</v>
       </c>
-      <c r="H162" t="s">
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162" t="s">
         <v>228</v>
       </c>
-      <c r="I162">
+      <c r="J162">
         <v>2023305</v>
       </c>
-      <c r="J162" t="s">
+      <c r="K162" t="s">
         <v>220</v>
-      </c>
-      <c r="K162">
-        <v>0</v>
       </c>
       <c r="N162">
         <v>999</v>
@@ -8855,17 +8858,17 @@
       <c r="G163">
         <v>2</v>
       </c>
-      <c r="H163" t="s">
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163" t="s">
         <v>230</v>
       </c>
-      <c r="I163">
+      <c r="J163">
         <v>2023401</v>
       </c>
-      <c r="J163" t="s">
+      <c r="K163" t="s">
         <v>231</v>
-      </c>
-      <c r="K163">
-        <v>0</v>
       </c>
       <c r="N163">
         <v>999</v>
@@ -8891,17 +8894,17 @@
       <c r="G164">
         <v>3</v>
       </c>
-      <c r="H164" t="s">
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164" t="s">
         <v>233</v>
       </c>
-      <c r="I164">
+      <c r="J164">
         <v>2023402</v>
       </c>
-      <c r="J164" t="s">
+      <c r="K164" t="s">
         <v>231</v>
-      </c>
-      <c r="K164">
-        <v>0</v>
       </c>
       <c r="N164">
         <v>999</v>
@@ -8927,17 +8930,17 @@
       <c r="G165">
         <v>4</v>
       </c>
-      <c r="H165" t="s">
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165" t="s">
         <v>235</v>
       </c>
-      <c r="I165">
+      <c r="J165">
         <v>2023403</v>
       </c>
-      <c r="J165" t="s">
+      <c r="K165" t="s">
         <v>231</v>
-      </c>
-      <c r="K165">
-        <v>0</v>
       </c>
       <c r="N165">
         <v>999</v>
@@ -8963,17 +8966,17 @@
       <c r="G166">
         <v>5</v>
       </c>
-      <c r="H166" t="s">
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166" t="s">
         <v>237</v>
       </c>
-      <c r="I166">
+      <c r="J166">
         <v>2023404</v>
       </c>
-      <c r="J166" t="s">
+      <c r="K166" t="s">
         <v>231</v>
-      </c>
-      <c r="K166">
-        <v>0</v>
       </c>
       <c r="N166">
         <v>999</v>
@@ -8999,17 +9002,17 @@
       <c r="G167">
         <v>6</v>
       </c>
-      <c r="H167" t="s">
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167" t="s">
         <v>239</v>
       </c>
-      <c r="I167">
+      <c r="J167">
         <v>2023405</v>
       </c>
-      <c r="J167" t="s">
+      <c r="K167" t="s">
         <v>231</v>
-      </c>
-      <c r="K167">
-        <v>0</v>
       </c>
       <c r="N167">
         <v>999</v>
@@ -9038,19 +9041,19 @@
       <c r="G168">
         <v>1</v>
       </c>
-      <c r="H168" t="str">
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168" t="str">
         <f>"itemicon_"&amp;A168&amp;".png"</f>
         <v>itemicon_1990000.png</v>
       </c>
-      <c r="I168">
+      <c r="J168">
         <f>2000000+E168*10000+B168</f>
         <v>2990000</v>
       </c>
-      <c r="J168" t="s">
+      <c r="K168" t="s">
         <v>242</v>
-      </c>
-      <c r="K168">
-        <v>0</v>
       </c>
       <c r="N168">
         <v>-1</v>
@@ -9079,19 +9082,19 @@
       <c r="G169">
         <v>1</v>
       </c>
-      <c r="H169" t="str">
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169" t="str">
         <f>"itemicon_"&amp;A169&amp;".png"</f>
         <v>itemicon_1980000.png</v>
       </c>
-      <c r="I169">
+      <c r="J169">
         <f>2000000+E169*10000+B169</f>
         <v>2980000</v>
       </c>
-      <c r="J169" t="s">
+      <c r="K169" t="s">
         <v>244</v>
-      </c>
-      <c r="K169">
-        <v>0</v>
       </c>
       <c r="N169">
         <v>-1</v>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -179,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F168" authorId="0">
+    <comment ref="F169" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="246">
   <si>
     <t>道具ID</t>
   </si>
@@ -761,6 +761,9 @@
   </si>
   <si>
     <t>在指定的游戏中产出</t>
+  </si>
+  <si>
+    <t>夺宝优惠券</t>
   </si>
   <si>
     <t>1星扳手</t>
@@ -2208,7 +2211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P170"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
@@ -7614,7 +7617,7 @@
         <v>1401</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:C142" si="19">1000000+E131*100000+B131</f>
+        <f t="shared" ref="C131:C143" si="19">1000000+E131*100000+B131</f>
         <v>1201401</v>
       </c>
       <c r="D131" s="10" t="s">
@@ -8118,13 +8121,17 @@
         <v>999</v>
       </c>
     </row>
-    <row r="143" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="143" customFormat="1" ht="18" customHeight="1" spans="1:14">
       <c r="A143">
-        <v>1023001</v>
-      </c>
-      <c r="B143" s="7"/>
+        <f t="shared" si="18"/>
+        <v>1022503</v>
+      </c>
+      <c r="B143">
+        <v>2503</v>
+      </c>
       <c r="C143">
-        <v>1023001</v>
+        <f t="shared" si="19"/>
+        <v>1202503</v>
       </c>
       <c r="D143" t="s">
         <v>185</v>
@@ -8136,19 +8143,20 @@
         <v>47</v>
       </c>
       <c r="G143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
       <c r="I143" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J143">
-        <v>2023001</v>
+        <f t="shared" si="21"/>
+        <v>2022503</v>
       </c>
       <c r="K143" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N143">
         <v>999</v>
@@ -8156,14 +8164,14 @@
     </row>
     <row r="144" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A144">
-        <v>1023002</v>
+        <v>1023001</v>
       </c>
       <c r="B144" s="7"/>
       <c r="C144">
-        <v>1023002</v>
+        <v>1023001</v>
       </c>
       <c r="D144" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E144">
         <v>2</v>
@@ -8172,19 +8180,19 @@
         <v>47</v>
       </c>
       <c r="G144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H144">
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J144">
-        <v>2023002</v>
+        <v>2023001</v>
       </c>
       <c r="K144" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N144">
         <v>999</v>
@@ -8192,14 +8200,14 @@
     </row>
     <row r="145" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A145">
-        <v>1023003</v>
+        <v>1023002</v>
       </c>
       <c r="B145" s="7"/>
       <c r="C145">
-        <v>1023003</v>
+        <v>1023002</v>
       </c>
       <c r="D145" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E145">
         <v>2</v>
@@ -8208,19 +8216,19 @@
         <v>47</v>
       </c>
       <c r="G145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J145">
-        <v>2023003</v>
+        <v>2023002</v>
       </c>
       <c r="K145" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N145">
         <v>999</v>
@@ -8228,14 +8236,14 @@
     </row>
     <row r="146" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A146">
-        <v>1023004</v>
+        <v>1023003</v>
       </c>
       <c r="B146" s="7"/>
       <c r="C146">
-        <v>1023004</v>
+        <v>1023003</v>
       </c>
       <c r="D146" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E146">
         <v>2</v>
@@ -8244,19 +8252,19 @@
         <v>47</v>
       </c>
       <c r="G146">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H146">
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J146">
-        <v>2023004</v>
+        <v>2023003</v>
       </c>
       <c r="K146" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N146">
         <v>999</v>
@@ -8264,14 +8272,14 @@
     </row>
     <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A147">
-        <v>1023005</v>
+        <v>1023004</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147">
-        <v>1023005</v>
+        <v>1023004</v>
       </c>
       <c r="D147" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E147">
         <v>2</v>
@@ -8280,19 +8288,19 @@
         <v>47</v>
       </c>
       <c r="G147">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J147">
-        <v>2023005</v>
+        <v>2023004</v>
       </c>
       <c r="K147" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N147">
         <v>999</v>
@@ -8300,14 +8308,14 @@
     </row>
     <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A148">
-        <v>1023101</v>
+        <v>1023005</v>
       </c>
       <c r="B148" s="7"/>
       <c r="C148">
-        <v>1023101</v>
+        <v>1023005</v>
       </c>
       <c r="D148" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E148">
         <v>2</v>
@@ -8316,19 +8324,19 @@
         <v>47</v>
       </c>
       <c r="G148">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J148">
-        <v>2023101</v>
+        <v>2023005</v>
       </c>
       <c r="K148" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="N148">
         <v>999</v>
@@ -8336,14 +8344,14 @@
     </row>
     <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A149">
-        <v>1023102</v>
+        <v>1023101</v>
       </c>
       <c r="B149" s="7"/>
       <c r="C149">
-        <v>1023102</v>
+        <v>1023101</v>
       </c>
       <c r="D149" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E149">
         <v>2</v>
@@ -8352,19 +8360,19 @@
         <v>47</v>
       </c>
       <c r="G149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J149">
-        <v>2023102</v>
+        <v>2023101</v>
       </c>
       <c r="K149" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N149">
         <v>999</v>
@@ -8372,14 +8380,14 @@
     </row>
     <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A150">
-        <v>1023103</v>
+        <v>1023102</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150">
-        <v>1023103</v>
+        <v>1023102</v>
       </c>
       <c r="D150" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E150">
         <v>2</v>
@@ -8388,19 +8396,19 @@
         <v>47</v>
       </c>
       <c r="G150">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J150">
-        <v>2023103</v>
+        <v>2023102</v>
       </c>
       <c r="K150" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N150">
         <v>999</v>
@@ -8408,14 +8416,14 @@
     </row>
     <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A151">
-        <v>1023104</v>
+        <v>1023103</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151">
-        <v>1023104</v>
+        <v>1023103</v>
       </c>
       <c r="D151" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E151">
         <v>2</v>
@@ -8424,19 +8432,19 @@
         <v>47</v>
       </c>
       <c r="G151">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J151">
-        <v>2023104</v>
+        <v>2023103</v>
       </c>
       <c r="K151" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N151">
         <v>999</v>
@@ -8444,14 +8452,14 @@
     </row>
     <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A152">
-        <v>1023105</v>
+        <v>1023104</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152">
-        <v>1023105</v>
+        <v>1023104</v>
       </c>
       <c r="D152" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -8460,19 +8468,19 @@
         <v>47</v>
       </c>
       <c r="G152">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H152">
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J152">
-        <v>2023105</v>
+        <v>2023104</v>
       </c>
       <c r="K152" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N152">
         <v>999</v>
@@ -8480,14 +8488,14 @@
     </row>
     <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A153">
-        <v>1023201</v>
+        <v>1023105</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153">
-        <v>1023201</v>
+        <v>1023105</v>
       </c>
       <c r="D153" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -8496,19 +8504,19 @@
         <v>47</v>
       </c>
       <c r="G153">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H153">
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J153">
-        <v>2023201</v>
+        <v>2023105</v>
       </c>
       <c r="K153" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="N153">
         <v>999</v>
@@ -8516,14 +8524,14 @@
     </row>
     <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A154">
-        <v>1023202</v>
+        <v>1023201</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154">
-        <v>1023202</v>
+        <v>1023201</v>
       </c>
       <c r="D154" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -8532,19 +8540,19 @@
         <v>47</v>
       </c>
       <c r="G154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H154">
         <v>0</v>
       </c>
       <c r="I154" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J154">
-        <v>2023202</v>
+        <v>2023201</v>
       </c>
       <c r="K154" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N154">
         <v>999</v>
@@ -8552,14 +8560,14 @@
     </row>
     <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A155">
-        <v>1023203</v>
+        <v>1023202</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155">
-        <v>1023203</v>
+        <v>1023202</v>
       </c>
       <c r="D155" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -8568,19 +8576,19 @@
         <v>47</v>
       </c>
       <c r="G155">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J155">
-        <v>2023203</v>
+        <v>2023202</v>
       </c>
       <c r="K155" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N155">
         <v>999</v>
@@ -8588,14 +8596,14 @@
     </row>
     <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A156">
-        <v>1023204</v>
+        <v>1023203</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156">
-        <v>1023204</v>
+        <v>1023203</v>
       </c>
       <c r="D156" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E156">
         <v>2</v>
@@ -8604,19 +8612,19 @@
         <v>47</v>
       </c>
       <c r="G156">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H156">
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J156">
-        <v>2023204</v>
+        <v>2023203</v>
       </c>
       <c r="K156" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N156">
         <v>999</v>
@@ -8624,14 +8632,14 @@
     </row>
     <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A157">
-        <v>1023205</v>
+        <v>1023204</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157">
-        <v>1023205</v>
+        <v>1023204</v>
       </c>
       <c r="D157" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -8640,19 +8648,19 @@
         <v>47</v>
       </c>
       <c r="G157">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H157">
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J157">
-        <v>2023205</v>
+        <v>2023204</v>
       </c>
       <c r="K157" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N157">
         <v>999</v>
@@ -8660,14 +8668,14 @@
     </row>
     <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A158">
-        <v>1023301</v>
+        <v>1023205</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158">
-        <v>1023301</v>
+        <v>1023205</v>
       </c>
       <c r="D158" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E158">
         <v>2</v>
@@ -8676,19 +8684,19 @@
         <v>47</v>
       </c>
       <c r="G158">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H158">
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J158">
-        <v>2023301</v>
+        <v>2023205</v>
       </c>
       <c r="K158" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="N158">
         <v>999</v>
@@ -8696,14 +8704,14 @@
     </row>
     <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A159">
-        <v>1023302</v>
+        <v>1023301</v>
       </c>
       <c r="B159" s="7"/>
       <c r="C159">
-        <v>1023302</v>
+        <v>1023301</v>
       </c>
       <c r="D159" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -8712,19 +8720,19 @@
         <v>47</v>
       </c>
       <c r="G159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H159">
         <v>0</v>
       </c>
       <c r="I159" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J159">
-        <v>2023302</v>
+        <v>2023301</v>
       </c>
       <c r="K159" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N159">
         <v>999</v>
@@ -8732,14 +8740,14 @@
     </row>
     <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A160">
-        <v>1023303</v>
+        <v>1023302</v>
       </c>
       <c r="B160" s="7"/>
       <c r="C160">
-        <v>1023303</v>
+        <v>1023302</v>
       </c>
       <c r="D160" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E160">
         <v>2</v>
@@ -8748,19 +8756,19 @@
         <v>47</v>
       </c>
       <c r="G160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H160">
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J160">
-        <v>2023303</v>
+        <v>2023302</v>
       </c>
       <c r="K160" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N160">
         <v>999</v>
@@ -8768,14 +8776,14 @@
     </row>
     <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A161">
-        <v>1023304</v>
+        <v>1023303</v>
       </c>
       <c r="B161" s="7"/>
       <c r="C161">
-        <v>1023304</v>
+        <v>1023303</v>
       </c>
       <c r="D161" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -8784,19 +8792,19 @@
         <v>47</v>
       </c>
       <c r="G161">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H161">
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J161">
-        <v>2023304</v>
+        <v>2023303</v>
       </c>
       <c r="K161" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N161">
         <v>999</v>
@@ -8804,14 +8812,14 @@
     </row>
     <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A162">
-        <v>1023305</v>
+        <v>1023304</v>
       </c>
       <c r="B162" s="7"/>
       <c r="C162">
-        <v>1023305</v>
+        <v>1023304</v>
       </c>
       <c r="D162" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -8820,19 +8828,19 @@
         <v>47</v>
       </c>
       <c r="G162">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H162">
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J162">
-        <v>2023305</v>
+        <v>2023304</v>
       </c>
       <c r="K162" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N162">
         <v>999</v>
@@ -8840,14 +8848,14 @@
     </row>
     <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A163">
-        <v>1023401</v>
+        <v>1023305</v>
       </c>
       <c r="B163" s="7"/>
       <c r="C163">
-        <v>1023401</v>
+        <v>1023305</v>
       </c>
       <c r="D163" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E163">
         <v>2</v>
@@ -8856,19 +8864,19 @@
         <v>47</v>
       </c>
       <c r="G163">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H163">
         <v>0</v>
       </c>
       <c r="I163" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J163">
-        <v>2023401</v>
+        <v>2023305</v>
       </c>
       <c r="K163" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="N163">
         <v>999</v>
@@ -8876,14 +8884,14 @@
     </row>
     <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A164">
-        <v>1023402</v>
+        <v>1023401</v>
       </c>
       <c r="B164" s="7"/>
       <c r="C164">
-        <v>1023402</v>
+        <v>1023401</v>
       </c>
       <c r="D164" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -8892,19 +8900,19 @@
         <v>47</v>
       </c>
       <c r="G164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H164">
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J164">
-        <v>2023402</v>
+        <v>2023401</v>
       </c>
       <c r="K164" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N164">
         <v>999</v>
@@ -8912,14 +8920,14 @@
     </row>
     <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A165">
-        <v>1023403</v>
+        <v>1023402</v>
       </c>
       <c r="B165" s="7"/>
       <c r="C165">
-        <v>1023403</v>
+        <v>1023402</v>
       </c>
       <c r="D165" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E165">
         <v>2</v>
@@ -8928,19 +8936,19 @@
         <v>47</v>
       </c>
       <c r="G165">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H165">
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J165">
-        <v>2023403</v>
+        <v>2023402</v>
       </c>
       <c r="K165" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N165">
         <v>999</v>
@@ -8948,14 +8956,14 @@
     </row>
     <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A166">
-        <v>1023404</v>
+        <v>1023403</v>
       </c>
       <c r="B166" s="7"/>
       <c r="C166">
-        <v>1023404</v>
+        <v>1023403</v>
       </c>
       <c r="D166" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -8964,19 +8972,19 @@
         <v>47</v>
       </c>
       <c r="G166">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H166">
         <v>0</v>
       </c>
       <c r="I166" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J166">
-        <v>2023404</v>
+        <v>2023403</v>
       </c>
       <c r="K166" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N166">
         <v>999</v>
@@ -8984,14 +8992,14 @@
     </row>
     <row r="167" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A167">
-        <v>1023405</v>
+        <v>1023404</v>
       </c>
       <c r="B167" s="7"/>
       <c r="C167">
-        <v>1023405</v>
+        <v>1023404</v>
       </c>
       <c r="D167" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E167">
         <v>2</v>
@@ -9000,84 +9008,79 @@
         <v>47</v>
       </c>
       <c r="G167">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H167">
         <v>0</v>
       </c>
       <c r="I167" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J167">
-        <v>2023405</v>
+        <v>2023404</v>
       </c>
       <c r="K167" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N167">
         <v>999</v>
       </c>
     </row>
-    <row r="168" ht="21" customHeight="1" spans="1:14">
+    <row r="168" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A168">
-        <f>1000000+E168*10000+B168</f>
-        <v>1990000</v>
-      </c>
-      <c r="B168" s="7">
-        <v>0</v>
-      </c>
+        <v>1023405</v>
+      </c>
+      <c r="B168" s="7"/>
       <c r="C168">
-        <v>1990000</v>
+        <v>1023405</v>
       </c>
       <c r="D168" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E168">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>241</v>
+        <v>47</v>
       </c>
       <c r="G168">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H168">
         <v>0</v>
       </c>
-      <c r="I168" t="str">
-        <f>"itemicon_"&amp;A168&amp;".png"</f>
-        <v>itemicon_1990000.png</v>
+      <c r="I168" t="s">
+        <v>240</v>
       </c>
       <c r="J168">
-        <f>2000000+E168*10000+B168</f>
-        <v>2990000</v>
+        <v>2023405</v>
       </c>
       <c r="K168" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="N168">
-        <v>-1</v>
+        <v>999</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1" spans="1:14">
       <c r="A169">
         <f>1000000+E169*10000+B169</f>
-        <v>1980000</v>
+        <v>1990000</v>
       </c>
       <c r="B169" s="7">
         <v>0</v>
       </c>
       <c r="C169">
-        <v>1980000</v>
+        <v>1990000</v>
       </c>
       <c r="D169" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E169">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F169" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -9087,16 +9090,57 @@
       </c>
       <c r="I169" t="str">
         <f>"itemicon_"&amp;A169&amp;".png"</f>
-        <v>itemicon_1980000.png</v>
+        <v>itemicon_1990000.png</v>
       </c>
       <c r="J169">
         <f>2000000+E169*10000+B169</f>
+        <v>2990000</v>
+      </c>
+      <c r="K169" t="s">
+        <v>243</v>
+      </c>
+      <c r="N169">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="170" ht="21" customHeight="1" spans="1:14">
+      <c r="A170">
+        <f>1000000+E170*10000+B170</f>
+        <v>1980000</v>
+      </c>
+      <c r="B170" s="7">
+        <v>0</v>
+      </c>
+      <c r="C170">
+        <v>1980000</v>
+      </c>
+      <c r="D170" t="s">
+        <v>244</v>
+      </c>
+      <c r="E170">
+        <v>98</v>
+      </c>
+      <c r="F170" t="s">
+        <v>242</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170" t="str">
+        <f>"itemicon_"&amp;A170&amp;".png"</f>
+        <v>itemicon_1980000.png</v>
+      </c>
+      <c r="J170">
+        <f>2000000+E170*10000+B170</f>
         <v>2980000</v>
       </c>
-      <c r="K169" t="s">
-        <v>244</v>
-      </c>
-      <c r="N169">
+      <c r="K170" t="s">
+        <v>245</v>
+      </c>
+      <c r="N170">
         <v>-1</v>
       </c>
     </row>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -179,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F169" authorId="0">
+    <comment ref="F170" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="248">
   <si>
     <t>道具ID</t>
   </si>
@@ -764,6 +764,12 @@
   </si>
   <si>
     <t>夺宝优惠券</t>
+  </si>
+  <si>
+    <t>积分</t>
+  </si>
+  <si>
+    <t>在[积分大奖]活动中产出</t>
   </si>
   <si>
     <t>1星扳手</t>
@@ -2211,7 +2217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
@@ -7617,7 +7623,7 @@
         <v>1401</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:C143" si="19">1000000+E131*100000+B131</f>
+        <f t="shared" ref="C131:C144" si="19">1000000+E131*100000+B131</f>
         <v>1201401</v>
       </c>
       <c r="D131" s="10" t="s">
@@ -8162,13 +8168,17 @@
         <v>999</v>
       </c>
     </row>
-    <row r="144" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="144" customFormat="1" ht="18" customHeight="1" spans="1:14">
       <c r="A144">
-        <v>1023001</v>
-      </c>
-      <c r="B144" s="7"/>
+        <f t="shared" si="18"/>
+        <v>1022504</v>
+      </c>
+      <c r="B144">
+        <v>2504</v>
+      </c>
       <c r="C144">
-        <v>1023001</v>
+        <f t="shared" si="19"/>
+        <v>1202504</v>
       </c>
       <c r="D144" t="s">
         <v>186</v>
@@ -8180,34 +8190,35 @@
         <v>47</v>
       </c>
       <c r="G144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H144">
         <v>0</v>
       </c>
       <c r="I144" t="s">
+        <v>183</v>
+      </c>
+      <c r="J144">
+        <f t="shared" si="21"/>
+        <v>2022504</v>
+      </c>
+      <c r="K144" t="s">
         <v>187</v>
       </c>
-      <c r="J144">
-        <v>2023001</v>
-      </c>
-      <c r="K144" t="s">
-        <v>188</v>
-      </c>
       <c r="N144">
-        <v>999</v>
+        <v>999999999</v>
       </c>
     </row>
     <row r="145" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A145">
-        <v>1023002</v>
+        <v>1023001</v>
       </c>
       <c r="B145" s="7"/>
       <c r="C145">
-        <v>1023002</v>
+        <v>1023001</v>
       </c>
       <c r="D145" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E145">
         <v>2</v>
@@ -8216,19 +8227,19 @@
         <v>47</v>
       </c>
       <c r="G145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
       <c r="I145" t="s">
+        <v>189</v>
+      </c>
+      <c r="J145">
+        <v>2023001</v>
+      </c>
+      <c r="K145" t="s">
         <v>190</v>
-      </c>
-      <c r="J145">
-        <v>2023002</v>
-      </c>
-      <c r="K145" t="s">
-        <v>188</v>
       </c>
       <c r="N145">
         <v>999</v>
@@ -8236,11 +8247,11 @@
     </row>
     <row r="146" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A146">
-        <v>1023003</v>
+        <v>1023002</v>
       </c>
       <c r="B146" s="7"/>
       <c r="C146">
-        <v>1023003</v>
+        <v>1023002</v>
       </c>
       <c r="D146" t="s">
         <v>191</v>
@@ -8252,7 +8263,7 @@
         <v>47</v>
       </c>
       <c r="G146">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -8261,10 +8272,10 @@
         <v>192</v>
       </c>
       <c r="J146">
-        <v>2023003</v>
+        <v>2023002</v>
       </c>
       <c r="K146" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N146">
         <v>999</v>
@@ -8272,11 +8283,11 @@
     </row>
     <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A147">
-        <v>1023004</v>
+        <v>1023003</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147">
-        <v>1023004</v>
+        <v>1023003</v>
       </c>
       <c r="D147" t="s">
         <v>193</v>
@@ -8288,7 +8299,7 @@
         <v>47</v>
       </c>
       <c r="G147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -8297,10 +8308,10 @@
         <v>194</v>
       </c>
       <c r="J147">
-        <v>2023004</v>
+        <v>2023003</v>
       </c>
       <c r="K147" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N147">
         <v>999</v>
@@ -8308,11 +8319,11 @@
     </row>
     <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A148">
-        <v>1023005</v>
+        <v>1023004</v>
       </c>
       <c r="B148" s="7"/>
       <c r="C148">
-        <v>1023005</v>
+        <v>1023004</v>
       </c>
       <c r="D148" t="s">
         <v>195</v>
@@ -8324,7 +8335,7 @@
         <v>47</v>
       </c>
       <c r="G148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -8333,10 +8344,10 @@
         <v>196</v>
       </c>
       <c r="J148">
-        <v>2023005</v>
+        <v>2023004</v>
       </c>
       <c r="K148" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N148">
         <v>999</v>
@@ -8344,11 +8355,11 @@
     </row>
     <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A149">
-        <v>1023101</v>
+        <v>1023005</v>
       </c>
       <c r="B149" s="7"/>
       <c r="C149">
-        <v>1023101</v>
+        <v>1023005</v>
       </c>
       <c r="D149" t="s">
         <v>197</v>
@@ -8360,7 +8371,7 @@
         <v>47</v>
       </c>
       <c r="G149">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -8369,10 +8380,10 @@
         <v>198</v>
       </c>
       <c r="J149">
-        <v>2023101</v>
+        <v>2023005</v>
       </c>
       <c r="K149" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="N149">
         <v>999</v>
@@ -8380,14 +8391,14 @@
     </row>
     <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A150">
-        <v>1023102</v>
+        <v>1023101</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150">
-        <v>1023102</v>
+        <v>1023101</v>
       </c>
       <c r="D150" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E150">
         <v>2</v>
@@ -8396,19 +8407,19 @@
         <v>47</v>
       </c>
       <c r="G150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
       <c r="I150" t="s">
+        <v>200</v>
+      </c>
+      <c r="J150">
+        <v>2023101</v>
+      </c>
+      <c r="K150" t="s">
         <v>201</v>
-      </c>
-      <c r="J150">
-        <v>2023102</v>
-      </c>
-      <c r="K150" t="s">
-        <v>199</v>
       </c>
       <c r="N150">
         <v>999</v>
@@ -8416,11 +8427,11 @@
     </row>
     <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A151">
-        <v>1023103</v>
+        <v>1023102</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151">
-        <v>1023103</v>
+        <v>1023102</v>
       </c>
       <c r="D151" t="s">
         <v>202</v>
@@ -8432,7 +8443,7 @@
         <v>47</v>
       </c>
       <c r="G151">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -8441,10 +8452,10 @@
         <v>203</v>
       </c>
       <c r="J151">
-        <v>2023103</v>
+        <v>2023102</v>
       </c>
       <c r="K151" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N151">
         <v>999</v>
@@ -8452,11 +8463,11 @@
     </row>
     <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A152">
-        <v>1023104</v>
+        <v>1023103</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152">
-        <v>1023104</v>
+        <v>1023103</v>
       </c>
       <c r="D152" t="s">
         <v>204</v>
@@ -8468,7 +8479,7 @@
         <v>47</v>
       </c>
       <c r="G152">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -8477,10 +8488,10 @@
         <v>205</v>
       </c>
       <c r="J152">
-        <v>2023104</v>
+        <v>2023103</v>
       </c>
       <c r="K152" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N152">
         <v>999</v>
@@ -8488,11 +8499,11 @@
     </row>
     <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A153">
-        <v>1023105</v>
+        <v>1023104</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153">
-        <v>1023105</v>
+        <v>1023104</v>
       </c>
       <c r="D153" t="s">
         <v>206</v>
@@ -8504,7 +8515,7 @@
         <v>47</v>
       </c>
       <c r="G153">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H153">
         <v>0</v>
@@ -8513,10 +8524,10 @@
         <v>207</v>
       </c>
       <c r="J153">
-        <v>2023105</v>
+        <v>2023104</v>
       </c>
       <c r="K153" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N153">
         <v>999</v>
@@ -8524,11 +8535,11 @@
     </row>
     <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A154">
-        <v>1023201</v>
+        <v>1023105</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154">
-        <v>1023201</v>
+        <v>1023105</v>
       </c>
       <c r="D154" t="s">
         <v>208</v>
@@ -8540,7 +8551,7 @@
         <v>47</v>
       </c>
       <c r="G154">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H154">
         <v>0</v>
@@ -8549,10 +8560,10 @@
         <v>209</v>
       </c>
       <c r="J154">
-        <v>2023201</v>
+        <v>2023105</v>
       </c>
       <c r="K154" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="N154">
         <v>999</v>
@@ -8560,14 +8571,14 @@
     </row>
     <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A155">
-        <v>1023202</v>
+        <v>1023201</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155">
-        <v>1023202</v>
+        <v>1023201</v>
       </c>
       <c r="D155" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -8576,19 +8587,19 @@
         <v>47</v>
       </c>
       <c r="G155">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155" t="s">
+        <v>211</v>
+      </c>
+      <c r="J155">
+        <v>2023201</v>
+      </c>
+      <c r="K155" t="s">
         <v>212</v>
-      </c>
-      <c r="J155">
-        <v>2023202</v>
-      </c>
-      <c r="K155" t="s">
-        <v>210</v>
       </c>
       <c r="N155">
         <v>999</v>
@@ -8596,11 +8607,11 @@
     </row>
     <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A156">
-        <v>1023203</v>
+        <v>1023202</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156">
-        <v>1023203</v>
+        <v>1023202</v>
       </c>
       <c r="D156" t="s">
         <v>213</v>
@@ -8612,7 +8623,7 @@
         <v>47</v>
       </c>
       <c r="G156">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -8621,10 +8632,10 @@
         <v>214</v>
       </c>
       <c r="J156">
-        <v>2023203</v>
+        <v>2023202</v>
       </c>
       <c r="K156" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N156">
         <v>999</v>
@@ -8632,11 +8643,11 @@
     </row>
     <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A157">
-        <v>1023204</v>
+        <v>1023203</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157">
-        <v>1023204</v>
+        <v>1023203</v>
       </c>
       <c r="D157" t="s">
         <v>215</v>
@@ -8648,7 +8659,7 @@
         <v>47</v>
       </c>
       <c r="G157">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H157">
         <v>0</v>
@@ -8657,10 +8668,10 @@
         <v>216</v>
       </c>
       <c r="J157">
-        <v>2023204</v>
+        <v>2023203</v>
       </c>
       <c r="K157" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N157">
         <v>999</v>
@@ -8668,11 +8679,11 @@
     </row>
     <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A158">
-        <v>1023205</v>
+        <v>1023204</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158">
-        <v>1023205</v>
+        <v>1023204</v>
       </c>
       <c r="D158" t="s">
         <v>217</v>
@@ -8684,7 +8695,7 @@
         <v>47</v>
       </c>
       <c r="G158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H158">
         <v>0</v>
@@ -8693,10 +8704,10 @@
         <v>218</v>
       </c>
       <c r="J158">
-        <v>2023205</v>
+        <v>2023204</v>
       </c>
       <c r="K158" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N158">
         <v>999</v>
@@ -8704,11 +8715,11 @@
     </row>
     <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A159">
-        <v>1023301</v>
+        <v>1023205</v>
       </c>
       <c r="B159" s="7"/>
       <c r="C159">
-        <v>1023301</v>
+        <v>1023205</v>
       </c>
       <c r="D159" t="s">
         <v>219</v>
@@ -8720,7 +8731,7 @@
         <v>47</v>
       </c>
       <c r="G159">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H159">
         <v>0</v>
@@ -8729,10 +8740,10 @@
         <v>220</v>
       </c>
       <c r="J159">
-        <v>2023301</v>
+        <v>2023205</v>
       </c>
       <c r="K159" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="N159">
         <v>999</v>
@@ -8740,14 +8751,14 @@
     </row>
     <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A160">
-        <v>1023302</v>
+        <v>1023301</v>
       </c>
       <c r="B160" s="7"/>
       <c r="C160">
-        <v>1023302</v>
+        <v>1023301</v>
       </c>
       <c r="D160" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E160">
         <v>2</v>
@@ -8756,19 +8767,19 @@
         <v>47</v>
       </c>
       <c r="G160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H160">
         <v>0</v>
       </c>
       <c r="I160" t="s">
+        <v>222</v>
+      </c>
+      <c r="J160">
+        <v>2023301</v>
+      </c>
+      <c r="K160" t="s">
         <v>223</v>
-      </c>
-      <c r="J160">
-        <v>2023302</v>
-      </c>
-      <c r="K160" t="s">
-        <v>221</v>
       </c>
       <c r="N160">
         <v>999</v>
@@ -8776,11 +8787,11 @@
     </row>
     <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A161">
-        <v>1023303</v>
+        <v>1023302</v>
       </c>
       <c r="B161" s="7"/>
       <c r="C161">
-        <v>1023303</v>
+        <v>1023302</v>
       </c>
       <c r="D161" t="s">
         <v>224</v>
@@ -8792,7 +8803,7 @@
         <v>47</v>
       </c>
       <c r="G161">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -8801,10 +8812,10 @@
         <v>225</v>
       </c>
       <c r="J161">
-        <v>2023303</v>
+        <v>2023302</v>
       </c>
       <c r="K161" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N161">
         <v>999</v>
@@ -8812,11 +8823,11 @@
     </row>
     <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A162">
-        <v>1023304</v>
+        <v>1023303</v>
       </c>
       <c r="B162" s="7"/>
       <c r="C162">
-        <v>1023304</v>
+        <v>1023303</v>
       </c>
       <c r="D162" t="s">
         <v>226</v>
@@ -8828,7 +8839,7 @@
         <v>47</v>
       </c>
       <c r="G162">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -8837,10 +8848,10 @@
         <v>227</v>
       </c>
       <c r="J162">
-        <v>2023304</v>
+        <v>2023303</v>
       </c>
       <c r="K162" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N162">
         <v>999</v>
@@ -8848,11 +8859,11 @@
     </row>
     <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A163">
-        <v>1023305</v>
+        <v>1023304</v>
       </c>
       <c r="B163" s="7"/>
       <c r="C163">
-        <v>1023305</v>
+        <v>1023304</v>
       </c>
       <c r="D163" t="s">
         <v>228</v>
@@ -8864,7 +8875,7 @@
         <v>47</v>
       </c>
       <c r="G163">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -8873,10 +8884,10 @@
         <v>229</v>
       </c>
       <c r="J163">
-        <v>2023305</v>
+        <v>2023304</v>
       </c>
       <c r="K163" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N163">
         <v>999</v>
@@ -8884,11 +8895,11 @@
     </row>
     <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A164">
-        <v>1023401</v>
+        <v>1023305</v>
       </c>
       <c r="B164" s="7"/>
       <c r="C164">
-        <v>1023401</v>
+        <v>1023305</v>
       </c>
       <c r="D164" t="s">
         <v>230</v>
@@ -8900,7 +8911,7 @@
         <v>47</v>
       </c>
       <c r="G164">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -8909,10 +8920,10 @@
         <v>231</v>
       </c>
       <c r="J164">
-        <v>2023401</v>
+        <v>2023305</v>
       </c>
       <c r="K164" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="N164">
         <v>999</v>
@@ -8920,14 +8931,14 @@
     </row>
     <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A165">
-        <v>1023402</v>
+        <v>1023401</v>
       </c>
       <c r="B165" s="7"/>
       <c r="C165">
-        <v>1023402</v>
+        <v>1023401</v>
       </c>
       <c r="D165" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E165">
         <v>2</v>
@@ -8936,19 +8947,19 @@
         <v>47</v>
       </c>
       <c r="G165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H165">
         <v>0</v>
       </c>
       <c r="I165" t="s">
+        <v>233</v>
+      </c>
+      <c r="J165">
+        <v>2023401</v>
+      </c>
+      <c r="K165" t="s">
         <v>234</v>
-      </c>
-      <c r="J165">
-        <v>2023402</v>
-      </c>
-      <c r="K165" t="s">
-        <v>232</v>
       </c>
       <c r="N165">
         <v>999</v>
@@ -8956,11 +8967,11 @@
     </row>
     <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A166">
-        <v>1023403</v>
+        <v>1023402</v>
       </c>
       <c r="B166" s="7"/>
       <c r="C166">
-        <v>1023403</v>
+        <v>1023402</v>
       </c>
       <c r="D166" t="s">
         <v>235</v>
@@ -8972,7 +8983,7 @@
         <v>47</v>
       </c>
       <c r="G166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -8981,10 +8992,10 @@
         <v>236</v>
       </c>
       <c r="J166">
-        <v>2023403</v>
+        <v>2023402</v>
       </c>
       <c r="K166" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N166">
         <v>999</v>
@@ -8992,11 +9003,11 @@
     </row>
     <row r="167" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A167">
-        <v>1023404</v>
+        <v>1023403</v>
       </c>
       <c r="B167" s="7"/>
       <c r="C167">
-        <v>1023404</v>
+        <v>1023403</v>
       </c>
       <c r="D167" t="s">
         <v>237</v>
@@ -9008,7 +9019,7 @@
         <v>47</v>
       </c>
       <c r="G167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H167">
         <v>0</v>
@@ -9017,10 +9028,10 @@
         <v>238</v>
       </c>
       <c r="J167">
-        <v>2023404</v>
+        <v>2023403</v>
       </c>
       <c r="K167" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N167">
         <v>999</v>
@@ -9028,11 +9039,11 @@
     </row>
     <row r="168" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A168">
-        <v>1023405</v>
+        <v>1023404</v>
       </c>
       <c r="B168" s="7"/>
       <c r="C168">
-        <v>1023405</v>
+        <v>1023404</v>
       </c>
       <c r="D168" t="s">
         <v>239</v>
@@ -9044,7 +9055,7 @@
         <v>47</v>
       </c>
       <c r="G168">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -9053,75 +9064,70 @@
         <v>240</v>
       </c>
       <c r="J168">
-        <v>2023405</v>
+        <v>2023404</v>
       </c>
       <c r="K168" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N168">
         <v>999</v>
       </c>
     </row>
-    <row r="169" ht="21" customHeight="1" spans="1:14">
+    <row r="169" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A169">
-        <f>1000000+E169*10000+B169</f>
-        <v>1990000</v>
-      </c>
-      <c r="B169" s="7">
-        <v>0</v>
-      </c>
+        <v>1023405</v>
+      </c>
+      <c r="B169" s="7"/>
       <c r="C169">
-        <v>1990000</v>
+        <v>1023405</v>
       </c>
       <c r="D169" t="s">
         <v>241</v>
       </c>
       <c r="E169">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>242</v>
+        <v>47</v>
       </c>
       <c r="G169">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H169">
         <v>0</v>
       </c>
-      <c r="I169" t="str">
-        <f>"itemicon_"&amp;A169&amp;".png"</f>
-        <v>itemicon_1990000.png</v>
+      <c r="I169" t="s">
+        <v>242</v>
       </c>
       <c r="J169">
-        <f>2000000+E169*10000+B169</f>
-        <v>2990000</v>
+        <v>2023405</v>
       </c>
       <c r="K169" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="N169">
-        <v>-1</v>
+        <v>999</v>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1" spans="1:14">
       <c r="A170">
         <f>1000000+E170*10000+B170</f>
-        <v>1980000</v>
+        <v>1990000</v>
       </c>
       <c r="B170" s="7">
         <v>0</v>
       </c>
       <c r="C170">
-        <v>1980000</v>
+        <v>1990000</v>
       </c>
       <c r="D170" t="s">
+        <v>243</v>
+      </c>
+      <c r="E170">
+        <v>99</v>
+      </c>
+      <c r="F170" t="s">
         <v>244</v>
-      </c>
-      <c r="E170">
-        <v>98</v>
-      </c>
-      <c r="F170" t="s">
-        <v>242</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -9131,16 +9137,57 @@
       </c>
       <c r="I170" t="str">
         <f>"itemicon_"&amp;A170&amp;".png"</f>
-        <v>itemicon_1980000.png</v>
+        <v>itemicon_1990000.png</v>
       </c>
       <c r="J170">
         <f>2000000+E170*10000+B170</f>
-        <v>2980000</v>
+        <v>2990000</v>
       </c>
       <c r="K170" t="s">
         <v>245</v>
       </c>
       <c r="N170">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="171" ht="21" customHeight="1" spans="1:14">
+      <c r="A171">
+        <f>1000000+E171*10000+B171</f>
+        <v>1980000</v>
+      </c>
+      <c r="B171" s="7">
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <v>1980000</v>
+      </c>
+      <c r="D171" t="s">
+        <v>246</v>
+      </c>
+      <c r="E171">
+        <v>98</v>
+      </c>
+      <c r="F171" t="s">
+        <v>244</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171" t="str">
+        <f>"itemicon_"&amp;A171&amp;".png"</f>
+        <v>itemicon_1980000.png</v>
+      </c>
+      <c r="J171">
+        <f>2000000+E171*10000+B171</f>
+        <v>2980000</v>
+      </c>
+      <c r="K171" t="s">
+        <v>247</v>
+      </c>
+      <c r="N171">
         <v>-1</v>
       </c>
     </row>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="248">
   <si>
     <t>道具ID</t>
   </si>
@@ -757,13 +757,13 @@
     <t>刮刮卡</t>
   </si>
   <si>
+    <t>在指定的游戏中产出</t>
+  </si>
+  <si>
+    <t>夺宝优惠券</t>
+  </si>
+  <si>
     <t>itemicon_1022501.png</t>
-  </si>
-  <si>
-    <t>在指定的游戏中产出</t>
-  </si>
-  <si>
-    <t>夺宝优惠券</t>
   </si>
   <si>
     <t>积分</t>
@@ -8113,15 +8113,16 @@
       <c r="H142">
         <v>0</v>
       </c>
-      <c r="I142" t="s">
-        <v>183</v>
+      <c r="I142" t="str">
+        <f>"itemicon_"&amp;A142&amp;".png"</f>
+        <v>itemicon_1022502.png</v>
       </c>
       <c r="J142">
         <f t="shared" si="21"/>
         <v>2022502</v>
       </c>
       <c r="K142" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N142">
         <v>999</v>
@@ -8140,7 +8141,7 @@
         <v>1202503</v>
       </c>
       <c r="D143" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E143">
         <v>2</v>
@@ -8155,14 +8156,14 @@
         <v>0</v>
       </c>
       <c r="I143" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J143">
         <f t="shared" si="21"/>
         <v>2022503</v>
       </c>
       <c r="K143" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N143">
         <v>999</v>
@@ -8196,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J144">
         <f t="shared" si="21"/>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="247">
   <si>
     <t>道具ID</t>
   </si>
@@ -761,9 +761,6 @@
   </si>
   <si>
     <t>夺宝优惠券</t>
-  </si>
-  <si>
-    <t>itemicon_1022501.png</t>
   </si>
   <si>
     <t>积分</t>
@@ -1128,12 +1125,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -8155,8 +8152,9 @@
       <c r="H143">
         <v>0</v>
       </c>
-      <c r="I143" t="s">
-        <v>185</v>
+      <c r="I143" t="str">
+        <f>"itemicon_"&amp;A143&amp;".png"</f>
+        <v>itemicon_1022503.png</v>
       </c>
       <c r="J143">
         <f t="shared" si="21"/>
@@ -8182,7 +8180,7 @@
         <v>1202504</v>
       </c>
       <c r="D144" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E144">
         <v>2</v>
@@ -8196,15 +8194,16 @@
       <c r="H144">
         <v>0</v>
       </c>
-      <c r="I144" t="s">
-        <v>185</v>
+      <c r="I144" t="str">
+        <f>"itemicon_"&amp;A144&amp;".png"</f>
+        <v>itemicon_1022504.png</v>
       </c>
       <c r="J144">
         <f t="shared" si="21"/>
         <v>2022504</v>
       </c>
       <c r="K144" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N144">
         <v>999999999</v>
@@ -8219,7 +8218,7 @@
         <v>1023001</v>
       </c>
       <c r="D145" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E145">
         <v>2</v>
@@ -8234,13 +8233,13 @@
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J145">
         <v>2023001</v>
       </c>
       <c r="K145" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N145">
         <v>999</v>
@@ -8255,7 +8254,7 @@
         <v>1023002</v>
       </c>
       <c r="D146" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E146">
         <v>2</v>
@@ -8270,13 +8269,13 @@
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J146">
         <v>2023002</v>
       </c>
       <c r="K146" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N146">
         <v>999</v>
@@ -8291,7 +8290,7 @@
         <v>1023003</v>
       </c>
       <c r="D147" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E147">
         <v>2</v>
@@ -8306,13 +8305,13 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J147">
         <v>2023003</v>
       </c>
       <c r="K147" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N147">
         <v>999</v>
@@ -8327,7 +8326,7 @@
         <v>1023004</v>
       </c>
       <c r="D148" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E148">
         <v>2</v>
@@ -8342,13 +8341,13 @@
         <v>0</v>
       </c>
       <c r="I148" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J148">
         <v>2023004</v>
       </c>
       <c r="K148" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N148">
         <v>999</v>
@@ -8363,7 +8362,7 @@
         <v>1023005</v>
       </c>
       <c r="D149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E149">
         <v>2</v>
@@ -8378,13 +8377,13 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J149">
         <v>2023005</v>
       </c>
       <c r="K149" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N149">
         <v>999</v>
@@ -8399,7 +8398,7 @@
         <v>1023101</v>
       </c>
       <c r="D150" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E150">
         <v>2</v>
@@ -8414,13 +8413,13 @@
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J150">
         <v>2023101</v>
       </c>
       <c r="K150" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N150">
         <v>999</v>
@@ -8435,7 +8434,7 @@
         <v>1023102</v>
       </c>
       <c r="D151" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E151">
         <v>2</v>
@@ -8450,13 +8449,13 @@
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J151">
         <v>2023102</v>
       </c>
       <c r="K151" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N151">
         <v>999</v>
@@ -8471,7 +8470,7 @@
         <v>1023103</v>
       </c>
       <c r="D152" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -8486,13 +8485,13 @@
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J152">
         <v>2023103</v>
       </c>
       <c r="K152" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N152">
         <v>999</v>
@@ -8507,7 +8506,7 @@
         <v>1023104</v>
       </c>
       <c r="D153" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -8522,13 +8521,13 @@
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J153">
         <v>2023104</v>
       </c>
       <c r="K153" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N153">
         <v>999</v>
@@ -8543,7 +8542,7 @@
         <v>1023105</v>
       </c>
       <c r="D154" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -8558,13 +8557,13 @@
         <v>0</v>
       </c>
       <c r="I154" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J154">
         <v>2023105</v>
       </c>
       <c r="K154" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N154">
         <v>999</v>
@@ -8579,7 +8578,7 @@
         <v>1023201</v>
       </c>
       <c r="D155" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -8594,13 +8593,13 @@
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J155">
         <v>2023201</v>
       </c>
       <c r="K155" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N155">
         <v>999</v>
@@ -8615,7 +8614,7 @@
         <v>1023202</v>
       </c>
       <c r="D156" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E156">
         <v>2</v>
@@ -8630,13 +8629,13 @@
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J156">
         <v>2023202</v>
       </c>
       <c r="K156" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N156">
         <v>999</v>
@@ -8651,7 +8650,7 @@
         <v>1023203</v>
       </c>
       <c r="D157" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -8666,13 +8665,13 @@
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J157">
         <v>2023203</v>
       </c>
       <c r="K157" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N157">
         <v>999</v>
@@ -8687,7 +8686,7 @@
         <v>1023204</v>
       </c>
       <c r="D158" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E158">
         <v>2</v>
@@ -8702,13 +8701,13 @@
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J158">
         <v>2023204</v>
       </c>
       <c r="K158" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N158">
         <v>999</v>
@@ -8723,7 +8722,7 @@
         <v>1023205</v>
       </c>
       <c r="D159" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -8738,13 +8737,13 @@
         <v>0</v>
       </c>
       <c r="I159" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J159">
         <v>2023205</v>
       </c>
       <c r="K159" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N159">
         <v>999</v>
@@ -8759,7 +8758,7 @@
         <v>1023301</v>
       </c>
       <c r="D160" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E160">
         <v>2</v>
@@ -8774,13 +8773,13 @@
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J160">
         <v>2023301</v>
       </c>
       <c r="K160" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N160">
         <v>999</v>
@@ -8795,7 +8794,7 @@
         <v>1023302</v>
       </c>
       <c r="D161" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -8810,13 +8809,13 @@
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J161">
         <v>2023302</v>
       </c>
       <c r="K161" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N161">
         <v>999</v>
@@ -8831,7 +8830,7 @@
         <v>1023303</v>
       </c>
       <c r="D162" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -8846,13 +8845,13 @@
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J162">
         <v>2023303</v>
       </c>
       <c r="K162" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N162">
         <v>999</v>
@@ -8867,7 +8866,7 @@
         <v>1023304</v>
       </c>
       <c r="D163" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E163">
         <v>2</v>
@@ -8882,13 +8881,13 @@
         <v>0</v>
       </c>
       <c r="I163" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J163">
         <v>2023304</v>
       </c>
       <c r="K163" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N163">
         <v>999</v>
@@ -8903,7 +8902,7 @@
         <v>1023305</v>
       </c>
       <c r="D164" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -8918,13 +8917,13 @@
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J164">
         <v>2023305</v>
       </c>
       <c r="K164" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N164">
         <v>999</v>
@@ -8939,7 +8938,7 @@
         <v>1023401</v>
       </c>
       <c r="D165" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E165">
         <v>2</v>
@@ -8954,13 +8953,13 @@
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J165">
         <v>2023401</v>
       </c>
       <c r="K165" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N165">
         <v>999</v>
@@ -8975,7 +8974,7 @@
         <v>1023402</v>
       </c>
       <c r="D166" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -8990,13 +8989,13 @@
         <v>0</v>
       </c>
       <c r="I166" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J166">
         <v>2023402</v>
       </c>
       <c r="K166" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N166">
         <v>999</v>
@@ -9011,7 +9010,7 @@
         <v>1023403</v>
       </c>
       <c r="D167" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E167">
         <v>2</v>
@@ -9026,13 +9025,13 @@
         <v>0</v>
       </c>
       <c r="I167" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J167">
         <v>2023403</v>
       </c>
       <c r="K167" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N167">
         <v>999</v>
@@ -9047,7 +9046,7 @@
         <v>1023404</v>
       </c>
       <c r="D168" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E168">
         <v>2</v>
@@ -9062,13 +9061,13 @@
         <v>0</v>
       </c>
       <c r="I168" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J168">
         <v>2023404</v>
       </c>
       <c r="K168" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N168">
         <v>999</v>
@@ -9083,7 +9082,7 @@
         <v>1023405</v>
       </c>
       <c r="D169" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -9098,13 +9097,13 @@
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J169">
         <v>2023405</v>
       </c>
       <c r="K169" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N169">
         <v>999</v>
@@ -9122,13 +9121,13 @@
         <v>1990000</v>
       </c>
       <c r="D170" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E170">
         <v>99</v>
       </c>
       <c r="F170" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -9145,7 +9144,7 @@
         <v>2990000</v>
       </c>
       <c r="K170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N170">
         <v>-1</v>
@@ -9163,13 +9162,13 @@
         <v>1980000</v>
       </c>
       <c r="D171" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E171">
         <v>98</v>
       </c>
       <c r="F171" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -9186,7 +9185,7 @@
         <v>2980000</v>
       </c>
       <c r="K171" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N171">
         <v>-1</v>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -157,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F125" authorId="0">
+    <comment ref="F127" authorId="0">
       <text>
         <r>
           <rPr>
@@ -179,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F170" authorId="0">
+    <comment ref="F172" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="253">
   <si>
     <t>道具ID</t>
   </si>
@@ -247,6 +247,9 @@
     <t>掉落ID</t>
   </si>
   <si>
+    <t>价值</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -313,19 +316,34 @@
     <t>1980000_10000</t>
   </si>
   <si>
-    <t>赌场材料随机包(普通)</t>
+    <t>赌场工具（普通）</t>
   </si>
   <si>
     <t>itemicon_1010101.png</t>
   </si>
   <si>
-    <t>使用后随机获得N个赌赌场材料道具</t>
-  </si>
-  <si>
-    <t>赌场材料随机包(豪华)</t>
-  </si>
-  <si>
-    <t>赌场材料随机包(尊贵)</t>
+    <t>使用后随机获得1~2星赌场建筑升级道具</t>
+  </si>
+  <si>
+    <t>赌场工具（精良）</t>
+  </si>
+  <si>
+    <t>赌场工具（优秀）</t>
+  </si>
+  <si>
+    <t>使用后随机获得1~3星赌场建筑升级道具</t>
+  </si>
+  <si>
+    <t>赌场工具（绝佳）</t>
+  </si>
+  <si>
+    <t>使用后随机获得1~4星赌场建筑升级道具</t>
+  </si>
+  <si>
+    <t>赌场工具（传奇）</t>
+  </si>
+  <si>
+    <t>使用后随机获得1~5星赌场建筑升级道具</t>
   </si>
   <si>
     <t>拼图随机礼包(一星)</t>
@@ -1125,12 +1143,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2214,7 +2232,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P171"/>
+  <dimension ref="A1:Q173"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
@@ -2235,7 +2253,7 @@
     <col min="20" max="20" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2277,88 +2295,91 @@
       <c r="P1" t="s">
         <v>12</v>
       </c>
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2367,7 +2388,7 @@
     </row>
     <row r="5" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A5">
-        <f t="shared" ref="A5:A14" si="0">1000000+E5*10000+B5</f>
+        <f>1000000+E5*10000+B5</f>
         <v>1010101</v>
       </c>
       <c r="B5" s="7">
@@ -2377,13 +2398,13 @@
         <v>1010101</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -2396,22 +2417,22 @@
         <v>itemicon_1010101.png</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5:J14" si="1">2000000+E5*10000+B5</f>
+        <f>2000000+E5*10000+B5</f>
         <v>2010101</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5">
         <v>999</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A6">
-        <f t="shared" si="0"/>
+        <f>1000000+E6*10000+B6</f>
         <v>1010201</v>
       </c>
       <c r="B6" s="7">
@@ -2421,13 +2442,13 @@
         <v>1010201</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -2440,542 +2461,563 @@
         <v>itemicon_1010201.png</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
+        <f>2000000+E6*10000+B6</f>
         <v>2010201</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N6">
         <v>999</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A7" s="1">
-        <f t="shared" si="0"/>
+        <f>1000000+E7*10000+B7</f>
         <v>1010301</v>
       </c>
       <c r="B7" s="1">
         <v>301</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" ref="C7:C14" si="2">1000000+E7*100000+B7</f>
+        <f>1000000+E7*100000+B7</f>
         <v>1100301</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" si="1"/>
+        <f>2000000+E7*10000+B7</f>
         <v>2010301</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N7" s="1">
         <v>999</v>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="1">
-        <v>100003</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>1010301</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
+        <f>1000000+E8*10000+B8</f>
         <v>1010302</v>
       </c>
       <c r="B8" s="1">
         <v>302</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="2"/>
+        <f>1000000+E8*100000+B8</f>
         <v>1100302</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" si="1"/>
+        <f>2000000+E8*10000+B8</f>
         <v>2010302</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N8" s="1">
         <v>999</v>
       </c>
       <c r="O8" s="9"/>
       <c r="P8" s="1">
-        <v>100004</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>1010302</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
+        <f>1000000+E9*10000+B9</f>
         <v>1010303</v>
       </c>
       <c r="B9" s="1">
         <v>303</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" si="2"/>
+        <f>1000000+E9*100000+B9</f>
         <v>1100303</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" si="1"/>
+        <f>2000000+E9*10000+B9</f>
         <v>2010303</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N9" s="1">
         <v>999</v>
       </c>
       <c r="O9" s="9"/>
       <c r="P9" s="1">
-        <v>100005</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>1010303</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
-        <v>1010311</v>
+        <f>1000000+E10*10000+B10</f>
+        <v>1010304</v>
       </c>
       <c r="B10" s="1">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" si="2"/>
-        <v>1100311</v>
+        <f>1000000+E10*100000+B10</f>
+        <v>1100304</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="1"/>
-        <v>2010311</v>
+        <f>2000000+E10*10000+B10</f>
+        <v>2010304</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N10" s="1">
         <v>999</v>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="1">
-        <v>100006</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>1010304</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
-        <v>1010312</v>
+        <f>1000000+E11*10000+B11</f>
+        <v>1010305</v>
       </c>
       <c r="B11" s="1">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" si="2"/>
-        <v>1100312</v>
+        <f>1000000+E11*100000+B11</f>
+        <v>1100305</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="1"/>
-        <v>2010312</v>
+        <f>2000000+E11*10000+B11</f>
+        <v>2010305</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N11" s="1">
         <v>999</v>
       </c>
       <c r="O11" s="9"/>
       <c r="P11" s="1">
-        <v>100007</v>
+        <v>1010305</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>49.99</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
-        <v>1010313</v>
+        <f>1000000+E12*10000+B12</f>
+        <v>1010311</v>
       </c>
       <c r="B12" s="1">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C12" s="1">
-        <f t="shared" si="2"/>
-        <v>1100313</v>
+        <f>1000000+E12*100000+B12</f>
+        <v>1100311</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="1"/>
-        <v>2010313</v>
+        <f>2000000+E12*10000+B12</f>
+        <v>2010311</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N12" s="1">
         <v>999</v>
       </c>
       <c r="O12" s="9"/>
       <c r="P12" s="1">
-        <v>100008</v>
+        <v>100006</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
-        <v>1010314</v>
+        <f>1000000+E13*10000+B13</f>
+        <v>1010312</v>
       </c>
       <c r="B13" s="1">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C13" s="1">
-        <f t="shared" si="2"/>
-        <v>1100314</v>
+        <f>1000000+E13*100000+B13</f>
+        <v>1100312</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="1"/>
-        <v>2010314</v>
+        <f>2000000+E13*10000+B13</f>
+        <v>2010312</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N13" s="1">
         <v>999</v>
       </c>
       <c r="O13" s="9"/>
       <c r="P13" s="1">
-        <v>100009</v>
+        <v>100007</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
-        <v>1010315</v>
+        <f>1000000+E14*10000+B14</f>
+        <v>1010313</v>
       </c>
       <c r="B14" s="1">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="2"/>
-        <v>1100315</v>
+        <f>1000000+E14*100000+B14</f>
+        <v>1100313</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" si="1"/>
-        <v>2010315</v>
+        <f>2000000+E14*10000+B14</f>
+        <v>2010313</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N14" s="1">
         <v>999</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="1">
-        <v>100010</v>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1" spans="1:14">
-      <c r="A15">
-        <f t="shared" ref="A15:A29" si="3">1000000+E15*10000+B15</f>
-        <v>1020001</v>
-      </c>
-      <c r="B15" s="7">
-        <f>COUNTIF($F$1:F15,F15)</f>
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>1020001</v>
-      </c>
-      <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
+        <v>100008</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A15" s="1">
+        <f>1000000+E15*10000+B15</f>
+        <v>1010314</v>
+      </c>
+      <c r="B15" s="1">
+        <v>314</v>
+      </c>
+      <c r="C15" s="1">
+        <f>1000000+E15*100000+B15</f>
+        <v>1100314</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15" t="str">
-        <f t="shared" ref="I15:I28" si="4">"itemicon_"&amp;A15&amp;".png"</f>
+      <c r="I15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="1">
+        <f>2000000+E15*10000+B15</f>
+        <v>2010314</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N15" s="1">
+        <v>999</v>
+      </c>
+      <c r="O15" s="9"/>
+      <c r="P15" s="1">
+        <v>100009</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A16" s="1">
+        <f>1000000+E16*10000+B16</f>
+        <v>1010315</v>
+      </c>
+      <c r="B16" s="1">
+        <v>315</v>
+      </c>
+      <c r="C16" s="1">
+        <f>1000000+E16*100000+B16</f>
+        <v>1100315</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="1">
+        <v>6</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="1">
+        <f>2000000+E16*10000+B16</f>
+        <v>2010315</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N16" s="1">
+        <v>999</v>
+      </c>
+      <c r="O16" s="9"/>
+      <c r="P16" s="1">
+        <v>100010</v>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1" spans="1:14">
+      <c r="A17">
+        <f t="shared" ref="A17:A31" si="0">1000000+E17*10000+B17</f>
+        <v>1020001</v>
+      </c>
+      <c r="B17" s="7">
+        <f>COUNTIF($F$1:F17,F17)</f>
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1020001</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" ref="I17:I30" si="1">"itemicon_"&amp;A17&amp;".png"</f>
         <v>itemicon_1020001.png</v>
       </c>
-      <c r="J15">
-        <f t="shared" ref="J15:J29" si="5">2000000+E15*10000+B15</f>
+      <c r="J17">
+        <f t="shared" ref="J17:J31" si="2">2000000+E17*10000+B17</f>
         <v>2020001</v>
       </c>
-      <c r="K15" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
-      <c r="A16" s="2">
-        <f t="shared" si="3"/>
-        <v>1020002</v>
-      </c>
-      <c r="B16" s="2">
-        <f>COUNTIF($F$1:F16,F16)</f>
-        <v>2</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1020002</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="2">
-        <v>2</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020002.png</v>
-      </c>
-      <c r="J16" s="2">
-        <f t="shared" si="5"/>
-        <v>2020002</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N16" s="2">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
-      <c r="A17" s="2">
-        <f t="shared" si="3"/>
-        <v>1020003</v>
-      </c>
-      <c r="B17" s="2">
-        <f>COUNTIF($F$1:F17,F17)</f>
-        <v>3</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1020003</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="2">
-        <v>2</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="2">
-        <v>3</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020003.png</v>
-      </c>
-      <c r="J17" s="2">
-        <f t="shared" si="5"/>
-        <v>2020003</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N17" s="2">
+      <c r="K17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17">
         <v>999</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A18" s="2">
-        <f t="shared" si="3"/>
-        <v>1020004</v>
+        <f t="shared" si="0"/>
+        <v>1020002</v>
       </c>
       <c r="B18" s="2">
         <f>COUNTIF($F$1:F18,F18)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2">
-        <v>1020004</v>
+        <v>1020002</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2">
         <v>2</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020004.png</v>
+        <f t="shared" si="1"/>
+        <v>itemicon_1020002.png</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" si="5"/>
-        <v>2020004</v>
+        <f t="shared" si="2"/>
+        <v>2020002</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="N18" s="2">
         <v>999</v>
@@ -2983,41 +3025,41 @@
     </row>
     <row r="19" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A19" s="2">
-        <f t="shared" si="3"/>
-        <v>1020005</v>
+        <f t="shared" si="0"/>
+        <v>1020003</v>
       </c>
       <c r="B19" s="2">
         <f>COUNTIF($F$1:F19,F19)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" s="2">
-        <v>1020005</v>
+        <v>1020003</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2">
         <v>2</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G19" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020005.png</v>
+        <f t="shared" si="1"/>
+        <v>itemicon_1020003.png</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="5"/>
-        <v>2020005</v>
+        <f t="shared" si="2"/>
+        <v>2020003</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="N19" s="2">
         <v>999</v>
@@ -3025,156 +3067,150 @@
     </row>
     <row r="20" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A20" s="2">
-        <f t="shared" si="3"/>
-        <v>1020006</v>
+        <f t="shared" si="0"/>
+        <v>1020004</v>
       </c>
       <c r="B20" s="2">
         <f>COUNTIF($F$1:F20,F20)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" s="2">
-        <v>1020006</v>
+        <v>1020004</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2">
         <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G20" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020006.png</v>
+        <f t="shared" si="1"/>
+        <v>itemicon_1020004.png</v>
       </c>
       <c r="J20" s="2">
-        <f t="shared" si="5"/>
-        <v>2020006</v>
+        <f t="shared" si="2"/>
+        <v>2020004</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="N20" s="2">
         <v>999</v>
       </c>
     </row>
-    <row r="21" ht="23" customHeight="1" spans="1:14">
-      <c r="A21">
-        <f t="shared" si="3"/>
-        <v>1030011</v>
-      </c>
-      <c r="B21" s="7">
-        <v>11</v>
-      </c>
-      <c r="C21">
-        <f t="shared" ref="C21:C29" si="6">1000000+E21*100000+B21</f>
-        <v>1300011</v>
-      </c>
-      <c r="D21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21">
-        <v>3</v>
-      </c>
-      <c r="F21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
+    <row r="21" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A21" s="2">
+        <f t="shared" si="0"/>
+        <v>1020005</v>
+      </c>
+      <c r="B21" s="2">
+        <f>COUNTIF($F$1:F21,F21)</f>
+        <v>5</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1020005</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="2">
+        <v>5</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
-      <c r="I21" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030011.png</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="5"/>
-        <v>2030011</v>
-      </c>
-      <c r="K21" t="s">
+      <c r="I21" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>itemicon_1020005.png</v>
+      </c>
+      <c r="J21" s="2">
+        <f t="shared" si="2"/>
+        <v>2020005</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M21">
-        <v>10001</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="23" customHeight="1" spans="1:14">
-      <c r="A22">
-        <f t="shared" si="3"/>
-        <v>1030012</v>
-      </c>
-      <c r="B22" s="7">
-        <v>12</v>
-      </c>
-      <c r="C22">
-        <f t="shared" si="6"/>
-        <v>1300012</v>
-      </c>
-      <c r="D22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
+      <c r="N21" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
+        <v>1020006</v>
+      </c>
+      <c r="B22" s="2">
+        <f>COUNTIF($F$1:F22,F22)</f>
+        <v>6</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1020006</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
-      <c r="I22" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030012.png</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="5"/>
-        <v>2030012</v>
-      </c>
-      <c r="K22" t="s">
+      <c r="I22" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>itemicon_1020006.png</v>
+      </c>
+      <c r="J22" s="2">
+        <f t="shared" si="2"/>
+        <v>2020006</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M22">
-        <v>10002</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
+      <c r="N22" s="2">
+        <v>999</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1" spans="1:14">
       <c r="A23">
-        <f t="shared" si="3"/>
-        <v>1030013</v>
+        <f t="shared" si="0"/>
+        <v>1030011</v>
       </c>
       <c r="B23" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C23">
-        <f t="shared" si="6"/>
-        <v>1300013</v>
+        <f t="shared" ref="C23:C31" si="3">1000000+E23*100000+B23</f>
+        <v>1300011</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3183,18 +3219,18 @@
         <v>1</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030013.png</v>
+        <f t="shared" si="1"/>
+        <v>itemicon_1030011.png</v>
       </c>
       <c r="J23">
-        <f t="shared" si="5"/>
-        <v>2030013</v>
+        <f t="shared" si="2"/>
+        <v>2030011</v>
       </c>
       <c r="K23" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M23">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="N23">
         <v>1</v>
@@ -3202,24 +3238,24 @@
     </row>
     <row r="24" ht="23" customHeight="1" spans="1:14">
       <c r="A24">
+        <f t="shared" si="0"/>
+        <v>1030012</v>
+      </c>
+      <c r="B24" s="7">
+        <v>12</v>
+      </c>
+      <c r="C24">
         <f t="shared" si="3"/>
-        <v>1030014</v>
-      </c>
-      <c r="B24" s="7">
-        <v>14</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="6"/>
-        <v>1300014</v>
+        <v>1300012</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -3228,18 +3264,18 @@
         <v>1</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030014.png</v>
+        <f t="shared" si="1"/>
+        <v>itemicon_1030012.png</v>
       </c>
       <c r="J24">
-        <f t="shared" si="5"/>
-        <v>2030014</v>
+        <f t="shared" si="2"/>
+        <v>2030012</v>
       </c>
       <c r="K24" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M24">
-        <v>10004</v>
+        <v>10002</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -3247,24 +3283,24 @@
     </row>
     <row r="25" ht="23" customHeight="1" spans="1:14">
       <c r="A25">
+        <f t="shared" si="0"/>
+        <v>1030013</v>
+      </c>
+      <c r="B25" s="7">
+        <v>13</v>
+      </c>
+      <c r="C25">
         <f t="shared" si="3"/>
-        <v>1030015</v>
-      </c>
-      <c r="B25" s="7">
-        <v>15</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="6"/>
-        <v>1300015</v>
+        <v>1300013</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3273,18 +3309,18 @@
         <v>1</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030015.png</v>
+        <f t="shared" si="1"/>
+        <v>itemicon_1030013.png</v>
       </c>
       <c r="J25">
-        <f t="shared" si="5"/>
-        <v>2030015</v>
+        <f t="shared" si="2"/>
+        <v>2030013</v>
       </c>
       <c r="K25" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M25">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -3292,24 +3328,24 @@
     </row>
     <row r="26" ht="23" customHeight="1" spans="1:14">
       <c r="A26">
+        <f t="shared" si="0"/>
+        <v>1030014</v>
+      </c>
+      <c r="B26" s="7">
+        <v>14</v>
+      </c>
+      <c r="C26">
         <f t="shared" si="3"/>
-        <v>1030016</v>
-      </c>
-      <c r="B26" s="7">
-        <v>16</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="6"/>
-        <v>1300016</v>
+        <v>1300014</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3318,18 +3354,18 @@
         <v>1</v>
       </c>
       <c r="I26" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030016.png</v>
+        <f t="shared" si="1"/>
+        <v>itemicon_1030014.png</v>
       </c>
       <c r="J26">
-        <f t="shared" si="5"/>
-        <v>2030016</v>
+        <f t="shared" si="2"/>
+        <v>2030014</v>
       </c>
       <c r="K26" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M26">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -3337,44 +3373,44 @@
     </row>
     <row r="27" ht="23" customHeight="1" spans="1:14">
       <c r="A27">
+        <f t="shared" si="0"/>
+        <v>1030015</v>
+      </c>
+      <c r="B27" s="7">
+        <v>15</v>
+      </c>
+      <c r="C27">
         <f t="shared" si="3"/>
-        <v>1030017</v>
-      </c>
-      <c r="B27" s="7">
-        <v>17</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="6"/>
-        <v>1300017</v>
+        <v>1300015</v>
       </c>
       <c r="D27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="1"/>
+        <v>itemicon_1030015.png</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="2"/>
+        <v>2030015</v>
+      </c>
+      <c r="K27" t="s">
         <v>62</v>
       </c>
-      <c r="E27">
-        <v>3</v>
-      </c>
-      <c r="F27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030017.png</v>
-      </c>
-      <c r="J27">
-        <f t="shared" si="5"/>
-        <v>2030017</v>
-      </c>
-      <c r="K27" t="s">
-        <v>56</v>
-      </c>
       <c r="M27">
-        <v>10007</v>
+        <v>10005</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -3382,126 +3418,134 @@
     </row>
     <row r="28" ht="23" customHeight="1" spans="1:14">
       <c r="A28">
+        <f t="shared" si="0"/>
+        <v>1030016</v>
+      </c>
+      <c r="B28" s="7">
+        <v>16</v>
+      </c>
+      <c r="C28">
         <f t="shared" si="3"/>
+        <v>1300016</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="1"/>
+        <v>itemicon_1030016.png</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="2"/>
+        <v>2030016</v>
+      </c>
+      <c r="K28" t="s">
+        <v>62</v>
+      </c>
+      <c r="M28">
+        <v>10006</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="23" customHeight="1" spans="1:14">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>1030017</v>
+      </c>
+      <c r="B29" s="7">
+        <v>17</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="3"/>
+        <v>1300017</v>
+      </c>
+      <c r="D29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="1"/>
+        <v>itemicon_1030017.png</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="2"/>
+        <v>2030017</v>
+      </c>
+      <c r="K29" t="s">
+        <v>62</v>
+      </c>
+      <c r="M29">
+        <v>10007</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="23" customHeight="1" spans="1:14">
+      <c r="A30">
+        <f t="shared" si="0"/>
         <v>1030018</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B30" s="7">
         <v>18</v>
       </c>
-      <c r="C28">
-        <f t="shared" si="6"/>
+      <c r="C30">
+        <f t="shared" si="3"/>
         <v>1300018</v>
       </c>
-      <c r="D28" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28">
-        <v>3</v>
-      </c>
-      <c r="F28" t="s">
-        <v>47</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28" t="str">
-        <f t="shared" si="4"/>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="1"/>
         <v>itemicon_1030018.png</v>
       </c>
-      <c r="J28">
-        <f t="shared" si="5"/>
+      <c r="J30">
+        <f t="shared" si="2"/>
         <v>2030018</v>
       </c>
-      <c r="K28" t="s">
-        <v>56</v>
-      </c>
-      <c r="M28">
+      <c r="K30" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30">
         <v>10008</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A29">
-        <f t="shared" si="3"/>
-        <v>1030101</v>
-      </c>
-      <c r="B29" s="7">
-        <v>101</v>
-      </c>
-      <c r="C29">
-        <f t="shared" si="6"/>
-        <v>1300101</v>
-      </c>
-      <c r="D29" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29">
-        <v>3</v>
-      </c>
-      <c r="F29" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29" t="s">
-        <v>65</v>
-      </c>
-      <c r="J29">
-        <f t="shared" si="5"/>
-        <v>2030101</v>
-      </c>
-      <c r="K29" t="s">
-        <v>66</v>
-      </c>
-      <c r="N29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" ht="23" customHeight="1" spans="1:14">
-      <c r="A30">
-        <f t="shared" ref="A30:A40" si="7">1000000+E30*10000+B30</f>
-        <v>1030102</v>
-      </c>
-      <c r="B30" s="7">
-        <v>102</v>
-      </c>
-      <c r="C30">
-        <f t="shared" ref="C30:C40" si="8">1000000+E30*100000+B30</f>
-        <v>1300102</v>
-      </c>
-      <c r="D30" t="s">
-        <v>67</v>
-      </c>
-      <c r="E30">
-        <v>3</v>
-      </c>
-      <c r="F30" t="s">
-        <v>47</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30" t="s">
-        <v>65</v>
-      </c>
-      <c r="J30">
-        <f t="shared" ref="J30:J61" si="9">2000000+E30*10000+B30</f>
-        <v>2030102</v>
-      </c>
-      <c r="K30" t="s">
-        <v>66</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -3509,40 +3553,40 @@
     </row>
     <row r="31" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A31">
-        <f t="shared" si="7"/>
-        <v>1030103</v>
+        <f t="shared" si="0"/>
+        <v>1030101</v>
       </c>
       <c r="B31" s="7">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C31">
-        <f t="shared" si="8"/>
-        <v>1300103</v>
+        <f t="shared" si="3"/>
+        <v>1300101</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J31">
-        <f t="shared" si="9"/>
-        <v>2030103</v>
+        <f t="shared" si="2"/>
+        <v>2030101</v>
       </c>
       <c r="K31" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -3550,40 +3594,40 @@
     </row>
     <row r="32" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A32">
-        <f t="shared" si="7"/>
-        <v>1030104</v>
+        <f t="shared" ref="A32:A42" si="4">1000000+E32*10000+B32</f>
+        <v>1030102</v>
       </c>
       <c r="B32" s="7">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C32">
-        <f t="shared" si="8"/>
-        <v>1300104</v>
+        <f t="shared" ref="C32:C42" si="5">1000000+E32*100000+B32</f>
+        <v>1300102</v>
       </c>
       <c r="D32" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J32">
-        <f t="shared" si="9"/>
-        <v>2030104</v>
+        <f t="shared" ref="J32:J63" si="6">2000000+E32*10000+B32</f>
+        <v>2030102</v>
       </c>
       <c r="K32" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -3591,40 +3635,40 @@
     </row>
     <row r="33" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A33">
-        <f t="shared" si="7"/>
-        <v>1030105</v>
+        <f t="shared" si="4"/>
+        <v>1030103</v>
       </c>
       <c r="B33" s="7">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C33">
-        <f t="shared" si="8"/>
-        <v>1300105</v>
+        <f t="shared" si="5"/>
+        <v>1300103</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E33">
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J33">
-        <f t="shared" si="9"/>
-        <v>2030105</v>
+        <f t="shared" si="6"/>
+        <v>2030103</v>
       </c>
       <c r="K33" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -3632,40 +3676,40 @@
     </row>
     <row r="34" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A34">
-        <f t="shared" si="7"/>
-        <v>1030106</v>
+        <f t="shared" si="4"/>
+        <v>1030104</v>
       </c>
       <c r="B34" s="7">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C34">
-        <f t="shared" si="8"/>
-        <v>1300106</v>
+        <f t="shared" si="5"/>
+        <v>1300104</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J34">
-        <f t="shared" si="9"/>
-        <v>2030106</v>
+        <f t="shared" si="6"/>
+        <v>2030104</v>
       </c>
       <c r="K34" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -3673,40 +3717,40 @@
     </row>
     <row r="35" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A35">
-        <f t="shared" si="7"/>
-        <v>1030107</v>
+        <f t="shared" si="4"/>
+        <v>1030105</v>
       </c>
       <c r="B35" s="7">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C35">
-        <f t="shared" si="8"/>
-        <v>1300107</v>
+        <f t="shared" si="5"/>
+        <v>1300105</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E35">
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J35">
-        <f t="shared" si="9"/>
-        <v>2030107</v>
+        <f t="shared" si="6"/>
+        <v>2030105</v>
       </c>
       <c r="K35" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -3714,40 +3758,40 @@
     </row>
     <row r="36" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A36">
-        <f t="shared" si="7"/>
-        <v>1030108</v>
+        <f t="shared" si="4"/>
+        <v>1030106</v>
       </c>
       <c r="B36" s="7">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C36">
-        <f t="shared" si="8"/>
-        <v>1300108</v>
+        <f t="shared" si="5"/>
+        <v>1300106</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J36">
-        <f t="shared" si="9"/>
-        <v>2030108</v>
+        <f t="shared" si="6"/>
+        <v>2030106</v>
       </c>
       <c r="K36" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -3755,40 +3799,40 @@
     </row>
     <row r="37" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A37">
-        <f t="shared" si="7"/>
-        <v>1030109</v>
+        <f t="shared" si="4"/>
+        <v>1030107</v>
       </c>
       <c r="B37" s="7">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C37">
-        <f t="shared" si="8"/>
-        <v>1300109</v>
+        <f t="shared" si="5"/>
+        <v>1300107</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J37">
-        <f t="shared" si="9"/>
-        <v>2030109</v>
+        <f t="shared" si="6"/>
+        <v>2030107</v>
       </c>
       <c r="K37" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -3796,40 +3840,40 @@
     </row>
     <row r="38" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A38">
-        <f t="shared" si="7"/>
-        <v>1030110</v>
+        <f t="shared" si="4"/>
+        <v>1030108</v>
       </c>
       <c r="B38" s="7">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C38">
-        <f t="shared" si="8"/>
-        <v>1300110</v>
+        <f t="shared" si="5"/>
+        <v>1300108</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J38">
-        <f t="shared" si="9"/>
-        <v>2030110</v>
+        <f t="shared" si="6"/>
+        <v>2030108</v>
       </c>
       <c r="K38" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -3837,40 +3881,40 @@
     </row>
     <row r="39" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A39">
-        <f t="shared" si="7"/>
-        <v>1030111</v>
+        <f t="shared" si="4"/>
+        <v>1030109</v>
       </c>
       <c r="B39" s="7">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C39">
-        <f t="shared" si="8"/>
-        <v>1300111</v>
+        <f t="shared" si="5"/>
+        <v>1300109</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J39">
-        <f t="shared" si="9"/>
-        <v>2030111</v>
+        <f t="shared" si="6"/>
+        <v>2030109</v>
       </c>
       <c r="K39" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -3878,40 +3922,40 @@
     </row>
     <row r="40" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A40">
-        <f t="shared" si="7"/>
-        <v>1030112</v>
+        <f t="shared" si="4"/>
+        <v>1030110</v>
       </c>
       <c r="B40" s="7">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C40">
-        <f t="shared" si="8"/>
-        <v>1300112</v>
+        <f t="shared" si="5"/>
+        <v>1300110</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J40">
-        <f t="shared" si="9"/>
-        <v>2030112</v>
+        <f t="shared" si="6"/>
+        <v>2030110</v>
       </c>
       <c r="K40" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -3919,40 +3963,40 @@
     </row>
     <row r="41" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A41">
-        <f t="shared" ref="A41:A66" si="10">1000000+E41*10000+B41</f>
-        <v>1030121</v>
+        <f t="shared" si="4"/>
+        <v>1030111</v>
       </c>
       <c r="B41" s="7">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C41">
-        <f t="shared" ref="C41:C66" si="11">1000000+E41*100000+B41</f>
-        <v>1300121</v>
+        <f t="shared" si="5"/>
+        <v>1300111</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E41">
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J41">
-        <f t="shared" si="9"/>
-        <v>2030121</v>
+        <f t="shared" si="6"/>
+        <v>2030111</v>
       </c>
       <c r="K41" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N41">
         <v>1</v>
@@ -3960,40 +4004,40 @@
     </row>
     <row r="42" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A42">
-        <f t="shared" si="10"/>
-        <v>1030122</v>
+        <f t="shared" si="4"/>
+        <v>1030112</v>
       </c>
       <c r="B42" s="7">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C42">
-        <f t="shared" si="11"/>
-        <v>1300122</v>
+        <f t="shared" si="5"/>
+        <v>1300112</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J42">
-        <f t="shared" si="9"/>
-        <v>2030122</v>
+        <f t="shared" si="6"/>
+        <v>2030112</v>
       </c>
       <c r="K42" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -4001,40 +4045,40 @@
     </row>
     <row r="43" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A43">
-        <f t="shared" si="10"/>
-        <v>1030123</v>
+        <f t="shared" ref="A43:A68" si="7">1000000+E43*10000+B43</f>
+        <v>1030121</v>
       </c>
       <c r="B43" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C43">
-        <f t="shared" si="11"/>
-        <v>1300123</v>
+        <f t="shared" ref="C43:C68" si="8">1000000+E43*100000+B43</f>
+        <v>1300121</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J43">
-        <f t="shared" si="9"/>
-        <v>2030123</v>
+        <f t="shared" si="6"/>
+        <v>2030121</v>
       </c>
       <c r="K43" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N43">
         <v>1</v>
@@ -4042,40 +4086,40 @@
     </row>
     <row r="44" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A44">
-        <f t="shared" si="10"/>
-        <v>1030124</v>
+        <f t="shared" si="7"/>
+        <v>1030122</v>
       </c>
       <c r="B44" s="7">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C44">
-        <f t="shared" si="11"/>
-        <v>1300124</v>
+        <f t="shared" si="8"/>
+        <v>1300122</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E44">
         <v>3</v>
       </c>
       <c r="F44" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J44">
-        <f t="shared" si="9"/>
-        <v>2030124</v>
+        <f t="shared" si="6"/>
+        <v>2030122</v>
       </c>
       <c r="K44" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -4083,40 +4127,40 @@
     </row>
     <row r="45" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A45">
-        <f t="shared" si="10"/>
-        <v>1030125</v>
+        <f t="shared" si="7"/>
+        <v>1030123</v>
       </c>
       <c r="B45" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C45">
-        <f t="shared" si="11"/>
-        <v>1300125</v>
+        <f t="shared" si="8"/>
+        <v>1300123</v>
       </c>
       <c r="D45" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E45">
         <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J45">
-        <f t="shared" si="9"/>
-        <v>2030125</v>
+        <f t="shared" si="6"/>
+        <v>2030123</v>
       </c>
       <c r="K45" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -4124,40 +4168,40 @@
     </row>
     <row r="46" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A46">
-        <f t="shared" si="10"/>
-        <v>1030126</v>
+        <f t="shared" si="7"/>
+        <v>1030124</v>
       </c>
       <c r="B46" s="7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C46">
-        <f t="shared" si="11"/>
-        <v>1300126</v>
+        <f t="shared" si="8"/>
+        <v>1300124</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E46">
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J46">
-        <f t="shared" si="9"/>
-        <v>2030126</v>
+        <f t="shared" si="6"/>
+        <v>2030124</v>
       </c>
       <c r="K46" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N46">
         <v>1</v>
@@ -4165,40 +4209,40 @@
     </row>
     <row r="47" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A47">
-        <f t="shared" si="10"/>
-        <v>1030127</v>
+        <f t="shared" si="7"/>
+        <v>1030125</v>
       </c>
       <c r="B47" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C47">
-        <f t="shared" si="11"/>
-        <v>1300127</v>
+        <f t="shared" si="8"/>
+        <v>1300125</v>
       </c>
       <c r="D47" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E47">
         <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J47">
-        <f t="shared" si="9"/>
-        <v>2030127</v>
+        <f t="shared" si="6"/>
+        <v>2030125</v>
       </c>
       <c r="K47" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -4206,40 +4250,40 @@
     </row>
     <row r="48" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A48">
-        <f t="shared" si="10"/>
-        <v>1030128</v>
+        <f t="shared" si="7"/>
+        <v>1030126</v>
       </c>
       <c r="B48" s="7">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C48">
-        <f t="shared" si="11"/>
-        <v>1300128</v>
+        <f t="shared" si="8"/>
+        <v>1300126</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E48">
         <v>3</v>
       </c>
       <c r="F48" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J48">
-        <f t="shared" si="9"/>
-        <v>2030128</v>
+        <f t="shared" si="6"/>
+        <v>2030126</v>
       </c>
       <c r="K48" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -4247,40 +4291,40 @@
     </row>
     <row r="49" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A49">
-        <f t="shared" si="10"/>
-        <v>1030129</v>
+        <f t="shared" si="7"/>
+        <v>1030127</v>
       </c>
       <c r="B49" s="7">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C49">
-        <f t="shared" si="11"/>
-        <v>1300129</v>
+        <f t="shared" si="8"/>
+        <v>1300127</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E49">
         <v>3</v>
       </c>
       <c r="F49" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J49">
-        <f t="shared" si="9"/>
-        <v>2030129</v>
+        <f t="shared" si="6"/>
+        <v>2030127</v>
       </c>
       <c r="K49" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N49">
         <v>1</v>
@@ -4288,40 +4332,40 @@
     </row>
     <row r="50" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A50">
-        <f t="shared" si="10"/>
-        <v>1030130</v>
+        <f t="shared" si="7"/>
+        <v>1030128</v>
       </c>
       <c r="B50" s="7">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C50">
-        <f t="shared" si="11"/>
-        <v>1300130</v>
+        <f t="shared" si="8"/>
+        <v>1300128</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E50">
         <v>3</v>
       </c>
       <c r="F50" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J50">
-        <f t="shared" si="9"/>
-        <v>2030130</v>
+        <f t="shared" si="6"/>
+        <v>2030128</v>
       </c>
       <c r="K50" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N50">
         <v>1</v>
@@ -4329,40 +4373,40 @@
     </row>
     <row r="51" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A51">
-        <f t="shared" si="10"/>
-        <v>1030131</v>
+        <f t="shared" si="7"/>
+        <v>1030129</v>
       </c>
       <c r="B51" s="7">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C51">
-        <f t="shared" si="11"/>
-        <v>1300131</v>
+        <f t="shared" si="8"/>
+        <v>1300129</v>
       </c>
       <c r="D51" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E51">
         <v>3</v>
       </c>
       <c r="F51" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J51">
-        <f t="shared" si="9"/>
-        <v>2030131</v>
+        <f t="shared" si="6"/>
+        <v>2030129</v>
       </c>
       <c r="K51" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N51">
         <v>1</v>
@@ -4370,40 +4414,40 @@
     </row>
     <row r="52" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A52">
-        <f t="shared" si="10"/>
-        <v>1030132</v>
+        <f t="shared" si="7"/>
+        <v>1030130</v>
       </c>
       <c r="B52" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C52">
-        <f t="shared" si="11"/>
-        <v>1300132</v>
+        <f t="shared" si="8"/>
+        <v>1300130</v>
       </c>
       <c r="D52" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E52">
         <v>3</v>
       </c>
       <c r="F52" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J52">
-        <f t="shared" si="9"/>
-        <v>2030132</v>
+        <f t="shared" si="6"/>
+        <v>2030130</v>
       </c>
       <c r="K52" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -4411,40 +4455,40 @@
     </row>
     <row r="53" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A53">
-        <f t="shared" si="10"/>
-        <v>1030141</v>
+        <f t="shared" si="7"/>
+        <v>1030131</v>
       </c>
       <c r="B53" s="7">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C53">
-        <f t="shared" si="11"/>
-        <v>1300141</v>
+        <f t="shared" si="8"/>
+        <v>1300131</v>
       </c>
       <c r="D53" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J53">
-        <f t="shared" si="9"/>
-        <v>2030141</v>
+        <f t="shared" si="6"/>
+        <v>2030131</v>
       </c>
       <c r="K53" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -4452,40 +4496,40 @@
     </row>
     <row r="54" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A54">
-        <f t="shared" si="10"/>
-        <v>1030142</v>
+        <f t="shared" si="7"/>
+        <v>1030132</v>
       </c>
       <c r="B54" s="7">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C54">
-        <f t="shared" si="11"/>
-        <v>1300142</v>
+        <f t="shared" si="8"/>
+        <v>1300132</v>
       </c>
       <c r="D54" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E54">
         <v>3</v>
       </c>
       <c r="F54" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J54">
-        <f t="shared" si="9"/>
-        <v>2030142</v>
+        <f t="shared" si="6"/>
+        <v>2030132</v>
       </c>
       <c r="K54" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N54">
         <v>1</v>
@@ -4493,40 +4537,40 @@
     </row>
     <row r="55" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A55">
-        <f t="shared" si="10"/>
-        <v>1030143</v>
+        <f t="shared" si="7"/>
+        <v>1030141</v>
       </c>
       <c r="B55" s="7">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C55">
-        <f t="shared" si="11"/>
-        <v>1300143</v>
+        <f t="shared" si="8"/>
+        <v>1300141</v>
       </c>
       <c r="D55" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E55">
         <v>3</v>
       </c>
       <c r="F55" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J55">
-        <f t="shared" si="9"/>
-        <v>2030143</v>
+        <f t="shared" si="6"/>
+        <v>2030141</v>
       </c>
       <c r="K55" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -4534,40 +4578,40 @@
     </row>
     <row r="56" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A56">
-        <f t="shared" si="10"/>
-        <v>1030144</v>
+        <f t="shared" si="7"/>
+        <v>1030142</v>
       </c>
       <c r="B56" s="7">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C56">
-        <f t="shared" si="11"/>
-        <v>1300144</v>
+        <f t="shared" si="8"/>
+        <v>1300142</v>
       </c>
       <c r="D56" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E56">
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J56">
-        <f t="shared" si="9"/>
-        <v>2030144</v>
+        <f t="shared" si="6"/>
+        <v>2030142</v>
       </c>
       <c r="K56" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -4575,40 +4619,40 @@
     </row>
     <row r="57" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A57">
-        <f t="shared" si="10"/>
-        <v>1030145</v>
+        <f t="shared" si="7"/>
+        <v>1030143</v>
       </c>
       <c r="B57" s="7">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C57">
-        <f t="shared" si="11"/>
-        <v>1300145</v>
+        <f t="shared" si="8"/>
+        <v>1300143</v>
       </c>
       <c r="D57" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E57">
         <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J57">
-        <f t="shared" si="9"/>
-        <v>2030145</v>
+        <f t="shared" si="6"/>
+        <v>2030143</v>
       </c>
       <c r="K57" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N57">
         <v>1</v>
@@ -4616,40 +4660,40 @@
     </row>
     <row r="58" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A58">
-        <f t="shared" si="10"/>
-        <v>1030146</v>
+        <f t="shared" si="7"/>
+        <v>1030144</v>
       </c>
       <c r="B58" s="7">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C58">
-        <f t="shared" si="11"/>
-        <v>1300146</v>
+        <f t="shared" si="8"/>
+        <v>1300144</v>
       </c>
       <c r="D58" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E58">
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J58">
-        <f t="shared" si="9"/>
-        <v>2030146</v>
+        <f t="shared" si="6"/>
+        <v>2030144</v>
       </c>
       <c r="K58" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N58">
         <v>1</v>
@@ -4657,40 +4701,40 @@
     </row>
     <row r="59" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A59">
-        <f t="shared" si="10"/>
-        <v>1030147</v>
+        <f t="shared" si="7"/>
+        <v>1030145</v>
       </c>
       <c r="B59" s="7">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C59">
-        <f t="shared" si="11"/>
-        <v>1300147</v>
+        <f t="shared" si="8"/>
+        <v>1300145</v>
       </c>
       <c r="D59" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E59">
         <v>3</v>
       </c>
       <c r="F59" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J59">
-        <f t="shared" si="9"/>
-        <v>2030147</v>
+        <f t="shared" si="6"/>
+        <v>2030145</v>
       </c>
       <c r="K59" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -4698,40 +4742,40 @@
     </row>
     <row r="60" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A60">
-        <f t="shared" si="10"/>
-        <v>1030148</v>
+        <f t="shared" si="7"/>
+        <v>1030146</v>
       </c>
       <c r="B60" s="7">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C60">
-        <f t="shared" si="11"/>
-        <v>1300148</v>
+        <f t="shared" si="8"/>
+        <v>1300146</v>
       </c>
       <c r="D60" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E60">
         <v>3</v>
       </c>
       <c r="F60" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J60">
-        <f t="shared" si="9"/>
-        <v>2030148</v>
+        <f t="shared" si="6"/>
+        <v>2030146</v>
       </c>
       <c r="K60" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -4739,40 +4783,40 @@
     </row>
     <row r="61" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A61">
-        <f t="shared" si="10"/>
-        <v>1030149</v>
+        <f t="shared" si="7"/>
+        <v>1030147</v>
       </c>
       <c r="B61" s="7">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C61">
-        <f t="shared" si="11"/>
-        <v>1300149</v>
+        <f t="shared" si="8"/>
+        <v>1300147</v>
       </c>
       <c r="D61" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J61">
-        <f t="shared" si="9"/>
-        <v>2030149</v>
+        <f t="shared" si="6"/>
+        <v>2030147</v>
       </c>
       <c r="K61" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -4780,40 +4824,40 @@
     </row>
     <row r="62" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A62">
-        <f t="shared" si="10"/>
-        <v>1030150</v>
+        <f t="shared" si="7"/>
+        <v>1030148</v>
       </c>
       <c r="B62" s="7">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C62">
-        <f t="shared" si="11"/>
-        <v>1300150</v>
+        <f t="shared" si="8"/>
+        <v>1300148</v>
       </c>
       <c r="D62" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E62">
         <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J62">
-        <f t="shared" ref="J62:J93" si="12">2000000+E62*10000+B62</f>
-        <v>2030150</v>
+        <f t="shared" si="6"/>
+        <v>2030148</v>
       </c>
       <c r="K62" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N62">
         <v>1</v>
@@ -4821,40 +4865,40 @@
     </row>
     <row r="63" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A63">
-        <f t="shared" si="10"/>
-        <v>1030151</v>
+        <f t="shared" si="7"/>
+        <v>1030149</v>
       </c>
       <c r="B63" s="7">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C63">
-        <f t="shared" si="11"/>
-        <v>1300151</v>
+        <f t="shared" si="8"/>
+        <v>1300149</v>
       </c>
       <c r="D63" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E63">
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J63">
-        <f t="shared" si="12"/>
-        <v>2030151</v>
+        <f t="shared" si="6"/>
+        <v>2030149</v>
       </c>
       <c r="K63" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -4862,40 +4906,40 @@
     </row>
     <row r="64" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A64">
-        <f t="shared" si="10"/>
-        <v>1030152</v>
+        <f t="shared" si="7"/>
+        <v>1030150</v>
       </c>
       <c r="B64" s="7">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C64">
-        <f t="shared" si="11"/>
-        <v>1300152</v>
+        <f t="shared" si="8"/>
+        <v>1300150</v>
       </c>
       <c r="D64" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E64">
         <v>3</v>
       </c>
       <c r="F64" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J64">
-        <f t="shared" si="12"/>
-        <v>2030152</v>
+        <f t="shared" ref="J64:J95" si="9">2000000+E64*10000+B64</f>
+        <v>2030150</v>
       </c>
       <c r="K64" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N64">
         <v>1</v>
@@ -4903,40 +4947,40 @@
     </row>
     <row r="65" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A65">
-        <f t="shared" si="10"/>
-        <v>1030161</v>
+        <f t="shared" si="7"/>
+        <v>1030151</v>
       </c>
       <c r="B65" s="7">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C65">
-        <f t="shared" si="11"/>
-        <v>1300161</v>
+        <f t="shared" si="8"/>
+        <v>1300151</v>
       </c>
       <c r="D65" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E65">
         <v>3</v>
       </c>
       <c r="F65" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J65">
-        <f t="shared" si="12"/>
-        <v>2030161</v>
+        <f t="shared" si="9"/>
+        <v>2030151</v>
       </c>
       <c r="K65" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N65">
         <v>1</v>
@@ -4944,40 +4988,40 @@
     </row>
     <row r="66" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A66">
-        <f t="shared" si="10"/>
-        <v>1030162</v>
+        <f t="shared" si="7"/>
+        <v>1030152</v>
       </c>
       <c r="B66" s="7">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C66">
-        <f t="shared" si="11"/>
-        <v>1300162</v>
+        <f t="shared" si="8"/>
+        <v>1300152</v>
       </c>
       <c r="D66" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E66">
         <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J66">
-        <f t="shared" si="12"/>
-        <v>2030162</v>
+        <f t="shared" si="9"/>
+        <v>2030152</v>
       </c>
       <c r="K66" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -4985,40 +5029,40 @@
     </row>
     <row r="67" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A67">
-        <f t="shared" ref="A67:A98" si="13">1000000+E67*10000+B67</f>
-        <v>1030163</v>
+        <f t="shared" si="7"/>
+        <v>1030161</v>
       </c>
       <c r="B67" s="7">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C98" si="14">1000000+E67*100000+B67</f>
-        <v>1300163</v>
+        <f t="shared" si="8"/>
+        <v>1300161</v>
       </c>
       <c r="D67" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E67">
         <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J67">
-        <f t="shared" si="12"/>
-        <v>2030163</v>
+        <f t="shared" si="9"/>
+        <v>2030161</v>
       </c>
       <c r="K67" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N67">
         <v>1</v>
@@ -5026,40 +5070,40 @@
     </row>
     <row r="68" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A68">
-        <f t="shared" si="13"/>
-        <v>1030164</v>
+        <f t="shared" si="7"/>
+        <v>1030162</v>
       </c>
       <c r="B68" s="7">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C68">
-        <f t="shared" si="14"/>
-        <v>1300164</v>
+        <f t="shared" si="8"/>
+        <v>1300162</v>
       </c>
       <c r="D68" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E68">
         <v>3</v>
       </c>
       <c r="F68" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J68">
-        <f t="shared" si="12"/>
-        <v>2030164</v>
+        <f t="shared" si="9"/>
+        <v>2030162</v>
       </c>
       <c r="K68" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N68">
         <v>1</v>
@@ -5067,40 +5111,40 @@
     </row>
     <row r="69" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A69">
-        <f t="shared" si="13"/>
-        <v>1030165</v>
+        <f t="shared" ref="A69:A100" si="10">1000000+E69*10000+B69</f>
+        <v>1030163</v>
       </c>
       <c r="B69" s="7">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C69">
-        <f t="shared" si="14"/>
-        <v>1300165</v>
+        <f t="shared" ref="C69:C100" si="11">1000000+E69*100000+B69</f>
+        <v>1300163</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E69">
         <v>3</v>
       </c>
       <c r="F69" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J69">
-        <f t="shared" si="12"/>
-        <v>2030165</v>
+        <f t="shared" si="9"/>
+        <v>2030163</v>
       </c>
       <c r="K69" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N69">
         <v>1</v>
@@ -5108,40 +5152,40 @@
     </row>
     <row r="70" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A70">
-        <f t="shared" si="13"/>
-        <v>1030166</v>
+        <f t="shared" si="10"/>
+        <v>1030164</v>
       </c>
       <c r="B70" s="7">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C70">
-        <f t="shared" si="14"/>
-        <v>1300166</v>
+        <f t="shared" si="11"/>
+        <v>1300164</v>
       </c>
       <c r="D70" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E70">
         <v>3</v>
       </c>
       <c r="F70" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J70">
-        <f t="shared" si="12"/>
-        <v>2030166</v>
+        <f t="shared" si="9"/>
+        <v>2030164</v>
       </c>
       <c r="K70" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N70">
         <v>1</v>
@@ -5149,40 +5193,40 @@
     </row>
     <row r="71" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A71">
-        <f t="shared" si="13"/>
-        <v>1030167</v>
+        <f t="shared" si="10"/>
+        <v>1030165</v>
       </c>
       <c r="B71" s="7">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C71">
-        <f t="shared" si="14"/>
-        <v>1300167</v>
+        <f t="shared" si="11"/>
+        <v>1300165</v>
       </c>
       <c r="D71" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E71">
         <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J71">
-        <f t="shared" si="12"/>
-        <v>2030167</v>
+        <f t="shared" si="9"/>
+        <v>2030165</v>
       </c>
       <c r="K71" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N71">
         <v>1</v>
@@ -5190,40 +5234,40 @@
     </row>
     <row r="72" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A72">
-        <f t="shared" si="13"/>
-        <v>1030168</v>
+        <f t="shared" si="10"/>
+        <v>1030166</v>
       </c>
       <c r="B72" s="7">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C72">
-        <f t="shared" si="14"/>
-        <v>1300168</v>
+        <f t="shared" si="11"/>
+        <v>1300166</v>
       </c>
       <c r="D72" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E72">
         <v>3</v>
       </c>
       <c r="F72" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J72">
-        <f t="shared" si="12"/>
-        <v>2030168</v>
+        <f t="shared" si="9"/>
+        <v>2030166</v>
       </c>
       <c r="K72" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N72">
         <v>1</v>
@@ -5231,40 +5275,40 @@
     </row>
     <row r="73" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A73">
-        <f t="shared" si="13"/>
-        <v>1030169</v>
+        <f t="shared" si="10"/>
+        <v>1030167</v>
       </c>
       <c r="B73" s="7">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C73">
-        <f t="shared" si="14"/>
-        <v>1300169</v>
+        <f t="shared" si="11"/>
+        <v>1300167</v>
       </c>
       <c r="D73" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E73">
         <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J73">
-        <f t="shared" si="12"/>
-        <v>2030169</v>
+        <f t="shared" si="9"/>
+        <v>2030167</v>
       </c>
       <c r="K73" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N73">
         <v>1</v>
@@ -5272,40 +5316,40 @@
     </row>
     <row r="74" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A74">
-        <f t="shared" si="13"/>
-        <v>1030170</v>
+        <f t="shared" si="10"/>
+        <v>1030168</v>
       </c>
       <c r="B74" s="7">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C74">
-        <f t="shared" si="14"/>
-        <v>1300170</v>
+        <f t="shared" si="11"/>
+        <v>1300168</v>
       </c>
       <c r="D74" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E74">
         <v>3</v>
       </c>
       <c r="F74" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J74">
-        <f t="shared" si="12"/>
-        <v>2030170</v>
+        <f t="shared" si="9"/>
+        <v>2030168</v>
       </c>
       <c r="K74" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N74">
         <v>1</v>
@@ -5313,40 +5357,40 @@
     </row>
     <row r="75" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A75">
-        <f t="shared" si="13"/>
-        <v>1030171</v>
+        <f t="shared" si="10"/>
+        <v>1030169</v>
       </c>
       <c r="B75" s="7">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C75">
-        <f t="shared" si="14"/>
-        <v>1300171</v>
+        <f t="shared" si="11"/>
+        <v>1300169</v>
       </c>
       <c r="D75" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E75">
         <v>3</v>
       </c>
       <c r="F75" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J75">
-        <f t="shared" si="12"/>
-        <v>2030171</v>
+        <f t="shared" si="9"/>
+        <v>2030169</v>
       </c>
       <c r="K75" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N75">
         <v>1</v>
@@ -5354,40 +5398,40 @@
     </row>
     <row r="76" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A76">
-        <f t="shared" si="13"/>
-        <v>1030172</v>
+        <f t="shared" si="10"/>
+        <v>1030170</v>
       </c>
       <c r="B76" s="7">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C76">
-        <f t="shared" si="14"/>
-        <v>1300172</v>
+        <f t="shared" si="11"/>
+        <v>1300170</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J76">
-        <f t="shared" si="12"/>
-        <v>2030172</v>
+        <f t="shared" si="9"/>
+        <v>2030170</v>
       </c>
       <c r="K76" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N76">
         <v>1</v>
@@ -5395,40 +5439,40 @@
     </row>
     <row r="77" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A77">
-        <f t="shared" si="13"/>
-        <v>1030181</v>
+        <f t="shared" si="10"/>
+        <v>1030171</v>
       </c>
       <c r="B77" s="7">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C77">
-        <f t="shared" si="14"/>
-        <v>1300181</v>
+        <f t="shared" si="11"/>
+        <v>1300171</v>
       </c>
       <c r="D77" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J77">
-        <f t="shared" si="12"/>
-        <v>2030181</v>
+        <f t="shared" si="9"/>
+        <v>2030171</v>
       </c>
       <c r="K77" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N77">
         <v>1</v>
@@ -5436,40 +5480,40 @@
     </row>
     <row r="78" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A78">
-        <f t="shared" si="13"/>
-        <v>1030182</v>
+        <f t="shared" si="10"/>
+        <v>1030172</v>
       </c>
       <c r="B78" s="7">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C78">
-        <f t="shared" si="14"/>
-        <v>1300182</v>
+        <f t="shared" si="11"/>
+        <v>1300172</v>
       </c>
       <c r="D78" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E78">
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J78">
-        <f t="shared" si="12"/>
-        <v>2030182</v>
+        <f t="shared" si="9"/>
+        <v>2030172</v>
       </c>
       <c r="K78" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N78">
         <v>1</v>
@@ -5477,40 +5521,40 @@
     </row>
     <row r="79" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A79">
-        <f t="shared" si="13"/>
-        <v>1030183</v>
+        <f t="shared" si="10"/>
+        <v>1030181</v>
       </c>
       <c r="B79" s="7">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C79">
-        <f t="shared" si="14"/>
-        <v>1300183</v>
+        <f t="shared" si="11"/>
+        <v>1300181</v>
       </c>
       <c r="D79" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E79">
         <v>3</v>
       </c>
       <c r="F79" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>1</v>
       </c>
       <c r="I79" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J79">
-        <f t="shared" si="12"/>
-        <v>2030183</v>
+        <f t="shared" si="9"/>
+        <v>2030181</v>
       </c>
       <c r="K79" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -5518,40 +5562,40 @@
     </row>
     <row r="80" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A80">
-        <f t="shared" si="13"/>
-        <v>1030184</v>
+        <f t="shared" si="10"/>
+        <v>1030182</v>
       </c>
       <c r="B80" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C80">
-        <f t="shared" si="14"/>
-        <v>1300184</v>
+        <f t="shared" si="11"/>
+        <v>1300182</v>
       </c>
       <c r="D80" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E80">
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J80">
-        <f t="shared" si="12"/>
-        <v>2030184</v>
+        <f t="shared" si="9"/>
+        <v>2030182</v>
       </c>
       <c r="K80" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N80">
         <v>1</v>
@@ -5559,40 +5603,40 @@
     </row>
     <row r="81" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A81">
-        <f t="shared" si="13"/>
-        <v>1030185</v>
+        <f t="shared" si="10"/>
+        <v>1030183</v>
       </c>
       <c r="B81" s="7">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C81">
-        <f t="shared" si="14"/>
-        <v>1300185</v>
+        <f t="shared" si="11"/>
+        <v>1300183</v>
       </c>
       <c r="D81" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J81">
-        <f t="shared" si="12"/>
-        <v>2030185</v>
+        <f t="shared" si="9"/>
+        <v>2030183</v>
       </c>
       <c r="K81" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -5600,40 +5644,40 @@
     </row>
     <row r="82" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A82">
-        <f t="shared" si="13"/>
-        <v>1030186</v>
+        <f t="shared" si="10"/>
+        <v>1030184</v>
       </c>
       <c r="B82" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C82">
-        <f t="shared" si="14"/>
-        <v>1300186</v>
+        <f t="shared" si="11"/>
+        <v>1300184</v>
       </c>
       <c r="D82" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E82">
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J82">
-        <f t="shared" si="12"/>
-        <v>2030186</v>
+        <f t="shared" si="9"/>
+        <v>2030184</v>
       </c>
       <c r="K82" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -5641,40 +5685,40 @@
     </row>
     <row r="83" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A83">
-        <f t="shared" si="13"/>
-        <v>1030187</v>
+        <f t="shared" si="10"/>
+        <v>1030185</v>
       </c>
       <c r="B83" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C83">
-        <f t="shared" si="14"/>
-        <v>1300187</v>
+        <f t="shared" si="11"/>
+        <v>1300185</v>
       </c>
       <c r="D83" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J83">
-        <f t="shared" si="12"/>
-        <v>2030187</v>
+        <f t="shared" si="9"/>
+        <v>2030185</v>
       </c>
       <c r="K83" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N83">
         <v>1</v>
@@ -5682,40 +5726,40 @@
     </row>
     <row r="84" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A84">
-        <f t="shared" si="13"/>
-        <v>1030188</v>
+        <f t="shared" si="10"/>
+        <v>1030186</v>
       </c>
       <c r="B84" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C84">
-        <f t="shared" si="14"/>
-        <v>1300188</v>
+        <f t="shared" si="11"/>
+        <v>1300186</v>
       </c>
       <c r="D84" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E84">
         <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J84">
-        <f t="shared" si="12"/>
-        <v>2030188</v>
+        <f t="shared" si="9"/>
+        <v>2030186</v>
       </c>
       <c r="K84" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N84">
         <v>1</v>
@@ -5723,40 +5767,40 @@
     </row>
     <row r="85" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A85">
-        <f t="shared" si="13"/>
-        <v>1030189</v>
+        <f t="shared" si="10"/>
+        <v>1030187</v>
       </c>
       <c r="B85" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C85">
-        <f t="shared" si="14"/>
-        <v>1300189</v>
+        <f t="shared" si="11"/>
+        <v>1300187</v>
       </c>
       <c r="D85" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E85">
         <v>3</v>
       </c>
       <c r="F85" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J85">
-        <f t="shared" si="12"/>
-        <v>2030189</v>
+        <f t="shared" si="9"/>
+        <v>2030187</v>
       </c>
       <c r="K85" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -5764,40 +5808,40 @@
     </row>
     <row r="86" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A86">
-        <f t="shared" si="13"/>
-        <v>1030190</v>
+        <f t="shared" si="10"/>
+        <v>1030188</v>
       </c>
       <c r="B86" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C86">
-        <f t="shared" si="14"/>
-        <v>1300190</v>
+        <f t="shared" si="11"/>
+        <v>1300188</v>
       </c>
       <c r="D86" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E86">
         <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G86">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J86">
-        <f t="shared" si="12"/>
-        <v>2030190</v>
+        <f t="shared" si="9"/>
+        <v>2030188</v>
       </c>
       <c r="K86" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -5805,40 +5849,40 @@
     </row>
     <row r="87" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A87">
-        <f t="shared" si="13"/>
-        <v>1030191</v>
+        <f t="shared" si="10"/>
+        <v>1030189</v>
       </c>
       <c r="B87" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C87">
-        <f t="shared" si="14"/>
-        <v>1300191</v>
+        <f t="shared" si="11"/>
+        <v>1300189</v>
       </c>
       <c r="D87" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E87">
         <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G87">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H87">
         <v>1</v>
       </c>
       <c r="I87" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J87">
-        <f t="shared" si="12"/>
-        <v>2030191</v>
+        <f t="shared" si="9"/>
+        <v>2030189</v>
       </c>
       <c r="K87" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -5846,40 +5890,40 @@
     </row>
     <row r="88" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A88">
-        <f t="shared" si="13"/>
-        <v>1030192</v>
+        <f t="shared" si="10"/>
+        <v>1030190</v>
       </c>
       <c r="B88" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C88">
-        <f t="shared" si="14"/>
-        <v>1300192</v>
+        <f t="shared" si="11"/>
+        <v>1300190</v>
       </c>
       <c r="D88" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E88">
         <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G88">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J88">
-        <f t="shared" si="12"/>
-        <v>2030192</v>
+        <f t="shared" si="9"/>
+        <v>2030190</v>
       </c>
       <c r="K88" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -5887,40 +5931,40 @@
     </row>
     <row r="89" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A89">
-        <f t="shared" si="13"/>
-        <v>1030201</v>
+        <f t="shared" si="10"/>
+        <v>1030191</v>
       </c>
       <c r="B89" s="7">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C89">
-        <f t="shared" si="14"/>
-        <v>1300201</v>
+        <f t="shared" si="11"/>
+        <v>1300191</v>
       </c>
       <c r="D89" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E89">
         <v>3</v>
       </c>
       <c r="F89" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J89">
-        <f t="shared" si="12"/>
-        <v>2030201</v>
+        <f t="shared" si="9"/>
+        <v>2030191</v>
       </c>
       <c r="K89" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N89">
         <v>1</v>
@@ -5928,40 +5972,40 @@
     </row>
     <row r="90" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A90">
-        <f t="shared" si="13"/>
-        <v>1030202</v>
+        <f t="shared" si="10"/>
+        <v>1030192</v>
       </c>
       <c r="B90" s="7">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C90">
-        <f t="shared" si="14"/>
-        <v>1300202</v>
+        <f t="shared" si="11"/>
+        <v>1300192</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E90">
         <v>3</v>
       </c>
       <c r="F90" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J90">
-        <f t="shared" si="12"/>
-        <v>2030202</v>
+        <f t="shared" si="9"/>
+        <v>2030192</v>
       </c>
       <c r="K90" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N90">
         <v>1</v>
@@ -5969,40 +6013,40 @@
     </row>
     <row r="91" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A91">
-        <f t="shared" si="13"/>
-        <v>1030203</v>
+        <f t="shared" si="10"/>
+        <v>1030201</v>
       </c>
       <c r="B91" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C91">
-        <f t="shared" si="14"/>
-        <v>1300203</v>
+        <f t="shared" si="11"/>
+        <v>1300201</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E91">
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91">
         <v>1</v>
       </c>
       <c r="I91" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J91">
-        <f t="shared" si="12"/>
-        <v>2030203</v>
+        <f t="shared" si="9"/>
+        <v>2030201</v>
       </c>
       <c r="K91" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -6010,40 +6054,40 @@
     </row>
     <row r="92" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A92">
-        <f t="shared" si="13"/>
-        <v>1030204</v>
+        <f t="shared" si="10"/>
+        <v>1030202</v>
       </c>
       <c r="B92" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C92">
-        <f t="shared" si="14"/>
-        <v>1300204</v>
+        <f t="shared" si="11"/>
+        <v>1300202</v>
       </c>
       <c r="D92" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E92">
         <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J92">
-        <f t="shared" si="12"/>
-        <v>2030204</v>
+        <f t="shared" si="9"/>
+        <v>2030202</v>
       </c>
       <c r="K92" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N92">
         <v>1</v>
@@ -6051,40 +6095,40 @@
     </row>
     <row r="93" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A93">
-        <f t="shared" si="13"/>
-        <v>1030205</v>
+        <f t="shared" si="10"/>
+        <v>1030203</v>
       </c>
       <c r="B93" s="7">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C93">
-        <f t="shared" si="14"/>
-        <v>1300205</v>
+        <f t="shared" si="11"/>
+        <v>1300203</v>
       </c>
       <c r="D93" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E93">
         <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J93">
-        <f t="shared" si="12"/>
-        <v>2030205</v>
+        <f t="shared" si="9"/>
+        <v>2030203</v>
       </c>
       <c r="K93" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -6092,40 +6136,40 @@
     </row>
     <row r="94" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A94">
-        <f t="shared" si="13"/>
-        <v>1030206</v>
+        <f t="shared" si="10"/>
+        <v>1030204</v>
       </c>
       <c r="B94" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C94">
-        <f t="shared" si="14"/>
-        <v>1300206</v>
+        <f t="shared" si="11"/>
+        <v>1300204</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E94">
         <v>3</v>
       </c>
       <c r="F94" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H94">
         <v>1</v>
       </c>
       <c r="I94" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J94">
-        <f t="shared" ref="J94:J128" si="15">2000000+E94*10000+B94</f>
-        <v>2030206</v>
+        <f t="shared" si="9"/>
+        <v>2030204</v>
       </c>
       <c r="K94" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N94">
         <v>1</v>
@@ -6133,40 +6177,40 @@
     </row>
     <row r="95" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A95">
-        <f t="shared" si="13"/>
-        <v>1030207</v>
+        <f t="shared" si="10"/>
+        <v>1030205</v>
       </c>
       <c r="B95" s="7">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C95">
-        <f t="shared" si="14"/>
-        <v>1300207</v>
+        <f t="shared" si="11"/>
+        <v>1300205</v>
       </c>
       <c r="D95" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E95">
         <v>3</v>
       </c>
       <c r="F95" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G95">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J95">
-        <f t="shared" si="15"/>
-        <v>2030207</v>
+        <f t="shared" si="9"/>
+        <v>2030205</v>
       </c>
       <c r="K95" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N95">
         <v>1</v>
@@ -6174,40 +6218,40 @@
     </row>
     <row r="96" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A96">
-        <f t="shared" si="13"/>
-        <v>1030208</v>
+        <f t="shared" si="10"/>
+        <v>1030206</v>
       </c>
       <c r="B96" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C96">
-        <f t="shared" si="14"/>
-        <v>1300208</v>
+        <f t="shared" si="11"/>
+        <v>1300206</v>
       </c>
       <c r="D96" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E96">
         <v>3</v>
       </c>
       <c r="F96" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G96">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J96">
-        <f t="shared" si="15"/>
-        <v>2030208</v>
+        <f t="shared" ref="J96:J130" si="12">2000000+E96*10000+B96</f>
+        <v>2030206</v>
       </c>
       <c r="K96" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -6215,40 +6259,40 @@
     </row>
     <row r="97" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A97">
-        <f t="shared" si="13"/>
-        <v>1030209</v>
+        <f t="shared" si="10"/>
+        <v>1030207</v>
       </c>
       <c r="B97" s="7">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C97">
-        <f t="shared" si="14"/>
-        <v>1300209</v>
+        <f t="shared" si="11"/>
+        <v>1300207</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E97">
         <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H97">
         <v>1</v>
       </c>
       <c r="I97" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J97">
-        <f t="shared" si="15"/>
-        <v>2030209</v>
+        <f t="shared" si="12"/>
+        <v>2030207</v>
       </c>
       <c r="K97" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N97">
         <v>1</v>
@@ -6256,40 +6300,40 @@
     </row>
     <row r="98" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A98">
-        <f t="shared" si="13"/>
-        <v>1030210</v>
+        <f t="shared" si="10"/>
+        <v>1030208</v>
       </c>
       <c r="B98" s="7">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C98">
-        <f t="shared" si="14"/>
-        <v>1300210</v>
+        <f t="shared" si="11"/>
+        <v>1300208</v>
       </c>
       <c r="D98" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E98">
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H98">
         <v>1</v>
       </c>
       <c r="I98" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J98">
-        <f t="shared" si="15"/>
-        <v>2030210</v>
+        <f t="shared" si="12"/>
+        <v>2030208</v>
       </c>
       <c r="K98" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N98">
         <v>1</v>
@@ -6297,40 +6341,40 @@
     </row>
     <row r="99" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A99">
-        <f t="shared" ref="A99:A130" si="16">1000000+E99*10000+B99</f>
-        <v>1030211</v>
+        <f t="shared" si="10"/>
+        <v>1030209</v>
       </c>
       <c r="B99" s="7">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C99">
-        <f t="shared" ref="C99:C128" si="17">1000000+E99*100000+B99</f>
-        <v>1300211</v>
+        <f t="shared" si="11"/>
+        <v>1300209</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E99">
         <v>3</v>
       </c>
       <c r="F99" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G99">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H99">
         <v>1</v>
       </c>
       <c r="I99" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J99">
-        <f t="shared" si="15"/>
-        <v>2030211</v>
+        <f t="shared" si="12"/>
+        <v>2030209</v>
       </c>
       <c r="K99" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -6338,40 +6382,40 @@
     </row>
     <row r="100" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A100">
-        <f t="shared" si="16"/>
-        <v>1030212</v>
+        <f t="shared" si="10"/>
+        <v>1030210</v>
       </c>
       <c r="B100" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C100">
-        <f t="shared" si="17"/>
-        <v>1300212</v>
+        <f t="shared" si="11"/>
+        <v>1300210</v>
       </c>
       <c r="D100" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E100">
         <v>3</v>
       </c>
       <c r="F100" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G100">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="I100" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J100">
-        <f t="shared" si="15"/>
-        <v>2030212</v>
+        <f t="shared" si="12"/>
+        <v>2030210</v>
       </c>
       <c r="K100" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N100">
         <v>1</v>
@@ -6379,40 +6423,40 @@
     </row>
     <row r="101" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A101">
-        <f t="shared" si="16"/>
-        <v>1030221</v>
+        <f t="shared" ref="A101:A132" si="13">1000000+E101*10000+B101</f>
+        <v>1030211</v>
       </c>
       <c r="B101" s="7">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C101">
-        <f t="shared" si="17"/>
-        <v>1300221</v>
+        <f t="shared" ref="C101:C130" si="14">1000000+E101*100000+B101</f>
+        <v>1300211</v>
       </c>
       <c r="D101" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E101">
         <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H101">
         <v>1</v>
       </c>
       <c r="I101" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J101">
-        <f t="shared" si="15"/>
-        <v>2030221</v>
+        <f t="shared" si="12"/>
+        <v>2030211</v>
       </c>
       <c r="K101" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N101">
         <v>1</v>
@@ -6420,40 +6464,40 @@
     </row>
     <row r="102" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A102">
-        <f t="shared" si="16"/>
-        <v>1030222</v>
+        <f t="shared" si="13"/>
+        <v>1030212</v>
       </c>
       <c r="B102" s="7">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C102">
-        <f t="shared" si="17"/>
-        <v>1300222</v>
+        <f t="shared" si="14"/>
+        <v>1300212</v>
       </c>
       <c r="D102" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E102">
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H102">
         <v>1</v>
       </c>
       <c r="I102" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J102">
-        <f t="shared" si="15"/>
-        <v>2030222</v>
+        <f t="shared" si="12"/>
+        <v>2030212</v>
       </c>
       <c r="K102" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N102">
         <v>1</v>
@@ -6461,40 +6505,40 @@
     </row>
     <row r="103" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A103">
-        <f t="shared" si="16"/>
-        <v>1030223</v>
+        <f t="shared" si="13"/>
+        <v>1030221</v>
       </c>
       <c r="B103" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C103">
-        <f t="shared" si="17"/>
-        <v>1300223</v>
+        <f t="shared" si="14"/>
+        <v>1300221</v>
       </c>
       <c r="D103" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E103">
         <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H103">
         <v>1</v>
       </c>
       <c r="I103" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J103">
-        <f t="shared" si="15"/>
-        <v>2030223</v>
+        <f t="shared" si="12"/>
+        <v>2030221</v>
       </c>
       <c r="K103" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N103">
         <v>1</v>
@@ -6502,40 +6546,40 @@
     </row>
     <row r="104" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A104">
-        <f t="shared" si="16"/>
-        <v>1030224</v>
+        <f t="shared" si="13"/>
+        <v>1030222</v>
       </c>
       <c r="B104" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C104">
-        <f t="shared" si="17"/>
-        <v>1300224</v>
+        <f t="shared" si="14"/>
+        <v>1300222</v>
       </c>
       <c r="D104" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E104">
         <v>3</v>
       </c>
       <c r="F104" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104">
         <v>1</v>
       </c>
       <c r="I104" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J104">
-        <f t="shared" si="15"/>
-        <v>2030224</v>
+        <f t="shared" si="12"/>
+        <v>2030222</v>
       </c>
       <c r="K104" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N104">
         <v>1</v>
@@ -6543,40 +6587,40 @@
     </row>
     <row r="105" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A105">
-        <f t="shared" si="16"/>
-        <v>1030225</v>
+        <f t="shared" si="13"/>
+        <v>1030223</v>
       </c>
       <c r="B105" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C105">
-        <f t="shared" si="17"/>
-        <v>1300225</v>
+        <f t="shared" si="14"/>
+        <v>1300223</v>
       </c>
       <c r="D105" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E105">
         <v>3</v>
       </c>
       <c r="F105" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H105">
         <v>1</v>
       </c>
       <c r="I105" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J105">
-        <f t="shared" si="15"/>
-        <v>2030225</v>
+        <f t="shared" si="12"/>
+        <v>2030223</v>
       </c>
       <c r="K105" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N105">
         <v>1</v>
@@ -6584,40 +6628,40 @@
     </row>
     <row r="106" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A106">
-        <f t="shared" si="16"/>
-        <v>1030226</v>
+        <f t="shared" si="13"/>
+        <v>1030224</v>
       </c>
       <c r="B106" s="7">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C106">
-        <f t="shared" si="17"/>
-        <v>1300226</v>
+        <f t="shared" si="14"/>
+        <v>1300224</v>
       </c>
       <c r="D106" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H106">
         <v>1</v>
       </c>
       <c r="I106" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J106">
-        <f t="shared" si="15"/>
-        <v>2030226</v>
+        <f t="shared" si="12"/>
+        <v>2030224</v>
       </c>
       <c r="K106" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N106">
         <v>1</v>
@@ -6625,40 +6669,40 @@
     </row>
     <row r="107" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A107">
-        <f t="shared" si="16"/>
-        <v>1030227</v>
+        <f t="shared" si="13"/>
+        <v>1030225</v>
       </c>
       <c r="B107" s="7">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C107">
-        <f t="shared" si="17"/>
-        <v>1300227</v>
+        <f t="shared" si="14"/>
+        <v>1300225</v>
       </c>
       <c r="D107" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H107">
         <v>1</v>
       </c>
       <c r="I107" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J107">
-        <f t="shared" si="15"/>
-        <v>2030227</v>
+        <f t="shared" si="12"/>
+        <v>2030225</v>
       </c>
       <c r="K107" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -6666,40 +6710,40 @@
     </row>
     <row r="108" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A108">
-        <f t="shared" si="16"/>
-        <v>1030228</v>
+        <f t="shared" si="13"/>
+        <v>1030226</v>
       </c>
       <c r="B108" s="7">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C108">
-        <f t="shared" si="17"/>
-        <v>1300228</v>
+        <f t="shared" si="14"/>
+        <v>1300226</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E108">
         <v>3</v>
       </c>
       <c r="F108" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H108">
         <v>1</v>
       </c>
       <c r="I108" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J108">
-        <f t="shared" si="15"/>
-        <v>2030228</v>
+        <f t="shared" si="12"/>
+        <v>2030226</v>
       </c>
       <c r="K108" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -6707,40 +6751,40 @@
     </row>
     <row r="109" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A109">
-        <f t="shared" si="16"/>
-        <v>1030229</v>
+        <f t="shared" si="13"/>
+        <v>1030227</v>
       </c>
       <c r="B109" s="7">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C109">
-        <f t="shared" si="17"/>
-        <v>1300229</v>
+        <f t="shared" si="14"/>
+        <v>1300227</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E109">
         <v>3</v>
       </c>
       <c r="F109" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G109">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H109">
         <v>1</v>
       </c>
       <c r="I109" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J109">
-        <f t="shared" si="15"/>
-        <v>2030229</v>
+        <f t="shared" si="12"/>
+        <v>2030227</v>
       </c>
       <c r="K109" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N109">
         <v>1</v>
@@ -6748,40 +6792,40 @@
     </row>
     <row r="110" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A110">
-        <f t="shared" si="16"/>
-        <v>1030230</v>
+        <f t="shared" si="13"/>
+        <v>1030228</v>
       </c>
       <c r="B110" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C110">
-        <f t="shared" si="17"/>
-        <v>1300230</v>
+        <f t="shared" si="14"/>
+        <v>1300228</v>
       </c>
       <c r="D110" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E110">
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H110">
         <v>1</v>
       </c>
       <c r="I110" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J110">
-        <f t="shared" si="15"/>
-        <v>2030230</v>
+        <f t="shared" si="12"/>
+        <v>2030228</v>
       </c>
       <c r="K110" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -6789,40 +6833,40 @@
     </row>
     <row r="111" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A111">
-        <f t="shared" si="16"/>
-        <v>1030231</v>
+        <f t="shared" si="13"/>
+        <v>1030229</v>
       </c>
       <c r="B111" s="7">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C111">
-        <f t="shared" si="17"/>
-        <v>1300231</v>
+        <f t="shared" si="14"/>
+        <v>1300229</v>
       </c>
       <c r="D111" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E111">
         <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G111">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H111">
         <v>1</v>
       </c>
       <c r="I111" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J111">
-        <f t="shared" si="15"/>
-        <v>2030231</v>
+        <f t="shared" si="12"/>
+        <v>2030229</v>
       </c>
       <c r="K111" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N111">
         <v>1</v>
@@ -6830,40 +6874,40 @@
     </row>
     <row r="112" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A112">
-        <f t="shared" si="16"/>
-        <v>1030232</v>
+        <f t="shared" si="13"/>
+        <v>1030230</v>
       </c>
       <c r="B112" s="7">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C112">
-        <f t="shared" si="17"/>
-        <v>1300232</v>
+        <f t="shared" si="14"/>
+        <v>1300230</v>
       </c>
       <c r="D112" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E112">
         <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G112">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H112">
         <v>1</v>
       </c>
       <c r="I112" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J112">
-        <f t="shared" si="15"/>
-        <v>2030232</v>
+        <f t="shared" si="12"/>
+        <v>2030230</v>
       </c>
       <c r="K112" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N112">
         <v>1</v>
@@ -6871,40 +6915,40 @@
     </row>
     <row r="113" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A113">
-        <f t="shared" si="16"/>
-        <v>1030241</v>
+        <f t="shared" si="13"/>
+        <v>1030231</v>
       </c>
       <c r="B113" s="7">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C113">
-        <f t="shared" si="17"/>
-        <v>1300241</v>
+        <f t="shared" si="14"/>
+        <v>1300231</v>
       </c>
       <c r="D113" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E113">
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H113">
         <v>1</v>
       </c>
       <c r="I113" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J113">
-        <f t="shared" si="15"/>
-        <v>2030241</v>
+        <f t="shared" si="12"/>
+        <v>2030231</v>
       </c>
       <c r="K113" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N113">
         <v>1</v>
@@ -6912,40 +6956,40 @@
     </row>
     <row r="114" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A114">
-        <f t="shared" si="16"/>
-        <v>1030242</v>
+        <f t="shared" si="13"/>
+        <v>1030232</v>
       </c>
       <c r="B114" s="7">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C114">
-        <f t="shared" si="17"/>
-        <v>1300242</v>
+        <f t="shared" si="14"/>
+        <v>1300232</v>
       </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E114">
         <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H114">
         <v>1</v>
       </c>
       <c r="I114" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J114">
-        <f t="shared" si="15"/>
-        <v>2030242</v>
+        <f t="shared" si="12"/>
+        <v>2030232</v>
       </c>
       <c r="K114" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -6953,40 +6997,40 @@
     </row>
     <row r="115" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A115">
-        <f t="shared" si="16"/>
-        <v>1030243</v>
+        <f t="shared" si="13"/>
+        <v>1030241</v>
       </c>
       <c r="B115" s="7">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C115">
-        <f t="shared" si="17"/>
-        <v>1300243</v>
+        <f t="shared" si="14"/>
+        <v>1300241</v>
       </c>
       <c r="D115" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E115">
         <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115">
         <v>1</v>
       </c>
       <c r="I115" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J115">
-        <f t="shared" si="15"/>
-        <v>2030243</v>
+        <f t="shared" si="12"/>
+        <v>2030241</v>
       </c>
       <c r="K115" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N115">
         <v>1</v>
@@ -6994,40 +7038,40 @@
     </row>
     <row r="116" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A116">
-        <f t="shared" si="16"/>
-        <v>1030244</v>
+        <f t="shared" si="13"/>
+        <v>1030242</v>
       </c>
       <c r="B116" s="7">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C116">
-        <f t="shared" si="17"/>
-        <v>1300244</v>
+        <f t="shared" si="14"/>
+        <v>1300242</v>
       </c>
       <c r="D116" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E116">
         <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116">
         <v>1</v>
       </c>
       <c r="I116" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J116">
-        <f t="shared" si="15"/>
-        <v>2030244</v>
+        <f t="shared" si="12"/>
+        <v>2030242</v>
       </c>
       <c r="K116" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N116">
         <v>1</v>
@@ -7035,40 +7079,40 @@
     </row>
     <row r="117" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A117">
-        <f t="shared" si="16"/>
-        <v>1030245</v>
+        <f t="shared" si="13"/>
+        <v>1030243</v>
       </c>
       <c r="B117" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C117">
-        <f t="shared" si="17"/>
-        <v>1300245</v>
+        <f t="shared" si="14"/>
+        <v>1300243</v>
       </c>
       <c r="D117" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E117">
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H117">
         <v>1</v>
       </c>
       <c r="I117" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J117">
-        <f t="shared" si="15"/>
-        <v>2030245</v>
+        <f t="shared" si="12"/>
+        <v>2030243</v>
       </c>
       <c r="K117" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -7076,40 +7120,40 @@
     </row>
     <row r="118" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A118">
-        <f t="shared" si="16"/>
-        <v>1030246</v>
+        <f t="shared" si="13"/>
+        <v>1030244</v>
       </c>
       <c r="B118" s="7">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C118">
-        <f t="shared" si="17"/>
-        <v>1300246</v>
+        <f t="shared" si="14"/>
+        <v>1300244</v>
       </c>
       <c r="D118" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E118">
         <v>3</v>
       </c>
       <c r="F118" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H118">
         <v>1</v>
       </c>
       <c r="I118" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J118">
-        <f t="shared" si="15"/>
-        <v>2030246</v>
+        <f t="shared" si="12"/>
+        <v>2030244</v>
       </c>
       <c r="K118" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N118">
         <v>1</v>
@@ -7117,40 +7161,40 @@
     </row>
     <row r="119" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A119">
-        <f t="shared" si="16"/>
-        <v>1030247</v>
+        <f t="shared" si="13"/>
+        <v>1030245</v>
       </c>
       <c r="B119" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C119">
-        <f t="shared" si="17"/>
-        <v>1300247</v>
+        <f t="shared" si="14"/>
+        <v>1300245</v>
       </c>
       <c r="D119" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E119">
         <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G119">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H119">
         <v>1</v>
       </c>
       <c r="I119" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J119">
-        <f t="shared" si="15"/>
-        <v>2030247</v>
+        <f t="shared" si="12"/>
+        <v>2030245</v>
       </c>
       <c r="K119" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -7158,40 +7202,40 @@
     </row>
     <row r="120" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A120">
-        <f t="shared" si="16"/>
-        <v>1030248</v>
+        <f t="shared" si="13"/>
+        <v>1030246</v>
       </c>
       <c r="B120" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C120">
-        <f t="shared" si="17"/>
-        <v>1300248</v>
+        <f t="shared" si="14"/>
+        <v>1300246</v>
       </c>
       <c r="D120" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E120">
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G120">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H120">
         <v>1</v>
       </c>
       <c r="I120" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J120">
-        <f t="shared" si="15"/>
-        <v>2030248</v>
+        <f t="shared" si="12"/>
+        <v>2030246</v>
       </c>
       <c r="K120" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N120">
         <v>1</v>
@@ -7199,40 +7243,40 @@
     </row>
     <row r="121" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A121">
-        <f t="shared" si="16"/>
-        <v>1030249</v>
+        <f t="shared" si="13"/>
+        <v>1030247</v>
       </c>
       <c r="B121" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C121">
-        <f t="shared" si="17"/>
-        <v>1300249</v>
+        <f t="shared" si="14"/>
+        <v>1300247</v>
       </c>
       <c r="D121" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E121">
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H121">
         <v>1</v>
       </c>
       <c r="I121" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J121">
-        <f t="shared" si="15"/>
-        <v>2030249</v>
+        <f t="shared" si="12"/>
+        <v>2030247</v>
       </c>
       <c r="K121" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -7240,40 +7284,40 @@
     </row>
     <row r="122" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A122">
-        <f t="shared" si="16"/>
-        <v>1030250</v>
+        <f t="shared" si="13"/>
+        <v>1030248</v>
       </c>
       <c r="B122" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C122">
-        <f t="shared" si="17"/>
-        <v>1300250</v>
+        <f t="shared" si="14"/>
+        <v>1300248</v>
       </c>
       <c r="D122" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E122">
         <v>3</v>
       </c>
       <c r="F122" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G122">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H122">
         <v>1</v>
       </c>
       <c r="I122" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J122">
-        <f t="shared" si="15"/>
-        <v>2030250</v>
+        <f t="shared" si="12"/>
+        <v>2030248</v>
       </c>
       <c r="K122" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N122">
         <v>1</v>
@@ -7281,40 +7325,40 @@
     </row>
     <row r="123" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A123">
-        <f t="shared" si="16"/>
-        <v>1030251</v>
+        <f t="shared" si="13"/>
+        <v>1030249</v>
       </c>
       <c r="B123" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C123">
-        <f t="shared" si="17"/>
-        <v>1300251</v>
+        <f t="shared" si="14"/>
+        <v>1300249</v>
       </c>
       <c r="D123" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E123">
         <v>3</v>
       </c>
       <c r="F123" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G123">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H123">
         <v>1</v>
       </c>
       <c r="I123" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J123">
-        <f t="shared" si="15"/>
-        <v>2030251</v>
+        <f t="shared" si="12"/>
+        <v>2030249</v>
       </c>
       <c r="K123" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N123">
         <v>1</v>
@@ -7322,40 +7366,40 @@
     </row>
     <row r="124" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A124">
-        <f t="shared" si="16"/>
-        <v>1030252</v>
+        <f t="shared" si="13"/>
+        <v>1030250</v>
       </c>
       <c r="B124" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C124">
-        <f t="shared" si="17"/>
-        <v>1300252</v>
+        <f t="shared" si="14"/>
+        <v>1300250</v>
       </c>
       <c r="D124" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E124">
         <v>3</v>
       </c>
       <c r="F124" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G124">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H124">
         <v>1</v>
       </c>
       <c r="I124" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J124">
-        <f t="shared" si="15"/>
-        <v>2030252</v>
+        <f t="shared" si="12"/>
+        <v>2030250</v>
       </c>
       <c r="K124" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N124">
         <v>1</v>
@@ -7363,110 +7407,106 @@
     </row>
     <row r="125" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A125">
-        <f t="shared" si="16"/>
-        <v>1031001</v>
+        <f t="shared" si="13"/>
+        <v>1030251</v>
       </c>
       <c r="B125" s="7">
-        <v>1001</v>
+        <v>251</v>
       </c>
       <c r="C125">
-        <f t="shared" si="17"/>
-        <v>1301001</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>162</v>
+        <f t="shared" si="14"/>
+        <v>1300251</v>
+      </c>
+      <c r="D125" t="s">
+        <v>166</v>
       </c>
       <c r="E125">
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G125">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H125">
         <v>1</v>
       </c>
-      <c r="I125" t="str">
-        <f>"itemicon_"&amp;A125&amp;".png"</f>
-        <v>itemicon_1031001.png</v>
+      <c r="I125" t="s">
+        <v>71</v>
       </c>
       <c r="J125">
-        <f t="shared" si="15"/>
-        <v>2031001</v>
-      </c>
-      <c r="L125">
-        <v>2</v>
-      </c>
-      <c r="M125"/>
+        <f t="shared" si="12"/>
+        <v>2030251</v>
+      </c>
+      <c r="K125" t="s">
+        <v>72</v>
+      </c>
       <c r="N125">
         <v>1</v>
       </c>
     </row>
     <row r="126" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A126">
-        <f t="shared" si="16"/>
-        <v>1031002</v>
+        <f t="shared" si="13"/>
+        <v>1030252</v>
       </c>
       <c r="B126" s="7">
-        <v>1002</v>
+        <v>252</v>
       </c>
       <c r="C126">
-        <f t="shared" si="17"/>
-        <v>1301002</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>163</v>
+        <f t="shared" si="14"/>
+        <v>1300252</v>
+      </c>
+      <c r="D126" t="s">
+        <v>167</v>
       </c>
       <c r="E126">
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G126">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H126">
         <v>1</v>
       </c>
-      <c r="I126" t="str">
-        <f>"itemicon_"&amp;A126&amp;".png"</f>
-        <v>itemicon_1031002.png</v>
+      <c r="I126" t="s">
+        <v>71</v>
       </c>
       <c r="J126">
-        <f t="shared" si="15"/>
-        <v>2031002</v>
-      </c>
-      <c r="L126">
-        <v>3</v>
-      </c>
-      <c r="M126"/>
+        <f t="shared" si="12"/>
+        <v>2030252</v>
+      </c>
+      <c r="K126" t="s">
+        <v>72</v>
+      </c>
       <c r="N126">
         <v>1</v>
       </c>
     </row>
     <row r="127" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A127">
-        <f t="shared" si="16"/>
-        <v>1031201</v>
+        <f t="shared" si="13"/>
+        <v>1031001</v>
       </c>
       <c r="B127" s="7">
-        <v>1201</v>
+        <v>1001</v>
       </c>
       <c r="C127">
-        <f t="shared" si="17"/>
-        <v>1301201</v>
-      </c>
-      <c r="D127" t="s">
-        <v>164</v>
+        <f t="shared" si="14"/>
+        <v>1301001</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="E127">
         <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -7476,14 +7516,14 @@
       </c>
       <c r="I127" t="str">
         <f>"itemicon_"&amp;A127&amp;".png"</f>
-        <v>itemicon_1031201.png</v>
+        <v>itemicon_1031001.png</v>
       </c>
       <c r="J127">
-        <f t="shared" si="15"/>
-        <v>2031201</v>
+        <f t="shared" si="12"/>
+        <v>2031001</v>
       </c>
       <c r="L127">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="M127"/>
       <c r="N127">
@@ -7492,24 +7532,24 @@
     </row>
     <row r="128" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A128">
-        <f t="shared" si="16"/>
-        <v>1031202</v>
+        <f t="shared" si="13"/>
+        <v>1031002</v>
       </c>
       <c r="B128" s="7">
-        <v>1202</v>
+        <v>1002</v>
       </c>
       <c r="C128">
-        <f t="shared" si="17"/>
-        <v>1301202</v>
-      </c>
-      <c r="D128" t="s">
-        <v>165</v>
+        <f t="shared" si="14"/>
+        <v>1301002</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="E128">
         <v>3</v>
       </c>
       <c r="F128" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -7519,14 +7559,14 @@
       </c>
       <c r="I128" t="str">
         <f>"itemicon_"&amp;A128&amp;".png"</f>
-        <v>itemicon_1031202.png</v>
+        <v>itemicon_1031002.png</v>
       </c>
       <c r="J128">
-        <f t="shared" si="15"/>
-        <v>2031202</v>
+        <f t="shared" si="12"/>
+        <v>2031002</v>
       </c>
       <c r="L128">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="M128"/>
       <c r="N128">
@@ -7535,23 +7575,24 @@
     </row>
     <row r="129" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A129">
-        <f t="shared" si="16"/>
-        <v>1031350</v>
+        <f t="shared" si="13"/>
+        <v>1031201</v>
       </c>
       <c r="B129" s="7">
-        <v>1350</v>
+        <v>1201</v>
       </c>
       <c r="C129">
-        <v>101801</v>
+        <f t="shared" si="14"/>
+        <v>1301201</v>
       </c>
       <c r="D129" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E129">
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -7559,38 +7600,42 @@
       <c r="H129">
         <v>1</v>
       </c>
-      <c r="I129" t="s">
-        <v>167</v>
+      <c r="I129" t="str">
+        <f>"itemicon_"&amp;A129&amp;".png"</f>
+        <v>itemicon_1031201.png</v>
       </c>
       <c r="J129">
-        <v>201801</v>
+        <f t="shared" si="12"/>
+        <v>2031201</v>
       </c>
       <c r="L129">
-        <v>1801</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="M129"/>
       <c r="N129">
         <v>1</v>
       </c>
     </row>
     <row r="130" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A130">
-        <f t="shared" si="16"/>
-        <v>1031351</v>
+        <f t="shared" si="13"/>
+        <v>1031202</v>
       </c>
       <c r="B130" s="7">
-        <v>1351</v>
+        <v>1202</v>
       </c>
       <c r="C130">
-        <v>101802</v>
+        <f t="shared" si="14"/>
+        <v>1301202</v>
       </c>
       <c r="D130" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E130">
         <v>3</v>
       </c>
       <c r="F130" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -7598,39 +7643,41 @@
       <c r="H130">
         <v>1</v>
       </c>
-      <c r="I130" t="s">
-        <v>169</v>
+      <c r="I130" t="str">
+        <f>"itemicon_"&amp;A130&amp;".png"</f>
+        <v>itemicon_1031202.png</v>
       </c>
       <c r="J130">
-        <v>201802</v>
+        <f t="shared" si="12"/>
+        <v>2031202</v>
       </c>
       <c r="L130">
-        <v>1802</v>
-      </c>
+        <v>1003</v>
+      </c>
+      <c r="M130"/>
       <c r="N130">
         <v>1</v>
       </c>
     </row>
     <row r="131" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A131">
-        <f t="shared" ref="A131:A144" si="18">1000000+E131*10000+B131</f>
-        <v>1021401</v>
+        <f t="shared" si="13"/>
+        <v>1031350</v>
       </c>
       <c r="B131" s="7">
-        <v>1401</v>
+        <v>1350</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:C144" si="19">1000000+E131*100000+B131</f>
-        <v>1201401</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>170</v>
+        <v>101801</v>
+      </c>
+      <c r="D131" t="s">
+        <v>172</v>
       </c>
       <c r="E131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -7638,42 +7685,38 @@
       <c r="H131">
         <v>1</v>
       </c>
-      <c r="I131" t="str">
-        <f t="shared" ref="I131:I144" si="20">"itemicon_"&amp;A131&amp;".png"</f>
-        <v>itemicon_1021401.png</v>
+      <c r="I131" t="s">
+        <v>173</v>
       </c>
       <c r="J131">
-        <f t="shared" ref="J131:J144" si="21">2000000+E131*10000+B131</f>
-        <v>2021401</v>
+        <v>201801</v>
       </c>
       <c r="L131">
-        <v>2002</v>
-      </c>
-      <c r="M131"/>
+        <v>1801</v>
+      </c>
       <c r="N131">
         <v>1</v>
       </c>
     </row>
     <row r="132" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A132">
-        <f t="shared" si="18"/>
-        <v>1021402</v>
+        <f t="shared" si="13"/>
+        <v>1031351</v>
       </c>
       <c r="B132" s="7">
-        <v>1402</v>
+        <v>1351</v>
       </c>
       <c r="C132">
-        <f t="shared" si="19"/>
-        <v>1201402</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>171</v>
+        <v>101802</v>
+      </c>
+      <c r="D132" t="s">
+        <v>174</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -7681,42 +7724,39 @@
       <c r="H132">
         <v>1</v>
       </c>
-      <c r="I132" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1021402.png</v>
+      <c r="I132" t="s">
+        <v>175</v>
       </c>
       <c r="J132">
-        <f t="shared" si="21"/>
-        <v>2021402</v>
+        <v>201802</v>
       </c>
       <c r="L132">
-        <v>2003</v>
-      </c>
-      <c r="M132"/>
+        <v>1802</v>
+      </c>
       <c r="N132">
         <v>1</v>
       </c>
     </row>
     <row r="133" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A133">
-        <f t="shared" si="18"/>
-        <v>1031601</v>
+        <f t="shared" ref="A133:A146" si="15">1000000+E133*10000+B133</f>
+        <v>1021401</v>
       </c>
       <c r="B133" s="7">
-        <v>1601</v>
+        <v>1401</v>
       </c>
       <c r="C133">
-        <f t="shared" si="19"/>
-        <v>1301601</v>
-      </c>
-      <c r="D133" s="11" t="s">
-        <v>172</v>
+        <f t="shared" ref="C133:C146" si="16">1000000+E133*100000+B133</f>
+        <v>1201401</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>176</v>
       </c>
       <c r="E133">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -7725,15 +7765,15 @@
         <v>1</v>
       </c>
       <c r="I133" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1031601.png</v>
+        <f t="shared" ref="I133:I146" si="17">"itemicon_"&amp;A133&amp;".png"</f>
+        <v>itemicon_1021401.png</v>
       </c>
       <c r="J133">
-        <f t="shared" si="21"/>
-        <v>2031601</v>
+        <f t="shared" ref="J133:J146" si="18">2000000+E133*10000+B133</f>
+        <v>2021401</v>
       </c>
       <c r="L133">
-        <v>3002</v>
+        <v>2002</v>
       </c>
       <c r="M133"/>
       <c r="N133">
@@ -7742,41 +7782,41 @@
     </row>
     <row r="134" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A134">
+        <f t="shared" si="15"/>
+        <v>1021402</v>
+      </c>
+      <c r="B134" s="7">
+        <v>1402</v>
+      </c>
+      <c r="C134">
+        <f t="shared" si="16"/>
+        <v>1201402</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
+      <c r="F134" t="s">
+        <v>53</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1021402.png</v>
+      </c>
+      <c r="J134">
         <f t="shared" si="18"/>
-        <v>1031602</v>
-      </c>
-      <c r="B134" s="7">
-        <v>1602</v>
-      </c>
-      <c r="C134">
-        <f t="shared" si="19"/>
-        <v>1301602</v>
-      </c>
-      <c r="D134" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E134">
-        <v>3</v>
-      </c>
-      <c r="F134" t="s">
-        <v>47</v>
-      </c>
-      <c r="G134">
-        <v>1</v>
-      </c>
-      <c r="H134">
-        <v>1</v>
-      </c>
-      <c r="I134" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1031602.png</v>
-      </c>
-      <c r="J134">
-        <f t="shared" si="21"/>
-        <v>2031602</v>
+        <v>2021402</v>
       </c>
       <c r="L134">
-        <v>3003</v>
+        <v>2003</v>
       </c>
       <c r="M134"/>
       <c r="N134">
@@ -7785,41 +7825,41 @@
     </row>
     <row r="135" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A135">
+        <f t="shared" si="15"/>
+        <v>1031601</v>
+      </c>
+      <c r="B135" s="7">
+        <v>1601</v>
+      </c>
+      <c r="C135">
+        <f t="shared" si="16"/>
+        <v>1301601</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E135">
+        <v>3</v>
+      </c>
+      <c r="F135" t="s">
+        <v>53</v>
+      </c>
+      <c r="G135">
+        <v>1</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1031601.png</v>
+      </c>
+      <c r="J135">
         <f t="shared" si="18"/>
-        <v>1031801</v>
-      </c>
-      <c r="B135" s="7">
-        <v>1801</v>
-      </c>
-      <c r="C135">
-        <f t="shared" si="19"/>
-        <v>1301801</v>
-      </c>
-      <c r="D135" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E135">
-        <v>3</v>
-      </c>
-      <c r="F135" t="s">
-        <v>47</v>
-      </c>
-      <c r="G135">
-        <v>1</v>
-      </c>
-      <c r="H135">
-        <v>1</v>
-      </c>
-      <c r="I135" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1031801.png</v>
-      </c>
-      <c r="J135">
-        <f t="shared" si="21"/>
-        <v>2031801</v>
+        <v>2031601</v>
       </c>
       <c r="L135">
-        <v>4002</v>
+        <v>3002</v>
       </c>
       <c r="M135"/>
       <c r="N135">
@@ -7828,41 +7868,41 @@
     </row>
     <row r="136" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A136">
+        <f t="shared" si="15"/>
+        <v>1031602</v>
+      </c>
+      <c r="B136" s="7">
+        <v>1602</v>
+      </c>
+      <c r="C136">
+        <f t="shared" si="16"/>
+        <v>1301602</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E136">
+        <v>3</v>
+      </c>
+      <c r="F136" t="s">
+        <v>53</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1031602.png</v>
+      </c>
+      <c r="J136">
         <f t="shared" si="18"/>
-        <v>1031802</v>
-      </c>
-      <c r="B136" s="7">
-        <v>1802</v>
-      </c>
-      <c r="C136">
-        <f t="shared" si="19"/>
-        <v>1301802</v>
-      </c>
-      <c r="D136" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="E136">
-        <v>3</v>
-      </c>
-      <c r="F136" t="s">
-        <v>47</v>
-      </c>
-      <c r="G136">
-        <v>1</v>
-      </c>
-      <c r="H136">
-        <v>1</v>
-      </c>
-      <c r="I136" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1031802.png</v>
-      </c>
-      <c r="J136">
-        <f t="shared" si="21"/>
-        <v>2031802</v>
+        <v>2031602</v>
       </c>
       <c r="L136">
-        <v>4003</v>
+        <v>3003</v>
       </c>
       <c r="M136"/>
       <c r="N136">
@@ -7871,41 +7911,41 @@
     </row>
     <row r="137" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A137">
+        <f t="shared" si="15"/>
+        <v>1031801</v>
+      </c>
+      <c r="B137" s="7">
+        <v>1801</v>
+      </c>
+      <c r="C137">
+        <f t="shared" si="16"/>
+        <v>1301801</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E137">
+        <v>3</v>
+      </c>
+      <c r="F137" t="s">
+        <v>53</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1031801.png</v>
+      </c>
+      <c r="J137">
         <f t="shared" si="18"/>
-        <v>1032001</v>
-      </c>
-      <c r="B137" s="7">
-        <v>2001</v>
-      </c>
-      <c r="C137">
-        <f t="shared" si="19"/>
-        <v>1302001</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="E137">
-        <v>3</v>
-      </c>
-      <c r="F137" t="s">
-        <v>47</v>
-      </c>
-      <c r="G137">
-        <v>1</v>
-      </c>
-      <c r="H137">
-        <v>1</v>
-      </c>
-      <c r="I137" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1032001.png</v>
-      </c>
-      <c r="J137">
-        <f t="shared" si="21"/>
-        <v>2032001</v>
+        <v>2031801</v>
       </c>
       <c r="L137">
-        <v>5002</v>
+        <v>4002</v>
       </c>
       <c r="M137"/>
       <c r="N137">
@@ -7914,41 +7954,41 @@
     </row>
     <row r="138" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A138">
+        <f t="shared" si="15"/>
+        <v>1031802</v>
+      </c>
+      <c r="B138" s="7">
+        <v>1802</v>
+      </c>
+      <c r="C138">
+        <f t="shared" si="16"/>
+        <v>1301802</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E138">
+        <v>3</v>
+      </c>
+      <c r="F138" t="s">
+        <v>53</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1031802.png</v>
+      </c>
+      <c r="J138">
         <f t="shared" si="18"/>
-        <v>1032002</v>
-      </c>
-      <c r="B138" s="7">
-        <v>2002</v>
-      </c>
-      <c r="C138">
-        <f t="shared" si="19"/>
-        <v>1302002</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E138">
-        <v>3</v>
-      </c>
-      <c r="F138" t="s">
-        <v>47</v>
-      </c>
-      <c r="G138">
-        <v>1</v>
-      </c>
-      <c r="H138">
-        <v>1</v>
-      </c>
-      <c r="I138" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1032002.png</v>
-      </c>
-      <c r="J138">
-        <f t="shared" si="21"/>
-        <v>2032002</v>
+        <v>2031802</v>
       </c>
       <c r="L138">
-        <v>5003</v>
+        <v>4003</v>
       </c>
       <c r="M138"/>
       <c r="N138">
@@ -7957,41 +7997,41 @@
     </row>
     <row r="139" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A139">
+        <f t="shared" si="15"/>
+        <v>1032001</v>
+      </c>
+      <c r="B139" s="7">
+        <v>2001</v>
+      </c>
+      <c r="C139">
+        <f t="shared" si="16"/>
+        <v>1302001</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E139">
+        <v>3</v>
+      </c>
+      <c r="F139" t="s">
+        <v>53</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1032001.png</v>
+      </c>
+      <c r="J139">
         <f t="shared" si="18"/>
-        <v>1032201</v>
-      </c>
-      <c r="B139" s="7">
-        <v>2201</v>
-      </c>
-      <c r="C139">
-        <f t="shared" si="19"/>
-        <v>1302201</v>
-      </c>
-      <c r="D139" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="E139">
-        <v>3</v>
-      </c>
-      <c r="F139" t="s">
-        <v>47</v>
-      </c>
-      <c r="G139">
-        <v>1</v>
-      </c>
-      <c r="H139">
-        <v>1</v>
-      </c>
-      <c r="I139" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1032201.png</v>
-      </c>
-      <c r="J139">
-        <f t="shared" si="21"/>
-        <v>2032201</v>
+        <v>2032001</v>
       </c>
       <c r="L139">
-        <v>6002</v>
+        <v>5002</v>
       </c>
       <c r="M139"/>
       <c r="N139">
@@ -8000,151 +8040,153 @@
     </row>
     <row r="140" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A140">
+        <f t="shared" si="15"/>
+        <v>1032002</v>
+      </c>
+      <c r="B140" s="7">
+        <v>2002</v>
+      </c>
+      <c r="C140">
+        <f t="shared" si="16"/>
+        <v>1302002</v>
+      </c>
+      <c r="D140" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E140">
+        <v>3</v>
+      </c>
+      <c r="F140" t="s">
+        <v>53</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1032002.png</v>
+      </c>
+      <c r="J140">
         <f t="shared" si="18"/>
-        <v>1032202</v>
-      </c>
-      <c r="B140" s="7">
-        <v>2202</v>
-      </c>
-      <c r="C140">
-        <f t="shared" si="19"/>
-        <v>1302202</v>
-      </c>
-      <c r="D140" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="E140">
-        <v>3</v>
-      </c>
-      <c r="F140" t="s">
-        <v>47</v>
-      </c>
-      <c r="G140">
-        <v>1</v>
-      </c>
-      <c r="H140">
-        <v>1</v>
-      </c>
-      <c r="I140" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1032202.png</v>
-      </c>
-      <c r="J140">
-        <f t="shared" si="21"/>
-        <v>2032202</v>
+        <v>2032002</v>
       </c>
       <c r="L140">
-        <v>6003</v>
+        <v>5003</v>
       </c>
       <c r="M140"/>
       <c r="N140">
         <v>1</v>
       </c>
     </row>
-    <row r="141" ht="18" customHeight="1" spans="1:14">
+    <row r="141" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A141">
+        <f t="shared" si="15"/>
+        <v>1032201</v>
+      </c>
+      <c r="B141" s="7">
+        <v>2201</v>
+      </c>
+      <c r="C141">
+        <f t="shared" si="16"/>
+        <v>1302201</v>
+      </c>
+      <c r="D141" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E141">
+        <v>3</v>
+      </c>
+      <c r="F141" t="s">
+        <v>53</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1032201.png</v>
+      </c>
+      <c r="J141">
         <f t="shared" si="18"/>
+        <v>2032201</v>
+      </c>
+      <c r="L141">
+        <v>6002</v>
+      </c>
+      <c r="M141"/>
+      <c r="N141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" customFormat="1" ht="23" customHeight="1" spans="1:14">
+      <c r="A142">
+        <f t="shared" si="15"/>
+        <v>1032202</v>
+      </c>
+      <c r="B142" s="7">
+        <v>2202</v>
+      </c>
+      <c r="C142">
+        <f t="shared" si="16"/>
+        <v>1302202</v>
+      </c>
+      <c r="D142" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E142">
+        <v>3</v>
+      </c>
+      <c r="F142" t="s">
+        <v>53</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="I142" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1032202.png</v>
+      </c>
+      <c r="J142">
+        <f t="shared" si="18"/>
+        <v>2032202</v>
+      </c>
+      <c r="L142">
+        <v>6003</v>
+      </c>
+      <c r="M142"/>
+      <c r="N142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1" spans="1:14">
+      <c r="A143">
+        <f t="shared" si="15"/>
         <v>1022501</v>
       </c>
-      <c r="B141">
+      <c r="B143">
         <v>2501</v>
       </c>
-      <c r="C141">
-        <f t="shared" si="19"/>
+      <c r="C143">
+        <f t="shared" si="16"/>
         <v>1202501</v>
       </c>
-      <c r="D141" t="s">
-        <v>180</v>
-      </c>
-      <c r="E141">
-        <v>2</v>
-      </c>
-      <c r="F141" t="s">
-        <v>47</v>
-      </c>
-      <c r="G141">
-        <v>1</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1022501.png</v>
-      </c>
-      <c r="J141">
-        <f t="shared" si="21"/>
-        <v>2022501</v>
-      </c>
-      <c r="K141" t="s">
-        <v>181</v>
-      </c>
-      <c r="N141">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="142" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A142">
-        <f t="shared" si="18"/>
-        <v>1022502</v>
-      </c>
-      <c r="B142">
-        <v>2502</v>
-      </c>
-      <c r="C142">
-        <f t="shared" si="19"/>
-        <v>1202502</v>
-      </c>
-      <c r="D142" t="s">
-        <v>182</v>
-      </c>
-      <c r="E142">
-        <v>2</v>
-      </c>
-      <c r="F142" t="s">
-        <v>47</v>
-      </c>
-      <c r="G142">
-        <v>1</v>
-      </c>
-      <c r="H142">
-        <v>0</v>
-      </c>
-      <c r="I142" t="str">
-        <f>"itemicon_"&amp;A142&amp;".png"</f>
-        <v>itemicon_1022502.png</v>
-      </c>
-      <c r="J142">
-        <f t="shared" si="21"/>
-        <v>2022502</v>
-      </c>
-      <c r="K142" t="s">
-        <v>183</v>
-      </c>
-      <c r="N142">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="143" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A143">
-        <f t="shared" si="18"/>
-        <v>1022503</v>
-      </c>
-      <c r="B143">
-        <v>2503</v>
-      </c>
-      <c r="C143">
-        <f t="shared" si="19"/>
-        <v>1202503</v>
-      </c>
       <c r="D143" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E143">
         <v>2</v>
       </c>
       <c r="F143" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -8153,40 +8195,40 @@
         <v>0</v>
       </c>
       <c r="I143" t="str">
-        <f>"itemicon_"&amp;A143&amp;".png"</f>
-        <v>itemicon_1022503.png</v>
+        <f t="shared" si="17"/>
+        <v>itemicon_1022501.png</v>
       </c>
       <c r="J143">
-        <f t="shared" si="21"/>
-        <v>2022503</v>
+        <f t="shared" si="18"/>
+        <v>2022501</v>
       </c>
       <c r="K143" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="N143">
         <v>999</v>
       </c>
     </row>
-    <row r="144" customFormat="1" ht="18" customHeight="1" spans="1:14">
+    <row r="144" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A144">
-        <f t="shared" si="18"/>
-        <v>1022504</v>
+        <f t="shared" si="15"/>
+        <v>1022502</v>
       </c>
       <c r="B144">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="C144">
-        <f t="shared" si="19"/>
-        <v>1202504</v>
+        <f t="shared" si="16"/>
+        <v>1202502</v>
       </c>
       <c r="D144" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E144">
         <v>2</v>
       </c>
       <c r="F144" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -8195,48 +8237,57 @@
         <v>0</v>
       </c>
       <c r="I144" t="str">
-        <f>"itemicon_"&amp;A144&amp;".png"</f>
-        <v>itemicon_1022504.png</v>
+        <f t="shared" si="17"/>
+        <v>itemicon_1022502.png</v>
       </c>
       <c r="J144">
-        <f t="shared" si="21"/>
-        <v>2022504</v>
+        <f t="shared" si="18"/>
+        <v>2022502</v>
       </c>
       <c r="K144" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="N144">
-        <v>999999999</v>
-      </c>
-    </row>
-    <row r="145" customFormat="1" ht="21" customHeight="1" spans="1:14">
+        <v>999</v>
+      </c>
+      <c r="Q144">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="145" customFormat="1" ht="18" customHeight="1" spans="1:14">
       <c r="A145">
-        <v>1023001</v>
-      </c>
-      <c r="B145" s="7"/>
+        <f t="shared" si="15"/>
+        <v>1022503</v>
+      </c>
+      <c r="B145">
+        <v>2503</v>
+      </c>
       <c r="C145">
-        <v>1023001</v>
+        <f t="shared" si="16"/>
+        <v>1202503</v>
       </c>
       <c r="D145" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E145">
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
-      <c r="I145" t="s">
-        <v>188</v>
+      <c r="I145" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1022503.png</v>
       </c>
       <c r="J145">
-        <v>2023001</v>
+        <f t="shared" si="18"/>
+        <v>2022503</v>
       </c>
       <c r="K145" t="s">
         <v>189</v>
@@ -8245,73 +8296,79 @@
         <v>999</v>
       </c>
     </row>
-    <row r="146" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="146" customFormat="1" ht="18" customHeight="1" spans="1:14">
       <c r="A146">
-        <v>1023002</v>
-      </c>
-      <c r="B146" s="7"/>
+        <f t="shared" si="15"/>
+        <v>1022504</v>
+      </c>
+      <c r="B146">
+        <v>2504</v>
+      </c>
       <c r="C146">
-        <v>1023002</v>
+        <f t="shared" si="16"/>
+        <v>1202504</v>
       </c>
       <c r="D146" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E146">
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H146">
         <v>0</v>
       </c>
-      <c r="I146" t="s">
-        <v>191</v>
+      <c r="I146" t="str">
+        <f t="shared" si="17"/>
+        <v>itemicon_1022504.png</v>
       </c>
       <c r="J146">
-        <v>2023002</v>
+        <f t="shared" si="18"/>
+        <v>2022504</v>
       </c>
       <c r="K146" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N146">
-        <v>999</v>
+        <v>999999999</v>
       </c>
     </row>
     <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A147">
-        <v>1023003</v>
+        <v>1023001</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147">
-        <v>1023003</v>
+        <v>1023001</v>
       </c>
       <c r="D147" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J147">
-        <v>2023003</v>
+        <v>2023001</v>
       </c>
       <c r="K147" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="N147">
         <v>999</v>
@@ -8319,35 +8376,35 @@
     </row>
     <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A148">
-        <v>1023004</v>
+        <v>1023002</v>
       </c>
       <c r="B148" s="7"/>
       <c r="C148">
-        <v>1023004</v>
+        <v>1023002</v>
       </c>
       <c r="D148" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E148">
         <v>2</v>
       </c>
       <c r="F148" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G148">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148" t="s">
+        <v>197</v>
+      </c>
+      <c r="J148">
+        <v>2023002</v>
+      </c>
+      <c r="K148" t="s">
         <v>195</v>
-      </c>
-      <c r="J148">
-        <v>2023004</v>
-      </c>
-      <c r="K148" t="s">
-        <v>189</v>
       </c>
       <c r="N148">
         <v>999</v>
@@ -8355,35 +8412,35 @@
     </row>
     <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A149">
-        <v>1023005</v>
+        <v>1023003</v>
       </c>
       <c r="B149" s="7"/>
       <c r="C149">
-        <v>1023005</v>
+        <v>1023003</v>
       </c>
       <c r="D149" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E149">
         <v>2</v>
       </c>
       <c r="F149" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G149">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J149">
-        <v>2023005</v>
+        <v>2023003</v>
       </c>
       <c r="K149" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="N149">
         <v>999</v>
@@ -8391,35 +8448,35 @@
     </row>
     <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A150">
-        <v>1023101</v>
+        <v>1023004</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150">
-        <v>1023101</v>
+        <v>1023004</v>
       </c>
       <c r="D150" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E150">
         <v>2</v>
       </c>
       <c r="F150" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G150">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J150">
-        <v>2023101</v>
+        <v>2023004</v>
       </c>
       <c r="K150" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N150">
         <v>999</v>
@@ -8427,35 +8484,35 @@
     </row>
     <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A151">
-        <v>1023102</v>
+        <v>1023005</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151">
-        <v>1023102</v>
+        <v>1023005</v>
       </c>
       <c r="D151" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E151">
         <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G151">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J151">
-        <v>2023102</v>
+        <v>2023005</v>
       </c>
       <c r="K151" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N151">
         <v>999</v>
@@ -8463,35 +8520,35 @@
     </row>
     <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A152">
-        <v>1023103</v>
+        <v>1023101</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152">
-        <v>1023103</v>
+        <v>1023101</v>
       </c>
       <c r="D152" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E152">
         <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G152">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H152">
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J152">
-        <v>2023103</v>
+        <v>2023101</v>
       </c>
       <c r="K152" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N152">
         <v>999</v>
@@ -8499,35 +8556,35 @@
     </row>
     <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A153">
-        <v>1023104</v>
+        <v>1023102</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153">
-        <v>1023104</v>
+        <v>1023102</v>
       </c>
       <c r="D153" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E153">
         <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G153">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H153">
         <v>0</v>
       </c>
       <c r="I153" t="s">
+        <v>208</v>
+      </c>
+      <c r="J153">
+        <v>2023102</v>
+      </c>
+      <c r="K153" t="s">
         <v>206</v>
-      </c>
-      <c r="J153">
-        <v>2023104</v>
-      </c>
-      <c r="K153" t="s">
-        <v>200</v>
       </c>
       <c r="N153">
         <v>999</v>
@@ -8535,35 +8592,35 @@
     </row>
     <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A154">
-        <v>1023105</v>
+        <v>1023103</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154">
-        <v>1023105</v>
+        <v>1023103</v>
       </c>
       <c r="D154" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E154">
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G154">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H154">
         <v>0</v>
       </c>
       <c r="I154" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J154">
-        <v>2023105</v>
+        <v>2023103</v>
       </c>
       <c r="K154" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N154">
         <v>999</v>
@@ -8571,35 +8628,35 @@
     </row>
     <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A155">
-        <v>1023201</v>
+        <v>1023104</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155">
-        <v>1023201</v>
+        <v>1023104</v>
       </c>
       <c r="D155" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E155">
         <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J155">
-        <v>2023201</v>
+        <v>2023104</v>
       </c>
       <c r="K155" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="N155">
         <v>999</v>
@@ -8607,35 +8664,35 @@
     </row>
     <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A156">
-        <v>1023202</v>
+        <v>1023105</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156">
-        <v>1023202</v>
+        <v>1023105</v>
       </c>
       <c r="D156" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E156">
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G156">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H156">
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J156">
-        <v>2023202</v>
+        <v>2023105</v>
       </c>
       <c r="K156" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="N156">
         <v>999</v>
@@ -8643,35 +8700,35 @@
     </row>
     <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A157">
-        <v>1023203</v>
+        <v>1023201</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157">
-        <v>1023203</v>
+        <v>1023201</v>
       </c>
       <c r="D157" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E157">
         <v>2</v>
       </c>
       <c r="F157" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G157">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H157">
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J157">
-        <v>2023203</v>
+        <v>2023201</v>
       </c>
       <c r="K157" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="N157">
         <v>999</v>
@@ -8679,35 +8736,35 @@
     </row>
     <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A158">
-        <v>1023204</v>
+        <v>1023202</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158">
-        <v>1023204</v>
+        <v>1023202</v>
       </c>
       <c r="D158" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E158">
         <v>2</v>
       </c>
       <c r="F158" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G158">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H158">
         <v>0</v>
       </c>
       <c r="I158" t="s">
+        <v>219</v>
+      </c>
+      <c r="J158">
+        <v>2023202</v>
+      </c>
+      <c r="K158" t="s">
         <v>217</v>
-      </c>
-      <c r="J158">
-        <v>2023204</v>
-      </c>
-      <c r="K158" t="s">
-        <v>211</v>
       </c>
       <c r="N158">
         <v>999</v>
@@ -8715,35 +8772,35 @@
     </row>
     <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A159">
-        <v>1023205</v>
+        <v>1023203</v>
       </c>
       <c r="B159" s="7"/>
       <c r="C159">
-        <v>1023205</v>
+        <v>1023203</v>
       </c>
       <c r="D159" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E159">
         <v>2</v>
       </c>
       <c r="F159" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G159">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H159">
         <v>0</v>
       </c>
       <c r="I159" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J159">
-        <v>2023205</v>
+        <v>2023203</v>
       </c>
       <c r="K159" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="N159">
         <v>999</v>
@@ -8751,35 +8808,35 @@
     </row>
     <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A160">
-        <v>1023301</v>
+        <v>1023204</v>
       </c>
       <c r="B160" s="7"/>
       <c r="C160">
-        <v>1023301</v>
+        <v>1023204</v>
       </c>
       <c r="D160" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E160">
         <v>2</v>
       </c>
       <c r="F160" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G160">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H160">
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J160">
-        <v>2023301</v>
+        <v>2023204</v>
       </c>
       <c r="K160" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N160">
         <v>999</v>
@@ -8787,35 +8844,35 @@
     </row>
     <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A161">
-        <v>1023302</v>
+        <v>1023205</v>
       </c>
       <c r="B161" s="7"/>
       <c r="C161">
-        <v>1023302</v>
+        <v>1023205</v>
       </c>
       <c r="D161" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E161">
         <v>2</v>
       </c>
       <c r="F161" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G161">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H161">
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J161">
-        <v>2023302</v>
+        <v>2023205</v>
       </c>
       <c r="K161" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N161">
         <v>999</v>
@@ -8823,35 +8880,35 @@
     </row>
     <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A162">
-        <v>1023303</v>
+        <v>1023301</v>
       </c>
       <c r="B162" s="7"/>
       <c r="C162">
-        <v>1023303</v>
+        <v>1023301</v>
       </c>
       <c r="D162" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E162">
         <v>2</v>
       </c>
       <c r="F162" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G162">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H162">
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J162">
-        <v>2023303</v>
+        <v>2023301</v>
       </c>
       <c r="K162" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N162">
         <v>999</v>
@@ -8859,35 +8916,35 @@
     </row>
     <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A163">
-        <v>1023304</v>
+        <v>1023302</v>
       </c>
       <c r="B163" s="7"/>
       <c r="C163">
-        <v>1023304</v>
+        <v>1023302</v>
       </c>
       <c r="D163" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E163">
         <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G163">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H163">
         <v>0</v>
       </c>
       <c r="I163" t="s">
+        <v>230</v>
+      </c>
+      <c r="J163">
+        <v>2023302</v>
+      </c>
+      <c r="K163" t="s">
         <v>228</v>
-      </c>
-      <c r="J163">
-        <v>2023304</v>
-      </c>
-      <c r="K163" t="s">
-        <v>222</v>
       </c>
       <c r="N163">
         <v>999</v>
@@ -8895,35 +8952,35 @@
     </row>
     <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A164">
-        <v>1023305</v>
+        <v>1023303</v>
       </c>
       <c r="B164" s="7"/>
       <c r="C164">
-        <v>1023305</v>
+        <v>1023303</v>
       </c>
       <c r="D164" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E164">
         <v>2</v>
       </c>
       <c r="F164" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G164">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H164">
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J164">
-        <v>2023305</v>
+        <v>2023303</v>
       </c>
       <c r="K164" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N164">
         <v>999</v>
@@ -8931,35 +8988,35 @@
     </row>
     <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A165">
-        <v>1023401</v>
+        <v>1023304</v>
       </c>
       <c r="B165" s="7"/>
       <c r="C165">
-        <v>1023401</v>
+        <v>1023304</v>
       </c>
       <c r="D165" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E165">
         <v>2</v>
       </c>
       <c r="F165" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G165">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H165">
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J165">
-        <v>2023401</v>
+        <v>2023304</v>
       </c>
       <c r="K165" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N165">
         <v>999</v>
@@ -8967,35 +9024,35 @@
     </row>
     <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A166">
-        <v>1023402</v>
+        <v>1023305</v>
       </c>
       <c r="B166" s="7"/>
       <c r="C166">
-        <v>1023402</v>
+        <v>1023305</v>
       </c>
       <c r="D166" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E166">
         <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G166">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H166">
         <v>0</v>
       </c>
       <c r="I166" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J166">
-        <v>2023402</v>
+        <v>2023305</v>
       </c>
       <c r="K166" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N166">
         <v>999</v>
@@ -9003,35 +9060,35 @@
     </row>
     <row r="167" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A167">
-        <v>1023403</v>
+        <v>1023401</v>
       </c>
       <c r="B167" s="7"/>
       <c r="C167">
-        <v>1023403</v>
+        <v>1023401</v>
       </c>
       <c r="D167" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E167">
         <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G167">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H167">
         <v>0</v>
       </c>
       <c r="I167" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J167">
-        <v>2023403</v>
+        <v>2023401</v>
       </c>
       <c r="K167" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N167">
         <v>999</v>
@@ -9039,35 +9096,35 @@
     </row>
     <row r="168" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A168">
-        <v>1023404</v>
+        <v>1023402</v>
       </c>
       <c r="B168" s="7"/>
       <c r="C168">
-        <v>1023404</v>
+        <v>1023402</v>
       </c>
       <c r="D168" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E168">
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G168">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H168">
         <v>0</v>
       </c>
       <c r="I168" t="s">
+        <v>241</v>
+      </c>
+      <c r="J168">
+        <v>2023402</v>
+      </c>
+      <c r="K168" t="s">
         <v>239</v>
-      </c>
-      <c r="J168">
-        <v>2023404</v>
-      </c>
-      <c r="K168" t="s">
-        <v>233</v>
       </c>
       <c r="N168">
         <v>999</v>
@@ -9075,119 +9132,191 @@
     </row>
     <row r="169" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A169">
-        <v>1023405</v>
+        <v>1023403</v>
       </c>
       <c r="B169" s="7"/>
       <c r="C169">
-        <v>1023405</v>
+        <v>1023403</v>
       </c>
       <c r="D169" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E169">
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G169">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H169">
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J169">
-        <v>2023405</v>
+        <v>2023403</v>
       </c>
       <c r="K169" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N169">
         <v>999</v>
       </c>
     </row>
-    <row r="170" ht="21" customHeight="1" spans="1:14">
+    <row r="170" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A170">
-        <f>1000000+E170*10000+B170</f>
-        <v>1990000</v>
-      </c>
-      <c r="B170" s="7">
-        <v>0</v>
-      </c>
+        <v>1023404</v>
+      </c>
+      <c r="B170" s="7"/>
       <c r="C170">
-        <v>1990000</v>
+        <v>1023404</v>
       </c>
       <c r="D170" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E170">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="F170" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H170">
         <v>0</v>
       </c>
-      <c r="I170" t="str">
-        <f>"itemicon_"&amp;A170&amp;".png"</f>
-        <v>itemicon_1990000.png</v>
+      <c r="I170" t="s">
+        <v>245</v>
       </c>
       <c r="J170">
-        <f>2000000+E170*10000+B170</f>
-        <v>2990000</v>
+        <v>2023404</v>
       </c>
       <c r="K170" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="N170">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="171" ht="21" customHeight="1" spans="1:14">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A171">
-        <f>1000000+E171*10000+B171</f>
-        <v>1980000</v>
-      </c>
-      <c r="B171" s="7">
-        <v>0</v>
-      </c>
+        <v>1023405</v>
+      </c>
+      <c r="B171" s="7"/>
       <c r="C171">
-        <v>1980000</v>
+        <v>1023405</v>
       </c>
       <c r="D171" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E171">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F171" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="G171">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H171">
         <v>0</v>
       </c>
-      <c r="I171" t="str">
-        <f>"itemicon_"&amp;A171&amp;".png"</f>
+      <c r="I171" t="s">
+        <v>247</v>
+      </c>
+      <c r="J171">
+        <v>2023405</v>
+      </c>
+      <c r="K171" t="s">
+        <v>239</v>
+      </c>
+      <c r="N171">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="172" ht="21" customHeight="1" spans="1:14">
+      <c r="A172">
+        <f>1000000+E172*10000+B172</f>
+        <v>1990000</v>
+      </c>
+      <c r="B172" s="7">
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <v>1990000</v>
+      </c>
+      <c r="D172" t="s">
+        <v>248</v>
+      </c>
+      <c r="E172">
+        <v>99</v>
+      </c>
+      <c r="F172" t="s">
+        <v>249</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172" t="str">
+        <f>"itemicon_"&amp;A172&amp;".png"</f>
+        <v>itemicon_1990000.png</v>
+      </c>
+      <c r="J172">
+        <f>2000000+E172*10000+B172</f>
+        <v>2990000</v>
+      </c>
+      <c r="K172" t="s">
+        <v>250</v>
+      </c>
+      <c r="N172">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="173" ht="21" customHeight="1" spans="1:14">
+      <c r="A173">
+        <f>1000000+E173*10000+B173</f>
+        <v>1980000</v>
+      </c>
+      <c r="B173" s="7">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>1980000</v>
+      </c>
+      <c r="D173" t="s">
+        <v>251</v>
+      </c>
+      <c r="E173">
+        <v>98</v>
+      </c>
+      <c r="F173" t="s">
+        <v>249</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173" t="str">
+        <f>"itemicon_"&amp;A173&amp;".png"</f>
         <v>itemicon_1980000.png</v>
       </c>
-      <c r="J171">
-        <f>2000000+E171*10000+B171</f>
+      <c r="J173">
+        <f>2000000+E173*10000+B173</f>
         <v>2980000</v>
       </c>
-      <c r="K171" t="s">
-        <v>246</v>
-      </c>
-      <c r="N171">
+      <c r="K173" t="s">
+        <v>252</v>
+      </c>
+      <c r="N173">
         <v>-1</v>
       </c>
     </row>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -2388,7 +2388,7 @@
     </row>
     <row r="5" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A5">
-        <f>1000000+E5*10000+B5</f>
+        <f t="shared" ref="A5:A16" si="0">1000000+E5*10000+B5</f>
         <v>1010101</v>
       </c>
       <c r="B5" s="7">
@@ -2417,7 +2417,7 @@
         <v>itemicon_1010101.png</v>
       </c>
       <c r="J5">
-        <f>2000000+E5*10000+B5</f>
+        <f t="shared" ref="J5:J16" si="1">2000000+E5*10000+B5</f>
         <v>2010101</v>
       </c>
       <c r="K5" t="s">
@@ -2432,7 +2432,7 @@
     </row>
     <row r="6" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A6">
-        <f>1000000+E6*10000+B6</f>
+        <f t="shared" si="0"/>
         <v>1010201</v>
       </c>
       <c r="B6" s="7">
@@ -2461,7 +2461,7 @@
         <v>itemicon_1010201.png</v>
       </c>
       <c r="J6">
-        <f>2000000+E6*10000+B6</f>
+        <f t="shared" si="1"/>
         <v>2010201</v>
       </c>
       <c r="K6" t="s">
@@ -2476,14 +2476,14 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A7" s="1">
-        <f>1000000+E7*10000+B7</f>
+        <f t="shared" si="0"/>
         <v>1010301</v>
       </c>
       <c r="B7" s="1">
         <v>301</v>
       </c>
       <c r="C7" s="1">
-        <f>1000000+E7*100000+B7</f>
+        <f t="shared" ref="C7:C16" si="2">1000000+E7*100000+B7</f>
         <v>1100301</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2505,7 +2505,7 @@
         <v>37</v>
       </c>
       <c r="J7" s="1">
-        <f>2000000+E7*10000+B7</f>
+        <f t="shared" si="1"/>
         <v>2010301</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -2524,14 +2524,14 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A8" s="1">
-        <f>1000000+E8*10000+B8</f>
+        <f t="shared" si="0"/>
         <v>1010302</v>
       </c>
       <c r="B8" s="1">
         <v>302</v>
       </c>
       <c r="C8" s="1">
-        <f>1000000+E8*100000+B8</f>
+        <f t="shared" si="2"/>
         <v>1100302</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2553,7 +2553,7 @@
         <v>37</v>
       </c>
       <c r="J8" s="1">
-        <f>2000000+E8*10000+B8</f>
+        <f t="shared" si="1"/>
         <v>2010302</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -2572,14 +2572,14 @@
     </row>
     <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A9" s="1">
-        <f>1000000+E9*10000+B9</f>
+        <f t="shared" si="0"/>
         <v>1010303</v>
       </c>
       <c r="B9" s="1">
         <v>303</v>
       </c>
       <c r="C9" s="1">
-        <f>1000000+E9*100000+B9</f>
+        <f t="shared" si="2"/>
         <v>1100303</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2601,7 +2601,7 @@
         <v>37</v>
       </c>
       <c r="J9" s="1">
-        <f>2000000+E9*10000+B9</f>
+        <f t="shared" si="1"/>
         <v>2010303</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -2620,14 +2620,14 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A10" s="1">
-        <f>1000000+E10*10000+B10</f>
+        <f t="shared" si="0"/>
         <v>1010304</v>
       </c>
       <c r="B10" s="1">
         <v>304</v>
       </c>
       <c r="C10" s="1">
-        <f>1000000+E10*100000+B10</f>
+        <f t="shared" si="2"/>
         <v>1100304</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2649,7 +2649,7 @@
         <v>37</v>
       </c>
       <c r="J10" s="1">
-        <f>2000000+E10*10000+B10</f>
+        <f t="shared" si="1"/>
         <v>2010304</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -2668,14 +2668,14 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A11" s="1">
-        <f>1000000+E11*10000+B11</f>
+        <f t="shared" si="0"/>
         <v>1010305</v>
       </c>
       <c r="B11" s="1">
         <v>305</v>
       </c>
       <c r="C11" s="1">
-        <f>1000000+E11*100000+B11</f>
+        <f t="shared" si="2"/>
         <v>1100305</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -2697,7 +2697,7 @@
         <v>37</v>
       </c>
       <c r="J11" s="1">
-        <f>2000000+E11*10000+B11</f>
+        <f t="shared" si="1"/>
         <v>2010305</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -2716,14 +2716,14 @@
     </row>
     <row r="12" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A12" s="1">
-        <f>1000000+E12*10000+B12</f>
+        <f t="shared" si="0"/>
         <v>1010311</v>
       </c>
       <c r="B12" s="1">
         <v>311</v>
       </c>
       <c r="C12" s="1">
-        <f>1000000+E12*100000+B12</f>
+        <f t="shared" si="2"/>
         <v>1100311</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2745,7 +2745,7 @@
         <v>37</v>
       </c>
       <c r="J12" s="1">
-        <f>2000000+E12*10000+B12</f>
+        <f t="shared" si="1"/>
         <v>2010311</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -2761,14 +2761,14 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A13" s="1">
-        <f>1000000+E13*10000+B13</f>
+        <f t="shared" si="0"/>
         <v>1010312</v>
       </c>
       <c r="B13" s="1">
         <v>312</v>
       </c>
       <c r="C13" s="1">
-        <f>1000000+E13*100000+B13</f>
+        <f t="shared" si="2"/>
         <v>1100312</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2790,7 +2790,7 @@
         <v>37</v>
       </c>
       <c r="J13" s="1">
-        <f>2000000+E13*10000+B13</f>
+        <f t="shared" si="1"/>
         <v>2010312</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -2806,14 +2806,14 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A14" s="1">
-        <f>1000000+E14*10000+B14</f>
+        <f t="shared" si="0"/>
         <v>1010313</v>
       </c>
       <c r="B14" s="1">
         <v>313</v>
       </c>
       <c r="C14" s="1">
-        <f>1000000+E14*100000+B14</f>
+        <f t="shared" si="2"/>
         <v>1100313</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2835,7 +2835,7 @@
         <v>37</v>
       </c>
       <c r="J14" s="1">
-        <f>2000000+E14*10000+B14</f>
+        <f t="shared" si="1"/>
         <v>2010313</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -2851,14 +2851,14 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A15" s="1">
-        <f>1000000+E15*10000+B15</f>
+        <f t="shared" si="0"/>
         <v>1010314</v>
       </c>
       <c r="B15" s="1">
         <v>314</v>
       </c>
       <c r="C15" s="1">
-        <f>1000000+E15*100000+B15</f>
+        <f t="shared" si="2"/>
         <v>1100314</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -2880,7 +2880,7 @@
         <v>37</v>
       </c>
       <c r="J15" s="1">
-        <f>2000000+E15*10000+B15</f>
+        <f t="shared" si="1"/>
         <v>2010314</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -2896,14 +2896,14 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A16" s="1">
-        <f>1000000+E16*10000+B16</f>
+        <f t="shared" si="0"/>
         <v>1010315</v>
       </c>
       <c r="B16" s="1">
         <v>315</v>
       </c>
       <c r="C16" s="1">
-        <f>1000000+E16*100000+B16</f>
+        <f t="shared" si="2"/>
         <v>1100315</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2925,7 +2925,7 @@
         <v>37</v>
       </c>
       <c r="J16" s="1">
-        <f>2000000+E16*10000+B16</f>
+        <f t="shared" si="1"/>
         <v>2010315</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -2941,7 +2941,7 @@
     </row>
     <row r="17" ht="21" customHeight="1" spans="1:14">
       <c r="A17">
-        <f t="shared" ref="A17:A31" si="0">1000000+E17*10000+B17</f>
+        <f t="shared" ref="A17:A31" si="3">1000000+E17*10000+B17</f>
         <v>1020001</v>
       </c>
       <c r="B17" s="7">
@@ -2967,11 +2967,11 @@
         <v>0</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" ref="I17:I30" si="1">"itemicon_"&amp;A17&amp;".png"</f>
+        <f t="shared" ref="I17:I30" si="4">"itemicon_"&amp;A17&amp;".png"</f>
         <v>itemicon_1020001.png</v>
       </c>
       <c r="J17">
-        <f t="shared" ref="J17:J31" si="2">2000000+E17*10000+B17</f>
+        <f t="shared" ref="J17:J31" si="5">2000000+E17*10000+B17</f>
         <v>2020001</v>
       </c>
       <c r="K17" t="s">
@@ -2983,7 +2983,7 @@
     </row>
     <row r="18" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1020002</v>
       </c>
       <c r="B18" s="2">
@@ -3009,11 +3009,11 @@
         <v>1</v>
       </c>
       <c r="I18" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1020002.png</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2020002</v>
       </c>
       <c r="K18" s="2" t="s">
@@ -3025,7 +3025,7 @@
     </row>
     <row r="19" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1020003</v>
       </c>
       <c r="B19" s="2">
@@ -3051,11 +3051,11 @@
         <v>1</v>
       </c>
       <c r="I19" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1020003.png</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2020003</v>
       </c>
       <c r="K19" s="2" t="s">
@@ -3067,7 +3067,7 @@
     </row>
     <row r="20" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1020004</v>
       </c>
       <c r="B20" s="2">
@@ -3093,11 +3093,11 @@
         <v>1</v>
       </c>
       <c r="I20" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1020004.png</v>
       </c>
       <c r="J20" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2020004</v>
       </c>
       <c r="K20" s="2" t="s">
@@ -3109,7 +3109,7 @@
     </row>
     <row r="21" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A21" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1020005</v>
       </c>
       <c r="B21" s="2">
@@ -3135,11 +3135,11 @@
         <v>1</v>
       </c>
       <c r="I21" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1020005.png</v>
       </c>
       <c r="J21" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2020005</v>
       </c>
       <c r="K21" s="2" t="s">
@@ -3151,7 +3151,7 @@
     </row>
     <row r="22" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1020006</v>
       </c>
       <c r="B22" s="2">
@@ -3177,11 +3177,11 @@
         <v>1</v>
       </c>
       <c r="I22" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1020006.png</v>
       </c>
       <c r="J22" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2020006</v>
       </c>
       <c r="K22" s="2" t="s">
@@ -3193,14 +3193,14 @@
     </row>
     <row r="23" ht="23" customHeight="1" spans="1:14">
       <c r="A23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1030011</v>
       </c>
       <c r="B23" s="7">
         <v>11</v>
       </c>
       <c r="C23">
-        <f t="shared" ref="C23:C31" si="3">1000000+E23*100000+B23</f>
+        <f t="shared" ref="C23:C31" si="6">1000000+E23*100000+B23</f>
         <v>1300011</v>
       </c>
       <c r="D23" t="s">
@@ -3219,11 +3219,11 @@
         <v>1</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1030011.png</v>
       </c>
       <c r="J23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2030011</v>
       </c>
       <c r="K23" t="s">
@@ -3238,14 +3238,14 @@
     </row>
     <row r="24" ht="23" customHeight="1" spans="1:14">
       <c r="A24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1030012</v>
       </c>
       <c r="B24" s="7">
         <v>12</v>
       </c>
       <c r="C24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1300012</v>
       </c>
       <c r="D24" t="s">
@@ -3264,11 +3264,11 @@
         <v>1</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1030012.png</v>
       </c>
       <c r="J24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2030012</v>
       </c>
       <c r="K24" t="s">
@@ -3283,14 +3283,14 @@
     </row>
     <row r="25" ht="23" customHeight="1" spans="1:14">
       <c r="A25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1030013</v>
       </c>
       <c r="B25" s="7">
         <v>13</v>
       </c>
       <c r="C25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1300013</v>
       </c>
       <c r="D25" t="s">
@@ -3309,11 +3309,11 @@
         <v>1</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1030013.png</v>
       </c>
       <c r="J25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2030013</v>
       </c>
       <c r="K25" t="s">
@@ -3328,14 +3328,14 @@
     </row>
     <row r="26" ht="23" customHeight="1" spans="1:14">
       <c r="A26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1030014</v>
       </c>
       <c r="B26" s="7">
         <v>14</v>
       </c>
       <c r="C26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1300014</v>
       </c>
       <c r="D26" t="s">
@@ -3354,11 +3354,11 @@
         <v>1</v>
       </c>
       <c r="I26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1030014.png</v>
       </c>
       <c r="J26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2030014</v>
       </c>
       <c r="K26" t="s">
@@ -3373,14 +3373,14 @@
     </row>
     <row r="27" ht="23" customHeight="1" spans="1:14">
       <c r="A27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1030015</v>
       </c>
       <c r="B27" s="7">
         <v>15</v>
       </c>
       <c r="C27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1300015</v>
       </c>
       <c r="D27" t="s">
@@ -3399,11 +3399,11 @@
         <v>1</v>
       </c>
       <c r="I27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1030015.png</v>
       </c>
       <c r="J27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2030015</v>
       </c>
       <c r="K27" t="s">
@@ -3418,14 +3418,14 @@
     </row>
     <row r="28" ht="23" customHeight="1" spans="1:14">
       <c r="A28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1030016</v>
       </c>
       <c r="B28" s="7">
         <v>16</v>
       </c>
       <c r="C28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1300016</v>
       </c>
       <c r="D28" t="s">
@@ -3444,11 +3444,11 @@
         <v>1</v>
       </c>
       <c r="I28" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1030016.png</v>
       </c>
       <c r="J28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2030016</v>
       </c>
       <c r="K28" t="s">
@@ -3463,14 +3463,14 @@
     </row>
     <row r="29" ht="23" customHeight="1" spans="1:14">
       <c r="A29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1030017</v>
       </c>
       <c r="B29" s="7">
         <v>17</v>
       </c>
       <c r="C29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1300017</v>
       </c>
       <c r="D29" t="s">
@@ -3489,11 +3489,11 @@
         <v>1</v>
       </c>
       <c r="I29" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1030017.png</v>
       </c>
       <c r="J29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2030017</v>
       </c>
       <c r="K29" t="s">
@@ -3508,14 +3508,14 @@
     </row>
     <row r="30" ht="23" customHeight="1" spans="1:14">
       <c r="A30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1030018</v>
       </c>
       <c r="B30" s="7">
         <v>18</v>
       </c>
       <c r="C30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1300018</v>
       </c>
       <c r="D30" t="s">
@@ -3534,11 +3534,11 @@
         <v>1</v>
       </c>
       <c r="I30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>itemicon_1030018.png</v>
       </c>
       <c r="J30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2030018</v>
       </c>
       <c r="K30" t="s">
@@ -3553,14 +3553,14 @@
     </row>
     <row r="31" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1030101</v>
       </c>
       <c r="B31" s="7">
         <v>101</v>
       </c>
       <c r="C31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1300101</v>
       </c>
       <c r="D31" t="s">
@@ -3582,7 +3582,7 @@
         <v>71</v>
       </c>
       <c r="J31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2030101</v>
       </c>
       <c r="K31" t="s">
@@ -3594,14 +3594,14 @@
     </row>
     <row r="32" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A32">
-        <f t="shared" ref="A32:A42" si="4">1000000+E32*10000+B32</f>
+        <f t="shared" ref="A32:A42" si="7">1000000+E32*10000+B32</f>
         <v>1030102</v>
       </c>
       <c r="B32" s="7">
         <v>102</v>
       </c>
       <c r="C32">
-        <f t="shared" ref="C32:C42" si="5">1000000+E32*100000+B32</f>
+        <f t="shared" ref="C32:C42" si="8">1000000+E32*100000+B32</f>
         <v>1300102</v>
       </c>
       <c r="D32" t="s">
@@ -3623,7 +3623,7 @@
         <v>71</v>
       </c>
       <c r="J32">
-        <f t="shared" ref="J32:J63" si="6">2000000+E32*10000+B32</f>
+        <f t="shared" ref="J32:J63" si="9">2000000+E32*10000+B32</f>
         <v>2030102</v>
       </c>
       <c r="K32" t="s">
@@ -3635,14 +3635,14 @@
     </row>
     <row r="33" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030103</v>
       </c>
       <c r="B33" s="7">
         <v>103</v>
       </c>
       <c r="C33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300103</v>
       </c>
       <c r="D33" t="s">
@@ -3664,7 +3664,7 @@
         <v>71</v>
       </c>
       <c r="J33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030103</v>
       </c>
       <c r="K33" t="s">
@@ -3676,14 +3676,14 @@
     </row>
     <row r="34" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030104</v>
       </c>
       <c r="B34" s="7">
         <v>104</v>
       </c>
       <c r="C34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300104</v>
       </c>
       <c r="D34" t="s">
@@ -3705,7 +3705,7 @@
         <v>71</v>
       </c>
       <c r="J34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030104</v>
       </c>
       <c r="K34" t="s">
@@ -3717,14 +3717,14 @@
     </row>
     <row r="35" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030105</v>
       </c>
       <c r="B35" s="7">
         <v>105</v>
       </c>
       <c r="C35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300105</v>
       </c>
       <c r="D35" t="s">
@@ -3746,7 +3746,7 @@
         <v>71</v>
       </c>
       <c r="J35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030105</v>
       </c>
       <c r="K35" t="s">
@@ -3758,14 +3758,14 @@
     </row>
     <row r="36" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030106</v>
       </c>
       <c r="B36" s="7">
         <v>106</v>
       </c>
       <c r="C36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300106</v>
       </c>
       <c r="D36" t="s">
@@ -3787,7 +3787,7 @@
         <v>71</v>
       </c>
       <c r="J36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030106</v>
       </c>
       <c r="K36" t="s">
@@ -3799,14 +3799,14 @@
     </row>
     <row r="37" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030107</v>
       </c>
       <c r="B37" s="7">
         <v>107</v>
       </c>
       <c r="C37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300107</v>
       </c>
       <c r="D37" t="s">
@@ -3828,7 +3828,7 @@
         <v>71</v>
       </c>
       <c r="J37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030107</v>
       </c>
       <c r="K37" t="s">
@@ -3840,14 +3840,14 @@
     </row>
     <row r="38" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030108</v>
       </c>
       <c r="B38" s="7">
         <v>108</v>
       </c>
       <c r="C38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300108</v>
       </c>
       <c r="D38" t="s">
@@ -3869,7 +3869,7 @@
         <v>71</v>
       </c>
       <c r="J38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030108</v>
       </c>
       <c r="K38" t="s">
@@ -3881,14 +3881,14 @@
     </row>
     <row r="39" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030109</v>
       </c>
       <c r="B39" s="7">
         <v>109</v>
       </c>
       <c r="C39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300109</v>
       </c>
       <c r="D39" t="s">
@@ -3910,7 +3910,7 @@
         <v>71</v>
       </c>
       <c r="J39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030109</v>
       </c>
       <c r="K39" t="s">
@@ -3922,14 +3922,14 @@
     </row>
     <row r="40" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030110</v>
       </c>
       <c r="B40" s="7">
         <v>110</v>
       </c>
       <c r="C40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300110</v>
       </c>
       <c r="D40" t="s">
@@ -3951,7 +3951,7 @@
         <v>71</v>
       </c>
       <c r="J40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030110</v>
       </c>
       <c r="K40" t="s">
@@ -3963,14 +3963,14 @@
     </row>
     <row r="41" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030111</v>
       </c>
       <c r="B41" s="7">
         <v>111</v>
       </c>
       <c r="C41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300111</v>
       </c>
       <c r="D41" t="s">
@@ -3992,7 +3992,7 @@
         <v>71</v>
       </c>
       <c r="J41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030111</v>
       </c>
       <c r="K41" t="s">
@@ -4004,14 +4004,14 @@
     </row>
     <row r="42" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1030112</v>
       </c>
       <c r="B42" s="7">
         <v>112</v>
       </c>
       <c r="C42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1300112</v>
       </c>
       <c r="D42" t="s">
@@ -4033,7 +4033,7 @@
         <v>71</v>
       </c>
       <c r="J42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030112</v>
       </c>
       <c r="K42" t="s">
@@ -4045,14 +4045,14 @@
     </row>
     <row r="43" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A43">
-        <f t="shared" ref="A43:A68" si="7">1000000+E43*10000+B43</f>
+        <f t="shared" ref="A43:A68" si="10">1000000+E43*10000+B43</f>
         <v>1030121</v>
       </c>
       <c r="B43" s="7">
         <v>121</v>
       </c>
       <c r="C43">
-        <f t="shared" ref="C43:C68" si="8">1000000+E43*100000+B43</f>
+        <f t="shared" ref="C43:C68" si="11">1000000+E43*100000+B43</f>
         <v>1300121</v>
       </c>
       <c r="D43" t="s">
@@ -4074,7 +4074,7 @@
         <v>71</v>
       </c>
       <c r="J43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030121</v>
       </c>
       <c r="K43" t="s">
@@ -4086,14 +4086,14 @@
     </row>
     <row r="44" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030122</v>
       </c>
       <c r="B44" s="7">
         <v>122</v>
       </c>
       <c r="C44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300122</v>
       </c>
       <c r="D44" t="s">
@@ -4115,7 +4115,7 @@
         <v>71</v>
       </c>
       <c r="J44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030122</v>
       </c>
       <c r="K44" t="s">
@@ -4127,14 +4127,14 @@
     </row>
     <row r="45" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A45">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030123</v>
       </c>
       <c r="B45" s="7">
         <v>123</v>
       </c>
       <c r="C45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300123</v>
       </c>
       <c r="D45" t="s">
@@ -4156,7 +4156,7 @@
         <v>71</v>
       </c>
       <c r="J45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030123</v>
       </c>
       <c r="K45" t="s">
@@ -4168,14 +4168,14 @@
     </row>
     <row r="46" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030124</v>
       </c>
       <c r="B46" s="7">
         <v>124</v>
       </c>
       <c r="C46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300124</v>
       </c>
       <c r="D46" t="s">
@@ -4197,7 +4197,7 @@
         <v>71</v>
       </c>
       <c r="J46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030124</v>
       </c>
       <c r="K46" t="s">
@@ -4209,14 +4209,14 @@
     </row>
     <row r="47" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A47">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030125</v>
       </c>
       <c r="B47" s="7">
         <v>125</v>
       </c>
       <c r="C47">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300125</v>
       </c>
       <c r="D47" t="s">
@@ -4238,7 +4238,7 @@
         <v>71</v>
       </c>
       <c r="J47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030125</v>
       </c>
       <c r="K47" t="s">
@@ -4250,14 +4250,14 @@
     </row>
     <row r="48" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030126</v>
       </c>
       <c r="B48" s="7">
         <v>126</v>
       </c>
       <c r="C48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300126</v>
       </c>
       <c r="D48" t="s">
@@ -4279,7 +4279,7 @@
         <v>71</v>
       </c>
       <c r="J48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030126</v>
       </c>
       <c r="K48" t="s">
@@ -4291,14 +4291,14 @@
     </row>
     <row r="49" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030127</v>
       </c>
       <c r="B49" s="7">
         <v>127</v>
       </c>
       <c r="C49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300127</v>
       </c>
       <c r="D49" t="s">
@@ -4320,7 +4320,7 @@
         <v>71</v>
       </c>
       <c r="J49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030127</v>
       </c>
       <c r="K49" t="s">
@@ -4332,14 +4332,14 @@
     </row>
     <row r="50" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030128</v>
       </c>
       <c r="B50" s="7">
         <v>128</v>
       </c>
       <c r="C50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300128</v>
       </c>
       <c r="D50" t="s">
@@ -4361,7 +4361,7 @@
         <v>71</v>
       </c>
       <c r="J50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030128</v>
       </c>
       <c r="K50" t="s">
@@ -4373,14 +4373,14 @@
     </row>
     <row r="51" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A51">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030129</v>
       </c>
       <c r="B51" s="7">
         <v>129</v>
       </c>
       <c r="C51">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300129</v>
       </c>
       <c r="D51" t="s">
@@ -4402,7 +4402,7 @@
         <v>71</v>
       </c>
       <c r="J51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030129</v>
       </c>
       <c r="K51" t="s">
@@ -4414,14 +4414,14 @@
     </row>
     <row r="52" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A52">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030130</v>
       </c>
       <c r="B52" s="7">
         <v>130</v>
       </c>
       <c r="C52">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300130</v>
       </c>
       <c r="D52" t="s">
@@ -4443,7 +4443,7 @@
         <v>71</v>
       </c>
       <c r="J52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030130</v>
       </c>
       <c r="K52" t="s">
@@ -4455,14 +4455,14 @@
     </row>
     <row r="53" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A53">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030131</v>
       </c>
       <c r="B53" s="7">
         <v>131</v>
       </c>
       <c r="C53">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300131</v>
       </c>
       <c r="D53" t="s">
@@ -4484,7 +4484,7 @@
         <v>71</v>
       </c>
       <c r="J53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030131</v>
       </c>
       <c r="K53" t="s">
@@ -4496,14 +4496,14 @@
     </row>
     <row r="54" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030132</v>
       </c>
       <c r="B54" s="7">
         <v>132</v>
       </c>
       <c r="C54">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300132</v>
       </c>
       <c r="D54" t="s">
@@ -4525,7 +4525,7 @@
         <v>71</v>
       </c>
       <c r="J54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030132</v>
       </c>
       <c r="K54" t="s">
@@ -4537,14 +4537,14 @@
     </row>
     <row r="55" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A55">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030141</v>
       </c>
       <c r="B55" s="7">
         <v>141</v>
       </c>
       <c r="C55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300141</v>
       </c>
       <c r="D55" t="s">
@@ -4566,7 +4566,7 @@
         <v>71</v>
       </c>
       <c r="J55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030141</v>
       </c>
       <c r="K55" t="s">
@@ -4578,14 +4578,14 @@
     </row>
     <row r="56" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A56">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030142</v>
       </c>
       <c r="B56" s="7">
         <v>142</v>
       </c>
       <c r="C56">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300142</v>
       </c>
       <c r="D56" t="s">
@@ -4607,7 +4607,7 @@
         <v>71</v>
       </c>
       <c r="J56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030142</v>
       </c>
       <c r="K56" t="s">
@@ -4619,14 +4619,14 @@
     </row>
     <row r="57" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A57">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030143</v>
       </c>
       <c r="B57" s="7">
         <v>143</v>
       </c>
       <c r="C57">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300143</v>
       </c>
       <c r="D57" t="s">
@@ -4648,7 +4648,7 @@
         <v>71</v>
       </c>
       <c r="J57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030143</v>
       </c>
       <c r="K57" t="s">
@@ -4660,14 +4660,14 @@
     </row>
     <row r="58" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030144</v>
       </c>
       <c r="B58" s="7">
         <v>144</v>
       </c>
       <c r="C58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300144</v>
       </c>
       <c r="D58" t="s">
@@ -4689,7 +4689,7 @@
         <v>71</v>
       </c>
       <c r="J58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030144</v>
       </c>
       <c r="K58" t="s">
@@ -4701,14 +4701,14 @@
     </row>
     <row r="59" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A59">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030145</v>
       </c>
       <c r="B59" s="7">
         <v>145</v>
       </c>
       <c r="C59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300145</v>
       </c>
       <c r="D59" t="s">
@@ -4730,7 +4730,7 @@
         <v>71</v>
       </c>
       <c r="J59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030145</v>
       </c>
       <c r="K59" t="s">
@@ -4742,14 +4742,14 @@
     </row>
     <row r="60" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030146</v>
       </c>
       <c r="B60" s="7">
         <v>146</v>
       </c>
       <c r="C60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300146</v>
       </c>
       <c r="D60" t="s">
@@ -4771,7 +4771,7 @@
         <v>71</v>
       </c>
       <c r="J60">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030146</v>
       </c>
       <c r="K60" t="s">
@@ -4783,14 +4783,14 @@
     </row>
     <row r="61" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A61">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030147</v>
       </c>
       <c r="B61" s="7">
         <v>147</v>
       </c>
       <c r="C61">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300147</v>
       </c>
       <c r="D61" t="s">
@@ -4812,7 +4812,7 @@
         <v>71</v>
       </c>
       <c r="J61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030147</v>
       </c>
       <c r="K61" t="s">
@@ -4824,14 +4824,14 @@
     </row>
     <row r="62" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A62">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030148</v>
       </c>
       <c r="B62" s="7">
         <v>148</v>
       </c>
       <c r="C62">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300148</v>
       </c>
       <c r="D62" t="s">
@@ -4853,7 +4853,7 @@
         <v>71</v>
       </c>
       <c r="J62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030148</v>
       </c>
       <c r="K62" t="s">
@@ -4865,14 +4865,14 @@
     </row>
     <row r="63" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030149</v>
       </c>
       <c r="B63" s="7">
         <v>149</v>
       </c>
       <c r="C63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300149</v>
       </c>
       <c r="D63" t="s">
@@ -4894,7 +4894,7 @@
         <v>71</v>
       </c>
       <c r="J63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2030149</v>
       </c>
       <c r="K63" t="s">
@@ -4906,14 +4906,14 @@
     </row>
     <row r="64" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A64">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030150</v>
       </c>
       <c r="B64" s="7">
         <v>150</v>
       </c>
       <c r="C64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300150</v>
       </c>
       <c r="D64" t="s">
@@ -4935,7 +4935,7 @@
         <v>71</v>
       </c>
       <c r="J64">
-        <f t="shared" ref="J64:J95" si="9">2000000+E64*10000+B64</f>
+        <f t="shared" ref="J64:J95" si="12">2000000+E64*10000+B64</f>
         <v>2030150</v>
       </c>
       <c r="K64" t="s">
@@ -4947,14 +4947,14 @@
     </row>
     <row r="65" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030151</v>
       </c>
       <c r="B65" s="7">
         <v>151</v>
       </c>
       <c r="C65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300151</v>
       </c>
       <c r="D65" t="s">
@@ -4976,7 +4976,7 @@
         <v>71</v>
       </c>
       <c r="J65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030151</v>
       </c>
       <c r="K65" t="s">
@@ -4988,14 +4988,14 @@
     </row>
     <row r="66" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030152</v>
       </c>
       <c r="B66" s="7">
         <v>152</v>
       </c>
       <c r="C66">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300152</v>
       </c>
       <c r="D66" t="s">
@@ -5017,7 +5017,7 @@
         <v>71</v>
       </c>
       <c r="J66">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030152</v>
       </c>
       <c r="K66" t="s">
@@ -5029,14 +5029,14 @@
     </row>
     <row r="67" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030161</v>
       </c>
       <c r="B67" s="7">
         <v>161</v>
       </c>
       <c r="C67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300161</v>
       </c>
       <c r="D67" t="s">
@@ -5058,7 +5058,7 @@
         <v>71</v>
       </c>
       <c r="J67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030161</v>
       </c>
       <c r="K67" t="s">
@@ -5070,14 +5070,14 @@
     </row>
     <row r="68" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1030162</v>
       </c>
       <c r="B68" s="7">
         <v>162</v>
       </c>
       <c r="C68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1300162</v>
       </c>
       <c r="D68" t="s">
@@ -5099,7 +5099,7 @@
         <v>71</v>
       </c>
       <c r="J68">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030162</v>
       </c>
       <c r="K68" t="s">
@@ -5111,14 +5111,14 @@
     </row>
     <row r="69" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A69">
-        <f t="shared" ref="A69:A100" si="10">1000000+E69*10000+B69</f>
+        <f t="shared" ref="A69:A100" si="13">1000000+E69*10000+B69</f>
         <v>1030163</v>
       </c>
       <c r="B69" s="7">
         <v>163</v>
       </c>
       <c r="C69">
-        <f t="shared" ref="C69:C100" si="11">1000000+E69*100000+B69</f>
+        <f t="shared" ref="C69:C100" si="14">1000000+E69*100000+B69</f>
         <v>1300163</v>
       </c>
       <c r="D69" t="s">
@@ -5140,7 +5140,7 @@
         <v>71</v>
       </c>
       <c r="J69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030163</v>
       </c>
       <c r="K69" t="s">
@@ -5152,14 +5152,14 @@
     </row>
     <row r="70" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A70">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030164</v>
       </c>
       <c r="B70" s="7">
         <v>164</v>
       </c>
       <c r="C70">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300164</v>
       </c>
       <c r="D70" t="s">
@@ -5181,7 +5181,7 @@
         <v>71</v>
       </c>
       <c r="J70">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030164</v>
       </c>
       <c r="K70" t="s">
@@ -5193,14 +5193,14 @@
     </row>
     <row r="71" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A71">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030165</v>
       </c>
       <c r="B71" s="7">
         <v>165</v>
       </c>
       <c r="C71">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300165</v>
       </c>
       <c r="D71" t="s">
@@ -5222,7 +5222,7 @@
         <v>71</v>
       </c>
       <c r="J71">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030165</v>
       </c>
       <c r="K71" t="s">
@@ -5234,14 +5234,14 @@
     </row>
     <row r="72" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A72">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030166</v>
       </c>
       <c r="B72" s="7">
         <v>166</v>
       </c>
       <c r="C72">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300166</v>
       </c>
       <c r="D72" t="s">
@@ -5263,7 +5263,7 @@
         <v>71</v>
       </c>
       <c r="J72">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030166</v>
       </c>
       <c r="K72" t="s">
@@ -5275,14 +5275,14 @@
     </row>
     <row r="73" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A73">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030167</v>
       </c>
       <c r="B73" s="7">
         <v>167</v>
       </c>
       <c r="C73">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300167</v>
       </c>
       <c r="D73" t="s">
@@ -5304,7 +5304,7 @@
         <v>71</v>
       </c>
       <c r="J73">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030167</v>
       </c>
       <c r="K73" t="s">
@@ -5316,14 +5316,14 @@
     </row>
     <row r="74" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A74">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030168</v>
       </c>
       <c r="B74" s="7">
         <v>168</v>
       </c>
       <c r="C74">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300168</v>
       </c>
       <c r="D74" t="s">
@@ -5345,7 +5345,7 @@
         <v>71</v>
       </c>
       <c r="J74">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030168</v>
       </c>
       <c r="K74" t="s">
@@ -5357,14 +5357,14 @@
     </row>
     <row r="75" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030169</v>
       </c>
       <c r="B75" s="7">
         <v>169</v>
       </c>
       <c r="C75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300169</v>
       </c>
       <c r="D75" t="s">
@@ -5386,7 +5386,7 @@
         <v>71</v>
       </c>
       <c r="J75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030169</v>
       </c>
       <c r="K75" t="s">
@@ -5398,14 +5398,14 @@
     </row>
     <row r="76" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A76">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030170</v>
       </c>
       <c r="B76" s="7">
         <v>170</v>
       </c>
       <c r="C76">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300170</v>
       </c>
       <c r="D76" t="s">
@@ -5427,7 +5427,7 @@
         <v>71</v>
       </c>
       <c r="J76">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030170</v>
       </c>
       <c r="K76" t="s">
@@ -5439,14 +5439,14 @@
     </row>
     <row r="77" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A77">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030171</v>
       </c>
       <c r="B77" s="7">
         <v>171</v>
       </c>
       <c r="C77">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300171</v>
       </c>
       <c r="D77" t="s">
@@ -5468,7 +5468,7 @@
         <v>71</v>
       </c>
       <c r="J77">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030171</v>
       </c>
       <c r="K77" t="s">
@@ -5480,14 +5480,14 @@
     </row>
     <row r="78" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A78">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030172</v>
       </c>
       <c r="B78" s="7">
         <v>172</v>
       </c>
       <c r="C78">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300172</v>
       </c>
       <c r="D78" t="s">
@@ -5509,7 +5509,7 @@
         <v>71</v>
       </c>
       <c r="J78">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030172</v>
       </c>
       <c r="K78" t="s">
@@ -5521,14 +5521,14 @@
     </row>
     <row r="79" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A79">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030181</v>
       </c>
       <c r="B79" s="7">
         <v>181</v>
       </c>
       <c r="C79">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300181</v>
       </c>
       <c r="D79" t="s">
@@ -5550,7 +5550,7 @@
         <v>71</v>
       </c>
       <c r="J79">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030181</v>
       </c>
       <c r="K79" t="s">
@@ -5562,14 +5562,14 @@
     </row>
     <row r="80" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A80">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030182</v>
       </c>
       <c r="B80" s="7">
         <v>182</v>
       </c>
       <c r="C80">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300182</v>
       </c>
       <c r="D80" t="s">
@@ -5591,7 +5591,7 @@
         <v>71</v>
       </c>
       <c r="J80">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030182</v>
       </c>
       <c r="K80" t="s">
@@ -5603,14 +5603,14 @@
     </row>
     <row r="81" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030183</v>
       </c>
       <c r="B81" s="7">
         <v>183</v>
       </c>
       <c r="C81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300183</v>
       </c>
       <c r="D81" t="s">
@@ -5632,7 +5632,7 @@
         <v>71</v>
       </c>
       <c r="J81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030183</v>
       </c>
       <c r="K81" t="s">
@@ -5644,14 +5644,14 @@
     </row>
     <row r="82" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A82">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030184</v>
       </c>
       <c r="B82" s="7">
         <v>184</v>
       </c>
       <c r="C82">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300184</v>
       </c>
       <c r="D82" t="s">
@@ -5673,7 +5673,7 @@
         <v>71</v>
       </c>
       <c r="J82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030184</v>
       </c>
       <c r="K82" t="s">
@@ -5685,14 +5685,14 @@
     </row>
     <row r="83" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030185</v>
       </c>
       <c r="B83" s="7">
         <v>185</v>
       </c>
       <c r="C83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300185</v>
       </c>
       <c r="D83" t="s">
@@ -5714,7 +5714,7 @@
         <v>71</v>
       </c>
       <c r="J83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030185</v>
       </c>
       <c r="K83" t="s">
@@ -5726,14 +5726,14 @@
     </row>
     <row r="84" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030186</v>
       </c>
       <c r="B84" s="7">
         <v>186</v>
       </c>
       <c r="C84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300186</v>
       </c>
       <c r="D84" t="s">
@@ -5755,7 +5755,7 @@
         <v>71</v>
       </c>
       <c r="J84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030186</v>
       </c>
       <c r="K84" t="s">
@@ -5767,14 +5767,14 @@
     </row>
     <row r="85" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030187</v>
       </c>
       <c r="B85" s="7">
         <v>187</v>
       </c>
       <c r="C85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300187</v>
       </c>
       <c r="D85" t="s">
@@ -5796,7 +5796,7 @@
         <v>71</v>
       </c>
       <c r="J85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030187</v>
       </c>
       <c r="K85" t="s">
@@ -5808,14 +5808,14 @@
     </row>
     <row r="86" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A86">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030188</v>
       </c>
       <c r="B86" s="7">
         <v>188</v>
       </c>
       <c r="C86">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300188</v>
       </c>
       <c r="D86" t="s">
@@ -5837,7 +5837,7 @@
         <v>71</v>
       </c>
       <c r="J86">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030188</v>
       </c>
       <c r="K86" t="s">
@@ -5849,14 +5849,14 @@
     </row>
     <row r="87" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A87">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030189</v>
       </c>
       <c r="B87" s="7">
         <v>189</v>
       </c>
       <c r="C87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300189</v>
       </c>
       <c r="D87" t="s">
@@ -5878,7 +5878,7 @@
         <v>71</v>
       </c>
       <c r="J87">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030189</v>
       </c>
       <c r="K87" t="s">
@@ -5890,14 +5890,14 @@
     </row>
     <row r="88" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A88">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030190</v>
       </c>
       <c r="B88" s="7">
         <v>190</v>
       </c>
       <c r="C88">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300190</v>
       </c>
       <c r="D88" t="s">
@@ -5919,7 +5919,7 @@
         <v>71</v>
       </c>
       <c r="J88">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030190</v>
       </c>
       <c r="K88" t="s">
@@ -5931,14 +5931,14 @@
     </row>
     <row r="89" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A89">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030191</v>
       </c>
       <c r="B89" s="7">
         <v>191</v>
       </c>
       <c r="C89">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300191</v>
       </c>
       <c r="D89" t="s">
@@ -5960,7 +5960,7 @@
         <v>71</v>
       </c>
       <c r="J89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030191</v>
       </c>
       <c r="K89" t="s">
@@ -5972,14 +5972,14 @@
     </row>
     <row r="90" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030192</v>
       </c>
       <c r="B90" s="7">
         <v>192</v>
       </c>
       <c r="C90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300192</v>
       </c>
       <c r="D90" t="s">
@@ -6001,7 +6001,7 @@
         <v>71</v>
       </c>
       <c r="J90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030192</v>
       </c>
       <c r="K90" t="s">
@@ -6013,14 +6013,14 @@
     </row>
     <row r="91" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030201</v>
       </c>
       <c r="B91" s="7">
         <v>201</v>
       </c>
       <c r="C91">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300201</v>
       </c>
       <c r="D91" t="s">
@@ -6042,7 +6042,7 @@
         <v>71</v>
       </c>
       <c r="J91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030201</v>
       </c>
       <c r="K91" t="s">
@@ -6054,14 +6054,14 @@
     </row>
     <row r="92" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A92">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030202</v>
       </c>
       <c r="B92" s="7">
         <v>202</v>
       </c>
       <c r="C92">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300202</v>
       </c>
       <c r="D92" t="s">
@@ -6083,7 +6083,7 @@
         <v>71</v>
       </c>
       <c r="J92">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030202</v>
       </c>
       <c r="K92" t="s">
@@ -6095,14 +6095,14 @@
     </row>
     <row r="93" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A93">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030203</v>
       </c>
       <c r="B93" s="7">
         <v>203</v>
       </c>
       <c r="C93">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300203</v>
       </c>
       <c r="D93" t="s">
@@ -6124,7 +6124,7 @@
         <v>71</v>
       </c>
       <c r="J93">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030203</v>
       </c>
       <c r="K93" t="s">
@@ -6136,14 +6136,14 @@
     </row>
     <row r="94" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A94">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030204</v>
       </c>
       <c r="B94" s="7">
         <v>204</v>
       </c>
       <c r="C94">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300204</v>
       </c>
       <c r="D94" t="s">
@@ -6165,7 +6165,7 @@
         <v>71</v>
       </c>
       <c r="J94">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030204</v>
       </c>
       <c r="K94" t="s">
@@ -6177,14 +6177,14 @@
     </row>
     <row r="95" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030205</v>
       </c>
       <c r="B95" s="7">
         <v>205</v>
       </c>
       <c r="C95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300205</v>
       </c>
       <c r="D95" t="s">
@@ -6206,7 +6206,7 @@
         <v>71</v>
       </c>
       <c r="J95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2030205</v>
       </c>
       <c r="K95" t="s">
@@ -6218,14 +6218,14 @@
     </row>
     <row r="96" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A96">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030206</v>
       </c>
       <c r="B96" s="7">
         <v>206</v>
       </c>
       <c r="C96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300206</v>
       </c>
       <c r="D96" t="s">
@@ -6247,7 +6247,7 @@
         <v>71</v>
       </c>
       <c r="J96">
-        <f t="shared" ref="J96:J130" si="12">2000000+E96*10000+B96</f>
+        <f t="shared" ref="J96:J130" si="15">2000000+E96*10000+B96</f>
         <v>2030206</v>
       </c>
       <c r="K96" t="s">
@@ -6259,14 +6259,14 @@
     </row>
     <row r="97" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A97">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030207</v>
       </c>
       <c r="B97" s="7">
         <v>207</v>
       </c>
       <c r="C97">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300207</v>
       </c>
       <c r="D97" t="s">
@@ -6288,7 +6288,7 @@
         <v>71</v>
       </c>
       <c r="J97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030207</v>
       </c>
       <c r="K97" t="s">
@@ -6300,14 +6300,14 @@
     </row>
     <row r="98" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A98">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030208</v>
       </c>
       <c r="B98" s="7">
         <v>208</v>
       </c>
       <c r="C98">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300208</v>
       </c>
       <c r="D98" t="s">
@@ -6329,7 +6329,7 @@
         <v>71</v>
       </c>
       <c r="J98">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030208</v>
       </c>
       <c r="K98" t="s">
@@ -6341,14 +6341,14 @@
     </row>
     <row r="99" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A99">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030209</v>
       </c>
       <c r="B99" s="7">
         <v>209</v>
       </c>
       <c r="C99">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300209</v>
       </c>
       <c r="D99" t="s">
@@ -6370,7 +6370,7 @@
         <v>71</v>
       </c>
       <c r="J99">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030209</v>
       </c>
       <c r="K99" t="s">
@@ -6382,14 +6382,14 @@
     </row>
     <row r="100" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A100">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1030210</v>
       </c>
       <c r="B100" s="7">
         <v>210</v>
       </c>
       <c r="C100">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1300210</v>
       </c>
       <c r="D100" t="s">
@@ -6411,7 +6411,7 @@
         <v>71</v>
       </c>
       <c r="J100">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030210</v>
       </c>
       <c r="K100" t="s">
@@ -6423,14 +6423,14 @@
     </row>
     <row r="101" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A101">
-        <f t="shared" ref="A101:A132" si="13">1000000+E101*10000+B101</f>
+        <f t="shared" ref="A101:A132" si="16">1000000+E101*10000+B101</f>
         <v>1030211</v>
       </c>
       <c r="B101" s="7">
         <v>211</v>
       </c>
       <c r="C101">
-        <f t="shared" ref="C101:C130" si="14">1000000+E101*100000+B101</f>
+        <f t="shared" ref="C101:C130" si="17">1000000+E101*100000+B101</f>
         <v>1300211</v>
       </c>
       <c r="D101" t="s">
@@ -6452,7 +6452,7 @@
         <v>71</v>
       </c>
       <c r="J101">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030211</v>
       </c>
       <c r="K101" t="s">
@@ -6464,14 +6464,14 @@
     </row>
     <row r="102" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030212</v>
       </c>
       <c r="B102" s="7">
         <v>212</v>
       </c>
       <c r="C102">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300212</v>
       </c>
       <c r="D102" t="s">
@@ -6493,7 +6493,7 @@
         <v>71</v>
       </c>
       <c r="J102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030212</v>
       </c>
       <c r="K102" t="s">
@@ -6505,14 +6505,14 @@
     </row>
     <row r="103" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030221</v>
       </c>
       <c r="B103" s="7">
         <v>221</v>
       </c>
       <c r="C103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300221</v>
       </c>
       <c r="D103" t="s">
@@ -6534,7 +6534,7 @@
         <v>71</v>
       </c>
       <c r="J103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030221</v>
       </c>
       <c r="K103" t="s">
@@ -6546,14 +6546,14 @@
     </row>
     <row r="104" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A104">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030222</v>
       </c>
       <c r="B104" s="7">
         <v>222</v>
       </c>
       <c r="C104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300222</v>
       </c>
       <c r="D104" t="s">
@@ -6575,7 +6575,7 @@
         <v>71</v>
       </c>
       <c r="J104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030222</v>
       </c>
       <c r="K104" t="s">
@@ -6587,14 +6587,14 @@
     </row>
     <row r="105" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030223</v>
       </c>
       <c r="B105" s="7">
         <v>223</v>
       </c>
       <c r="C105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300223</v>
       </c>
       <c r="D105" t="s">
@@ -6616,7 +6616,7 @@
         <v>71</v>
       </c>
       <c r="J105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030223</v>
       </c>
       <c r="K105" t="s">
@@ -6628,14 +6628,14 @@
     </row>
     <row r="106" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A106">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030224</v>
       </c>
       <c r="B106" s="7">
         <v>224</v>
       </c>
       <c r="C106">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300224</v>
       </c>
       <c r="D106" t="s">
@@ -6657,7 +6657,7 @@
         <v>71</v>
       </c>
       <c r="J106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030224</v>
       </c>
       <c r="K106" t="s">
@@ -6669,14 +6669,14 @@
     </row>
     <row r="107" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A107">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030225</v>
       </c>
       <c r="B107" s="7">
         <v>225</v>
       </c>
       <c r="C107">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300225</v>
       </c>
       <c r="D107" t="s">
@@ -6698,7 +6698,7 @@
         <v>71</v>
       </c>
       <c r="J107">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030225</v>
       </c>
       <c r="K107" t="s">
@@ -6710,14 +6710,14 @@
     </row>
     <row r="108" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A108">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030226</v>
       </c>
       <c r="B108" s="7">
         <v>226</v>
       </c>
       <c r="C108">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300226</v>
       </c>
       <c r="D108" t="s">
@@ -6739,7 +6739,7 @@
         <v>71</v>
       </c>
       <c r="J108">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030226</v>
       </c>
       <c r="K108" t="s">
@@ -6751,14 +6751,14 @@
     </row>
     <row r="109" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A109">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030227</v>
       </c>
       <c r="B109" s="7">
         <v>227</v>
       </c>
       <c r="C109">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300227</v>
       </c>
       <c r="D109" t="s">
@@ -6780,7 +6780,7 @@
         <v>71</v>
       </c>
       <c r="J109">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030227</v>
       </c>
       <c r="K109" t="s">
@@ -6792,14 +6792,14 @@
     </row>
     <row r="110" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A110">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030228</v>
       </c>
       <c r="B110" s="7">
         <v>228</v>
       </c>
       <c r="C110">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300228</v>
       </c>
       <c r="D110" t="s">
@@ -6821,7 +6821,7 @@
         <v>71</v>
       </c>
       <c r="J110">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030228</v>
       </c>
       <c r="K110" t="s">
@@ -6833,14 +6833,14 @@
     </row>
     <row r="111" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A111">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030229</v>
       </c>
       <c r="B111" s="7">
         <v>229</v>
       </c>
       <c r="C111">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300229</v>
       </c>
       <c r="D111" t="s">
@@ -6862,7 +6862,7 @@
         <v>71</v>
       </c>
       <c r="J111">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030229</v>
       </c>
       <c r="K111" t="s">
@@ -6874,14 +6874,14 @@
     </row>
     <row r="112" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A112">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030230</v>
       </c>
       <c r="B112" s="7">
         <v>230</v>
       </c>
       <c r="C112">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300230</v>
       </c>
       <c r="D112" t="s">
@@ -6903,7 +6903,7 @@
         <v>71</v>
       </c>
       <c r="J112">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030230</v>
       </c>
       <c r="K112" t="s">
@@ -6915,14 +6915,14 @@
     </row>
     <row r="113" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A113">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030231</v>
       </c>
       <c r="B113" s="7">
         <v>231</v>
       </c>
       <c r="C113">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300231</v>
       </c>
       <c r="D113" t="s">
@@ -6944,7 +6944,7 @@
         <v>71</v>
       </c>
       <c r="J113">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030231</v>
       </c>
       <c r="K113" t="s">
@@ -6956,14 +6956,14 @@
     </row>
     <row r="114" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A114">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030232</v>
       </c>
       <c r="B114" s="7">
         <v>232</v>
       </c>
       <c r="C114">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300232</v>
       </c>
       <c r="D114" t="s">
@@ -6985,7 +6985,7 @@
         <v>71</v>
       </c>
       <c r="J114">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030232</v>
       </c>
       <c r="K114" t="s">
@@ -6997,14 +6997,14 @@
     </row>
     <row r="115" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A115">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030241</v>
       </c>
       <c r="B115" s="7">
         <v>241</v>
       </c>
       <c r="C115">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300241</v>
       </c>
       <c r="D115" t="s">
@@ -7026,7 +7026,7 @@
         <v>71</v>
       </c>
       <c r="J115">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030241</v>
       </c>
       <c r="K115" t="s">
@@ -7038,14 +7038,14 @@
     </row>
     <row r="116" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A116">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030242</v>
       </c>
       <c r="B116" s="7">
         <v>242</v>
       </c>
       <c r="C116">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300242</v>
       </c>
       <c r="D116" t="s">
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="J116">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030242</v>
       </c>
       <c r="K116" t="s">
@@ -7079,14 +7079,14 @@
     </row>
     <row r="117" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A117">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030243</v>
       </c>
       <c r="B117" s="7">
         <v>243</v>
       </c>
       <c r="C117">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300243</v>
       </c>
       <c r="D117" t="s">
@@ -7108,7 +7108,7 @@
         <v>71</v>
       </c>
       <c r="J117">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030243</v>
       </c>
       <c r="K117" t="s">
@@ -7120,14 +7120,14 @@
     </row>
     <row r="118" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A118">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030244</v>
       </c>
       <c r="B118" s="7">
         <v>244</v>
       </c>
       <c r="C118">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300244</v>
       </c>
       <c r="D118" t="s">
@@ -7149,7 +7149,7 @@
         <v>71</v>
       </c>
       <c r="J118">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030244</v>
       </c>
       <c r="K118" t="s">
@@ -7161,14 +7161,14 @@
     </row>
     <row r="119" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A119">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030245</v>
       </c>
       <c r="B119" s="7">
         <v>245</v>
       </c>
       <c r="C119">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300245</v>
       </c>
       <c r="D119" t="s">
@@ -7190,7 +7190,7 @@
         <v>71</v>
       </c>
       <c r="J119">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030245</v>
       </c>
       <c r="K119" t="s">
@@ -7202,14 +7202,14 @@
     </row>
     <row r="120" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A120">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030246</v>
       </c>
       <c r="B120" s="7">
         <v>246</v>
       </c>
       <c r="C120">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300246</v>
       </c>
       <c r="D120" t="s">
@@ -7231,7 +7231,7 @@
         <v>71</v>
       </c>
       <c r="J120">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030246</v>
       </c>
       <c r="K120" t="s">
@@ -7243,14 +7243,14 @@
     </row>
     <row r="121" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A121">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030247</v>
       </c>
       <c r="B121" s="7">
         <v>247</v>
       </c>
       <c r="C121">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300247</v>
       </c>
       <c r="D121" t="s">
@@ -7272,7 +7272,7 @@
         <v>71</v>
       </c>
       <c r="J121">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030247</v>
       </c>
       <c r="K121" t="s">
@@ -7284,14 +7284,14 @@
     </row>
     <row r="122" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A122">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030248</v>
       </c>
       <c r="B122" s="7">
         <v>248</v>
       </c>
       <c r="C122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300248</v>
       </c>
       <c r="D122" t="s">
@@ -7313,7 +7313,7 @@
         <v>71</v>
       </c>
       <c r="J122">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030248</v>
       </c>
       <c r="K122" t="s">
@@ -7325,14 +7325,14 @@
     </row>
     <row r="123" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A123">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030249</v>
       </c>
       <c r="B123" s="7">
         <v>249</v>
       </c>
       <c r="C123">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300249</v>
       </c>
       <c r="D123" t="s">
@@ -7354,7 +7354,7 @@
         <v>71</v>
       </c>
       <c r="J123">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030249</v>
       </c>
       <c r="K123" t="s">
@@ -7366,14 +7366,14 @@
     </row>
     <row r="124" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A124">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030250</v>
       </c>
       <c r="B124" s="7">
         <v>250</v>
       </c>
       <c r="C124">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300250</v>
       </c>
       <c r="D124" t="s">
@@ -7395,7 +7395,7 @@
         <v>71</v>
       </c>
       <c r="J124">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030250</v>
       </c>
       <c r="K124" t="s">
@@ -7407,14 +7407,14 @@
     </row>
     <row r="125" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A125">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030251</v>
       </c>
       <c r="B125" s="7">
         <v>251</v>
       </c>
       <c r="C125">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300251</v>
       </c>
       <c r="D125" t="s">
@@ -7436,7 +7436,7 @@
         <v>71</v>
       </c>
       <c r="J125">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030251</v>
       </c>
       <c r="K125" t="s">
@@ -7448,14 +7448,14 @@
     </row>
     <row r="126" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A126">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1030252</v>
       </c>
       <c r="B126" s="7">
         <v>252</v>
       </c>
       <c r="C126">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1300252</v>
       </c>
       <c r="D126" t="s">
@@ -7477,7 +7477,7 @@
         <v>71</v>
       </c>
       <c r="J126">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2030252</v>
       </c>
       <c r="K126" t="s">
@@ -7489,14 +7489,14 @@
     </row>
     <row r="127" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A127">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1031001</v>
       </c>
       <c r="B127" s="7">
         <v>1001</v>
       </c>
       <c r="C127">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1301001</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -7519,7 +7519,7 @@
         <v>itemicon_1031001.png</v>
       </c>
       <c r="J127">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2031001</v>
       </c>
       <c r="L127">
@@ -7532,14 +7532,14 @@
     </row>
     <row r="128" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A128">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1031002</v>
       </c>
       <c r="B128" s="7">
         <v>1002</v>
       </c>
       <c r="C128">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1301002</v>
       </c>
       <c r="D128" s="7" t="s">
@@ -7562,7 +7562,7 @@
         <v>itemicon_1031002.png</v>
       </c>
       <c r="J128">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2031002</v>
       </c>
       <c r="L128">
@@ -7575,14 +7575,14 @@
     </row>
     <row r="129" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A129">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1031201</v>
       </c>
       <c r="B129" s="7">
         <v>1201</v>
       </c>
       <c r="C129">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1301201</v>
       </c>
       <c r="D129" t="s">
@@ -7605,7 +7605,7 @@
         <v>itemicon_1031201.png</v>
       </c>
       <c r="J129">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2031201</v>
       </c>
       <c r="L129">
@@ -7618,14 +7618,14 @@
     </row>
     <row r="130" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A130">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1031202</v>
       </c>
       <c r="B130" s="7">
         <v>1202</v>
       </c>
       <c r="C130">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1301202</v>
       </c>
       <c r="D130" t="s">
@@ -7648,7 +7648,7 @@
         <v>itemicon_1031202.png</v>
       </c>
       <c r="J130">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2031202</v>
       </c>
       <c r="L130">
@@ -7661,7 +7661,7 @@
     </row>
     <row r="131" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A131">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1031350</v>
       </c>
       <c r="B131" s="7">
@@ -7700,7 +7700,7 @@
     </row>
     <row r="132" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A132">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1031351</v>
       </c>
       <c r="B132" s="7">
@@ -7739,14 +7739,14 @@
     </row>
     <row r="133" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A133">
-        <f t="shared" ref="A133:A146" si="15">1000000+E133*10000+B133</f>
+        <f t="shared" ref="A133:A146" si="18">1000000+E133*10000+B133</f>
         <v>1021401</v>
       </c>
       <c r="B133" s="7">
         <v>1401</v>
       </c>
       <c r="C133">
-        <f t="shared" ref="C133:C146" si="16">1000000+E133*100000+B133</f>
+        <f t="shared" ref="C133:C146" si="19">1000000+E133*100000+B133</f>
         <v>1201401</v>
       </c>
       <c r="D133" s="10" t="s">
@@ -7765,11 +7765,11 @@
         <v>1</v>
       </c>
       <c r="I133" t="str">
-        <f t="shared" ref="I133:I146" si="17">"itemicon_"&amp;A133&amp;".png"</f>
+        <f t="shared" ref="I133:I146" si="20">"itemicon_"&amp;A133&amp;".png"</f>
         <v>itemicon_1021401.png</v>
       </c>
       <c r="J133">
-        <f t="shared" ref="J133:J146" si="18">2000000+E133*10000+B133</f>
+        <f t="shared" ref="J133:J146" si="21">2000000+E133*10000+B133</f>
         <v>2021401</v>
       </c>
       <c r="L133">
@@ -7782,14 +7782,14 @@
     </row>
     <row r="134" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A134">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1021402</v>
       </c>
       <c r="B134" s="7">
         <v>1402</v>
       </c>
       <c r="C134">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1201402</v>
       </c>
       <c r="D134" s="10" t="s">
@@ -7808,11 +7808,11 @@
         <v>1</v>
       </c>
       <c r="I134" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1021402.png</v>
       </c>
       <c r="J134">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2021402</v>
       </c>
       <c r="L134">
@@ -7825,14 +7825,14 @@
     </row>
     <row r="135" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A135">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1031601</v>
       </c>
       <c r="B135" s="7">
         <v>1601</v>
       </c>
       <c r="C135">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1301601</v>
       </c>
       <c r="D135" s="11" t="s">
@@ -7851,11 +7851,11 @@
         <v>1</v>
       </c>
       <c r="I135" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1031601.png</v>
       </c>
       <c r="J135">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2031601</v>
       </c>
       <c r="L135">
@@ -7868,14 +7868,14 @@
     </row>
     <row r="136" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A136">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1031602</v>
       </c>
       <c r="B136" s="7">
         <v>1602</v>
       </c>
       <c r="C136">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1301602</v>
       </c>
       <c r="D136" s="11" t="s">
@@ -7894,11 +7894,11 @@
         <v>1</v>
       </c>
       <c r="I136" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1031602.png</v>
       </c>
       <c r="J136">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2031602</v>
       </c>
       <c r="L136">
@@ -7911,14 +7911,14 @@
     </row>
     <row r="137" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A137">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1031801</v>
       </c>
       <c r="B137" s="7">
         <v>1801</v>
       </c>
       <c r="C137">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1301801</v>
       </c>
       <c r="D137" s="12" t="s">
@@ -7937,11 +7937,11 @@
         <v>1</v>
       </c>
       <c r="I137" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1031801.png</v>
       </c>
       <c r="J137">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2031801</v>
       </c>
       <c r="L137">
@@ -7954,14 +7954,14 @@
     </row>
     <row r="138" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A138">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1031802</v>
       </c>
       <c r="B138" s="7">
         <v>1802</v>
       </c>
       <c r="C138">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1301802</v>
       </c>
       <c r="D138" s="12" t="s">
@@ -7980,11 +7980,11 @@
         <v>1</v>
       </c>
       <c r="I138" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1031802.png</v>
       </c>
       <c r="J138">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2031802</v>
       </c>
       <c r="L138">
@@ -7997,14 +7997,14 @@
     </row>
     <row r="139" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A139">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1032001</v>
       </c>
       <c r="B139" s="7">
         <v>2001</v>
       </c>
       <c r="C139">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1302001</v>
       </c>
       <c r="D139" s="13" t="s">
@@ -8023,11 +8023,11 @@
         <v>1</v>
       </c>
       <c r="I139" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1032001.png</v>
       </c>
       <c r="J139">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2032001</v>
       </c>
       <c r="L139">
@@ -8040,14 +8040,14 @@
     </row>
     <row r="140" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A140">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1032002</v>
       </c>
       <c r="B140" s="7">
         <v>2002</v>
       </c>
       <c r="C140">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1302002</v>
       </c>
       <c r="D140" s="13" t="s">
@@ -8066,11 +8066,11 @@
         <v>1</v>
       </c>
       <c r="I140" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1032002.png</v>
       </c>
       <c r="J140">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2032002</v>
       </c>
       <c r="L140">
@@ -8083,14 +8083,14 @@
     </row>
     <row r="141" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A141">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1032201</v>
       </c>
       <c r="B141" s="7">
         <v>2201</v>
       </c>
       <c r="C141">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1302201</v>
       </c>
       <c r="D141" s="14" t="s">
@@ -8109,11 +8109,11 @@
         <v>1</v>
       </c>
       <c r="I141" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1032201.png</v>
       </c>
       <c r="J141">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2032201</v>
       </c>
       <c r="L141">
@@ -8126,14 +8126,14 @@
     </row>
     <row r="142" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A142">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1032202</v>
       </c>
       <c r="B142" s="7">
         <v>2202</v>
       </c>
       <c r="C142">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1302202</v>
       </c>
       <c r="D142" s="14" t="s">
@@ -8152,11 +8152,11 @@
         <v>1</v>
       </c>
       <c r="I142" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1032202.png</v>
       </c>
       <c r="J142">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2032202</v>
       </c>
       <c r="L142">
@@ -8169,14 +8169,14 @@
     </row>
     <row r="143" ht="18" customHeight="1" spans="1:14">
       <c r="A143">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1022501</v>
       </c>
       <c r="B143">
         <v>2501</v>
       </c>
       <c r="C143">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1202501</v>
       </c>
       <c r="D143" t="s">
@@ -8195,11 +8195,11 @@
         <v>0</v>
       </c>
       <c r="I143" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1022501.png</v>
       </c>
       <c r="J143">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2022501</v>
       </c>
       <c r="K143" t="s">
@@ -8211,14 +8211,14 @@
     </row>
     <row r="144" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A144">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1022502</v>
       </c>
       <c r="B144">
         <v>2502</v>
       </c>
       <c r="C144">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1202502</v>
       </c>
       <c r="D144" t="s">
@@ -8237,11 +8237,11 @@
         <v>0</v>
       </c>
       <c r="I144" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1022502.png</v>
       </c>
       <c r="J144">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2022502</v>
       </c>
       <c r="K144" t="s">
@@ -8254,16 +8254,16 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="145" customFormat="1" ht="18" customHeight="1" spans="1:14">
+    <row r="145" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A145">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1022503</v>
       </c>
       <c r="B145">
         <v>2503</v>
       </c>
       <c r="C145">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1202503</v>
       </c>
       <c r="D145" t="s">
@@ -8282,11 +8282,11 @@
         <v>0</v>
       </c>
       <c r="I145" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1022503.png</v>
       </c>
       <c r="J145">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2022503</v>
       </c>
       <c r="K145" t="s">
@@ -8295,17 +8295,20 @@
       <c r="N145">
         <v>999</v>
       </c>
+      <c r="Q145">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="146" customFormat="1" ht="18" customHeight="1" spans="1:14">
       <c r="A146">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1022504</v>
       </c>
       <c r="B146">
         <v>2504</v>
       </c>
       <c r="C146">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1202504</v>
       </c>
       <c r="D146" t="s">
@@ -8324,11 +8327,11 @@
         <v>0</v>
       </c>
       <c r="I146" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>itemicon_1022504.png</v>
       </c>
       <c r="J146">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2022504</v>
       </c>
       <c r="K146" t="s">
@@ -8338,7 +8341,7 @@
         <v>999999999</v>
       </c>
     </row>
-    <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A147">
         <v>1023001</v>
       </c>
@@ -8373,8 +8376,11 @@
       <c r="N147">
         <v>999</v>
       </c>
-    </row>
-    <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q147">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A148">
         <v>1023002</v>
       </c>
@@ -8409,8 +8415,11 @@
       <c r="N148">
         <v>999</v>
       </c>
-    </row>
-    <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q148">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A149">
         <v>1023003</v>
       </c>
@@ -8445,8 +8454,11 @@
       <c r="N149">
         <v>999</v>
       </c>
-    </row>
-    <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q149">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A150">
         <v>1023004</v>
       </c>
@@ -8481,8 +8493,11 @@
       <c r="N150">
         <v>999</v>
       </c>
-    </row>
-    <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q150">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A151">
         <v>1023005</v>
       </c>
@@ -8517,8 +8532,11 @@
       <c r="N151">
         <v>999</v>
       </c>
-    </row>
-    <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q151">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A152">
         <v>1023101</v>
       </c>
@@ -8553,8 +8571,11 @@
       <c r="N152">
         <v>999</v>
       </c>
-    </row>
-    <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q152">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A153">
         <v>1023102</v>
       </c>
@@ -8589,8 +8610,11 @@
       <c r="N153">
         <v>999</v>
       </c>
-    </row>
-    <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q153">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A154">
         <v>1023103</v>
       </c>
@@ -8625,8 +8649,11 @@
       <c r="N154">
         <v>999</v>
       </c>
-    </row>
-    <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q154">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A155">
         <v>1023104</v>
       </c>
@@ -8661,8 +8688,11 @@
       <c r="N155">
         <v>999</v>
       </c>
-    </row>
-    <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q155">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A156">
         <v>1023105</v>
       </c>
@@ -8697,8 +8727,11 @@
       <c r="N156">
         <v>999</v>
       </c>
-    </row>
-    <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q156">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A157">
         <v>1023201</v>
       </c>
@@ -8733,8 +8766,11 @@
       <c r="N157">
         <v>999</v>
       </c>
-    </row>
-    <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q157">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A158">
         <v>1023202</v>
       </c>
@@ -8769,8 +8805,11 @@
       <c r="N158">
         <v>999</v>
       </c>
-    </row>
-    <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q158">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A159">
         <v>1023203</v>
       </c>
@@ -8805,8 +8844,11 @@
       <c r="N159">
         <v>999</v>
       </c>
-    </row>
-    <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q159">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A160">
         <v>1023204</v>
       </c>
@@ -8841,8 +8883,11 @@
       <c r="N160">
         <v>999</v>
       </c>
-    </row>
-    <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q160">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A161">
         <v>1023205</v>
       </c>
@@ -8877,8 +8922,11 @@
       <c r="N161">
         <v>999</v>
       </c>
-    </row>
-    <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q161">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A162">
         <v>1023301</v>
       </c>
@@ -8913,8 +8961,11 @@
       <c r="N162">
         <v>999</v>
       </c>
-    </row>
-    <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q162">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A163">
         <v>1023302</v>
       </c>
@@ -8949,8 +9000,11 @@
       <c r="N163">
         <v>999</v>
       </c>
-    </row>
-    <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q163">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A164">
         <v>1023303</v>
       </c>
@@ -8985,8 +9039,11 @@
       <c r="N164">
         <v>999</v>
       </c>
-    </row>
-    <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q164">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A165">
         <v>1023304</v>
       </c>
@@ -9021,8 +9078,11 @@
       <c r="N165">
         <v>999</v>
       </c>
-    </row>
-    <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q165">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A166">
         <v>1023305</v>
       </c>
@@ -9057,8 +9117,11 @@
       <c r="N166">
         <v>999</v>
       </c>
-    </row>
-    <row r="167" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q166">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A167">
         <v>1023401</v>
       </c>
@@ -9093,8 +9156,11 @@
       <c r="N167">
         <v>999</v>
       </c>
-    </row>
-    <row r="168" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q167">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="168" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A168">
         <v>1023402</v>
       </c>
@@ -9129,8 +9195,11 @@
       <c r="N168">
         <v>999</v>
       </c>
-    </row>
-    <row r="169" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q168">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="169" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A169">
         <v>1023403</v>
       </c>
@@ -9165,8 +9234,11 @@
       <c r="N169">
         <v>999</v>
       </c>
-    </row>
-    <row r="170" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q169">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A170">
         <v>1023404</v>
       </c>
@@ -9201,8 +9273,11 @@
       <c r="N170">
         <v>999</v>
       </c>
-    </row>
-    <row r="171" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q170">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A171">
         <v>1023405</v>
       </c>
@@ -9236,6 +9311,9 @@
       </c>
       <c r="N171">
         <v>999</v>
+      </c>
+      <c r="Q171">
+        <v>57.6</v>
       </c>
     </row>
     <row r="172" ht="21" customHeight="1" spans="1:14">

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -157,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F125" authorId="0">
+    <comment ref="F127" authorId="0">
       <text>
         <r>
           <rPr>
@@ -179,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F170" authorId="0">
+    <comment ref="F172" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="253">
   <si>
     <t>道具ID</t>
   </si>
@@ -247,6 +247,9 @@
     <t>掉落ID</t>
   </si>
   <si>
+    <t>价值</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -313,19 +316,34 @@
     <t>1980000_10000</t>
   </si>
   <si>
-    <t>赌场材料随机包(普通)</t>
+    <t>赌场工具（普通）</t>
   </si>
   <si>
     <t>itemicon_1010101.png</t>
   </si>
   <si>
-    <t>使用后随机获得N个赌赌场材料道具</t>
-  </si>
-  <si>
-    <t>赌场材料随机包(豪华)</t>
-  </si>
-  <si>
-    <t>赌场材料随机包(尊贵)</t>
+    <t>使用后随机获得1~2星赌场建筑升级道具</t>
+  </si>
+  <si>
+    <t>赌场工具（精良）</t>
+  </si>
+  <si>
+    <t>赌场工具（优秀）</t>
+  </si>
+  <si>
+    <t>使用后随机获得1~3星赌场建筑升级道具</t>
+  </si>
+  <si>
+    <t>赌场工具（绝佳）</t>
+  </si>
+  <si>
+    <t>使用后随机获得1~4星赌场建筑升级道具</t>
+  </si>
+  <si>
+    <t>赌场工具（传奇）</t>
+  </si>
+  <si>
+    <t>使用后随机获得1~5星赌场建筑升级道具</t>
   </si>
   <si>
     <t>拼图随机礼包(一星)</t>
@@ -1125,12 +1143,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2214,7 +2232,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P171"/>
+  <dimension ref="A1:Q173"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
@@ -2235,7 +2253,7 @@
     <col min="20" max="20" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2277,88 +2295,91 @@
       <c r="P1" t="s">
         <v>12</v>
       </c>
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2367,7 +2388,7 @@
     </row>
     <row r="5" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A5">
-        <f t="shared" ref="A5:A14" si="0">1000000+E5*10000+B5</f>
+        <f t="shared" ref="A5:A16" si="0">1000000+E5*10000+B5</f>
         <v>1010101</v>
       </c>
       <c r="B5" s="7">
@@ -2377,13 +2398,13 @@
         <v>1010101</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -2396,17 +2417,17 @@
         <v>itemicon_1010101.png</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5:J14" si="1">2000000+E5*10000+B5</f>
+        <f t="shared" ref="J5:J16" si="1">2000000+E5*10000+B5</f>
         <v>2010101</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5">
         <v>999</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="21" customHeight="1" spans="1:15">
@@ -2421,13 +2442,13 @@
         <v>1010201</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -2444,16 +2465,16 @@
         <v>2010201</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N6">
         <v>999</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1010301</v>
@@ -2462,43 +2483,46 @@
         <v>301</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" ref="C7:C14" si="2">1000000+E7*100000+B7</f>
+        <f t="shared" ref="C7:C16" si="2">1000000+E7*100000+B7</f>
         <v>1100301</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" si="1"/>
         <v>2010301</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N7" s="1">
         <v>999</v>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="1">
-        <v>100003</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>1010301</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>1010302</v>
@@ -2511,39 +2535,42 @@
         <v>1100302</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="1"/>
         <v>2010302</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N8" s="1">
         <v>999</v>
       </c>
       <c r="O8" s="9"/>
       <c r="P8" s="1">
-        <v>100004</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>1010302</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>1010303</v>
@@ -2556,426 +2583,441 @@
         <v>1100303</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" si="1"/>
         <v>2010303</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N9" s="1">
         <v>999</v>
       </c>
       <c r="O9" s="9"/>
       <c r="P9" s="1">
-        <v>100005</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>1010303</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>1010311</v>
+        <v>1010304</v>
       </c>
       <c r="B10" s="1">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="2"/>
-        <v>1100311</v>
+        <v>1100304</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" si="1"/>
-        <v>2010311</v>
+        <v>2010304</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N10" s="1">
         <v>999</v>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="1">
-        <v>100006</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+        <v>1010304</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>1010312</v>
+        <v>1010305</v>
       </c>
       <c r="B11" s="1">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="2"/>
-        <v>1100312</v>
+        <v>1100305</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" si="1"/>
-        <v>2010312</v>
+        <v>2010305</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N11" s="1">
         <v>999</v>
       </c>
       <c r="O11" s="9"/>
       <c r="P11" s="1">
-        <v>100007</v>
+        <v>1010305</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>49.99</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>1010313</v>
+        <v>1010311</v>
       </c>
       <c r="B12" s="1">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="2"/>
-        <v>1100313</v>
+        <v>1100311</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="1"/>
-        <v>2010313</v>
+        <v>2010311</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N12" s="1">
         <v>999</v>
       </c>
       <c r="O12" s="9"/>
       <c r="P12" s="1">
-        <v>100008</v>
+        <v>100006</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>1010314</v>
+        <v>1010312</v>
       </c>
       <c r="B13" s="1">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="2"/>
-        <v>1100314</v>
+        <v>1100312</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" si="1"/>
-        <v>2010314</v>
+        <v>2010312</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N13" s="1">
         <v>999</v>
       </c>
       <c r="O13" s="9"/>
       <c r="P13" s="1">
-        <v>100009</v>
+        <v>100007</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>1010315</v>
+        <v>1010313</v>
       </c>
       <c r="B14" s="1">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="2"/>
-        <v>1100315</v>
+        <v>1100313</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" si="1"/>
-        <v>2010315</v>
+        <v>2010313</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N14" s="1">
         <v>999</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="1">
-        <v>100010</v>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1" spans="1:14">
-      <c r="A15">
-        <f t="shared" ref="A15:A29" si="3">1000000+E15*10000+B15</f>
-        <v>1020001</v>
-      </c>
-      <c r="B15" s="7">
-        <f>COUNTIF($F$1:F15,F15)</f>
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>1020001</v>
-      </c>
-      <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
+        <v>100008</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>1010314</v>
+      </c>
+      <c r="B15" s="1">
+        <v>314</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="2"/>
+        <v>1100314</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15" t="str">
-        <f t="shared" ref="I15:I28" si="4">"itemicon_"&amp;A15&amp;".png"</f>
+      <c r="I15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="1"/>
+        <v>2010314</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N15" s="1">
+        <v>999</v>
+      </c>
+      <c r="O15" s="9"/>
+      <c r="P15" s="1">
+        <v>100009</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>1010315</v>
+      </c>
+      <c r="B16" s="1">
+        <v>315</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="2"/>
+        <v>1100315</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="1">
+        <v>6</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="1"/>
+        <v>2010315</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N16" s="1">
+        <v>999</v>
+      </c>
+      <c r="O16" s="9"/>
+      <c r="P16" s="1">
+        <v>100010</v>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1" spans="1:14">
+      <c r="A17">
+        <f t="shared" ref="A17:A31" si="3">1000000+E17*10000+B17</f>
+        <v>1020001</v>
+      </c>
+      <c r="B17" s="7">
+        <f>COUNTIF($F$1:F17,F17)</f>
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1020001</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" ref="I17:I30" si="4">"itemicon_"&amp;A17&amp;".png"</f>
         <v>itemicon_1020001.png</v>
       </c>
-      <c r="J15">
-        <f t="shared" ref="J15:J29" si="5">2000000+E15*10000+B15</f>
+      <c r="J17">
+        <f t="shared" ref="J17:J31" si="5">2000000+E17*10000+B17</f>
         <v>2020001</v>
       </c>
-      <c r="K15" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
-      <c r="A16" s="2">
-        <f t="shared" si="3"/>
-        <v>1020002</v>
-      </c>
-      <c r="B16" s="2">
-        <f>COUNTIF($F$1:F16,F16)</f>
-        <v>2</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1020002</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="2">
-        <v>2</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020002.png</v>
-      </c>
-      <c r="J16" s="2">
-        <f t="shared" si="5"/>
-        <v>2020002</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N16" s="2">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
-      <c r="A17" s="2">
-        <f t="shared" si="3"/>
-        <v>1020003</v>
-      </c>
-      <c r="B17" s="2">
-        <f>COUNTIF($F$1:F17,F17)</f>
-        <v>3</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1020003</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="2">
-        <v>2</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="2">
-        <v>3</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020003.png</v>
-      </c>
-      <c r="J17" s="2">
-        <f t="shared" si="5"/>
-        <v>2020003</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N17" s="2">
+      <c r="K17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17">
         <v>999</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A18" s="2">
         <f t="shared" si="3"/>
-        <v>1020004</v>
+        <v>1020002</v>
       </c>
       <c r="B18" s="2">
         <f>COUNTIF($F$1:F18,F18)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2">
-        <v>1020004</v>
+        <v>1020002</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2">
         <v>2</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020004.png</v>
+        <v>itemicon_1020002.png</v>
       </c>
       <c r="J18" s="2">
         <f t="shared" si="5"/>
-        <v>2020004</v>
+        <v>2020002</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="N18" s="2">
         <v>999</v>
@@ -2984,40 +3026,40 @@
     <row r="19" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A19" s="2">
         <f t="shared" si="3"/>
-        <v>1020005</v>
+        <v>1020003</v>
       </c>
       <c r="B19" s="2">
         <f>COUNTIF($F$1:F19,F19)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" s="2">
-        <v>1020005</v>
+        <v>1020003</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2">
         <v>2</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G19" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020005.png</v>
+        <v>itemicon_1020003.png</v>
       </c>
       <c r="J19" s="2">
         <f t="shared" si="5"/>
-        <v>2020005</v>
+        <v>2020003</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="N19" s="2">
         <v>999</v>
@@ -3026,155 +3068,149 @@
     <row r="20" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A20" s="2">
         <f t="shared" si="3"/>
-        <v>1020006</v>
+        <v>1020004</v>
       </c>
       <c r="B20" s="2">
         <f>COUNTIF($F$1:F20,F20)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" s="2">
-        <v>1020006</v>
+        <v>1020004</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2">
         <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G20" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1020006.png</v>
+        <v>itemicon_1020004.png</v>
       </c>
       <c r="J20" s="2">
         <f t="shared" si="5"/>
-        <v>2020006</v>
+        <v>2020004</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="N20" s="2">
         <v>999</v>
       </c>
     </row>
-    <row r="21" ht="23" customHeight="1" spans="1:14">
-      <c r="A21">
+    <row r="21" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A21" s="2">
         <f t="shared" si="3"/>
-        <v>1030011</v>
-      </c>
-      <c r="B21" s="7">
-        <v>11</v>
-      </c>
-      <c r="C21">
-        <f t="shared" ref="C21:C29" si="6">1000000+E21*100000+B21</f>
-        <v>1300011</v>
-      </c>
-      <c r="D21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21">
-        <v>3</v>
-      </c>
-      <c r="F21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
+        <v>1020005</v>
+      </c>
+      <c r="B21" s="2">
+        <f>COUNTIF($F$1:F21,F21)</f>
+        <v>5</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1020005</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="2">
+        <v>5</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
-      <c r="I21" t="str">
+      <c r="I21" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1030011.png</v>
-      </c>
-      <c r="J21">
+        <v>itemicon_1020005.png</v>
+      </c>
+      <c r="J21" s="2">
         <f t="shared" si="5"/>
-        <v>2030011</v>
-      </c>
-      <c r="K21" t="s">
+        <v>2020005</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M21">
-        <v>10001</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="23" customHeight="1" spans="1:14">
-      <c r="A22">
+      <c r="N21" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A22" s="2">
         <f t="shared" si="3"/>
-        <v>1030012</v>
-      </c>
-      <c r="B22" s="7">
-        <v>12</v>
-      </c>
-      <c r="C22">
-        <f t="shared" si="6"/>
-        <v>1300012</v>
-      </c>
-      <c r="D22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
+        <v>1020006</v>
+      </c>
+      <c r="B22" s="2">
+        <f>COUNTIF($F$1:F22,F22)</f>
+        <v>6</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1020006</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
-      <c r="I22" t="str">
+      <c r="I22" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1030012.png</v>
-      </c>
-      <c r="J22">
+        <v>itemicon_1020006.png</v>
+      </c>
+      <c r="J22" s="2">
         <f t="shared" si="5"/>
-        <v>2030012</v>
-      </c>
-      <c r="K22" t="s">
+        <v>2020006</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M22">
-        <v>10002</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
+      <c r="N22" s="2">
+        <v>999</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1" spans="1:14">
       <c r="A23">
         <f t="shared" si="3"/>
-        <v>1030013</v>
+        <v>1030011</v>
       </c>
       <c r="B23" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C23">
-        <f t="shared" si="6"/>
-        <v>1300013</v>
+        <f t="shared" ref="C23:C31" si="6">1000000+E23*100000+B23</f>
+        <v>1300011</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3184,17 +3220,17 @@
       </c>
       <c r="I23" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1030013.png</v>
+        <v>itemicon_1030011.png</v>
       </c>
       <c r="J23">
         <f t="shared" si="5"/>
-        <v>2030013</v>
+        <v>2030011</v>
       </c>
       <c r="K23" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M23">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="N23">
         <v>1</v>
@@ -3203,23 +3239,23 @@
     <row r="24" ht="23" customHeight="1" spans="1:14">
       <c r="A24">
         <f t="shared" si="3"/>
-        <v>1030014</v>
+        <v>1030012</v>
       </c>
       <c r="B24" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C24">
         <f t="shared" si="6"/>
-        <v>1300014</v>
+        <v>1300012</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -3229,17 +3265,17 @@
       </c>
       <c r="I24" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1030014.png</v>
+        <v>itemicon_1030012.png</v>
       </c>
       <c r="J24">
         <f t="shared" si="5"/>
-        <v>2030014</v>
+        <v>2030012</v>
       </c>
       <c r="K24" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M24">
-        <v>10004</v>
+        <v>10002</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -3248,23 +3284,23 @@
     <row r="25" ht="23" customHeight="1" spans="1:14">
       <c r="A25">
         <f t="shared" si="3"/>
-        <v>1030015</v>
+        <v>1030013</v>
       </c>
       <c r="B25" s="7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25">
         <f t="shared" si="6"/>
-        <v>1300015</v>
+        <v>1300013</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3274,17 +3310,17 @@
       </c>
       <c r="I25" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1030015.png</v>
+        <v>itemicon_1030013.png</v>
       </c>
       <c r="J25">
         <f t="shared" si="5"/>
-        <v>2030015</v>
+        <v>2030013</v>
       </c>
       <c r="K25" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M25">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -3293,23 +3329,23 @@
     <row r="26" ht="23" customHeight="1" spans="1:14">
       <c r="A26">
         <f t="shared" si="3"/>
-        <v>1030016</v>
+        <v>1030014</v>
       </c>
       <c r="B26" s="7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C26">
         <f t="shared" si="6"/>
-        <v>1300016</v>
+        <v>1300014</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3319,17 +3355,17 @@
       </c>
       <c r="I26" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1030016.png</v>
+        <v>itemicon_1030014.png</v>
       </c>
       <c r="J26">
         <f t="shared" si="5"/>
-        <v>2030016</v>
+        <v>2030014</v>
       </c>
       <c r="K26" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M26">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -3338,23 +3374,23 @@
     <row r="27" ht="23" customHeight="1" spans="1:14">
       <c r="A27">
         <f t="shared" si="3"/>
-        <v>1030017</v>
+        <v>1030015</v>
       </c>
       <c r="B27" s="7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C27">
         <f t="shared" si="6"/>
-        <v>1300017</v>
+        <v>1300015</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3364,17 +3400,17 @@
       </c>
       <c r="I27" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1030017.png</v>
+        <v>itemicon_1030015.png</v>
       </c>
       <c r="J27">
         <f t="shared" si="5"/>
-        <v>2030017</v>
+        <v>2030015</v>
       </c>
       <c r="K27" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M27">
-        <v>10007</v>
+        <v>10005</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -3383,23 +3419,23 @@
     <row r="28" ht="23" customHeight="1" spans="1:14">
       <c r="A28">
         <f t="shared" si="3"/>
-        <v>1030018</v>
+        <v>1030016</v>
       </c>
       <c r="B28" s="7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C28">
         <f t="shared" si="6"/>
-        <v>1300018</v>
+        <v>1300016</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3409,42 +3445,42 @@
       </c>
       <c r="I28" t="str">
         <f t="shared" si="4"/>
-        <v>itemicon_1030018.png</v>
+        <v>itemicon_1030016.png</v>
       </c>
       <c r="J28">
         <f t="shared" si="5"/>
-        <v>2030018</v>
+        <v>2030016</v>
       </c>
       <c r="K28" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M28">
-        <v>10008</v>
+        <v>10006</v>
       </c>
       <c r="N28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="29" ht="23" customHeight="1" spans="1:14">
       <c r="A29">
         <f t="shared" si="3"/>
-        <v>1030101</v>
+        <v>1030017</v>
       </c>
       <c r="B29" s="7">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="C29">
         <f t="shared" si="6"/>
-        <v>1300101</v>
+        <v>1300017</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3452,40 +3488,44 @@
       <c r="H29">
         <v>1</v>
       </c>
-      <c r="I29" t="s">
-        <v>65</v>
+      <c r="I29" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1030017.png</v>
       </c>
       <c r="J29">
         <f t="shared" si="5"/>
-        <v>2030101</v>
+        <v>2030017</v>
       </c>
       <c r="K29" t="s">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="M29">
+        <v>10007</v>
       </c>
       <c r="N29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="30" ht="23" customHeight="1" spans="1:14">
       <c r="A30">
-        <f t="shared" ref="A30:A40" si="7">1000000+E30*10000+B30</f>
-        <v>1030102</v>
+        <f t="shared" si="3"/>
+        <v>1030018</v>
       </c>
       <c r="B30" s="7">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="C30">
-        <f t="shared" ref="C30:C40" si="8">1000000+E30*100000+B30</f>
-        <v>1300102</v>
+        <f t="shared" si="6"/>
+        <v>1300018</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3493,15 +3533,19 @@
       <c r="H30">
         <v>1</v>
       </c>
-      <c r="I30" t="s">
-        <v>65</v>
+      <c r="I30" t="str">
+        <f t="shared" si="4"/>
+        <v>itemicon_1030018.png</v>
       </c>
       <c r="J30">
-        <f t="shared" ref="J30:J61" si="9">2000000+E30*10000+B30</f>
-        <v>2030102</v>
+        <f t="shared" si="5"/>
+        <v>2030018</v>
       </c>
       <c r="K30" t="s">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="M30">
+        <v>10008</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -3509,40 +3553,40 @@
     </row>
     <row r="31" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A31">
-        <f t="shared" si="7"/>
-        <v>1030103</v>
+        <f t="shared" si="3"/>
+        <v>1030101</v>
       </c>
       <c r="B31" s="7">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C31">
-        <f t="shared" si="8"/>
-        <v>1300103</v>
+        <f t="shared" si="6"/>
+        <v>1300101</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J31">
-        <f t="shared" si="9"/>
-        <v>2030103</v>
+        <f t="shared" si="5"/>
+        <v>2030101</v>
       </c>
       <c r="K31" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -3550,40 +3594,40 @@
     </row>
     <row r="32" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A32">
-        <f t="shared" si="7"/>
-        <v>1030104</v>
+        <f t="shared" ref="A32:A42" si="7">1000000+E32*10000+B32</f>
+        <v>1030102</v>
       </c>
       <c r="B32" s="7">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C32">
-        <f t="shared" si="8"/>
-        <v>1300104</v>
+        <f t="shared" ref="C32:C42" si="8">1000000+E32*100000+B32</f>
+        <v>1300102</v>
       </c>
       <c r="D32" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J32">
-        <f t="shared" si="9"/>
-        <v>2030104</v>
+        <f t="shared" ref="J32:J63" si="9">2000000+E32*10000+B32</f>
+        <v>2030102</v>
       </c>
       <c r="K32" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -3592,39 +3636,39 @@
     <row r="33" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A33">
         <f t="shared" si="7"/>
-        <v>1030105</v>
+        <v>1030103</v>
       </c>
       <c r="B33" s="7">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C33">
         <f t="shared" si="8"/>
-        <v>1300105</v>
+        <v>1300103</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E33">
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J33">
         <f t="shared" si="9"/>
-        <v>2030105</v>
+        <v>2030103</v>
       </c>
       <c r="K33" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -3633,39 +3677,39 @@
     <row r="34" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A34">
         <f t="shared" si="7"/>
-        <v>1030106</v>
+        <v>1030104</v>
       </c>
       <c r="B34" s="7">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C34">
         <f t="shared" si="8"/>
-        <v>1300106</v>
+        <v>1300104</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J34">
         <f t="shared" si="9"/>
-        <v>2030106</v>
+        <v>2030104</v>
       </c>
       <c r="K34" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -3674,39 +3718,39 @@
     <row r="35" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A35">
         <f t="shared" si="7"/>
-        <v>1030107</v>
+        <v>1030105</v>
       </c>
       <c r="B35" s="7">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C35">
         <f t="shared" si="8"/>
-        <v>1300107</v>
+        <v>1300105</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E35">
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J35">
         <f t="shared" si="9"/>
-        <v>2030107</v>
+        <v>2030105</v>
       </c>
       <c r="K35" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -3715,39 +3759,39 @@
     <row r="36" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A36">
         <f t="shared" si="7"/>
-        <v>1030108</v>
+        <v>1030106</v>
       </c>
       <c r="B36" s="7">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C36">
         <f t="shared" si="8"/>
-        <v>1300108</v>
+        <v>1300106</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J36">
         <f t="shared" si="9"/>
-        <v>2030108</v>
+        <v>2030106</v>
       </c>
       <c r="K36" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -3756,39 +3800,39 @@
     <row r="37" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A37">
         <f t="shared" si="7"/>
-        <v>1030109</v>
+        <v>1030107</v>
       </c>
       <c r="B37" s="7">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C37">
         <f t="shared" si="8"/>
-        <v>1300109</v>
+        <v>1300107</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J37">
         <f t="shared" si="9"/>
-        <v>2030109</v>
+        <v>2030107</v>
       </c>
       <c r="K37" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -3797,39 +3841,39 @@
     <row r="38" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A38">
         <f t="shared" si="7"/>
-        <v>1030110</v>
+        <v>1030108</v>
       </c>
       <c r="B38" s="7">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C38">
         <f t="shared" si="8"/>
-        <v>1300110</v>
+        <v>1300108</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J38">
         <f t="shared" si="9"/>
-        <v>2030110</v>
+        <v>2030108</v>
       </c>
       <c r="K38" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -3838,39 +3882,39 @@
     <row r="39" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A39">
         <f t="shared" si="7"/>
-        <v>1030111</v>
+        <v>1030109</v>
       </c>
       <c r="B39" s="7">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C39">
         <f t="shared" si="8"/>
-        <v>1300111</v>
+        <v>1300109</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J39">
         <f t="shared" si="9"/>
-        <v>2030111</v>
+        <v>2030109</v>
       </c>
       <c r="K39" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -3879,39 +3923,39 @@
     <row r="40" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A40">
         <f t="shared" si="7"/>
-        <v>1030112</v>
+        <v>1030110</v>
       </c>
       <c r="B40" s="7">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C40">
         <f t="shared" si="8"/>
-        <v>1300112</v>
+        <v>1300110</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J40">
         <f t="shared" si="9"/>
-        <v>2030112</v>
+        <v>2030110</v>
       </c>
       <c r="K40" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -3919,40 +3963,40 @@
     </row>
     <row r="41" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A41">
-        <f t="shared" ref="A41:A66" si="10">1000000+E41*10000+B41</f>
-        <v>1030121</v>
+        <f t="shared" si="7"/>
+        <v>1030111</v>
       </c>
       <c r="B41" s="7">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C41">
-        <f t="shared" ref="C41:C66" si="11">1000000+E41*100000+B41</f>
-        <v>1300121</v>
+        <f t="shared" si="8"/>
+        <v>1300111</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E41">
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J41">
         <f t="shared" si="9"/>
-        <v>2030121</v>
+        <v>2030111</v>
       </c>
       <c r="K41" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N41">
         <v>1</v>
@@ -3960,40 +4004,40 @@
     </row>
     <row r="42" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A42">
-        <f t="shared" si="10"/>
-        <v>1030122</v>
+        <f t="shared" si="7"/>
+        <v>1030112</v>
       </c>
       <c r="B42" s="7">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C42">
-        <f t="shared" si="11"/>
-        <v>1300122</v>
+        <f t="shared" si="8"/>
+        <v>1300112</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J42">
         <f t="shared" si="9"/>
-        <v>2030122</v>
+        <v>2030112</v>
       </c>
       <c r="K42" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -4001,40 +4045,40 @@
     </row>
     <row r="43" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A43">
-        <f t="shared" si="10"/>
-        <v>1030123</v>
+        <f t="shared" ref="A43:A68" si="10">1000000+E43*10000+B43</f>
+        <v>1030121</v>
       </c>
       <c r="B43" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C43">
-        <f t="shared" si="11"/>
-        <v>1300123</v>
+        <f t="shared" ref="C43:C68" si="11">1000000+E43*100000+B43</f>
+        <v>1300121</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J43">
         <f t="shared" si="9"/>
-        <v>2030123</v>
+        <v>2030121</v>
       </c>
       <c r="K43" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N43">
         <v>1</v>
@@ -4043,39 +4087,39 @@
     <row r="44" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A44">
         <f t="shared" si="10"/>
-        <v>1030124</v>
+        <v>1030122</v>
       </c>
       <c r="B44" s="7">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C44">
         <f t="shared" si="11"/>
-        <v>1300124</v>
+        <v>1300122</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E44">
         <v>3</v>
       </c>
       <c r="F44" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J44">
         <f t="shared" si="9"/>
-        <v>2030124</v>
+        <v>2030122</v>
       </c>
       <c r="K44" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -4084,39 +4128,39 @@
     <row r="45" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A45">
         <f t="shared" si="10"/>
-        <v>1030125</v>
+        <v>1030123</v>
       </c>
       <c r="B45" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C45">
         <f t="shared" si="11"/>
-        <v>1300125</v>
+        <v>1300123</v>
       </c>
       <c r="D45" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E45">
         <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J45">
         <f t="shared" si="9"/>
-        <v>2030125</v>
+        <v>2030123</v>
       </c>
       <c r="K45" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -4125,39 +4169,39 @@
     <row r="46" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A46">
         <f t="shared" si="10"/>
-        <v>1030126</v>
+        <v>1030124</v>
       </c>
       <c r="B46" s="7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C46">
         <f t="shared" si="11"/>
-        <v>1300126</v>
+        <v>1300124</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E46">
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J46">
         <f t="shared" si="9"/>
-        <v>2030126</v>
+        <v>2030124</v>
       </c>
       <c r="K46" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N46">
         <v>1</v>
@@ -4166,39 +4210,39 @@
     <row r="47" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A47">
         <f t="shared" si="10"/>
-        <v>1030127</v>
+        <v>1030125</v>
       </c>
       <c r="B47" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C47">
         <f t="shared" si="11"/>
-        <v>1300127</v>
+        <v>1300125</v>
       </c>
       <c r="D47" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E47">
         <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J47">
         <f t="shared" si="9"/>
-        <v>2030127</v>
+        <v>2030125</v>
       </c>
       <c r="K47" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -4207,39 +4251,39 @@
     <row r="48" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A48">
         <f t="shared" si="10"/>
-        <v>1030128</v>
+        <v>1030126</v>
       </c>
       <c r="B48" s="7">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C48">
         <f t="shared" si="11"/>
-        <v>1300128</v>
+        <v>1300126</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E48">
         <v>3</v>
       </c>
       <c r="F48" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J48">
         <f t="shared" si="9"/>
-        <v>2030128</v>
+        <v>2030126</v>
       </c>
       <c r="K48" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -4248,39 +4292,39 @@
     <row r="49" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A49">
         <f t="shared" si="10"/>
-        <v>1030129</v>
+        <v>1030127</v>
       </c>
       <c r="B49" s="7">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C49">
         <f t="shared" si="11"/>
-        <v>1300129</v>
+        <v>1300127</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E49">
         <v>3</v>
       </c>
       <c r="F49" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J49">
         <f t="shared" si="9"/>
-        <v>2030129</v>
+        <v>2030127</v>
       </c>
       <c r="K49" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N49">
         <v>1</v>
@@ -4289,39 +4333,39 @@
     <row r="50" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A50">
         <f t="shared" si="10"/>
-        <v>1030130</v>
+        <v>1030128</v>
       </c>
       <c r="B50" s="7">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C50">
         <f t="shared" si="11"/>
-        <v>1300130</v>
+        <v>1300128</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E50">
         <v>3</v>
       </c>
       <c r="F50" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J50">
         <f t="shared" si="9"/>
-        <v>2030130</v>
+        <v>2030128</v>
       </c>
       <c r="K50" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N50">
         <v>1</v>
@@ -4330,39 +4374,39 @@
     <row r="51" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A51">
         <f t="shared" si="10"/>
-        <v>1030131</v>
+        <v>1030129</v>
       </c>
       <c r="B51" s="7">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C51">
         <f t="shared" si="11"/>
-        <v>1300131</v>
+        <v>1300129</v>
       </c>
       <c r="D51" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E51">
         <v>3</v>
       </c>
       <c r="F51" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J51">
         <f t="shared" si="9"/>
-        <v>2030131</v>
+        <v>2030129</v>
       </c>
       <c r="K51" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N51">
         <v>1</v>
@@ -4371,39 +4415,39 @@
     <row r="52" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A52">
         <f t="shared" si="10"/>
-        <v>1030132</v>
+        <v>1030130</v>
       </c>
       <c r="B52" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C52">
         <f t="shared" si="11"/>
-        <v>1300132</v>
+        <v>1300130</v>
       </c>
       <c r="D52" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E52">
         <v>3</v>
       </c>
       <c r="F52" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J52">
         <f t="shared" si="9"/>
-        <v>2030132</v>
+        <v>2030130</v>
       </c>
       <c r="K52" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -4412,39 +4456,39 @@
     <row r="53" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A53">
         <f t="shared" si="10"/>
-        <v>1030141</v>
+        <v>1030131</v>
       </c>
       <c r="B53" s="7">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C53">
         <f t="shared" si="11"/>
-        <v>1300141</v>
+        <v>1300131</v>
       </c>
       <c r="D53" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J53">
         <f t="shared" si="9"/>
-        <v>2030141</v>
+        <v>2030131</v>
       </c>
       <c r="K53" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -4453,39 +4497,39 @@
     <row r="54" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A54">
         <f t="shared" si="10"/>
-        <v>1030142</v>
+        <v>1030132</v>
       </c>
       <c r="B54" s="7">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C54">
         <f t="shared" si="11"/>
-        <v>1300142</v>
+        <v>1300132</v>
       </c>
       <c r="D54" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E54">
         <v>3</v>
       </c>
       <c r="F54" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J54">
         <f t="shared" si="9"/>
-        <v>2030142</v>
+        <v>2030132</v>
       </c>
       <c r="K54" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N54">
         <v>1</v>
@@ -4494,39 +4538,39 @@
     <row r="55" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A55">
         <f t="shared" si="10"/>
-        <v>1030143</v>
+        <v>1030141</v>
       </c>
       <c r="B55" s="7">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C55">
         <f t="shared" si="11"/>
-        <v>1300143</v>
+        <v>1300141</v>
       </c>
       <c r="D55" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E55">
         <v>3</v>
       </c>
       <c r="F55" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J55">
         <f t="shared" si="9"/>
-        <v>2030143</v>
+        <v>2030141</v>
       </c>
       <c r="K55" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -4535,39 +4579,39 @@
     <row r="56" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A56">
         <f t="shared" si="10"/>
-        <v>1030144</v>
+        <v>1030142</v>
       </c>
       <c r="B56" s="7">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C56">
         <f t="shared" si="11"/>
-        <v>1300144</v>
+        <v>1300142</v>
       </c>
       <c r="D56" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E56">
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J56">
         <f t="shared" si="9"/>
-        <v>2030144</v>
+        <v>2030142</v>
       </c>
       <c r="K56" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -4576,39 +4620,39 @@
     <row r="57" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A57">
         <f t="shared" si="10"/>
-        <v>1030145</v>
+        <v>1030143</v>
       </c>
       <c r="B57" s="7">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C57">
         <f t="shared" si="11"/>
-        <v>1300145</v>
+        <v>1300143</v>
       </c>
       <c r="D57" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E57">
         <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J57">
         <f t="shared" si="9"/>
-        <v>2030145</v>
+        <v>2030143</v>
       </c>
       <c r="K57" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N57">
         <v>1</v>
@@ -4617,39 +4661,39 @@
     <row r="58" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A58">
         <f t="shared" si="10"/>
-        <v>1030146</v>
+        <v>1030144</v>
       </c>
       <c r="B58" s="7">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C58">
         <f t="shared" si="11"/>
-        <v>1300146</v>
+        <v>1300144</v>
       </c>
       <c r="D58" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E58">
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J58">
         <f t="shared" si="9"/>
-        <v>2030146</v>
+        <v>2030144</v>
       </c>
       <c r="K58" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N58">
         <v>1</v>
@@ -4658,39 +4702,39 @@
     <row r="59" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A59">
         <f t="shared" si="10"/>
-        <v>1030147</v>
+        <v>1030145</v>
       </c>
       <c r="B59" s="7">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C59">
         <f t="shared" si="11"/>
-        <v>1300147</v>
+        <v>1300145</v>
       </c>
       <c r="D59" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E59">
         <v>3</v>
       </c>
       <c r="F59" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J59">
         <f t="shared" si="9"/>
-        <v>2030147</v>
+        <v>2030145</v>
       </c>
       <c r="K59" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -4699,39 +4743,39 @@
     <row r="60" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A60">
         <f t="shared" si="10"/>
-        <v>1030148</v>
+        <v>1030146</v>
       </c>
       <c r="B60" s="7">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C60">
         <f t="shared" si="11"/>
-        <v>1300148</v>
+        <v>1300146</v>
       </c>
       <c r="D60" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E60">
         <v>3</v>
       </c>
       <c r="F60" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J60">
         <f t="shared" si="9"/>
-        <v>2030148</v>
+        <v>2030146</v>
       </c>
       <c r="K60" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -4740,39 +4784,39 @@
     <row r="61" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A61">
         <f t="shared" si="10"/>
-        <v>1030149</v>
+        <v>1030147</v>
       </c>
       <c r="B61" s="7">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C61">
         <f t="shared" si="11"/>
-        <v>1300149</v>
+        <v>1300147</v>
       </c>
       <c r="D61" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J61">
         <f t="shared" si="9"/>
-        <v>2030149</v>
+        <v>2030147</v>
       </c>
       <c r="K61" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -4781,39 +4825,39 @@
     <row r="62" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A62">
         <f t="shared" si="10"/>
-        <v>1030150</v>
+        <v>1030148</v>
       </c>
       <c r="B62" s="7">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C62">
         <f t="shared" si="11"/>
-        <v>1300150</v>
+        <v>1300148</v>
       </c>
       <c r="D62" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E62">
         <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J62">
-        <f t="shared" ref="J62:J93" si="12">2000000+E62*10000+B62</f>
-        <v>2030150</v>
+        <f t="shared" si="9"/>
+        <v>2030148</v>
       </c>
       <c r="K62" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N62">
         <v>1</v>
@@ -4822,39 +4866,39 @@
     <row r="63" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A63">
         <f t="shared" si="10"/>
-        <v>1030151</v>
+        <v>1030149</v>
       </c>
       <c r="B63" s="7">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C63">
         <f t="shared" si="11"/>
-        <v>1300151</v>
+        <v>1300149</v>
       </c>
       <c r="D63" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E63">
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J63">
-        <f t="shared" si="12"/>
-        <v>2030151</v>
+        <f t="shared" si="9"/>
+        <v>2030149</v>
       </c>
       <c r="K63" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -4863,39 +4907,39 @@
     <row r="64" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A64">
         <f t="shared" si="10"/>
-        <v>1030152</v>
+        <v>1030150</v>
       </c>
       <c r="B64" s="7">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C64">
         <f t="shared" si="11"/>
-        <v>1300152</v>
+        <v>1300150</v>
       </c>
       <c r="D64" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E64">
         <v>3</v>
       </c>
       <c r="F64" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J64">
-        <f t="shared" si="12"/>
-        <v>2030152</v>
+        <f t="shared" ref="J64:J95" si="12">2000000+E64*10000+B64</f>
+        <v>2030150</v>
       </c>
       <c r="K64" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N64">
         <v>1</v>
@@ -4904,39 +4948,39 @@
     <row r="65" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A65">
         <f t="shared" si="10"/>
-        <v>1030161</v>
+        <v>1030151</v>
       </c>
       <c r="B65" s="7">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C65">
         <f t="shared" si="11"/>
-        <v>1300161</v>
+        <v>1300151</v>
       </c>
       <c r="D65" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E65">
         <v>3</v>
       </c>
       <c r="F65" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J65">
         <f t="shared" si="12"/>
-        <v>2030161</v>
+        <v>2030151</v>
       </c>
       <c r="K65" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N65">
         <v>1</v>
@@ -4945,39 +4989,39 @@
     <row r="66" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A66">
         <f t="shared" si="10"/>
-        <v>1030162</v>
+        <v>1030152</v>
       </c>
       <c r="B66" s="7">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C66">
         <f t="shared" si="11"/>
-        <v>1300162</v>
+        <v>1300152</v>
       </c>
       <c r="D66" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E66">
         <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J66">
         <f t="shared" si="12"/>
-        <v>2030162</v>
+        <v>2030152</v>
       </c>
       <c r="K66" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -4985,40 +5029,40 @@
     </row>
     <row r="67" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A67">
-        <f t="shared" ref="A67:A98" si="13">1000000+E67*10000+B67</f>
-        <v>1030163</v>
+        <f t="shared" si="10"/>
+        <v>1030161</v>
       </c>
       <c r="B67" s="7">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C98" si="14">1000000+E67*100000+B67</f>
-        <v>1300163</v>
+        <f t="shared" si="11"/>
+        <v>1300161</v>
       </c>
       <c r="D67" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E67">
         <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J67">
         <f t="shared" si="12"/>
-        <v>2030163</v>
+        <v>2030161</v>
       </c>
       <c r="K67" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N67">
         <v>1</v>
@@ -5026,40 +5070,40 @@
     </row>
     <row r="68" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A68">
-        <f t="shared" si="13"/>
-        <v>1030164</v>
+        <f t="shared" si="10"/>
+        <v>1030162</v>
       </c>
       <c r="B68" s="7">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C68">
-        <f t="shared" si="14"/>
-        <v>1300164</v>
+        <f t="shared" si="11"/>
+        <v>1300162</v>
       </c>
       <c r="D68" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E68">
         <v>3</v>
       </c>
       <c r="F68" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J68">
         <f t="shared" si="12"/>
-        <v>2030164</v>
+        <v>2030162</v>
       </c>
       <c r="K68" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N68">
         <v>1</v>
@@ -5067,40 +5111,40 @@
     </row>
     <row r="69" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A69">
-        <f t="shared" si="13"/>
-        <v>1030165</v>
+        <f t="shared" ref="A69:A100" si="13">1000000+E69*10000+B69</f>
+        <v>1030163</v>
       </c>
       <c r="B69" s="7">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C69">
-        <f t="shared" si="14"/>
-        <v>1300165</v>
+        <f t="shared" ref="C69:C100" si="14">1000000+E69*100000+B69</f>
+        <v>1300163</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E69">
         <v>3</v>
       </c>
       <c r="F69" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J69">
         <f t="shared" si="12"/>
-        <v>2030165</v>
+        <v>2030163</v>
       </c>
       <c r="K69" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N69">
         <v>1</v>
@@ -5109,39 +5153,39 @@
     <row r="70" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A70">
         <f t="shared" si="13"/>
-        <v>1030166</v>
+        <v>1030164</v>
       </c>
       <c r="B70" s="7">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C70">
         <f t="shared" si="14"/>
-        <v>1300166</v>
+        <v>1300164</v>
       </c>
       <c r="D70" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E70">
         <v>3</v>
       </c>
       <c r="F70" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J70">
         <f t="shared" si="12"/>
-        <v>2030166</v>
+        <v>2030164</v>
       </c>
       <c r="K70" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N70">
         <v>1</v>
@@ -5150,39 +5194,39 @@
     <row r="71" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A71">
         <f t="shared" si="13"/>
-        <v>1030167</v>
+        <v>1030165</v>
       </c>
       <c r="B71" s="7">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C71">
         <f t="shared" si="14"/>
-        <v>1300167</v>
+        <v>1300165</v>
       </c>
       <c r="D71" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E71">
         <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J71">
         <f t="shared" si="12"/>
-        <v>2030167</v>
+        <v>2030165</v>
       </c>
       <c r="K71" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N71">
         <v>1</v>
@@ -5191,39 +5235,39 @@
     <row r="72" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A72">
         <f t="shared" si="13"/>
-        <v>1030168</v>
+        <v>1030166</v>
       </c>
       <c r="B72" s="7">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C72">
         <f t="shared" si="14"/>
-        <v>1300168</v>
+        <v>1300166</v>
       </c>
       <c r="D72" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E72">
         <v>3</v>
       </c>
       <c r="F72" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J72">
         <f t="shared" si="12"/>
-        <v>2030168</v>
+        <v>2030166</v>
       </c>
       <c r="K72" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N72">
         <v>1</v>
@@ -5232,39 +5276,39 @@
     <row r="73" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A73">
         <f t="shared" si="13"/>
-        <v>1030169</v>
+        <v>1030167</v>
       </c>
       <c r="B73" s="7">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C73">
         <f t="shared" si="14"/>
-        <v>1300169</v>
+        <v>1300167</v>
       </c>
       <c r="D73" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E73">
         <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J73">
         <f t="shared" si="12"/>
-        <v>2030169</v>
+        <v>2030167</v>
       </c>
       <c r="K73" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N73">
         <v>1</v>
@@ -5273,39 +5317,39 @@
     <row r="74" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A74">
         <f t="shared" si="13"/>
-        <v>1030170</v>
+        <v>1030168</v>
       </c>
       <c r="B74" s="7">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C74">
         <f t="shared" si="14"/>
-        <v>1300170</v>
+        <v>1300168</v>
       </c>
       <c r="D74" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E74">
         <v>3</v>
       </c>
       <c r="F74" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J74">
         <f t="shared" si="12"/>
-        <v>2030170</v>
+        <v>2030168</v>
       </c>
       <c r="K74" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N74">
         <v>1</v>
@@ -5314,39 +5358,39 @@
     <row r="75" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A75">
         <f t="shared" si="13"/>
-        <v>1030171</v>
+        <v>1030169</v>
       </c>
       <c r="B75" s="7">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C75">
         <f t="shared" si="14"/>
-        <v>1300171</v>
+        <v>1300169</v>
       </c>
       <c r="D75" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E75">
         <v>3</v>
       </c>
       <c r="F75" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J75">
         <f t="shared" si="12"/>
-        <v>2030171</v>
+        <v>2030169</v>
       </c>
       <c r="K75" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N75">
         <v>1</v>
@@ -5355,39 +5399,39 @@
     <row r="76" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A76">
         <f t="shared" si="13"/>
-        <v>1030172</v>
+        <v>1030170</v>
       </c>
       <c r="B76" s="7">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C76">
         <f t="shared" si="14"/>
-        <v>1300172</v>
+        <v>1300170</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J76">
         <f t="shared" si="12"/>
-        <v>2030172</v>
+        <v>2030170</v>
       </c>
       <c r="K76" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N76">
         <v>1</v>
@@ -5396,39 +5440,39 @@
     <row r="77" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A77">
         <f t="shared" si="13"/>
-        <v>1030181</v>
+        <v>1030171</v>
       </c>
       <c r="B77" s="7">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C77">
         <f t="shared" si="14"/>
-        <v>1300181</v>
+        <v>1300171</v>
       </c>
       <c r="D77" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J77">
         <f t="shared" si="12"/>
-        <v>2030181</v>
+        <v>2030171</v>
       </c>
       <c r="K77" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N77">
         <v>1</v>
@@ -5437,39 +5481,39 @@
     <row r="78" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A78">
         <f t="shared" si="13"/>
-        <v>1030182</v>
+        <v>1030172</v>
       </c>
       <c r="B78" s="7">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C78">
         <f t="shared" si="14"/>
-        <v>1300182</v>
+        <v>1300172</v>
       </c>
       <c r="D78" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E78">
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J78">
         <f t="shared" si="12"/>
-        <v>2030182</v>
+        <v>2030172</v>
       </c>
       <c r="K78" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N78">
         <v>1</v>
@@ -5478,39 +5522,39 @@
     <row r="79" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A79">
         <f t="shared" si="13"/>
-        <v>1030183</v>
+        <v>1030181</v>
       </c>
       <c r="B79" s="7">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C79">
         <f t="shared" si="14"/>
-        <v>1300183</v>
+        <v>1300181</v>
       </c>
       <c r="D79" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E79">
         <v>3</v>
       </c>
       <c r="F79" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>1</v>
       </c>
       <c r="I79" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J79">
         <f t="shared" si="12"/>
-        <v>2030183</v>
+        <v>2030181</v>
       </c>
       <c r="K79" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -5519,39 +5563,39 @@
     <row r="80" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A80">
         <f t="shared" si="13"/>
-        <v>1030184</v>
+        <v>1030182</v>
       </c>
       <c r="B80" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C80">
         <f t="shared" si="14"/>
-        <v>1300184</v>
+        <v>1300182</v>
       </c>
       <c r="D80" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E80">
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J80">
         <f t="shared" si="12"/>
-        <v>2030184</v>
+        <v>2030182</v>
       </c>
       <c r="K80" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N80">
         <v>1</v>
@@ -5560,39 +5604,39 @@
     <row r="81" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A81">
         <f t="shared" si="13"/>
-        <v>1030185</v>
+        <v>1030183</v>
       </c>
       <c r="B81" s="7">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C81">
         <f t="shared" si="14"/>
-        <v>1300185</v>
+        <v>1300183</v>
       </c>
       <c r="D81" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J81">
         <f t="shared" si="12"/>
-        <v>2030185</v>
+        <v>2030183</v>
       </c>
       <c r="K81" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -5601,39 +5645,39 @@
     <row r="82" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A82">
         <f t="shared" si="13"/>
-        <v>1030186</v>
+        <v>1030184</v>
       </c>
       <c r="B82" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C82">
         <f t="shared" si="14"/>
-        <v>1300186</v>
+        <v>1300184</v>
       </c>
       <c r="D82" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E82">
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J82">
         <f t="shared" si="12"/>
-        <v>2030186</v>
+        <v>2030184</v>
       </c>
       <c r="K82" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -5642,39 +5686,39 @@
     <row r="83" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A83">
         <f t="shared" si="13"/>
-        <v>1030187</v>
+        <v>1030185</v>
       </c>
       <c r="B83" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C83">
         <f t="shared" si="14"/>
-        <v>1300187</v>
+        <v>1300185</v>
       </c>
       <c r="D83" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J83">
         <f t="shared" si="12"/>
-        <v>2030187</v>
+        <v>2030185</v>
       </c>
       <c r="K83" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N83">
         <v>1</v>
@@ -5683,39 +5727,39 @@
     <row r="84" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A84">
         <f t="shared" si="13"/>
-        <v>1030188</v>
+        <v>1030186</v>
       </c>
       <c r="B84" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C84">
         <f t="shared" si="14"/>
-        <v>1300188</v>
+        <v>1300186</v>
       </c>
       <c r="D84" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E84">
         <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J84">
         <f t="shared" si="12"/>
-        <v>2030188</v>
+        <v>2030186</v>
       </c>
       <c r="K84" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N84">
         <v>1</v>
@@ -5724,39 +5768,39 @@
     <row r="85" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A85">
         <f t="shared" si="13"/>
-        <v>1030189</v>
+        <v>1030187</v>
       </c>
       <c r="B85" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C85">
         <f t="shared" si="14"/>
-        <v>1300189</v>
+        <v>1300187</v>
       </c>
       <c r="D85" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E85">
         <v>3</v>
       </c>
       <c r="F85" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J85">
         <f t="shared" si="12"/>
-        <v>2030189</v>
+        <v>2030187</v>
       </c>
       <c r="K85" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -5765,39 +5809,39 @@
     <row r="86" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A86">
         <f t="shared" si="13"/>
-        <v>1030190</v>
+        <v>1030188</v>
       </c>
       <c r="B86" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C86">
         <f t="shared" si="14"/>
-        <v>1300190</v>
+        <v>1300188</v>
       </c>
       <c r="D86" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E86">
         <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G86">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J86">
         <f t="shared" si="12"/>
-        <v>2030190</v>
+        <v>2030188</v>
       </c>
       <c r="K86" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -5806,39 +5850,39 @@
     <row r="87" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A87">
         <f t="shared" si="13"/>
-        <v>1030191</v>
+        <v>1030189</v>
       </c>
       <c r="B87" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C87">
         <f t="shared" si="14"/>
-        <v>1300191</v>
+        <v>1300189</v>
       </c>
       <c r="D87" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E87">
         <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G87">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H87">
         <v>1</v>
       </c>
       <c r="I87" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J87">
         <f t="shared" si="12"/>
-        <v>2030191</v>
+        <v>2030189</v>
       </c>
       <c r="K87" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -5847,39 +5891,39 @@
     <row r="88" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A88">
         <f t="shared" si="13"/>
-        <v>1030192</v>
+        <v>1030190</v>
       </c>
       <c r="B88" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C88">
         <f t="shared" si="14"/>
-        <v>1300192</v>
+        <v>1300190</v>
       </c>
       <c r="D88" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E88">
         <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G88">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J88">
         <f t="shared" si="12"/>
-        <v>2030192</v>
+        <v>2030190</v>
       </c>
       <c r="K88" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -5888,39 +5932,39 @@
     <row r="89" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A89">
         <f t="shared" si="13"/>
-        <v>1030201</v>
+        <v>1030191</v>
       </c>
       <c r="B89" s="7">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C89">
         <f t="shared" si="14"/>
-        <v>1300201</v>
+        <v>1300191</v>
       </c>
       <c r="D89" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E89">
         <v>3</v>
       </c>
       <c r="F89" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J89">
         <f t="shared" si="12"/>
-        <v>2030201</v>
+        <v>2030191</v>
       </c>
       <c r="K89" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N89">
         <v>1</v>
@@ -5929,39 +5973,39 @@
     <row r="90" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A90">
         <f t="shared" si="13"/>
-        <v>1030202</v>
+        <v>1030192</v>
       </c>
       <c r="B90" s="7">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C90">
         <f t="shared" si="14"/>
-        <v>1300202</v>
+        <v>1300192</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E90">
         <v>3</v>
       </c>
       <c r="F90" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J90">
         <f t="shared" si="12"/>
-        <v>2030202</v>
+        <v>2030192</v>
       </c>
       <c r="K90" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N90">
         <v>1</v>
@@ -5970,39 +6014,39 @@
     <row r="91" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A91">
         <f t="shared" si="13"/>
-        <v>1030203</v>
+        <v>1030201</v>
       </c>
       <c r="B91" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C91">
         <f t="shared" si="14"/>
-        <v>1300203</v>
+        <v>1300201</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E91">
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91">
         <v>1</v>
       </c>
       <c r="I91" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J91">
         <f t="shared" si="12"/>
-        <v>2030203</v>
+        <v>2030201</v>
       </c>
       <c r="K91" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -6011,39 +6055,39 @@
     <row r="92" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A92">
         <f t="shared" si="13"/>
-        <v>1030204</v>
+        <v>1030202</v>
       </c>
       <c r="B92" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C92">
         <f t="shared" si="14"/>
-        <v>1300204</v>
+        <v>1300202</v>
       </c>
       <c r="D92" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E92">
         <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J92">
         <f t="shared" si="12"/>
-        <v>2030204</v>
+        <v>2030202</v>
       </c>
       <c r="K92" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N92">
         <v>1</v>
@@ -6052,39 +6096,39 @@
     <row r="93" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A93">
         <f t="shared" si="13"/>
-        <v>1030205</v>
+        <v>1030203</v>
       </c>
       <c r="B93" s="7">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C93">
         <f t="shared" si="14"/>
-        <v>1300205</v>
+        <v>1300203</v>
       </c>
       <c r="D93" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E93">
         <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J93">
         <f t="shared" si="12"/>
-        <v>2030205</v>
+        <v>2030203</v>
       </c>
       <c r="K93" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -6093,39 +6137,39 @@
     <row r="94" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A94">
         <f t="shared" si="13"/>
-        <v>1030206</v>
+        <v>1030204</v>
       </c>
       <c r="B94" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C94">
         <f t="shared" si="14"/>
-        <v>1300206</v>
+        <v>1300204</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E94">
         <v>3</v>
       </c>
       <c r="F94" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H94">
         <v>1</v>
       </c>
       <c r="I94" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J94">
-        <f t="shared" ref="J94:J128" si="15">2000000+E94*10000+B94</f>
-        <v>2030206</v>
+        <f t="shared" si="12"/>
+        <v>2030204</v>
       </c>
       <c r="K94" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N94">
         <v>1</v>
@@ -6134,39 +6178,39 @@
     <row r="95" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A95">
         <f t="shared" si="13"/>
-        <v>1030207</v>
+        <v>1030205</v>
       </c>
       <c r="B95" s="7">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C95">
         <f t="shared" si="14"/>
-        <v>1300207</v>
+        <v>1300205</v>
       </c>
       <c r="D95" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E95">
         <v>3</v>
       </c>
       <c r="F95" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G95">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J95">
-        <f t="shared" si="15"/>
-        <v>2030207</v>
+        <f t="shared" si="12"/>
+        <v>2030205</v>
       </c>
       <c r="K95" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N95">
         <v>1</v>
@@ -6175,39 +6219,39 @@
     <row r="96" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A96">
         <f t="shared" si="13"/>
-        <v>1030208</v>
+        <v>1030206</v>
       </c>
       <c r="B96" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C96">
         <f t="shared" si="14"/>
-        <v>1300208</v>
+        <v>1300206</v>
       </c>
       <c r="D96" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E96">
         <v>3</v>
       </c>
       <c r="F96" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G96">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J96">
-        <f t="shared" si="15"/>
-        <v>2030208</v>
+        <f t="shared" ref="J96:J130" si="15">2000000+E96*10000+B96</f>
+        <v>2030206</v>
       </c>
       <c r="K96" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -6216,39 +6260,39 @@
     <row r="97" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A97">
         <f t="shared" si="13"/>
-        <v>1030209</v>
+        <v>1030207</v>
       </c>
       <c r="B97" s="7">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C97">
         <f t="shared" si="14"/>
-        <v>1300209</v>
+        <v>1300207</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E97">
         <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H97">
         <v>1</v>
       </c>
       <c r="I97" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J97">
         <f t="shared" si="15"/>
-        <v>2030209</v>
+        <v>2030207</v>
       </c>
       <c r="K97" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N97">
         <v>1</v>
@@ -6257,39 +6301,39 @@
     <row r="98" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A98">
         <f t="shared" si="13"/>
-        <v>1030210</v>
+        <v>1030208</v>
       </c>
       <c r="B98" s="7">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C98">
         <f t="shared" si="14"/>
-        <v>1300210</v>
+        <v>1300208</v>
       </c>
       <c r="D98" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E98">
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H98">
         <v>1</v>
       </c>
       <c r="I98" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J98">
         <f t="shared" si="15"/>
-        <v>2030210</v>
+        <v>2030208</v>
       </c>
       <c r="K98" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N98">
         <v>1</v>
@@ -6297,40 +6341,40 @@
     </row>
     <row r="99" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A99">
-        <f t="shared" ref="A99:A130" si="16">1000000+E99*10000+B99</f>
-        <v>1030211</v>
+        <f t="shared" si="13"/>
+        <v>1030209</v>
       </c>
       <c r="B99" s="7">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C99">
-        <f t="shared" ref="C99:C128" si="17">1000000+E99*100000+B99</f>
-        <v>1300211</v>
+        <f t="shared" si="14"/>
+        <v>1300209</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E99">
         <v>3</v>
       </c>
       <c r="F99" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G99">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H99">
         <v>1</v>
       </c>
       <c r="I99" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J99">
         <f t="shared" si="15"/>
-        <v>2030211</v>
+        <v>2030209</v>
       </c>
       <c r="K99" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -6338,40 +6382,40 @@
     </row>
     <row r="100" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A100">
-        <f t="shared" si="16"/>
-        <v>1030212</v>
+        <f t="shared" si="13"/>
+        <v>1030210</v>
       </c>
       <c r="B100" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C100">
-        <f t="shared" si="17"/>
-        <v>1300212</v>
+        <f t="shared" si="14"/>
+        <v>1300210</v>
       </c>
       <c r="D100" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E100">
         <v>3</v>
       </c>
       <c r="F100" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G100">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="I100" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J100">
         <f t="shared" si="15"/>
-        <v>2030212</v>
+        <v>2030210</v>
       </c>
       <c r="K100" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N100">
         <v>1</v>
@@ -6379,40 +6423,40 @@
     </row>
     <row r="101" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A101">
-        <f t="shared" si="16"/>
-        <v>1030221</v>
+        <f t="shared" ref="A101:A132" si="16">1000000+E101*10000+B101</f>
+        <v>1030211</v>
       </c>
       <c r="B101" s="7">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C101">
-        <f t="shared" si="17"/>
-        <v>1300221</v>
+        <f t="shared" ref="C101:C130" si="17">1000000+E101*100000+B101</f>
+        <v>1300211</v>
       </c>
       <c r="D101" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E101">
         <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H101">
         <v>1</v>
       </c>
       <c r="I101" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J101">
         <f t="shared" si="15"/>
-        <v>2030221</v>
+        <v>2030211</v>
       </c>
       <c r="K101" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N101">
         <v>1</v>
@@ -6421,39 +6465,39 @@
     <row r="102" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A102">
         <f t="shared" si="16"/>
-        <v>1030222</v>
+        <v>1030212</v>
       </c>
       <c r="B102" s="7">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C102">
         <f t="shared" si="17"/>
-        <v>1300222</v>
+        <v>1300212</v>
       </c>
       <c r="D102" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E102">
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H102">
         <v>1</v>
       </c>
       <c r="I102" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J102">
         <f t="shared" si="15"/>
-        <v>2030222</v>
+        <v>2030212</v>
       </c>
       <c r="K102" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N102">
         <v>1</v>
@@ -6462,39 +6506,39 @@
     <row r="103" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A103">
         <f t="shared" si="16"/>
-        <v>1030223</v>
+        <v>1030221</v>
       </c>
       <c r="B103" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C103">
         <f t="shared" si="17"/>
-        <v>1300223</v>
+        <v>1300221</v>
       </c>
       <c r="D103" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E103">
         <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H103">
         <v>1</v>
       </c>
       <c r="I103" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J103">
         <f t="shared" si="15"/>
-        <v>2030223</v>
+        <v>2030221</v>
       </c>
       <c r="K103" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N103">
         <v>1</v>
@@ -6503,39 +6547,39 @@
     <row r="104" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A104">
         <f t="shared" si="16"/>
-        <v>1030224</v>
+        <v>1030222</v>
       </c>
       <c r="B104" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C104">
         <f t="shared" si="17"/>
-        <v>1300224</v>
+        <v>1300222</v>
       </c>
       <c r="D104" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E104">
         <v>3</v>
       </c>
       <c r="F104" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104">
         <v>1</v>
       </c>
       <c r="I104" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J104">
         <f t="shared" si="15"/>
-        <v>2030224</v>
+        <v>2030222</v>
       </c>
       <c r="K104" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N104">
         <v>1</v>
@@ -6544,39 +6588,39 @@
     <row r="105" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A105">
         <f t="shared" si="16"/>
-        <v>1030225</v>
+        <v>1030223</v>
       </c>
       <c r="B105" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C105">
         <f t="shared" si="17"/>
-        <v>1300225</v>
+        <v>1300223</v>
       </c>
       <c r="D105" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E105">
         <v>3</v>
       </c>
       <c r="F105" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H105">
         <v>1</v>
       </c>
       <c r="I105" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J105">
         <f t="shared" si="15"/>
-        <v>2030225</v>
+        <v>2030223</v>
       </c>
       <c r="K105" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N105">
         <v>1</v>
@@ -6585,39 +6629,39 @@
     <row r="106" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A106">
         <f t="shared" si="16"/>
-        <v>1030226</v>
+        <v>1030224</v>
       </c>
       <c r="B106" s="7">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C106">
         <f t="shared" si="17"/>
-        <v>1300226</v>
+        <v>1300224</v>
       </c>
       <c r="D106" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H106">
         <v>1</v>
       </c>
       <c r="I106" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J106">
         <f t="shared" si="15"/>
-        <v>2030226</v>
+        <v>2030224</v>
       </c>
       <c r="K106" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N106">
         <v>1</v>
@@ -6626,39 +6670,39 @@
     <row r="107" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A107">
         <f t="shared" si="16"/>
-        <v>1030227</v>
+        <v>1030225</v>
       </c>
       <c r="B107" s="7">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C107">
         <f t="shared" si="17"/>
-        <v>1300227</v>
+        <v>1300225</v>
       </c>
       <c r="D107" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H107">
         <v>1</v>
       </c>
       <c r="I107" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J107">
         <f t="shared" si="15"/>
-        <v>2030227</v>
+        <v>2030225</v>
       </c>
       <c r="K107" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -6667,39 +6711,39 @@
     <row r="108" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A108">
         <f t="shared" si="16"/>
-        <v>1030228</v>
+        <v>1030226</v>
       </c>
       <c r="B108" s="7">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C108">
         <f t="shared" si="17"/>
-        <v>1300228</v>
+        <v>1300226</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E108">
         <v>3</v>
       </c>
       <c r="F108" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H108">
         <v>1</v>
       </c>
       <c r="I108" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J108">
         <f t="shared" si="15"/>
-        <v>2030228</v>
+        <v>2030226</v>
       </c>
       <c r="K108" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -6708,39 +6752,39 @@
     <row r="109" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A109">
         <f t="shared" si="16"/>
-        <v>1030229</v>
+        <v>1030227</v>
       </c>
       <c r="B109" s="7">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C109">
         <f t="shared" si="17"/>
-        <v>1300229</v>
+        <v>1300227</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E109">
         <v>3</v>
       </c>
       <c r="F109" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G109">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H109">
         <v>1</v>
       </c>
       <c r="I109" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J109">
         <f t="shared" si="15"/>
-        <v>2030229</v>
+        <v>2030227</v>
       </c>
       <c r="K109" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N109">
         <v>1</v>
@@ -6749,39 +6793,39 @@
     <row r="110" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A110">
         <f t="shared" si="16"/>
-        <v>1030230</v>
+        <v>1030228</v>
       </c>
       <c r="B110" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C110">
         <f t="shared" si="17"/>
-        <v>1300230</v>
+        <v>1300228</v>
       </c>
       <c r="D110" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E110">
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H110">
         <v>1</v>
       </c>
       <c r="I110" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J110">
         <f t="shared" si="15"/>
-        <v>2030230</v>
+        <v>2030228</v>
       </c>
       <c r="K110" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -6790,39 +6834,39 @@
     <row r="111" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A111">
         <f t="shared" si="16"/>
-        <v>1030231</v>
+        <v>1030229</v>
       </c>
       <c r="B111" s="7">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C111">
         <f t="shared" si="17"/>
-        <v>1300231</v>
+        <v>1300229</v>
       </c>
       <c r="D111" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E111">
         <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G111">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H111">
         <v>1</v>
       </c>
       <c r="I111" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J111">
         <f t="shared" si="15"/>
-        <v>2030231</v>
+        <v>2030229</v>
       </c>
       <c r="K111" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N111">
         <v>1</v>
@@ -6831,39 +6875,39 @@
     <row r="112" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A112">
         <f t="shared" si="16"/>
-        <v>1030232</v>
+        <v>1030230</v>
       </c>
       <c r="B112" s="7">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C112">
         <f t="shared" si="17"/>
-        <v>1300232</v>
+        <v>1300230</v>
       </c>
       <c r="D112" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E112">
         <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G112">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H112">
         <v>1</v>
       </c>
       <c r="I112" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J112">
         <f t="shared" si="15"/>
-        <v>2030232</v>
+        <v>2030230</v>
       </c>
       <c r="K112" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N112">
         <v>1</v>
@@ -6872,39 +6916,39 @@
     <row r="113" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A113">
         <f t="shared" si="16"/>
-        <v>1030241</v>
+        <v>1030231</v>
       </c>
       <c r="B113" s="7">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C113">
         <f t="shared" si="17"/>
-        <v>1300241</v>
+        <v>1300231</v>
       </c>
       <c r="D113" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E113">
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H113">
         <v>1</v>
       </c>
       <c r="I113" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J113">
         <f t="shared" si="15"/>
-        <v>2030241</v>
+        <v>2030231</v>
       </c>
       <c r="K113" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N113">
         <v>1</v>
@@ -6913,39 +6957,39 @@
     <row r="114" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A114">
         <f t="shared" si="16"/>
-        <v>1030242</v>
+        <v>1030232</v>
       </c>
       <c r="B114" s="7">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C114">
         <f t="shared" si="17"/>
-        <v>1300242</v>
+        <v>1300232</v>
       </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E114">
         <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H114">
         <v>1</v>
       </c>
       <c r="I114" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J114">
         <f t="shared" si="15"/>
-        <v>2030242</v>
+        <v>2030232</v>
       </c>
       <c r="K114" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -6954,39 +6998,39 @@
     <row r="115" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A115">
         <f t="shared" si="16"/>
-        <v>1030243</v>
+        <v>1030241</v>
       </c>
       <c r="B115" s="7">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C115">
         <f t="shared" si="17"/>
-        <v>1300243</v>
+        <v>1300241</v>
       </c>
       <c r="D115" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E115">
         <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115">
         <v>1</v>
       </c>
       <c r="I115" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J115">
         <f t="shared" si="15"/>
-        <v>2030243</v>
+        <v>2030241</v>
       </c>
       <c r="K115" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N115">
         <v>1</v>
@@ -6995,39 +7039,39 @@
     <row r="116" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A116">
         <f t="shared" si="16"/>
-        <v>1030244</v>
+        <v>1030242</v>
       </c>
       <c r="B116" s="7">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C116">
         <f t="shared" si="17"/>
-        <v>1300244</v>
+        <v>1300242</v>
       </c>
       <c r="D116" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E116">
         <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116">
         <v>1</v>
       </c>
       <c r="I116" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J116">
         <f t="shared" si="15"/>
-        <v>2030244</v>
+        <v>2030242</v>
       </c>
       <c r="K116" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N116">
         <v>1</v>
@@ -7036,39 +7080,39 @@
     <row r="117" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A117">
         <f t="shared" si="16"/>
-        <v>1030245</v>
+        <v>1030243</v>
       </c>
       <c r="B117" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C117">
         <f t="shared" si="17"/>
-        <v>1300245</v>
+        <v>1300243</v>
       </c>
       <c r="D117" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E117">
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H117">
         <v>1</v>
       </c>
       <c r="I117" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J117">
         <f t="shared" si="15"/>
-        <v>2030245</v>
+        <v>2030243</v>
       </c>
       <c r="K117" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -7077,39 +7121,39 @@
     <row r="118" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A118">
         <f t="shared" si="16"/>
-        <v>1030246</v>
+        <v>1030244</v>
       </c>
       <c r="B118" s="7">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C118">
         <f t="shared" si="17"/>
-        <v>1300246</v>
+        <v>1300244</v>
       </c>
       <c r="D118" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E118">
         <v>3</v>
       </c>
       <c r="F118" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H118">
         <v>1</v>
       </c>
       <c r="I118" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J118">
         <f t="shared" si="15"/>
-        <v>2030246</v>
+        <v>2030244</v>
       </c>
       <c r="K118" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N118">
         <v>1</v>
@@ -7118,39 +7162,39 @@
     <row r="119" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A119">
         <f t="shared" si="16"/>
-        <v>1030247</v>
+        <v>1030245</v>
       </c>
       <c r="B119" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C119">
         <f t="shared" si="17"/>
-        <v>1300247</v>
+        <v>1300245</v>
       </c>
       <c r="D119" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E119">
         <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G119">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H119">
         <v>1</v>
       </c>
       <c r="I119" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J119">
         <f t="shared" si="15"/>
-        <v>2030247</v>
+        <v>2030245</v>
       </c>
       <c r="K119" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -7159,39 +7203,39 @@
     <row r="120" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A120">
         <f t="shared" si="16"/>
-        <v>1030248</v>
+        <v>1030246</v>
       </c>
       <c r="B120" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C120">
         <f t="shared" si="17"/>
-        <v>1300248</v>
+        <v>1300246</v>
       </c>
       <c r="D120" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E120">
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G120">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H120">
         <v>1</v>
       </c>
       <c r="I120" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J120">
         <f t="shared" si="15"/>
-        <v>2030248</v>
+        <v>2030246</v>
       </c>
       <c r="K120" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N120">
         <v>1</v>
@@ -7200,39 +7244,39 @@
     <row r="121" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A121">
         <f t="shared" si="16"/>
-        <v>1030249</v>
+        <v>1030247</v>
       </c>
       <c r="B121" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C121">
         <f t="shared" si="17"/>
-        <v>1300249</v>
+        <v>1300247</v>
       </c>
       <c r="D121" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E121">
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H121">
         <v>1</v>
       </c>
       <c r="I121" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J121">
         <f t="shared" si="15"/>
-        <v>2030249</v>
+        <v>2030247</v>
       </c>
       <c r="K121" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -7241,39 +7285,39 @@
     <row r="122" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A122">
         <f t="shared" si="16"/>
-        <v>1030250</v>
+        <v>1030248</v>
       </c>
       <c r="B122" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C122">
         <f t="shared" si="17"/>
-        <v>1300250</v>
+        <v>1300248</v>
       </c>
       <c r="D122" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E122">
         <v>3</v>
       </c>
       <c r="F122" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G122">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H122">
         <v>1</v>
       </c>
       <c r="I122" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J122">
         <f t="shared" si="15"/>
-        <v>2030250</v>
+        <v>2030248</v>
       </c>
       <c r="K122" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N122">
         <v>1</v>
@@ -7282,39 +7326,39 @@
     <row r="123" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A123">
         <f t="shared" si="16"/>
-        <v>1030251</v>
+        <v>1030249</v>
       </c>
       <c r="B123" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C123">
         <f t="shared" si="17"/>
-        <v>1300251</v>
+        <v>1300249</v>
       </c>
       <c r="D123" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E123">
         <v>3</v>
       </c>
       <c r="F123" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G123">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H123">
         <v>1</v>
       </c>
       <c r="I123" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J123">
         <f t="shared" si="15"/>
-        <v>2030251</v>
+        <v>2030249</v>
       </c>
       <c r="K123" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N123">
         <v>1</v>
@@ -7323,39 +7367,39 @@
     <row r="124" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A124">
         <f t="shared" si="16"/>
-        <v>1030252</v>
+        <v>1030250</v>
       </c>
       <c r="B124" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C124">
         <f t="shared" si="17"/>
-        <v>1300252</v>
+        <v>1300250</v>
       </c>
       <c r="D124" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E124">
         <v>3</v>
       </c>
       <c r="F124" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G124">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H124">
         <v>1</v>
       </c>
       <c r="I124" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J124">
         <f t="shared" si="15"/>
-        <v>2030252</v>
+        <v>2030250</v>
       </c>
       <c r="K124" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N124">
         <v>1</v>
@@ -7364,42 +7408,40 @@
     <row r="125" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A125">
         <f t="shared" si="16"/>
-        <v>1031001</v>
+        <v>1030251</v>
       </c>
       <c r="B125" s="7">
-        <v>1001</v>
+        <v>251</v>
       </c>
       <c r="C125">
         <f t="shared" si="17"/>
-        <v>1301001</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>162</v>
+        <v>1300251</v>
+      </c>
+      <c r="D125" t="s">
+        <v>166</v>
       </c>
       <c r="E125">
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G125">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H125">
         <v>1</v>
       </c>
-      <c r="I125" t="str">
-        <f>"itemicon_"&amp;A125&amp;".png"</f>
-        <v>itemicon_1031001.png</v>
+      <c r="I125" t="s">
+        <v>71</v>
       </c>
       <c r="J125">
         <f t="shared" si="15"/>
-        <v>2031001</v>
-      </c>
-      <c r="L125">
-        <v>2</v>
-      </c>
-      <c r="M125"/>
+        <v>2030251</v>
+      </c>
+      <c r="K125" t="s">
+        <v>72</v>
+      </c>
       <c r="N125">
         <v>1</v>
       </c>
@@ -7407,42 +7449,40 @@
     <row r="126" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A126">
         <f t="shared" si="16"/>
-        <v>1031002</v>
+        <v>1030252</v>
       </c>
       <c r="B126" s="7">
-        <v>1002</v>
+        <v>252</v>
       </c>
       <c r="C126">
         <f t="shared" si="17"/>
-        <v>1301002</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>163</v>
+        <v>1300252</v>
+      </c>
+      <c r="D126" t="s">
+        <v>167</v>
       </c>
       <c r="E126">
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G126">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H126">
         <v>1</v>
       </c>
-      <c r="I126" t="str">
-        <f>"itemicon_"&amp;A126&amp;".png"</f>
-        <v>itemicon_1031002.png</v>
+      <c r="I126" t="s">
+        <v>71</v>
       </c>
       <c r="J126">
         <f t="shared" si="15"/>
-        <v>2031002</v>
-      </c>
-      <c r="L126">
-        <v>3</v>
-      </c>
-      <c r="M126"/>
+        <v>2030252</v>
+      </c>
+      <c r="K126" t="s">
+        <v>72</v>
+      </c>
       <c r="N126">
         <v>1</v>
       </c>
@@ -7450,23 +7490,23 @@
     <row r="127" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A127">
         <f t="shared" si="16"/>
-        <v>1031201</v>
+        <v>1031001</v>
       </c>
       <c r="B127" s="7">
-        <v>1201</v>
+        <v>1001</v>
       </c>
       <c r="C127">
         <f t="shared" si="17"/>
-        <v>1301201</v>
-      </c>
-      <c r="D127" t="s">
-        <v>164</v>
+        <v>1301001</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="E127">
         <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -7476,14 +7516,14 @@
       </c>
       <c r="I127" t="str">
         <f>"itemicon_"&amp;A127&amp;".png"</f>
-        <v>itemicon_1031201.png</v>
+        <v>itemicon_1031001.png</v>
       </c>
       <c r="J127">
         <f t="shared" si="15"/>
-        <v>2031201</v>
+        <v>2031001</v>
       </c>
       <c r="L127">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="M127"/>
       <c r="N127">
@@ -7493,23 +7533,23 @@
     <row r="128" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A128">
         <f t="shared" si="16"/>
-        <v>1031202</v>
+        <v>1031002</v>
       </c>
       <c r="B128" s="7">
-        <v>1202</v>
+        <v>1002</v>
       </c>
       <c r="C128">
         <f t="shared" si="17"/>
-        <v>1301202</v>
-      </c>
-      <c r="D128" t="s">
-        <v>165</v>
+        <v>1301002</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="E128">
         <v>3</v>
       </c>
       <c r="F128" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -7519,14 +7559,14 @@
       </c>
       <c r="I128" t="str">
         <f>"itemicon_"&amp;A128&amp;".png"</f>
-        <v>itemicon_1031202.png</v>
+        <v>itemicon_1031002.png</v>
       </c>
       <c r="J128">
         <f t="shared" si="15"/>
-        <v>2031202</v>
+        <v>2031002</v>
       </c>
       <c r="L128">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="M128"/>
       <c r="N128">
@@ -7536,22 +7576,23 @@
     <row r="129" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A129">
         <f t="shared" si="16"/>
-        <v>1031350</v>
+        <v>1031201</v>
       </c>
       <c r="B129" s="7">
-        <v>1350</v>
+        <v>1201</v>
       </c>
       <c r="C129">
-        <v>101801</v>
+        <f t="shared" si="17"/>
+        <v>1301201</v>
       </c>
       <c r="D129" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E129">
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -7559,15 +7600,18 @@
       <c r="H129">
         <v>1</v>
       </c>
-      <c r="I129" t="s">
-        <v>167</v>
+      <c r="I129" t="str">
+        <f>"itemicon_"&amp;A129&amp;".png"</f>
+        <v>itemicon_1031201.png</v>
       </c>
       <c r="J129">
-        <v>201801</v>
+        <f t="shared" si="15"/>
+        <v>2031201</v>
       </c>
       <c r="L129">
-        <v>1801</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="M129"/>
       <c r="N129">
         <v>1</v>
       </c>
@@ -7575,22 +7619,23 @@
     <row r="130" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A130">
         <f t="shared" si="16"/>
-        <v>1031351</v>
+        <v>1031202</v>
       </c>
       <c r="B130" s="7">
-        <v>1351</v>
+        <v>1202</v>
       </c>
       <c r="C130">
-        <v>101802</v>
+        <f t="shared" si="17"/>
+        <v>1301202</v>
       </c>
       <c r="D130" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E130">
         <v>3</v>
       </c>
       <c r="F130" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -7598,39 +7643,41 @@
       <c r="H130">
         <v>1</v>
       </c>
-      <c r="I130" t="s">
-        <v>169</v>
+      <c r="I130" t="str">
+        <f>"itemicon_"&amp;A130&amp;".png"</f>
+        <v>itemicon_1031202.png</v>
       </c>
       <c r="J130">
-        <v>201802</v>
+        <f t="shared" si="15"/>
+        <v>2031202</v>
       </c>
       <c r="L130">
-        <v>1802</v>
-      </c>
+        <v>1003</v>
+      </c>
+      <c r="M130"/>
       <c r="N130">
         <v>1</v>
       </c>
     </row>
     <row r="131" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A131">
-        <f t="shared" ref="A131:A144" si="18">1000000+E131*10000+B131</f>
-        <v>1021401</v>
+        <f t="shared" si="16"/>
+        <v>1031350</v>
       </c>
       <c r="B131" s="7">
-        <v>1401</v>
+        <v>1350</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:C144" si="19">1000000+E131*100000+B131</f>
-        <v>1201401</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>170</v>
+        <v>101801</v>
+      </c>
+      <c r="D131" t="s">
+        <v>172</v>
       </c>
       <c r="E131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -7638,42 +7685,38 @@
       <c r="H131">
         <v>1</v>
       </c>
-      <c r="I131" t="str">
-        <f t="shared" ref="I131:I144" si="20">"itemicon_"&amp;A131&amp;".png"</f>
-        <v>itemicon_1021401.png</v>
+      <c r="I131" t="s">
+        <v>173</v>
       </c>
       <c r="J131">
-        <f t="shared" ref="J131:J144" si="21">2000000+E131*10000+B131</f>
-        <v>2021401</v>
+        <v>201801</v>
       </c>
       <c r="L131">
-        <v>2002</v>
-      </c>
-      <c r="M131"/>
+        <v>1801</v>
+      </c>
       <c r="N131">
         <v>1</v>
       </c>
     </row>
     <row r="132" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A132">
-        <f t="shared" si="18"/>
-        <v>1021402</v>
+        <f t="shared" si="16"/>
+        <v>1031351</v>
       </c>
       <c r="B132" s="7">
-        <v>1402</v>
+        <v>1351</v>
       </c>
       <c r="C132">
-        <f t="shared" si="19"/>
-        <v>1201402</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>171</v>
+        <v>101802</v>
+      </c>
+      <c r="D132" t="s">
+        <v>174</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -7681,42 +7724,39 @@
       <c r="H132">
         <v>1</v>
       </c>
-      <c r="I132" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1021402.png</v>
+      <c r="I132" t="s">
+        <v>175</v>
       </c>
       <c r="J132">
-        <f t="shared" si="21"/>
-        <v>2021402</v>
+        <v>201802</v>
       </c>
       <c r="L132">
-        <v>2003</v>
-      </c>
-      <c r="M132"/>
+        <v>1802</v>
+      </c>
       <c r="N132">
         <v>1</v>
       </c>
     </row>
     <row r="133" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A133">
-        <f t="shared" si="18"/>
-        <v>1031601</v>
+        <f t="shared" ref="A133:A146" si="18">1000000+E133*10000+B133</f>
+        <v>1021401</v>
       </c>
       <c r="B133" s="7">
-        <v>1601</v>
+        <v>1401</v>
       </c>
       <c r="C133">
-        <f t="shared" si="19"/>
-        <v>1301601</v>
-      </c>
-      <c r="D133" s="11" t="s">
-        <v>172</v>
+        <f t="shared" ref="C133:C146" si="19">1000000+E133*100000+B133</f>
+        <v>1201401</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>176</v>
       </c>
       <c r="E133">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -7725,15 +7765,15 @@
         <v>1</v>
       </c>
       <c r="I133" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1031601.png</v>
+        <f t="shared" ref="I133:I146" si="20">"itemicon_"&amp;A133&amp;".png"</f>
+        <v>itemicon_1021401.png</v>
       </c>
       <c r="J133">
-        <f t="shared" si="21"/>
-        <v>2031601</v>
+        <f t="shared" ref="J133:J146" si="21">2000000+E133*10000+B133</f>
+        <v>2021401</v>
       </c>
       <c r="L133">
-        <v>3002</v>
+        <v>2002</v>
       </c>
       <c r="M133"/>
       <c r="N133">
@@ -7743,23 +7783,23 @@
     <row r="134" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A134">
         <f t="shared" si="18"/>
-        <v>1031602</v>
+        <v>1021402</v>
       </c>
       <c r="B134" s="7">
-        <v>1602</v>
+        <v>1402</v>
       </c>
       <c r="C134">
         <f t="shared" si="19"/>
-        <v>1301602</v>
-      </c>
-      <c r="D134" s="11" t="s">
-        <v>173</v>
+        <v>1201402</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>177</v>
       </c>
       <c r="E134">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -7769,14 +7809,14 @@
       </c>
       <c r="I134" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1031602.png</v>
+        <v>itemicon_1021402.png</v>
       </c>
       <c r="J134">
         <f t="shared" si="21"/>
-        <v>2031602</v>
+        <v>2021402</v>
       </c>
       <c r="L134">
-        <v>3003</v>
+        <v>2003</v>
       </c>
       <c r="M134"/>
       <c r="N134">
@@ -7786,23 +7826,23 @@
     <row r="135" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A135">
         <f t="shared" si="18"/>
-        <v>1031801</v>
+        <v>1031601</v>
       </c>
       <c r="B135" s="7">
-        <v>1801</v>
+        <v>1601</v>
       </c>
       <c r="C135">
         <f t="shared" si="19"/>
-        <v>1301801</v>
-      </c>
-      <c r="D135" s="12" t="s">
-        <v>174</v>
+        <v>1301601</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="E135">
         <v>3</v>
       </c>
       <c r="F135" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -7812,14 +7852,14 @@
       </c>
       <c r="I135" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1031801.png</v>
+        <v>itemicon_1031601.png</v>
       </c>
       <c r="J135">
         <f t="shared" si="21"/>
-        <v>2031801</v>
+        <v>2031601</v>
       </c>
       <c r="L135">
-        <v>4002</v>
+        <v>3002</v>
       </c>
       <c r="M135"/>
       <c r="N135">
@@ -7829,23 +7869,23 @@
     <row r="136" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A136">
         <f t="shared" si="18"/>
-        <v>1031802</v>
+        <v>1031602</v>
       </c>
       <c r="B136" s="7">
-        <v>1802</v>
+        <v>1602</v>
       </c>
       <c r="C136">
         <f t="shared" si="19"/>
-        <v>1301802</v>
-      </c>
-      <c r="D136" s="12" t="s">
-        <v>175</v>
+        <v>1301602</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>179</v>
       </c>
       <c r="E136">
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -7855,14 +7895,14 @@
       </c>
       <c r="I136" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1031802.png</v>
+        <v>itemicon_1031602.png</v>
       </c>
       <c r="J136">
         <f t="shared" si="21"/>
-        <v>2031802</v>
+        <v>2031602</v>
       </c>
       <c r="L136">
-        <v>4003</v>
+        <v>3003</v>
       </c>
       <c r="M136"/>
       <c r="N136">
@@ -7872,23 +7912,23 @@
     <row r="137" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A137">
         <f t="shared" si="18"/>
-        <v>1032001</v>
+        <v>1031801</v>
       </c>
       <c r="B137" s="7">
-        <v>2001</v>
+        <v>1801</v>
       </c>
       <c r="C137">
         <f t="shared" si="19"/>
-        <v>1302001</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>176</v>
+        <v>1301801</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>180</v>
       </c>
       <c r="E137">
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -7898,14 +7938,14 @@
       </c>
       <c r="I137" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1032001.png</v>
+        <v>itemicon_1031801.png</v>
       </c>
       <c r="J137">
         <f t="shared" si="21"/>
-        <v>2032001</v>
+        <v>2031801</v>
       </c>
       <c r="L137">
-        <v>5002</v>
+        <v>4002</v>
       </c>
       <c r="M137"/>
       <c r="N137">
@@ -7915,23 +7955,23 @@
     <row r="138" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A138">
         <f t="shared" si="18"/>
-        <v>1032002</v>
+        <v>1031802</v>
       </c>
       <c r="B138" s="7">
-        <v>2002</v>
+        <v>1802</v>
       </c>
       <c r="C138">
         <f t="shared" si="19"/>
-        <v>1302002</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>177</v>
+        <v>1301802</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="E138">
         <v>3</v>
       </c>
       <c r="F138" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -7941,14 +7981,14 @@
       </c>
       <c r="I138" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1032002.png</v>
+        <v>itemicon_1031802.png</v>
       </c>
       <c r="J138">
         <f t="shared" si="21"/>
-        <v>2032002</v>
+        <v>2031802</v>
       </c>
       <c r="L138">
-        <v>5003</v>
+        <v>4003</v>
       </c>
       <c r="M138"/>
       <c r="N138">
@@ -7958,23 +7998,23 @@
     <row r="139" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A139">
         <f t="shared" si="18"/>
-        <v>1032201</v>
+        <v>1032001</v>
       </c>
       <c r="B139" s="7">
-        <v>2201</v>
+        <v>2001</v>
       </c>
       <c r="C139">
         <f t="shared" si="19"/>
-        <v>1302201</v>
-      </c>
-      <c r="D139" s="14" t="s">
-        <v>178</v>
+        <v>1302001</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="E139">
         <v>3</v>
       </c>
       <c r="F139" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -7984,14 +8024,14 @@
       </c>
       <c r="I139" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1032201.png</v>
+        <v>itemicon_1032001.png</v>
       </c>
       <c r="J139">
         <f t="shared" si="21"/>
-        <v>2032201</v>
+        <v>2032001</v>
       </c>
       <c r="L139">
-        <v>6002</v>
+        <v>5002</v>
       </c>
       <c r="M139"/>
       <c r="N139">
@@ -8001,23 +8041,23 @@
     <row r="140" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A140">
         <f t="shared" si="18"/>
-        <v>1032202</v>
+        <v>1032002</v>
       </c>
       <c r="B140" s="7">
-        <v>2202</v>
+        <v>2002</v>
       </c>
       <c r="C140">
         <f t="shared" si="19"/>
-        <v>1302202</v>
-      </c>
-      <c r="D140" s="14" t="s">
-        <v>179</v>
+        <v>1302002</v>
+      </c>
+      <c r="D140" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="E140">
         <v>3</v>
       </c>
       <c r="F140" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -8027,124 +8067,126 @@
       </c>
       <c r="I140" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1032202.png</v>
+        <v>itemicon_1032002.png</v>
       </c>
       <c r="J140">
         <f t="shared" si="21"/>
-        <v>2032202</v>
+        <v>2032002</v>
       </c>
       <c r="L140">
-        <v>6003</v>
+        <v>5003</v>
       </c>
       <c r="M140"/>
       <c r="N140">
         <v>1</v>
       </c>
     </row>
-    <row r="141" ht="18" customHeight="1" spans="1:14">
+    <row r="141" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A141">
         <f t="shared" si="18"/>
-        <v>1022501</v>
-      </c>
-      <c r="B141">
-        <v>2501</v>
+        <v>1032201</v>
+      </c>
+      <c r="B141" s="7">
+        <v>2201</v>
       </c>
       <c r="C141">
         <f t="shared" si="19"/>
-        <v>1202501</v>
-      </c>
-      <c r="D141" t="s">
-        <v>180</v>
+        <v>1302201</v>
+      </c>
+      <c r="D141" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="E141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F141" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G141">
         <v>1</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141" t="str">
         <f t="shared" si="20"/>
-        <v>itemicon_1022501.png</v>
+        <v>itemicon_1032201.png</v>
       </c>
       <c r="J141">
         <f t="shared" si="21"/>
-        <v>2022501</v>
-      </c>
-      <c r="K141" t="s">
-        <v>181</v>
-      </c>
+        <v>2032201</v>
+      </c>
+      <c r="L141">
+        <v>6002</v>
+      </c>
+      <c r="M141"/>
       <c r="N141">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="142" customFormat="1" ht="18" customHeight="1" spans="1:14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" customFormat="1" ht="23" customHeight="1" spans="1:14">
       <c r="A142">
         <f t="shared" si="18"/>
-        <v>1022502</v>
-      </c>
-      <c r="B142">
-        <v>2502</v>
+        <v>1032202</v>
+      </c>
+      <c r="B142" s="7">
+        <v>2202</v>
       </c>
       <c r="C142">
         <f t="shared" si="19"/>
-        <v>1202502</v>
-      </c>
-      <c r="D142" t="s">
-        <v>182</v>
+        <v>1302202</v>
+      </c>
+      <c r="D142" s="14" t="s">
+        <v>185</v>
       </c>
       <c r="E142">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F142" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G142">
         <v>1</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142" t="str">
-        <f>"itemicon_"&amp;A142&amp;".png"</f>
-        <v>itemicon_1022502.png</v>
+        <f t="shared" si="20"/>
+        <v>itemicon_1032202.png</v>
       </c>
       <c r="J142">
         <f t="shared" si="21"/>
-        <v>2022502</v>
-      </c>
-      <c r="K142" t="s">
-        <v>183</v>
-      </c>
+        <v>2032202</v>
+      </c>
+      <c r="L142">
+        <v>6003</v>
+      </c>
+      <c r="M142"/>
       <c r="N142">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="143" customFormat="1" ht="18" customHeight="1" spans="1:14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1" spans="1:14">
       <c r="A143">
         <f t="shared" si="18"/>
-        <v>1022503</v>
+        <v>1022501</v>
       </c>
       <c r="B143">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="C143">
         <f t="shared" si="19"/>
-        <v>1202503</v>
+        <v>1202501</v>
       </c>
       <c r="D143" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E143">
         <v>2</v>
       </c>
       <c r="F143" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -8153,40 +8195,40 @@
         <v>0</v>
       </c>
       <c r="I143" t="str">
-        <f>"itemicon_"&amp;A143&amp;".png"</f>
-        <v>itemicon_1022503.png</v>
+        <f t="shared" si="20"/>
+        <v>itemicon_1022501.png</v>
       </c>
       <c r="J143">
         <f t="shared" si="21"/>
-        <v>2022503</v>
+        <v>2022501</v>
       </c>
       <c r="K143" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="N143">
         <v>999</v>
       </c>
     </row>
-    <row r="144" customFormat="1" ht="18" customHeight="1" spans="1:14">
+    <row r="144" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A144">
         <f t="shared" si="18"/>
-        <v>1022504</v>
+        <v>1022502</v>
       </c>
       <c r="B144">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="C144">
         <f t="shared" si="19"/>
-        <v>1202504</v>
+        <v>1202502</v>
       </c>
       <c r="D144" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E144">
         <v>2</v>
       </c>
       <c r="F144" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -8195,48 +8237,57 @@
         <v>0</v>
       </c>
       <c r="I144" t="str">
-        <f>"itemicon_"&amp;A144&amp;".png"</f>
-        <v>itemicon_1022504.png</v>
+        <f t="shared" si="20"/>
+        <v>itemicon_1022502.png</v>
       </c>
       <c r="J144">
         <f t="shared" si="21"/>
-        <v>2022504</v>
+        <v>2022502</v>
       </c>
       <c r="K144" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="N144">
-        <v>999999999</v>
-      </c>
-    </row>
-    <row r="145" customFormat="1" ht="21" customHeight="1" spans="1:14">
+        <v>999</v>
+      </c>
+      <c r="Q144">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="145" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A145">
-        <v>1023001</v>
-      </c>
-      <c r="B145" s="7"/>
+        <f t="shared" si="18"/>
+        <v>1022503</v>
+      </c>
+      <c r="B145">
+        <v>2503</v>
+      </c>
       <c r="C145">
-        <v>1023001</v>
+        <f t="shared" si="19"/>
+        <v>1202503</v>
       </c>
       <c r="D145" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E145">
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
-      <c r="I145" t="s">
-        <v>188</v>
+      <c r="I145" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1022503.png</v>
       </c>
       <c r="J145">
-        <v>2023001</v>
+        <f t="shared" si="21"/>
+        <v>2022503</v>
       </c>
       <c r="K145" t="s">
         <v>189</v>
@@ -8244,950 +8295,1106 @@
       <c r="N145">
         <v>999</v>
       </c>
-    </row>
-    <row r="146" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q145">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="146" customFormat="1" ht="18" customHeight="1" spans="1:14">
       <c r="A146">
-        <v>1023002</v>
-      </c>
-      <c r="B146" s="7"/>
+        <f t="shared" si="18"/>
+        <v>1022504</v>
+      </c>
+      <c r="B146">
+        <v>2504</v>
+      </c>
       <c r="C146">
-        <v>1023002</v>
+        <f t="shared" si="19"/>
+        <v>1202504</v>
       </c>
       <c r="D146" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E146">
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H146">
         <v>0</v>
       </c>
-      <c r="I146" t="s">
-        <v>191</v>
+      <c r="I146" t="str">
+        <f t="shared" si="20"/>
+        <v>itemicon_1022504.png</v>
       </c>
       <c r="J146">
-        <v>2023002</v>
+        <f t="shared" si="21"/>
+        <v>2022504</v>
       </c>
       <c r="K146" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N146">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:14">
+        <v>999999999</v>
+      </c>
+    </row>
+    <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A147">
-        <v>1023003</v>
+        <v>1023001</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147">
-        <v>1023003</v>
+        <v>1023001</v>
       </c>
       <c r="D147" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J147">
-        <v>2023003</v>
+        <v>2023001</v>
       </c>
       <c r="K147" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="N147">
         <v>999</v>
       </c>
-    </row>
-    <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q147">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A148">
-        <v>1023004</v>
+        <v>1023002</v>
       </c>
       <c r="B148" s="7"/>
       <c r="C148">
-        <v>1023004</v>
+        <v>1023002</v>
       </c>
       <c r="D148" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E148">
         <v>2</v>
       </c>
       <c r="F148" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G148">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148" t="s">
+        <v>197</v>
+      </c>
+      <c r="J148">
+        <v>2023002</v>
+      </c>
+      <c r="K148" t="s">
         <v>195</v>
-      </c>
-      <c r="J148">
-        <v>2023004</v>
-      </c>
-      <c r="K148" t="s">
-        <v>189</v>
       </c>
       <c r="N148">
         <v>999</v>
       </c>
-    </row>
-    <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q148">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A149">
-        <v>1023005</v>
+        <v>1023003</v>
       </c>
       <c r="B149" s="7"/>
       <c r="C149">
-        <v>1023005</v>
+        <v>1023003</v>
       </c>
       <c r="D149" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E149">
         <v>2</v>
       </c>
       <c r="F149" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G149">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J149">
-        <v>2023005</v>
+        <v>2023003</v>
       </c>
       <c r="K149" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="N149">
         <v>999</v>
       </c>
-    </row>
-    <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q149">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A150">
-        <v>1023101</v>
+        <v>1023004</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150">
-        <v>1023101</v>
+        <v>1023004</v>
       </c>
       <c r="D150" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E150">
         <v>2</v>
       </c>
       <c r="F150" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G150">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J150">
-        <v>2023101</v>
+        <v>2023004</v>
       </c>
       <c r="K150" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N150">
         <v>999</v>
       </c>
-    </row>
-    <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q150">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A151">
-        <v>1023102</v>
+        <v>1023005</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151">
-        <v>1023102</v>
+        <v>1023005</v>
       </c>
       <c r="D151" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E151">
         <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G151">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J151">
-        <v>2023102</v>
+        <v>2023005</v>
       </c>
       <c r="K151" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N151">
         <v>999</v>
       </c>
-    </row>
-    <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q151">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A152">
-        <v>1023103</v>
+        <v>1023101</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152">
-        <v>1023103</v>
+        <v>1023101</v>
       </c>
       <c r="D152" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E152">
         <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G152">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H152">
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J152">
-        <v>2023103</v>
+        <v>2023101</v>
       </c>
       <c r="K152" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N152">
         <v>999</v>
       </c>
-    </row>
-    <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q152">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A153">
-        <v>1023104</v>
+        <v>1023102</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153">
-        <v>1023104</v>
+        <v>1023102</v>
       </c>
       <c r="D153" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E153">
         <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G153">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H153">
         <v>0</v>
       </c>
       <c r="I153" t="s">
+        <v>208</v>
+      </c>
+      <c r="J153">
+        <v>2023102</v>
+      </c>
+      <c r="K153" t="s">
         <v>206</v>
-      </c>
-      <c r="J153">
-        <v>2023104</v>
-      </c>
-      <c r="K153" t="s">
-        <v>200</v>
       </c>
       <c r="N153">
         <v>999</v>
       </c>
-    </row>
-    <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q153">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A154">
-        <v>1023105</v>
+        <v>1023103</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154">
-        <v>1023105</v>
+        <v>1023103</v>
       </c>
       <c r="D154" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E154">
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G154">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H154">
         <v>0</v>
       </c>
       <c r="I154" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J154">
-        <v>2023105</v>
+        <v>2023103</v>
       </c>
       <c r="K154" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N154">
         <v>999</v>
       </c>
-    </row>
-    <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q154">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A155">
-        <v>1023201</v>
+        <v>1023104</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155">
-        <v>1023201</v>
+        <v>1023104</v>
       </c>
       <c r="D155" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E155">
         <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J155">
-        <v>2023201</v>
+        <v>2023104</v>
       </c>
       <c r="K155" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="N155">
         <v>999</v>
       </c>
-    </row>
-    <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q155">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A156">
-        <v>1023202</v>
+        <v>1023105</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156">
-        <v>1023202</v>
+        <v>1023105</v>
       </c>
       <c r="D156" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E156">
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G156">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H156">
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J156">
-        <v>2023202</v>
+        <v>2023105</v>
       </c>
       <c r="K156" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="N156">
         <v>999</v>
       </c>
-    </row>
-    <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q156">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A157">
-        <v>1023203</v>
+        <v>1023201</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157">
-        <v>1023203</v>
+        <v>1023201</v>
       </c>
       <c r="D157" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E157">
         <v>2</v>
       </c>
       <c r="F157" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G157">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H157">
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J157">
-        <v>2023203</v>
+        <v>2023201</v>
       </c>
       <c r="K157" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="N157">
         <v>999</v>
       </c>
-    </row>
-    <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q157">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A158">
-        <v>1023204</v>
+        <v>1023202</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158">
-        <v>1023204</v>
+        <v>1023202</v>
       </c>
       <c r="D158" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E158">
         <v>2</v>
       </c>
       <c r="F158" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G158">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H158">
         <v>0</v>
       </c>
       <c r="I158" t="s">
+        <v>219</v>
+      </c>
+      <c r="J158">
+        <v>2023202</v>
+      </c>
+      <c r="K158" t="s">
         <v>217</v>
-      </c>
-      <c r="J158">
-        <v>2023204</v>
-      </c>
-      <c r="K158" t="s">
-        <v>211</v>
       </c>
       <c r="N158">
         <v>999</v>
       </c>
-    </row>
-    <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q158">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A159">
-        <v>1023205</v>
+        <v>1023203</v>
       </c>
       <c r="B159" s="7"/>
       <c r="C159">
-        <v>1023205</v>
+        <v>1023203</v>
       </c>
       <c r="D159" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E159">
         <v>2</v>
       </c>
       <c r="F159" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G159">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H159">
         <v>0</v>
       </c>
       <c r="I159" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J159">
-        <v>2023205</v>
+        <v>2023203</v>
       </c>
       <c r="K159" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="N159">
         <v>999</v>
       </c>
-    </row>
-    <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q159">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A160">
-        <v>1023301</v>
+        <v>1023204</v>
       </c>
       <c r="B160" s="7"/>
       <c r="C160">
-        <v>1023301</v>
+        <v>1023204</v>
       </c>
       <c r="D160" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E160">
         <v>2</v>
       </c>
       <c r="F160" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G160">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H160">
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J160">
-        <v>2023301</v>
+        <v>2023204</v>
       </c>
       <c r="K160" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N160">
         <v>999</v>
       </c>
-    </row>
-    <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q160">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A161">
-        <v>1023302</v>
+        <v>1023205</v>
       </c>
       <c r="B161" s="7"/>
       <c r="C161">
-        <v>1023302</v>
+        <v>1023205</v>
       </c>
       <c r="D161" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E161">
         <v>2</v>
       </c>
       <c r="F161" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G161">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H161">
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J161">
-        <v>2023302</v>
+        <v>2023205</v>
       </c>
       <c r="K161" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N161">
         <v>999</v>
       </c>
-    </row>
-    <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q161">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A162">
-        <v>1023303</v>
+        <v>1023301</v>
       </c>
       <c r="B162" s="7"/>
       <c r="C162">
-        <v>1023303</v>
+        <v>1023301</v>
       </c>
       <c r="D162" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E162">
         <v>2</v>
       </c>
       <c r="F162" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G162">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H162">
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J162">
-        <v>2023303</v>
+        <v>2023301</v>
       </c>
       <c r="K162" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N162">
         <v>999</v>
       </c>
-    </row>
-    <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q162">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A163">
-        <v>1023304</v>
+        <v>1023302</v>
       </c>
       <c r="B163" s="7"/>
       <c r="C163">
-        <v>1023304</v>
+        <v>1023302</v>
       </c>
       <c r="D163" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E163">
         <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G163">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H163">
         <v>0</v>
       </c>
       <c r="I163" t="s">
+        <v>230</v>
+      </c>
+      <c r="J163">
+        <v>2023302</v>
+      </c>
+      <c r="K163" t="s">
         <v>228</v>
-      </c>
-      <c r="J163">
-        <v>2023304</v>
-      </c>
-      <c r="K163" t="s">
-        <v>222</v>
       </c>
       <c r="N163">
         <v>999</v>
       </c>
-    </row>
-    <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q163">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A164">
-        <v>1023305</v>
+        <v>1023303</v>
       </c>
       <c r="B164" s="7"/>
       <c r="C164">
-        <v>1023305</v>
+        <v>1023303</v>
       </c>
       <c r="D164" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E164">
         <v>2</v>
       </c>
       <c r="F164" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G164">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H164">
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J164">
-        <v>2023305</v>
+        <v>2023303</v>
       </c>
       <c r="K164" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N164">
         <v>999</v>
       </c>
-    </row>
-    <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q164">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A165">
-        <v>1023401</v>
+        <v>1023304</v>
       </c>
       <c r="B165" s="7"/>
       <c r="C165">
-        <v>1023401</v>
+        <v>1023304</v>
       </c>
       <c r="D165" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E165">
         <v>2</v>
       </c>
       <c r="F165" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G165">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H165">
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J165">
-        <v>2023401</v>
+        <v>2023304</v>
       </c>
       <c r="K165" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N165">
         <v>999</v>
       </c>
-    </row>
-    <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q165">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A166">
-        <v>1023402</v>
+        <v>1023305</v>
       </c>
       <c r="B166" s="7"/>
       <c r="C166">
-        <v>1023402</v>
+        <v>1023305</v>
       </c>
       <c r="D166" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E166">
         <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G166">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H166">
         <v>0</v>
       </c>
       <c r="I166" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J166">
-        <v>2023402</v>
+        <v>2023305</v>
       </c>
       <c r="K166" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N166">
         <v>999</v>
       </c>
-    </row>
-    <row r="167" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q166">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A167">
-        <v>1023403</v>
+        <v>1023401</v>
       </c>
       <c r="B167" s="7"/>
       <c r="C167">
-        <v>1023403</v>
+        <v>1023401</v>
       </c>
       <c r="D167" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E167">
         <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G167">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H167">
         <v>0</v>
       </c>
       <c r="I167" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J167">
-        <v>2023403</v>
+        <v>2023401</v>
       </c>
       <c r="K167" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N167">
         <v>999</v>
       </c>
-    </row>
-    <row r="168" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q167">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="168" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A168">
-        <v>1023404</v>
+        <v>1023402</v>
       </c>
       <c r="B168" s="7"/>
       <c r="C168">
-        <v>1023404</v>
+        <v>1023402</v>
       </c>
       <c r="D168" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E168">
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G168">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H168">
         <v>0</v>
       </c>
       <c r="I168" t="s">
+        <v>241</v>
+      </c>
+      <c r="J168">
+        <v>2023402</v>
+      </c>
+      <c r="K168" t="s">
         <v>239</v>
-      </c>
-      <c r="J168">
-        <v>2023404</v>
-      </c>
-      <c r="K168" t="s">
-        <v>233</v>
       </c>
       <c r="N168">
         <v>999</v>
       </c>
-    </row>
-    <row r="169" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="Q168">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="169" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A169">
-        <v>1023405</v>
+        <v>1023403</v>
       </c>
       <c r="B169" s="7"/>
       <c r="C169">
-        <v>1023405</v>
+        <v>1023403</v>
       </c>
       <c r="D169" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E169">
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G169">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H169">
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J169">
-        <v>2023405</v>
+        <v>2023403</v>
       </c>
       <c r="K169" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N169">
         <v>999</v>
       </c>
-    </row>
-    <row r="170" ht="21" customHeight="1" spans="1:14">
+      <c r="Q169">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A170">
-        <f>1000000+E170*10000+B170</f>
-        <v>1990000</v>
-      </c>
-      <c r="B170" s="7">
-        <v>0</v>
-      </c>
+        <v>1023404</v>
+      </c>
+      <c r="B170" s="7"/>
       <c r="C170">
-        <v>1990000</v>
+        <v>1023404</v>
       </c>
       <c r="D170" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E170">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="F170" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H170">
         <v>0</v>
       </c>
-      <c r="I170" t="str">
-        <f>"itemicon_"&amp;A170&amp;".png"</f>
-        <v>itemicon_1990000.png</v>
+      <c r="I170" t="s">
+        <v>245</v>
       </c>
       <c r="J170">
-        <f>2000000+E170*10000+B170</f>
-        <v>2990000</v>
+        <v>2023404</v>
       </c>
       <c r="K170" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="N170">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="171" ht="21" customHeight="1" spans="1:14">
+        <v>999</v>
+      </c>
+      <c r="Q170">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" ht="21" customHeight="1" spans="1:17">
       <c r="A171">
-        <f>1000000+E171*10000+B171</f>
-        <v>1980000</v>
-      </c>
-      <c r="B171" s="7">
-        <v>0</v>
-      </c>
+        <v>1023405</v>
+      </c>
+      <c r="B171" s="7"/>
       <c r="C171">
-        <v>1980000</v>
+        <v>1023405</v>
       </c>
       <c r="D171" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E171">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F171" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="G171">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H171">
         <v>0</v>
       </c>
-      <c r="I171" t="str">
-        <f>"itemicon_"&amp;A171&amp;".png"</f>
+      <c r="I171" t="s">
+        <v>247</v>
+      </c>
+      <c r="J171">
+        <v>2023405</v>
+      </c>
+      <c r="K171" t="s">
+        <v>239</v>
+      </c>
+      <c r="N171">
+        <v>999</v>
+      </c>
+      <c r="Q171">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="172" ht="21" customHeight="1" spans="1:14">
+      <c r="A172">
+        <f>1000000+E172*10000+B172</f>
+        <v>1990000</v>
+      </c>
+      <c r="B172" s="7">
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <v>1990000</v>
+      </c>
+      <c r="D172" t="s">
+        <v>248</v>
+      </c>
+      <c r="E172">
+        <v>99</v>
+      </c>
+      <c r="F172" t="s">
+        <v>249</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172" t="str">
+        <f>"itemicon_"&amp;A172&amp;".png"</f>
+        <v>itemicon_1990000.png</v>
+      </c>
+      <c r="J172">
+        <f>2000000+E172*10000+B172</f>
+        <v>2990000</v>
+      </c>
+      <c r="K172" t="s">
+        <v>250</v>
+      </c>
+      <c r="N172">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="173" ht="21" customHeight="1" spans="1:14">
+      <c r="A173">
+        <f>1000000+E173*10000+B173</f>
+        <v>1980000</v>
+      </c>
+      <c r="B173" s="7">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>1980000</v>
+      </c>
+      <c r="D173" t="s">
+        <v>251</v>
+      </c>
+      <c r="E173">
+        <v>98</v>
+      </c>
+      <c r="F173" t="s">
+        <v>249</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173" t="str">
+        <f>"itemicon_"&amp;A173&amp;".png"</f>
         <v>itemicon_1980000.png</v>
       </c>
-      <c r="J171">
-        <f>2000000+E171*10000+B171</f>
+      <c r="J173">
+        <f>2000000+E173*10000+B173</f>
         <v>2980000</v>
       </c>
-      <c r="K171" t="s">
-        <v>246</v>
-      </c>
-      <c r="N171">
+      <c r="K173" t="s">
+        <v>252</v>
+      </c>
+      <c r="N173">
         <v>-1</v>
       </c>
     </row>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91E5300-7E63-4290-84C6-5763DE000A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -61,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -88,7 +94,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -112,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -134,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -157,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F127" authorId="0">
+    <comment ref="F127" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -179,7 +185,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F172" authorId="0">
+    <comment ref="F172" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -206,7 +212,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="287">
   <si>
     <t>道具ID</t>
   </si>
@@ -965,19 +971,115 @@
   </si>
   <si>
     <t>在私密房间内下注时需要用的货币，同时是使用部分功能需要消耗的特殊货币</t>
+  </si>
+  <si>
+    <t>itemicon_1010201.png</t>
+  </si>
+  <si>
+    <t>itemicon_1020002.png</t>
+  </si>
+  <si>
+    <t>itemicon_1020003.png</t>
+  </si>
+  <si>
+    <t>itemicon_1020004.png</t>
+  </si>
+  <si>
+    <t>itemicon_1020005.png</t>
+  </si>
+  <si>
+    <t>itemicon_1020006.png</t>
+  </si>
+  <si>
+    <t>itemicon_1030011.png</t>
+  </si>
+  <si>
+    <t>itemicon_1030012.png</t>
+  </si>
+  <si>
+    <t>itemicon_1030013.png</t>
+  </si>
+  <si>
+    <t>itemicon_1030014.png</t>
+  </si>
+  <si>
+    <t>itemicon_1030015.png</t>
+  </si>
+  <si>
+    <t>itemicon_1030016.png</t>
+  </si>
+  <si>
+    <t>itemicon_1030017.png</t>
+  </si>
+  <si>
+    <t>itemicon_1030018.png</t>
+  </si>
+  <si>
+    <t>itemicon_1031001.png</t>
+  </si>
+  <si>
+    <t>itemicon_1031002.png</t>
+  </si>
+  <si>
+    <t>itemicon_1031201.png</t>
+  </si>
+  <si>
+    <t>itemicon_1031202.png</t>
+  </si>
+  <si>
+    <t>itemicon_1021401.png</t>
+  </si>
+  <si>
+    <t>itemicon_1021402.png</t>
+  </si>
+  <si>
+    <t>itemicon_1031601.png</t>
+  </si>
+  <si>
+    <t>itemicon_1031602.png</t>
+  </si>
+  <si>
+    <t>itemicon_1031801.png</t>
+  </si>
+  <si>
+    <t>itemicon_1031802.png</t>
+  </si>
+  <si>
+    <t>itemicon_1032001.png</t>
+  </si>
+  <si>
+    <t>itemicon_1032002.png</t>
+  </si>
+  <si>
+    <t>itemicon_1032201.png</t>
+  </si>
+  <si>
+    <t>itemicon_1032202.png</t>
+  </si>
+  <si>
+    <t>itemicon_1022501.png</t>
+  </si>
+  <si>
+    <t>itemicon_1022502.png</t>
+  </si>
+  <si>
+    <t>itemicon_1022503.png</t>
+  </si>
+  <si>
+    <t>itemicon_1022504.png</t>
+  </si>
+  <si>
+    <t>itemicon_1990000.png</t>
+  </si>
+  <si>
+    <t>itemicon_1980000.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -999,150 +1101,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1153,8 +1111,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1163,234 +1127,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.15"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1413,251 +1191,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1708,89 +1244,158 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1801,7 +1406,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1829,154 +1434,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2226,34 +1717,34 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q173"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="4" max="4" width="17.05" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="5.5" customWidth="1"/>
     <col min="6" max="6" width="10.875" customWidth="1"/>
     <col min="7" max="7" width="8.875" customWidth="1"/>
     <col min="8" max="8" width="17.125" customWidth="1"/>
     <col min="9" max="9" width="22.625" customWidth="1"/>
-    <col min="10" max="10" width="12.0583333333333" customWidth="1"/>
-    <col min="11" max="11" width="28.825" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="28.875" customWidth="1"/>
     <col min="12" max="12" width="10.875" customWidth="1"/>
     <col min="13" max="13" width="17.25" customWidth="1"/>
-    <col min="14" max="14" width="12.2" customWidth="1"/>
+    <col min="14" max="14" width="12.25" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>
-    <col min="16" max="16" width="18.8166666666667" customWidth="1"/>
+    <col min="16" max="16" width="18.875" customWidth="1"/>
     <col min="20" max="20" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2299,7 +1790,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -2341,7 +1832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -2382,13 +1873,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
     </row>
-    <row r="5" customFormat="1" ht="21" customHeight="1" spans="1:15">
+    <row r="5" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5">
-        <f t="shared" ref="A5:A16" si="0">1000000+E5*10000+B5</f>
         <v>1010101</v>
       </c>
       <c r="B5" s="7">
@@ -2412,12 +1902,10 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" t="str">
-        <f>"itemicon_"&amp;A5&amp;".png"</f>
-        <v>itemicon_1010101.png</v>
+      <c r="I5" t="s">
+        <v>37</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5:J16" si="1">2000000+E5*10000+B5</f>
         <v>2010101</v>
       </c>
       <c r="K5" t="s">
@@ -2430,9 +1918,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="21" customHeight="1" spans="1:15">
+    <row r="6" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6">
-        <f t="shared" si="0"/>
         <v>1010201</v>
       </c>
       <c r="B6" s="7">
@@ -2456,12 +1943,10 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" t="str">
-        <f>"itemicon_"&amp;A6&amp;".png"</f>
-        <v>itemicon_1010201.png</v>
+      <c r="I6" t="s">
+        <v>253</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
         <v>2010201</v>
       </c>
       <c r="K6" t="s">
@@ -2474,16 +1959,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
+    <row r="7" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
-        <f t="shared" si="0"/>
         <v>1010301</v>
       </c>
       <c r="B7" s="1">
         <v>301</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" ref="C7:C16" si="2">1000000+E7*100000+B7</f>
         <v>1100301</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2505,7 +1988,6 @@
         <v>37</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" si="1"/>
         <v>2010301</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -2522,16 +2004,14 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
         <v>1010302</v>
       </c>
       <c r="B8" s="1">
         <v>302</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="2"/>
         <v>1100302</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2553,7 +2033,6 @@
         <v>37</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" si="1"/>
         <v>2010302</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -2570,16 +2049,14 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
+    <row r="9" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
         <v>1010303</v>
       </c>
       <c r="B9" s="1">
         <v>303</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" si="2"/>
         <v>1100303</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2601,7 +2078,6 @@
         <v>37</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" si="1"/>
         <v>2010303</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -2618,16 +2094,14 @@
         <v>14.99</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
         <v>1010304</v>
       </c>
       <c r="B10" s="1">
         <v>304</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" si="2"/>
         <v>1100304</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2649,7 +2123,6 @@
         <v>37</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="1"/>
         <v>2010304</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -2666,16 +2139,14 @@
         <v>24.99</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
+    <row r="11" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
         <v>1010305</v>
       </c>
       <c r="B11" s="1">
         <v>305</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" si="2"/>
         <v>1100305</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -2697,7 +2168,6 @@
         <v>37</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="1"/>
         <v>2010305</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -2714,16 +2184,14 @@
         <v>49.99</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="12" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
         <v>1010311</v>
       </c>
       <c r="B12" s="1">
         <v>311</v>
       </c>
       <c r="C12" s="1">
-        <f t="shared" si="2"/>
         <v>1100311</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2745,7 +2213,6 @@
         <v>37</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="1"/>
         <v>2010311</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -2759,16 +2226,14 @@
         <v>100006</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="13" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
         <v>1010312</v>
       </c>
       <c r="B13" s="1">
         <v>312</v>
       </c>
       <c r="C13" s="1">
-        <f t="shared" si="2"/>
         <v>1100312</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2790,7 +2255,6 @@
         <v>37</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="1"/>
         <v>2010312</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -2804,16 +2268,14 @@
         <v>100007</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="14" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
         <v>1010313</v>
       </c>
       <c r="B14" s="1">
         <v>313</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="2"/>
         <v>1100313</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2835,7 +2297,6 @@
         <v>37</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" si="1"/>
         <v>2010313</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -2849,16 +2310,14 @@
         <v>100008</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="15" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
         <v>1010314</v>
       </c>
       <c r="B15" s="1">
         <v>314</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" si="2"/>
         <v>1100314</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -2880,7 +2339,6 @@
         <v>37</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="1"/>
         <v>2010314</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -2894,16 +2352,14 @@
         <v>100009</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="16" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
         <v>1010315</v>
       </c>
       <c r="B16" s="1">
         <v>315</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" si="2"/>
         <v>1100315</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2925,7 +2381,6 @@
         <v>37</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="1"/>
         <v>2010315</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -2939,13 +2394,11 @@
         <v>100010</v>
       </c>
     </row>
-    <row r="17" ht="21" customHeight="1" spans="1:14">
+    <row r="17" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17">
-        <f t="shared" ref="A17:A31" si="3">1000000+E17*10000+B17</f>
         <v>1020001</v>
       </c>
       <c r="B17" s="7">
-        <f>COUNTIF($F$1:F17,F17)</f>
         <v>1</v>
       </c>
       <c r="C17">
@@ -2966,12 +2419,10 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17" t="str">
-        <f t="shared" ref="I17:I30" si="4">"itemicon_"&amp;A17&amp;".png"</f>
-        <v>itemicon_1020001.png</v>
+      <c r="I17" t="s">
+        <v>71</v>
       </c>
       <c r="J17">
-        <f t="shared" ref="J17:J31" si="5">2000000+E17*10000+B17</f>
         <v>2020001</v>
       </c>
       <c r="K17" t="s">
@@ -2981,13 +2432,11 @@
         <v>999</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="18" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
-        <f t="shared" si="3"/>
         <v>1020002</v>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF($F$1:F18,F18)</f>
         <v>2</v>
       </c>
       <c r="C18" s="2">
@@ -3008,12 +2457,10 @@
       <c r="H18">
         <v>1</v>
       </c>
-      <c r="I18" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020002.png</v>
+      <c r="I18" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" si="5"/>
         <v>2020002</v>
       </c>
       <c r="K18" s="2" t="s">
@@ -3023,13 +2470,11 @@
         <v>999</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="19" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
-        <f t="shared" si="3"/>
         <v>1020003</v>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF($F$1:F19,F19)</f>
         <v>3</v>
       </c>
       <c r="C19" s="2">
@@ -3050,12 +2495,10 @@
       <c r="H19">
         <v>1</v>
       </c>
-      <c r="I19" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020003.png</v>
+      <c r="I19" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="5"/>
         <v>2020003</v>
       </c>
       <c r="K19" s="2" t="s">
@@ -3065,13 +2508,11 @@
         <v>999</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="20" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
-        <f t="shared" si="3"/>
         <v>1020004</v>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIF($F$1:F20,F20)</f>
         <v>4</v>
       </c>
       <c r="C20" s="2">
@@ -3092,12 +2533,10 @@
       <c r="H20">
         <v>1</v>
       </c>
-      <c r="I20" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020004.png</v>
+      <c r="I20" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="J20" s="2">
-        <f t="shared" si="5"/>
         <v>2020004</v>
       </c>
       <c r="K20" s="2" t="s">
@@ -3107,13 +2546,11 @@
         <v>999</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
-        <f t="shared" si="3"/>
         <v>1020005</v>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIF($F$1:F21,F21)</f>
         <v>5</v>
       </c>
       <c r="C21" s="2">
@@ -3134,12 +2571,10 @@
       <c r="H21">
         <v>1</v>
       </c>
-      <c r="I21" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020005.png</v>
+      <c r="I21" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="J21" s="2">
-        <f t="shared" si="5"/>
         <v>2020005</v>
       </c>
       <c r="K21" s="2" t="s">
@@ -3149,13 +2584,11 @@
         <v>999</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
+    <row r="22" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
-        <f t="shared" si="3"/>
         <v>1020006</v>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIF($F$1:F22,F22)</f>
         <v>6</v>
       </c>
       <c r="C22" s="2">
@@ -3176,12 +2609,10 @@
       <c r="H22">
         <v>1</v>
       </c>
-      <c r="I22" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1020006.png</v>
+      <c r="I22" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="J22" s="2">
-        <f t="shared" si="5"/>
         <v>2020006</v>
       </c>
       <c r="K22" s="2" t="s">
@@ -3191,16 +2622,14 @@
         <v>999</v>
       </c>
     </row>
-    <row r="23" ht="23" customHeight="1" spans="1:14">
+    <row r="23" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23">
-        <f t="shared" si="3"/>
         <v>1030011</v>
       </c>
       <c r="B23" s="7">
         <v>11</v>
       </c>
       <c r="C23">
-        <f t="shared" ref="C23:C31" si="6">1000000+E23*100000+B23</f>
         <v>1300011</v>
       </c>
       <c r="D23" t="s">
@@ -3218,12 +2647,10 @@
       <c r="H23">
         <v>1</v>
       </c>
-      <c r="I23" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030011.png</v>
+      <c r="I23" t="s">
+        <v>259</v>
       </c>
       <c r="J23">
-        <f t="shared" si="5"/>
         <v>2030011</v>
       </c>
       <c r="K23" t="s">
@@ -3236,16 +2663,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="23" customHeight="1" spans="1:14">
+    <row r="24" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24">
-        <f t="shared" si="3"/>
         <v>1030012</v>
       </c>
       <c r="B24" s="7">
         <v>12</v>
       </c>
       <c r="C24">
-        <f t="shared" si="6"/>
         <v>1300012</v>
       </c>
       <c r="D24" t="s">
@@ -3263,12 +2688,10 @@
       <c r="H24">
         <v>1</v>
       </c>
-      <c r="I24" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030012.png</v>
+      <c r="I24" t="s">
+        <v>260</v>
       </c>
       <c r="J24">
-        <f t="shared" si="5"/>
         <v>2030012</v>
       </c>
       <c r="K24" t="s">
@@ -3281,16 +2704,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="23" customHeight="1" spans="1:14">
+    <row r="25" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25">
-        <f t="shared" si="3"/>
         <v>1030013</v>
       </c>
       <c r="B25" s="7">
         <v>13</v>
       </c>
       <c r="C25">
-        <f t="shared" si="6"/>
         <v>1300013</v>
       </c>
       <c r="D25" t="s">
@@ -3308,12 +2729,10 @@
       <c r="H25">
         <v>1</v>
       </c>
-      <c r="I25" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030013.png</v>
+      <c r="I25" t="s">
+        <v>261</v>
       </c>
       <c r="J25">
-        <f t="shared" si="5"/>
         <v>2030013</v>
       </c>
       <c r="K25" t="s">
@@ -3326,16 +2745,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="23" customHeight="1" spans="1:14">
+    <row r="26" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26">
-        <f t="shared" si="3"/>
         <v>1030014</v>
       </c>
       <c r="B26" s="7">
         <v>14</v>
       </c>
       <c r="C26">
-        <f t="shared" si="6"/>
         <v>1300014</v>
       </c>
       <c r="D26" t="s">
@@ -3353,12 +2770,10 @@
       <c r="H26">
         <v>1</v>
       </c>
-      <c r="I26" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030014.png</v>
+      <c r="I26" t="s">
+        <v>262</v>
       </c>
       <c r="J26">
-        <f t="shared" si="5"/>
         <v>2030014</v>
       </c>
       <c r="K26" t="s">
@@ -3371,16 +2786,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="23" customHeight="1" spans="1:14">
+    <row r="27" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27">
-        <f t="shared" si="3"/>
         <v>1030015</v>
       </c>
       <c r="B27" s="7">
         <v>15</v>
       </c>
       <c r="C27">
-        <f t="shared" si="6"/>
         <v>1300015</v>
       </c>
       <c r="D27" t="s">
@@ -3398,12 +2811,10 @@
       <c r="H27">
         <v>1</v>
       </c>
-      <c r="I27" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030015.png</v>
+      <c r="I27" t="s">
+        <v>263</v>
       </c>
       <c r="J27">
-        <f t="shared" si="5"/>
         <v>2030015</v>
       </c>
       <c r="K27" t="s">
@@ -3416,16 +2827,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="23" customHeight="1" spans="1:14">
+    <row r="28" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28">
-        <f t="shared" si="3"/>
         <v>1030016</v>
       </c>
       <c r="B28" s="7">
         <v>16</v>
       </c>
       <c r="C28">
-        <f t="shared" si="6"/>
         <v>1300016</v>
       </c>
       <c r="D28" t="s">
@@ -3443,12 +2852,10 @@
       <c r="H28">
         <v>1</v>
       </c>
-      <c r="I28" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030016.png</v>
+      <c r="I28" t="s">
+        <v>264</v>
       </c>
       <c r="J28">
-        <f t="shared" si="5"/>
         <v>2030016</v>
       </c>
       <c r="K28" t="s">
@@ -3461,16 +2868,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="23" customHeight="1" spans="1:14">
+    <row r="29" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29">
-        <f t="shared" si="3"/>
         <v>1030017</v>
       </c>
       <c r="B29" s="7">
         <v>17</v>
       </c>
       <c r="C29">
-        <f t="shared" si="6"/>
         <v>1300017</v>
       </c>
       <c r="D29" t="s">
@@ -3488,12 +2893,10 @@
       <c r="H29">
         <v>1</v>
       </c>
-      <c r="I29" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030017.png</v>
+      <c r="I29" t="s">
+        <v>265</v>
       </c>
       <c r="J29">
-        <f t="shared" si="5"/>
         <v>2030017</v>
       </c>
       <c r="K29" t="s">
@@ -3506,16 +2909,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="23" customHeight="1" spans="1:14">
+    <row r="30" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30">
-        <f t="shared" si="3"/>
         <v>1030018</v>
       </c>
       <c r="B30" s="7">
         <v>18</v>
       </c>
       <c r="C30">
-        <f t="shared" si="6"/>
         <v>1300018</v>
       </c>
       <c r="D30" t="s">
@@ -3533,12 +2934,10 @@
       <c r="H30">
         <v>1</v>
       </c>
-      <c r="I30" t="str">
-        <f t="shared" si="4"/>
-        <v>itemicon_1030018.png</v>
+      <c r="I30" t="s">
+        <v>266</v>
       </c>
       <c r="J30">
-        <f t="shared" si="5"/>
         <v>2030018</v>
       </c>
       <c r="K30" t="s">
@@ -3551,16 +2950,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="31" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31">
-        <f t="shared" si="3"/>
         <v>1030101</v>
       </c>
       <c r="B31" s="7">
         <v>101</v>
       </c>
       <c r="C31">
-        <f t="shared" si="6"/>
         <v>1300101</v>
       </c>
       <c r="D31" t="s">
@@ -3582,7 +2979,6 @@
         <v>71</v>
       </c>
       <c r="J31">
-        <f t="shared" si="5"/>
         <v>2030101</v>
       </c>
       <c r="K31" t="s">
@@ -3592,16 +2988,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="32" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32">
-        <f t="shared" ref="A32:A42" si="7">1000000+E32*10000+B32</f>
         <v>1030102</v>
       </c>
       <c r="B32" s="7">
         <v>102</v>
       </c>
       <c r="C32">
-        <f t="shared" ref="C32:C42" si="8">1000000+E32*100000+B32</f>
         <v>1300102</v>
       </c>
       <c r="D32" t="s">
@@ -3623,7 +3017,6 @@
         <v>71</v>
       </c>
       <c r="J32">
-        <f t="shared" ref="J32:J63" si="9">2000000+E32*10000+B32</f>
         <v>2030102</v>
       </c>
       <c r="K32" t="s">
@@ -3633,16 +3026,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="33" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33">
-        <f t="shared" si="7"/>
         <v>1030103</v>
       </c>
       <c r="B33" s="7">
         <v>103</v>
       </c>
       <c r="C33">
-        <f t="shared" si="8"/>
         <v>1300103</v>
       </c>
       <c r="D33" t="s">
@@ -3664,7 +3055,6 @@
         <v>71</v>
       </c>
       <c r="J33">
-        <f t="shared" si="9"/>
         <v>2030103</v>
       </c>
       <c r="K33" t="s">
@@ -3674,16 +3064,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="34" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34">
-        <f t="shared" si="7"/>
         <v>1030104</v>
       </c>
       <c r="B34" s="7">
         <v>104</v>
       </c>
       <c r="C34">
-        <f t="shared" si="8"/>
         <v>1300104</v>
       </c>
       <c r="D34" t="s">
@@ -3705,7 +3093,6 @@
         <v>71</v>
       </c>
       <c r="J34">
-        <f t="shared" si="9"/>
         <v>2030104</v>
       </c>
       <c r="K34" t="s">
@@ -3715,16 +3102,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="35" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35">
-        <f t="shared" si="7"/>
         <v>1030105</v>
       </c>
       <c r="B35" s="7">
         <v>105</v>
       </c>
       <c r="C35">
-        <f t="shared" si="8"/>
         <v>1300105</v>
       </c>
       <c r="D35" t="s">
@@ -3746,7 +3131,6 @@
         <v>71</v>
       </c>
       <c r="J35">
-        <f t="shared" si="9"/>
         <v>2030105</v>
       </c>
       <c r="K35" t="s">
@@ -3756,16 +3140,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="36" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36">
-        <f t="shared" si="7"/>
         <v>1030106</v>
       </c>
       <c r="B36" s="7">
         <v>106</v>
       </c>
       <c r="C36">
-        <f t="shared" si="8"/>
         <v>1300106</v>
       </c>
       <c r="D36" t="s">
@@ -3787,7 +3169,6 @@
         <v>71</v>
       </c>
       <c r="J36">
-        <f t="shared" si="9"/>
         <v>2030106</v>
       </c>
       <c r="K36" t="s">
@@ -3797,16 +3178,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="37" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37">
-        <f t="shared" si="7"/>
         <v>1030107</v>
       </c>
       <c r="B37" s="7">
         <v>107</v>
       </c>
       <c r="C37">
-        <f t="shared" si="8"/>
         <v>1300107</v>
       </c>
       <c r="D37" t="s">
@@ -3828,7 +3207,6 @@
         <v>71</v>
       </c>
       <c r="J37">
-        <f t="shared" si="9"/>
         <v>2030107</v>
       </c>
       <c r="K37" t="s">
@@ -3838,16 +3216,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="38" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38">
-        <f t="shared" si="7"/>
         <v>1030108</v>
       </c>
       <c r="B38" s="7">
         <v>108</v>
       </c>
       <c r="C38">
-        <f t="shared" si="8"/>
         <v>1300108</v>
       </c>
       <c r="D38" t="s">
@@ -3869,7 +3245,6 @@
         <v>71</v>
       </c>
       <c r="J38">
-        <f t="shared" si="9"/>
         <v>2030108</v>
       </c>
       <c r="K38" t="s">
@@ -3879,16 +3254,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="39" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39">
-        <f t="shared" si="7"/>
         <v>1030109</v>
       </c>
       <c r="B39" s="7">
         <v>109</v>
       </c>
       <c r="C39">
-        <f t="shared" si="8"/>
         <v>1300109</v>
       </c>
       <c r="D39" t="s">
@@ -3910,7 +3283,6 @@
         <v>71</v>
       </c>
       <c r="J39">
-        <f t="shared" si="9"/>
         <v>2030109</v>
       </c>
       <c r="K39" t="s">
@@ -3920,16 +3292,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="40" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40">
-        <f t="shared" si="7"/>
         <v>1030110</v>
       </c>
       <c r="B40" s="7">
         <v>110</v>
       </c>
       <c r="C40">
-        <f t="shared" si="8"/>
         <v>1300110</v>
       </c>
       <c r="D40" t="s">
@@ -3951,7 +3321,6 @@
         <v>71</v>
       </c>
       <c r="J40">
-        <f t="shared" si="9"/>
         <v>2030110</v>
       </c>
       <c r="K40" t="s">
@@ -3961,16 +3330,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="41" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41">
-        <f t="shared" si="7"/>
         <v>1030111</v>
       </c>
       <c r="B41" s="7">
         <v>111</v>
       </c>
       <c r="C41">
-        <f t="shared" si="8"/>
         <v>1300111</v>
       </c>
       <c r="D41" t="s">
@@ -3992,7 +3359,6 @@
         <v>71</v>
       </c>
       <c r="J41">
-        <f t="shared" si="9"/>
         <v>2030111</v>
       </c>
       <c r="K41" t="s">
@@ -4002,16 +3368,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="42" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42">
-        <f t="shared" si="7"/>
         <v>1030112</v>
       </c>
       <c r="B42" s="7">
         <v>112</v>
       </c>
       <c r="C42">
-        <f t="shared" si="8"/>
         <v>1300112</v>
       </c>
       <c r="D42" t="s">
@@ -4033,7 +3397,6 @@
         <v>71</v>
       </c>
       <c r="J42">
-        <f t="shared" si="9"/>
         <v>2030112</v>
       </c>
       <c r="K42" t="s">
@@ -4043,16 +3406,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="43" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43">
-        <f t="shared" ref="A43:A68" si="10">1000000+E43*10000+B43</f>
         <v>1030121</v>
       </c>
       <c r="B43" s="7">
         <v>121</v>
       </c>
       <c r="C43">
-        <f t="shared" ref="C43:C68" si="11">1000000+E43*100000+B43</f>
         <v>1300121</v>
       </c>
       <c r="D43" t="s">
@@ -4074,7 +3435,6 @@
         <v>71</v>
       </c>
       <c r="J43">
-        <f t="shared" si="9"/>
         <v>2030121</v>
       </c>
       <c r="K43" t="s">
@@ -4084,16 +3444,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="44" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44">
-        <f t="shared" si="10"/>
         <v>1030122</v>
       </c>
       <c r="B44" s="7">
         <v>122</v>
       </c>
       <c r="C44">
-        <f t="shared" si="11"/>
         <v>1300122</v>
       </c>
       <c r="D44" t="s">
@@ -4115,7 +3473,6 @@
         <v>71</v>
       </c>
       <c r="J44">
-        <f t="shared" si="9"/>
         <v>2030122</v>
       </c>
       <c r="K44" t="s">
@@ -4125,16 +3482,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="45" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45">
-        <f t="shared" si="10"/>
         <v>1030123</v>
       </c>
       <c r="B45" s="7">
         <v>123</v>
       </c>
       <c r="C45">
-        <f t="shared" si="11"/>
         <v>1300123</v>
       </c>
       <c r="D45" t="s">
@@ -4156,7 +3511,6 @@
         <v>71</v>
       </c>
       <c r="J45">
-        <f t="shared" si="9"/>
         <v>2030123</v>
       </c>
       <c r="K45" t="s">
@@ -4166,16 +3520,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="46" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46">
-        <f t="shared" si="10"/>
         <v>1030124</v>
       </c>
       <c r="B46" s="7">
         <v>124</v>
       </c>
       <c r="C46">
-        <f t="shared" si="11"/>
         <v>1300124</v>
       </c>
       <c r="D46" t="s">
@@ -4197,7 +3549,6 @@
         <v>71</v>
       </c>
       <c r="J46">
-        <f t="shared" si="9"/>
         <v>2030124</v>
       </c>
       <c r="K46" t="s">
@@ -4207,16 +3558,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="47" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47">
-        <f t="shared" si="10"/>
         <v>1030125</v>
       </c>
       <c r="B47" s="7">
         <v>125</v>
       </c>
       <c r="C47">
-        <f t="shared" si="11"/>
         <v>1300125</v>
       </c>
       <c r="D47" t="s">
@@ -4238,7 +3587,6 @@
         <v>71</v>
       </c>
       <c r="J47">
-        <f t="shared" si="9"/>
         <v>2030125</v>
       </c>
       <c r="K47" t="s">
@@ -4248,16 +3596,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="48" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48">
-        <f t="shared" si="10"/>
         <v>1030126</v>
       </c>
       <c r="B48" s="7">
         <v>126</v>
       </c>
       <c r="C48">
-        <f t="shared" si="11"/>
         <v>1300126</v>
       </c>
       <c r="D48" t="s">
@@ -4279,7 +3625,6 @@
         <v>71</v>
       </c>
       <c r="J48">
-        <f t="shared" si="9"/>
         <v>2030126</v>
       </c>
       <c r="K48" t="s">
@@ -4289,16 +3634,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="49" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49">
-        <f t="shared" si="10"/>
         <v>1030127</v>
       </c>
       <c r="B49" s="7">
         <v>127</v>
       </c>
       <c r="C49">
-        <f t="shared" si="11"/>
         <v>1300127</v>
       </c>
       <c r="D49" t="s">
@@ -4320,7 +3663,6 @@
         <v>71</v>
       </c>
       <c r="J49">
-        <f t="shared" si="9"/>
         <v>2030127</v>
       </c>
       <c r="K49" t="s">
@@ -4330,16 +3672,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="50" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50">
-        <f t="shared" si="10"/>
         <v>1030128</v>
       </c>
       <c r="B50" s="7">
         <v>128</v>
       </c>
       <c r="C50">
-        <f t="shared" si="11"/>
         <v>1300128</v>
       </c>
       <c r="D50" t="s">
@@ -4361,7 +3701,6 @@
         <v>71</v>
       </c>
       <c r="J50">
-        <f t="shared" si="9"/>
         <v>2030128</v>
       </c>
       <c r="K50" t="s">
@@ -4371,16 +3710,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="51" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51">
-        <f t="shared" si="10"/>
         <v>1030129</v>
       </c>
       <c r="B51" s="7">
         <v>129</v>
       </c>
       <c r="C51">
-        <f t="shared" si="11"/>
         <v>1300129</v>
       </c>
       <c r="D51" t="s">
@@ -4402,7 +3739,6 @@
         <v>71</v>
       </c>
       <c r="J51">
-        <f t="shared" si="9"/>
         <v>2030129</v>
       </c>
       <c r="K51" t="s">
@@ -4412,16 +3748,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="52" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52">
-        <f t="shared" si="10"/>
         <v>1030130</v>
       </c>
       <c r="B52" s="7">
         <v>130</v>
       </c>
       <c r="C52">
-        <f t="shared" si="11"/>
         <v>1300130</v>
       </c>
       <c r="D52" t="s">
@@ -4443,7 +3777,6 @@
         <v>71</v>
       </c>
       <c r="J52">
-        <f t="shared" si="9"/>
         <v>2030130</v>
       </c>
       <c r="K52" t="s">
@@ -4453,16 +3786,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="53" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53">
-        <f t="shared" si="10"/>
         <v>1030131</v>
       </c>
       <c r="B53" s="7">
         <v>131</v>
       </c>
       <c r="C53">
-        <f t="shared" si="11"/>
         <v>1300131</v>
       </c>
       <c r="D53" t="s">
@@ -4484,7 +3815,6 @@
         <v>71</v>
       </c>
       <c r="J53">
-        <f t="shared" si="9"/>
         <v>2030131</v>
       </c>
       <c r="K53" t="s">
@@ -4494,16 +3824,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="54" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54">
-        <f t="shared" si="10"/>
         <v>1030132</v>
       </c>
       <c r="B54" s="7">
         <v>132</v>
       </c>
       <c r="C54">
-        <f t="shared" si="11"/>
         <v>1300132</v>
       </c>
       <c r="D54" t="s">
@@ -4525,7 +3853,6 @@
         <v>71</v>
       </c>
       <c r="J54">
-        <f t="shared" si="9"/>
         <v>2030132</v>
       </c>
       <c r="K54" t="s">
@@ -4535,16 +3862,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="55" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55">
-        <f t="shared" si="10"/>
         <v>1030141</v>
       </c>
       <c r="B55" s="7">
         <v>141</v>
       </c>
       <c r="C55">
-        <f t="shared" si="11"/>
         <v>1300141</v>
       </c>
       <c r="D55" t="s">
@@ -4566,7 +3891,6 @@
         <v>71</v>
       </c>
       <c r="J55">
-        <f t="shared" si="9"/>
         <v>2030141</v>
       </c>
       <c r="K55" t="s">
@@ -4576,16 +3900,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="56" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56">
-        <f t="shared" si="10"/>
         <v>1030142</v>
       </c>
       <c r="B56" s="7">
         <v>142</v>
       </c>
       <c r="C56">
-        <f t="shared" si="11"/>
         <v>1300142</v>
       </c>
       <c r="D56" t="s">
@@ -4607,7 +3929,6 @@
         <v>71</v>
       </c>
       <c r="J56">
-        <f t="shared" si="9"/>
         <v>2030142</v>
       </c>
       <c r="K56" t="s">
@@ -4617,16 +3938,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="57" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57">
-        <f t="shared" si="10"/>
         <v>1030143</v>
       </c>
       <c r="B57" s="7">
         <v>143</v>
       </c>
       <c r="C57">
-        <f t="shared" si="11"/>
         <v>1300143</v>
       </c>
       <c r="D57" t="s">
@@ -4648,7 +3967,6 @@
         <v>71</v>
       </c>
       <c r="J57">
-        <f t="shared" si="9"/>
         <v>2030143</v>
       </c>
       <c r="K57" t="s">
@@ -4658,16 +3976,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="58" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58">
-        <f t="shared" si="10"/>
         <v>1030144</v>
       </c>
       <c r="B58" s="7">
         <v>144</v>
       </c>
       <c r="C58">
-        <f t="shared" si="11"/>
         <v>1300144</v>
       </c>
       <c r="D58" t="s">
@@ -4689,7 +4005,6 @@
         <v>71</v>
       </c>
       <c r="J58">
-        <f t="shared" si="9"/>
         <v>2030144</v>
       </c>
       <c r="K58" t="s">
@@ -4699,16 +4014,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="59" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59">
-        <f t="shared" si="10"/>
         <v>1030145</v>
       </c>
       <c r="B59" s="7">
         <v>145</v>
       </c>
       <c r="C59">
-        <f t="shared" si="11"/>
         <v>1300145</v>
       </c>
       <c r="D59" t="s">
@@ -4730,7 +4043,6 @@
         <v>71</v>
       </c>
       <c r="J59">
-        <f t="shared" si="9"/>
         <v>2030145</v>
       </c>
       <c r="K59" t="s">
@@ -4740,16 +4052,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="60" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60">
-        <f t="shared" si="10"/>
         <v>1030146</v>
       </c>
       <c r="B60" s="7">
         <v>146</v>
       </c>
       <c r="C60">
-        <f t="shared" si="11"/>
         <v>1300146</v>
       </c>
       <c r="D60" t="s">
@@ -4771,7 +4081,6 @@
         <v>71</v>
       </c>
       <c r="J60">
-        <f t="shared" si="9"/>
         <v>2030146</v>
       </c>
       <c r="K60" t="s">
@@ -4781,16 +4090,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="61" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61">
-        <f t="shared" si="10"/>
         <v>1030147</v>
       </c>
       <c r="B61" s="7">
         <v>147</v>
       </c>
       <c r="C61">
-        <f t="shared" si="11"/>
         <v>1300147</v>
       </c>
       <c r="D61" t="s">
@@ -4812,7 +4119,6 @@
         <v>71</v>
       </c>
       <c r="J61">
-        <f t="shared" si="9"/>
         <v>2030147</v>
       </c>
       <c r="K61" t="s">
@@ -4822,16 +4128,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="62" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62">
-        <f t="shared" si="10"/>
         <v>1030148</v>
       </c>
       <c r="B62" s="7">
         <v>148</v>
       </c>
       <c r="C62">
-        <f t="shared" si="11"/>
         <v>1300148</v>
       </c>
       <c r="D62" t="s">
@@ -4853,7 +4157,6 @@
         <v>71</v>
       </c>
       <c r="J62">
-        <f t="shared" si="9"/>
         <v>2030148</v>
       </c>
       <c r="K62" t="s">
@@ -4863,16 +4166,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="63" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63">
-        <f t="shared" si="10"/>
         <v>1030149</v>
       </c>
       <c r="B63" s="7">
         <v>149</v>
       </c>
       <c r="C63">
-        <f t="shared" si="11"/>
         <v>1300149</v>
       </c>
       <c r="D63" t="s">
@@ -4894,7 +4195,6 @@
         <v>71</v>
       </c>
       <c r="J63">
-        <f t="shared" si="9"/>
         <v>2030149</v>
       </c>
       <c r="K63" t="s">
@@ -4904,16 +4204,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="64" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64">
-        <f t="shared" si="10"/>
         <v>1030150</v>
       </c>
       <c r="B64" s="7">
         <v>150</v>
       </c>
       <c r="C64">
-        <f t="shared" si="11"/>
         <v>1300150</v>
       </c>
       <c r="D64" t="s">
@@ -4935,7 +4233,6 @@
         <v>71</v>
       </c>
       <c r="J64">
-        <f t="shared" ref="J64:J95" si="12">2000000+E64*10000+B64</f>
         <v>2030150</v>
       </c>
       <c r="K64" t="s">
@@ -4945,16 +4242,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="65" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65">
-        <f t="shared" si="10"/>
         <v>1030151</v>
       </c>
       <c r="B65" s="7">
         <v>151</v>
       </c>
       <c r="C65">
-        <f t="shared" si="11"/>
         <v>1300151</v>
       </c>
       <c r="D65" t="s">
@@ -4976,7 +4271,6 @@
         <v>71</v>
       </c>
       <c r="J65">
-        <f t="shared" si="12"/>
         <v>2030151</v>
       </c>
       <c r="K65" t="s">
@@ -4986,16 +4280,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="66" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66">
-        <f t="shared" si="10"/>
         <v>1030152</v>
       </c>
       <c r="B66" s="7">
         <v>152</v>
       </c>
       <c r="C66">
-        <f t="shared" si="11"/>
         <v>1300152</v>
       </c>
       <c r="D66" t="s">
@@ -5017,7 +4309,6 @@
         <v>71</v>
       </c>
       <c r="J66">
-        <f t="shared" si="12"/>
         <v>2030152</v>
       </c>
       <c r="K66" t="s">
@@ -5027,16 +4318,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="67" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67">
-        <f t="shared" si="10"/>
         <v>1030161</v>
       </c>
       <c r="B67" s="7">
         <v>161</v>
       </c>
       <c r="C67">
-        <f t="shared" si="11"/>
         <v>1300161</v>
       </c>
       <c r="D67" t="s">
@@ -5058,7 +4347,6 @@
         <v>71</v>
       </c>
       <c r="J67">
-        <f t="shared" si="12"/>
         <v>2030161</v>
       </c>
       <c r="K67" t="s">
@@ -5068,16 +4356,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="68" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68">
-        <f t="shared" si="10"/>
         <v>1030162</v>
       </c>
       <c r="B68" s="7">
         <v>162</v>
       </c>
       <c r="C68">
-        <f t="shared" si="11"/>
         <v>1300162</v>
       </c>
       <c r="D68" t="s">
@@ -5099,7 +4385,6 @@
         <v>71</v>
       </c>
       <c r="J68">
-        <f t="shared" si="12"/>
         <v>2030162</v>
       </c>
       <c r="K68" t="s">
@@ -5109,16 +4394,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="69" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69">
-        <f t="shared" ref="A69:A100" si="13">1000000+E69*10000+B69</f>
         <v>1030163</v>
       </c>
       <c r="B69" s="7">
         <v>163</v>
       </c>
       <c r="C69">
-        <f t="shared" ref="C69:C100" si="14">1000000+E69*100000+B69</f>
         <v>1300163</v>
       </c>
       <c r="D69" t="s">
@@ -5140,7 +4423,6 @@
         <v>71</v>
       </c>
       <c r="J69">
-        <f t="shared" si="12"/>
         <v>2030163</v>
       </c>
       <c r="K69" t="s">
@@ -5150,16 +4432,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="70" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70">
-        <f t="shared" si="13"/>
         <v>1030164</v>
       </c>
       <c r="B70" s="7">
         <v>164</v>
       </c>
       <c r="C70">
-        <f t="shared" si="14"/>
         <v>1300164</v>
       </c>
       <c r="D70" t="s">
@@ -5181,7 +4461,6 @@
         <v>71</v>
       </c>
       <c r="J70">
-        <f t="shared" si="12"/>
         <v>2030164</v>
       </c>
       <c r="K70" t="s">
@@ -5191,16 +4470,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="71" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71">
-        <f t="shared" si="13"/>
         <v>1030165</v>
       </c>
       <c r="B71" s="7">
         <v>165</v>
       </c>
       <c r="C71">
-        <f t="shared" si="14"/>
         <v>1300165</v>
       </c>
       <c r="D71" t="s">
@@ -5222,7 +4499,6 @@
         <v>71</v>
       </c>
       <c r="J71">
-        <f t="shared" si="12"/>
         <v>2030165</v>
       </c>
       <c r="K71" t="s">
@@ -5232,16 +4508,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="72" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72">
-        <f t="shared" si="13"/>
         <v>1030166</v>
       </c>
       <c r="B72" s="7">
         <v>166</v>
       </c>
       <c r="C72">
-        <f t="shared" si="14"/>
         <v>1300166</v>
       </c>
       <c r="D72" t="s">
@@ -5263,7 +4537,6 @@
         <v>71</v>
       </c>
       <c r="J72">
-        <f t="shared" si="12"/>
         <v>2030166</v>
       </c>
       <c r="K72" t="s">
@@ -5273,16 +4546,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="73" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73">
-        <f t="shared" si="13"/>
         <v>1030167</v>
       </c>
       <c r="B73" s="7">
         <v>167</v>
       </c>
       <c r="C73">
-        <f t="shared" si="14"/>
         <v>1300167</v>
       </c>
       <c r="D73" t="s">
@@ -5304,7 +4575,6 @@
         <v>71</v>
       </c>
       <c r="J73">
-        <f t="shared" si="12"/>
         <v>2030167</v>
       </c>
       <c r="K73" t="s">
@@ -5314,16 +4584,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="74" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74">
-        <f t="shared" si="13"/>
         <v>1030168</v>
       </c>
       <c r="B74" s="7">
         <v>168</v>
       </c>
       <c r="C74">
-        <f t="shared" si="14"/>
         <v>1300168</v>
       </c>
       <c r="D74" t="s">
@@ -5345,7 +4613,6 @@
         <v>71</v>
       </c>
       <c r="J74">
-        <f t="shared" si="12"/>
         <v>2030168</v>
       </c>
       <c r="K74" t="s">
@@ -5355,16 +4622,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="75" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75">
-        <f t="shared" si="13"/>
         <v>1030169</v>
       </c>
       <c r="B75" s="7">
         <v>169</v>
       </c>
       <c r="C75">
-        <f t="shared" si="14"/>
         <v>1300169</v>
       </c>
       <c r="D75" t="s">
@@ -5386,7 +4651,6 @@
         <v>71</v>
       </c>
       <c r="J75">
-        <f t="shared" si="12"/>
         <v>2030169</v>
       </c>
       <c r="K75" t="s">
@@ -5396,16 +4660,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="76" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76">
-        <f t="shared" si="13"/>
         <v>1030170</v>
       </c>
       <c r="B76" s="7">
         <v>170</v>
       </c>
       <c r="C76">
-        <f t="shared" si="14"/>
         <v>1300170</v>
       </c>
       <c r="D76" t="s">
@@ -5427,7 +4689,6 @@
         <v>71</v>
       </c>
       <c r="J76">
-        <f t="shared" si="12"/>
         <v>2030170</v>
       </c>
       <c r="K76" t="s">
@@ -5437,16 +4698,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="77" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77">
-        <f t="shared" si="13"/>
         <v>1030171</v>
       </c>
       <c r="B77" s="7">
         <v>171</v>
       </c>
       <c r="C77">
-        <f t="shared" si="14"/>
         <v>1300171</v>
       </c>
       <c r="D77" t="s">
@@ -5468,7 +4727,6 @@
         <v>71</v>
       </c>
       <c r="J77">
-        <f t="shared" si="12"/>
         <v>2030171</v>
       </c>
       <c r="K77" t="s">
@@ -5478,16 +4736,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="78" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78">
-        <f t="shared" si="13"/>
         <v>1030172</v>
       </c>
       <c r="B78" s="7">
         <v>172</v>
       </c>
       <c r="C78">
-        <f t="shared" si="14"/>
         <v>1300172</v>
       </c>
       <c r="D78" t="s">
@@ -5509,7 +4765,6 @@
         <v>71</v>
       </c>
       <c r="J78">
-        <f t="shared" si="12"/>
         <v>2030172</v>
       </c>
       <c r="K78" t="s">
@@ -5519,16 +4774,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="79" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79">
-        <f t="shared" si="13"/>
         <v>1030181</v>
       </c>
       <c r="B79" s="7">
         <v>181</v>
       </c>
       <c r="C79">
-        <f t="shared" si="14"/>
         <v>1300181</v>
       </c>
       <c r="D79" t="s">
@@ -5550,7 +4803,6 @@
         <v>71</v>
       </c>
       <c r="J79">
-        <f t="shared" si="12"/>
         <v>2030181</v>
       </c>
       <c r="K79" t="s">
@@ -5560,16 +4812,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="80" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80">
-        <f t="shared" si="13"/>
         <v>1030182</v>
       </c>
       <c r="B80" s="7">
         <v>182</v>
       </c>
       <c r="C80">
-        <f t="shared" si="14"/>
         <v>1300182</v>
       </c>
       <c r="D80" t="s">
@@ -5591,7 +4841,6 @@
         <v>71</v>
       </c>
       <c r="J80">
-        <f t="shared" si="12"/>
         <v>2030182</v>
       </c>
       <c r="K80" t="s">
@@ -5601,16 +4850,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="81" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81">
-        <f t="shared" si="13"/>
         <v>1030183</v>
       </c>
       <c r="B81" s="7">
         <v>183</v>
       </c>
       <c r="C81">
-        <f t="shared" si="14"/>
         <v>1300183</v>
       </c>
       <c r="D81" t="s">
@@ -5632,7 +4879,6 @@
         <v>71</v>
       </c>
       <c r="J81">
-        <f t="shared" si="12"/>
         <v>2030183</v>
       </c>
       <c r="K81" t="s">
@@ -5642,16 +4888,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="82" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82">
-        <f t="shared" si="13"/>
         <v>1030184</v>
       </c>
       <c r="B82" s="7">
         <v>184</v>
       </c>
       <c r="C82">
-        <f t="shared" si="14"/>
         <v>1300184</v>
       </c>
       <c r="D82" t="s">
@@ -5673,7 +4917,6 @@
         <v>71</v>
       </c>
       <c r="J82">
-        <f t="shared" si="12"/>
         <v>2030184</v>
       </c>
       <c r="K82" t="s">
@@ -5683,16 +4926,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="83" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83">
-        <f t="shared" si="13"/>
         <v>1030185</v>
       </c>
       <c r="B83" s="7">
         <v>185</v>
       </c>
       <c r="C83">
-        <f t="shared" si="14"/>
         <v>1300185</v>
       </c>
       <c r="D83" t="s">
@@ -5714,7 +4955,6 @@
         <v>71</v>
       </c>
       <c r="J83">
-        <f t="shared" si="12"/>
         <v>2030185</v>
       </c>
       <c r="K83" t="s">
@@ -5724,16 +4964,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="84" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84">
-        <f t="shared" si="13"/>
         <v>1030186</v>
       </c>
       <c r="B84" s="7">
         <v>186</v>
       </c>
       <c r="C84">
-        <f t="shared" si="14"/>
         <v>1300186</v>
       </c>
       <c r="D84" t="s">
@@ -5755,7 +4993,6 @@
         <v>71</v>
       </c>
       <c r="J84">
-        <f t="shared" si="12"/>
         <v>2030186</v>
       </c>
       <c r="K84" t="s">
@@ -5765,16 +5002,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="85" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85">
-        <f t="shared" si="13"/>
         <v>1030187</v>
       </c>
       <c r="B85" s="7">
         <v>187</v>
       </c>
       <c r="C85">
-        <f t="shared" si="14"/>
         <v>1300187</v>
       </c>
       <c r="D85" t="s">
@@ -5796,7 +5031,6 @@
         <v>71</v>
       </c>
       <c r="J85">
-        <f t="shared" si="12"/>
         <v>2030187</v>
       </c>
       <c r="K85" t="s">
@@ -5806,16 +5040,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="86" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86">
-        <f t="shared" si="13"/>
         <v>1030188</v>
       </c>
       <c r="B86" s="7">
         <v>188</v>
       </c>
       <c r="C86">
-        <f t="shared" si="14"/>
         <v>1300188</v>
       </c>
       <c r="D86" t="s">
@@ -5837,7 +5069,6 @@
         <v>71</v>
       </c>
       <c r="J86">
-        <f t="shared" si="12"/>
         <v>2030188</v>
       </c>
       <c r="K86" t="s">
@@ -5847,16 +5078,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="87" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87">
-        <f t="shared" si="13"/>
         <v>1030189</v>
       </c>
       <c r="B87" s="7">
         <v>189</v>
       </c>
       <c r="C87">
-        <f t="shared" si="14"/>
         <v>1300189</v>
       </c>
       <c r="D87" t="s">
@@ -5878,7 +5107,6 @@
         <v>71</v>
       </c>
       <c r="J87">
-        <f t="shared" si="12"/>
         <v>2030189</v>
       </c>
       <c r="K87" t="s">
@@ -5888,16 +5116,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="88" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88">
-        <f t="shared" si="13"/>
         <v>1030190</v>
       </c>
       <c r="B88" s="7">
         <v>190</v>
       </c>
       <c r="C88">
-        <f t="shared" si="14"/>
         <v>1300190</v>
       </c>
       <c r="D88" t="s">
@@ -5919,7 +5145,6 @@
         <v>71</v>
       </c>
       <c r="J88">
-        <f t="shared" si="12"/>
         <v>2030190</v>
       </c>
       <c r="K88" t="s">
@@ -5929,16 +5154,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="89" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89">
-        <f t="shared" si="13"/>
         <v>1030191</v>
       </c>
       <c r="B89" s="7">
         <v>191</v>
       </c>
       <c r="C89">
-        <f t="shared" si="14"/>
         <v>1300191</v>
       </c>
       <c r="D89" t="s">
@@ -5960,7 +5183,6 @@
         <v>71</v>
       </c>
       <c r="J89">
-        <f t="shared" si="12"/>
         <v>2030191</v>
       </c>
       <c r="K89" t="s">
@@ -5970,16 +5192,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="90" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90">
-        <f t="shared" si="13"/>
         <v>1030192</v>
       </c>
       <c r="B90" s="7">
         <v>192</v>
       </c>
       <c r="C90">
-        <f t="shared" si="14"/>
         <v>1300192</v>
       </c>
       <c r="D90" t="s">
@@ -6001,7 +5221,6 @@
         <v>71</v>
       </c>
       <c r="J90">
-        <f t="shared" si="12"/>
         <v>2030192</v>
       </c>
       <c r="K90" t="s">
@@ -6011,16 +5230,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="91" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91">
-        <f t="shared" si="13"/>
         <v>1030201</v>
       </c>
       <c r="B91" s="7">
         <v>201</v>
       </c>
       <c r="C91">
-        <f t="shared" si="14"/>
         <v>1300201</v>
       </c>
       <c r="D91" t="s">
@@ -6042,7 +5259,6 @@
         <v>71</v>
       </c>
       <c r="J91">
-        <f t="shared" si="12"/>
         <v>2030201</v>
       </c>
       <c r="K91" t="s">
@@ -6052,16 +5268,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="92" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92">
-        <f t="shared" si="13"/>
         <v>1030202</v>
       </c>
       <c r="B92" s="7">
         <v>202</v>
       </c>
       <c r="C92">
-        <f t="shared" si="14"/>
         <v>1300202</v>
       </c>
       <c r="D92" t="s">
@@ -6083,7 +5297,6 @@
         <v>71</v>
       </c>
       <c r="J92">
-        <f t="shared" si="12"/>
         <v>2030202</v>
       </c>
       <c r="K92" t="s">
@@ -6093,16 +5306,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="93" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93">
-        <f t="shared" si="13"/>
         <v>1030203</v>
       </c>
       <c r="B93" s="7">
         <v>203</v>
       </c>
       <c r="C93">
-        <f t="shared" si="14"/>
         <v>1300203</v>
       </c>
       <c r="D93" t="s">
@@ -6124,7 +5335,6 @@
         <v>71</v>
       </c>
       <c r="J93">
-        <f t="shared" si="12"/>
         <v>2030203</v>
       </c>
       <c r="K93" t="s">
@@ -6134,16 +5344,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="94" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94">
-        <f t="shared" si="13"/>
         <v>1030204</v>
       </c>
       <c r="B94" s="7">
         <v>204</v>
       </c>
       <c r="C94">
-        <f t="shared" si="14"/>
         <v>1300204</v>
       </c>
       <c r="D94" t="s">
@@ -6165,7 +5373,6 @@
         <v>71</v>
       </c>
       <c r="J94">
-        <f t="shared" si="12"/>
         <v>2030204</v>
       </c>
       <c r="K94" t="s">
@@ -6175,16 +5382,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="95" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95">
-        <f t="shared" si="13"/>
         <v>1030205</v>
       </c>
       <c r="B95" s="7">
         <v>205</v>
       </c>
       <c r="C95">
-        <f t="shared" si="14"/>
         <v>1300205</v>
       </c>
       <c r="D95" t="s">
@@ -6206,7 +5411,6 @@
         <v>71</v>
       </c>
       <c r="J95">
-        <f t="shared" si="12"/>
         <v>2030205</v>
       </c>
       <c r="K95" t="s">
@@ -6216,16 +5420,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="96" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96">
-        <f t="shared" si="13"/>
         <v>1030206</v>
       </c>
       <c r="B96" s="7">
         <v>206</v>
       </c>
       <c r="C96">
-        <f t="shared" si="14"/>
         <v>1300206</v>
       </c>
       <c r="D96" t="s">
@@ -6247,7 +5449,6 @@
         <v>71</v>
       </c>
       <c r="J96">
-        <f t="shared" ref="J96:J130" si="15">2000000+E96*10000+B96</f>
         <v>2030206</v>
       </c>
       <c r="K96" t="s">
@@ -6257,16 +5458,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="97" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97">
-        <f t="shared" si="13"/>
         <v>1030207</v>
       </c>
       <c r="B97" s="7">
         <v>207</v>
       </c>
       <c r="C97">
-        <f t="shared" si="14"/>
         <v>1300207</v>
       </c>
       <c r="D97" t="s">
@@ -6288,7 +5487,6 @@
         <v>71</v>
       </c>
       <c r="J97">
-        <f t="shared" si="15"/>
         <v>2030207</v>
       </c>
       <c r="K97" t="s">
@@ -6298,16 +5496,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="98" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98">
-        <f t="shared" si="13"/>
         <v>1030208</v>
       </c>
       <c r="B98" s="7">
         <v>208</v>
       </c>
       <c r="C98">
-        <f t="shared" si="14"/>
         <v>1300208</v>
       </c>
       <c r="D98" t="s">
@@ -6329,7 +5525,6 @@
         <v>71</v>
       </c>
       <c r="J98">
-        <f t="shared" si="15"/>
         <v>2030208</v>
       </c>
       <c r="K98" t="s">
@@ -6339,16 +5534,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="99" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99">
-        <f t="shared" si="13"/>
         <v>1030209</v>
       </c>
       <c r="B99" s="7">
         <v>209</v>
       </c>
       <c r="C99">
-        <f t="shared" si="14"/>
         <v>1300209</v>
       </c>
       <c r="D99" t="s">
@@ -6370,7 +5563,6 @@
         <v>71</v>
       </c>
       <c r="J99">
-        <f t="shared" si="15"/>
         <v>2030209</v>
       </c>
       <c r="K99" t="s">
@@ -6380,16 +5572,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="100" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100">
-        <f t="shared" si="13"/>
         <v>1030210</v>
       </c>
       <c r="B100" s="7">
         <v>210</v>
       </c>
       <c r="C100">
-        <f t="shared" si="14"/>
         <v>1300210</v>
       </c>
       <c r="D100" t="s">
@@ -6411,7 +5601,6 @@
         <v>71</v>
       </c>
       <c r="J100">
-        <f t="shared" si="15"/>
         <v>2030210</v>
       </c>
       <c r="K100" t="s">
@@ -6421,16 +5610,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="101" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101">
-        <f t="shared" ref="A101:A132" si="16">1000000+E101*10000+B101</f>
         <v>1030211</v>
       </c>
       <c r="B101" s="7">
         <v>211</v>
       </c>
       <c r="C101">
-        <f t="shared" ref="C101:C130" si="17">1000000+E101*100000+B101</f>
         <v>1300211</v>
       </c>
       <c r="D101" t="s">
@@ -6452,7 +5639,6 @@
         <v>71</v>
       </c>
       <c r="J101">
-        <f t="shared" si="15"/>
         <v>2030211</v>
       </c>
       <c r="K101" t="s">
@@ -6462,16 +5648,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="102" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102">
-        <f t="shared" si="16"/>
         <v>1030212</v>
       </c>
       <c r="B102" s="7">
         <v>212</v>
       </c>
       <c r="C102">
-        <f t="shared" si="17"/>
         <v>1300212</v>
       </c>
       <c r="D102" t="s">
@@ -6493,7 +5677,6 @@
         <v>71</v>
       </c>
       <c r="J102">
-        <f t="shared" si="15"/>
         <v>2030212</v>
       </c>
       <c r="K102" t="s">
@@ -6503,16 +5686,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="103" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103">
-        <f t="shared" si="16"/>
         <v>1030221</v>
       </c>
       <c r="B103" s="7">
         <v>221</v>
       </c>
       <c r="C103">
-        <f t="shared" si="17"/>
         <v>1300221</v>
       </c>
       <c r="D103" t="s">
@@ -6534,7 +5715,6 @@
         <v>71</v>
       </c>
       <c r="J103">
-        <f t="shared" si="15"/>
         <v>2030221</v>
       </c>
       <c r="K103" t="s">
@@ -6544,16 +5724,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="104" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104">
-        <f t="shared" si="16"/>
         <v>1030222</v>
       </c>
       <c r="B104" s="7">
         <v>222</v>
       </c>
       <c r="C104">
-        <f t="shared" si="17"/>
         <v>1300222</v>
       </c>
       <c r="D104" t="s">
@@ -6575,7 +5753,6 @@
         <v>71</v>
       </c>
       <c r="J104">
-        <f t="shared" si="15"/>
         <v>2030222</v>
       </c>
       <c r="K104" t="s">
@@ -6585,16 +5762,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="105" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105">
-        <f t="shared" si="16"/>
         <v>1030223</v>
       </c>
       <c r="B105" s="7">
         <v>223</v>
       </c>
       <c r="C105">
-        <f t="shared" si="17"/>
         <v>1300223</v>
       </c>
       <c r="D105" t="s">
@@ -6616,7 +5791,6 @@
         <v>71</v>
       </c>
       <c r="J105">
-        <f t="shared" si="15"/>
         <v>2030223</v>
       </c>
       <c r="K105" t="s">
@@ -6626,16 +5800,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="106" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106">
-        <f t="shared" si="16"/>
         <v>1030224</v>
       </c>
       <c r="B106" s="7">
         <v>224</v>
       </c>
       <c r="C106">
-        <f t="shared" si="17"/>
         <v>1300224</v>
       </c>
       <c r="D106" t="s">
@@ -6657,7 +5829,6 @@
         <v>71</v>
       </c>
       <c r="J106">
-        <f t="shared" si="15"/>
         <v>2030224</v>
       </c>
       <c r="K106" t="s">
@@ -6667,16 +5838,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="107" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107">
-        <f t="shared" si="16"/>
         <v>1030225</v>
       </c>
       <c r="B107" s="7">
         <v>225</v>
       </c>
       <c r="C107">
-        <f t="shared" si="17"/>
         <v>1300225</v>
       </c>
       <c r="D107" t="s">
@@ -6698,7 +5867,6 @@
         <v>71</v>
       </c>
       <c r="J107">
-        <f t="shared" si="15"/>
         <v>2030225</v>
       </c>
       <c r="K107" t="s">
@@ -6708,16 +5876,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="108" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108">
-        <f t="shared" si="16"/>
         <v>1030226</v>
       </c>
       <c r="B108" s="7">
         <v>226</v>
       </c>
       <c r="C108">
-        <f t="shared" si="17"/>
         <v>1300226</v>
       </c>
       <c r="D108" t="s">
@@ -6739,7 +5905,6 @@
         <v>71</v>
       </c>
       <c r="J108">
-        <f t="shared" si="15"/>
         <v>2030226</v>
       </c>
       <c r="K108" t="s">
@@ -6749,16 +5914,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="109" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109">
-        <f t="shared" si="16"/>
         <v>1030227</v>
       </c>
       <c r="B109" s="7">
         <v>227</v>
       </c>
       <c r="C109">
-        <f t="shared" si="17"/>
         <v>1300227</v>
       </c>
       <c r="D109" t="s">
@@ -6780,7 +5943,6 @@
         <v>71</v>
       </c>
       <c r="J109">
-        <f t="shared" si="15"/>
         <v>2030227</v>
       </c>
       <c r="K109" t="s">
@@ -6790,16 +5952,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="110" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110">
-        <f t="shared" si="16"/>
         <v>1030228</v>
       </c>
       <c r="B110" s="7">
         <v>228</v>
       </c>
       <c r="C110">
-        <f t="shared" si="17"/>
         <v>1300228</v>
       </c>
       <c r="D110" t="s">
@@ -6821,7 +5981,6 @@
         <v>71</v>
       </c>
       <c r="J110">
-        <f t="shared" si="15"/>
         <v>2030228</v>
       </c>
       <c r="K110" t="s">
@@ -6831,16 +5990,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="111" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111">
-        <f t="shared" si="16"/>
         <v>1030229</v>
       </c>
       <c r="B111" s="7">
         <v>229</v>
       </c>
       <c r="C111">
-        <f t="shared" si="17"/>
         <v>1300229</v>
       </c>
       <c r="D111" t="s">
@@ -6862,7 +6019,6 @@
         <v>71</v>
       </c>
       <c r="J111">
-        <f t="shared" si="15"/>
         <v>2030229</v>
       </c>
       <c r="K111" t="s">
@@ -6872,16 +6028,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="112" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112">
-        <f t="shared" si="16"/>
         <v>1030230</v>
       </c>
       <c r="B112" s="7">
         <v>230</v>
       </c>
       <c r="C112">
-        <f t="shared" si="17"/>
         <v>1300230</v>
       </c>
       <c r="D112" t="s">
@@ -6903,7 +6057,6 @@
         <v>71</v>
       </c>
       <c r="J112">
-        <f t="shared" si="15"/>
         <v>2030230</v>
       </c>
       <c r="K112" t="s">
@@ -6913,16 +6066,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="113" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113">
-        <f t="shared" si="16"/>
         <v>1030231</v>
       </c>
       <c r="B113" s="7">
         <v>231</v>
       </c>
       <c r="C113">
-        <f t="shared" si="17"/>
         <v>1300231</v>
       </c>
       <c r="D113" t="s">
@@ -6944,7 +6095,6 @@
         <v>71</v>
       </c>
       <c r="J113">
-        <f t="shared" si="15"/>
         <v>2030231</v>
       </c>
       <c r="K113" t="s">
@@ -6954,16 +6104,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="114" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114">
-        <f t="shared" si="16"/>
         <v>1030232</v>
       </c>
       <c r="B114" s="7">
         <v>232</v>
       </c>
       <c r="C114">
-        <f t="shared" si="17"/>
         <v>1300232</v>
       </c>
       <c r="D114" t="s">
@@ -6985,7 +6133,6 @@
         <v>71</v>
       </c>
       <c r="J114">
-        <f t="shared" si="15"/>
         <v>2030232</v>
       </c>
       <c r="K114" t="s">
@@ -6995,16 +6142,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="115" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115">
-        <f t="shared" si="16"/>
         <v>1030241</v>
       </c>
       <c r="B115" s="7">
         <v>241</v>
       </c>
       <c r="C115">
-        <f t="shared" si="17"/>
         <v>1300241</v>
       </c>
       <c r="D115" t="s">
@@ -7026,7 +6171,6 @@
         <v>71</v>
       </c>
       <c r="J115">
-        <f t="shared" si="15"/>
         <v>2030241</v>
       </c>
       <c r="K115" t="s">
@@ -7036,16 +6180,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="116" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116">
-        <f t="shared" si="16"/>
         <v>1030242</v>
       </c>
       <c r="B116" s="7">
         <v>242</v>
       </c>
       <c r="C116">
-        <f t="shared" si="17"/>
         <v>1300242</v>
       </c>
       <c r="D116" t="s">
@@ -7067,7 +6209,6 @@
         <v>71</v>
       </c>
       <c r="J116">
-        <f t="shared" si="15"/>
         <v>2030242</v>
       </c>
       <c r="K116" t="s">
@@ -7077,16 +6218,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="117" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117">
-        <f t="shared" si="16"/>
         <v>1030243</v>
       </c>
       <c r="B117" s="7">
         <v>243</v>
       </c>
       <c r="C117">
-        <f t="shared" si="17"/>
         <v>1300243</v>
       </c>
       <c r="D117" t="s">
@@ -7108,7 +6247,6 @@
         <v>71</v>
       </c>
       <c r="J117">
-        <f t="shared" si="15"/>
         <v>2030243</v>
       </c>
       <c r="K117" t="s">
@@ -7118,16 +6256,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="118" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118">
-        <f t="shared" si="16"/>
         <v>1030244</v>
       </c>
       <c r="B118" s="7">
         <v>244</v>
       </c>
       <c r="C118">
-        <f t="shared" si="17"/>
         <v>1300244</v>
       </c>
       <c r="D118" t="s">
@@ -7149,7 +6285,6 @@
         <v>71</v>
       </c>
       <c r="J118">
-        <f t="shared" si="15"/>
         <v>2030244</v>
       </c>
       <c r="K118" t="s">
@@ -7159,16 +6294,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="119" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119">
-        <f t="shared" si="16"/>
         <v>1030245</v>
       </c>
       <c r="B119" s="7">
         <v>245</v>
       </c>
       <c r="C119">
-        <f t="shared" si="17"/>
         <v>1300245</v>
       </c>
       <c r="D119" t="s">
@@ -7190,7 +6323,6 @@
         <v>71</v>
       </c>
       <c r="J119">
-        <f t="shared" si="15"/>
         <v>2030245</v>
       </c>
       <c r="K119" t="s">
@@ -7200,16 +6332,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="120" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120">
-        <f t="shared" si="16"/>
         <v>1030246</v>
       </c>
       <c r="B120" s="7">
         <v>246</v>
       </c>
       <c r="C120">
-        <f t="shared" si="17"/>
         <v>1300246</v>
       </c>
       <c r="D120" t="s">
@@ -7231,7 +6361,6 @@
         <v>71</v>
       </c>
       <c r="J120">
-        <f t="shared" si="15"/>
         <v>2030246</v>
       </c>
       <c r="K120" t="s">
@@ -7241,16 +6370,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="121" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121">
-        <f t="shared" si="16"/>
         <v>1030247</v>
       </c>
       <c r="B121" s="7">
         <v>247</v>
       </c>
       <c r="C121">
-        <f t="shared" si="17"/>
         <v>1300247</v>
       </c>
       <c r="D121" t="s">
@@ -7272,7 +6399,6 @@
         <v>71</v>
       </c>
       <c r="J121">
-        <f t="shared" si="15"/>
         <v>2030247</v>
       </c>
       <c r="K121" t="s">
@@ -7282,16 +6408,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="122" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122">
-        <f t="shared" si="16"/>
         <v>1030248</v>
       </c>
       <c r="B122" s="7">
         <v>248</v>
       </c>
       <c r="C122">
-        <f t="shared" si="17"/>
         <v>1300248</v>
       </c>
       <c r="D122" t="s">
@@ -7313,7 +6437,6 @@
         <v>71</v>
       </c>
       <c r="J122">
-        <f t="shared" si="15"/>
         <v>2030248</v>
       </c>
       <c r="K122" t="s">
@@ -7323,16 +6446,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="123" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123">
-        <f t="shared" si="16"/>
         <v>1030249</v>
       </c>
       <c r="B123" s="7">
         <v>249</v>
       </c>
       <c r="C123">
-        <f t="shared" si="17"/>
         <v>1300249</v>
       </c>
       <c r="D123" t="s">
@@ -7354,7 +6475,6 @@
         <v>71</v>
       </c>
       <c r="J123">
-        <f t="shared" si="15"/>
         <v>2030249</v>
       </c>
       <c r="K123" t="s">
@@ -7364,16 +6484,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="124" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124">
-        <f t="shared" si="16"/>
         <v>1030250</v>
       </c>
       <c r="B124" s="7">
         <v>250</v>
       </c>
       <c r="C124">
-        <f t="shared" si="17"/>
         <v>1300250</v>
       </c>
       <c r="D124" t="s">
@@ -7395,7 +6513,6 @@
         <v>71</v>
       </c>
       <c r="J124">
-        <f t="shared" si="15"/>
         <v>2030250</v>
       </c>
       <c r="K124" t="s">
@@ -7405,16 +6522,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="125" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125">
-        <f t="shared" si="16"/>
         <v>1030251</v>
       </c>
       <c r="B125" s="7">
         <v>251</v>
       </c>
       <c r="C125">
-        <f t="shared" si="17"/>
         <v>1300251</v>
       </c>
       <c r="D125" t="s">
@@ -7436,7 +6551,6 @@
         <v>71</v>
       </c>
       <c r="J125">
-        <f t="shared" si="15"/>
         <v>2030251</v>
       </c>
       <c r="K125" t="s">
@@ -7446,16 +6560,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="126" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126">
-        <f t="shared" si="16"/>
         <v>1030252</v>
       </c>
       <c r="B126" s="7">
         <v>252</v>
       </c>
       <c r="C126">
-        <f t="shared" si="17"/>
         <v>1300252</v>
       </c>
       <c r="D126" t="s">
@@ -7477,7 +6589,6 @@
         <v>71</v>
       </c>
       <c r="J126">
-        <f t="shared" si="15"/>
         <v>2030252</v>
       </c>
       <c r="K126" t="s">
@@ -7487,16 +6598,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="127" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127">
-        <f t="shared" si="16"/>
         <v>1031001</v>
       </c>
       <c r="B127" s="7">
         <v>1001</v>
       </c>
       <c r="C127">
-        <f t="shared" si="17"/>
         <v>1301001</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -7514,32 +6623,27 @@
       <c r="H127">
         <v>1</v>
       </c>
-      <c r="I127" t="str">
-        <f>"itemicon_"&amp;A127&amp;".png"</f>
-        <v>itemicon_1031001.png</v>
+      <c r="I127" t="s">
+        <v>267</v>
       </c>
       <c r="J127">
-        <f t="shared" si="15"/>
         <v>2031001</v>
       </c>
       <c r="L127">
         <v>2</v>
       </c>
-      <c r="M127"/>
       <c r="N127">
         <v>1</v>
       </c>
     </row>
-    <row r="128" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="128" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128">
-        <f t="shared" si="16"/>
         <v>1031002</v>
       </c>
       <c r="B128" s="7">
         <v>1002</v>
       </c>
       <c r="C128">
-        <f t="shared" si="17"/>
         <v>1301002</v>
       </c>
       <c r="D128" s="7" t="s">
@@ -7557,32 +6661,27 @@
       <c r="H128">
         <v>1</v>
       </c>
-      <c r="I128" t="str">
-        <f>"itemicon_"&amp;A128&amp;".png"</f>
-        <v>itemicon_1031002.png</v>
+      <c r="I128" t="s">
+        <v>268</v>
       </c>
       <c r="J128">
-        <f t="shared" si="15"/>
         <v>2031002</v>
       </c>
       <c r="L128">
         <v>3</v>
       </c>
-      <c r="M128"/>
       <c r="N128">
         <v>1</v>
       </c>
     </row>
-    <row r="129" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="129" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129">
-        <f t="shared" si="16"/>
         <v>1031201</v>
       </c>
       <c r="B129" s="7">
         <v>1201</v>
       </c>
       <c r="C129">
-        <f t="shared" si="17"/>
         <v>1301201</v>
       </c>
       <c r="D129" t="s">
@@ -7600,32 +6699,27 @@
       <c r="H129">
         <v>1</v>
       </c>
-      <c r="I129" t="str">
-        <f>"itemicon_"&amp;A129&amp;".png"</f>
-        <v>itemicon_1031201.png</v>
+      <c r="I129" t="s">
+        <v>269</v>
       </c>
       <c r="J129">
-        <f t="shared" si="15"/>
         <v>2031201</v>
       </c>
       <c r="L129">
         <v>1002</v>
       </c>
-      <c r="M129"/>
       <c r="N129">
         <v>1</v>
       </c>
     </row>
-    <row r="130" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="130" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130">
-        <f t="shared" si="16"/>
         <v>1031202</v>
       </c>
       <c r="B130" s="7">
         <v>1202</v>
       </c>
       <c r="C130">
-        <f t="shared" si="17"/>
         <v>1301202</v>
       </c>
       <c r="D130" t="s">
@@ -7643,25 +6737,21 @@
       <c r="H130">
         <v>1</v>
       </c>
-      <c r="I130" t="str">
-        <f>"itemicon_"&amp;A130&amp;".png"</f>
-        <v>itemicon_1031202.png</v>
+      <c r="I130" t="s">
+        <v>270</v>
       </c>
       <c r="J130">
-        <f t="shared" si="15"/>
         <v>2031202</v>
       </c>
       <c r="L130">
         <v>1003</v>
       </c>
-      <c r="M130"/>
       <c r="N130">
         <v>1</v>
       </c>
     </row>
-    <row r="131" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="131" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131">
-        <f t="shared" si="16"/>
         <v>1031350</v>
       </c>
       <c r="B131" s="7">
@@ -7698,9 +6788,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="132" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132">
-        <f t="shared" si="16"/>
         <v>1031351</v>
       </c>
       <c r="B132" s="7">
@@ -7737,16 +6826,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="133" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133">
-        <f t="shared" ref="A133:A146" si="18">1000000+E133*10000+B133</f>
         <v>1021401</v>
       </c>
       <c r="B133" s="7">
         <v>1401</v>
       </c>
       <c r="C133">
-        <f t="shared" ref="C133:C146" si="19">1000000+E133*100000+B133</f>
         <v>1201401</v>
       </c>
       <c r="D133" s="10" t="s">
@@ -7764,32 +6851,27 @@
       <c r="H133">
         <v>1</v>
       </c>
-      <c r="I133" t="str">
-        <f t="shared" ref="I133:I146" si="20">"itemicon_"&amp;A133&amp;".png"</f>
-        <v>itemicon_1021401.png</v>
+      <c r="I133" t="s">
+        <v>271</v>
       </c>
       <c r="J133">
-        <f t="shared" ref="J133:J146" si="21">2000000+E133*10000+B133</f>
         <v>2021401</v>
       </c>
       <c r="L133">
         <v>2002</v>
       </c>
-      <c r="M133"/>
       <c r="N133">
         <v>1</v>
       </c>
     </row>
-    <row r="134" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="134" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134">
-        <f t="shared" si="18"/>
         <v>1021402</v>
       </c>
       <c r="B134" s="7">
         <v>1402</v>
       </c>
       <c r="C134">
-        <f t="shared" si="19"/>
         <v>1201402</v>
       </c>
       <c r="D134" s="10" t="s">
@@ -7807,32 +6889,27 @@
       <c r="H134">
         <v>1</v>
       </c>
-      <c r="I134" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1021402.png</v>
+      <c r="I134" t="s">
+        <v>272</v>
       </c>
       <c r="J134">
-        <f t="shared" si="21"/>
         <v>2021402</v>
       </c>
       <c r="L134">
         <v>2003</v>
       </c>
-      <c r="M134"/>
       <c r="N134">
         <v>1</v>
       </c>
     </row>
-    <row r="135" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="135" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135">
-        <f t="shared" si="18"/>
         <v>1031601</v>
       </c>
       <c r="B135" s="7">
         <v>1601</v>
       </c>
       <c r="C135">
-        <f t="shared" si="19"/>
         <v>1301601</v>
       </c>
       <c r="D135" s="11" t="s">
@@ -7850,32 +6927,27 @@
       <c r="H135">
         <v>1</v>
       </c>
-      <c r="I135" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1031601.png</v>
+      <c r="I135" t="s">
+        <v>273</v>
       </c>
       <c r="J135">
-        <f t="shared" si="21"/>
         <v>2031601</v>
       </c>
       <c r="L135">
         <v>3002</v>
       </c>
-      <c r="M135"/>
       <c r="N135">
         <v>1</v>
       </c>
     </row>
-    <row r="136" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="136" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136">
-        <f t="shared" si="18"/>
         <v>1031602</v>
       </c>
       <c r="B136" s="7">
         <v>1602</v>
       </c>
       <c r="C136">
-        <f t="shared" si="19"/>
         <v>1301602</v>
       </c>
       <c r="D136" s="11" t="s">
@@ -7893,32 +6965,27 @@
       <c r="H136">
         <v>1</v>
       </c>
-      <c r="I136" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1031602.png</v>
+      <c r="I136" t="s">
+        <v>274</v>
       </c>
       <c r="J136">
-        <f t="shared" si="21"/>
         <v>2031602</v>
       </c>
       <c r="L136">
         <v>3003</v>
       </c>
-      <c r="M136"/>
       <c r="N136">
         <v>1</v>
       </c>
     </row>
-    <row r="137" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="137" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137">
-        <f t="shared" si="18"/>
         <v>1031801</v>
       </c>
       <c r="B137" s="7">
         <v>1801</v>
       </c>
       <c r="C137">
-        <f t="shared" si="19"/>
         <v>1301801</v>
       </c>
       <c r="D137" s="12" t="s">
@@ -7936,32 +7003,27 @@
       <c r="H137">
         <v>1</v>
       </c>
-      <c r="I137" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1031801.png</v>
+      <c r="I137" t="s">
+        <v>275</v>
       </c>
       <c r="J137">
-        <f t="shared" si="21"/>
         <v>2031801</v>
       </c>
       <c r="L137">
         <v>4002</v>
       </c>
-      <c r="M137"/>
       <c r="N137">
         <v>1</v>
       </c>
     </row>
-    <row r="138" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="138" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138">
-        <f t="shared" si="18"/>
         <v>1031802</v>
       </c>
       <c r="B138" s="7">
         <v>1802</v>
       </c>
       <c r="C138">
-        <f t="shared" si="19"/>
         <v>1301802</v>
       </c>
       <c r="D138" s="12" t="s">
@@ -7979,32 +7041,27 @@
       <c r="H138">
         <v>1</v>
       </c>
-      <c r="I138" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1031802.png</v>
+      <c r="I138" t="s">
+        <v>276</v>
       </c>
       <c r="J138">
-        <f t="shared" si="21"/>
         <v>2031802</v>
       </c>
       <c r="L138">
         <v>4003</v>
       </c>
-      <c r="M138"/>
       <c r="N138">
         <v>1</v>
       </c>
     </row>
-    <row r="139" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="139" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139">
-        <f t="shared" si="18"/>
         <v>1032001</v>
       </c>
       <c r="B139" s="7">
         <v>2001</v>
       </c>
       <c r="C139">
-        <f t="shared" si="19"/>
         <v>1302001</v>
       </c>
       <c r="D139" s="13" t="s">
@@ -8022,32 +7079,27 @@
       <c r="H139">
         <v>1</v>
       </c>
-      <c r="I139" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1032001.png</v>
+      <c r="I139" t="s">
+        <v>277</v>
       </c>
       <c r="J139">
-        <f t="shared" si="21"/>
         <v>2032001</v>
       </c>
       <c r="L139">
         <v>5002</v>
       </c>
-      <c r="M139"/>
       <c r="N139">
         <v>1</v>
       </c>
     </row>
-    <row r="140" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="140" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140">
-        <f t="shared" si="18"/>
         <v>1032002</v>
       </c>
       <c r="B140" s="7">
         <v>2002</v>
       </c>
       <c r="C140">
-        <f t="shared" si="19"/>
         <v>1302002</v>
       </c>
       <c r="D140" s="13" t="s">
@@ -8065,32 +7117,27 @@
       <c r="H140">
         <v>1</v>
       </c>
-      <c r="I140" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1032002.png</v>
+      <c r="I140" t="s">
+        <v>278</v>
       </c>
       <c r="J140">
-        <f t="shared" si="21"/>
         <v>2032002</v>
       </c>
       <c r="L140">
         <v>5003</v>
       </c>
-      <c r="M140"/>
       <c r="N140">
         <v>1</v>
       </c>
     </row>
-    <row r="141" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="141" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141">
-        <f t="shared" si="18"/>
         <v>1032201</v>
       </c>
       <c r="B141" s="7">
         <v>2201</v>
       </c>
       <c r="C141">
-        <f t="shared" si="19"/>
         <v>1302201</v>
       </c>
       <c r="D141" s="14" t="s">
@@ -8108,32 +7155,27 @@
       <c r="H141">
         <v>1</v>
       </c>
-      <c r="I141" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1032201.png</v>
+      <c r="I141" t="s">
+        <v>279</v>
       </c>
       <c r="J141">
-        <f t="shared" si="21"/>
         <v>2032201</v>
       </c>
       <c r="L141">
         <v>6002</v>
       </c>
-      <c r="M141"/>
       <c r="N141">
         <v>1</v>
       </c>
     </row>
-    <row r="142" customFormat="1" ht="23" customHeight="1" spans="1:14">
+    <row r="142" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142">
-        <f t="shared" si="18"/>
         <v>1032202</v>
       </c>
       <c r="B142" s="7">
         <v>2202</v>
       </c>
       <c r="C142">
-        <f t="shared" si="19"/>
         <v>1302202</v>
       </c>
       <c r="D142" s="14" t="s">
@@ -8151,32 +7193,27 @@
       <c r="H142">
         <v>1</v>
       </c>
-      <c r="I142" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1032202.png</v>
+      <c r="I142" t="s">
+        <v>280</v>
       </c>
       <c r="J142">
-        <f t="shared" si="21"/>
         <v>2032202</v>
       </c>
       <c r="L142">
         <v>6003</v>
       </c>
-      <c r="M142"/>
       <c r="N142">
         <v>1</v>
       </c>
     </row>
-    <row r="143" ht="18" customHeight="1" spans="1:14">
+    <row r="143" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143">
-        <f t="shared" si="18"/>
         <v>1022501</v>
       </c>
       <c r="B143">
         <v>2501</v>
       </c>
       <c r="C143">
-        <f t="shared" si="19"/>
         <v>1202501</v>
       </c>
       <c r="D143" t="s">
@@ -8194,12 +7231,10 @@
       <c r="H143">
         <v>0</v>
       </c>
-      <c r="I143" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1022501.png</v>
+      <c r="I143" t="s">
+        <v>281</v>
       </c>
       <c r="J143">
-        <f t="shared" si="21"/>
         <v>2022501</v>
       </c>
       <c r="K143" t="s">
@@ -8208,17 +7243,18 @@
       <c r="N143">
         <v>999</v>
       </c>
-    </row>
-    <row r="144" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="Q143">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144">
-        <f t="shared" si="18"/>
         <v>1022502</v>
       </c>
       <c r="B144">
         <v>2502</v>
       </c>
       <c r="C144">
-        <f t="shared" si="19"/>
         <v>1202502</v>
       </c>
       <c r="D144" t="s">
@@ -8236,12 +7272,10 @@
       <c r="H144">
         <v>0</v>
       </c>
-      <c r="I144" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1022502.png</v>
+      <c r="I144" t="s">
+        <v>282</v>
       </c>
       <c r="J144">
-        <f t="shared" si="21"/>
         <v>2022502</v>
       </c>
       <c r="K144" t="s">
@@ -8254,16 +7288,14 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="145" customFormat="1" ht="18" customHeight="1" spans="1:17">
+    <row r="145" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145">
-        <f t="shared" si="18"/>
         <v>1022503</v>
       </c>
       <c r="B145">
         <v>2503</v>
       </c>
       <c r="C145">
-        <f t="shared" si="19"/>
         <v>1202503</v>
       </c>
       <c r="D145" t="s">
@@ -8281,12 +7313,10 @@
       <c r="H145">
         <v>0</v>
       </c>
-      <c r="I145" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1022503.png</v>
+      <c r="I145" t="s">
+        <v>283</v>
       </c>
       <c r="J145">
-        <f t="shared" si="21"/>
         <v>2022503</v>
       </c>
       <c r="K145" t="s">
@@ -8299,16 +7329,14 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="146" customFormat="1" ht="18" customHeight="1" spans="1:14">
+    <row r="146" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146">
-        <f t="shared" si="18"/>
         <v>1022504</v>
       </c>
       <c r="B146">
         <v>2504</v>
       </c>
       <c r="C146">
-        <f t="shared" si="19"/>
         <v>1202504</v>
       </c>
       <c r="D146" t="s">
@@ -8326,12 +7354,10 @@
       <c r="H146">
         <v>0</v>
       </c>
-      <c r="I146" t="str">
-        <f t="shared" si="20"/>
-        <v>itemicon_1022504.png</v>
+      <c r="I146" t="s">
+        <v>284</v>
       </c>
       <c r="J146">
-        <f t="shared" si="21"/>
         <v>2022504</v>
       </c>
       <c r="K146" t="s">
@@ -8341,7 +7367,7 @@
         <v>999999999</v>
       </c>
     </row>
-    <row r="147" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="147" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147">
         <v>1023001</v>
       </c>
@@ -8380,7 +7406,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="148" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="148" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148">
         <v>1023002</v>
       </c>
@@ -8419,7 +7445,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="149" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="149" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149">
         <v>1023003</v>
       </c>
@@ -8458,7 +7484,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="150" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="150" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150">
         <v>1023004</v>
       </c>
@@ -8497,7 +7523,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="151" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="151" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151">
         <v>1023005</v>
       </c>
@@ -8536,7 +7562,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="152" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="152" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152">
         <v>1023101</v>
       </c>
@@ -8575,7 +7601,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="153" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="153" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153">
         <v>1023102</v>
       </c>
@@ -8614,7 +7640,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="154" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="154" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154">
         <v>1023103</v>
       </c>
@@ -8653,7 +7679,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="155" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="155" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155">
         <v>1023104</v>
       </c>
@@ -8692,7 +7718,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="156" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="156" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156">
         <v>1023105</v>
       </c>
@@ -8731,7 +7757,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="157" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="157" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157">
         <v>1023201</v>
       </c>
@@ -8770,7 +7796,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="158" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="158" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158">
         <v>1023202</v>
       </c>
@@ -8809,7 +7835,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="159" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="159" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159">
         <v>1023203</v>
       </c>
@@ -8848,7 +7874,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="160" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="160" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160">
         <v>1023204</v>
       </c>
@@ -8887,7 +7913,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="161" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="161" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161">
         <v>1023205</v>
       </c>
@@ -8926,7 +7952,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="162" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="162" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162">
         <v>1023301</v>
       </c>
@@ -8965,7 +7991,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="163" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="163" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163">
         <v>1023302</v>
       </c>
@@ -9004,7 +8030,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="164" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="164" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164">
         <v>1023303</v>
       </c>
@@ -9043,7 +8069,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="165" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="165" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165">
         <v>1023304</v>
       </c>
@@ -9082,7 +8108,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="166" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="166" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166">
         <v>1023305</v>
       </c>
@@ -9121,7 +8147,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="167" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="167" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167">
         <v>1023401</v>
       </c>
@@ -9160,7 +8186,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="168" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="168" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168">
         <v>1023402</v>
       </c>
@@ -9199,7 +8225,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="169" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="169" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169">
         <v>1023403</v>
       </c>
@@ -9238,7 +8264,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="170" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="170" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170">
         <v>1023404</v>
       </c>
@@ -9277,7 +8303,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="171" customFormat="1" ht="21" customHeight="1" spans="1:17">
+    <row r="171" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171">
         <v>1023405</v>
       </c>
@@ -9316,9 +8342,8 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="172" ht="21" customHeight="1" spans="1:14">
+    <row r="172" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172">
-        <f>1000000+E172*10000+B172</f>
         <v>1990000</v>
       </c>
       <c r="B172" s="7">
@@ -9342,12 +8367,10 @@
       <c r="H172">
         <v>0</v>
       </c>
-      <c r="I172" t="str">
-        <f>"itemicon_"&amp;A172&amp;".png"</f>
-        <v>itemicon_1990000.png</v>
+      <c r="I172" t="s">
+        <v>285</v>
       </c>
       <c r="J172">
-        <f>2000000+E172*10000+B172</f>
         <v>2990000</v>
       </c>
       <c r="K172" t="s">
@@ -9357,9 +8380,8 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="173" ht="21" customHeight="1" spans="1:14">
+    <row r="173" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173">
-        <f>1000000+E173*10000+B173</f>
         <v>1980000</v>
       </c>
       <c r="B173" s="7">
@@ -9383,12 +8405,10 @@
       <c r="H173">
         <v>0</v>
       </c>
-      <c r="I173" t="str">
-        <f>"itemicon_"&amp;A173&amp;".png"</f>
-        <v>itemicon_1980000.png</v>
+      <c r="I173" t="s">
+        <v>286</v>
       </c>
       <c r="J173">
-        <f>2000000+E173*10000+B173</f>
         <v>2980000</v>
       </c>
       <c r="K173" t="s">
@@ -9399,8 +8419,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace\gamedoc\游戏配置表\common\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91E5300-7E63-4290-84C6-5763DE000A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -67,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -94,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -118,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -140,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F127" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="F127" authorId="0">
       <text>
         <r>
           <rPr>
@@ -185,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F172" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="F172" authorId="0">
       <text>
         <r>
           <rPr>
@@ -307,6 +301,9 @@
     <t>可使用道具</t>
   </si>
   <si>
+    <t>itemicon_1010101.png</t>
+  </si>
+  <si>
     <t>使用后可额外获得50%流水，持续时间1小时。多次使用可以叠加持续时间</t>
   </si>
   <si>
@@ -316,6 +313,9 @@
     <t>钻石礼包</t>
   </si>
   <si>
+    <t>itemicon_1010201.png</t>
+  </si>
+  <si>
     <t>使用后可额外获得100%流水，持续时间2小时。多次使用可以叠加持续时间</t>
   </si>
   <si>
@@ -325,9 +325,6 @@
     <t>赌场工具（普通）</t>
   </si>
   <si>
-    <t>itemicon_1010101.png</t>
-  </si>
-  <si>
     <t>使用后随机获得1~2星赌场建筑升级道具</t>
   </si>
   <si>
@@ -376,60 +373,99 @@
     <t>常规道具</t>
   </si>
   <si>
+    <t>itemicon_1020001.png</t>
+  </si>
+  <si>
     <t>创建私人包房时可以抵扣钻石</t>
   </si>
   <si>
     <t>测试道具2</t>
   </si>
   <si>
+    <t>itemicon_1020002.png</t>
+  </si>
+  <si>
     <t>活动期间获得，集齐6个可领取奖励</t>
   </si>
   <si>
     <t>测试道具3</t>
   </si>
   <si>
+    <t>itemicon_1020003.png</t>
+  </si>
+  <si>
     <t>测试道具4</t>
   </si>
   <si>
+    <t>itemicon_1020004.png</t>
+  </si>
+  <si>
     <t>测试道具5</t>
   </si>
   <si>
+    <t>itemicon_1020005.png</t>
+  </si>
+  <si>
     <t>测试道具6</t>
   </si>
   <si>
+    <t>itemicon_1020006.png</t>
+  </si>
+  <si>
     <t>图鉴1-图片</t>
   </si>
   <si>
+    <t>itemicon_1030011.png</t>
+  </si>
+  <si>
     <t>一張精美的圖片，由12張碎片組成</t>
   </si>
   <si>
     <t>图鉴2-图片</t>
   </si>
   <si>
+    <t>itemicon_1030012.png</t>
+  </si>
+  <si>
     <t>图鉴3-图片</t>
   </si>
   <si>
+    <t>itemicon_1030013.png</t>
+  </si>
+  <si>
     <t>图鉴4-图片</t>
   </si>
   <si>
+    <t>itemicon_1030014.png</t>
+  </si>
+  <si>
     <t>图鉴5-图片</t>
   </si>
   <si>
+    <t>itemicon_1030015.png</t>
+  </si>
+  <si>
     <t>图鉴6-图片</t>
   </si>
   <si>
+    <t>itemicon_1030016.png</t>
+  </si>
+  <si>
     <t>图鉴7-图片</t>
   </si>
   <si>
+    <t>itemicon_1030017.png</t>
+  </si>
+  <si>
     <t>图鉴8-图片</t>
   </si>
   <si>
+    <t>itemicon_1030018.png</t>
+  </si>
+  <si>
     <t>图鉴1-碎片1</t>
   </si>
   <si>
-    <t>itemicon_1020001.png</t>
-  </si>
-  <si>
     <t>用於組成一張精美圖片[圖片名稱]的碎片，在各遊戲中下注有概率獲得</t>
   </si>
   <si>
@@ -721,15 +757,27 @@
     <t>头像2</t>
   </si>
   <si>
+    <t>itemicon_1031001.png</t>
+  </si>
+  <si>
     <t>头像3</t>
   </si>
   <si>
+    <t>itemicon_1031002.png</t>
+  </si>
+  <si>
     <t>头像框2</t>
   </si>
   <si>
+    <t>itemicon_1031201.png</t>
+  </si>
+  <si>
     <t>头像框3</t>
   </si>
   <si>
+    <t>itemicon_1031202.png</t>
+  </si>
+  <si>
     <t>头像框-特权卡专属</t>
   </si>
   <si>
@@ -745,51 +793,93 @@
     <t>国旗2</t>
   </si>
   <si>
+    <t>itemicon_1021401.png</t>
+  </si>
+  <si>
     <t>国旗3</t>
   </si>
   <si>
+    <t>itemicon_1021402.png</t>
+  </si>
+  <si>
     <t>头衔2</t>
   </si>
   <si>
+    <t>itemicon_1031601.png</t>
+  </si>
+  <si>
     <t>头衔3</t>
   </si>
   <si>
+    <t>itemicon_1031602.png</t>
+  </si>
+  <si>
     <t>筹码2</t>
   </si>
   <si>
+    <t>itemicon_1031801.png</t>
+  </si>
+  <si>
     <t>筹码3</t>
   </si>
   <si>
+    <t>itemicon_1031802.png</t>
+  </si>
+  <si>
     <t>牌背2</t>
   </si>
   <si>
+    <t>itemicon_1032001.png</t>
+  </si>
+  <si>
     <t>牌背3</t>
   </si>
   <si>
+    <t>itemicon_1032002.png</t>
+  </si>
+  <si>
     <t>大厅背景2</t>
   </si>
   <si>
+    <t>itemicon_1032201.png</t>
+  </si>
+  <si>
     <t>大厅背景3</t>
   </si>
   <si>
+    <t>itemicon_1032202.png</t>
+  </si>
+  <si>
     <t>祈福卡</t>
   </si>
   <si>
+    <t>itemicon_1022501.png</t>
+  </si>
+  <si>
     <t>在搖錢樹活動中祈福使用，可在指定禮包中購買獲得</t>
   </si>
   <si>
     <t>刮刮卡</t>
   </si>
   <si>
+    <t>itemicon_1022502.png</t>
+  </si>
+  <si>
     <t>在指定的游戏中产出</t>
   </si>
   <si>
     <t>夺宝优惠券</t>
   </si>
   <si>
+    <t>itemicon_1022503.png</t>
+  </si>
+  <si>
     <t>积分</t>
   </si>
   <si>
+    <t>itemicon_1022504.png</t>
+  </si>
+  <si>
     <t>在[积分大奖]活动中产出</t>
   </si>
   <si>
@@ -964,122 +1054,32 @@
     <t>货币</t>
   </si>
   <si>
+    <t>itemicon_1990000.png</t>
+  </si>
+  <si>
     <t>下注时需要用的货币</t>
   </si>
   <si>
     <t>钻石</t>
   </si>
   <si>
+    <t>itemicon_1980000.png</t>
+  </si>
+  <si>
     <t>在私密房间内下注时需要用的货币，同时是使用部分功能需要消耗的特殊货币</t>
-  </si>
-  <si>
-    <t>itemicon_1010201.png</t>
-  </si>
-  <si>
-    <t>itemicon_1020002.png</t>
-  </si>
-  <si>
-    <t>itemicon_1020003.png</t>
-  </si>
-  <si>
-    <t>itemicon_1020004.png</t>
-  </si>
-  <si>
-    <t>itemicon_1020005.png</t>
-  </si>
-  <si>
-    <t>itemicon_1020006.png</t>
-  </si>
-  <si>
-    <t>itemicon_1030011.png</t>
-  </si>
-  <si>
-    <t>itemicon_1030012.png</t>
-  </si>
-  <si>
-    <t>itemicon_1030013.png</t>
-  </si>
-  <si>
-    <t>itemicon_1030014.png</t>
-  </si>
-  <si>
-    <t>itemicon_1030015.png</t>
-  </si>
-  <si>
-    <t>itemicon_1030016.png</t>
-  </si>
-  <si>
-    <t>itemicon_1030017.png</t>
-  </si>
-  <si>
-    <t>itemicon_1030018.png</t>
-  </si>
-  <si>
-    <t>itemicon_1031001.png</t>
-  </si>
-  <si>
-    <t>itemicon_1031002.png</t>
-  </si>
-  <si>
-    <t>itemicon_1031201.png</t>
-  </si>
-  <si>
-    <t>itemicon_1031202.png</t>
-  </si>
-  <si>
-    <t>itemicon_1021401.png</t>
-  </si>
-  <si>
-    <t>itemicon_1021402.png</t>
-  </si>
-  <si>
-    <t>itemicon_1031601.png</t>
-  </si>
-  <si>
-    <t>itemicon_1031602.png</t>
-  </si>
-  <si>
-    <t>itemicon_1031801.png</t>
-  </si>
-  <si>
-    <t>itemicon_1031802.png</t>
-  </si>
-  <si>
-    <t>itemicon_1032001.png</t>
-  </si>
-  <si>
-    <t>itemicon_1032002.png</t>
-  </si>
-  <si>
-    <t>itemicon_1032201.png</t>
-  </si>
-  <si>
-    <t>itemicon_1032202.png</t>
-  </si>
-  <si>
-    <t>itemicon_1022501.png</t>
-  </si>
-  <si>
-    <t>itemicon_1022502.png</t>
-  </si>
-  <si>
-    <t>itemicon_1022503.png</t>
-  </si>
-  <si>
-    <t>itemicon_1022504.png</t>
-  </si>
-  <si>
-    <t>itemicon_1990000.png</t>
-  </si>
-  <si>
-    <t>itemicon_1980000.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1101,6 +1101,150 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1111,14 +1255,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1127,48 +1265,234 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.149998474074526"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1191,9 +1515,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1244,158 +1810,89 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1406,7 +1903,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1434,40 +1931,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1717,14 +2328,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Q173"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
     <col min="3" max="3" width="15.5" customWidth="1"/>
@@ -1741,10 +2352,11 @@
     <col min="14" max="14" width="12.25" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="18.875" customWidth="1"/>
+    <col min="17" max="17" width="9.375"/>
     <col min="20" max="20" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1790,7 +2402,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -1832,7 +2444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -1873,11 +2485,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
     </row>
-    <row r="5" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" ht="21" customHeight="1" spans="1:15">
       <c r="A5">
         <v>1010101</v>
       </c>
@@ -1903,22 +2515,22 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J5">
         <v>2010101</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N5">
         <v>999</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1" spans="1:15">
       <c r="A6">
         <v>1010201</v>
       </c>
@@ -1929,7 +2541,7 @@
         <v>1010201</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1944,22 +2556,22 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>253</v>
+        <v>35</v>
       </c>
       <c r="J6">
         <v>2010201</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N6">
         <v>999</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A7" s="1">
         <v>1010301</v>
       </c>
@@ -1970,7 +2582,7 @@
         <v>1100301</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1985,13 +2597,13 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J7" s="1">
         <v>2010301</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N7" s="1">
         <v>999</v>
@@ -2004,7 +2616,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A8" s="1">
         <v>1010302</v>
       </c>
@@ -2015,7 +2627,7 @@
         <v>1100302</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2030,13 +2642,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J8" s="1">
         <v>2010302</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N8" s="1">
         <v>999</v>
@@ -2049,7 +2661,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A9" s="1">
         <v>1010303</v>
       </c>
@@ -2060,7 +2672,7 @@
         <v>1100303</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2075,13 +2687,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J9" s="1">
         <v>2010303</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N9" s="1">
         <v>999</v>
@@ -2094,7 +2706,7 @@
         <v>14.99</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A10" s="1">
         <v>1010304</v>
       </c>
@@ -2105,7 +2717,7 @@
         <v>1100304</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2120,13 +2732,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J10" s="1">
         <v>2010304</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N10" s="1">
         <v>999</v>
@@ -2139,7 +2751,7 @@
         <v>24.99</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A11" s="1">
         <v>1010305</v>
       </c>
@@ -2150,7 +2762,7 @@
         <v>1100305</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2165,13 +2777,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J11" s="1">
         <v>2010305</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N11" s="1">
         <v>999</v>
@@ -2184,7 +2796,7 @@
         <v>49.99</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A12" s="1">
         <v>1010311</v>
       </c>
@@ -2195,7 +2807,7 @@
         <v>1100311</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -2210,13 +2822,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J12" s="1">
         <v>2010311</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N12" s="1">
         <v>999</v>
@@ -2226,7 +2838,7 @@
         <v>100006</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A13" s="1">
         <v>1010312</v>
       </c>
@@ -2237,7 +2849,7 @@
         <v>1100312</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -2252,13 +2864,13 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J13" s="1">
         <v>2010312</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N13" s="1">
         <v>999</v>
@@ -2268,7 +2880,7 @@
         <v>100007</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A14" s="1">
         <v>1010313</v>
       </c>
@@ -2279,7 +2891,7 @@
         <v>1100313</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -2294,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J14" s="1">
         <v>2010313</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N14" s="1">
         <v>999</v>
@@ -2310,7 +2922,7 @@
         <v>100008</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A15" s="1">
         <v>1010314</v>
       </c>
@@ -2321,7 +2933,7 @@
         <v>1100314</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -2336,13 +2948,13 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J15" s="1">
         <v>2010314</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N15" s="1">
         <v>999</v>
@@ -2352,7 +2964,7 @@
         <v>100009</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A16" s="1">
         <v>1010315</v>
       </c>
@@ -2363,7 +2975,7 @@
         <v>1100315</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -2378,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J16" s="1">
         <v>2010315</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N16" s="1">
         <v>999</v>
@@ -2394,7 +3006,7 @@
         <v>100010</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" ht="21" customHeight="1" spans="1:14">
       <c r="A17">
         <v>1020001</v>
       </c>
@@ -2405,13 +3017,13 @@
         <v>1020001</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -2420,19 +3032,19 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J17">
         <v>2020001</v>
       </c>
       <c r="K17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N17">
         <v>999</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A18" s="2">
         <v>1020002</v>
       </c>
@@ -2443,13 +3055,13 @@
         <v>1020002</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2">
         <v>2</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" s="2">
         <v>2</v>
@@ -2458,19 +3070,19 @@
         <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>254</v>
+        <v>58</v>
       </c>
       <c r="J18" s="2">
         <v>2020002</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2">
         <v>999</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A19" s="2">
         <v>1020003</v>
       </c>
@@ -2481,13 +3093,13 @@
         <v>1020003</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2">
         <v>2</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" s="2">
         <v>3</v>
@@ -2496,19 +3108,19 @@
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>255</v>
+        <v>61</v>
       </c>
       <c r="J19" s="2">
         <v>2020003</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N19" s="2">
         <v>999</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A20" s="2">
         <v>1020004</v>
       </c>
@@ -2519,13 +3131,13 @@
         <v>1020004</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2">
         <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="2">
         <v>4</v>
@@ -2534,19 +3146,19 @@
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>256</v>
+        <v>63</v>
       </c>
       <c r="J20" s="2">
         <v>2020004</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N20" s="2">
         <v>999</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A21" s="2">
         <v>1020005</v>
       </c>
@@ -2557,13 +3169,13 @@
         <v>1020005</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E21" s="2">
         <v>2</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G21" s="2">
         <v>5</v>
@@ -2572,19 +3184,19 @@
         <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>257</v>
+        <v>65</v>
       </c>
       <c r="J21" s="2">
         <v>2020005</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N21" s="2">
         <v>999</v>
       </c>
     </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" s="2" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A22" s="2">
         <v>1020006</v>
       </c>
@@ -2595,13 +3207,13 @@
         <v>1020006</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2">
         <v>2</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" s="2">
         <v>6</v>
@@ -2610,19 +3222,19 @@
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>258</v>
+        <v>67</v>
       </c>
       <c r="J22" s="2">
         <v>2020006</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N22" s="2">
         <v>999</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" ht="23.1" customHeight="1" spans="1:14">
       <c r="A23">
         <v>1030011</v>
       </c>
@@ -2633,13 +3245,13 @@
         <v>1300011</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2648,13 +3260,13 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>259</v>
+        <v>69</v>
       </c>
       <c r="J23">
         <v>2030011</v>
       </c>
       <c r="K23" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M23">
         <v>10001</v>
@@ -2663,7 +3275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" ht="23.1" customHeight="1" spans="1:14">
       <c r="A24">
         <v>1030012</v>
       </c>
@@ -2674,13 +3286,13 @@
         <v>1300012</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2689,13 +3301,13 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="J24">
         <v>2030012</v>
       </c>
       <c r="K24" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M24">
         <v>10002</v>
@@ -2704,7 +3316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" ht="23.1" customHeight="1" spans="1:14">
       <c r="A25">
         <v>1030013</v>
       </c>
@@ -2715,13 +3327,13 @@
         <v>1300013</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2730,13 +3342,13 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>261</v>
+        <v>74</v>
       </c>
       <c r="J25">
         <v>2030013</v>
       </c>
       <c r="K25" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M25">
         <v>10003</v>
@@ -2745,7 +3357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" ht="23.1" customHeight="1" spans="1:14">
       <c r="A26">
         <v>1030014</v>
       </c>
@@ -2756,13 +3368,13 @@
         <v>1300014</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2771,13 +3383,13 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>262</v>
+        <v>76</v>
       </c>
       <c r="J26">
         <v>2030014</v>
       </c>
       <c r="K26" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M26">
         <v>10004</v>
@@ -2786,7 +3398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" ht="23.1" customHeight="1" spans="1:14">
       <c r="A27">
         <v>1030015</v>
       </c>
@@ -2797,13 +3409,13 @@
         <v>1300015</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2812,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="J27">
         <v>2030015</v>
       </c>
       <c r="K27" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M27">
         <v>10005</v>
@@ -2827,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" ht="23.1" customHeight="1" spans="1:14">
       <c r="A28">
         <v>1030016</v>
       </c>
@@ -2838,13 +3450,13 @@
         <v>1300016</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2853,13 +3465,13 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="J28">
         <v>2030016</v>
       </c>
       <c r="K28" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M28">
         <v>10006</v>
@@ -2868,7 +3480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" ht="23.1" customHeight="1" spans="1:14">
       <c r="A29">
         <v>1030017</v>
       </c>
@@ -2879,13 +3491,13 @@
         <v>1300017</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2894,13 +3506,13 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="J29">
         <v>2030017</v>
       </c>
       <c r="K29" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M29">
         <v>10007</v>
@@ -2909,7 +3521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" ht="23.1" customHeight="1" spans="1:14">
       <c r="A30">
         <v>1030018</v>
       </c>
@@ -2920,13 +3532,13 @@
         <v>1300018</v>
       </c>
       <c r="D30" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2935,13 +3547,13 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>266</v>
+        <v>84</v>
       </c>
       <c r="J30">
         <v>2030018</v>
       </c>
       <c r="K30" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M30">
         <v>10008</v>
@@ -2950,7 +3562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" ht="23.1" customHeight="1" spans="1:14">
       <c r="A31">
         <v>1030101</v>
       </c>
@@ -2961,13 +3573,13 @@
         <v>1300101</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2976,19 +3588,19 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J31">
         <v>2030101</v>
       </c>
       <c r="K31" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" ht="23.1" customHeight="1" spans="1:14">
       <c r="A32">
         <v>1030102</v>
       </c>
@@ -2999,13 +3611,13 @@
         <v>1300102</v>
       </c>
       <c r="D32" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -3014,19 +3626,19 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J32">
         <v>2030102</v>
       </c>
       <c r="K32" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" ht="23.1" customHeight="1" spans="1:14">
       <c r="A33">
         <v>1030103</v>
       </c>
@@ -3037,13 +3649,13 @@
         <v>1300103</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E33">
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -3052,19 +3664,19 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J33">
         <v>2030103</v>
       </c>
       <c r="K33" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" ht="23.1" customHeight="1" spans="1:14">
       <c r="A34">
         <v>1030104</v>
       </c>
@@ -3075,13 +3687,13 @@
         <v>1300104</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -3090,19 +3702,19 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J34">
         <v>2030104</v>
       </c>
       <c r="K34" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" ht="23.1" customHeight="1" spans="1:14">
       <c r="A35">
         <v>1030105</v>
       </c>
@@ -3113,13 +3725,13 @@
         <v>1300105</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E35">
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -3128,19 +3740,19 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J35">
         <v>2030105</v>
       </c>
       <c r="K35" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" ht="23.1" customHeight="1" spans="1:14">
       <c r="A36">
         <v>1030106</v>
       </c>
@@ -3151,13 +3763,13 @@
         <v>1300106</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -3166,19 +3778,19 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J36">
         <v>2030106</v>
       </c>
       <c r="K36" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" ht="23.1" customHeight="1" spans="1:14">
       <c r="A37">
         <v>1030107</v>
       </c>
@@ -3189,13 +3801,13 @@
         <v>1300107</v>
       </c>
       <c r="D37" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -3204,19 +3816,19 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J37">
         <v>2030107</v>
       </c>
       <c r="K37" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" ht="23.1" customHeight="1" spans="1:14">
       <c r="A38">
         <v>1030108</v>
       </c>
@@ -3227,13 +3839,13 @@
         <v>1300108</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -3242,19 +3854,19 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J38">
         <v>2030108</v>
       </c>
       <c r="K38" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" ht="23.1" customHeight="1" spans="1:14">
       <c r="A39">
         <v>1030109</v>
       </c>
@@ -3265,13 +3877,13 @@
         <v>1300109</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -3280,19 +3892,19 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J39">
         <v>2030109</v>
       </c>
       <c r="K39" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" ht="23.1" customHeight="1" spans="1:14">
       <c r="A40">
         <v>1030110</v>
       </c>
@@ -3303,13 +3915,13 @@
         <v>1300110</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -3318,19 +3930,19 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J40">
         <v>2030110</v>
       </c>
       <c r="K40" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" ht="23.1" customHeight="1" spans="1:14">
       <c r="A41">
         <v>1030111</v>
       </c>
@@ -3341,13 +3953,13 @@
         <v>1300111</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E41">
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G41">
         <v>6</v>
@@ -3356,19 +3968,19 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J41">
         <v>2030111</v>
       </c>
       <c r="K41" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" ht="23.1" customHeight="1" spans="1:14">
       <c r="A42">
         <v>1030112</v>
       </c>
@@ -3379,13 +3991,13 @@
         <v>1300112</v>
       </c>
       <c r="D42" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -3394,19 +4006,19 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J42">
         <v>2030112</v>
       </c>
       <c r="K42" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" ht="23.1" customHeight="1" spans="1:14">
       <c r="A43">
         <v>1030121</v>
       </c>
@@ -3417,13 +4029,13 @@
         <v>1300121</v>
       </c>
       <c r="D43" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -3432,19 +4044,19 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J43">
         <v>2030121</v>
       </c>
       <c r="K43" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" ht="23.1" customHeight="1" spans="1:14">
       <c r="A44">
         <v>1030122</v>
       </c>
@@ -3455,13 +4067,13 @@
         <v>1300122</v>
       </c>
       <c r="D44" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E44">
         <v>3</v>
       </c>
       <c r="F44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -3470,19 +4082,19 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J44">
         <v>2030122</v>
       </c>
       <c r="K44" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" ht="23.1" customHeight="1" spans="1:14">
       <c r="A45">
         <v>1030123</v>
       </c>
@@ -3493,13 +4105,13 @@
         <v>1300123</v>
       </c>
       <c r="D45" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="E45">
         <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -3508,19 +4120,19 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J45">
         <v>2030123</v>
       </c>
       <c r="K45" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N45">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" ht="23.1" customHeight="1" spans="1:14">
       <c r="A46">
         <v>1030124</v>
       </c>
@@ -3531,13 +4143,13 @@
         <v>1300124</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E46">
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -3546,19 +4158,19 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J46">
         <v>2030124</v>
       </c>
       <c r="K46" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" ht="23.1" customHeight="1" spans="1:14">
       <c r="A47">
         <v>1030125</v>
       </c>
@@ -3569,13 +4181,13 @@
         <v>1300125</v>
       </c>
       <c r="D47" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="E47">
         <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G47">
         <v>3</v>
@@ -3584,19 +4196,19 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J47">
         <v>2030125</v>
       </c>
       <c r="K47" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" ht="23.1" customHeight="1" spans="1:14">
       <c r="A48">
         <v>1030126</v>
       </c>
@@ -3607,13 +4219,13 @@
         <v>1300126</v>
       </c>
       <c r="D48" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E48">
         <v>3</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G48">
         <v>3</v>
@@ -3622,19 +4234,19 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J48">
         <v>2030126</v>
       </c>
       <c r="K48" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" ht="23.1" customHeight="1" spans="1:14">
       <c r="A49">
         <v>1030127</v>
       </c>
@@ -3645,13 +4257,13 @@
         <v>1300127</v>
       </c>
       <c r="D49" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E49">
         <v>3</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -3660,19 +4272,19 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J49">
         <v>2030127</v>
       </c>
       <c r="K49" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" ht="23.1" customHeight="1" spans="1:14">
       <c r="A50">
         <v>1030128</v>
       </c>
@@ -3683,13 +4295,13 @@
         <v>1300128</v>
       </c>
       <c r="D50" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E50">
         <v>3</v>
       </c>
       <c r="F50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -3698,19 +4310,19 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J50">
         <v>2030128</v>
       </c>
       <c r="K50" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" ht="23.1" customHeight="1" spans="1:14">
       <c r="A51">
         <v>1030129</v>
       </c>
@@ -3721,13 +4333,13 @@
         <v>1300129</v>
       </c>
       <c r="D51" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="E51">
         <v>3</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -3736,19 +4348,19 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J51">
         <v>2030129</v>
       </c>
       <c r="K51" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N51">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" ht="23.1" customHeight="1" spans="1:14">
       <c r="A52">
         <v>1030130</v>
       </c>
@@ -3759,13 +4371,13 @@
         <v>1300130</v>
       </c>
       <c r="D52" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E52">
         <v>3</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -3774,19 +4386,19 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J52">
         <v>2030130</v>
       </c>
       <c r="K52" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" ht="23.1" customHeight="1" spans="1:14">
       <c r="A53">
         <v>1030131</v>
       </c>
@@ -3797,13 +4409,13 @@
         <v>1300131</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G53">
         <v>6</v>
@@ -3812,19 +4424,19 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J53">
         <v>2030131</v>
       </c>
       <c r="K53" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N53">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" ht="23.1" customHeight="1" spans="1:14">
       <c r="A54">
         <v>1030132</v>
       </c>
@@ -3835,13 +4447,13 @@
         <v>1300132</v>
       </c>
       <c r="D54" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E54">
         <v>3</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -3850,19 +4462,19 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J54">
         <v>2030132</v>
       </c>
       <c r="K54" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" ht="23.1" customHeight="1" spans="1:14">
       <c r="A55">
         <v>1030141</v>
       </c>
@@ -3873,13 +4485,13 @@
         <v>1300141</v>
       </c>
       <c r="D55" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E55">
         <v>3</v>
       </c>
       <c r="F55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3888,19 +4500,19 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J55">
         <v>2030141</v>
       </c>
       <c r="K55" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N55">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" ht="23.1" customHeight="1" spans="1:14">
       <c r="A56">
         <v>1030142</v>
       </c>
@@ -3911,13 +4523,13 @@
         <v>1300142</v>
       </c>
       <c r="D56" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E56">
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -3926,19 +4538,19 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J56">
         <v>2030142</v>
       </c>
       <c r="K56" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" ht="23.1" customHeight="1" spans="1:14">
       <c r="A57">
         <v>1030143</v>
       </c>
@@ -3949,13 +4561,13 @@
         <v>1300143</v>
       </c>
       <c r="D57" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E57">
         <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -3964,19 +4576,19 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J57">
         <v>2030143</v>
       </c>
       <c r="K57" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" ht="23.1" customHeight="1" spans="1:14">
       <c r="A58">
         <v>1030144</v>
       </c>
@@ -3987,13 +4599,13 @@
         <v>1300144</v>
       </c>
       <c r="D58" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="E58">
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -4002,19 +4614,19 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J58">
         <v>2030144</v>
       </c>
       <c r="K58" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N58">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" ht="23.1" customHeight="1" spans="1:14">
       <c r="A59">
         <v>1030145</v>
       </c>
@@ -4025,13 +4637,13 @@
         <v>1300145</v>
       </c>
       <c r="D59" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="E59">
         <v>3</v>
       </c>
       <c r="F59" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -4040,19 +4652,19 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J59">
         <v>2030145</v>
       </c>
       <c r="K59" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N59">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" ht="23.1" customHeight="1" spans="1:14">
       <c r="A60">
         <v>1030146</v>
       </c>
@@ -4063,13 +4675,13 @@
         <v>1300146</v>
       </c>
       <c r="D60" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="E60">
         <v>3</v>
       </c>
       <c r="F60" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G60">
         <v>3</v>
@@ -4078,19 +4690,19 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J60">
         <v>2030146</v>
       </c>
       <c r="K60" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N60">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" ht="23.1" customHeight="1" spans="1:14">
       <c r="A61">
         <v>1030147</v>
       </c>
@@ -4101,13 +4713,13 @@
         <v>1300147</v>
       </c>
       <c r="D61" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G61">
         <v>4</v>
@@ -4116,19 +4728,19 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J61">
         <v>2030147</v>
       </c>
       <c r="K61" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" ht="23.1" customHeight="1" spans="1:14">
       <c r="A62">
         <v>1030148</v>
       </c>
@@ -4139,13 +4751,13 @@
         <v>1300148</v>
       </c>
       <c r="D62" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E62">
         <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G62">
         <v>4</v>
@@ -4154,19 +4766,19 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J62">
         <v>2030148</v>
       </c>
       <c r="K62" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" ht="23.1" customHeight="1" spans="1:14">
       <c r="A63">
         <v>1030149</v>
       </c>
@@ -4177,13 +4789,13 @@
         <v>1300149</v>
       </c>
       <c r="D63" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E63">
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G63">
         <v>5</v>
@@ -4192,19 +4804,19 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J63">
         <v>2030149</v>
       </c>
       <c r="K63" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N63">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" ht="23.1" customHeight="1" spans="1:14">
       <c r="A64">
         <v>1030150</v>
       </c>
@@ -4215,13 +4827,13 @@
         <v>1300150</v>
       </c>
       <c r="D64" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="E64">
         <v>3</v>
       </c>
       <c r="F64" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -4230,19 +4842,19 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J64">
         <v>2030150</v>
       </c>
       <c r="K64" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" ht="23.1" customHeight="1" spans="1:14">
       <c r="A65">
         <v>1030151</v>
       </c>
@@ -4253,13 +4865,13 @@
         <v>1300151</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E65">
         <v>3</v>
       </c>
       <c r="F65" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G65">
         <v>6</v>
@@ -4268,19 +4880,19 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J65">
         <v>2030151</v>
       </c>
       <c r="K65" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N65">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" ht="23.1" customHeight="1" spans="1:14">
       <c r="A66">
         <v>1030152</v>
       </c>
@@ -4291,13 +4903,13 @@
         <v>1300152</v>
       </c>
       <c r="D66" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E66">
         <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G66">
         <v>6</v>
@@ -4306,19 +4918,19 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J66">
         <v>2030152</v>
       </c>
       <c r="K66" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N66">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" ht="23.1" customHeight="1" spans="1:14">
       <c r="A67">
         <v>1030161</v>
       </c>
@@ -4329,13 +4941,13 @@
         <v>1300161</v>
       </c>
       <c r="D67" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E67">
         <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -4344,19 +4956,19 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J67">
         <v>2030161</v>
       </c>
       <c r="K67" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N67">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" ht="23.1" customHeight="1" spans="1:14">
       <c r="A68">
         <v>1030162</v>
       </c>
@@ -4367,13 +4979,13 @@
         <v>1300162</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="E68">
         <v>3</v>
       </c>
       <c r="F68" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -4382,19 +4994,19 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J68">
         <v>2030162</v>
       </c>
       <c r="K68" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" ht="23.1" customHeight="1" spans="1:14">
       <c r="A69">
         <v>1030163</v>
       </c>
@@ -4405,13 +5017,13 @@
         <v>1300163</v>
       </c>
       <c r="D69" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="E69">
         <v>3</v>
       </c>
       <c r="F69" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G69">
         <v>2</v>
@@ -4420,19 +5032,19 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J69">
         <v>2030163</v>
       </c>
       <c r="K69" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" ht="23.1" customHeight="1" spans="1:14">
       <c r="A70">
         <v>1030164</v>
       </c>
@@ -4443,13 +5055,13 @@
         <v>1300164</v>
       </c>
       <c r="D70" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E70">
         <v>3</v>
       </c>
       <c r="F70" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G70">
         <v>2</v>
@@ -4458,19 +5070,19 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J70">
         <v>2030164</v>
       </c>
       <c r="K70" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" ht="23.1" customHeight="1" spans="1:14">
       <c r="A71">
         <v>1030165</v>
       </c>
@@ -4481,13 +5093,13 @@
         <v>1300165</v>
       </c>
       <c r="D71" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E71">
         <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G71">
         <v>3</v>
@@ -4496,19 +5108,19 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J71">
         <v>2030165</v>
       </c>
       <c r="K71" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" ht="23.1" customHeight="1" spans="1:14">
       <c r="A72">
         <v>1030166</v>
       </c>
@@ -4519,13 +5131,13 @@
         <v>1300166</v>
       </c>
       <c r="D72" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E72">
         <v>3</v>
       </c>
       <c r="F72" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G72">
         <v>3</v>
@@ -4534,19 +5146,19 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J72">
         <v>2030166</v>
       </c>
       <c r="K72" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" ht="23.1" customHeight="1" spans="1:14">
       <c r="A73">
         <v>1030167</v>
       </c>
@@ -4557,13 +5169,13 @@
         <v>1300167</v>
       </c>
       <c r="D73" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E73">
         <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G73">
         <v>4</v>
@@ -4572,19 +5184,19 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J73">
         <v>2030167</v>
       </c>
       <c r="K73" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" ht="23.1" customHeight="1" spans="1:14">
       <c r="A74">
         <v>1030168</v>
       </c>
@@ -4595,13 +5207,13 @@
         <v>1300168</v>
       </c>
       <c r="D74" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E74">
         <v>3</v>
       </c>
       <c r="F74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G74">
         <v>4</v>
@@ -4610,19 +5222,19 @@
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J74">
         <v>2030168</v>
       </c>
       <c r="K74" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" ht="23.1" customHeight="1" spans="1:14">
       <c r="A75">
         <v>1030169</v>
       </c>
@@ -4633,13 +5245,13 @@
         <v>1300169</v>
       </c>
       <c r="D75" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="E75">
         <v>3</v>
       </c>
       <c r="F75" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G75">
         <v>5</v>
@@ -4648,19 +5260,19 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J75">
         <v>2030169</v>
       </c>
       <c r="K75" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N75">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" ht="23.1" customHeight="1" spans="1:14">
       <c r="A76">
         <v>1030170</v>
       </c>
@@ -4671,13 +5283,13 @@
         <v>1300170</v>
       </c>
       <c r="D76" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G76">
         <v>5</v>
@@ -4686,19 +5298,19 @@
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J76">
         <v>2030170</v>
       </c>
       <c r="K76" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N76">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" ht="23.1" customHeight="1" spans="1:14">
       <c r="A77">
         <v>1030171</v>
       </c>
@@ -4709,13 +5321,13 @@
         <v>1300171</v>
       </c>
       <c r="D77" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G77">
         <v>6</v>
@@ -4724,19 +5336,19 @@
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J77">
         <v>2030171</v>
       </c>
       <c r="K77" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N77">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" ht="23.1" customHeight="1" spans="1:14">
       <c r="A78">
         <v>1030172</v>
       </c>
@@ -4747,13 +5359,13 @@
         <v>1300172</v>
       </c>
       <c r="D78" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E78">
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G78">
         <v>6</v>
@@ -4762,19 +5374,19 @@
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J78">
         <v>2030172</v>
       </c>
       <c r="K78" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" ht="23.1" customHeight="1" spans="1:14">
       <c r="A79">
         <v>1030181</v>
       </c>
@@ -4785,13 +5397,13 @@
         <v>1300181</v>
       </c>
       <c r="D79" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E79">
         <v>3</v>
       </c>
       <c r="F79" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -4800,19 +5412,19 @@
         <v>1</v>
       </c>
       <c r="I79" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J79">
         <v>2030181</v>
       </c>
       <c r="K79" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" ht="23.1" customHeight="1" spans="1:14">
       <c r="A80">
         <v>1030182</v>
       </c>
@@ -4823,13 +5435,13 @@
         <v>1300182</v>
       </c>
       <c r="D80" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="E80">
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -4838,19 +5450,19 @@
         <v>1</v>
       </c>
       <c r="I80" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J80">
         <v>2030182</v>
       </c>
       <c r="K80" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N80">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" ht="23.1" customHeight="1" spans="1:14">
       <c r="A81">
         <v>1030183</v>
       </c>
@@ -4861,13 +5473,13 @@
         <v>1300183</v>
       </c>
       <c r="D81" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G81">
         <v>2</v>
@@ -4876,19 +5488,19 @@
         <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J81">
         <v>2030183</v>
       </c>
       <c r="K81" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N81">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" ht="23.1" customHeight="1" spans="1:14">
       <c r="A82">
         <v>1030184</v>
       </c>
@@ -4899,13 +5511,13 @@
         <v>1300184</v>
       </c>
       <c r="D82" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="E82">
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G82">
         <v>2</v>
@@ -4914,19 +5526,19 @@
         <v>1</v>
       </c>
       <c r="I82" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J82">
         <v>2030184</v>
       </c>
       <c r="K82" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N82">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" ht="23.1" customHeight="1" spans="1:14">
       <c r="A83">
         <v>1030185</v>
       </c>
@@ -4937,13 +5549,13 @@
         <v>1300185</v>
       </c>
       <c r="D83" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G83">
         <v>3</v>
@@ -4952,19 +5564,19 @@
         <v>1</v>
       </c>
       <c r="I83" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J83">
         <v>2030185</v>
       </c>
       <c r="K83" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N83">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" ht="23.1" customHeight="1" spans="1:14">
       <c r="A84">
         <v>1030186</v>
       </c>
@@ -4975,13 +5587,13 @@
         <v>1300186</v>
       </c>
       <c r="D84" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="E84">
         <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G84">
         <v>3</v>
@@ -4990,19 +5602,19 @@
         <v>1</v>
       </c>
       <c r="I84" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J84">
         <v>2030186</v>
       </c>
       <c r="K84" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N84">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" ht="23.1" customHeight="1" spans="1:14">
       <c r="A85">
         <v>1030187</v>
       </c>
@@ -5013,13 +5625,13 @@
         <v>1300187</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E85">
         <v>3</v>
       </c>
       <c r="F85" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G85">
         <v>4</v>
@@ -5028,19 +5640,19 @@
         <v>1</v>
       </c>
       <c r="I85" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J85">
         <v>2030187</v>
       </c>
       <c r="K85" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N85">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" ht="23.1" customHeight="1" spans="1:14">
       <c r="A86">
         <v>1030188</v>
       </c>
@@ -5051,13 +5663,13 @@
         <v>1300188</v>
       </c>
       <c r="D86" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E86">
         <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G86">
         <v>4</v>
@@ -5066,19 +5678,19 @@
         <v>1</v>
       </c>
       <c r="I86" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J86">
         <v>2030188</v>
       </c>
       <c r="K86" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N86">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" ht="23.1" customHeight="1" spans="1:14">
       <c r="A87">
         <v>1030189</v>
       </c>
@@ -5089,13 +5701,13 @@
         <v>1300189</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E87">
         <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G87">
         <v>5</v>
@@ -5104,19 +5716,19 @@
         <v>1</v>
       </c>
       <c r="I87" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J87">
         <v>2030189</v>
       </c>
       <c r="K87" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N87">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" ht="23.1" customHeight="1" spans="1:14">
       <c r="A88">
         <v>1030190</v>
       </c>
@@ -5127,13 +5739,13 @@
         <v>1300190</v>
       </c>
       <c r="D88" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E88">
         <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G88">
         <v>5</v>
@@ -5142,19 +5754,19 @@
         <v>1</v>
       </c>
       <c r="I88" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J88">
         <v>2030190</v>
       </c>
       <c r="K88" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N88">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" ht="23.1" customHeight="1" spans="1:14">
       <c r="A89">
         <v>1030191</v>
       </c>
@@ -5165,13 +5777,13 @@
         <v>1300191</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E89">
         <v>3</v>
       </c>
       <c r="F89" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G89">
         <v>6</v>
@@ -5180,19 +5792,19 @@
         <v>1</v>
       </c>
       <c r="I89" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J89">
         <v>2030191</v>
       </c>
       <c r="K89" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N89">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" ht="23.1" customHeight="1" spans="1:14">
       <c r="A90">
         <v>1030192</v>
       </c>
@@ -5203,13 +5815,13 @@
         <v>1300192</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E90">
         <v>3</v>
       </c>
       <c r="F90" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G90">
         <v>6</v>
@@ -5218,19 +5830,19 @@
         <v>1</v>
       </c>
       <c r="I90" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J90">
         <v>2030192</v>
       </c>
       <c r="K90" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N90">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" ht="23.1" customHeight="1" spans="1:14">
       <c r="A91">
         <v>1030201</v>
       </c>
@@ -5241,13 +5853,13 @@
         <v>1300201</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E91">
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -5256,19 +5868,19 @@
         <v>1</v>
       </c>
       <c r="I91" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J91">
         <v>2030201</v>
       </c>
       <c r="K91" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N91">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" ht="23.1" customHeight="1" spans="1:14">
       <c r="A92">
         <v>1030202</v>
       </c>
@@ -5279,13 +5891,13 @@
         <v>1300202</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="E92">
         <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -5294,19 +5906,19 @@
         <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J92">
         <v>2030202</v>
       </c>
       <c r="K92" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N92">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" ht="23.1" customHeight="1" spans="1:14">
       <c r="A93">
         <v>1030203</v>
       </c>
@@ -5317,13 +5929,13 @@
         <v>1300203</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E93">
         <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G93">
         <v>2</v>
@@ -5332,19 +5944,19 @@
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J93">
         <v>2030203</v>
       </c>
       <c r="K93" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N93">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" ht="23.1" customHeight="1" spans="1:14">
       <c r="A94">
         <v>1030204</v>
       </c>
@@ -5355,13 +5967,13 @@
         <v>1300204</v>
       </c>
       <c r="D94" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E94">
         <v>3</v>
       </c>
       <c r="F94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G94">
         <v>2</v>
@@ -5370,19 +5982,19 @@
         <v>1</v>
       </c>
       <c r="I94" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J94">
         <v>2030204</v>
       </c>
       <c r="K94" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N94">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" ht="23.1" customHeight="1" spans="1:14">
       <c r="A95">
         <v>1030205</v>
       </c>
@@ -5393,13 +6005,13 @@
         <v>1300205</v>
       </c>
       <c r="D95" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E95">
         <v>3</v>
       </c>
       <c r="F95" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G95">
         <v>3</v>
@@ -5408,19 +6020,19 @@
         <v>1</v>
       </c>
       <c r="I95" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J95">
         <v>2030205</v>
       </c>
       <c r="K95" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N95">
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" ht="23.1" customHeight="1" spans="1:14">
       <c r="A96">
         <v>1030206</v>
       </c>
@@ -5431,13 +6043,13 @@
         <v>1300206</v>
       </c>
       <c r="D96" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="E96">
         <v>3</v>
       </c>
       <c r="F96" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G96">
         <v>3</v>
@@ -5446,19 +6058,19 @@
         <v>1</v>
       </c>
       <c r="I96" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J96">
         <v>2030206</v>
       </c>
       <c r="K96" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N96">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" ht="23.1" customHeight="1" spans="1:14">
       <c r="A97">
         <v>1030207</v>
       </c>
@@ -5469,13 +6081,13 @@
         <v>1300207</v>
       </c>
       <c r="D97" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E97">
         <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G97">
         <v>4</v>
@@ -5484,19 +6096,19 @@
         <v>1</v>
       </c>
       <c r="I97" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J97">
         <v>2030207</v>
       </c>
       <c r="K97" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N97">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" ht="23.1" customHeight="1" spans="1:14">
       <c r="A98">
         <v>1030208</v>
       </c>
@@ -5507,13 +6119,13 @@
         <v>1300208</v>
       </c>
       <c r="D98" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E98">
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G98">
         <v>4</v>
@@ -5522,19 +6134,19 @@
         <v>1</v>
       </c>
       <c r="I98" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J98">
         <v>2030208</v>
       </c>
       <c r="K98" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N98">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" ht="23.1" customHeight="1" spans="1:14">
       <c r="A99">
         <v>1030209</v>
       </c>
@@ -5545,13 +6157,13 @@
         <v>1300209</v>
       </c>
       <c r="D99" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E99">
         <v>3</v>
       </c>
       <c r="F99" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G99">
         <v>5</v>
@@ -5560,19 +6172,19 @@
         <v>1</v>
       </c>
       <c r="I99" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J99">
         <v>2030209</v>
       </c>
       <c r="K99" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N99">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" ht="23.1" customHeight="1" spans="1:14">
       <c r="A100">
         <v>1030210</v>
       </c>
@@ -5583,13 +6195,13 @@
         <v>1300210</v>
       </c>
       <c r="D100" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E100">
         <v>3</v>
       </c>
       <c r="F100" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G100">
         <v>5</v>
@@ -5598,19 +6210,19 @@
         <v>1</v>
       </c>
       <c r="I100" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J100">
         <v>2030210</v>
       </c>
       <c r="K100" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N100">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" ht="23.1" customHeight="1" spans="1:14">
       <c r="A101">
         <v>1030211</v>
       </c>
@@ -5621,13 +6233,13 @@
         <v>1300211</v>
       </c>
       <c r="D101" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E101">
         <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G101">
         <v>6</v>
@@ -5636,19 +6248,19 @@
         <v>1</v>
       </c>
       <c r="I101" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J101">
         <v>2030211</v>
       </c>
       <c r="K101" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" ht="23.1" customHeight="1" spans="1:14">
       <c r="A102">
         <v>1030212</v>
       </c>
@@ -5659,13 +6271,13 @@
         <v>1300212</v>
       </c>
       <c r="D102" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="E102">
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G102">
         <v>6</v>
@@ -5674,19 +6286,19 @@
         <v>1</v>
       </c>
       <c r="I102" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J102">
         <v>2030212</v>
       </c>
       <c r="K102" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N102">
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" ht="23.1" customHeight="1" spans="1:14">
       <c r="A103">
         <v>1030221</v>
       </c>
@@ -5697,13 +6309,13 @@
         <v>1300221</v>
       </c>
       <c r="D103" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E103">
         <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -5712,19 +6324,19 @@
         <v>1</v>
       </c>
       <c r="I103" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J103">
         <v>2030221</v>
       </c>
       <c r="K103" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" ht="23.1" customHeight="1" spans="1:14">
       <c r="A104">
         <v>1030222</v>
       </c>
@@ -5735,13 +6347,13 @@
         <v>1300222</v>
       </c>
       <c r="D104" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="E104">
         <v>3</v>
       </c>
       <c r="F104" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -5750,19 +6362,19 @@
         <v>1</v>
       </c>
       <c r="I104" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J104">
         <v>2030222</v>
       </c>
       <c r="K104" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" ht="23.1" customHeight="1" spans="1:14">
       <c r="A105">
         <v>1030223</v>
       </c>
@@ -5773,13 +6385,13 @@
         <v>1300223</v>
       </c>
       <c r="D105" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="E105">
         <v>3</v>
       </c>
       <c r="F105" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G105">
         <v>2</v>
@@ -5788,19 +6400,19 @@
         <v>1</v>
       </c>
       <c r="I105" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J105">
         <v>2030223</v>
       </c>
       <c r="K105" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" ht="23.1" customHeight="1" spans="1:14">
       <c r="A106">
         <v>1030224</v>
       </c>
@@ -5811,13 +6423,13 @@
         <v>1300224</v>
       </c>
       <c r="D106" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G106">
         <v>2</v>
@@ -5826,19 +6438,19 @@
         <v>1</v>
       </c>
       <c r="I106" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J106">
         <v>2030224</v>
       </c>
       <c r="K106" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N106">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" ht="23.1" customHeight="1" spans="1:14">
       <c r="A107">
         <v>1030225</v>
       </c>
@@ -5849,13 +6461,13 @@
         <v>1300225</v>
       </c>
       <c r="D107" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G107">
         <v>3</v>
@@ -5864,19 +6476,19 @@
         <v>1</v>
       </c>
       <c r="I107" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J107">
         <v>2030225</v>
       </c>
       <c r="K107" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N107">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" ht="23.1" customHeight="1" spans="1:14">
       <c r="A108">
         <v>1030226</v>
       </c>
@@ -5887,13 +6499,13 @@
         <v>1300226</v>
       </c>
       <c r="D108" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="E108">
         <v>3</v>
       </c>
       <c r="F108" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G108">
         <v>3</v>
@@ -5902,19 +6514,19 @@
         <v>1</v>
       </c>
       <c r="I108" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J108">
         <v>2030226</v>
       </c>
       <c r="K108" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N108">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" ht="23.1" customHeight="1" spans="1:14">
       <c r="A109">
         <v>1030227</v>
       </c>
@@ -5925,13 +6537,13 @@
         <v>1300227</v>
       </c>
       <c r="D109" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="E109">
         <v>3</v>
       </c>
       <c r="F109" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G109">
         <v>4</v>
@@ -5940,19 +6552,19 @@
         <v>1</v>
       </c>
       <c r="I109" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J109">
         <v>2030227</v>
       </c>
       <c r="K109" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N109">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" ht="23.1" customHeight="1" spans="1:14">
       <c r="A110">
         <v>1030228</v>
       </c>
@@ -5963,13 +6575,13 @@
         <v>1300228</v>
       </c>
       <c r="D110" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E110">
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G110">
         <v>4</v>
@@ -5978,19 +6590,19 @@
         <v>1</v>
       </c>
       <c r="I110" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J110">
         <v>2030228</v>
       </c>
       <c r="K110" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N110">
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" ht="23.1" customHeight="1" spans="1:14">
       <c r="A111">
         <v>1030229</v>
       </c>
@@ -6001,13 +6613,13 @@
         <v>1300229</v>
       </c>
       <c r="D111" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="E111">
         <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G111">
         <v>5</v>
@@ -6016,19 +6628,19 @@
         <v>1</v>
       </c>
       <c r="I111" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J111">
         <v>2030229</v>
       </c>
       <c r="K111" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N111">
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" ht="23.1" customHeight="1" spans="1:14">
       <c r="A112">
         <v>1030230</v>
       </c>
@@ -6039,13 +6651,13 @@
         <v>1300230</v>
       </c>
       <c r="D112" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="E112">
         <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G112">
         <v>5</v>
@@ -6054,19 +6666,19 @@
         <v>1</v>
       </c>
       <c r="I112" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J112">
         <v>2030230</v>
       </c>
       <c r="K112" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N112">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" ht="23.1" customHeight="1" spans="1:14">
       <c r="A113">
         <v>1030231</v>
       </c>
@@ -6077,13 +6689,13 @@
         <v>1300231</v>
       </c>
       <c r="D113" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="E113">
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G113">
         <v>6</v>
@@ -6092,19 +6704,19 @@
         <v>1</v>
       </c>
       <c r="I113" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J113">
         <v>2030231</v>
       </c>
       <c r="K113" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N113">
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" ht="23.1" customHeight="1" spans="1:14">
       <c r="A114">
         <v>1030232</v>
       </c>
@@ -6115,13 +6727,13 @@
         <v>1300232</v>
       </c>
       <c r="D114" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E114">
         <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G114">
         <v>6</v>
@@ -6130,19 +6742,19 @@
         <v>1</v>
       </c>
       <c r="I114" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J114">
         <v>2030232</v>
       </c>
       <c r="K114" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N114">
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" ht="23.1" customHeight="1" spans="1:14">
       <c r="A115">
         <v>1030241</v>
       </c>
@@ -6153,13 +6765,13 @@
         <v>1300241</v>
       </c>
       <c r="D115" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="E115">
         <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -6168,19 +6780,19 @@
         <v>1</v>
       </c>
       <c r="I115" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J115">
         <v>2030241</v>
       </c>
       <c r="K115" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N115">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" ht="23.1" customHeight="1" spans="1:14">
       <c r="A116">
         <v>1030242</v>
       </c>
@@ -6191,13 +6803,13 @@
         <v>1300242</v>
       </c>
       <c r="D116" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="E116">
         <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -6206,19 +6818,19 @@
         <v>1</v>
       </c>
       <c r="I116" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J116">
         <v>2030242</v>
       </c>
       <c r="K116" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" ht="23.1" customHeight="1" spans="1:14">
       <c r="A117">
         <v>1030243</v>
       </c>
@@ -6229,13 +6841,13 @@
         <v>1300243</v>
       </c>
       <c r="D117" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="E117">
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G117">
         <v>2</v>
@@ -6244,19 +6856,19 @@
         <v>1</v>
       </c>
       <c r="I117" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J117">
         <v>2030243</v>
       </c>
       <c r="K117" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N117">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" ht="23.1" customHeight="1" spans="1:14">
       <c r="A118">
         <v>1030244</v>
       </c>
@@ -6267,13 +6879,13 @@
         <v>1300244</v>
       </c>
       <c r="D118" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E118">
         <v>3</v>
       </c>
       <c r="F118" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G118">
         <v>2</v>
@@ -6282,19 +6894,19 @@
         <v>1</v>
       </c>
       <c r="I118" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J118">
         <v>2030244</v>
       </c>
       <c r="K118" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N118">
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" ht="23.1" customHeight="1" spans="1:14">
       <c r="A119">
         <v>1030245</v>
       </c>
@@ -6305,13 +6917,13 @@
         <v>1300245</v>
       </c>
       <c r="D119" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E119">
         <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G119">
         <v>3</v>
@@ -6320,19 +6932,19 @@
         <v>1</v>
       </c>
       <c r="I119" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J119">
         <v>2030245</v>
       </c>
       <c r="K119" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N119">
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" ht="23.1" customHeight="1" spans="1:14">
       <c r="A120">
         <v>1030246</v>
       </c>
@@ -6343,13 +6955,13 @@
         <v>1300246</v>
       </c>
       <c r="D120" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E120">
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G120">
         <v>3</v>
@@ -6358,19 +6970,19 @@
         <v>1</v>
       </c>
       <c r="I120" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J120">
         <v>2030246</v>
       </c>
       <c r="K120" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N120">
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" ht="23.1" customHeight="1" spans="1:14">
       <c r="A121">
         <v>1030247</v>
       </c>
@@ -6381,13 +6993,13 @@
         <v>1300247</v>
       </c>
       <c r="D121" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E121">
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G121">
         <v>4</v>
@@ -6396,19 +7008,19 @@
         <v>1</v>
       </c>
       <c r="I121" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J121">
         <v>2030247</v>
       </c>
       <c r="K121" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N121">
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" ht="23.1" customHeight="1" spans="1:14">
       <c r="A122">
         <v>1030248</v>
       </c>
@@ -6419,13 +7031,13 @@
         <v>1300248</v>
       </c>
       <c r="D122" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E122">
         <v>3</v>
       </c>
       <c r="F122" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G122">
         <v>4</v>
@@ -6434,19 +7046,19 @@
         <v>1</v>
       </c>
       <c r="I122" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J122">
         <v>2030248</v>
       </c>
       <c r="K122" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N122">
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" ht="23.1" customHeight="1" spans="1:14">
       <c r="A123">
         <v>1030249</v>
       </c>
@@ -6457,13 +7069,13 @@
         <v>1300249</v>
       </c>
       <c r="D123" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E123">
         <v>3</v>
       </c>
       <c r="F123" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G123">
         <v>5</v>
@@ -6472,19 +7084,19 @@
         <v>1</v>
       </c>
       <c r="I123" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J123">
         <v>2030249</v>
       </c>
       <c r="K123" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N123">
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" ht="23.1" customHeight="1" spans="1:14">
       <c r="A124">
         <v>1030250</v>
       </c>
@@ -6495,13 +7107,13 @@
         <v>1300250</v>
       </c>
       <c r="D124" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E124">
         <v>3</v>
       </c>
       <c r="F124" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G124">
         <v>5</v>
@@ -6510,19 +7122,19 @@
         <v>1</v>
       </c>
       <c r="I124" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J124">
         <v>2030250</v>
       </c>
       <c r="K124" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N124">
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" ht="23.1" customHeight="1" spans="1:14">
       <c r="A125">
         <v>1030251</v>
       </c>
@@ -6533,13 +7145,13 @@
         <v>1300251</v>
       </c>
       <c r="D125" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E125">
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G125">
         <v>6</v>
@@ -6548,19 +7160,19 @@
         <v>1</v>
       </c>
       <c r="I125" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J125">
         <v>2030251</v>
       </c>
       <c r="K125" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N125">
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" ht="23.1" customHeight="1" spans="1:14">
       <c r="A126">
         <v>1030252</v>
       </c>
@@ -6571,13 +7183,13 @@
         <v>1300252</v>
       </c>
       <c r="D126" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E126">
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G126">
         <v>6</v>
@@ -6586,19 +7198,19 @@
         <v>1</v>
       </c>
       <c r="I126" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J126">
         <v>2030252</v>
       </c>
       <c r="K126" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N126">
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" ht="23.1" customHeight="1" spans="1:14">
       <c r="A127">
         <v>1031001</v>
       </c>
@@ -6609,13 +7221,13 @@
         <v>1301001</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E127">
         <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -6624,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="I127" t="s">
-        <v>267</v>
+        <v>183</v>
       </c>
       <c r="J127">
         <v>2031001</v>
@@ -6636,7 +7248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" ht="23.1" customHeight="1" spans="1:14">
       <c r="A128">
         <v>1031002</v>
       </c>
@@ -6647,13 +7259,13 @@
         <v>1301002</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="E128">
         <v>3</v>
       </c>
       <c r="F128" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -6662,7 +7274,7 @@
         <v>1</v>
       </c>
       <c r="I128" t="s">
-        <v>268</v>
+        <v>185</v>
       </c>
       <c r="J128">
         <v>2031002</v>
@@ -6674,7 +7286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" ht="23.1" customHeight="1" spans="1:14">
       <c r="A129">
         <v>1031201</v>
       </c>
@@ -6685,13 +7297,13 @@
         <v>1301201</v>
       </c>
       <c r="D129" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="E129">
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -6700,7 +7312,7 @@
         <v>1</v>
       </c>
       <c r="I129" t="s">
-        <v>269</v>
+        <v>187</v>
       </c>
       <c r="J129">
         <v>2031201</v>
@@ -6712,7 +7324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" ht="23.1" customHeight="1" spans="1:14">
       <c r="A130">
         <v>1031202</v>
       </c>
@@ -6723,13 +7335,13 @@
         <v>1301202</v>
       </c>
       <c r="D130" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="E130">
         <v>3</v>
       </c>
       <c r="F130" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -6738,7 +7350,7 @@
         <v>1</v>
       </c>
       <c r="I130" t="s">
-        <v>270</v>
+        <v>189</v>
       </c>
       <c r="J130">
         <v>2031202</v>
@@ -6750,7 +7362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" ht="23.1" customHeight="1" spans="1:14">
       <c r="A131">
         <v>1031350</v>
       </c>
@@ -6761,13 +7373,13 @@
         <v>101801</v>
       </c>
       <c r="D131" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="E131">
         <v>3</v>
       </c>
       <c r="F131" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -6776,7 +7388,7 @@
         <v>1</v>
       </c>
       <c r="I131" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="J131">
         <v>201801</v>
@@ -6788,7 +7400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" ht="23.1" customHeight="1" spans="1:14">
       <c r="A132">
         <v>1031351</v>
       </c>
@@ -6799,13 +7411,13 @@
         <v>101802</v>
       </c>
       <c r="D132" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="E132">
         <v>3</v>
       </c>
       <c r="F132" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -6814,7 +7426,7 @@
         <v>1</v>
       </c>
       <c r="I132" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="J132">
         <v>201802</v>
@@ -6826,7 +7438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" ht="23.1" customHeight="1" spans="1:14">
       <c r="A133">
         <v>1021401</v>
       </c>
@@ -6837,13 +7449,13 @@
         <v>1201401</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="E133">
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -6852,7 +7464,7 @@
         <v>1</v>
       </c>
       <c r="I133" t="s">
-        <v>271</v>
+        <v>195</v>
       </c>
       <c r="J133">
         <v>2021401</v>
@@ -6864,7 +7476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" ht="23.1" customHeight="1" spans="1:14">
       <c r="A134">
         <v>1021402</v>
       </c>
@@ -6875,13 +7487,13 @@
         <v>1201402</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="E134">
         <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -6890,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="I134" t="s">
-        <v>272</v>
+        <v>197</v>
       </c>
       <c r="J134">
         <v>2021402</v>
@@ -6902,7 +7514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" ht="23.1" customHeight="1" spans="1:14">
       <c r="A135">
         <v>1031601</v>
       </c>
@@ -6913,13 +7525,13 @@
         <v>1301601</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="E135">
         <v>3</v>
       </c>
       <c r="F135" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -6928,7 +7540,7 @@
         <v>1</v>
       </c>
       <c r="I135" t="s">
-        <v>273</v>
+        <v>199</v>
       </c>
       <c r="J135">
         <v>2031601</v>
@@ -6940,7 +7552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" ht="23.1" customHeight="1" spans="1:14">
       <c r="A136">
         <v>1031602</v>
       </c>
@@ -6951,13 +7563,13 @@
         <v>1301602</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="E136">
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -6966,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="I136" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="J136">
         <v>2031602</v>
@@ -6978,7 +7590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" ht="23.1" customHeight="1" spans="1:14">
       <c r="A137">
         <v>1031801</v>
       </c>
@@ -6989,13 +7601,13 @@
         <v>1301801</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="E137">
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -7004,7 +7616,7 @@
         <v>1</v>
       </c>
       <c r="I137" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="J137">
         <v>2031801</v>
@@ -7016,7 +7628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" ht="23.1" customHeight="1" spans="1:14">
       <c r="A138">
         <v>1031802</v>
       </c>
@@ -7027,13 +7639,13 @@
         <v>1301802</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="E138">
         <v>3</v>
       </c>
       <c r="F138" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -7042,7 +7654,7 @@
         <v>1</v>
       </c>
       <c r="I138" t="s">
-        <v>276</v>
+        <v>205</v>
       </c>
       <c r="J138">
         <v>2031802</v>
@@ -7054,7 +7666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" ht="23.1" customHeight="1" spans="1:14">
       <c r="A139">
         <v>1032001</v>
       </c>
@@ -7065,13 +7677,13 @@
         <v>1302001</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="E139">
         <v>3</v>
       </c>
       <c r="F139" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -7080,7 +7692,7 @@
         <v>1</v>
       </c>
       <c r="I139" t="s">
-        <v>277</v>
+        <v>207</v>
       </c>
       <c r="J139">
         <v>2032001</v>
@@ -7092,7 +7704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" ht="23.1" customHeight="1" spans="1:14">
       <c r="A140">
         <v>1032002</v>
       </c>
@@ -7103,13 +7715,13 @@
         <v>1302002</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="E140">
         <v>3</v>
       </c>
       <c r="F140" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -7118,7 +7730,7 @@
         <v>1</v>
       </c>
       <c r="I140" t="s">
-        <v>278</v>
+        <v>209</v>
       </c>
       <c r="J140">
         <v>2032002</v>
@@ -7130,7 +7742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" ht="23.1" customHeight="1" spans="1:14">
       <c r="A141">
         <v>1032201</v>
       </c>
@@ -7141,13 +7753,13 @@
         <v>1302201</v>
       </c>
       <c r="D141" s="14" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="E141">
         <v>3</v>
       </c>
       <c r="F141" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -7156,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="I141" t="s">
-        <v>279</v>
+        <v>211</v>
       </c>
       <c r="J141">
         <v>2032201</v>
@@ -7168,7 +7780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" ht="23.1" customHeight="1" spans="1:14">
       <c r="A142">
         <v>1032202</v>
       </c>
@@ -7179,13 +7791,13 @@
         <v>1302202</v>
       </c>
       <c r="D142" s="14" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="E142">
         <v>3</v>
       </c>
       <c r="F142" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -7194,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="I142" t="s">
-        <v>280</v>
+        <v>213</v>
       </c>
       <c r="J142">
         <v>2032202</v>
@@ -7206,7 +7818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" ht="18" customHeight="1" spans="1:17">
       <c r="A143">
         <v>1022501</v>
       </c>
@@ -7217,13 +7829,13 @@
         <v>1202501</v>
       </c>
       <c r="D143" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="E143">
         <v>2</v>
       </c>
       <c r="F143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -7232,13 +7844,13 @@
         <v>0</v>
       </c>
       <c r="I143" t="s">
-        <v>281</v>
+        <v>215</v>
       </c>
       <c r="J143">
         <v>2022501</v>
       </c>
       <c r="K143" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="N143">
         <v>999</v>
@@ -7247,7 +7859,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" ht="18" customHeight="1" spans="1:17">
       <c r="A144">
         <v>1022502</v>
       </c>
@@ -7258,13 +7870,13 @@
         <v>1202502</v>
       </c>
       <c r="D144" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="E144">
         <v>2</v>
       </c>
       <c r="F144" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -7273,13 +7885,13 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>282</v>
+        <v>218</v>
       </c>
       <c r="J144">
         <v>2022502</v>
       </c>
       <c r="K144" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="N144">
         <v>999</v>
@@ -7288,7 +7900,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" ht="18" customHeight="1" spans="1:17">
       <c r="A145">
         <v>1022503</v>
       </c>
@@ -7299,13 +7911,13 @@
         <v>1202503</v>
       </c>
       <c r="D145" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="E145">
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -7314,13 +7926,13 @@
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>283</v>
+        <v>221</v>
       </c>
       <c r="J145">
         <v>2022503</v>
       </c>
       <c r="K145" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="N145">
         <v>999</v>
@@ -7329,7 +7941,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" ht="18" customHeight="1" spans="1:14">
       <c r="A146">
         <v>1022504</v>
       </c>
@@ -7340,13 +7952,13 @@
         <v>1202504</v>
       </c>
       <c r="D146" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="E146">
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -7355,19 +7967,19 @@
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>284</v>
+        <v>223</v>
       </c>
       <c r="J146">
         <v>2022504</v>
       </c>
       <c r="K146" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="N146">
         <v>999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" ht="21" customHeight="1" spans="1:17">
       <c r="A147">
         <v>1023001</v>
       </c>
@@ -7376,13 +7988,13 @@
         <v>1023001</v>
       </c>
       <c r="D147" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G147">
         <v>2</v>
@@ -7391,13 +8003,13 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="J147">
         <v>2023001</v>
       </c>
       <c r="K147" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="N147">
         <v>999</v>
@@ -7406,7 +8018,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" ht="21" customHeight="1" spans="1:17">
       <c r="A148">
         <v>1023002</v>
       </c>
@@ -7415,13 +8027,13 @@
         <v>1023002</v>
       </c>
       <c r="D148" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="E148">
         <v>2</v>
       </c>
       <c r="F148" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G148">
         <v>3</v>
@@ -7430,13 +8042,13 @@
         <v>0</v>
       </c>
       <c r="I148" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="J148">
         <v>2023002</v>
       </c>
       <c r="K148" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="N148">
         <v>999</v>
@@ -7445,7 +8057,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" ht="21" customHeight="1" spans="1:17">
       <c r="A149">
         <v>1023003</v>
       </c>
@@ -7454,13 +8066,13 @@
         <v>1023003</v>
       </c>
       <c r="D149" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="E149">
         <v>2</v>
       </c>
       <c r="F149" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G149">
         <v>4</v>
@@ -7469,13 +8081,13 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="J149">
         <v>2023003</v>
       </c>
       <c r="K149" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="N149">
         <v>999</v>
@@ -7484,7 +8096,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" ht="21" customHeight="1" spans="1:17">
       <c r="A150">
         <v>1023004</v>
       </c>
@@ -7493,13 +8105,13 @@
         <v>1023004</v>
       </c>
       <c r="D150" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="E150">
         <v>2</v>
       </c>
       <c r="F150" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G150">
         <v>5</v>
@@ -7508,13 +8120,13 @@
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="J150">
         <v>2023004</v>
       </c>
       <c r="K150" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="N150">
         <v>999</v>
@@ -7523,7 +8135,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" ht="21" customHeight="1" spans="1:17">
       <c r="A151">
         <v>1023005</v>
       </c>
@@ -7532,13 +8144,13 @@
         <v>1023005</v>
       </c>
       <c r="D151" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="E151">
         <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G151">
         <v>6</v>
@@ -7547,13 +8159,13 @@
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="J151">
         <v>2023005</v>
       </c>
       <c r="K151" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="N151">
         <v>999</v>
@@ -7562,7 +8174,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" ht="21" customHeight="1" spans="1:17">
       <c r="A152">
         <v>1023101</v>
       </c>
@@ -7571,13 +8183,13 @@
         <v>1023101</v>
       </c>
       <c r="D152" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="E152">
         <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G152">
         <v>2</v>
@@ -7586,13 +8198,13 @@
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="J152">
         <v>2023101</v>
       </c>
       <c r="K152" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="N152">
         <v>999</v>
@@ -7601,7 +8213,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" ht="21" customHeight="1" spans="1:17">
       <c r="A153">
         <v>1023102</v>
       </c>
@@ -7610,13 +8222,13 @@
         <v>1023102</v>
       </c>
       <c r="D153" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="E153">
         <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G153">
         <v>3</v>
@@ -7625,13 +8237,13 @@
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="J153">
         <v>2023102</v>
       </c>
       <c r="K153" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="N153">
         <v>999</v>
@@ -7640,7 +8252,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" ht="21" customHeight="1" spans="1:17">
       <c r="A154">
         <v>1023103</v>
       </c>
@@ -7649,13 +8261,13 @@
         <v>1023103</v>
       </c>
       <c r="D154" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="E154">
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G154">
         <v>4</v>
@@ -7664,13 +8276,13 @@
         <v>0</v>
       </c>
       <c r="I154" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="J154">
         <v>2023103</v>
       </c>
       <c r="K154" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="N154">
         <v>999</v>
@@ -7679,7 +8291,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" ht="21" customHeight="1" spans="1:17">
       <c r="A155">
         <v>1023104</v>
       </c>
@@ -7688,13 +8300,13 @@
         <v>1023104</v>
       </c>
       <c r="D155" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="E155">
         <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G155">
         <v>5</v>
@@ -7703,13 +8315,13 @@
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="J155">
         <v>2023104</v>
       </c>
       <c r="K155" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="N155">
         <v>999</v>
@@ -7718,7 +8330,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" ht="21" customHeight="1" spans="1:17">
       <c r="A156">
         <v>1023105</v>
       </c>
@@ -7727,13 +8339,13 @@
         <v>1023105</v>
       </c>
       <c r="D156" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="E156">
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G156">
         <v>6</v>
@@ -7742,13 +8354,13 @@
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="J156">
         <v>2023105</v>
       </c>
       <c r="K156" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="N156">
         <v>999</v>
@@ -7757,7 +8369,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" ht="21" customHeight="1" spans="1:17">
       <c r="A157">
         <v>1023201</v>
       </c>
@@ -7766,13 +8378,13 @@
         <v>1023201</v>
       </c>
       <c r="D157" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="E157">
         <v>2</v>
       </c>
       <c r="F157" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G157">
         <v>2</v>
@@ -7781,13 +8393,13 @@
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="J157">
         <v>2023201</v>
       </c>
       <c r="K157" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="N157">
         <v>999</v>
@@ -7796,7 +8408,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" ht="21" customHeight="1" spans="1:17">
       <c r="A158">
         <v>1023202</v>
       </c>
@@ -7805,13 +8417,13 @@
         <v>1023202</v>
       </c>
       <c r="D158" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="E158">
         <v>2</v>
       </c>
       <c r="F158" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G158">
         <v>3</v>
@@ -7820,13 +8432,13 @@
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="J158">
         <v>2023202</v>
       </c>
       <c r="K158" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="N158">
         <v>999</v>
@@ -7835,7 +8447,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="159" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" ht="21" customHeight="1" spans="1:17">
       <c r="A159">
         <v>1023203</v>
       </c>
@@ -7844,13 +8456,13 @@
         <v>1023203</v>
       </c>
       <c r="D159" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="E159">
         <v>2</v>
       </c>
       <c r="F159" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G159">
         <v>4</v>
@@ -7859,13 +8471,13 @@
         <v>0</v>
       </c>
       <c r="I159" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="J159">
         <v>2023203</v>
       </c>
       <c r="K159" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="N159">
         <v>999</v>
@@ -7874,7 +8486,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="160" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" ht="21" customHeight="1" spans="1:17">
       <c r="A160">
         <v>1023204</v>
       </c>
@@ -7883,13 +8495,13 @@
         <v>1023204</v>
       </c>
       <c r="D160" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="E160">
         <v>2</v>
       </c>
       <c r="F160" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G160">
         <v>5</v>
@@ -7898,13 +8510,13 @@
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="J160">
         <v>2023204</v>
       </c>
       <c r="K160" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="N160">
         <v>999</v>
@@ -7913,7 +8525,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" ht="21" customHeight="1" spans="1:17">
       <c r="A161">
         <v>1023205</v>
       </c>
@@ -7922,13 +8534,13 @@
         <v>1023205</v>
       </c>
       <c r="D161" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E161">
         <v>2</v>
       </c>
       <c r="F161" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G161">
         <v>6</v>
@@ -7937,13 +8549,13 @@
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="J161">
         <v>2023205</v>
       </c>
       <c r="K161" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="N161">
         <v>999</v>
@@ -7952,7 +8564,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" ht="21" customHeight="1" spans="1:17">
       <c r="A162">
         <v>1023301</v>
       </c>
@@ -7961,13 +8573,13 @@
         <v>1023301</v>
       </c>
       <c r="D162" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="E162">
         <v>2</v>
       </c>
       <c r="F162" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G162">
         <v>2</v>
@@ -7976,13 +8588,13 @@
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="J162">
         <v>2023301</v>
       </c>
       <c r="K162" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="N162">
         <v>999</v>
@@ -7991,7 +8603,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="163" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" ht="21" customHeight="1" spans="1:17">
       <c r="A163">
         <v>1023302</v>
       </c>
@@ -8000,13 +8612,13 @@
         <v>1023302</v>
       </c>
       <c r="D163" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="E163">
         <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G163">
         <v>3</v>
@@ -8015,13 +8627,13 @@
         <v>0</v>
       </c>
       <c r="I163" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="J163">
         <v>2023302</v>
       </c>
       <c r="K163" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="N163">
         <v>999</v>
@@ -8030,7 +8642,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" ht="21" customHeight="1" spans="1:17">
       <c r="A164">
         <v>1023303</v>
       </c>
@@ -8039,13 +8651,13 @@
         <v>1023303</v>
       </c>
       <c r="D164" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="E164">
         <v>2</v>
       </c>
       <c r="F164" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G164">
         <v>4</v>
@@ -8054,13 +8666,13 @@
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="J164">
         <v>2023303</v>
       </c>
       <c r="K164" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="N164">
         <v>999</v>
@@ -8069,7 +8681,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="165" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" ht="21" customHeight="1" spans="1:17">
       <c r="A165">
         <v>1023304</v>
       </c>
@@ -8078,13 +8690,13 @@
         <v>1023304</v>
       </c>
       <c r="D165" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="E165">
         <v>2</v>
       </c>
       <c r="F165" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G165">
         <v>5</v>
@@ -8093,13 +8705,13 @@
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="J165">
         <v>2023304</v>
       </c>
       <c r="K165" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="N165">
         <v>999</v>
@@ -8108,7 +8720,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" ht="21" customHeight="1" spans="1:17">
       <c r="A166">
         <v>1023305</v>
       </c>
@@ -8117,13 +8729,13 @@
         <v>1023305</v>
       </c>
       <c r="D166" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="E166">
         <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G166">
         <v>6</v>
@@ -8132,13 +8744,13 @@
         <v>0</v>
       </c>
       <c r="I166" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="J166">
         <v>2023305</v>
       </c>
       <c r="K166" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="N166">
         <v>999</v>
@@ -8147,7 +8759,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="167" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" ht="21" customHeight="1" spans="1:17">
       <c r="A167">
         <v>1023401</v>
       </c>
@@ -8156,13 +8768,13 @@
         <v>1023401</v>
       </c>
       <c r="D167" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="E167">
         <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G167">
         <v>2</v>
@@ -8171,13 +8783,13 @@
         <v>0</v>
       </c>
       <c r="I167" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="J167">
         <v>2023401</v>
       </c>
       <c r="K167" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="N167">
         <v>999</v>
@@ -8186,7 +8798,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="168" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" ht="21" customHeight="1" spans="1:17">
       <c r="A168">
         <v>1023402</v>
       </c>
@@ -8195,13 +8807,13 @@
         <v>1023402</v>
       </c>
       <c r="D168" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="E168">
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G168">
         <v>3</v>
@@ -8210,13 +8822,13 @@
         <v>0</v>
       </c>
       <c r="I168" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="J168">
         <v>2023402</v>
       </c>
       <c r="K168" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="N168">
         <v>999</v>
@@ -8225,7 +8837,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" ht="21" customHeight="1" spans="1:17">
       <c r="A169">
         <v>1023403</v>
       </c>
@@ -8234,13 +8846,13 @@
         <v>1023403</v>
       </c>
       <c r="D169" t="s">
-        <v>242</v>
+        <v>274</v>
       </c>
       <c r="E169">
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G169">
         <v>4</v>
@@ -8249,13 +8861,13 @@
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="J169">
         <v>2023403</v>
       </c>
       <c r="K169" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="N169">
         <v>999</v>
@@ -8264,7 +8876,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" ht="21" customHeight="1" spans="1:17">
       <c r="A170">
         <v>1023404</v>
       </c>
@@ -8273,13 +8885,13 @@
         <v>1023404</v>
       </c>
       <c r="D170" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="E170">
         <v>2</v>
       </c>
       <c r="F170" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G170">
         <v>5</v>
@@ -8288,13 +8900,13 @@
         <v>0</v>
       </c>
       <c r="I170" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="J170">
         <v>2023404</v>
       </c>
       <c r="K170" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="N170">
         <v>999</v>
@@ -8303,7 +8915,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" ht="21" customHeight="1" spans="1:17">
       <c r="A171">
         <v>1023405</v>
       </c>
@@ -8312,13 +8924,13 @@
         <v>1023405</v>
       </c>
       <c r="D171" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="E171">
         <v>2</v>
       </c>
       <c r="F171" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G171">
         <v>6</v>
@@ -8327,13 +8939,13 @@
         <v>0</v>
       </c>
       <c r="I171" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="J171">
         <v>2023405</v>
       </c>
       <c r="K171" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="N171">
         <v>999</v>
@@ -8342,7 +8954,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" ht="21" customHeight="1" spans="1:17">
       <c r="A172">
         <v>1990000</v>
       </c>
@@ -8353,13 +8965,13 @@
         <v>1990000</v>
       </c>
       <c r="D172" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="E172">
         <v>99</v>
       </c>
       <c r="F172" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="G172">
         <v>1</v>
@@ -8368,19 +8980,23 @@
         <v>0</v>
       </c>
       <c r="I172" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J172">
         <v>2990000</v>
       </c>
       <c r="K172" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="N172">
         <v>-1</v>
       </c>
-    </row>
-    <row r="173" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q172">
+        <f>1/100000</f>
+        <v>1e-5</v>
+      </c>
+    </row>
+    <row r="173" ht="21" customHeight="1" spans="1:17">
       <c r="A173">
         <v>1980000</v>
       </c>
@@ -8391,13 +9007,13 @@
         <v>1980000</v>
       </c>
       <c r="D173" t="s">
-        <v>251</v>
+        <v>284</v>
       </c>
       <c r="E173">
         <v>98</v>
       </c>
       <c r="F173" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -8406,21 +9022,25 @@
         <v>0</v>
       </c>
       <c r="I173" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J173">
         <v>2980000</v>
       </c>
       <c r="K173" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="N173">
         <v>-1</v>
       </c>
+      <c r="Q173">
+        <f>1/100</f>
+        <v>0.01</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -778,7 +778,7 @@
     <t>itemicon_1031202.png</t>
   </si>
   <si>
-    <t>头像框-特权卡专属</t>
+    <t>头像框-每日奖金</t>
   </si>
   <si>
     <t>frame_801.png</t>
@@ -1079,7 +1079,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1096,6 +1096,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1256,7 +1263,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1355,12 +1362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1374,12 +1375,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1403,12 +1398,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1422,12 +1411,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1451,12 +1434,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1470,12 +1447,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1633,16 +1604,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1651,58 +1619,67 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1711,59 +1688,53 @@
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1792,6 +1763,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -2402,7 +2376,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -2444,7 +2418,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -2485,11 +2459,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:17">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
     </row>
-    <row r="5" ht="21" customHeight="1" spans="1:15">
+    <row r="5" ht="21" customHeight="1" spans="1:17">
       <c r="A5">
         <v>1010101</v>
       </c>
@@ -2530,7 +2504,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" ht="21" customHeight="1" spans="1:15">
+    <row r="6" ht="21" customHeight="1" spans="1:17">
       <c r="A6">
         <v>1010201</v>
       </c>
@@ -2796,7 +2770,7 @@
         <v>49.99</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A12" s="1">
         <v>1010311</v>
       </c>
@@ -2838,7 +2812,7 @@
         <v>100006</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A13" s="1">
         <v>1010312</v>
       </c>
@@ -2880,7 +2854,7 @@
         <v>100007</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A14" s="1">
         <v>1010313</v>
       </c>
@@ -2922,7 +2896,7 @@
         <v>100008</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A15" s="1">
         <v>1010314</v>
       </c>
@@ -2964,7 +2938,7 @@
         <v>100009</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A16" s="1">
         <v>1010315</v>
       </c>
@@ -7286,7 +7260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" ht="23.1" customHeight="1" spans="1:14">
+    <row r="129" ht="23.1" customHeight="1" spans="1:17">
       <c r="A129">
         <v>1031201</v>
       </c>
@@ -7324,7 +7298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" ht="23.1" customHeight="1" spans="1:14">
+    <row r="130" ht="23.1" customHeight="1" spans="1:17">
       <c r="A130">
         <v>1031202</v>
       </c>
@@ -7362,7 +7336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" ht="23.1" customHeight="1" spans="1:14">
+    <row r="131" ht="23.1" customHeight="1" spans="1:17">
       <c r="A131">
         <v>1031350</v>
       </c>
@@ -7393,14 +7367,14 @@
       <c r="J131">
         <v>201801</v>
       </c>
-      <c r="L131">
-        <v>1801</v>
+      <c r="L131" s="10">
+        <v>1006</v>
       </c>
       <c r="N131">
         <v>1</v>
       </c>
     </row>
-    <row r="132" ht="23.1" customHeight="1" spans="1:14">
+    <row r="132" ht="23.1" customHeight="1" spans="1:17">
       <c r="A132">
         <v>1031351</v>
       </c>
@@ -7431,14 +7405,14 @@
       <c r="J132">
         <v>201802</v>
       </c>
-      <c r="L132">
-        <v>1802</v>
+      <c r="L132" s="10">
+        <v>1007</v>
       </c>
       <c r="N132">
         <v>1</v>
       </c>
     </row>
-    <row r="133" ht="23.1" customHeight="1" spans="1:14">
+    <row r="133" ht="23.1" customHeight="1" spans="1:17">
       <c r="A133">
         <v>1021401</v>
       </c>
@@ -7448,7 +7422,7 @@
       <c r="C133">
         <v>1201401</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="D133" s="11" t="s">
         <v>194</v>
       </c>
       <c r="E133">
@@ -7476,7 +7450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" ht="23.1" customHeight="1" spans="1:14">
+    <row r="134" ht="23.1" customHeight="1" spans="1:17">
       <c r="A134">
         <v>1021402</v>
       </c>
@@ -7486,7 +7460,7 @@
       <c r="C134">
         <v>1201402</v>
       </c>
-      <c r="D134" s="10" t="s">
+      <c r="D134" s="11" t="s">
         <v>196</v>
       </c>
       <c r="E134">
@@ -7514,7 +7488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" ht="23.1" customHeight="1" spans="1:14">
+    <row r="135" ht="23.1" customHeight="1" spans="1:17">
       <c r="A135">
         <v>1031601</v>
       </c>
@@ -7524,7 +7498,7 @@
       <c r="C135">
         <v>1301601</v>
       </c>
-      <c r="D135" s="11" t="s">
+      <c r="D135" s="12" t="s">
         <v>198</v>
       </c>
       <c r="E135">
@@ -7552,7 +7526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" ht="23.1" customHeight="1" spans="1:14">
+    <row r="136" ht="23.1" customHeight="1" spans="1:17">
       <c r="A136">
         <v>1031602</v>
       </c>
@@ -7562,7 +7536,7 @@
       <c r="C136">
         <v>1301602</v>
       </c>
-      <c r="D136" s="11" t="s">
+      <c r="D136" s="12" t="s">
         <v>200</v>
       </c>
       <c r="E136">
@@ -7590,7 +7564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" ht="23.1" customHeight="1" spans="1:14">
+    <row r="137" ht="23.1" customHeight="1" spans="1:17">
       <c r="A137">
         <v>1031801</v>
       </c>
@@ -7600,7 +7574,7 @@
       <c r="C137">
         <v>1301801</v>
       </c>
-      <c r="D137" s="12" t="s">
+      <c r="D137" s="13" t="s">
         <v>202</v>
       </c>
       <c r="E137">
@@ -7628,7 +7602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" ht="23.1" customHeight="1" spans="1:14">
+    <row r="138" ht="23.1" customHeight="1" spans="1:17">
       <c r="A138">
         <v>1031802</v>
       </c>
@@ -7638,7 +7612,7 @@
       <c r="C138">
         <v>1301802</v>
       </c>
-      <c r="D138" s="12" t="s">
+      <c r="D138" s="13" t="s">
         <v>204</v>
       </c>
       <c r="E138">
@@ -7666,7 +7640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" ht="23.1" customHeight="1" spans="1:14">
+    <row r="139" ht="23.1" customHeight="1" spans="1:17">
       <c r="A139">
         <v>1032001</v>
       </c>
@@ -7676,7 +7650,7 @@
       <c r="C139">
         <v>1302001</v>
       </c>
-      <c r="D139" s="13" t="s">
+      <c r="D139" s="14" t="s">
         <v>206</v>
       </c>
       <c r="E139">
@@ -7704,7 +7678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" ht="23.1" customHeight="1" spans="1:14">
+    <row r="140" ht="23.1" customHeight="1" spans="1:17">
       <c r="A140">
         <v>1032002</v>
       </c>
@@ -7714,7 +7688,7 @@
       <c r="C140">
         <v>1302002</v>
       </c>
-      <c r="D140" s="13" t="s">
+      <c r="D140" s="14" t="s">
         <v>208</v>
       </c>
       <c r="E140">
@@ -7742,7 +7716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" ht="23.1" customHeight="1" spans="1:14">
+    <row r="141" ht="23.1" customHeight="1" spans="1:17">
       <c r="A141">
         <v>1032201</v>
       </c>
@@ -7752,7 +7726,7 @@
       <c r="C141">
         <v>1302201</v>
       </c>
-      <c r="D141" s="14" t="s">
+      <c r="D141" s="15" t="s">
         <v>210</v>
       </c>
       <c r="E141">
@@ -7780,7 +7754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" ht="23.1" customHeight="1" spans="1:14">
+    <row r="142" ht="23.1" customHeight="1" spans="1:17">
       <c r="A142">
         <v>1032202</v>
       </c>
@@ -7790,7 +7764,7 @@
       <c r="C142">
         <v>1302202</v>
       </c>
-      <c r="D142" s="14" t="s">
+      <c r="D142" s="15" t="s">
         <v>212</v>
       </c>
       <c r="E142">
@@ -7941,7 +7915,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1" spans="1:14">
+    <row r="146" ht="18" customHeight="1" spans="1:17">
       <c r="A146">
         <v>1022504</v>
       </c>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -2326,7 +2326,7 @@
     <col min="14" max="14" width="12.25" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="18.875" customWidth="1"/>
-    <col min="17" max="17" width="9.375"/>
+    <col min="17" max="17" width="12.625"/>
     <col min="20" max="20" width="9.375"/>
   </cols>
   <sheetData>
@@ -8966,8 +8966,8 @@
         <v>-1</v>
       </c>
       <c r="Q172">
-        <f>1/100000</f>
-        <v>1e-5</v>
+        <f>1/700000</f>
+        <v>1.42857142857143e-6</v>
       </c>
     </row>
     <row r="173" ht="21" customHeight="1" spans="1:17">

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -2321,7 +2321,7 @@
     <col min="9" max="9" width="22.625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="28.875" customWidth="1"/>
-    <col min="12" max="12" width="10.875" customWidth="1"/>
+    <col min="12" max="12" width="13.375" customWidth="1"/>
     <col min="13" max="13" width="17.25" customWidth="1"/>
     <col min="14" max="14" width="12.25" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -7368,7 +7368,7 @@
         <v>201801</v>
       </c>
       <c r="L131" s="10">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="N131">
         <v>1</v>
@@ -7406,7 +7406,7 @@
         <v>201802</v>
       </c>
       <c r="L132" s="10">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N132">
         <v>1</v>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -179,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F172" authorId="0">
+    <comment ref="F173" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="278">
   <si>
     <t>道具ID</t>
   </si>
@@ -793,63 +793,39 @@
     <t>国旗2</t>
   </si>
   <si>
-    <t>itemicon_1021401.png</t>
+    <t>itemicon_1022503.png</t>
   </si>
   <si>
     <t>国旗3</t>
   </si>
   <si>
-    <t>itemicon_1021402.png</t>
+    <t>头衔1</t>
   </si>
   <si>
     <t>头衔2</t>
   </si>
   <si>
-    <t>itemicon_1031601.png</t>
-  </si>
-  <si>
     <t>头衔3</t>
   </si>
   <si>
-    <t>itemicon_1031602.png</t>
-  </si>
-  <si>
     <t>筹码2</t>
   </si>
   <si>
-    <t>itemicon_1031801.png</t>
-  </si>
-  <si>
     <t>筹码3</t>
   </si>
   <si>
-    <t>itemicon_1031802.png</t>
-  </si>
-  <si>
     <t>牌背2</t>
   </si>
   <si>
-    <t>itemicon_1032001.png</t>
-  </si>
-  <si>
     <t>牌背3</t>
   </si>
   <si>
-    <t>itemicon_1032002.png</t>
-  </si>
-  <si>
     <t>大厅背景2</t>
   </si>
   <si>
-    <t>itemicon_1032201.png</t>
-  </si>
-  <si>
     <t>大厅背景3</t>
   </si>
   <si>
-    <t>itemicon_1032202.png</t>
-  </si>
-  <si>
     <t>祈福卡</t>
   </si>
   <si>
@@ -869,9 +845,6 @@
   </si>
   <si>
     <t>夺宝优惠券</t>
-  </si>
-  <si>
-    <t>itemicon_1022503.png</t>
   </si>
   <si>
     <t>积分</t>
@@ -1094,15 +1067,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1734,7 +1707,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1744,13 +1717,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1765,10 +1741,13 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
@@ -2308,7 +2287,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q173"/>
+  <dimension ref="A1:Q174"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
@@ -2331,27 +2310,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4" t="s">
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J1" t="s">
@@ -2363,7 +2342,7 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="O1" t="s">
@@ -2377,38 +2356,38 @@
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="6"/>
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>14</v>
       </c>
       <c r="O2" t="s">
@@ -2419,25 +2398,25 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J3" t="s">
@@ -2449,7 +2428,7 @@
       <c r="M3" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="5" t="s">
         <v>26</v>
       </c>
       <c r="O3" t="s">
@@ -2460,14 +2439,14 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
     </row>
     <row r="5" ht="21" customHeight="1" spans="1:17">
       <c r="A5">
         <v>1010101</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>101</v>
       </c>
       <c r="C5">
@@ -2500,7 +2479,7 @@
       <c r="N5">
         <v>999</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="9" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2508,7 +2487,7 @@
       <c r="A6">
         <v>1010201</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <v>201</v>
       </c>
       <c r="C6">
@@ -2541,7 +2520,7 @@
       <c r="N6">
         <v>999</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2582,7 +2561,7 @@
       <c r="N7" s="1">
         <v>999</v>
       </c>
-      <c r="O7" s="9"/>
+      <c r="O7" s="10"/>
       <c r="P7" s="1">
         <v>1010301</v>
       </c>
@@ -2627,7 +2606,7 @@
       <c r="N8" s="1">
         <v>999</v>
       </c>
-      <c r="O8" s="9"/>
+      <c r="O8" s="10"/>
       <c r="P8" s="1">
         <v>1010302</v>
       </c>
@@ -2672,7 +2651,7 @@
       <c r="N9" s="1">
         <v>999</v>
       </c>
-      <c r="O9" s="9"/>
+      <c r="O9" s="10"/>
       <c r="P9" s="1">
         <v>1010303</v>
       </c>
@@ -2717,7 +2696,7 @@
       <c r="N10" s="1">
         <v>999</v>
       </c>
-      <c r="O10" s="9"/>
+      <c r="O10" s="10"/>
       <c r="P10" s="1">
         <v>1010304</v>
       </c>
@@ -2762,7 +2741,7 @@
       <c r="N11" s="1">
         <v>999</v>
       </c>
-      <c r="O11" s="9"/>
+      <c r="O11" s="10"/>
       <c r="P11" s="1">
         <v>1010305</v>
       </c>
@@ -2807,7 +2786,7 @@
       <c r="N12" s="1">
         <v>999</v>
       </c>
-      <c r="O12" s="9"/>
+      <c r="O12" s="10"/>
       <c r="P12" s="1">
         <v>100006</v>
       </c>
@@ -2849,7 +2828,7 @@
       <c r="N13" s="1">
         <v>999</v>
       </c>
-      <c r="O13" s="9"/>
+      <c r="O13" s="10"/>
       <c r="P13" s="1">
         <v>100007</v>
       </c>
@@ -2891,7 +2870,7 @@
       <c r="N14" s="1">
         <v>999</v>
       </c>
-      <c r="O14" s="9"/>
+      <c r="O14" s="10"/>
       <c r="P14" s="1">
         <v>100008</v>
       </c>
@@ -2933,7 +2912,7 @@
       <c r="N15" s="1">
         <v>999</v>
       </c>
-      <c r="O15" s="9"/>
+      <c r="O15" s="10"/>
       <c r="P15" s="1">
         <v>100009</v>
       </c>
@@ -2975,7 +2954,7 @@
       <c r="N16" s="1">
         <v>999</v>
       </c>
-      <c r="O16" s="9"/>
+      <c r="O16" s="10"/>
       <c r="P16" s="1">
         <v>100010</v>
       </c>
@@ -2984,7 +2963,7 @@
       <c r="A17">
         <v>1020001</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <v>1</v>
       </c>
       <c r="C17">
@@ -3212,7 +3191,7 @@
       <c r="A23">
         <v>1030011</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="8">
         <v>11</v>
       </c>
       <c r="C23">
@@ -3253,7 +3232,7 @@
       <c r="A24">
         <v>1030012</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="8">
         <v>12</v>
       </c>
       <c r="C24">
@@ -3294,7 +3273,7 @@
       <c r="A25">
         <v>1030013</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="8">
         <v>13</v>
       </c>
       <c r="C25">
@@ -3335,7 +3314,7 @@
       <c r="A26">
         <v>1030014</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <v>14</v>
       </c>
       <c r="C26">
@@ -3376,7 +3355,7 @@
       <c r="A27">
         <v>1030015</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <v>15</v>
       </c>
       <c r="C27">
@@ -3417,7 +3396,7 @@
       <c r="A28">
         <v>1030016</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <v>16</v>
       </c>
       <c r="C28">
@@ -3458,7 +3437,7 @@
       <c r="A29">
         <v>1030017</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="8">
         <v>17</v>
       </c>
       <c r="C29">
@@ -3499,7 +3478,7 @@
       <c r="A30">
         <v>1030018</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="8">
         <v>18</v>
       </c>
       <c r="C30">
@@ -3540,7 +3519,7 @@
       <c r="A31">
         <v>1030101</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="8">
         <v>101</v>
       </c>
       <c r="C31">
@@ -3578,7 +3557,7 @@
       <c r="A32">
         <v>1030102</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="8">
         <v>102</v>
       </c>
       <c r="C32">
@@ -3616,7 +3595,7 @@
       <c r="A33">
         <v>1030103</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="8">
         <v>103</v>
       </c>
       <c r="C33">
@@ -3654,7 +3633,7 @@
       <c r="A34">
         <v>1030104</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="8">
         <v>104</v>
       </c>
       <c r="C34">
@@ -3692,7 +3671,7 @@
       <c r="A35">
         <v>1030105</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="8">
         <v>105</v>
       </c>
       <c r="C35">
@@ -3730,7 +3709,7 @@
       <c r="A36">
         <v>1030106</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="8">
         <v>106</v>
       </c>
       <c r="C36">
@@ -3768,7 +3747,7 @@
       <c r="A37">
         <v>1030107</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="8">
         <v>107</v>
       </c>
       <c r="C37">
@@ -3806,7 +3785,7 @@
       <c r="A38">
         <v>1030108</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="8">
         <v>108</v>
       </c>
       <c r="C38">
@@ -3844,7 +3823,7 @@
       <c r="A39">
         <v>1030109</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="8">
         <v>109</v>
       </c>
       <c r="C39">
@@ -3882,7 +3861,7 @@
       <c r="A40">
         <v>1030110</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="8">
         <v>110</v>
       </c>
       <c r="C40">
@@ -3920,7 +3899,7 @@
       <c r="A41">
         <v>1030111</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="8">
         <v>111</v>
       </c>
       <c r="C41">
@@ -3958,7 +3937,7 @@
       <c r="A42">
         <v>1030112</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="8">
         <v>112</v>
       </c>
       <c r="C42">
@@ -3996,7 +3975,7 @@
       <c r="A43">
         <v>1030121</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="8">
         <v>121</v>
       </c>
       <c r="C43">
@@ -4034,7 +4013,7 @@
       <c r="A44">
         <v>1030122</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="8">
         <v>122</v>
       </c>
       <c r="C44">
@@ -4072,7 +4051,7 @@
       <c r="A45">
         <v>1030123</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="8">
         <v>123</v>
       </c>
       <c r="C45">
@@ -4110,7 +4089,7 @@
       <c r="A46">
         <v>1030124</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="8">
         <v>124</v>
       </c>
       <c r="C46">
@@ -4148,7 +4127,7 @@
       <c r="A47">
         <v>1030125</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="8">
         <v>125</v>
       </c>
       <c r="C47">
@@ -4186,7 +4165,7 @@
       <c r="A48">
         <v>1030126</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="8">
         <v>126</v>
       </c>
       <c r="C48">
@@ -4224,7 +4203,7 @@
       <c r="A49">
         <v>1030127</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="8">
         <v>127</v>
       </c>
       <c r="C49">
@@ -4262,7 +4241,7 @@
       <c r="A50">
         <v>1030128</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="8">
         <v>128</v>
       </c>
       <c r="C50">
@@ -4300,7 +4279,7 @@
       <c r="A51">
         <v>1030129</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="8">
         <v>129</v>
       </c>
       <c r="C51">
@@ -4338,7 +4317,7 @@
       <c r="A52">
         <v>1030130</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="8">
         <v>130</v>
       </c>
       <c r="C52">
@@ -4376,7 +4355,7 @@
       <c r="A53">
         <v>1030131</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="8">
         <v>131</v>
       </c>
       <c r="C53">
@@ -4414,7 +4393,7 @@
       <c r="A54">
         <v>1030132</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="8">
         <v>132</v>
       </c>
       <c r="C54">
@@ -4452,7 +4431,7 @@
       <c r="A55">
         <v>1030141</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="8">
         <v>141</v>
       </c>
       <c r="C55">
@@ -4490,7 +4469,7 @@
       <c r="A56">
         <v>1030142</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="8">
         <v>142</v>
       </c>
       <c r="C56">
@@ -4528,7 +4507,7 @@
       <c r="A57">
         <v>1030143</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="8">
         <v>143</v>
       </c>
       <c r="C57">
@@ -4566,7 +4545,7 @@
       <c r="A58">
         <v>1030144</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="8">
         <v>144</v>
       </c>
       <c r="C58">
@@ -4604,7 +4583,7 @@
       <c r="A59">
         <v>1030145</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="8">
         <v>145</v>
       </c>
       <c r="C59">
@@ -4642,7 +4621,7 @@
       <c r="A60">
         <v>1030146</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="8">
         <v>146</v>
       </c>
       <c r="C60">
@@ -4680,7 +4659,7 @@
       <c r="A61">
         <v>1030147</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="8">
         <v>147</v>
       </c>
       <c r="C61">
@@ -4718,7 +4697,7 @@
       <c r="A62">
         <v>1030148</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="8">
         <v>148</v>
       </c>
       <c r="C62">
@@ -4756,7 +4735,7 @@
       <c r="A63">
         <v>1030149</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="8">
         <v>149</v>
       </c>
       <c r="C63">
@@ -4794,7 +4773,7 @@
       <c r="A64">
         <v>1030150</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="8">
         <v>150</v>
       </c>
       <c r="C64">
@@ -4832,7 +4811,7 @@
       <c r="A65">
         <v>1030151</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="8">
         <v>151</v>
       </c>
       <c r="C65">
@@ -4870,7 +4849,7 @@
       <c r="A66">
         <v>1030152</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="8">
         <v>152</v>
       </c>
       <c r="C66">
@@ -4908,7 +4887,7 @@
       <c r="A67">
         <v>1030161</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="8">
         <v>161</v>
       </c>
       <c r="C67">
@@ -4946,7 +4925,7 @@
       <c r="A68">
         <v>1030162</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="8">
         <v>162</v>
       </c>
       <c r="C68">
@@ -4984,7 +4963,7 @@
       <c r="A69">
         <v>1030163</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="8">
         <v>163</v>
       </c>
       <c r="C69">
@@ -5022,7 +5001,7 @@
       <c r="A70">
         <v>1030164</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="8">
         <v>164</v>
       </c>
       <c r="C70">
@@ -5060,7 +5039,7 @@
       <c r="A71">
         <v>1030165</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="8">
         <v>165</v>
       </c>
       <c r="C71">
@@ -5098,7 +5077,7 @@
       <c r="A72">
         <v>1030166</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="8">
         <v>166</v>
       </c>
       <c r="C72">
@@ -5136,7 +5115,7 @@
       <c r="A73">
         <v>1030167</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73" s="8">
         <v>167</v>
       </c>
       <c r="C73">
@@ -5174,7 +5153,7 @@
       <c r="A74">
         <v>1030168</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="8">
         <v>168</v>
       </c>
       <c r="C74">
@@ -5212,7 +5191,7 @@
       <c r="A75">
         <v>1030169</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="8">
         <v>169</v>
       </c>
       <c r="C75">
@@ -5250,7 +5229,7 @@
       <c r="A76">
         <v>1030170</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="8">
         <v>170</v>
       </c>
       <c r="C76">
@@ -5288,7 +5267,7 @@
       <c r="A77">
         <v>1030171</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="8">
         <v>171</v>
       </c>
       <c r="C77">
@@ -5326,7 +5305,7 @@
       <c r="A78">
         <v>1030172</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="8">
         <v>172</v>
       </c>
       <c r="C78">
@@ -5364,7 +5343,7 @@
       <c r="A79">
         <v>1030181</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="8">
         <v>181</v>
       </c>
       <c r="C79">
@@ -5402,7 +5381,7 @@
       <c r="A80">
         <v>1030182</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="8">
         <v>182</v>
       </c>
       <c r="C80">
@@ -5440,7 +5419,7 @@
       <c r="A81">
         <v>1030183</v>
       </c>
-      <c r="B81" s="7">
+      <c r="B81" s="8">
         <v>183</v>
       </c>
       <c r="C81">
@@ -5478,7 +5457,7 @@
       <c r="A82">
         <v>1030184</v>
       </c>
-      <c r="B82" s="7">
+      <c r="B82" s="8">
         <v>184</v>
       </c>
       <c r="C82">
@@ -5516,7 +5495,7 @@
       <c r="A83">
         <v>1030185</v>
       </c>
-      <c r="B83" s="7">
+      <c r="B83" s="8">
         <v>185</v>
       </c>
       <c r="C83">
@@ -5554,7 +5533,7 @@
       <c r="A84">
         <v>1030186</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="8">
         <v>186</v>
       </c>
       <c r="C84">
@@ -5592,7 +5571,7 @@
       <c r="A85">
         <v>1030187</v>
       </c>
-      <c r="B85" s="7">
+      <c r="B85" s="8">
         <v>187</v>
       </c>
       <c r="C85">
@@ -5630,7 +5609,7 @@
       <c r="A86">
         <v>1030188</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="8">
         <v>188</v>
       </c>
       <c r="C86">
@@ -5668,7 +5647,7 @@
       <c r="A87">
         <v>1030189</v>
       </c>
-      <c r="B87" s="7">
+      <c r="B87" s="8">
         <v>189</v>
       </c>
       <c r="C87">
@@ -5706,7 +5685,7 @@
       <c r="A88">
         <v>1030190</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="8">
         <v>190</v>
       </c>
       <c r="C88">
@@ -5744,7 +5723,7 @@
       <c r="A89">
         <v>1030191</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89" s="8">
         <v>191</v>
       </c>
       <c r="C89">
@@ -5782,7 +5761,7 @@
       <c r="A90">
         <v>1030192</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="8">
         <v>192</v>
       </c>
       <c r="C90">
@@ -5820,7 +5799,7 @@
       <c r="A91">
         <v>1030201</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="8">
         <v>201</v>
       </c>
       <c r="C91">
@@ -5858,7 +5837,7 @@
       <c r="A92">
         <v>1030202</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="8">
         <v>202</v>
       </c>
       <c r="C92">
@@ -5896,7 +5875,7 @@
       <c r="A93">
         <v>1030203</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="8">
         <v>203</v>
       </c>
       <c r="C93">
@@ -5934,7 +5913,7 @@
       <c r="A94">
         <v>1030204</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="8">
         <v>204</v>
       </c>
       <c r="C94">
@@ -5972,7 +5951,7 @@
       <c r="A95">
         <v>1030205</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="8">
         <v>205</v>
       </c>
       <c r="C95">
@@ -6010,7 +5989,7 @@
       <c r="A96">
         <v>1030206</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="8">
         <v>206</v>
       </c>
       <c r="C96">
@@ -6048,7 +6027,7 @@
       <c r="A97">
         <v>1030207</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="8">
         <v>207</v>
       </c>
       <c r="C97">
@@ -6086,7 +6065,7 @@
       <c r="A98">
         <v>1030208</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="8">
         <v>208</v>
       </c>
       <c r="C98">
@@ -6124,7 +6103,7 @@
       <c r="A99">
         <v>1030209</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99" s="8">
         <v>209</v>
       </c>
       <c r="C99">
@@ -6162,7 +6141,7 @@
       <c r="A100">
         <v>1030210</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="8">
         <v>210</v>
       </c>
       <c r="C100">
@@ -6200,7 +6179,7 @@
       <c r="A101">
         <v>1030211</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="8">
         <v>211</v>
       </c>
       <c r="C101">
@@ -6238,7 +6217,7 @@
       <c r="A102">
         <v>1030212</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="8">
         <v>212</v>
       </c>
       <c r="C102">
@@ -6276,7 +6255,7 @@
       <c r="A103">
         <v>1030221</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="8">
         <v>221</v>
       </c>
       <c r="C103">
@@ -6314,7 +6293,7 @@
       <c r="A104">
         <v>1030222</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="8">
         <v>222</v>
       </c>
       <c r="C104">
@@ -6352,7 +6331,7 @@
       <c r="A105">
         <v>1030223</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="8">
         <v>223</v>
       </c>
       <c r="C105">
@@ -6390,7 +6369,7 @@
       <c r="A106">
         <v>1030224</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="8">
         <v>224</v>
       </c>
       <c r="C106">
@@ -6428,7 +6407,7 @@
       <c r="A107">
         <v>1030225</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B107" s="8">
         <v>225</v>
       </c>
       <c r="C107">
@@ -6466,7 +6445,7 @@
       <c r="A108">
         <v>1030226</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="8">
         <v>226</v>
       </c>
       <c r="C108">
@@ -6504,7 +6483,7 @@
       <c r="A109">
         <v>1030227</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="8">
         <v>227</v>
       </c>
       <c r="C109">
@@ -6542,7 +6521,7 @@
       <c r="A110">
         <v>1030228</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="8">
         <v>228</v>
       </c>
       <c r="C110">
@@ -6580,7 +6559,7 @@
       <c r="A111">
         <v>1030229</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="8">
         <v>229</v>
       </c>
       <c r="C111">
@@ -6618,7 +6597,7 @@
       <c r="A112">
         <v>1030230</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="8">
         <v>230</v>
       </c>
       <c r="C112">
@@ -6656,7 +6635,7 @@
       <c r="A113">
         <v>1030231</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="8">
         <v>231</v>
       </c>
       <c r="C113">
@@ -6694,7 +6673,7 @@
       <c r="A114">
         <v>1030232</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="8">
         <v>232</v>
       </c>
       <c r="C114">
@@ -6732,7 +6711,7 @@
       <c r="A115">
         <v>1030241</v>
       </c>
-      <c r="B115" s="7">
+      <c r="B115" s="8">
         <v>241</v>
       </c>
       <c r="C115">
@@ -6770,7 +6749,7 @@
       <c r="A116">
         <v>1030242</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="8">
         <v>242</v>
       </c>
       <c r="C116">
@@ -6808,7 +6787,7 @@
       <c r="A117">
         <v>1030243</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="8">
         <v>243</v>
       </c>
       <c r="C117">
@@ -6846,7 +6825,7 @@
       <c r="A118">
         <v>1030244</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="8">
         <v>244</v>
       </c>
       <c r="C118">
@@ -6884,7 +6863,7 @@
       <c r="A119">
         <v>1030245</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="8">
         <v>245</v>
       </c>
       <c r="C119">
@@ -6922,7 +6901,7 @@
       <c r="A120">
         <v>1030246</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="8">
         <v>246</v>
       </c>
       <c r="C120">
@@ -6960,7 +6939,7 @@
       <c r="A121">
         <v>1030247</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="8">
         <v>247</v>
       </c>
       <c r="C121">
@@ -6998,7 +6977,7 @@
       <c r="A122">
         <v>1030248</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="8">
         <v>248</v>
       </c>
       <c r="C122">
@@ -7036,7 +7015,7 @@
       <c r="A123">
         <v>1030249</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="8">
         <v>249</v>
       </c>
       <c r="C123">
@@ -7074,7 +7053,7 @@
       <c r="A124">
         <v>1030250</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="8">
         <v>250</v>
       </c>
       <c r="C124">
@@ -7112,7 +7091,7 @@
       <c r="A125">
         <v>1030251</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="8">
         <v>251</v>
       </c>
       <c r="C125">
@@ -7150,7 +7129,7 @@
       <c r="A126">
         <v>1030252</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="8">
         <v>252</v>
       </c>
       <c r="C126">
@@ -7188,13 +7167,13 @@
       <c r="A127">
         <v>1031001</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="8">
         <v>1001</v>
       </c>
       <c r="C127">
         <v>1301001</v>
       </c>
-      <c r="D127" s="7" t="s">
+      <c r="D127" s="8" t="s">
         <v>182</v>
       </c>
       <c r="E127">
@@ -7226,13 +7205,13 @@
       <c r="A128">
         <v>1031002</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="8">
         <v>1002</v>
       </c>
       <c r="C128">
         <v>1301002</v>
       </c>
-      <c r="D128" s="7" t="s">
+      <c r="D128" s="8" t="s">
         <v>184</v>
       </c>
       <c r="E128">
@@ -7264,7 +7243,7 @@
       <c r="A129">
         <v>1031201</v>
       </c>
-      <c r="B129" s="7">
+      <c r="B129" s="8">
         <v>1201</v>
       </c>
       <c r="C129">
@@ -7302,7 +7281,7 @@
       <c r="A130">
         <v>1031202</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="8">
         <v>1202</v>
       </c>
       <c r="C130">
@@ -7340,7 +7319,7 @@
       <c r="A131">
         <v>1031350</v>
       </c>
-      <c r="B131" s="7">
+      <c r="B131" s="8">
         <v>1350</v>
       </c>
       <c r="C131">
@@ -7367,7 +7346,7 @@
       <c r="J131">
         <v>201801</v>
       </c>
-      <c r="L131" s="10">
+      <c r="L131" s="3">
         <v>1005</v>
       </c>
       <c r="N131">
@@ -7378,7 +7357,7 @@
       <c r="A132">
         <v>1031351</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="8">
         <v>1351</v>
       </c>
       <c r="C132">
@@ -7405,7 +7384,7 @@
       <c r="J132">
         <v>201802</v>
       </c>
-      <c r="L132" s="10">
+      <c r="L132" s="3">
         <v>1006</v>
       </c>
       <c r="N132">
@@ -7416,7 +7395,7 @@
       <c r="A133">
         <v>1021401</v>
       </c>
-      <c r="B133" s="7">
+      <c r="B133" s="8">
         <v>1401</v>
       </c>
       <c r="C133">
@@ -7454,7 +7433,7 @@
       <c r="A134">
         <v>1021402</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="8">
         <v>1402</v>
       </c>
       <c r="C134">
@@ -7476,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="I134" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J134">
         <v>2021402</v>
@@ -7488,56 +7467,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" ht="23.1" customHeight="1" spans="1:17">
-      <c r="A135">
-        <v>1031601</v>
-      </c>
-      <c r="B135" s="7">
-        <v>1601</v>
-      </c>
-      <c r="C135">
-        <v>1301601</v>
-      </c>
-      <c r="D135" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E135">
-        <v>3</v>
-      </c>
-      <c r="F135" t="s">
-        <v>54</v>
-      </c>
-      <c r="G135">
-        <v>1</v>
-      </c>
-      <c r="H135">
+    <row r="135" s="3" customFormat="1" ht="23.1" customHeight="1" spans="1:17">
+      <c r="A135" s="3">
+        <v>1031600</v>
+      </c>
+      <c r="B135" s="12">
+        <v>1600</v>
+      </c>
+      <c r="C135" s="3">
+        <v>1301600</v>
+      </c>
+      <c r="D135" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E135" s="3">
+        <v>3</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G135" s="3">
+        <v>1</v>
+      </c>
+      <c r="H135" s="3">
         <v>1</v>
       </c>
       <c r="I135" t="s">
-        <v>199</v>
-      </c>
-      <c r="J135">
-        <v>2031601</v>
-      </c>
-      <c r="L135">
-        <v>3002</v>
-      </c>
-      <c r="N135">
+        <v>195</v>
+      </c>
+      <c r="J135" s="3">
+        <v>2031600</v>
+      </c>
+      <c r="L135" s="3">
+        <v>3001</v>
+      </c>
+      <c r="N135" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="136" ht="23.1" customHeight="1" spans="1:17">
       <c r="A136">
-        <v>1031602</v>
-      </c>
-      <c r="B136" s="7">
-        <v>1602</v>
+        <v>1031601</v>
+      </c>
+      <c r="B136" s="8">
+        <v>1601</v>
       </c>
       <c r="C136">
-        <v>1301602</v>
-      </c>
-      <c r="D136" s="12" t="s">
-        <v>200</v>
+        <v>1301601</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>198</v>
       </c>
       <c r="E136">
         <v>3</v>
@@ -7552,13 +7531,13 @@
         <v>1</v>
       </c>
       <c r="I136" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="J136">
-        <v>2031602</v>
+        <v>2031601</v>
       </c>
       <c r="L136">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="N136">
         <v>1</v>
@@ -7566,16 +7545,16 @@
     </row>
     <row r="137" ht="23.1" customHeight="1" spans="1:17">
       <c r="A137">
-        <v>1031801</v>
-      </c>
-      <c r="B137" s="7">
-        <v>1801</v>
+        <v>1031602</v>
+      </c>
+      <c r="B137" s="8">
+        <v>1602</v>
       </c>
       <c r="C137">
-        <v>1301801</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>202</v>
+        <v>1301602</v>
+      </c>
+      <c r="D137" s="14" t="s">
+        <v>199</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -7590,13 +7569,13 @@
         <v>1</v>
       </c>
       <c r="I137" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="J137">
-        <v>2031801</v>
+        <v>2031602</v>
       </c>
       <c r="L137">
-        <v>4002</v>
+        <v>3003</v>
       </c>
       <c r="N137">
         <v>1</v>
@@ -7604,16 +7583,16 @@
     </row>
     <row r="138" ht="23.1" customHeight="1" spans="1:17">
       <c r="A138">
-        <v>1031802</v>
-      </c>
-      <c r="B138" s="7">
-        <v>1802</v>
+        <v>1031801</v>
+      </c>
+      <c r="B138" s="8">
+        <v>1801</v>
       </c>
       <c r="C138">
-        <v>1301802</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>204</v>
+        <v>1301801</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="E138">
         <v>3</v>
@@ -7628,13 +7607,13 @@
         <v>1</v>
       </c>
       <c r="I138" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="J138">
-        <v>2031802</v>
+        <v>2031801</v>
       </c>
       <c r="L138">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="N138">
         <v>1</v>
@@ -7642,16 +7621,16 @@
     </row>
     <row r="139" ht="23.1" customHeight="1" spans="1:17">
       <c r="A139">
-        <v>1032001</v>
-      </c>
-      <c r="B139" s="7">
-        <v>2001</v>
+        <v>1031802</v>
+      </c>
+      <c r="B139" s="8">
+        <v>1802</v>
       </c>
       <c r="C139">
-        <v>1302001</v>
-      </c>
-      <c r="D139" s="14" t="s">
-        <v>206</v>
+        <v>1301802</v>
+      </c>
+      <c r="D139" s="15" t="s">
+        <v>201</v>
       </c>
       <c r="E139">
         <v>3</v>
@@ -7666,13 +7645,13 @@
         <v>1</v>
       </c>
       <c r="I139" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="J139">
-        <v>2032001</v>
+        <v>2031802</v>
       </c>
       <c r="L139">
-        <v>5002</v>
+        <v>4003</v>
       </c>
       <c r="N139">
         <v>1</v>
@@ -7680,16 +7659,16 @@
     </row>
     <row r="140" ht="23.1" customHeight="1" spans="1:17">
       <c r="A140">
-        <v>1032002</v>
-      </c>
-      <c r="B140" s="7">
-        <v>2002</v>
+        <v>1032001</v>
+      </c>
+      <c r="B140" s="8">
+        <v>2001</v>
       </c>
       <c r="C140">
-        <v>1302002</v>
-      </c>
-      <c r="D140" s="14" t="s">
-        <v>208</v>
+        <v>1302001</v>
+      </c>
+      <c r="D140" s="16" t="s">
+        <v>202</v>
       </c>
       <c r="E140">
         <v>3</v>
@@ -7704,13 +7683,13 @@
         <v>1</v>
       </c>
       <c r="I140" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="J140">
-        <v>2032002</v>
+        <v>2032001</v>
       </c>
       <c r="L140">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="N140">
         <v>1</v>
@@ -7718,16 +7697,16 @@
     </row>
     <row r="141" ht="23.1" customHeight="1" spans="1:17">
       <c r="A141">
-        <v>1032201</v>
-      </c>
-      <c r="B141" s="7">
-        <v>2201</v>
+        <v>1032002</v>
+      </c>
+      <c r="B141" s="8">
+        <v>2002</v>
       </c>
       <c r="C141">
-        <v>1302201</v>
-      </c>
-      <c r="D141" s="15" t="s">
-        <v>210</v>
+        <v>1302002</v>
+      </c>
+      <c r="D141" s="16" t="s">
+        <v>203</v>
       </c>
       <c r="E141">
         <v>3</v>
@@ -7742,13 +7721,13 @@
         <v>1</v>
       </c>
       <c r="I141" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="J141">
-        <v>2032201</v>
+        <v>2032002</v>
       </c>
       <c r="L141">
-        <v>6002</v>
+        <v>5003</v>
       </c>
       <c r="N141">
         <v>1</v>
@@ -7756,95 +7735,92 @@
     </row>
     <row r="142" ht="23.1" customHeight="1" spans="1:17">
       <c r="A142">
+        <v>1032201</v>
+      </c>
+      <c r="B142" s="8">
+        <v>2201</v>
+      </c>
+      <c r="C142">
+        <v>1302201</v>
+      </c>
+      <c r="D142" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E142">
+        <v>3</v>
+      </c>
+      <c r="F142" t="s">
+        <v>54</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="I142" t="s">
+        <v>195</v>
+      </c>
+      <c r="J142">
+        <v>2032201</v>
+      </c>
+      <c r="L142">
+        <v>6002</v>
+      </c>
+      <c r="N142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" ht="23.1" customHeight="1" spans="1:17">
+      <c r="A143">
         <v>1032202</v>
       </c>
-      <c r="B142" s="7">
+      <c r="B143" s="8">
         <v>2202</v>
       </c>
-      <c r="C142">
+      <c r="C143">
         <v>1302202</v>
       </c>
-      <c r="D142" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="E142">
-        <v>3</v>
-      </c>
-      <c r="F142" t="s">
-        <v>54</v>
-      </c>
-      <c r="G142">
-        <v>1</v>
-      </c>
-      <c r="H142">
-        <v>1</v>
-      </c>
-      <c r="I142" t="s">
-        <v>213</v>
-      </c>
-      <c r="J142">
+      <c r="D143" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E143">
+        <v>3</v>
+      </c>
+      <c r="F143" t="s">
+        <v>54</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143" t="s">
+        <v>195</v>
+      </c>
+      <c r="J143">
         <v>2032202</v>
       </c>
-      <c r="L142">
+      <c r="L143">
         <v>6003</v>
       </c>
-      <c r="N142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1" spans="1:17">
-      <c r="A143">
-        <v>1022501</v>
-      </c>
-      <c r="B143">
-        <v>2501</v>
-      </c>
-      <c r="C143">
-        <v>1202501</v>
-      </c>
-      <c r="D143" t="s">
-        <v>214</v>
-      </c>
-      <c r="E143">
-        <v>2</v>
-      </c>
-      <c r="F143" t="s">
-        <v>54</v>
-      </c>
-      <c r="G143">
-        <v>1</v>
-      </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
-      <c r="I143" t="s">
-        <v>215</v>
-      </c>
-      <c r="J143">
-        <v>2022501</v>
-      </c>
-      <c r="K143" t="s">
-        <v>216</v>
-      </c>
       <c r="N143">
-        <v>999</v>
-      </c>
-      <c r="Q143">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1" spans="1:17">
       <c r="A144">
-        <v>1022502</v>
+        <v>1022501</v>
       </c>
       <c r="B144">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C144">
-        <v>1202502</v>
+        <v>1202501</v>
       </c>
       <c r="D144" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E144">
         <v>2</v>
@@ -7859,33 +7835,33 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J144">
-        <v>2022502</v>
+        <v>2022501</v>
       </c>
       <c r="K144" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="N144">
         <v>999</v>
       </c>
       <c r="Q144">
-        <v>0.99</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1" spans="1:17">
       <c r="A145">
-        <v>1022503</v>
+        <v>1022502</v>
       </c>
       <c r="B145">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="C145">
-        <v>1202503</v>
+        <v>1202502</v>
       </c>
       <c r="D145" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E145">
         <v>2</v>
@@ -7900,13 +7876,13 @@
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="J145">
-        <v>2022503</v>
+        <v>2022502</v>
       </c>
       <c r="K145" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="N145">
         <v>999</v>
@@ -7917,16 +7893,16 @@
     </row>
     <row r="146" ht="18" customHeight="1" spans="1:17">
       <c r="A146">
-        <v>1022504</v>
+        <v>1022503</v>
       </c>
       <c r="B146">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="C146">
-        <v>1202504</v>
+        <v>1202503</v>
       </c>
       <c r="D146" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="E146">
         <v>2</v>
@@ -7941,28 +7917,33 @@
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="J146">
-        <v>2022504</v>
+        <v>2022503</v>
       </c>
       <c r="K146" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="N146">
-        <v>999999999</v>
-      </c>
-    </row>
-    <row r="147" ht="21" customHeight="1" spans="1:17">
+        <v>999</v>
+      </c>
+      <c r="Q146">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1" spans="1:17">
       <c r="A147">
-        <v>1023001</v>
-      </c>
-      <c r="B147" s="7"/>
+        <v>1022504</v>
+      </c>
+      <c r="B147">
+        <v>2504</v>
+      </c>
       <c r="C147">
-        <v>1023001</v>
+        <v>1202504</v>
       </c>
       <c r="D147" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="E147">
         <v>2</v>
@@ -7971,37 +7952,34 @@
         <v>54</v>
       </c>
       <c r="G147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="J147">
-        <v>2023001</v>
+        <v>2022504</v>
       </c>
       <c r="K147" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="N147">
-        <v>999</v>
-      </c>
-      <c r="Q147">
-        <v>0.2</v>
+        <v>999999999</v>
       </c>
     </row>
     <row r="148" ht="21" customHeight="1" spans="1:17">
       <c r="A148">
-        <v>1023002</v>
-      </c>
-      <c r="B148" s="7"/>
+        <v>1023001</v>
+      </c>
+      <c r="B148" s="8"/>
       <c r="C148">
-        <v>1023002</v>
+        <v>1023001</v>
       </c>
       <c r="D148" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E148">
         <v>2</v>
@@ -8010,37 +7988,37 @@
         <v>54</v>
       </c>
       <c r="G148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="J148">
-        <v>2023002</v>
+        <v>2023001</v>
       </c>
       <c r="K148" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="N148">
         <v>999</v>
       </c>
       <c r="Q148">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="149" ht="21" customHeight="1" spans="1:17">
       <c r="A149">
-        <v>1023003</v>
-      </c>
-      <c r="B149" s="7"/>
+        <v>1023002</v>
+      </c>
+      <c r="B149" s="8"/>
       <c r="C149">
-        <v>1023003</v>
+        <v>1023002</v>
       </c>
       <c r="D149" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E149">
         <v>2</v>
@@ -8049,37 +8027,37 @@
         <v>54</v>
       </c>
       <c r="G149">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="J149">
-        <v>2023003</v>
+        <v>2023002</v>
       </c>
       <c r="K149" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="N149">
         <v>999</v>
       </c>
       <c r="Q149">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="150" ht="21" customHeight="1" spans="1:17">
       <c r="A150">
-        <v>1023004</v>
-      </c>
-      <c r="B150" s="7"/>
+        <v>1023003</v>
+      </c>
+      <c r="B150" s="8"/>
       <c r="C150">
-        <v>1023004</v>
+        <v>1023003</v>
       </c>
       <c r="D150" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E150">
         <v>2</v>
@@ -8088,37 +8066,37 @@
         <v>54</v>
       </c>
       <c r="G150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="J150">
-        <v>2023004</v>
+        <v>2023003</v>
       </c>
       <c r="K150" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="N150">
         <v>999</v>
       </c>
       <c r="Q150">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="151" ht="21" customHeight="1" spans="1:17">
       <c r="A151">
-        <v>1023005</v>
-      </c>
-      <c r="B151" s="7"/>
+        <v>1023004</v>
+      </c>
+      <c r="B151" s="8"/>
       <c r="C151">
-        <v>1023005</v>
+        <v>1023004</v>
       </c>
       <c r="D151" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E151">
         <v>2</v>
@@ -8127,37 +8105,37 @@
         <v>54</v>
       </c>
       <c r="G151">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="J151">
-        <v>2023005</v>
+        <v>2023004</v>
       </c>
       <c r="K151" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="N151">
         <v>999</v>
       </c>
       <c r="Q151">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="152" ht="21" customHeight="1" spans="1:17">
       <c r="A152">
-        <v>1023101</v>
-      </c>
-      <c r="B152" s="7"/>
+        <v>1023005</v>
+      </c>
+      <c r="B152" s="8"/>
       <c r="C152">
-        <v>1023101</v>
+        <v>1023005</v>
       </c>
       <c r="D152" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -8166,37 +8144,37 @@
         <v>54</v>
       </c>
       <c r="G152">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H152">
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="J152">
-        <v>2023101</v>
+        <v>2023005</v>
       </c>
       <c r="K152" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="N152">
         <v>999</v>
       </c>
       <c r="Q152">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="153" ht="21" customHeight="1" spans="1:17">
       <c r="A153">
-        <v>1023102</v>
-      </c>
-      <c r="B153" s="7"/>
+        <v>1023101</v>
+      </c>
+      <c r="B153" s="8"/>
       <c r="C153">
-        <v>1023102</v>
+        <v>1023101</v>
       </c>
       <c r="D153" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -8205,37 +8183,37 @@
         <v>54</v>
       </c>
       <c r="G153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H153">
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="J153">
-        <v>2023102</v>
+        <v>2023101</v>
       </c>
       <c r="K153" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N153">
         <v>999</v>
       </c>
       <c r="Q153">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="154" ht="21" customHeight="1" spans="1:17">
       <c r="A154">
-        <v>1023103</v>
-      </c>
-      <c r="B154" s="7"/>
+        <v>1023102</v>
+      </c>
+      <c r="B154" s="8"/>
       <c r="C154">
-        <v>1023103</v>
+        <v>1023102</v>
       </c>
       <c r="D154" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -8244,37 +8222,37 @@
         <v>54</v>
       </c>
       <c r="G154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H154">
         <v>0</v>
       </c>
       <c r="I154" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="J154">
-        <v>2023103</v>
+        <v>2023102</v>
       </c>
       <c r="K154" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N154">
         <v>999</v>
       </c>
       <c r="Q154">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="155" ht="21" customHeight="1" spans="1:17">
       <c r="A155">
-        <v>1023104</v>
-      </c>
-      <c r="B155" s="7"/>
+        <v>1023103</v>
+      </c>
+      <c r="B155" s="8"/>
       <c r="C155">
-        <v>1023104</v>
+        <v>1023103</v>
       </c>
       <c r="D155" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -8283,37 +8261,37 @@
         <v>54</v>
       </c>
       <c r="G155">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="J155">
-        <v>2023104</v>
+        <v>2023103</v>
       </c>
       <c r="K155" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N155">
         <v>999</v>
       </c>
       <c r="Q155">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1" spans="1:17">
       <c r="A156">
-        <v>1023105</v>
-      </c>
-      <c r="B156" s="7"/>
+        <v>1023104</v>
+      </c>
+      <c r="B156" s="8"/>
       <c r="C156">
-        <v>1023105</v>
+        <v>1023104</v>
       </c>
       <c r="D156" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="E156">
         <v>2</v>
@@ -8322,37 +8300,37 @@
         <v>54</v>
       </c>
       <c r="G156">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H156">
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="J156">
-        <v>2023105</v>
+        <v>2023104</v>
       </c>
       <c r="K156" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N156">
         <v>999</v>
       </c>
       <c r="Q156">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="157" ht="21" customHeight="1" spans="1:17">
       <c r="A157">
-        <v>1023201</v>
-      </c>
-      <c r="B157" s="7"/>
+        <v>1023105</v>
+      </c>
+      <c r="B157" s="8"/>
       <c r="C157">
-        <v>1023201</v>
+        <v>1023105</v>
       </c>
       <c r="D157" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -8361,37 +8339,37 @@
         <v>54</v>
       </c>
       <c r="G157">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H157">
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="J157">
-        <v>2023201</v>
+        <v>2023105</v>
       </c>
       <c r="K157" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="N157">
         <v>999</v>
       </c>
       <c r="Q157">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="158" ht="21" customHeight="1" spans="1:17">
       <c r="A158">
-        <v>1023202</v>
-      </c>
-      <c r="B158" s="7"/>
+        <v>1023201</v>
+      </c>
+      <c r="B158" s="8"/>
       <c r="C158">
-        <v>1023202</v>
+        <v>1023201</v>
       </c>
       <c r="D158" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E158">
         <v>2</v>
@@ -8400,37 +8378,37 @@
         <v>54</v>
       </c>
       <c r="G158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H158">
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="J158">
-        <v>2023202</v>
+        <v>2023201</v>
       </c>
       <c r="K158" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="N158">
         <v>999</v>
       </c>
       <c r="Q158">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="159" ht="21" customHeight="1" spans="1:17">
       <c r="A159">
-        <v>1023203</v>
-      </c>
-      <c r="B159" s="7"/>
+        <v>1023202</v>
+      </c>
+      <c r="B159" s="8"/>
       <c r="C159">
-        <v>1023203</v>
+        <v>1023202</v>
       </c>
       <c r="D159" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -8439,37 +8417,37 @@
         <v>54</v>
       </c>
       <c r="G159">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H159">
         <v>0</v>
       </c>
       <c r="I159" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="J159">
-        <v>2023203</v>
+        <v>2023202</v>
       </c>
       <c r="K159" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="N159">
         <v>999</v>
       </c>
       <c r="Q159">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1" spans="1:17">
       <c r="A160">
-        <v>1023204</v>
-      </c>
-      <c r="B160" s="7"/>
+        <v>1023203</v>
+      </c>
+      <c r="B160" s="8"/>
       <c r="C160">
-        <v>1023204</v>
+        <v>1023203</v>
       </c>
       <c r="D160" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="E160">
         <v>2</v>
@@ -8478,37 +8456,37 @@
         <v>54</v>
       </c>
       <c r="G160">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H160">
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="J160">
-        <v>2023204</v>
+        <v>2023203</v>
       </c>
       <c r="K160" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="N160">
         <v>999</v>
       </c>
       <c r="Q160">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="161" ht="21" customHeight="1" spans="1:17">
       <c r="A161">
-        <v>1023205</v>
-      </c>
-      <c r="B161" s="7"/>
+        <v>1023204</v>
+      </c>
+      <c r="B161" s="8"/>
       <c r="C161">
-        <v>1023205</v>
+        <v>1023204</v>
       </c>
       <c r="D161" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -8517,37 +8495,37 @@
         <v>54</v>
       </c>
       <c r="G161">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H161">
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="J161">
-        <v>2023205</v>
+        <v>2023204</v>
       </c>
       <c r="K161" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="N161">
         <v>999</v>
       </c>
       <c r="Q161">
-        <v>14.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="162" ht="21" customHeight="1" spans="1:17">
       <c r="A162">
-        <v>1023301</v>
-      </c>
-      <c r="B162" s="7"/>
+        <v>1023205</v>
+      </c>
+      <c r="B162" s="8"/>
       <c r="C162">
-        <v>1023301</v>
+        <v>1023205</v>
       </c>
       <c r="D162" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -8556,37 +8534,37 @@
         <v>54</v>
       </c>
       <c r="G162">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H162">
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="J162">
-        <v>2023301</v>
+        <v>2023205</v>
       </c>
       <c r="K162" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="N162">
         <v>999</v>
       </c>
       <c r="Q162">
-        <v>4.8</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="163" ht="21" customHeight="1" spans="1:17">
       <c r="A163">
-        <v>1023302</v>
-      </c>
-      <c r="B163" s="7"/>
+        <v>1023301</v>
+      </c>
+      <c r="B163" s="8"/>
       <c r="C163">
-        <v>1023302</v>
+        <v>1023301</v>
       </c>
       <c r="D163" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E163">
         <v>2</v>
@@ -8595,37 +8573,37 @@
         <v>54</v>
       </c>
       <c r="G163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H163">
         <v>0</v>
       </c>
       <c r="I163" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="J163">
-        <v>2023302</v>
+        <v>2023301</v>
       </c>
       <c r="K163" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="N163">
         <v>999</v>
       </c>
       <c r="Q163">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1" spans="1:17">
       <c r="A164">
-        <v>1023303</v>
-      </c>
-      <c r="B164" s="7"/>
+        <v>1023302</v>
+      </c>
+      <c r="B164" s="8"/>
       <c r="C164">
-        <v>1023303</v>
+        <v>1023302</v>
       </c>
       <c r="D164" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -8634,37 +8612,37 @@
         <v>54</v>
       </c>
       <c r="G164">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H164">
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="J164">
-        <v>2023303</v>
+        <v>2023302</v>
       </c>
       <c r="K164" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="N164">
         <v>999</v>
       </c>
       <c r="Q164">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="165" ht="21" customHeight="1" spans="1:17">
       <c r="A165">
-        <v>1023304</v>
-      </c>
-      <c r="B165" s="7"/>
+        <v>1023303</v>
+      </c>
+      <c r="B165" s="8"/>
       <c r="C165">
-        <v>1023304</v>
+        <v>1023303</v>
       </c>
       <c r="D165" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="E165">
         <v>2</v>
@@ -8673,37 +8651,37 @@
         <v>54</v>
       </c>
       <c r="G165">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H165">
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="J165">
-        <v>2023304</v>
+        <v>2023303</v>
       </c>
       <c r="K165" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="N165">
         <v>999</v>
       </c>
       <c r="Q165">
-        <v>14.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1" spans="1:17">
       <c r="A166">
-        <v>1023305</v>
-      </c>
-      <c r="B166" s="7"/>
+        <v>1023304</v>
+      </c>
+      <c r="B166" s="8"/>
       <c r="C166">
-        <v>1023305</v>
+        <v>1023304</v>
       </c>
       <c r="D166" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -8712,37 +8690,37 @@
         <v>54</v>
       </c>
       <c r="G166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H166">
         <v>0</v>
       </c>
       <c r="I166" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="J166">
-        <v>2023305</v>
+        <v>2023304</v>
       </c>
       <c r="K166" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="N166">
         <v>999</v>
       </c>
       <c r="Q166">
-        <v>28.8</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1" spans="1:17">
       <c r="A167">
-        <v>1023401</v>
-      </c>
-      <c r="B167" s="7"/>
+        <v>1023305</v>
+      </c>
+      <c r="B167" s="8"/>
       <c r="C167">
-        <v>1023401</v>
+        <v>1023305</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="E167">
         <v>2</v>
@@ -8751,37 +8729,37 @@
         <v>54</v>
       </c>
       <c r="G167">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H167">
         <v>0</v>
       </c>
       <c r="I167" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="J167">
-        <v>2023401</v>
+        <v>2023305</v>
       </c>
       <c r="K167" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="N167">
         <v>999</v>
       </c>
       <c r="Q167">
-        <v>9.6</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1" spans="1:17">
       <c r="A168">
-        <v>1023402</v>
-      </c>
-      <c r="B168" s="7"/>
+        <v>1023401</v>
+      </c>
+      <c r="B168" s="8"/>
       <c r="C168">
-        <v>1023402</v>
+        <v>1023401</v>
       </c>
       <c r="D168" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="E168">
         <v>2</v>
@@ -8790,37 +8768,37 @@
         <v>54</v>
       </c>
       <c r="G168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H168">
         <v>0</v>
       </c>
       <c r="I168" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="J168">
-        <v>2023402</v>
+        <v>2023401</v>
       </c>
       <c r="K168" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="N168">
         <v>999</v>
       </c>
       <c r="Q168">
-        <v>14.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1" spans="1:17">
       <c r="A169">
-        <v>1023403</v>
-      </c>
-      <c r="B169" s="7"/>
+        <v>1023402</v>
+      </c>
+      <c r="B169" s="8"/>
       <c r="C169">
-        <v>1023403</v>
+        <v>1023402</v>
       </c>
       <c r="D169" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -8829,37 +8807,37 @@
         <v>54</v>
       </c>
       <c r="G169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H169">
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="J169">
-        <v>2023403</v>
+        <v>2023402</v>
       </c>
       <c r="K169" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="N169">
         <v>999</v>
       </c>
       <c r="Q169">
-        <v>19.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1" spans="1:17">
       <c r="A170">
-        <v>1023404</v>
-      </c>
-      <c r="B170" s="7"/>
+        <v>1023403</v>
+      </c>
+      <c r="B170" s="8"/>
       <c r="C170">
-        <v>1023404</v>
+        <v>1023403</v>
       </c>
       <c r="D170" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="E170">
         <v>2</v>
@@ -8868,37 +8846,37 @@
         <v>54</v>
       </c>
       <c r="G170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H170">
         <v>0</v>
       </c>
       <c r="I170" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="J170">
-        <v>2023404</v>
+        <v>2023403</v>
       </c>
       <c r="K170" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="N170">
         <v>999</v>
       </c>
       <c r="Q170">
-        <v>28.8</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="171" ht="21" customHeight="1" spans="1:17">
       <c r="A171">
-        <v>1023405</v>
-      </c>
-      <c r="B171" s="7"/>
+        <v>1023404</v>
+      </c>
+      <c r="B171" s="8"/>
       <c r="C171">
-        <v>1023405</v>
+        <v>1023404</v>
       </c>
       <c r="D171" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -8907,107 +8885,146 @@
         <v>54</v>
       </c>
       <c r="G171">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H171">
         <v>0</v>
       </c>
       <c r="I171" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="J171">
-        <v>2023405</v>
+        <v>2023404</v>
       </c>
       <c r="K171" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="N171">
         <v>999</v>
       </c>
       <c r="Q171">
-        <v>57.6</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="172" ht="21" customHeight="1" spans="1:17">
       <c r="A172">
-        <v>1990000</v>
-      </c>
-      <c r="B172" s="7">
-        <v>0</v>
-      </c>
+        <v>1023405</v>
+      </c>
+      <c r="B172" s="8"/>
       <c r="C172">
-        <v>1990000</v>
+        <v>1023405</v>
       </c>
       <c r="D172" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="E172">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="F172" t="s">
-        <v>281</v>
+        <v>54</v>
       </c>
       <c r="G172">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="J172">
+        <v>2023405</v>
+      </c>
+      <c r="K172" t="s">
+        <v>262</v>
+      </c>
+      <c r="N172">
+        <v>999</v>
+      </c>
+      <c r="Q172">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="173" ht="21" customHeight="1" spans="1:17">
+      <c r="A173">
+        <v>1990000</v>
+      </c>
+      <c r="B173" s="8">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>1990000</v>
+      </c>
+      <c r="D173" t="s">
+        <v>271</v>
+      </c>
+      <c r="E173">
+        <v>99</v>
+      </c>
+      <c r="F173" t="s">
+        <v>272</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173" t="s">
+        <v>273</v>
+      </c>
+      <c r="J173">
         <v>2990000</v>
       </c>
-      <c r="K172" t="s">
-        <v>283</v>
-      </c>
-      <c r="N172">
+      <c r="K173" t="s">
+        <v>274</v>
+      </c>
+      <c r="N173">
         <v>-1</v>
       </c>
-      <c r="Q172">
+      <c r="Q173">
         <f>1/700000</f>
         <v>1.42857142857143e-6</v>
       </c>
     </row>
-    <row r="173" ht="21" customHeight="1" spans="1:17">
-      <c r="A173">
+    <row r="174" ht="21" customHeight="1" spans="1:17">
+      <c r="A174">
         <v>1980000</v>
       </c>
-      <c r="B173" s="7">
+      <c r="B174" s="8">
         <v>0</v>
       </c>
-      <c r="C173">
+      <c r="C174">
         <v>1980000</v>
       </c>
-      <c r="D173" t="s">
-        <v>284</v>
-      </c>
-      <c r="E173">
+      <c r="D174" t="s">
+        <v>275</v>
+      </c>
+      <c r="E174">
         <v>98</v>
       </c>
-      <c r="F173" t="s">
-        <v>281</v>
-      </c>
-      <c r="G173">
-        <v>1</v>
-      </c>
-      <c r="H173">
+      <c r="F174" t="s">
+        <v>272</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+      <c r="H174">
         <v>0</v>
       </c>
-      <c r="I173" t="s">
-        <v>285</v>
-      </c>
-      <c r="J173">
+      <c r="I174" t="s">
+        <v>276</v>
+      </c>
+      <c r="J174">
         <v>2980000</v>
       </c>
-      <c r="K173" t="s">
-        <v>286</v>
-      </c>
-      <c r="N173">
+      <c r="K174" t="s">
+        <v>277</v>
+      </c>
+      <c r="N174">
         <v>-1</v>
       </c>
-      <c r="Q173">
+      <c r="Q174">
         <f>1/100</f>
         <v>0.01</v>
       </c>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="287">
   <si>
     <t>道具ID</t>
   </si>
@@ -802,28 +802,55 @@
     <t>头衔1</t>
   </si>
   <si>
+    <t>daoju1_8.png</t>
+  </si>
+  <si>
     <t>头衔2</t>
   </si>
   <si>
+    <t>daoju_9.png</t>
+  </si>
+  <si>
     <t>头衔3</t>
   </si>
   <si>
+    <t>daoju1_7.png</t>
+  </si>
+  <si>
     <t>筹码2</t>
   </si>
   <si>
+    <t>daoju1_1.png</t>
+  </si>
+  <si>
     <t>筹码3</t>
   </si>
   <si>
+    <t>daoju1_2.png</t>
+  </si>
+  <si>
     <t>牌背2</t>
   </si>
   <si>
+    <t>daoju1_3.png</t>
+  </si>
+  <si>
     <t>牌背3</t>
   </si>
   <si>
+    <t>daoju1_4.png</t>
+  </si>
+  <si>
     <t>大厅背景2</t>
   </si>
   <si>
+    <t>daoju1_5.png</t>
+  </si>
+  <si>
     <t>大厅背景3</t>
+  </si>
+  <si>
+    <t>daoju1_6.png</t>
   </si>
   <si>
     <t>祈福卡</t>
@@ -7493,7 +7520,7 @@
         <v>1</v>
       </c>
       <c r="I135" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J135" s="3">
         <v>2031600</v>
@@ -7516,7 +7543,7 @@
         <v>1301601</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E136">
         <v>3</v>
@@ -7531,7 +7558,7 @@
         <v>1</v>
       </c>
       <c r="I136" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J136">
         <v>2031601</v>
@@ -7554,7 +7581,7 @@
         <v>1301602</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -7569,7 +7596,7 @@
         <v>1</v>
       </c>
       <c r="I137" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="J137">
         <v>2031602</v>
@@ -7592,7 +7619,7 @@
         <v>1301801</v>
       </c>
       <c r="D138" s="15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E138">
         <v>3</v>
@@ -7607,7 +7634,7 @@
         <v>1</v>
       </c>
       <c r="I138" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="J138">
         <v>2031801</v>
@@ -7630,7 +7657,7 @@
         <v>1301802</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E139">
         <v>3</v>
@@ -7645,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="I139" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="J139">
         <v>2031802</v>
@@ -7668,7 +7695,7 @@
         <v>1302001</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E140">
         <v>3</v>
@@ -7683,7 +7710,7 @@
         <v>1</v>
       </c>
       <c r="I140" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="J140">
         <v>2032001</v>
@@ -7706,7 +7733,7 @@
         <v>1302002</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E141">
         <v>3</v>
@@ -7721,7 +7748,7 @@
         <v>1</v>
       </c>
       <c r="I141" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="J141">
         <v>2032002</v>
@@ -7744,7 +7771,7 @@
         <v>1302201</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E142">
         <v>3</v>
@@ -7759,7 +7786,7 @@
         <v>1</v>
       </c>
       <c r="I142" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="J142">
         <v>2032201</v>
@@ -7782,7 +7809,7 @@
         <v>1302202</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -7797,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="I143" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="J143">
         <v>2032202</v>
@@ -7820,7 +7847,7 @@
         <v>1202501</v>
       </c>
       <c r="D144" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="E144">
         <v>2</v>
@@ -7835,13 +7862,13 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="J144">
         <v>2022501</v>
       </c>
       <c r="K144" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="N144">
         <v>999</v>
@@ -7861,7 +7888,7 @@
         <v>1202502</v>
       </c>
       <c r="D145" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E145">
         <v>2</v>
@@ -7876,13 +7903,13 @@
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="J145">
         <v>2022502</v>
       </c>
       <c r="K145" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="N145">
         <v>999</v>
@@ -7902,7 +7929,7 @@
         <v>1202503</v>
       </c>
       <c r="D146" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E146">
         <v>2</v>
@@ -7923,7 +7950,7 @@
         <v>2022503</v>
       </c>
       <c r="K146" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="N146">
         <v>999</v>
@@ -7943,7 +7970,7 @@
         <v>1202504</v>
       </c>
       <c r="D147" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E147">
         <v>2</v>
@@ -7958,13 +7985,13 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="J147">
         <v>2022504</v>
       </c>
       <c r="K147" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="N147">
         <v>999999999</v>
@@ -7979,7 +8006,7 @@
         <v>1023001</v>
       </c>
       <c r="D148" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E148">
         <v>2</v>
@@ -7994,13 +8021,13 @@
         <v>0</v>
       </c>
       <c r="I148" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J148">
         <v>2023001</v>
       </c>
       <c r="K148" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="N148">
         <v>999</v>
@@ -8018,7 +8045,7 @@
         <v>1023002</v>
       </c>
       <c r="D149" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E149">
         <v>2</v>
@@ -8033,13 +8060,13 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="J149">
         <v>2023002</v>
       </c>
       <c r="K149" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="N149">
         <v>999</v>
@@ -8057,7 +8084,7 @@
         <v>1023003</v>
       </c>
       <c r="D150" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E150">
         <v>2</v>
@@ -8072,13 +8099,13 @@
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="J150">
         <v>2023003</v>
       </c>
       <c r="K150" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="N150">
         <v>999</v>
@@ -8096,7 +8123,7 @@
         <v>1023004</v>
       </c>
       <c r="D151" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="E151">
         <v>2</v>
@@ -8111,13 +8138,13 @@
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="J151">
         <v>2023004</v>
       </c>
       <c r="K151" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="N151">
         <v>999</v>
@@ -8135,7 +8162,7 @@
         <v>1023005</v>
       </c>
       <c r="D152" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -8150,13 +8177,13 @@
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="J152">
         <v>2023005</v>
       </c>
       <c r="K152" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="N152">
         <v>999</v>
@@ -8174,7 +8201,7 @@
         <v>1023101</v>
       </c>
       <c r="D153" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -8189,13 +8216,13 @@
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="J153">
         <v>2023101</v>
       </c>
       <c r="K153" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N153">
         <v>999</v>
@@ -8213,7 +8240,7 @@
         <v>1023102</v>
       </c>
       <c r="D154" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -8228,13 +8255,13 @@
         <v>0</v>
       </c>
       <c r="I154" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="J154">
         <v>2023102</v>
       </c>
       <c r="K154" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N154">
         <v>999</v>
@@ -8252,7 +8279,7 @@
         <v>1023103</v>
       </c>
       <c r="D155" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -8267,13 +8294,13 @@
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="J155">
         <v>2023103</v>
       </c>
       <c r="K155" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N155">
         <v>999</v>
@@ -8291,7 +8318,7 @@
         <v>1023104</v>
       </c>
       <c r="D156" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E156">
         <v>2</v>
@@ -8306,13 +8333,13 @@
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="J156">
         <v>2023104</v>
       </c>
       <c r="K156" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N156">
         <v>999</v>
@@ -8330,7 +8357,7 @@
         <v>1023105</v>
       </c>
       <c r="D157" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -8345,13 +8372,13 @@
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="J157">
         <v>2023105</v>
       </c>
       <c r="K157" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N157">
         <v>999</v>
@@ -8369,7 +8396,7 @@
         <v>1023201</v>
       </c>
       <c r="D158" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="E158">
         <v>2</v>
@@ -8384,13 +8411,13 @@
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="J158">
         <v>2023201</v>
       </c>
       <c r="K158" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="N158">
         <v>999</v>
@@ -8408,7 +8435,7 @@
         <v>1023202</v>
       </c>
       <c r="D159" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -8423,13 +8450,13 @@
         <v>0</v>
       </c>
       <c r="I159" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="J159">
         <v>2023202</v>
       </c>
       <c r="K159" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="N159">
         <v>999</v>
@@ -8447,7 +8474,7 @@
         <v>1023203</v>
       </c>
       <c r="D160" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E160">
         <v>2</v>
@@ -8462,13 +8489,13 @@
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="J160">
         <v>2023203</v>
       </c>
       <c r="K160" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="N160">
         <v>999</v>
@@ -8486,7 +8513,7 @@
         <v>1023204</v>
       </c>
       <c r="D161" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -8501,13 +8528,13 @@
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="J161">
         <v>2023204</v>
       </c>
       <c r="K161" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="N161">
         <v>999</v>
@@ -8525,7 +8552,7 @@
         <v>1023205</v>
       </c>
       <c r="D162" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -8540,13 +8567,13 @@
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="J162">
         <v>2023205</v>
       </c>
       <c r="K162" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="N162">
         <v>999</v>
@@ -8564,7 +8591,7 @@
         <v>1023301</v>
       </c>
       <c r="D163" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="E163">
         <v>2</v>
@@ -8579,13 +8606,13 @@
         <v>0</v>
       </c>
       <c r="I163" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="J163">
         <v>2023301</v>
       </c>
       <c r="K163" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="N163">
         <v>999</v>
@@ -8603,7 +8630,7 @@
         <v>1023302</v>
       </c>
       <c r="D164" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -8618,13 +8645,13 @@
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="J164">
         <v>2023302</v>
       </c>
       <c r="K164" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="N164">
         <v>999</v>
@@ -8642,7 +8669,7 @@
         <v>1023303</v>
       </c>
       <c r="D165" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="E165">
         <v>2</v>
@@ -8657,13 +8684,13 @@
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="J165">
         <v>2023303</v>
       </c>
       <c r="K165" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="N165">
         <v>999</v>
@@ -8681,7 +8708,7 @@
         <v>1023304</v>
       </c>
       <c r="D166" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -8696,13 +8723,13 @@
         <v>0</v>
       </c>
       <c r="I166" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="J166">
         <v>2023304</v>
       </c>
       <c r="K166" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="N166">
         <v>999</v>
@@ -8720,7 +8747,7 @@
         <v>1023305</v>
       </c>
       <c r="D167" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="E167">
         <v>2</v>
@@ -8735,13 +8762,13 @@
         <v>0</v>
       </c>
       <c r="I167" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="J167">
         <v>2023305</v>
       </c>
       <c r="K167" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="N167">
         <v>999</v>
@@ -8759,7 +8786,7 @@
         <v>1023401</v>
       </c>
       <c r="D168" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E168">
         <v>2</v>
@@ -8774,13 +8801,13 @@
         <v>0</v>
       </c>
       <c r="I168" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="J168">
         <v>2023401</v>
       </c>
       <c r="K168" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="N168">
         <v>999</v>
@@ -8798,7 +8825,7 @@
         <v>1023402</v>
       </c>
       <c r="D169" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -8813,13 +8840,13 @@
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="J169">
         <v>2023402</v>
       </c>
       <c r="K169" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="N169">
         <v>999</v>
@@ -8837,7 +8864,7 @@
         <v>1023403</v>
       </c>
       <c r="D170" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="E170">
         <v>2</v>
@@ -8852,13 +8879,13 @@
         <v>0</v>
       </c>
       <c r="I170" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="J170">
         <v>2023403</v>
       </c>
       <c r="K170" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="N170">
         <v>999</v>
@@ -8876,7 +8903,7 @@
         <v>1023404</v>
       </c>
       <c r="D171" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -8891,13 +8918,13 @@
         <v>0</v>
       </c>
       <c r="I171" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="J171">
         <v>2023404</v>
       </c>
       <c r="K171" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="N171">
         <v>999</v>
@@ -8915,7 +8942,7 @@
         <v>1023405</v>
       </c>
       <c r="D172" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -8930,13 +8957,13 @@
         <v>0</v>
       </c>
       <c r="I172" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="J172">
         <v>2023405</v>
       </c>
       <c r="K172" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="N172">
         <v>999</v>
@@ -8956,13 +8983,13 @@
         <v>1990000</v>
       </c>
       <c r="D173" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="E173">
         <v>99</v>
       </c>
       <c r="F173" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -8971,13 +8998,13 @@
         <v>0</v>
       </c>
       <c r="I173" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="J173">
         <v>2990000</v>
       </c>
       <c r="K173" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="N173">
         <v>-1</v>
@@ -8998,13 +9025,13 @@
         <v>1980000</v>
       </c>
       <c r="D174" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E174">
         <v>98</v>
       </c>
       <c r="F174" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -9013,13 +9040,13 @@
         <v>0</v>
       </c>
       <c r="I174" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="J174">
         <v>2980000</v>
       </c>
       <c r="K174" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="N174">
         <v>-1</v>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="291">
   <si>
     <t>道具ID</t>
   </si>
@@ -247,7 +247,7 @@
     <t>掉落ID</t>
   </si>
   <si>
-    <t>价值</t>
+    <t>价值/美元</t>
   </si>
   <si>
     <t>int</t>
@@ -325,15 +325,24 @@
     <t>赌场工具（普通）</t>
   </si>
   <si>
+    <t>wdcc_ccb_1.png</t>
+  </si>
+  <si>
     <t>使用后随机获得1~2星赌场建筑升级道具</t>
   </si>
   <si>
     <t>赌场工具（精良）</t>
   </si>
   <si>
+    <t>wdcc_ccb_2.png</t>
+  </si>
+  <si>
     <t>赌场工具（优秀）</t>
   </si>
   <si>
+    <t>wdcc_ccb_3.png</t>
+  </si>
+  <si>
     <t>使用后随机获得1~3星赌场建筑升级道具</t>
   </si>
   <si>
@@ -799,55 +808,55 @@
     <t>国旗3</t>
   </si>
   <si>
-    <t>头衔1</t>
+    <t>头衔1-财富大亨</t>
   </si>
   <si>
     <t>daoju1_8.png</t>
   </si>
   <si>
-    <t>头衔2</t>
+    <t>头衔2-一夜暴富</t>
   </si>
   <si>
     <t>daoju_9.png</t>
   </si>
   <si>
-    <t>头衔3</t>
+    <t>头衔3-招财进宝</t>
   </si>
   <si>
     <t>daoju1_7.png</t>
   </si>
   <si>
-    <t>筹码2</t>
+    <t>筹码2-鸿运</t>
   </si>
   <si>
     <t>daoju1_1.png</t>
   </si>
   <si>
-    <t>筹码3</t>
+    <t>筹码3-万贯</t>
   </si>
   <si>
     <t>daoju1_2.png</t>
   </si>
   <si>
-    <t>牌背2</t>
+    <t>牌背2-百宝</t>
   </si>
   <si>
     <t>daoju1_3.png</t>
   </si>
   <si>
-    <t>牌背3</t>
+    <t>牌背3-金麟</t>
   </si>
   <si>
     <t>daoju1_4.png</t>
   </si>
   <si>
-    <t>大厅背景2</t>
+    <t>大厅背景2-运动</t>
   </si>
   <si>
     <t>daoju1_5.png</t>
   </si>
   <si>
-    <t>大厅背景3</t>
+    <t>大厅背景3-星空</t>
   </si>
   <si>
     <t>daoju1_6.png</t>
@@ -856,7 +865,7 @@
     <t>祈福卡</t>
   </si>
   <si>
-    <t>itemicon_1022501.png</t>
+    <t>daoju_4.png</t>
   </si>
   <si>
     <t>在搖錢樹活動中祈福使用，可在指定禮包中購買獲得</t>
@@ -865,7 +874,7 @@
     <t>刮刮卡</t>
   </si>
   <si>
-    <t>itemicon_1022502.png</t>
+    <t>daoju_5.png</t>
   </si>
   <si>
     <t>在指定的游戏中产出</t>
@@ -874,6 +883,9 @@
     <t>夺宝优惠券</t>
   </si>
   <si>
+    <t>itemicon_duobaoquan.png</t>
+  </si>
+  <si>
     <t>积分</t>
   </si>
   <si>
@@ -1054,7 +1066,7 @@
     <t>货币</t>
   </si>
   <si>
-    <t>itemicon_1990000.png</t>
+    <t>jinbi_1.png</t>
   </si>
   <si>
     <t>下注时需要用的货币</t>
@@ -1063,7 +1075,7 @@
     <t>钻石</t>
   </si>
   <si>
-    <t>itemicon_1980000.png</t>
+    <t>jinbi_11.png</t>
   </si>
   <si>
     <t>在私密房间内下注时需要用的货币，同时是使用部分功能需要消耗的特殊货币</t>
@@ -2577,13 +2589,13 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J7" s="1">
         <v>2010301</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N7" s="1">
         <v>999</v>
@@ -2593,7 +2605,7 @@
         <v>1010301</v>
       </c>
       <c r="Q7" s="1">
-        <v>1.99</v>
+        <v>0.0360375324282976</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -2607,7 +2619,7 @@
         <v>1100302</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2622,13 +2634,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J8" s="1">
         <v>2010302</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N8" s="1">
         <v>999</v>
@@ -2638,7 +2650,7 @@
         <v>1010302</v>
       </c>
       <c r="Q8" s="1">
-        <v>4.99</v>
+        <v>0.0429678271260472</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -2652,7 +2664,7 @@
         <v>1100303</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2667,13 +2679,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J9" s="1">
         <v>2010303</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N9" s="1">
         <v>999</v>
@@ -2683,7 +2695,7 @@
         <v>1010303</v>
       </c>
       <c r="Q9" s="1">
-        <v>14.99</v>
+        <v>0.0572904361680629</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -2697,7 +2709,7 @@
         <v>1100304</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2718,7 +2730,7 @@
         <v>2010304</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N10" s="1">
         <v>999</v>
@@ -2728,7 +2740,7 @@
         <v>1010304</v>
       </c>
       <c r="Q10" s="1">
-        <v>24.99</v>
+        <v>0.0709310162080779</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -2742,7 +2754,7 @@
         <v>1100305</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2763,7 +2775,7 @@
         <v>2010305</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N11" s="1">
         <v>999</v>
@@ -2773,7 +2785,7 @@
         <v>1010305</v>
       </c>
       <c r="Q11" s="1">
-        <v>49.99</v>
+        <v>0.106396524312117</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -2787,7 +2799,7 @@
         <v>1100311</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -2808,7 +2820,7 @@
         <v>2010311</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N12" s="1">
         <v>999</v>
@@ -2829,7 +2841,7 @@
         <v>1100312</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -2850,7 +2862,7 @@
         <v>2010312</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N13" s="1">
         <v>999</v>
@@ -2871,7 +2883,7 @@
         <v>1100313</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -2892,7 +2904,7 @@
         <v>2010313</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N14" s="1">
         <v>999</v>
@@ -2913,7 +2925,7 @@
         <v>1100314</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -2934,7 +2946,7 @@
         <v>2010314</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N15" s="1">
         <v>999</v>
@@ -2955,7 +2967,7 @@
         <v>1100315</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -2976,7 +2988,7 @@
         <v>2010315</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N16" s="1">
         <v>999</v>
@@ -2997,13 +3009,13 @@
         <v>1020001</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -3012,13 +3024,13 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J17">
         <v>2020001</v>
       </c>
       <c r="K17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N17">
         <v>999</v>
@@ -3035,13 +3047,13 @@
         <v>1020002</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2">
         <v>2</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G18" s="2">
         <v>2</v>
@@ -3050,13 +3062,13 @@
         <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J18" s="2">
         <v>2020002</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N18" s="2">
         <v>999</v>
@@ -3073,13 +3085,13 @@
         <v>1020003</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2">
         <v>2</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G19" s="2">
         <v>3</v>
@@ -3088,13 +3100,13 @@
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J19" s="2">
         <v>2020003</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N19" s="2">
         <v>999</v>
@@ -3111,13 +3123,13 @@
         <v>1020004</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E20" s="2">
         <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G20" s="2">
         <v>4</v>
@@ -3126,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J20" s="2">
         <v>2020004</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N20" s="2">
         <v>999</v>
@@ -3149,13 +3161,13 @@
         <v>1020005</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E21" s="2">
         <v>2</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G21" s="2">
         <v>5</v>
@@ -3164,13 +3176,13 @@
         <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J21" s="2">
         <v>2020005</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N21" s="2">
         <v>999</v>
@@ -3187,13 +3199,13 @@
         <v>1020006</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E22" s="2">
         <v>2</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G22" s="2">
         <v>6</v>
@@ -3202,13 +3214,13 @@
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J22" s="2">
         <v>2020006</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N22" s="2">
         <v>999</v>
@@ -3225,13 +3237,13 @@
         <v>1300011</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3240,13 +3252,13 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J23">
         <v>2030011</v>
       </c>
       <c r="K23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M23">
         <v>10001</v>
@@ -3266,13 +3278,13 @@
         <v>1300012</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -3281,13 +3293,13 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J24">
         <v>2030012</v>
       </c>
       <c r="K24" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M24">
         <v>10002</v>
@@ -3307,13 +3319,13 @@
         <v>1300013</v>
       </c>
       <c r="D25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3322,13 +3334,13 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J25">
         <v>2030013</v>
       </c>
       <c r="K25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M25">
         <v>10003</v>
@@ -3348,13 +3360,13 @@
         <v>1300014</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3363,13 +3375,13 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J26">
         <v>2030014</v>
       </c>
       <c r="K26" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M26">
         <v>10004</v>
@@ -3389,13 +3401,13 @@
         <v>1300015</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3404,13 +3416,13 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J27">
         <v>2030015</v>
       </c>
       <c r="K27" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M27">
         <v>10005</v>
@@ -3430,13 +3442,13 @@
         <v>1300016</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3445,13 +3457,13 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J28">
         <v>2030016</v>
       </c>
       <c r="K28" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M28">
         <v>10006</v>
@@ -3471,13 +3483,13 @@
         <v>1300017</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3486,13 +3498,13 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J29">
         <v>2030017</v>
       </c>
       <c r="K29" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M29">
         <v>10007</v>
@@ -3512,13 +3524,13 @@
         <v>1300018</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3527,13 +3539,13 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J30">
         <v>2030018</v>
       </c>
       <c r="K30" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M30">
         <v>10008</v>
@@ -3553,13 +3565,13 @@
         <v>1300101</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -3568,13 +3580,13 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J31">
         <v>2030101</v>
       </c>
       <c r="K31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -3591,13 +3603,13 @@
         <v>1300102</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -3606,13 +3618,13 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J32">
         <v>2030102</v>
       </c>
       <c r="K32" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -3629,13 +3641,13 @@
         <v>1300103</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E33">
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -3644,13 +3656,13 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J33">
         <v>2030103</v>
       </c>
       <c r="K33" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -3667,13 +3679,13 @@
         <v>1300104</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -3682,13 +3694,13 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J34">
         <v>2030104</v>
       </c>
       <c r="K34" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -3705,13 +3717,13 @@
         <v>1300105</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E35">
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -3720,13 +3732,13 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J35">
         <v>2030105</v>
       </c>
       <c r="K35" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -3743,13 +3755,13 @@
         <v>1300106</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -3758,13 +3770,13 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J36">
         <v>2030106</v>
       </c>
       <c r="K36" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -3781,13 +3793,13 @@
         <v>1300107</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -3796,13 +3808,13 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J37">
         <v>2030107</v>
       </c>
       <c r="K37" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -3819,13 +3831,13 @@
         <v>1300108</v>
       </c>
       <c r="D38" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -3834,13 +3846,13 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J38">
         <v>2030108</v>
       </c>
       <c r="K38" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -3857,13 +3869,13 @@
         <v>1300109</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -3872,13 +3884,13 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J39">
         <v>2030109</v>
       </c>
       <c r="K39" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -3895,13 +3907,13 @@
         <v>1300110</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -3910,13 +3922,13 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J40">
         <v>2030110</v>
       </c>
       <c r="K40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -3933,13 +3945,13 @@
         <v>1300111</v>
       </c>
       <c r="D41" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E41">
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G41">
         <v>6</v>
@@ -3948,13 +3960,13 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J41">
         <v>2030111</v>
       </c>
       <c r="K41" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N41">
         <v>1</v>
@@ -3971,13 +3983,13 @@
         <v>1300112</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -3986,13 +3998,13 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J42">
         <v>2030112</v>
       </c>
       <c r="K42" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -4009,13 +4021,13 @@
         <v>1300121</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -4024,13 +4036,13 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J43">
         <v>2030121</v>
       </c>
       <c r="K43" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N43">
         <v>1</v>
@@ -4047,13 +4059,13 @@
         <v>1300122</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E44">
         <v>3</v>
       </c>
       <c r="F44" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -4062,13 +4074,13 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J44">
         <v>2030122</v>
       </c>
       <c r="K44" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -4085,13 +4097,13 @@
         <v>1300123</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E45">
         <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -4100,13 +4112,13 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J45">
         <v>2030123</v>
       </c>
       <c r="K45" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -4123,13 +4135,13 @@
         <v>1300124</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E46">
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -4138,13 +4150,13 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J46">
         <v>2030124</v>
       </c>
       <c r="K46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N46">
         <v>1</v>
@@ -4161,13 +4173,13 @@
         <v>1300125</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E47">
         <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G47">
         <v>3</v>
@@ -4176,13 +4188,13 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J47">
         <v>2030125</v>
       </c>
       <c r="K47" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -4199,13 +4211,13 @@
         <v>1300126</v>
       </c>
       <c r="D48" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E48">
         <v>3</v>
       </c>
       <c r="F48" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G48">
         <v>3</v>
@@ -4214,13 +4226,13 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J48">
         <v>2030126</v>
       </c>
       <c r="K48" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -4237,13 +4249,13 @@
         <v>1300127</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E49">
         <v>3</v>
       </c>
       <c r="F49" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -4252,13 +4264,13 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J49">
         <v>2030127</v>
       </c>
       <c r="K49" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N49">
         <v>1</v>
@@ -4275,13 +4287,13 @@
         <v>1300128</v>
       </c>
       <c r="D50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E50">
         <v>3</v>
       </c>
       <c r="F50" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -4290,13 +4302,13 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J50">
         <v>2030128</v>
       </c>
       <c r="K50" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N50">
         <v>1</v>
@@ -4313,13 +4325,13 @@
         <v>1300129</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E51">
         <v>3</v>
       </c>
       <c r="F51" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -4328,13 +4340,13 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J51">
         <v>2030129</v>
       </c>
       <c r="K51" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N51">
         <v>1</v>
@@ -4351,13 +4363,13 @@
         <v>1300130</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E52">
         <v>3</v>
       </c>
       <c r="F52" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -4366,13 +4378,13 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J52">
         <v>2030130</v>
       </c>
       <c r="K52" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -4389,13 +4401,13 @@
         <v>1300131</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G53">
         <v>6</v>
@@ -4404,13 +4416,13 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J53">
         <v>2030131</v>
       </c>
       <c r="K53" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -4427,13 +4439,13 @@
         <v>1300132</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E54">
         <v>3</v>
       </c>
       <c r="F54" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -4442,13 +4454,13 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J54">
         <v>2030132</v>
       </c>
       <c r="K54" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N54">
         <v>1</v>
@@ -4465,13 +4477,13 @@
         <v>1300141</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E55">
         <v>3</v>
       </c>
       <c r="F55" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -4480,13 +4492,13 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J55">
         <v>2030141</v>
       </c>
       <c r="K55" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -4503,13 +4515,13 @@
         <v>1300142</v>
       </c>
       <c r="D56" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E56">
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -4518,13 +4530,13 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J56">
         <v>2030142</v>
       </c>
       <c r="K56" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -4541,13 +4553,13 @@
         <v>1300143</v>
       </c>
       <c r="D57" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E57">
         <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -4556,13 +4568,13 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J57">
         <v>2030143</v>
       </c>
       <c r="K57" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N57">
         <v>1</v>
@@ -4579,13 +4591,13 @@
         <v>1300144</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E58">
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -4594,13 +4606,13 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J58">
         <v>2030144</v>
       </c>
       <c r="K58" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N58">
         <v>1</v>
@@ -4617,13 +4629,13 @@
         <v>1300145</v>
       </c>
       <c r="D59" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E59">
         <v>3</v>
       </c>
       <c r="F59" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -4632,13 +4644,13 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J59">
         <v>2030145</v>
       </c>
       <c r="K59" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -4655,13 +4667,13 @@
         <v>1300146</v>
       </c>
       <c r="D60" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E60">
         <v>3</v>
       </c>
       <c r="F60" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G60">
         <v>3</v>
@@ -4670,13 +4682,13 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J60">
         <v>2030146</v>
       </c>
       <c r="K60" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -4693,13 +4705,13 @@
         <v>1300147</v>
       </c>
       <c r="D61" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G61">
         <v>4</v>
@@ -4708,13 +4720,13 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J61">
         <v>2030147</v>
       </c>
       <c r="K61" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -4731,13 +4743,13 @@
         <v>1300148</v>
       </c>
       <c r="D62" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E62">
         <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G62">
         <v>4</v>
@@ -4746,13 +4758,13 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J62">
         <v>2030148</v>
       </c>
       <c r="K62" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N62">
         <v>1</v>
@@ -4769,13 +4781,13 @@
         <v>1300149</v>
       </c>
       <c r="D63" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E63">
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G63">
         <v>5</v>
@@ -4784,13 +4796,13 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J63">
         <v>2030149</v>
       </c>
       <c r="K63" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -4807,13 +4819,13 @@
         <v>1300150</v>
       </c>
       <c r="D64" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E64">
         <v>3</v>
       </c>
       <c r="F64" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -4822,13 +4834,13 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J64">
         <v>2030150</v>
       </c>
       <c r="K64" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N64">
         <v>1</v>
@@ -4845,13 +4857,13 @@
         <v>1300151</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E65">
         <v>3</v>
       </c>
       <c r="F65" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G65">
         <v>6</v>
@@ -4860,13 +4872,13 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J65">
         <v>2030151</v>
       </c>
       <c r="K65" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N65">
         <v>1</v>
@@ -4883,13 +4895,13 @@
         <v>1300152</v>
       </c>
       <c r="D66" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E66">
         <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G66">
         <v>6</v>
@@ -4898,13 +4910,13 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J66">
         <v>2030152</v>
       </c>
       <c r="K66" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -4921,13 +4933,13 @@
         <v>1300161</v>
       </c>
       <c r="D67" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E67">
         <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -4936,13 +4948,13 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J67">
         <v>2030161</v>
       </c>
       <c r="K67" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N67">
         <v>1</v>
@@ -4959,13 +4971,13 @@
         <v>1300162</v>
       </c>
       <c r="D68" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E68">
         <v>3</v>
       </c>
       <c r="F68" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -4974,13 +4986,13 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J68">
         <v>2030162</v>
       </c>
       <c r="K68" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N68">
         <v>1</v>
@@ -4997,13 +5009,13 @@
         <v>1300163</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E69">
         <v>3</v>
       </c>
       <c r="F69" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G69">
         <v>2</v>
@@ -5012,13 +5024,13 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J69">
         <v>2030163</v>
       </c>
       <c r="K69" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N69">
         <v>1</v>
@@ -5035,13 +5047,13 @@
         <v>1300164</v>
       </c>
       <c r="D70" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E70">
         <v>3</v>
       </c>
       <c r="F70" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G70">
         <v>2</v>
@@ -5050,13 +5062,13 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J70">
         <v>2030164</v>
       </c>
       <c r="K70" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N70">
         <v>1</v>
@@ -5073,13 +5085,13 @@
         <v>1300165</v>
       </c>
       <c r="D71" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E71">
         <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G71">
         <v>3</v>
@@ -5088,13 +5100,13 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J71">
         <v>2030165</v>
       </c>
       <c r="K71" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N71">
         <v>1</v>
@@ -5111,13 +5123,13 @@
         <v>1300166</v>
       </c>
       <c r="D72" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E72">
         <v>3</v>
       </c>
       <c r="F72" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G72">
         <v>3</v>
@@ -5126,13 +5138,13 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J72">
         <v>2030166</v>
       </c>
       <c r="K72" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N72">
         <v>1</v>
@@ -5149,13 +5161,13 @@
         <v>1300167</v>
       </c>
       <c r="D73" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E73">
         <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G73">
         <v>4</v>
@@ -5164,13 +5176,13 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J73">
         <v>2030167</v>
       </c>
       <c r="K73" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N73">
         <v>1</v>
@@ -5187,13 +5199,13 @@
         <v>1300168</v>
       </c>
       <c r="D74" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E74">
         <v>3</v>
       </c>
       <c r="F74" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G74">
         <v>4</v>
@@ -5202,13 +5214,13 @@
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J74">
         <v>2030168</v>
       </c>
       <c r="K74" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N74">
         <v>1</v>
@@ -5225,13 +5237,13 @@
         <v>1300169</v>
       </c>
       <c r="D75" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E75">
         <v>3</v>
       </c>
       <c r="F75" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G75">
         <v>5</v>
@@ -5240,13 +5252,13 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J75">
         <v>2030169</v>
       </c>
       <c r="K75" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N75">
         <v>1</v>
@@ -5263,13 +5275,13 @@
         <v>1300170</v>
       </c>
       <c r="D76" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G76">
         <v>5</v>
@@ -5278,13 +5290,13 @@
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J76">
         <v>2030170</v>
       </c>
       <c r="K76" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N76">
         <v>1</v>
@@ -5301,13 +5313,13 @@
         <v>1300171</v>
       </c>
       <c r="D77" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G77">
         <v>6</v>
@@ -5316,13 +5328,13 @@
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J77">
         <v>2030171</v>
       </c>
       <c r="K77" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N77">
         <v>1</v>
@@ -5339,13 +5351,13 @@
         <v>1300172</v>
       </c>
       <c r="D78" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E78">
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G78">
         <v>6</v>
@@ -5354,13 +5366,13 @@
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J78">
         <v>2030172</v>
       </c>
       <c r="K78" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N78">
         <v>1</v>
@@ -5377,13 +5389,13 @@
         <v>1300181</v>
       </c>
       <c r="D79" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E79">
         <v>3</v>
       </c>
       <c r="F79" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -5392,13 +5404,13 @@
         <v>1</v>
       </c>
       <c r="I79" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J79">
         <v>2030181</v>
       </c>
       <c r="K79" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -5415,13 +5427,13 @@
         <v>1300182</v>
       </c>
       <c r="D80" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E80">
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -5430,13 +5442,13 @@
         <v>1</v>
       </c>
       <c r="I80" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J80">
         <v>2030182</v>
       </c>
       <c r="K80" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N80">
         <v>1</v>
@@ -5453,13 +5465,13 @@
         <v>1300183</v>
       </c>
       <c r="D81" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G81">
         <v>2</v>
@@ -5468,13 +5480,13 @@
         <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J81">
         <v>2030183</v>
       </c>
       <c r="K81" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -5491,13 +5503,13 @@
         <v>1300184</v>
       </c>
       <c r="D82" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E82">
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G82">
         <v>2</v>
@@ -5506,13 +5518,13 @@
         <v>1</v>
       </c>
       <c r="I82" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J82">
         <v>2030184</v>
       </c>
       <c r="K82" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -5529,13 +5541,13 @@
         <v>1300185</v>
       </c>
       <c r="D83" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G83">
         <v>3</v>
@@ -5544,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="I83" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J83">
         <v>2030185</v>
       </c>
       <c r="K83" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N83">
         <v>1</v>
@@ -5567,13 +5579,13 @@
         <v>1300186</v>
       </c>
       <c r="D84" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E84">
         <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G84">
         <v>3</v>
@@ -5582,13 +5594,13 @@
         <v>1</v>
       </c>
       <c r="I84" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J84">
         <v>2030186</v>
       </c>
       <c r="K84" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N84">
         <v>1</v>
@@ -5605,13 +5617,13 @@
         <v>1300187</v>
       </c>
       <c r="D85" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E85">
         <v>3</v>
       </c>
       <c r="F85" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G85">
         <v>4</v>
@@ -5620,13 +5632,13 @@
         <v>1</v>
       </c>
       <c r="I85" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J85">
         <v>2030187</v>
       </c>
       <c r="K85" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -5643,13 +5655,13 @@
         <v>1300188</v>
       </c>
       <c r="D86" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E86">
         <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G86">
         <v>4</v>
@@ -5658,13 +5670,13 @@
         <v>1</v>
       </c>
       <c r="I86" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J86">
         <v>2030188</v>
       </c>
       <c r="K86" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -5681,13 +5693,13 @@
         <v>1300189</v>
       </c>
       <c r="D87" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E87">
         <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G87">
         <v>5</v>
@@ -5696,13 +5708,13 @@
         <v>1</v>
       </c>
       <c r="I87" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J87">
         <v>2030189</v>
       </c>
       <c r="K87" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -5719,13 +5731,13 @@
         <v>1300190</v>
       </c>
       <c r="D88" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E88">
         <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G88">
         <v>5</v>
@@ -5734,13 +5746,13 @@
         <v>1</v>
       </c>
       <c r="I88" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J88">
         <v>2030190</v>
       </c>
       <c r="K88" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -5757,13 +5769,13 @@
         <v>1300191</v>
       </c>
       <c r="D89" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E89">
         <v>3</v>
       </c>
       <c r="F89" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G89">
         <v>6</v>
@@ -5772,13 +5784,13 @@
         <v>1</v>
       </c>
       <c r="I89" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J89">
         <v>2030191</v>
       </c>
       <c r="K89" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N89">
         <v>1</v>
@@ -5795,13 +5807,13 @@
         <v>1300192</v>
       </c>
       <c r="D90" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E90">
         <v>3</v>
       </c>
       <c r="F90" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G90">
         <v>6</v>
@@ -5810,13 +5822,13 @@
         <v>1</v>
       </c>
       <c r="I90" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J90">
         <v>2030192</v>
       </c>
       <c r="K90" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N90">
         <v>1</v>
@@ -5833,13 +5845,13 @@
         <v>1300201</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E91">
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -5848,13 +5860,13 @@
         <v>1</v>
       </c>
       <c r="I91" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J91">
         <v>2030201</v>
       </c>
       <c r="K91" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -5871,13 +5883,13 @@
         <v>1300202</v>
       </c>
       <c r="D92" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E92">
         <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -5886,13 +5898,13 @@
         <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J92">
         <v>2030202</v>
       </c>
       <c r="K92" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N92">
         <v>1</v>
@@ -5909,13 +5921,13 @@
         <v>1300203</v>
       </c>
       <c r="D93" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E93">
         <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G93">
         <v>2</v>
@@ -5924,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J93">
         <v>2030203</v>
       </c>
       <c r="K93" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -5947,13 +5959,13 @@
         <v>1300204</v>
       </c>
       <c r="D94" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E94">
         <v>3</v>
       </c>
       <c r="F94" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G94">
         <v>2</v>
@@ -5962,13 +5974,13 @@
         <v>1</v>
       </c>
       <c r="I94" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J94">
         <v>2030204</v>
       </c>
       <c r="K94" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N94">
         <v>1</v>
@@ -5985,13 +5997,13 @@
         <v>1300205</v>
       </c>
       <c r="D95" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E95">
         <v>3</v>
       </c>
       <c r="F95" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G95">
         <v>3</v>
@@ -6000,13 +6012,13 @@
         <v>1</v>
       </c>
       <c r="I95" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J95">
         <v>2030205</v>
       </c>
       <c r="K95" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N95">
         <v>1</v>
@@ -6023,13 +6035,13 @@
         <v>1300206</v>
       </c>
       <c r="D96" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E96">
         <v>3</v>
       </c>
       <c r="F96" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G96">
         <v>3</v>
@@ -6038,13 +6050,13 @@
         <v>1</v>
       </c>
       <c r="I96" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J96">
         <v>2030206</v>
       </c>
       <c r="K96" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -6061,13 +6073,13 @@
         <v>1300207</v>
       </c>
       <c r="D97" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E97">
         <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G97">
         <v>4</v>
@@ -6076,13 +6088,13 @@
         <v>1</v>
       </c>
       <c r="I97" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J97">
         <v>2030207</v>
       </c>
       <c r="K97" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N97">
         <v>1</v>
@@ -6099,13 +6111,13 @@
         <v>1300208</v>
       </c>
       <c r="D98" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E98">
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G98">
         <v>4</v>
@@ -6114,13 +6126,13 @@
         <v>1</v>
       </c>
       <c r="I98" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J98">
         <v>2030208</v>
       </c>
       <c r="K98" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N98">
         <v>1</v>
@@ -6137,13 +6149,13 @@
         <v>1300209</v>
       </c>
       <c r="D99" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E99">
         <v>3</v>
       </c>
       <c r="F99" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G99">
         <v>5</v>
@@ -6152,13 +6164,13 @@
         <v>1</v>
       </c>
       <c r="I99" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J99">
         <v>2030209</v>
       </c>
       <c r="K99" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -6175,13 +6187,13 @@
         <v>1300210</v>
       </c>
       <c r="D100" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E100">
         <v>3</v>
       </c>
       <c r="F100" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G100">
         <v>5</v>
@@ -6190,13 +6202,13 @@
         <v>1</v>
       </c>
       <c r="I100" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J100">
         <v>2030210</v>
       </c>
       <c r="K100" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N100">
         <v>1</v>
@@ -6213,13 +6225,13 @@
         <v>1300211</v>
       </c>
       <c r="D101" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E101">
         <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G101">
         <v>6</v>
@@ -6228,13 +6240,13 @@
         <v>1</v>
       </c>
       <c r="I101" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J101">
         <v>2030211</v>
       </c>
       <c r="K101" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N101">
         <v>1</v>
@@ -6251,13 +6263,13 @@
         <v>1300212</v>
       </c>
       <c r="D102" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E102">
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G102">
         <v>6</v>
@@ -6266,13 +6278,13 @@
         <v>1</v>
       </c>
       <c r="I102" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J102">
         <v>2030212</v>
       </c>
       <c r="K102" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N102">
         <v>1</v>
@@ -6289,13 +6301,13 @@
         <v>1300221</v>
       </c>
       <c r="D103" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E103">
         <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -6304,13 +6316,13 @@
         <v>1</v>
       </c>
       <c r="I103" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J103">
         <v>2030221</v>
       </c>
       <c r="K103" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N103">
         <v>1</v>
@@ -6327,13 +6339,13 @@
         <v>1300222</v>
       </c>
       <c r="D104" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E104">
         <v>3</v>
       </c>
       <c r="F104" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -6342,13 +6354,13 @@
         <v>1</v>
       </c>
       <c r="I104" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J104">
         <v>2030222</v>
       </c>
       <c r="K104" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N104">
         <v>1</v>
@@ -6365,13 +6377,13 @@
         <v>1300223</v>
       </c>
       <c r="D105" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E105">
         <v>3</v>
       </c>
       <c r="F105" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G105">
         <v>2</v>
@@ -6380,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="I105" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J105">
         <v>2030223</v>
       </c>
       <c r="K105" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N105">
         <v>1</v>
@@ -6403,13 +6415,13 @@
         <v>1300224</v>
       </c>
       <c r="D106" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G106">
         <v>2</v>
@@ -6418,13 +6430,13 @@
         <v>1</v>
       </c>
       <c r="I106" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J106">
         <v>2030224</v>
       </c>
       <c r="K106" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N106">
         <v>1</v>
@@ -6441,13 +6453,13 @@
         <v>1300225</v>
       </c>
       <c r="D107" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G107">
         <v>3</v>
@@ -6456,13 +6468,13 @@
         <v>1</v>
       </c>
       <c r="I107" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J107">
         <v>2030225</v>
       </c>
       <c r="K107" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -6479,13 +6491,13 @@
         <v>1300226</v>
       </c>
       <c r="D108" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E108">
         <v>3</v>
       </c>
       <c r="F108" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G108">
         <v>3</v>
@@ -6494,13 +6506,13 @@
         <v>1</v>
       </c>
       <c r="I108" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J108">
         <v>2030226</v>
       </c>
       <c r="K108" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -6517,13 +6529,13 @@
         <v>1300227</v>
       </c>
       <c r="D109" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E109">
         <v>3</v>
       </c>
       <c r="F109" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G109">
         <v>4</v>
@@ -6532,13 +6544,13 @@
         <v>1</v>
       </c>
       <c r="I109" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J109">
         <v>2030227</v>
       </c>
       <c r="K109" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N109">
         <v>1</v>
@@ -6555,13 +6567,13 @@
         <v>1300228</v>
       </c>
       <c r="D110" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E110">
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G110">
         <v>4</v>
@@ -6570,13 +6582,13 @@
         <v>1</v>
       </c>
       <c r="I110" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J110">
         <v>2030228</v>
       </c>
       <c r="K110" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -6593,13 +6605,13 @@
         <v>1300229</v>
       </c>
       <c r="D111" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E111">
         <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G111">
         <v>5</v>
@@ -6608,13 +6620,13 @@
         <v>1</v>
       </c>
       <c r="I111" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J111">
         <v>2030229</v>
       </c>
       <c r="K111" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N111">
         <v>1</v>
@@ -6631,13 +6643,13 @@
         <v>1300230</v>
       </c>
       <c r="D112" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E112">
         <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G112">
         <v>5</v>
@@ -6646,13 +6658,13 @@
         <v>1</v>
       </c>
       <c r="I112" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J112">
         <v>2030230</v>
       </c>
       <c r="K112" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N112">
         <v>1</v>
@@ -6669,13 +6681,13 @@
         <v>1300231</v>
       </c>
       <c r="D113" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E113">
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G113">
         <v>6</v>
@@ -6684,13 +6696,13 @@
         <v>1</v>
       </c>
       <c r="I113" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J113">
         <v>2030231</v>
       </c>
       <c r="K113" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N113">
         <v>1</v>
@@ -6707,13 +6719,13 @@
         <v>1300232</v>
       </c>
       <c r="D114" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E114">
         <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G114">
         <v>6</v>
@@ -6722,13 +6734,13 @@
         <v>1</v>
       </c>
       <c r="I114" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J114">
         <v>2030232</v>
       </c>
       <c r="K114" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -6745,13 +6757,13 @@
         <v>1300241</v>
       </c>
       <c r="D115" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E115">
         <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -6760,13 +6772,13 @@
         <v>1</v>
       </c>
       <c r="I115" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J115">
         <v>2030241</v>
       </c>
       <c r="K115" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N115">
         <v>1</v>
@@ -6783,13 +6795,13 @@
         <v>1300242</v>
       </c>
       <c r="D116" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E116">
         <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -6798,13 +6810,13 @@
         <v>1</v>
       </c>
       <c r="I116" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J116">
         <v>2030242</v>
       </c>
       <c r="K116" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N116">
         <v>1</v>
@@ -6821,13 +6833,13 @@
         <v>1300243</v>
       </c>
       <c r="D117" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E117">
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G117">
         <v>2</v>
@@ -6836,13 +6848,13 @@
         <v>1</v>
       </c>
       <c r="I117" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J117">
         <v>2030243</v>
       </c>
       <c r="K117" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -6859,13 +6871,13 @@
         <v>1300244</v>
       </c>
       <c r="D118" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E118">
         <v>3</v>
       </c>
       <c r="F118" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G118">
         <v>2</v>
@@ -6874,13 +6886,13 @@
         <v>1</v>
       </c>
       <c r="I118" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J118">
         <v>2030244</v>
       </c>
       <c r="K118" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N118">
         <v>1</v>
@@ -6897,13 +6909,13 @@
         <v>1300245</v>
       </c>
       <c r="D119" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E119">
         <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G119">
         <v>3</v>
@@ -6912,13 +6924,13 @@
         <v>1</v>
       </c>
       <c r="I119" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J119">
         <v>2030245</v>
       </c>
       <c r="K119" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -6935,13 +6947,13 @@
         <v>1300246</v>
       </c>
       <c r="D120" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E120">
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G120">
         <v>3</v>
@@ -6950,13 +6962,13 @@
         <v>1</v>
       </c>
       <c r="I120" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J120">
         <v>2030246</v>
       </c>
       <c r="K120" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N120">
         <v>1</v>
@@ -6973,13 +6985,13 @@
         <v>1300247</v>
       </c>
       <c r="D121" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E121">
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G121">
         <v>4</v>
@@ -6988,13 +7000,13 @@
         <v>1</v>
       </c>
       <c r="I121" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J121">
         <v>2030247</v>
       </c>
       <c r="K121" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -7011,13 +7023,13 @@
         <v>1300248</v>
       </c>
       <c r="D122" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E122">
         <v>3</v>
       </c>
       <c r="F122" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G122">
         <v>4</v>
@@ -7026,13 +7038,13 @@
         <v>1</v>
       </c>
       <c r="I122" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J122">
         <v>2030248</v>
       </c>
       <c r="K122" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N122">
         <v>1</v>
@@ -7049,13 +7061,13 @@
         <v>1300249</v>
       </c>
       <c r="D123" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E123">
         <v>3</v>
       </c>
       <c r="F123" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G123">
         <v>5</v>
@@ -7064,13 +7076,13 @@
         <v>1</v>
       </c>
       <c r="I123" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J123">
         <v>2030249</v>
       </c>
       <c r="K123" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N123">
         <v>1</v>
@@ -7087,13 +7099,13 @@
         <v>1300250</v>
       </c>
       <c r="D124" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E124">
         <v>3</v>
       </c>
       <c r="F124" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G124">
         <v>5</v>
@@ -7102,13 +7114,13 @@
         <v>1</v>
       </c>
       <c r="I124" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J124">
         <v>2030250</v>
       </c>
       <c r="K124" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N124">
         <v>1</v>
@@ -7125,13 +7137,13 @@
         <v>1300251</v>
       </c>
       <c r="D125" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E125">
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G125">
         <v>6</v>
@@ -7140,13 +7152,13 @@
         <v>1</v>
       </c>
       <c r="I125" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J125">
         <v>2030251</v>
       </c>
       <c r="K125" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N125">
         <v>1</v>
@@ -7163,13 +7175,13 @@
         <v>1300252</v>
       </c>
       <c r="D126" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E126">
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G126">
         <v>6</v>
@@ -7178,13 +7190,13 @@
         <v>1</v>
       </c>
       <c r="I126" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J126">
         <v>2030252</v>
       </c>
       <c r="K126" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N126">
         <v>1</v>
@@ -7201,13 +7213,13 @@
         <v>1301001</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E127">
         <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -7216,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="I127" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J127">
         <v>2031001</v>
@@ -7239,13 +7251,13 @@
         <v>1301002</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E128">
         <v>3</v>
       </c>
       <c r="F128" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -7254,7 +7266,7 @@
         <v>1</v>
       </c>
       <c r="I128" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J128">
         <v>2031002</v>
@@ -7277,13 +7289,13 @@
         <v>1301201</v>
       </c>
       <c r="D129" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E129">
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -7292,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="I129" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J129">
         <v>2031201</v>
@@ -7315,13 +7327,13 @@
         <v>1301202</v>
       </c>
       <c r="D130" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E130">
         <v>3</v>
       </c>
       <c r="F130" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -7330,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="I130" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J130">
         <v>2031202</v>
@@ -7353,13 +7365,13 @@
         <v>101801</v>
       </c>
       <c r="D131" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E131">
         <v>3</v>
       </c>
       <c r="F131" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -7368,7 +7380,7 @@
         <v>1</v>
       </c>
       <c r="I131" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J131">
         <v>201801</v>
@@ -7391,13 +7403,13 @@
         <v>101802</v>
       </c>
       <c r="D132" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E132">
         <v>3</v>
       </c>
       <c r="F132" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -7406,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="I132" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J132">
         <v>201802</v>
@@ -7429,13 +7441,13 @@
         <v>1201401</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E133">
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -7444,7 +7456,7 @@
         <v>1</v>
       </c>
       <c r="I133" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J133">
         <v>2021401</v>
@@ -7467,13 +7479,13 @@
         <v>1201402</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E134">
         <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -7482,7 +7494,7 @@
         <v>1</v>
       </c>
       <c r="I134" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J134">
         <v>2021402</v>
@@ -7505,13 +7517,13 @@
         <v>1301600</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E135" s="3">
         <v>3</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G135" s="3">
         <v>1</v>
@@ -7520,7 +7532,7 @@
         <v>1</v>
       </c>
       <c r="I135" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J135" s="3">
         <v>2031600</v>
@@ -7543,13 +7555,13 @@
         <v>1301601</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E136">
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -7558,7 +7570,7 @@
         <v>1</v>
       </c>
       <c r="I136" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="J136">
         <v>2031601</v>
@@ -7581,13 +7593,13 @@
         <v>1301602</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E137">
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -7596,7 +7608,7 @@
         <v>1</v>
       </c>
       <c r="I137" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J137">
         <v>2031602</v>
@@ -7619,13 +7631,13 @@
         <v>1301801</v>
       </c>
       <c r="D138" s="15" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E138">
         <v>3</v>
       </c>
       <c r="F138" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -7634,7 +7646,7 @@
         <v>1</v>
       </c>
       <c r="I138" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J138">
         <v>2031801</v>
@@ -7657,13 +7669,13 @@
         <v>1301802</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E139">
         <v>3</v>
       </c>
       <c r="F139" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -7672,7 +7684,7 @@
         <v>1</v>
       </c>
       <c r="I139" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J139">
         <v>2031802</v>
@@ -7695,13 +7707,13 @@
         <v>1302001</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E140">
         <v>3</v>
       </c>
       <c r="F140" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -7710,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="I140" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J140">
         <v>2032001</v>
@@ -7733,13 +7745,13 @@
         <v>1302002</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E141">
         <v>3</v>
       </c>
       <c r="F141" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -7748,7 +7760,7 @@
         <v>1</v>
       </c>
       <c r="I141" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J141">
         <v>2032002</v>
@@ -7771,13 +7783,13 @@
         <v>1302201</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E142">
         <v>3</v>
       </c>
       <c r="F142" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -7786,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="I142" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J142">
         <v>2032201</v>
@@ -7809,13 +7821,13 @@
         <v>1302202</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E143">
         <v>3</v>
       </c>
       <c r="F143" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -7824,7 +7836,7 @@
         <v>1</v>
       </c>
       <c r="I143" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J143">
         <v>2032202</v>
@@ -7847,13 +7859,13 @@
         <v>1202501</v>
       </c>
       <c r="D144" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E144">
         <v>2</v>
       </c>
       <c r="F144" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -7862,13 +7874,13 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J144">
         <v>2022501</v>
       </c>
       <c r="K144" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="N144">
         <v>999</v>
@@ -7888,13 +7900,13 @@
         <v>1202502</v>
       </c>
       <c r="D145" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E145">
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -7903,13 +7915,13 @@
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J145">
         <v>2022502</v>
       </c>
       <c r="K145" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N145">
         <v>999</v>
@@ -7929,13 +7941,13 @@
         <v>1202503</v>
       </c>
       <c r="D146" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E146">
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -7944,13 +7956,13 @@
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="J146">
         <v>2022503</v>
       </c>
       <c r="K146" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N146">
         <v>999</v>
@@ -7970,13 +7982,13 @@
         <v>1202504</v>
       </c>
       <c r="D147" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -7985,13 +7997,13 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="J147">
         <v>2022504</v>
       </c>
       <c r="K147" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="N147">
         <v>999999999</v>
@@ -8006,13 +8018,13 @@
         <v>1023001</v>
       </c>
       <c r="D148" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E148">
         <v>2</v>
       </c>
       <c r="F148" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G148">
         <v>2</v>
@@ -8021,19 +8033,19 @@
         <v>0</v>
       </c>
       <c r="I148" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J148">
         <v>2023001</v>
       </c>
       <c r="K148" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N148">
         <v>999</v>
       </c>
       <c r="Q148">
-        <v>0.2</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="149" ht="21" customHeight="1" spans="1:17">
@@ -8045,13 +8057,13 @@
         <v>1023002</v>
       </c>
       <c r="D149" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E149">
         <v>2</v>
       </c>
       <c r="F149" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G149">
         <v>3</v>
@@ -8060,19 +8072,19 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J149">
         <v>2023002</v>
       </c>
       <c r="K149" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N149">
         <v>999</v>
       </c>
       <c r="Q149">
-        <v>0.3</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="150" ht="21" customHeight="1" spans="1:17">
@@ -8084,13 +8096,13 @@
         <v>1023003</v>
       </c>
       <c r="D150" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E150">
         <v>2</v>
       </c>
       <c r="F150" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G150">
         <v>4</v>
@@ -8099,19 +8111,19 @@
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J150">
         <v>2023003</v>
       </c>
       <c r="K150" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N150">
         <v>999</v>
       </c>
       <c r="Q150">
-        <v>0.4</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="151" ht="21" customHeight="1" spans="1:17">
@@ -8123,13 +8135,13 @@
         <v>1023004</v>
       </c>
       <c r="D151" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E151">
         <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G151">
         <v>5</v>
@@ -8138,19 +8150,19 @@
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J151">
         <v>2023004</v>
       </c>
       <c r="K151" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N151">
         <v>999</v>
       </c>
       <c r="Q151">
-        <v>0.6</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="152" ht="21" customHeight="1" spans="1:17">
@@ -8162,13 +8174,13 @@
         <v>1023005</v>
       </c>
       <c r="D152" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E152">
         <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G152">
         <v>6</v>
@@ -8177,19 +8189,19 @@
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J152">
         <v>2023005</v>
       </c>
       <c r="K152" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N152">
         <v>999</v>
       </c>
       <c r="Q152">
-        <v>1.2</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="153" ht="21" customHeight="1" spans="1:17">
@@ -8201,13 +8213,13 @@
         <v>1023101</v>
       </c>
       <c r="D153" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E153">
         <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G153">
         <v>2</v>
@@ -8216,19 +8228,19 @@
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J153">
         <v>2023101</v>
       </c>
       <c r="K153" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N153">
         <v>999</v>
       </c>
       <c r="Q153">
-        <v>0.6</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="154" ht="21" customHeight="1" spans="1:17">
@@ -8240,13 +8252,13 @@
         <v>1023102</v>
       </c>
       <c r="D154" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E154">
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G154">
         <v>3</v>
@@ -8255,19 +8267,19 @@
         <v>0</v>
       </c>
       <c r="I154" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J154">
         <v>2023102</v>
       </c>
       <c r="K154" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N154">
         <v>999</v>
       </c>
       <c r="Q154">
-        <v>0.9</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="155" ht="21" customHeight="1" spans="1:17">
@@ -8279,13 +8291,13 @@
         <v>1023103</v>
       </c>
       <c r="D155" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E155">
         <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G155">
         <v>4</v>
@@ -8294,19 +8306,19 @@
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J155">
         <v>2023103</v>
       </c>
       <c r="K155" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N155">
         <v>999</v>
       </c>
       <c r="Q155">
-        <v>1.2</v>
+        <v>0.0129</v>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1" spans="1:17">
@@ -8318,13 +8330,13 @@
         <v>1023104</v>
       </c>
       <c r="D156" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E156">
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G156">
         <v>5</v>
@@ -8333,19 +8345,19 @@
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="J156">
         <v>2023104</v>
       </c>
       <c r="K156" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N156">
         <v>999</v>
       </c>
       <c r="Q156">
-        <v>1.8</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="157" ht="21" customHeight="1" spans="1:17">
@@ -8357,13 +8369,13 @@
         <v>1023105</v>
       </c>
       <c r="D157" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E157">
         <v>2</v>
       </c>
       <c r="F157" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G157">
         <v>6</v>
@@ -8372,19 +8384,19 @@
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="J157">
         <v>2023105</v>
       </c>
       <c r="K157" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N157">
         <v>999</v>
       </c>
       <c r="Q157">
-        <v>3.6</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="158" ht="21" customHeight="1" spans="1:17">
@@ -8396,13 +8408,13 @@
         <v>1023201</v>
       </c>
       <c r="D158" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E158">
         <v>2</v>
       </c>
       <c r="F158" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G158">
         <v>2</v>
@@ -8411,19 +8423,19 @@
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="J158">
         <v>2023201</v>
       </c>
       <c r="K158" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N158">
         <v>999</v>
       </c>
       <c r="Q158">
-        <v>2.4</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="159" ht="21" customHeight="1" spans="1:17">
@@ -8435,13 +8447,13 @@
         <v>1023202</v>
       </c>
       <c r="D159" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E159">
         <v>2</v>
       </c>
       <c r="F159" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G159">
         <v>3</v>
@@ -8450,19 +8462,19 @@
         <v>0</v>
       </c>
       <c r="I159" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="J159">
         <v>2023202</v>
       </c>
       <c r="K159" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N159">
         <v>999</v>
       </c>
       <c r="Q159">
-        <v>3.6</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1" spans="1:17">
@@ -8474,13 +8486,13 @@
         <v>1023203</v>
       </c>
       <c r="D160" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E160">
         <v>2</v>
       </c>
       <c r="F160" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G160">
         <v>4</v>
@@ -8489,19 +8501,19 @@
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="J160">
         <v>2023203</v>
       </c>
       <c r="K160" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N160">
         <v>999</v>
       </c>
       <c r="Q160">
-        <v>4.8</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="161" ht="21" customHeight="1" spans="1:17">
@@ -8513,13 +8525,13 @@
         <v>1023204</v>
       </c>
       <c r="D161" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E161">
         <v>2</v>
       </c>
       <c r="F161" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G161">
         <v>5</v>
@@ -8528,19 +8540,19 @@
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J161">
         <v>2023204</v>
       </c>
       <c r="K161" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N161">
         <v>999</v>
       </c>
       <c r="Q161">
-        <v>7.2</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="162" ht="21" customHeight="1" spans="1:17">
@@ -8552,13 +8564,13 @@
         <v>1023205</v>
       </c>
       <c r="D162" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E162">
         <v>2</v>
       </c>
       <c r="F162" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G162">
         <v>6</v>
@@ -8567,19 +8579,19 @@
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J162">
         <v>2023205</v>
       </c>
       <c r="K162" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N162">
         <v>999</v>
       </c>
       <c r="Q162">
-        <v>14.4</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="163" ht="21" customHeight="1" spans="1:17">
@@ -8591,13 +8603,13 @@
         <v>1023301</v>
       </c>
       <c r="D163" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E163">
         <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G163">
         <v>2</v>
@@ -8606,19 +8618,19 @@
         <v>0</v>
       </c>
       <c r="I163" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="J163">
         <v>2023301</v>
       </c>
       <c r="K163" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N163">
         <v>999</v>
       </c>
       <c r="Q163">
-        <v>4.8</v>
+        <v>0.0229</v>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1" spans="1:17">
@@ -8630,13 +8642,13 @@
         <v>1023302</v>
       </c>
       <c r="D164" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E164">
         <v>2</v>
       </c>
       <c r="F164" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G164">
         <v>3</v>
@@ -8645,19 +8657,19 @@
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="J164">
         <v>2023302</v>
       </c>
       <c r="K164" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N164">
         <v>999</v>
       </c>
       <c r="Q164">
-        <v>7.2</v>
+        <v>0.0273</v>
       </c>
     </row>
     <row r="165" ht="21" customHeight="1" spans="1:17">
@@ -8669,13 +8681,13 @@
         <v>1023303</v>
       </c>
       <c r="D165" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E165">
         <v>2</v>
       </c>
       <c r="F165" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G165">
         <v>4</v>
@@ -8684,19 +8696,19 @@
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J165">
         <v>2023303</v>
       </c>
       <c r="K165" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N165">
         <v>999</v>
       </c>
       <c r="Q165">
-        <v>9.6</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1" spans="1:17">
@@ -8708,13 +8720,13 @@
         <v>1023304</v>
       </c>
       <c r="D166" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E166">
         <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G166">
         <v>5</v>
@@ -8723,19 +8735,19 @@
         <v>0</v>
       </c>
       <c r="I166" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J166">
         <v>2023304</v>
       </c>
       <c r="K166" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N166">
         <v>999</v>
       </c>
       <c r="Q166">
-        <v>14.4</v>
+        <v>0.0451</v>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1" spans="1:17">
@@ -8747,13 +8759,13 @@
         <v>1023305</v>
       </c>
       <c r="D167" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E167">
         <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G167">
         <v>6</v>
@@ -8762,19 +8774,19 @@
         <v>0</v>
       </c>
       <c r="I167" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="J167">
         <v>2023305</v>
       </c>
       <c r="K167" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N167">
         <v>999</v>
       </c>
       <c r="Q167">
-        <v>28.8</v>
+        <v>0.0676</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1" spans="1:17">
@@ -8786,13 +8798,13 @@
         <v>1023401</v>
       </c>
       <c r="D168" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E168">
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G168">
         <v>2</v>
@@ -8801,19 +8813,19 @@
         <v>0</v>
       </c>
       <c r="I168" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="J168">
         <v>2023401</v>
       </c>
       <c r="K168" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N168">
         <v>999</v>
       </c>
       <c r="Q168">
-        <v>9.6</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1" spans="1:17">
@@ -8825,13 +8837,13 @@
         <v>1023402</v>
       </c>
       <c r="D169" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E169">
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G169">
         <v>3</v>
@@ -8840,19 +8852,19 @@
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J169">
         <v>2023402</v>
       </c>
       <c r="K169" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N169">
         <v>999</v>
       </c>
       <c r="Q169">
-        <v>14.4</v>
+        <v>0.0546</v>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1" spans="1:17">
@@ -8864,13 +8876,13 @@
         <v>1023403</v>
       </c>
       <c r="D170" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E170">
         <v>2</v>
       </c>
       <c r="F170" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G170">
         <v>4</v>
@@ -8879,19 +8891,19 @@
         <v>0</v>
       </c>
       <c r="I170" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="J170">
         <v>2023403</v>
       </c>
       <c r="K170" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N170">
         <v>999</v>
       </c>
       <c r="Q170">
-        <v>19.2</v>
+        <v>0.0728</v>
       </c>
     </row>
     <row r="171" ht="21" customHeight="1" spans="1:17">
@@ -8903,13 +8915,13 @@
         <v>1023404</v>
       </c>
       <c r="D171" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E171">
         <v>2</v>
       </c>
       <c r="F171" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G171">
         <v>5</v>
@@ -8918,19 +8930,19 @@
         <v>0</v>
       </c>
       <c r="I171" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="J171">
         <v>2023404</v>
       </c>
       <c r="K171" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N171">
         <v>999</v>
       </c>
       <c r="Q171">
-        <v>28.8</v>
+        <v>0.0902</v>
       </c>
     </row>
     <row r="172" ht="21" customHeight="1" spans="1:17">
@@ -8942,13 +8954,13 @@
         <v>1023405</v>
       </c>
       <c r="D172" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E172">
         <v>2</v>
       </c>
       <c r="F172" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G172">
         <v>6</v>
@@ -8957,19 +8969,19 @@
         <v>0</v>
       </c>
       <c r="I172" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="J172">
         <v>2023405</v>
       </c>
       <c r="K172" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N172">
         <v>999</v>
       </c>
       <c r="Q172">
-        <v>57.6</v>
+        <v>0.1352</v>
       </c>
     </row>
     <row r="173" ht="21" customHeight="1" spans="1:17">
@@ -8983,13 +8995,13 @@
         <v>1990000</v>
       </c>
       <c r="D173" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E173">
         <v>99</v>
       </c>
       <c r="F173" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -8998,13 +9010,13 @@
         <v>0</v>
       </c>
       <c r="I173" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="J173">
         <v>2990000</v>
       </c>
       <c r="K173" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="N173">
         <v>-1</v>
@@ -9025,13 +9037,13 @@
         <v>1980000</v>
       </c>
       <c r="D174" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E174">
         <v>98</v>
       </c>
       <c r="F174" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -9040,20 +9052,20 @@
         <v>0</v>
       </c>
       <c r="I174" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="J174">
         <v>2980000</v>
       </c>
       <c r="K174" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="N174">
         <v>-1</v>
       </c>
       <c r="Q174">
-        <f>1/100</f>
-        <v>0.01</v>
+        <f>1/700</f>
+        <v>0.00142857142857143</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -808,7 +808,7 @@
     <t>国旗3</t>
   </si>
   <si>
-    <t>头衔1-财富大亨</t>
+    <t>头衔1-财富贵族</t>
   </si>
   <si>
     <t>daoju1_8.png</t>
@@ -820,43 +820,43 @@
     <t>daoju_9.png</t>
   </si>
   <si>
-    <t>头衔3-招财进宝</t>
+    <t>头衔3-四方来财</t>
   </si>
   <si>
     <t>daoju1_7.png</t>
   </si>
   <si>
-    <t>筹码2-鸿运</t>
+    <t>筹码2-翡翠贵族</t>
   </si>
   <si>
     <t>daoju1_1.png</t>
   </si>
   <si>
-    <t>筹码3-万贯</t>
+    <t>筹码3-水晶皇室</t>
   </si>
   <si>
     <t>daoju1_2.png</t>
   </si>
   <si>
-    <t>牌背2-百宝</t>
+    <t>牌背2-神秘塔罗</t>
   </si>
   <si>
     <t>daoju1_3.png</t>
   </si>
   <si>
-    <t>牌背3-金麟</t>
+    <t>牌背3-命运之手</t>
   </si>
   <si>
     <t>daoju1_4.png</t>
   </si>
   <si>
-    <t>大厅背景2-运动</t>
+    <t>大厅背景2-决赛之夜</t>
   </si>
   <si>
     <t>daoju1_5.png</t>
   </si>
   <si>
-    <t>大厅背景3-星空</t>
+    <t>大厅背景3-度假海滩</t>
   </si>
   <si>
     <t>daoju1_6.png</t>
@@ -7514,7 +7514,7 @@
         <v>1600</v>
       </c>
       <c r="C135" s="3">
-        <v>1301600</v>
+        <v>103001</v>
       </c>
       <c r="D135" s="13" t="s">
         <v>200</v>
@@ -7552,7 +7552,7 @@
         <v>1601</v>
       </c>
       <c r="C136">
-        <v>1301601</v>
+        <v>103002</v>
       </c>
       <c r="D136" s="14" t="s">
         <v>202</v>
@@ -7590,7 +7590,7 @@
         <v>1602</v>
       </c>
       <c r="C137">
-        <v>1301602</v>
+        <v>103003</v>
       </c>
       <c r="D137" s="14" t="s">
         <v>204</v>
@@ -7628,7 +7628,7 @@
         <v>1801</v>
       </c>
       <c r="C138">
-        <v>1301801</v>
+        <v>104002</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>206</v>
@@ -7666,7 +7666,7 @@
         <v>1802</v>
       </c>
       <c r="C139">
-        <v>1301802</v>
+        <v>104003</v>
       </c>
       <c r="D139" s="15" t="s">
         <v>208</v>
@@ -7704,7 +7704,7 @@
         <v>2001</v>
       </c>
       <c r="C140">
-        <v>1302001</v>
+        <v>105002</v>
       </c>
       <c r="D140" s="16" t="s">
         <v>210</v>
@@ -7742,7 +7742,7 @@
         <v>2002</v>
       </c>
       <c r="C141">
-        <v>1302002</v>
+        <v>105003</v>
       </c>
       <c r="D141" s="16" t="s">
         <v>212</v>
@@ -7780,7 +7780,7 @@
         <v>2201</v>
       </c>
       <c r="C142">
-        <v>1302201</v>
+        <v>106002</v>
       </c>
       <c r="D142" s="17" t="s">
         <v>214</v>
@@ -7818,7 +7818,7 @@
         <v>2202</v>
       </c>
       <c r="C143">
-        <v>1302202</v>
+        <v>106003</v>
       </c>
       <c r="D143" s="17" t="s">
         <v>216</v>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -7886,7 +7886,7 @@
         <v>999</v>
       </c>
       <c r="Q144">
-        <v>0.25</v>
+        <v>0.00411628027210884</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1" spans="1:17">

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -2605,7 +2605,7 @@
         <v>1010301</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.0360375324282976</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -2650,7 +2650,8 @@
         <v>1010302</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.0429678271260472</v>
+        <f>Q7*2</f>
+        <v>0.198</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -2695,7 +2696,8 @@
         <v>1010303</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.0572904361680629</v>
+        <f>Q7*6</f>
+        <v>0.594</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -2740,7 +2742,8 @@
         <v>1010304</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.0709310162080779</v>
+        <f>Q7*8</f>
+        <v>0.792</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -2785,7 +2788,8 @@
         <v>1010305</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.106396524312117</v>
+        <f>Q7*10</f>
+        <v>0.99</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
@@ -7886,7 +7890,7 @@
         <v>999</v>
       </c>
       <c r="Q144">
-        <v>0.00411628027210884</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1" spans="1:17">
@@ -7927,7 +7931,7 @@
         <v>999</v>
       </c>
       <c r="Q145">
-        <v>0.99</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1" spans="1:17">
@@ -8045,7 +8049,7 @@
         <v>999</v>
       </c>
       <c r="Q148">
-        <v>0.0038</v>
+        <v>0.000544077728550903</v>
       </c>
     </row>
     <row r="149" ht="21" customHeight="1" spans="1:17">
@@ -8084,7 +8088,7 @@
         <v>999</v>
       </c>
       <c r="Q149">
-        <v>0.0046</v>
+        <v>0.0045080726079932</v>
       </c>
     </row>
     <row r="150" ht="21" customHeight="1" spans="1:17">
@@ -8123,7 +8127,7 @@
         <v>999</v>
       </c>
       <c r="Q150">
-        <v>0.0061</v>
+        <v>0.0067621089119898</v>
       </c>
     </row>
     <row r="151" ht="21" customHeight="1" spans="1:17">
@@ -8162,7 +8166,7 @@
         <v>999</v>
       </c>
       <c r="Q151">
-        <v>0.0075</v>
+        <v>0.012622603302381</v>
       </c>
     </row>
     <row r="152" ht="21" customHeight="1" spans="1:17">
@@ -8201,7 +8205,7 @@
         <v>999</v>
       </c>
       <c r="Q152">
-        <v>0.0113</v>
+        <v>0.0139155435712012</v>
       </c>
     </row>
     <row r="153" ht="21" customHeight="1" spans="1:17">
@@ -8240,7 +8244,7 @@
         <v>999</v>
       </c>
       <c r="Q153">
-        <v>0.0081</v>
+        <v>0.00174104873136289</v>
       </c>
     </row>
     <row r="154" ht="21" customHeight="1" spans="1:17">
@@ -8279,7 +8283,7 @@
         <v>999</v>
       </c>
       <c r="Q154">
-        <v>0.0097</v>
+        <v>0.0144258323455782</v>
       </c>
     </row>
     <row r="155" ht="21" customHeight="1" spans="1:17">
@@ -8318,7 +8322,7 @@
         <v>999</v>
       </c>
       <c r="Q155">
-        <v>0.0129</v>
+        <v>0.0216387485183673</v>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1" spans="1:17">
@@ -8357,7 +8361,7 @@
         <v>999</v>
       </c>
       <c r="Q156">
-        <v>0.016</v>
+        <v>0.0403923305676191</v>
       </c>
     </row>
     <row r="157" ht="21" customHeight="1" spans="1:17">
@@ -8396,7 +8400,7 @@
         <v>999</v>
       </c>
       <c r="Q157">
-        <v>0.024</v>
+        <v>0.0445297394278439</v>
       </c>
     </row>
     <row r="158" ht="21" customHeight="1" spans="1:17">
@@ -8435,7 +8439,7 @@
         <v>999</v>
       </c>
       <c r="Q158">
-        <v>0.0204</v>
+        <v>0.00348209746272578</v>
       </c>
     </row>
     <row r="159" ht="21" customHeight="1" spans="1:17">
@@ -8474,7 +8478,7 @@
         <v>999</v>
       </c>
       <c r="Q159">
-        <v>0.0243</v>
+        <v>0.0288516646911565</v>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1" spans="1:17">
@@ -8513,7 +8517,7 @@
         <v>999</v>
       </c>
       <c r="Q160">
-        <v>0.0324</v>
+        <v>0.0432774970367347</v>
       </c>
     </row>
     <row r="161" ht="21" customHeight="1" spans="1:17">
@@ -8552,7 +8556,7 @@
         <v>999</v>
       </c>
       <c r="Q161">
-        <v>0.0401</v>
+        <v>0.0807846611352381</v>
       </c>
     </row>
     <row r="162" ht="21" customHeight="1" spans="1:17">
@@ -8591,7 +8595,7 @@
         <v>999</v>
       </c>
       <c r="Q162">
-        <v>0.0601</v>
+        <v>0.0890594788556878</v>
       </c>
     </row>
     <row r="163" ht="21" customHeight="1" spans="1:17">
@@ -8630,7 +8634,7 @@
         <v>999</v>
       </c>
       <c r="Q163">
-        <v>0.0229</v>
+        <v>0.0039173596455665</v>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1" spans="1:17">
@@ -8669,7 +8673,7 @@
         <v>999</v>
       </c>
       <c r="Q164">
-        <v>0.0273</v>
+        <v>0.032458122777551</v>
       </c>
     </row>
     <row r="165" ht="21" customHeight="1" spans="1:17">
@@ -8708,7 +8712,7 @@
         <v>999</v>
       </c>
       <c r="Q165">
-        <v>0.0364</v>
+        <v>0.0486871841663265</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1" spans="1:17">
@@ -8747,7 +8751,7 @@
         <v>999</v>
       </c>
       <c r="Q166">
-        <v>0.0451</v>
+        <v>0.0908827437771429</v>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1" spans="1:17">
@@ -8786,7 +8790,7 @@
         <v>999</v>
       </c>
       <c r="Q167">
-        <v>0.0676</v>
+        <v>0.100191913712649</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1" spans="1:17">
@@ -8825,7 +8829,7 @@
         <v>999</v>
       </c>
       <c r="Q168">
-        <v>0.0458</v>
+        <v>0.00783471929113301</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1" spans="1:17">
@@ -8864,7 +8868,7 @@
         <v>999</v>
       </c>
       <c r="Q169">
-        <v>0.0546</v>
+        <v>0.064916245555102</v>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1" spans="1:17">
@@ -8903,7 +8907,7 @@
         <v>999</v>
       </c>
       <c r="Q170">
-        <v>0.0728</v>
+        <v>0.097374368332653</v>
       </c>
     </row>
     <row r="171" ht="21" customHeight="1" spans="1:17">
@@ -8942,7 +8946,7 @@
         <v>999</v>
       </c>
       <c r="Q171">
-        <v>0.0902</v>
+        <v>0.181765487554286</v>
       </c>
     </row>
     <row r="172" ht="21" customHeight="1" spans="1:17">
@@ -8981,7 +8985,7 @@
         <v>999</v>
       </c>
       <c r="Q172">
-        <v>0.1352</v>
+        <v>0.200383827425298</v>
       </c>
     </row>
     <row r="173" ht="21" customHeight="1" spans="1:17">

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -112,7 +112,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+为TRUE时，会调用多语言包内的同名资源</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -134,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="Q1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +228,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="156">
   <si>
     <t>道具ID</t>
   </si>
@@ -232,6 +254,9 @@
     <t>描述多语言ID</t>
   </si>
   <si>
+    <t>是否需要调用多语言</t>
+  </si>
+  <si>
     <t>激活的装扮</t>
   </si>
   <si>
@@ -256,6 +281,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>map&lt;int{_}long&gt;{;}</t>
   </si>
   <si>
@@ -278,6 +306,9 @@
   </si>
   <si>
     <t>text</t>
+  </si>
+  <si>
+    <t>needlanguage</t>
   </si>
   <si>
     <t>avatarID</t>
@@ -1900,7 +1931,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -1913,17 +1944,18 @@
     <col min="8" max="8" width="21.25" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="10" width="13.125" customWidth="1"/>
-    <col min="11" max="11" width="37.6416666666667" customWidth="1"/>
-    <col min="12" max="12" width="10.875" customWidth="1"/>
-    <col min="13" max="13" width="17.25" customWidth="1"/>
-    <col min="14" max="14" width="12.875" customWidth="1"/>
-    <col min="15" max="15" width="20.375" customWidth="1"/>
-    <col min="16" max="16" width="8.375" customWidth="1"/>
-    <col min="17" max="17" width="12.625" customWidth="1"/>
-    <col min="20" max="20" width="9.375"/>
+    <col min="11" max="11" width="15.8833333333333" customWidth="1"/>
+    <col min="12" max="12" width="37.6416666666667" customWidth="1"/>
+    <col min="13" max="13" width="10.875" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="12.875" customWidth="1"/>
+    <col min="16" max="16" width="20.375" customWidth="1"/>
+    <col min="17" max="17" width="8.375" customWidth="1"/>
+    <col min="18" max="18" width="12.625" customWidth="1"/>
+    <col min="21" max="21" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1950,16 +1982,16 @@
       <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="P1" t="s">
@@ -1968,95 +2000,104 @@
       <c r="Q1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="K2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="4"/>
       <c r="M2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="P2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>18</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" t="s">
         <v>27</v>
       </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="P3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
     </row>
-    <row r="5" ht="21" customHeight="1" spans="1:17">
+    <row r="5" ht="21" customHeight="1" spans="1:18">
       <c r="A5">
         <v>1990000</v>
       </c>
@@ -2067,13 +2108,13 @@
         <v>1990000</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2082,23 +2123,26 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J5">
         <v>2990000</v>
       </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5">
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5">
         <v>-1</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <f>1/700000</f>
         <v>1.42857142857143e-6</v>
       </c>
     </row>
-    <row r="6" ht="21" customHeight="1" spans="1:17">
+    <row r="6" ht="21" customHeight="1" spans="1:18">
       <c r="A6">
         <v>1980000</v>
       </c>
@@ -2109,13 +2153,13 @@
         <v>1980000</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -2124,23 +2168,26 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J6">
         <v>2980000</v>
       </c>
-      <c r="K6" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6">
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6">
         <v>-1</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <f>1/700</f>
         <v>0.00142857142857143</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A7" s="1">
         <v>1010301</v>
       </c>
@@ -2151,13 +2198,13 @@
         <v>1100301</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -2166,26 +2213,29 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J7" s="1">
         <v>2010301</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" s="1">
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O7" s="1">
         <v>999</v>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="1">
+      <c r="P7" s="8"/>
+      <c r="Q7" s="1">
         <v>1010301</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>0.099</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A8" s="1">
         <v>1010302</v>
       </c>
@@ -2196,13 +2246,13 @@
         <v>1100302</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -2211,27 +2261,30 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J8" s="1">
         <v>2010302</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8" s="1">
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O8" s="1">
         <v>999</v>
       </c>
-      <c r="O8" s="8"/>
-      <c r="P8" s="1">
+      <c r="P8" s="8"/>
+      <c r="Q8" s="1">
         <v>1010302</v>
       </c>
-      <c r="Q8" s="1">
-        <f>Q7*2</f>
+      <c r="R8" s="1">
+        <f>R7*2</f>
         <v>0.198</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A9" s="1">
         <v>1010303</v>
       </c>
@@ -2242,13 +2295,13 @@
         <v>1100303</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -2257,27 +2310,30 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J9" s="1">
         <v>2010303</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N9" s="1">
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O9" s="1">
         <v>999</v>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="1">
+      <c r="P9" s="8"/>
+      <c r="Q9" s="1">
         <v>1010303</v>
       </c>
-      <c r="Q9" s="1">
-        <f>Q7*6</f>
+      <c r="R9" s="1">
+        <f>R7*6</f>
         <v>0.594</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A10" s="1">
         <v>1010304</v>
       </c>
@@ -2288,13 +2344,13 @@
         <v>1100304</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -2303,27 +2359,30 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J10" s="1">
         <v>2010304</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" s="1">
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="1">
         <v>999</v>
       </c>
-      <c r="O10" s="8"/>
-      <c r="P10" s="1">
+      <c r="P10" s="8"/>
+      <c r="Q10" s="1">
         <v>1010304</v>
       </c>
-      <c r="Q10" s="1">
-        <f>Q7*8</f>
+      <c r="R10" s="1">
+        <f>R7*8</f>
         <v>0.792</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A11" s="1">
         <v>1010305</v>
       </c>
@@ -2334,13 +2393,13 @@
         <v>1100305</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
@@ -2349,27 +2408,30 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J11" s="1">
         <v>2010305</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11" s="1">
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O11" s="1">
         <v>999</v>
       </c>
-      <c r="O11" s="8"/>
-      <c r="P11" s="1">
+      <c r="P11" s="8"/>
+      <c r="Q11" s="1">
         <v>1010305</v>
       </c>
-      <c r="Q11" s="1">
-        <f>Q7*10</f>
+      <c r="R11" s="1">
+        <f>R7*10</f>
         <v>0.99</v>
       </c>
     </row>
-    <row r="12" ht="21" customHeight="1" spans="1:17">
+    <row r="12" ht="21" customHeight="1" spans="1:18">
       <c r="A12">
         <v>1020001</v>
       </c>
@@ -2380,13 +2442,13 @@
         <v>1020001</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2395,19 +2457,22 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J12">
         <v>2020001</v>
       </c>
-      <c r="K12" t="s">
-        <v>53</v>
-      </c>
-      <c r="N12">
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>56</v>
+      </c>
+      <c r="O12">
         <v>999</v>
       </c>
     </row>
-    <row r="13" ht="23.1" customHeight="1" spans="1:17">
+    <row r="13" ht="23.1" customHeight="1" spans="1:18">
       <c r="A13">
         <v>1031001</v>
       </c>
@@ -2418,13 +2483,13 @@
         <v>1301001</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2433,19 +2498,22 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J13">
         <v>2031001</v>
       </c>
-      <c r="L13">
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>2</v>
       </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="23.1" customHeight="1" spans="1:18">
       <c r="A14">
         <v>1031002</v>
       </c>
@@ -2456,13 +2524,13 @@
         <v>1301002</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2471,19 +2539,22 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J14">
         <v>2031002</v>
       </c>
-      <c r="L14">
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>3</v>
       </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="23.1" customHeight="1" spans="1:18">
       <c r="A15">
         <v>1031201</v>
       </c>
@@ -2494,13 +2565,13 @@
         <v>1301201</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2509,19 +2580,22 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J15">
         <v>2031201</v>
       </c>
-      <c r="L15">
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>1002</v>
       </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="23.1" customHeight="1" spans="1:18">
       <c r="A16">
         <v>1031202</v>
       </c>
@@ -2532,13 +2606,13 @@
         <v>1301202</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -2547,19 +2621,22 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J16">
         <v>2031202</v>
       </c>
-      <c r="L16">
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>1003</v>
       </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="23.1" customHeight="1" spans="1:18">
       <c r="A17">
         <v>1031350</v>
       </c>
@@ -2570,13 +2647,13 @@
         <v>101801</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -2585,19 +2662,22 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J17">
         <v>201801</v>
       </c>
-      <c r="L17" s="2">
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
         <v>1005</v>
       </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="23.1" customHeight="1" spans="1:18">
       <c r="A18">
         <v>1031351</v>
       </c>
@@ -2608,13 +2688,13 @@
         <v>101802</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2623,19 +2703,22 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J18">
         <v>201802</v>
       </c>
-      <c r="L18" s="2">
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
         <v>1006</v>
       </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="23.1" customHeight="1" spans="1:18">
       <c r="A19">
         <v>1021401</v>
       </c>
@@ -2646,13 +2729,13 @@
         <v>1201401</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -2661,19 +2744,22 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J19">
         <v>2021401</v>
       </c>
-      <c r="L19">
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>2002</v>
       </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="23.1" customHeight="1" spans="1:18">
       <c r="A20">
         <v>1021402</v>
       </c>
@@ -2684,13 +2770,13 @@
         <v>1201402</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2699,19 +2785,22 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J20">
         <v>2021402</v>
       </c>
-      <c r="L20">
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>2003</v>
       </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="23.1" customHeight="1" spans="1:18">
       <c r="A21" s="2">
         <v>1031600</v>
       </c>
@@ -2722,13 +2811,13 @@
         <v>103001</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2">
         <v>3</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -2737,19 +2826,22 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J21" s="2">
         <v>2031600</v>
       </c>
-      <c r="L21" s="2">
+      <c r="K21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2">
         <v>3001</v>
       </c>
-      <c r="N21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="23.1" customHeight="1" spans="1:18">
       <c r="A22">
         <v>1031601</v>
       </c>
@@ -2760,13 +2852,13 @@
         <v>103002</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2775,19 +2867,22 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J22">
         <v>2031601</v>
       </c>
-      <c r="L22">
+      <c r="K22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22">
         <v>3002</v>
       </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="23.1" customHeight="1" spans="1:18">
       <c r="A23">
         <v>1031602</v>
       </c>
@@ -2798,13 +2893,13 @@
         <v>103003</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2813,19 +2908,22 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J23">
         <v>2031602</v>
       </c>
-      <c r="L23">
+      <c r="K23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23">
         <v>3003</v>
       </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="23.1" customHeight="1" spans="1:18">
       <c r="A24">
         <v>1031801</v>
       </c>
@@ -2836,13 +2934,13 @@
         <v>104002</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2851,19 +2949,22 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J24">
         <v>2031801</v>
       </c>
-      <c r="L24">
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>4002</v>
       </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="23.1" customHeight="1" spans="1:18">
       <c r="A25">
         <v>1031802</v>
       </c>
@@ -2874,13 +2975,13 @@
         <v>104003</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2889,19 +2990,22 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J25">
         <v>2031802</v>
       </c>
-      <c r="L25">
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>4003</v>
       </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="23.1" customHeight="1" spans="1:18">
       <c r="A26">
         <v>1032001</v>
       </c>
@@ -2912,13 +3016,13 @@
         <v>105002</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2927,19 +3031,22 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J26">
         <v>2032001</v>
       </c>
-      <c r="L26">
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>5002</v>
       </c>
-      <c r="N26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="23.1" customHeight="1" spans="1:18">
       <c r="A27">
         <v>1032002</v>
       </c>
@@ -2950,13 +3057,13 @@
         <v>105003</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2965,19 +3072,22 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J27">
         <v>2032002</v>
       </c>
-      <c r="L27">
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>5003</v>
       </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="23.1" customHeight="1" spans="1:18">
       <c r="A28">
         <v>1032201</v>
       </c>
@@ -2988,13 +3098,13 @@
         <v>106002</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3003,19 +3113,22 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J28">
         <v>2032201</v>
       </c>
-      <c r="L28">
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>6002</v>
       </c>
-      <c r="N28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" ht="23.1" customHeight="1" spans="1:17">
+      <c r="O28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="23.1" customHeight="1" spans="1:18">
       <c r="A29">
         <v>1032202</v>
       </c>
@@ -3026,13 +3139,13 @@
         <v>106003</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3041,19 +3154,22 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J29">
         <v>2032202</v>
       </c>
-      <c r="L29">
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>6003</v>
       </c>
-      <c r="N29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:17">
+      <c r="O29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:18">
       <c r="A30">
         <v>1022501</v>
       </c>
@@ -3064,13 +3180,13 @@
         <v>1202501</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E30">
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3079,22 +3195,25 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J30">
         <v>2022501</v>
       </c>
-      <c r="K30" t="s">
-        <v>89</v>
-      </c>
-      <c r="N30">
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
+        <v>92</v>
+      </c>
+      <c r="O30">
         <v>999</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>0.003</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1" spans="1:17">
+    <row r="31" ht="18" customHeight="1" spans="1:18">
       <c r="A31">
         <v>1022502</v>
       </c>
@@ -3105,13 +3224,13 @@
         <v>1202502</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -3120,22 +3239,25 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J31">
         <v>2022502</v>
       </c>
-      <c r="K31" t="s">
-        <v>92</v>
-      </c>
-      <c r="N31">
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
+        <v>95</v>
+      </c>
+      <c r="O31">
         <v>999</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>0.495</v>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1" spans="1:17">
+    <row r="32" ht="18" customHeight="1" spans="1:18">
       <c r="A32">
         <v>1022503</v>
       </c>
@@ -3146,13 +3268,13 @@
         <v>1202503</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -3161,22 +3283,25 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J32">
         <v>2022503</v>
       </c>
-      <c r="K32" t="s">
-        <v>92</v>
-      </c>
-      <c r="N32">
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="s">
+        <v>95</v>
+      </c>
+      <c r="O32">
         <v>999</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>0.99</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1" spans="1:17">
+    <row r="33" ht="18" customHeight="1" spans="1:18">
       <c r="A33">
         <v>1022504</v>
       </c>
@@ -3187,13 +3312,13 @@
         <v>1202504</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3202,19 +3327,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J33">
         <v>2022504</v>
       </c>
-      <c r="K33" t="s">
-        <v>97</v>
-      </c>
-      <c r="N33">
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="s">
+        <v>100</v>
+      </c>
+      <c r="O33">
         <v>999999999</v>
       </c>
     </row>
-    <row r="34" ht="21" customHeight="1" spans="1:17">
+    <row r="34" ht="21" customHeight="1" spans="1:18">
       <c r="A34">
         <v>1023001</v>
       </c>
@@ -3223,13 +3351,13 @@
         <v>1023001</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -3238,22 +3366,25 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J34">
         <v>2023001</v>
       </c>
-      <c r="K34" t="s">
-        <v>100</v>
-      </c>
-      <c r="N34">
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="s">
+        <v>103</v>
+      </c>
+      <c r="O34">
         <v>999</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>0.000544077728550903</v>
       </c>
     </row>
-    <row r="35" ht="21" customHeight="1" spans="1:17">
+    <row r="35" ht="21" customHeight="1" spans="1:18">
       <c r="A35">
         <v>1023002</v>
       </c>
@@ -3262,13 +3393,13 @@
         <v>1023002</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -3277,22 +3408,25 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J35">
         <v>2023002</v>
       </c>
-      <c r="K35" t="s">
-        <v>100</v>
-      </c>
-      <c r="N35">
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s">
+        <v>103</v>
+      </c>
+      <c r="O35">
         <v>999</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>0.0045080726079932</v>
       </c>
     </row>
-    <row r="36" ht="21" customHeight="1" spans="1:17">
+    <row r="36" ht="21" customHeight="1" spans="1:18">
       <c r="A36">
         <v>1023003</v>
       </c>
@@ -3301,13 +3435,13 @@
         <v>1023003</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -3316,22 +3450,25 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J36">
         <v>2023003</v>
       </c>
-      <c r="K36" t="s">
-        <v>100</v>
-      </c>
-      <c r="N36">
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="s">
+        <v>103</v>
+      </c>
+      <c r="O36">
         <v>999</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>0.0067621089119898</v>
       </c>
     </row>
-    <row r="37" ht="21" customHeight="1" spans="1:17">
+    <row r="37" ht="21" customHeight="1" spans="1:18">
       <c r="A37">
         <v>1023004</v>
       </c>
@@ -3340,13 +3477,13 @@
         <v>1023004</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -3355,22 +3492,25 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J37">
         <v>2023004</v>
       </c>
-      <c r="K37" t="s">
-        <v>100</v>
-      </c>
-      <c r="N37">
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="s">
+        <v>103</v>
+      </c>
+      <c r="O37">
         <v>999</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>0.012622603302381</v>
       </c>
     </row>
-    <row r="38" ht="21" customHeight="1" spans="1:17">
+    <row r="38" ht="21" customHeight="1" spans="1:18">
       <c r="A38">
         <v>1023005</v>
       </c>
@@ -3379,13 +3519,13 @@
         <v>1023005</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G38">
         <v>6</v>
@@ -3394,22 +3534,25 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J38">
         <v>2023005</v>
       </c>
-      <c r="K38" t="s">
-        <v>100</v>
-      </c>
-      <c r="N38">
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="s">
+        <v>103</v>
+      </c>
+      <c r="O38">
         <v>999</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>0.0139155435712012</v>
       </c>
     </row>
-    <row r="39" ht="21" customHeight="1" spans="1:17">
+    <row r="39" ht="21" customHeight="1" spans="1:18">
       <c r="A39">
         <v>1023101</v>
       </c>
@@ -3418,13 +3561,13 @@
         <v>1023101</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E39">
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -3433,22 +3576,25 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J39">
         <v>2023101</v>
       </c>
-      <c r="K39" t="s">
-        <v>111</v>
-      </c>
-      <c r="N39">
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="s">
+        <v>114</v>
+      </c>
+      <c r="O39">
         <v>999</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <v>0.00174104873136289</v>
       </c>
     </row>
-    <row r="40" ht="21" customHeight="1" spans="1:17">
+    <row r="40" ht="21" customHeight="1" spans="1:18">
       <c r="A40">
         <v>1023102</v>
       </c>
@@ -3457,13 +3603,13 @@
         <v>1023102</v>
       </c>
       <c r="D40" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -3472,22 +3618,25 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J40">
         <v>2023102</v>
       </c>
-      <c r="K40" t="s">
-        <v>111</v>
-      </c>
-      <c r="N40">
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="s">
+        <v>114</v>
+      </c>
+      <c r="O40">
         <v>999</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>0.0144258323455782</v>
       </c>
     </row>
-    <row r="41" ht="21" customHeight="1" spans="1:17">
+    <row r="41" ht="21" customHeight="1" spans="1:18">
       <c r="A41">
         <v>1023103</v>
       </c>
@@ -3496,13 +3645,13 @@
         <v>1023103</v>
       </c>
       <c r="D41" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -3511,22 +3660,25 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J41">
         <v>2023103</v>
       </c>
-      <c r="K41" t="s">
-        <v>111</v>
-      </c>
-      <c r="N41">
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="s">
+        <v>114</v>
+      </c>
+      <c r="O41">
         <v>999</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>0.0216387485183673</v>
       </c>
     </row>
-    <row r="42" ht="21" customHeight="1" spans="1:17">
+    <row r="42" ht="21" customHeight="1" spans="1:18">
       <c r="A42">
         <v>1023104</v>
       </c>
@@ -3535,13 +3687,13 @@
         <v>1023104</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E42">
         <v>2</v>
       </c>
       <c r="F42" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G42">
         <v>5</v>
@@ -3550,22 +3702,25 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J42">
         <v>2023104</v>
       </c>
-      <c r="K42" t="s">
-        <v>111</v>
-      </c>
-      <c r="N42">
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="s">
+        <v>114</v>
+      </c>
+      <c r="O42">
         <v>999</v>
       </c>
-      <c r="Q42">
+      <c r="R42">
         <v>0.0403923305676191</v>
       </c>
     </row>
-    <row r="43" ht="21" customHeight="1" spans="1:17">
+    <row r="43" ht="21" customHeight="1" spans="1:18">
       <c r="A43">
         <v>1023105</v>
       </c>
@@ -3574,13 +3729,13 @@
         <v>1023105</v>
       </c>
       <c r="D43" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G43">
         <v>6</v>
@@ -3589,22 +3744,25 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J43">
         <v>2023105</v>
       </c>
-      <c r="K43" t="s">
-        <v>111</v>
-      </c>
-      <c r="N43">
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="s">
+        <v>114</v>
+      </c>
+      <c r="O43">
         <v>999</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>0.0445297394278439</v>
       </c>
     </row>
-    <row r="44" ht="21" customHeight="1" spans="1:17">
+    <row r="44" ht="21" customHeight="1" spans="1:18">
       <c r="A44">
         <v>1023201</v>
       </c>
@@ -3613,13 +3771,13 @@
         <v>1023201</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E44">
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -3628,22 +3786,25 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J44">
         <v>2023201</v>
       </c>
-      <c r="K44" t="s">
-        <v>122</v>
-      </c>
-      <c r="N44">
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="s">
+        <v>125</v>
+      </c>
+      <c r="O44">
         <v>999</v>
       </c>
-      <c r="Q44">
+      <c r="R44">
         <v>0.00348209746272578</v>
       </c>
     </row>
-    <row r="45" ht="21" customHeight="1" spans="1:17">
+    <row r="45" ht="21" customHeight="1" spans="1:18">
       <c r="A45">
         <v>1023202</v>
       </c>
@@ -3652,13 +3813,13 @@
         <v>1023202</v>
       </c>
       <c r="D45" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E45">
         <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G45">
         <v>3</v>
@@ -3667,22 +3828,25 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J45">
         <v>2023202</v>
       </c>
-      <c r="K45" t="s">
-        <v>122</v>
-      </c>
-      <c r="N45">
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
+        <v>125</v>
+      </c>
+      <c r="O45">
         <v>999</v>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <v>0.0288516646911565</v>
       </c>
     </row>
-    <row r="46" ht="21" customHeight="1" spans="1:17">
+    <row r="46" ht="21" customHeight="1" spans="1:18">
       <c r="A46">
         <v>1023203</v>
       </c>
@@ -3691,13 +3855,13 @@
         <v>1023203</v>
       </c>
       <c r="D46" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E46">
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -3706,22 +3870,25 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J46">
         <v>2023203</v>
       </c>
-      <c r="K46" t="s">
-        <v>122</v>
-      </c>
-      <c r="N46">
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="s">
+        <v>125</v>
+      </c>
+      <c r="O46">
         <v>999</v>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <v>0.0432774970367347</v>
       </c>
     </row>
-    <row r="47" ht="21" customHeight="1" spans="1:17">
+    <row r="47" ht="21" customHeight="1" spans="1:18">
       <c r="A47">
         <v>1023204</v>
       </c>
@@ -3730,13 +3897,13 @@
         <v>1023204</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G47">
         <v>5</v>
@@ -3745,22 +3912,25 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J47">
         <v>2023204</v>
       </c>
-      <c r="K47" t="s">
-        <v>122</v>
-      </c>
-      <c r="N47">
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>125</v>
+      </c>
+      <c r="O47">
         <v>999</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>0.0807846611352381</v>
       </c>
     </row>
-    <row r="48" ht="21" customHeight="1" spans="1:17">
+    <row r="48" ht="21" customHeight="1" spans="1:18">
       <c r="A48">
         <v>1023205</v>
       </c>
@@ -3769,13 +3939,13 @@
         <v>1023205</v>
       </c>
       <c r="D48" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -3784,22 +3954,25 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J48">
         <v>2023205</v>
       </c>
-      <c r="K48" t="s">
-        <v>122</v>
-      </c>
-      <c r="N48">
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
+        <v>125</v>
+      </c>
+      <c r="O48">
         <v>999</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>0.0890594788556878</v>
       </c>
     </row>
-    <row r="49" ht="21" customHeight="1" spans="1:17">
+    <row r="49" ht="21" customHeight="1" spans="1:18">
       <c r="A49">
         <v>1023301</v>
       </c>
@@ -3808,13 +3981,13 @@
         <v>1023301</v>
       </c>
       <c r="D49" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E49">
         <v>2</v>
       </c>
       <c r="F49" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -3823,22 +3996,25 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J49">
         <v>2023301</v>
       </c>
-      <c r="K49" t="s">
-        <v>133</v>
-      </c>
-      <c r="N49">
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="s">
+        <v>136</v>
+      </c>
+      <c r="O49">
         <v>999</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <v>0.0039173596455665</v>
       </c>
     </row>
-    <row r="50" ht="21" customHeight="1" spans="1:17">
+    <row r="50" ht="21" customHeight="1" spans="1:18">
       <c r="A50">
         <v>1023302</v>
       </c>
@@ -3847,13 +4023,13 @@
         <v>1023302</v>
       </c>
       <c r="D50" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E50">
         <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G50">
         <v>3</v>
@@ -3862,22 +4038,25 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J50">
         <v>2023302</v>
       </c>
-      <c r="K50" t="s">
-        <v>133</v>
-      </c>
-      <c r="N50">
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="s">
+        <v>136</v>
+      </c>
+      <c r="O50">
         <v>999</v>
       </c>
-      <c r="Q50">
+      <c r="R50">
         <v>0.032458122777551</v>
       </c>
     </row>
-    <row r="51" ht="21" customHeight="1" spans="1:17">
+    <row r="51" ht="21" customHeight="1" spans="1:18">
       <c r="A51">
         <v>1023303</v>
       </c>
@@ -3886,13 +4065,13 @@
         <v>1023303</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E51">
         <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G51">
         <v>4</v>
@@ -3901,22 +4080,25 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J51">
         <v>2023303</v>
       </c>
-      <c r="K51" t="s">
-        <v>133</v>
-      </c>
-      <c r="N51">
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
+        <v>136</v>
+      </c>
+      <c r="O51">
         <v>999</v>
       </c>
-      <c r="Q51">
+      <c r="R51">
         <v>0.0486871841663265</v>
       </c>
     </row>
-    <row r="52" ht="21" customHeight="1" spans="1:17">
+    <row r="52" ht="21" customHeight="1" spans="1:18">
       <c r="A52">
         <v>1023304</v>
       </c>
@@ -3925,13 +4107,13 @@
         <v>1023304</v>
       </c>
       <c r="D52" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -3940,22 +4122,25 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J52">
         <v>2023304</v>
       </c>
-      <c r="K52" t="s">
-        <v>133</v>
-      </c>
-      <c r="N52">
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="s">
+        <v>136</v>
+      </c>
+      <c r="O52">
         <v>999</v>
       </c>
-      <c r="Q52">
+      <c r="R52">
         <v>0.0908827437771429</v>
       </c>
     </row>
-    <row r="53" ht="21" customHeight="1" spans="1:17">
+    <row r="53" ht="21" customHeight="1" spans="1:18">
       <c r="A53">
         <v>1023305</v>
       </c>
@@ -3964,13 +4149,13 @@
         <v>1023305</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E53">
         <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G53">
         <v>6</v>
@@ -3979,22 +4164,25 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J53">
         <v>2023305</v>
       </c>
-      <c r="K53" t="s">
-        <v>133</v>
-      </c>
-      <c r="N53">
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O53">
         <v>999</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>0.100191913712649</v>
       </c>
     </row>
-    <row r="54" ht="21" customHeight="1" spans="1:17">
+    <row r="54" ht="21" customHeight="1" spans="1:18">
       <c r="A54">
         <v>1023401</v>
       </c>
@@ -4003,13 +4191,13 @@
         <v>1023401</v>
       </c>
       <c r="D54" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E54">
         <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -4018,22 +4206,25 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J54">
         <v>2023401</v>
       </c>
-      <c r="K54" t="s">
-        <v>144</v>
-      </c>
-      <c r="N54">
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="s">
+        <v>147</v>
+      </c>
+      <c r="O54">
         <v>999</v>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <v>0.00783471929113301</v>
       </c>
     </row>
-    <row r="55" ht="21" customHeight="1" spans="1:17">
+    <row r="55" ht="21" customHeight="1" spans="1:18">
       <c r="A55">
         <v>1023402</v>
       </c>
@@ -4042,13 +4233,13 @@
         <v>1023402</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E55">
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -4057,22 +4248,25 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J55">
         <v>2023402</v>
       </c>
-      <c r="K55" t="s">
-        <v>144</v>
-      </c>
-      <c r="N55">
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>147</v>
+      </c>
+      <c r="O55">
         <v>999</v>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <v>0.064916245555102</v>
       </c>
     </row>
-    <row r="56" ht="21" customHeight="1" spans="1:17">
+    <row r="56" ht="21" customHeight="1" spans="1:18">
       <c r="A56">
         <v>1023403</v>
       </c>
@@ -4081,13 +4275,13 @@
         <v>1023403</v>
       </c>
       <c r="D56" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E56">
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G56">
         <v>4</v>
@@ -4096,22 +4290,25 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J56">
         <v>2023403</v>
       </c>
-      <c r="K56" t="s">
-        <v>144</v>
-      </c>
-      <c r="N56">
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="s">
+        <v>147</v>
+      </c>
+      <c r="O56">
         <v>999</v>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <v>0.097374368332653</v>
       </c>
     </row>
-    <row r="57" ht="21" customHeight="1" spans="1:17">
+    <row r="57" ht="21" customHeight="1" spans="1:18">
       <c r="A57">
         <v>1023404</v>
       </c>
@@ -4120,13 +4317,13 @@
         <v>1023404</v>
       </c>
       <c r="D57" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E57">
         <v>2</v>
       </c>
       <c r="F57" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G57">
         <v>5</v>
@@ -4135,22 +4332,25 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J57">
         <v>2023404</v>
       </c>
-      <c r="K57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N57">
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="s">
+        <v>147</v>
+      </c>
+      <c r="O57">
         <v>999</v>
       </c>
-      <c r="Q57">
+      <c r="R57">
         <v>0.181765487554286</v>
       </c>
     </row>
-    <row r="58" ht="21" customHeight="1" spans="1:17">
+    <row r="58" ht="21" customHeight="1" spans="1:18">
       <c r="A58">
         <v>1023405</v>
       </c>
@@ -4159,13 +4359,13 @@
         <v>1023405</v>
       </c>
       <c r="D58" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E58">
         <v>2</v>
       </c>
       <c r="F58" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -4174,18 +4374,21 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J58">
         <v>2023405</v>
       </c>
-      <c r="K58" t="s">
-        <v>144</v>
-      </c>
-      <c r="N58">
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="s">
+        <v>147</v>
+      </c>
+      <c r="O58">
         <v>999</v>
       </c>
-      <c r="Q58">
+      <c r="R58">
         <v>0.200383827425298</v>
       </c>
     </row>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -201,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0">
+    <comment ref="F16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -347,6 +347,42 @@
     <t>在私密房间内下注时需要用的货币，同时是使用部分功能需要消耗的特殊货币</t>
   </si>
   <si>
+    <t>白金卡</t>
+  </si>
+  <si>
+    <t>常规道具</t>
+  </si>
+  <si>
+    <t>itemicon_1020001.png</t>
+  </si>
+  <si>
+    <t>创建私人包房时可以抵扣钻石</t>
+  </si>
+  <si>
+    <t>祈福卡</t>
+  </si>
+  <si>
+    <t>daoju_4.png</t>
+  </si>
+  <si>
+    <t>在搖錢樹活動中祈福使用，可在指定禮包中購買獲得</t>
+  </si>
+  <si>
+    <t>刮刮卡</t>
+  </si>
+  <si>
+    <t>daoju_5.png</t>
+  </si>
+  <si>
+    <t>在指定的游戏中产出</t>
+  </si>
+  <si>
+    <t>夺宝优惠券</t>
+  </si>
+  <si>
+    <t>itemicon_duobaoquan.png</t>
+  </si>
+  <si>
     <t>赌场工具（普通）</t>
   </si>
   <si>
@@ -389,18 +425,6 @@
     <t>使用后随机获得1~5星赌场建筑升级道具</t>
   </si>
   <si>
-    <t>白金卡</t>
-  </si>
-  <si>
-    <t>常规道具</t>
-  </si>
-  <si>
-    <t>itemicon_1020001.png</t>
-  </si>
-  <si>
-    <t>创建私人包房时可以抵扣钻石</t>
-  </si>
-  <si>
     <t>头像2</t>
   </si>
   <si>
@@ -498,30 +522,6 @@
   </si>
   <si>
     <t>daoju1_6.png</t>
-  </si>
-  <si>
-    <t>祈福卡</t>
-  </si>
-  <si>
-    <t>daoju_4.png</t>
-  </si>
-  <si>
-    <t>在搖錢樹活動中祈福使用，可在指定禮包中購買獲得</t>
-  </si>
-  <si>
-    <t>刮刮卡</t>
-  </si>
-  <si>
-    <t>daoju_5.png</t>
-  </si>
-  <si>
-    <t>在指定的游戏中产出</t>
-  </si>
-  <si>
-    <t>夺宝优惠券</t>
-  </si>
-  <si>
-    <t>itemicon_duobaoquan.png</t>
   </si>
   <si>
     <t>积分</t>
@@ -2187,210 +2187,188 @@
         <v>0.00142857142857143</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
-      <c r="A7" s="1">
-        <v>1010301</v>
-      </c>
-      <c r="B7" s="1">
-        <v>301</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1100301</v>
-      </c>
-      <c r="D7" s="1" t="s">
+    <row r="7" ht="21" customHeight="1" spans="1:18">
+      <c r="A7">
+        <v>1020001</v>
+      </c>
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1020001</v>
+      </c>
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="E7">
         <v>2</v>
       </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="1">
-        <v>2010301</v>
+      <c r="J7">
+        <v>2020001</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" t="s">
         <v>42</v>
       </c>
-      <c r="O7" s="1">
+      <c r="O7">
         <v>999</v>
       </c>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="1">
-        <v>1010301</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0.099</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
-      <c r="A8" s="1">
-        <v>1010302</v>
-      </c>
-      <c r="B8" s="1">
-        <v>302</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1100302</v>
-      </c>
-      <c r="D8" s="1" t="s">
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:18">
+      <c r="A8">
+        <v>1022501</v>
+      </c>
+      <c r="B8">
+        <v>2501</v>
+      </c>
+      <c r="C8">
+        <v>1202501</v>
+      </c>
+      <c r="D8" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="1">
-        <v>3</v>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="1">
-        <v>2010302</v>
+      <c r="J8">
+        <v>2022501</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O8" s="1">
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8">
         <v>999</v>
       </c>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="1">
-        <v>1010302</v>
-      </c>
-      <c r="R8" s="1">
-        <f>R7*2</f>
-        <v>0.198</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
-      <c r="A9" s="1">
-        <v>1010303</v>
-      </c>
-      <c r="B9" s="1">
-        <v>303</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1100303</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="1">
-        <v>4</v>
+      <c r="R8">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:18">
+      <c r="A9">
+        <v>1022502</v>
+      </c>
+      <c r="B9">
+        <v>2502</v>
+      </c>
+      <c r="C9">
+        <v>1202502</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="1">
-        <v>2010303</v>
+      <c r="I9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9">
+        <v>2022502</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9">
         <v>999</v>
       </c>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="1">
-        <v>1010303</v>
-      </c>
-      <c r="R9" s="1">
-        <f>R7*6</f>
-        <v>0.594</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
-      <c r="A10" s="1">
-        <v>1010304</v>
-      </c>
-      <c r="B10" s="1">
-        <v>304</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1100304</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="R9">
+        <v>0.495</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:18">
+      <c r="A10">
+        <v>1022503</v>
+      </c>
+      <c r="B10">
+        <v>2503</v>
+      </c>
+      <c r="C10">
+        <v>1202503</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10">
+        <v>2022503</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="1">
-        <v>5</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="1">
-        <v>2010304</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O10" s="1">
+      <c r="O10">
         <v>999</v>
       </c>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="1">
-        <v>1010304</v>
-      </c>
-      <c r="R10" s="1">
-        <f>R7*8</f>
-        <v>0.792</v>
+      <c r="R10">
+        <v>0.99</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A11" s="1">
-        <v>1010305</v>
+        <v>1010301</v>
       </c>
       <c r="B11" s="1">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C11" s="1">
-        <v>1100305</v>
+        <v>1100301</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>51</v>
@@ -2399,220 +2377,251 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G11" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J11" s="1">
-        <v>2010305</v>
+        <v>2010301</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O11" s="1">
         <v>999</v>
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="1">
+        <v>1010301</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+      <c r="A12" s="1">
+        <v>1010302</v>
+      </c>
+      <c r="B12" s="1">
+        <v>302</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1100302</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2010302</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="1">
+        <v>999</v>
+      </c>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="1">
+        <v>1010302</v>
+      </c>
+      <c r="R12" s="1">
+        <f>R11*2</f>
+        <v>0.198</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+      <c r="A13" s="1">
+        <v>1010303</v>
+      </c>
+      <c r="B13" s="1">
+        <v>303</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1100303</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2010303</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" s="1">
+        <v>999</v>
+      </c>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="1">
+        <v>1010303</v>
+      </c>
+      <c r="R13" s="1">
+        <f>R11*6</f>
+        <v>0.594</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+      <c r="A14" s="1">
+        <v>1010304</v>
+      </c>
+      <c r="B14" s="1">
+        <v>304</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1100304</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="1">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2010304</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O14" s="1">
+        <v>999</v>
+      </c>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="1">
+        <v>1010304</v>
+      </c>
+      <c r="R14" s="1">
+        <f>R11*8</f>
+        <v>0.792</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+      <c r="A15" s="1">
         <v>1010305</v>
       </c>
-      <c r="R11" s="1">
-        <f>R7*10</f>
+      <c r="B15" s="1">
+        <v>305</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1100305</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="1">
+        <v>6</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2010305</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O15" s="1">
+        <v>999</v>
+      </c>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="1">
+        <v>1010305</v>
+      </c>
+      <c r="R15" s="1">
+        <f>R11*10</f>
         <v>0.99</v>
-      </c>
-    </row>
-    <row r="12" ht="21" customHeight="1" spans="1:18">
-      <c r="A12">
-        <v>1020001</v>
-      </c>
-      <c r="B12" s="7">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>1020001</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="s">
-        <v>55</v>
-      </c>
-      <c r="J12">
-        <v>2020001</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>56</v>
-      </c>
-      <c r="O12">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="13" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A13">
-        <v>1031001</v>
-      </c>
-      <c r="B13" s="7">
-        <v>1001</v>
-      </c>
-      <c r="C13">
-        <v>1301001</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13">
-        <v>3</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13">
-        <v>2031001</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>2</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A14">
-        <v>1031002</v>
-      </c>
-      <c r="B14" s="7">
-        <v>1002</v>
-      </c>
-      <c r="C14">
-        <v>1301002</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14">
-        <v>2031002</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>3</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A15">
-        <v>1031201</v>
-      </c>
-      <c r="B15" s="7">
-        <v>1201</v>
-      </c>
-      <c r="C15">
-        <v>1301201</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15">
-        <v>2031201</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>1002</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
       </c>
     </row>
     <row r="16" ht="23.1" customHeight="1" spans="1:18">
       <c r="A16">
-        <v>1031202</v>
+        <v>1031001</v>
       </c>
       <c r="B16" s="7">
-        <v>1202</v>
+        <v>1001</v>
       </c>
       <c r="C16">
-        <v>1301202</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
+        <v>1301001</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -2621,39 +2630,39 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J16">
-        <v>2031202</v>
+        <v>2031001</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>1003</v>
+        <v>2</v>
       </c>
       <c r="O16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="23.1" customHeight="1" spans="1:18">
+    <row r="17" ht="23.1" customHeight="1" spans="1:15">
       <c r="A17">
-        <v>1031350</v>
+        <v>1031002</v>
       </c>
       <c r="B17" s="7">
-        <v>1350</v>
+        <v>1002</v>
       </c>
       <c r="C17">
-        <v>101801</v>
-      </c>
-      <c r="D17" t="s">
-        <v>65</v>
+        <v>1301002</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -2662,39 +2671,39 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J17">
-        <v>201801</v>
+        <v>2031002</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
-      <c r="M17" s="2">
-        <v>1005</v>
+      <c r="M17">
+        <v>3</v>
       </c>
       <c r="O17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="23.1" customHeight="1" spans="1:18">
+    <row r="18" ht="23.1" customHeight="1" spans="1:15">
       <c r="A18">
-        <v>1031351</v>
+        <v>1031201</v>
       </c>
       <c r="B18" s="7">
-        <v>1351</v>
+        <v>1201</v>
       </c>
       <c r="C18">
-        <v>101802</v>
+        <v>1301201</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2703,285 +2712,285 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J18">
+        <v>2031201</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1002</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="23.1" customHeight="1" spans="1:15">
+      <c r="A19">
+        <v>1031202</v>
+      </c>
+      <c r="B19" s="7">
+        <v>1202</v>
+      </c>
+      <c r="C19">
+        <v>1301202</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19">
+        <v>2031202</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1003</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="23.1" customHeight="1" spans="1:15">
+      <c r="A20">
+        <v>1031350</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1350</v>
+      </c>
+      <c r="C20">
+        <v>101801</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>74</v>
+      </c>
+      <c r="J20">
+        <v>201801</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <v>1005</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="23.1" customHeight="1" spans="1:15">
+      <c r="A21">
+        <v>1031351</v>
+      </c>
+      <c r="B21" s="7">
+        <v>1351</v>
+      </c>
+      <c r="C21">
+        <v>101802</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>76</v>
+      </c>
+      <c r="J21">
         <v>201802</v>
       </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2">
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
         <v>1006</v>
       </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A19">
+      <c r="O21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="23.1" customHeight="1" spans="1:15">
+      <c r="A22">
         <v>1021401</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B22" s="7">
         <v>1401</v>
       </c>
-      <c r="C19">
+      <c r="C22">
         <v>1201401</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19">
+      <c r="D22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22">
         <v>2</v>
       </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>70</v>
-      </c>
-      <c r="J19">
+      <c r="F22" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J22">
         <v>2021401</v>
       </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="M19">
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>2002</v>
       </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A20">
+      <c r="O22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="23.1" customHeight="1" spans="1:15">
+      <c r="A23">
         <v>1021402</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B23" s="7">
         <v>1402</v>
       </c>
-      <c r="C20">
+      <c r="C23">
         <v>1201402</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20">
+      <c r="D23" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23">
         <v>2</v>
       </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20">
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23">
         <v>2021402</v>
       </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M20">
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>2003</v>
       </c>
-      <c r="O20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A21" s="2">
+      <c r="O23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="23.1" customHeight="1" spans="1:15">
+      <c r="A24" s="2">
         <v>1031600</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B24" s="10">
         <v>1600</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C24" s="2">
         <v>103001</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="D24" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="2">
         <v>3</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" t="s">
-        <v>73</v>
-      </c>
-      <c r="J21" s="2">
+      <c r="F24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>81</v>
+      </c>
+      <c r="J24" s="2">
         <v>2031600</v>
       </c>
-      <c r="K21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="2">
+      <c r="K24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2">
         <v>3001</v>
       </c>
-      <c r="O21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A22">
+      <c r="O24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="23.1" customHeight="1" spans="1:15">
+      <c r="A25">
         <v>1031601</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B25" s="7">
         <v>1601</v>
       </c>
-      <c r="C22">
+      <c r="C25">
         <v>103002</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22" t="s">
-        <v>75</v>
-      </c>
-      <c r="J22">
-        <v>2031601</v>
-      </c>
-      <c r="K22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>3002</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A23">
-        <v>1031602</v>
-      </c>
-      <c r="B23" s="7">
-        <v>1602</v>
-      </c>
-      <c r="C23">
-        <v>103003</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23">
-        <v>3</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23" t="s">
-        <v>77</v>
-      </c>
-      <c r="J23">
-        <v>2031602</v>
-      </c>
-      <c r="K23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23">
-        <v>3003</v>
-      </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A24">
-        <v>1031801</v>
-      </c>
-      <c r="B24" s="7">
-        <v>1801</v>
-      </c>
-      <c r="C24">
-        <v>104002</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24">
-        <v>3</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24" t="s">
-        <v>79</v>
-      </c>
-      <c r="J24">
-        <v>2031801</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>4002</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="23.1" customHeight="1" spans="1:18">
-      <c r="A25">
-        <v>1031802</v>
-      </c>
-      <c r="B25" s="7">
-        <v>1802</v>
-      </c>
-      <c r="C25">
-        <v>104003</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>80</v>
+      <c r="D25" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2990,39 +2999,39 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J25">
-        <v>2031802</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
+        <v>2031601</v>
+      </c>
+      <c r="K25" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>4003</v>
+        <v>3002</v>
       </c>
       <c r="O25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="23.1" customHeight="1" spans="1:18">
+    <row r="26" ht="23.1" customHeight="1" spans="1:15">
       <c r="A26">
-        <v>1032001</v>
+        <v>1031602</v>
       </c>
       <c r="B26" s="7">
-        <v>2001</v>
+        <v>1602</v>
       </c>
       <c r="C26">
-        <v>105002</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>82</v>
+        <v>103003</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3031,39 +3040,39 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J26">
-        <v>2032001</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
+        <v>2031602</v>
+      </c>
+      <c r="K26" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="M26">
-        <v>5002</v>
+        <v>3003</v>
       </c>
       <c r="O26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="23.1" customHeight="1" spans="1:18">
+    <row r="27" ht="23.1" customHeight="1" spans="1:15">
       <c r="A27">
-        <v>1032002</v>
+        <v>1031801</v>
       </c>
       <c r="B27" s="7">
-        <v>2002</v>
+        <v>1801</v>
       </c>
       <c r="C27">
-        <v>105003</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>84</v>
+        <v>104002</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3072,39 +3081,39 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J27">
-        <v>2032002</v>
+        <v>2031801</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>5003</v>
+        <v>4002</v>
       </c>
       <c r="O27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="23.1" customHeight="1" spans="1:18">
+    <row r="28" ht="23.1" customHeight="1" spans="1:15">
       <c r="A28">
-        <v>1032201</v>
+        <v>1031802</v>
       </c>
       <c r="B28" s="7">
-        <v>2201</v>
+        <v>1802</v>
       </c>
       <c r="C28">
-        <v>106002</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>86</v>
+        <v>104003</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3113,39 +3122,39 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J28">
-        <v>2032201</v>
+        <v>2031802</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
       </c>
       <c r="M28">
-        <v>6002</v>
+        <v>4003</v>
       </c>
       <c r="O28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="23.1" customHeight="1" spans="1:18">
+    <row r="29" ht="23.1" customHeight="1" spans="1:15">
       <c r="A29">
-        <v>1032202</v>
+        <v>1032001</v>
       </c>
       <c r="B29" s="7">
-        <v>2202</v>
+        <v>2001</v>
       </c>
       <c r="C29">
-        <v>106003</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>88</v>
+        <v>105002</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3154,151 +3163,142 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J29">
-        <v>2032202</v>
+        <v>2032001</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>6003</v>
+        <v>5002</v>
       </c>
       <c r="O29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1" spans="1:18">
+    <row r="30" ht="23.1" customHeight="1" spans="1:15">
       <c r="A30">
-        <v>1022501</v>
-      </c>
-      <c r="B30">
-        <v>2501</v>
+        <v>1032002</v>
+      </c>
+      <c r="B30" s="7">
+        <v>2002</v>
       </c>
       <c r="C30">
-        <v>1202501</v>
-      </c>
-      <c r="D30" t="s">
-        <v>90</v>
+        <v>105003</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>92</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J30">
-        <v>2022501</v>
+        <v>2032002</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
-      <c r="L30" t="s">
-        <v>92</v>
+      <c r="M30">
+        <v>5003</v>
       </c>
       <c r="O30">
-        <v>999</v>
-      </c>
-      <c r="R30">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="23.1" customHeight="1" spans="1:15">
       <c r="A31">
-        <v>1022502</v>
-      </c>
-      <c r="B31">
-        <v>2502</v>
+        <v>1032201</v>
+      </c>
+      <c r="B31" s="7">
+        <v>2201</v>
       </c>
       <c r="C31">
-        <v>1202502</v>
-      </c>
-      <c r="D31" t="s">
-        <v>93</v>
+        <v>106002</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>94</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J31">
-        <v>2022502</v>
+        <v>2032201</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
       </c>
-      <c r="L31" t="s">
-        <v>95</v>
+      <c r="M31">
+        <v>6002</v>
       </c>
       <c r="O31">
-        <v>999</v>
-      </c>
-      <c r="R31">
-        <v>0.495</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="23.1" customHeight="1" spans="1:15">
       <c r="A32">
-        <v>1022503</v>
-      </c>
-      <c r="B32">
-        <v>2503</v>
+        <v>1032202</v>
+      </c>
+      <c r="B32" s="7">
+        <v>2202</v>
       </c>
       <c r="C32">
-        <v>1202503</v>
-      </c>
-      <c r="D32" t="s">
+        <v>106003</v>
+      </c>
+      <c r="D32" s="15" t="s">
         <v>96</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="s">
         <v>97</v>
       </c>
       <c r="J32">
-        <v>2022503</v>
+        <v>2032202</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
       </c>
-      <c r="L32" t="s">
-        <v>95</v>
+      <c r="M32">
+        <v>6003</v>
       </c>
       <c r="O32">
-        <v>999</v>
-      </c>
-      <c r="R32">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:18">
@@ -3318,7 +3318,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3357,7 +3357,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -3399,7 +3399,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -3441,7 +3441,7 @@
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -3483,7 +3483,7 @@
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -3525,7 +3525,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G38">
         <v>6</v>
@@ -3567,7 +3567,7 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -3609,7 +3609,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -3651,7 +3651,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -3693,7 +3693,7 @@
         <v>2</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G42">
         <v>5</v>
@@ -3735,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G43">
         <v>6</v>
@@ -3777,7 +3777,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -3819,7 +3819,7 @@
         <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G45">
         <v>3</v>
@@ -3861,7 +3861,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -3903,7 +3903,7 @@
         <v>2</v>
       </c>
       <c r="F47" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G47">
         <v>5</v>
@@ -3945,7 +3945,7 @@
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -3987,7 +3987,7 @@
         <v>2</v>
       </c>
       <c r="F49" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -4029,7 +4029,7 @@
         <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G50">
         <v>3</v>
@@ -4071,7 +4071,7 @@
         <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G51">
         <v>4</v>
@@ -4113,7 +4113,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -4155,7 +4155,7 @@
         <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G53">
         <v>6</v>
@@ -4197,7 +4197,7 @@
         <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -4239,7 +4239,7 @@
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -4281,7 +4281,7 @@
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G56">
         <v>4</v>
@@ -4323,7 +4323,7 @@
         <v>2</v>
       </c>
       <c r="F57" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G57">
         <v>5</v>
@@ -4365,7 +4365,7 @@
         <v>2</v>
       </c>
       <c r="F58" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G58">
         <v>6</v>

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -2269,7 +2269,7 @@
         <v>999</v>
       </c>
       <c r="R8">
-        <v>0.003</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:18">
@@ -2313,7 +2313,7 @@
         <v>999</v>
       </c>
       <c r="R9">
-        <v>0.495</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:18">

--- a/table/resources/sample/Item.xlsx
+++ b/table/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -2269,7 +2269,7 @@
         <v>999</v>
       </c>
       <c r="R8">
-        <v>0.05</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:18">
@@ -2313,7 +2313,7 @@
         <v>999</v>
       </c>
       <c r="R9">
-        <v>0.99</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:18">
